--- a/data/IWB.MI.xlsx
+++ b/data/IWB.MI.xlsx
@@ -38,40 +38,40 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84661674499512</t>
+    <t xml:space="preserve">7.84661626815796</t>
   </si>
   <si>
     <t xml:space="preserve">IWB.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7986741065979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83063650131226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74274015426636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75073003768921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.710777759552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6947979927063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59092140197754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51101732254028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31125593185425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44709253311157</t>
+    <t xml:space="preserve">7.79867458343506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8306360244751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74274110794067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75072908401489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71077871322632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69479656219482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59092235565186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51101779937744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31125688552856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44709300994873</t>
   </si>
   <si>
     <t xml:space="preserve">7.35120868682861</t>
@@ -80,70 +80,70 @@
     <t xml:space="preserve">7.29527521133423</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26331472396851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29927062988281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29128122329712</t>
+    <t xml:space="preserve">7.26331377029419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29927110671997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29128074645996</t>
   </si>
   <si>
     <t xml:space="preserve">7.27130460739136</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24733304977417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37518119812012</t>
+    <t xml:space="preserve">7.24733352661133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3751802444458</t>
   </si>
   <si>
     <t xml:space="preserve">7.43111324310303</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47106552124023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15144681930542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41513299942017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32723712921143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28728532791138</t>
+    <t xml:space="preserve">7.47106504440308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15144824981689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41513252258301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32723808288574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28728628158569</t>
   </si>
   <si>
     <t xml:space="preserve">6.99163913726807</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11149597167969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1914005279541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25532245635986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41912794113159</t>
+    <t xml:space="preserve">7.11149454116821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19140100479126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2553243637085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41912841796875</t>
   </si>
   <si>
     <t xml:space="preserve">7.42312240600586</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63087511062622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67082691192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49903297424316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58293294906616</t>
+    <t xml:space="preserve">7.6308741569519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67082643508911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49903249740601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58293056488037</t>
   </si>
   <si>
     <t xml:space="preserve">7.89455938339233</t>
@@ -152,226 +152,226 @@
     <t xml:space="preserve">7.98644924163818</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91054010391235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54297924041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82264566421509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64285945892334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62288379669189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77470254898071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76671171188354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79068374633789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87058877944946</t>
+    <t xml:space="preserve">7.9105396270752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54297971725464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82264518737793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64285898208618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62288475036621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77470302581787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7667121887207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79068231582642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87058734893799</t>
   </si>
   <si>
     <t xml:space="preserve">7.9664740562439</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71876955032349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66283655166626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57094717025757</t>
+    <t xml:space="preserve">7.71876859664917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66283702850342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57094621658325</t>
   </si>
   <si>
     <t xml:space="preserve">7.55896043777466</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39116096496582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46307516098022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60690450668335</t>
+    <t xml:space="preserve">7.39116048812866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46307563781738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60690402984619</t>
   </si>
   <si>
     <t xml:space="preserve">7.54697513580322</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36718940734863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31525182723999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33123350143433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34721374511719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50302648544312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24333763122559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2233624458313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.239342212677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45908117294312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46707105636597</t>
+    <t xml:space="preserve">7.36719036102295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31525230407715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33123254776001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34721231460571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50302696228027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2433385848999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22336149215698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23934268951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4590802192688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46707057952881</t>
   </si>
   <si>
     <t xml:space="preserve">7.10350608825684</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89974927902222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91173505783081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95168590545654</t>
+    <t xml:space="preserve">6.89974880218506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91173410415649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9516863822937</t>
   </si>
   <si>
     <t xml:space="preserve">7.00762033462524</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87178325653076</t>
+    <t xml:space="preserve">6.8717827796936</t>
   </si>
   <si>
     <t xml:space="preserve">6.87577724456787</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87977170944214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86778736114502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75192594528198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7439341545105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82383918762207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6640305519104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83182954788208</t>
+    <t xml:space="preserve">6.87977313995361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86778688430786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75192499160767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74393510818481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82384014129639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66403102874756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83183002471924</t>
   </si>
   <si>
     <t xml:space="preserve">6.89575386047363</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03159046173096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07154369354248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33522796630859</t>
+    <t xml:space="preserve">7.03159141540527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07154321670532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33522844314575</t>
   </si>
   <si>
     <t xml:space="preserve">7.25931930541992</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17941379547119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26730823516846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23135232925415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09551477432251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18340969085693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1874041557312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2073802947998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14345741271973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12348127365112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23534774780273</t>
+    <t xml:space="preserve">7.17941427230835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26730966567993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23135185241699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09551429748535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18340921401978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18740558624268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20738172531128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14345788955688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12348222732544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23534727096558</t>
   </si>
   <si>
     <t xml:space="preserve">7.74673652648926</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83463001251221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98245477676392</t>
+    <t xml:space="preserve">7.83463096618652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98245525360107</t>
   </si>
   <si>
     <t xml:space="preserve">7.92652177810669</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78269147872925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63886547088623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73475027084351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07034969329834</t>
+    <t xml:space="preserve">7.78269338607788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63886404037476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73474979400635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07034873962402</t>
   </si>
   <si>
     <t xml:space="preserve">8.21417617797852</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16623497009277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18221378326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27011013031006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57374668121338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54977512359619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35001373291016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46987152099609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.525803565979</t>
+    <t xml:space="preserve">8.16623687744141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18221473693848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27011108398438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5737476348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54977607727051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35001277923584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46987056732178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52580451965332</t>
   </si>
   <si>
     <t xml:space="preserve">8.50982189178467</t>
@@ -380,124 +380,124 @@
     <t xml:space="preserve">8.59771823883057</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60571098327637</t>
+    <t xml:space="preserve">8.60570907592773</t>
   </si>
   <si>
     <t xml:space="preserve">8.58173847198486</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64687347412109</t>
+    <t xml:space="preserve">8.64687538146973</t>
   </si>
   <si>
     <t xml:space="preserve">8.67129898071289</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61430644989014</t>
+    <t xml:space="preserve">8.61430549621582</t>
   </si>
   <si>
     <t xml:space="preserve">8.63059043884277</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75272083282471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82600021362305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87485027313232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95627307891846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74458026885986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85856914520264</t>
+    <t xml:space="preserve">8.75272178649902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82599830627441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87485122680664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95627117156982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74457740783691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85856819152832</t>
   </si>
   <si>
     <t xml:space="preserve">8.84228324890137</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91556358337402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03769302368164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00512504577637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9481315612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99698352813721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1272554397583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19239234924316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11911201477051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14353847503662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98069858551025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13539791107178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16796588897705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15982341766357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18425178527832</t>
+    <t xml:space="preserve">8.91556167602539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03769397735596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00512599945068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94812870025635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99698257446289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12725734710693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19239139556885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11911392211914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14354038238525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98069763183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13539695739746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16796684265137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15982532501221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18424987792969</t>
   </si>
   <si>
     <t xml:space="preserve">9.15168285369873</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07026195526123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9644136428833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92370510101318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80157279968262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79343032836914</t>
+    <t xml:space="preserve">9.07026290893555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96441459655762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92370414733887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80157375335693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79343223571777</t>
   </si>
   <si>
     <t xml:space="preserve">8.8667106628418</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90741920471191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89113616943359</t>
+    <t xml:space="preserve">8.90742111206055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89113712310791</t>
   </si>
   <si>
     <t xml:space="preserve">9.11097145080566</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20053291320801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28195476531982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35523509979248</t>
+    <t xml:space="preserve">9.20053482055664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28195381164551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35523414611816</t>
   </si>
   <si>
     <t xml:space="preserve">9.39594554901123</t>
@@ -506,58 +506,58 @@
     <t xml:space="preserve">9.32266521453857</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64834880828857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60763740539551</t>
+    <t xml:space="preserve">9.64834785461426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60763835906982</t>
   </si>
   <si>
     <t xml:space="preserve">9.90075206756592</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99031448364258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1205883026123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1368703842163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1775817871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1043033599854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1531572341919</t>
+    <t xml:space="preserve">9.99031543731689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.120587348938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1368713378906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1775827407837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.104305267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1531553268433</t>
   </si>
   <si>
     <t xml:space="preserve">10.0961618423462</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94146251678467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90889453887939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77047920227051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83561515808105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91703605651855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7949047088623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77862071990967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78676414489746</t>
+    <t xml:space="preserve">9.94146156311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90889263153076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77047824859619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83561706542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91703701019287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79490566253662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77862167358398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78676319122314</t>
   </si>
   <si>
     <t xml:space="preserve">9.9577465057373</t>
@@ -572,7 +572,7 @@
     <t xml:space="preserve">9.88446807861328</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86004257202148</t>
+    <t xml:space="preserve">9.86004066467285</t>
   </si>
   <si>
     <t xml:space="preserve">9.85189914703369</t>
@@ -581,31 +581,31 @@
     <t xml:space="preserve">9.89260959625244</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2590017318726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3404226303101</t>
+    <t xml:space="preserve">10.2590045928955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3404245376587</t>
   </si>
   <si>
     <t xml:space="preserve">10.4625549316406</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5276899337769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5765438079834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5439767837524</t>
+    <t xml:space="preserve">10.5276937484741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5765419006348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5439748764038</t>
   </si>
   <si>
     <t xml:space="preserve">10.535834312439</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5032653808594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5521183013916</t>
+    <t xml:space="preserve">10.5032634735107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5521192550659</t>
   </si>
   <si>
     <t xml:space="preserve">10.3485651016235</t>
@@ -614,106 +614,106 @@
     <t xml:space="preserve">10.4381284713745</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3241386413574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3811340332031</t>
+    <t xml:space="preserve">10.3241395950317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3811349868774</t>
   </si>
   <si>
     <t xml:space="preserve">10.3648490905762</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4218444824219</t>
+    <t xml:space="preserve">10.4218435287476</t>
   </si>
   <si>
     <t xml:space="preserve">10.4137020111084</t>
   </si>
   <si>
-    <t xml:space="preserve">10.372992515564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.389274597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2915716171265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.267144203186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2264347076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1938676834106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3159952163696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2182922363281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2834310531616</t>
+    <t xml:space="preserve">10.372989654541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3892755508423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2915725708008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2671451568604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2264337539673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1938667297363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3159990310669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2182912826538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.283429145813</t>
   </si>
   <si>
     <t xml:space="preserve">10.429986000061</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3322820663452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2427196502686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5846853256226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6661062240601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7068176269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7475280761719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7882356643677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6253957748413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8696575164795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8289470672607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0324993133545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2360496520996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4396018981934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6838645935059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0732069015503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9917879104614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1546287536621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3174715042114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2767601013184</t>
+    <t xml:space="preserve">10.3322811126709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2427206039429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5846843719482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6661071777344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7068157196045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7475271224976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7882375717163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6253967285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8696565628052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8289489746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0325002670288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2360515594482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4396028518677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6838636398315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0732088088989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9917888641357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1546316146851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3174705505371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2767610549927</t>
   </si>
   <si>
     <t xml:space="preserve">11.1953401565552</t>
@@ -722,154 +722,160 @@
     <t xml:space="preserve">11.3581819534302</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4839172363281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5258293151855</t>
+    <t xml:space="preserve">11.4839181900024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5258302688599</t>
   </si>
   <si>
     <t xml:space="preserve">11.5677433013916</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4000949859619</t>
+    <t xml:space="preserve">11.4000930786133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0228834152222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1486215591431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2324447631836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1905336380005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.274356842041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8971471786499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0647983551025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3581829071045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4420070648193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8552360534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6875886917114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.325475692749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2822484970093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1957941055298</t>
   </si>
   <si>
     <t xml:space="preserve">11.0228853225708</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1486215591431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2324438095093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1905345916748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2743587493896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8971490859985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0647974014282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.442006111145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8552370071411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6875877380371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.325475692749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.282247543335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1957931518555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2390213012695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1525659561157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9364290237427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0661106109619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.109338760376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9796581268311</t>
+    <t xml:space="preserve">11.2390193939209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1525640487671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9364309310913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0661125183105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1093397140503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9796590805054</t>
   </si>
   <si>
     <t xml:space="preserve">10.7635221481323</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5906143188477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8499774932861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7202978134155</t>
+    <t xml:space="preserve">10.5906162261963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8499765396118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7202959060669</t>
   </si>
   <si>
     <t xml:space="preserve">10.6770677566528</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8067493438721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8932056427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6338424682617</t>
+    <t xml:space="preserve">10.8067502975464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8932046890259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6338415145874</t>
   </si>
   <si>
     <t xml:space="preserve">11.4119281768799</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4551563262939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3687019348145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5416107177734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6280641555786</t>
+    <t xml:space="preserve">11.4551544189453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3687000274658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5416088104248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6280632019043</t>
   </si>
   <si>
     <t xml:space="preserve">11.5848350524902</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4609336853027</t>
+    <t xml:space="preserve">10.4609346389771</t>
   </si>
   <si>
     <t xml:space="preserve">10.3312530517578</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3744792938232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2880249023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5041608810425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0286636352539</t>
+    <t xml:space="preserve">10.3744783401489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2880277633667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5041618347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0286626815796</t>
   </si>
   <si>
     <t xml:space="preserve">9.94220924377441</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59639453887939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63961982727051</t>
+    <t xml:space="preserve">9.59639549255371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63962078094482</t>
   </si>
   <si>
     <t xml:space="preserve">9.81252956390381</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85575485229492</t>
+    <t xml:space="preserve">9.85575580596924</t>
   </si>
   <si>
     <t xml:space="preserve">9.55316734313965</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03444385528564</t>
+    <t xml:space="preserve">9.03444194793701</t>
   </si>
   <si>
     <t xml:space="preserve">8.81830787658691</t>
@@ -878,61 +884,61 @@
     <t xml:space="preserve">8.86153602600098</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77508163452148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07767105102539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1641263961792</t>
+    <t xml:space="preserve">8.77508068084717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07767009735107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16412353515625</t>
   </si>
   <si>
     <t xml:space="preserve">9.25057697296143</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33703231811523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29380512237549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2448015213013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6828498840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1583452224731</t>
+    <t xml:space="preserve">9.33703327178955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2938060760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.244800567627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68284797668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1583442687988</t>
   </si>
   <si>
     <t xml:space="preserve">9.98543834686279</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8989839553833</t>
+    <t xml:space="preserve">9.89898300170898</t>
   </si>
   <si>
     <t xml:space="preserve">9.76930236816406</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72607421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46671199798584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50994110107422</t>
+    <t xml:space="preserve">9.72607517242432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46671295166016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50993919372559</t>
   </si>
   <si>
     <t xml:space="preserve">9.38025951385498</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42348670959473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.207350730896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.071891784668</t>
+    <t xml:space="preserve">9.42348575592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20734977722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0718898773193</t>
   </si>
   <si>
     <t xml:space="preserve">10.2972888946533</t>
@@ -944,19 +950,19 @@
     <t xml:space="preserve">10.1629772186279</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3420600891113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4316024780273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3868312835693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1182060241699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2525186538696</t>
+    <t xml:space="preserve">10.342059135437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.431601524353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.386833190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1182069778442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2525196075439</t>
   </si>
   <si>
     <t xml:space="preserve">10.4763717651367</t>
@@ -965,67 +971,64 @@
     <t xml:space="preserve">10.6554546356201</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7897682189941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7449970245361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5659151077271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7002267837524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1031656265259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9688510894775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9240818023682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8793087005615</t>
+    <t xml:space="preserve">10.7897691726685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7449979782104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5659160614014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7002248764038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1031637191772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9688520431519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9240808486938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8793096542358</t>
   </si>
   <si>
     <t xml:space="preserve">11.1479339599609</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2822484970093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2374773025513</t>
+    <t xml:space="preserve">11.237476348877</t>
   </si>
   <si>
     <t xml:space="preserve">11.4613304138184</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3270168304443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1927051544189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3717889785767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4165601730347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0583934783936</t>
+    <t xml:space="preserve">11.327018737793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1927061080933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3717880249023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4165592193604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0583944320679</t>
   </si>
   <si>
     <t xml:space="preserve">11.6404142379761</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7299566268921</t>
+    <t xml:space="preserve">11.7299575805664</t>
   </si>
   <si>
     <t xml:space="preserve">11.6851844787598</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7747268676758</t>
+    <t xml:space="preserve">11.7747259140015</t>
   </si>
   <si>
     <t xml:space="preserve">11.8194961547852</t>
@@ -1040,10 +1043,10 @@
     <t xml:space="preserve">11.5956439971924</t>
   </si>
   <si>
-    <t xml:space="preserve">10.521143913269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0136222839355</t>
+    <t xml:space="preserve">10.5211429595947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0136213302612</t>
   </si>
   <si>
     <t xml:space="preserve">10.8345394134521</t>
@@ -1052,10 +1055,10 @@
     <t xml:space="preserve">11.9985799789429</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0881223678589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0433521270752</t>
+    <t xml:space="preserve">12.0881233215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0433502197266</t>
   </si>
   <si>
     <t xml:space="preserve">12.1328926086426</t>
@@ -1067,13 +1070,13 @@
     <t xml:space="preserve">12.1776647567749</t>
   </si>
   <si>
-    <t xml:space="preserve">12.356746673584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2672061920166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.401517868042</t>
+    <t xml:space="preserve">12.3567485809326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2672052383423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4015197753906</t>
   </si>
   <si>
     <t xml:space="preserve">12.311975479126</t>
@@ -1082,58 +1085,55 @@
     <t xml:space="preserve">12.6701431274414</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6253728866577</t>
+    <t xml:space="preserve">12.625373840332</t>
   </si>
   <si>
     <t xml:space="preserve">12.5806016921997</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6106872558594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6257266998291</t>
+    <t xml:space="preserve">10.6106853485107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62572574615479</t>
   </si>
   <si>
     <t xml:space="preserve">10.0734348297119</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0286655426025</t>
-  </si>
-  <si>
     <t xml:space="preserve">12.4910593032837</t>
   </si>
   <si>
     <t xml:space="preserve">11.9090394973755</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1626214981079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6998720169067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8789567947388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0132665634155</t>
+    <t xml:space="preserve">13.1626224517822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6998729705811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8789548873901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0132684707642</t>
   </si>
   <si>
     <t xml:space="preserve">14.1475801467896</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2371215820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1923532485962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9237270355225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9684963226318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7894134521484</t>
+    <t xml:space="preserve">14.2371206283569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1923513412476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9237251281738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9684982299805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7894124984741</t>
   </si>
   <si>
     <t xml:space="preserve">14.2818918228149</t>
@@ -1148,30 +1148,27 @@
     <t xml:space="preserve">13.4312467575073</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5655584335327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.610330581665</t>
+    <t xml:space="preserve">13.565559387207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6103296279907</t>
   </si>
   <si>
     <t xml:space="preserve">13.7004642486572</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7905988693237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8356657028198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6553974151611</t>
+    <t xml:space="preserve">13.7906007766724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8356666564941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6553964614868</t>
   </si>
   <si>
     <t xml:space="preserve">13.5201950073242</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6103315353394</t>
-  </si>
-  <si>
     <t xml:space="preserve">13.2948579788208</t>
   </si>
   <si>
@@ -1181,22 +1178,22 @@
     <t xml:space="preserve">13.069522857666</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9793863296509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.708984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5737819671631</t>
+    <t xml:space="preserve">12.9793882369995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7089834213257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5737810134888</t>
   </si>
   <si>
     <t xml:space="preserve">12.6188488006592</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3399267196655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1145906448364</t>
+    <t xml:space="preserve">13.3399257659912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1145896911621</t>
   </si>
   <si>
     <t xml:space="preserve">13.4751281738281</t>
@@ -1208,7 +1205,7 @@
     <t xml:space="preserve">12.7540502548218</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8441848754883</t>
+    <t xml:space="preserve">12.8441867828369</t>
   </si>
   <si>
     <t xml:space="preserve">14.0610027313232</t>
@@ -1220,7 +1217,7 @@
     <t xml:space="preserve">14.1962041854858</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3314065933228</t>
+    <t xml:space="preserve">14.3314056396484</t>
   </si>
   <si>
     <t xml:space="preserve">14.4215421676636</t>
@@ -1229,7 +1226,7 @@
     <t xml:space="preserve">14.3764734268188</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5116758346558</t>
+    <t xml:space="preserve">14.5116767883301</t>
   </si>
   <si>
     <t xml:space="preserve">14.4666090011597</t>
@@ -1238,58 +1235,58 @@
     <t xml:space="preserve">14.6018114089966</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6919441223145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8722143173218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2327518463135</t>
+    <t xml:space="preserve">14.6919450759888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8722133636475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2327547073364</t>
   </si>
   <si>
     <t xml:space="preserve">15.0074167251587</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3228883743286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1876859664917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2242336273193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9538297653198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8551750183105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3143672943115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9903774261475</t>
+    <t xml:space="preserve">15.3228874206543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1876888275146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2242317199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9538307189941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8551769256592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3143692016602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9903793334961</t>
   </si>
   <si>
     <t xml:space="preserve">16.8101100921631</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7565250396729</t>
+    <t xml:space="preserve">17.7565231323242</t>
   </si>
   <si>
     <t xml:space="preserve">18.026927947998</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9367923736572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3509178161621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4410514831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4861221313477</t>
+    <t xml:space="preserve">17.9367942810059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3509159088135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4410533905029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.486120223999</t>
   </si>
   <si>
     <t xml:space="preserve">17.0354442596436</t>
@@ -1298,13 +1295,13 @@
     <t xml:space="preserve">16.6298408508301</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7199745178223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.404504776001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6749057769775</t>
+    <t xml:space="preserve">16.7199726104736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4045085906982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6749095916748</t>
   </si>
   <si>
     <t xml:space="preserve">16.9453105926514</t>
@@ -1313,79 +1310,79 @@
     <t xml:space="preserve">16.765043258667</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8636960983276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9988985061646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4946365356445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3594360351562</t>
+    <t xml:space="preserve">15.863697052002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9988965988159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4946384429932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3594341278076</t>
   </si>
   <si>
     <t xml:space="preserve">16.1791667938232</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5847702026367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5397071838379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6834259033203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0890350341797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5932922363281</t>
+    <t xml:space="preserve">16.5847721099854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5397052764893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6834268569946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0890312194824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5932912826538</t>
   </si>
   <si>
     <t xml:space="preserve">16.2693004608154</t>
   </si>
   <si>
-    <t xml:space="preserve">17.125581741333</t>
+    <t xml:space="preserve">17.1255779266357</t>
   </si>
   <si>
     <t xml:space="preserve">17.5762519836426</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6663875579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8466567993164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5677394866943</t>
+    <t xml:space="preserve">17.666389465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8466548919678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5677318572998</t>
   </si>
   <si>
     <t xml:space="preserve">18.3874664306641</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7480010986328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3789443969727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0098896026611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5506954193115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.460563659668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2802925109863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3704261779785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1000213623047</t>
+    <t xml:space="preserve">18.7480030059814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3789482116699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0098876953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5506935119629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4605617523193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.280294418335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3704280853271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1000232696533</t>
   </si>
   <si>
     <t xml:space="preserve">20.6408309936523</t>
@@ -1400,16 +1397,19 @@
     <t xml:space="preserve">21.9027137756348</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5361423492432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1695690155029</t>
+    <t xml:space="preserve">21.5361442565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9027156829834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1695728302002</t>
   </si>
   <si>
     <t xml:space="preserve">21.7194309234619</t>
   </si>
   <si>
-    <t xml:space="preserve">22.360933303833</t>
+    <t xml:space="preserve">22.3609313964844</t>
   </si>
   <si>
     <t xml:space="preserve">22.4525737762451</t>
@@ -1418,7 +1418,7 @@
     <t xml:space="preserve">22.269287109375</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0860004425049</t>
+    <t xml:space="preserve">22.0860042572021</t>
   </si>
   <si>
     <t xml:space="preserve">21.9943599700928</t>
@@ -1430,16 +1430,16 @@
     <t xml:space="preserve">23.2773628234863</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9107894897461</t>
+    <t xml:space="preserve">22.9107913970947</t>
   </si>
   <si>
     <t xml:space="preserve">22.727502822876</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1776466369629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6358623504639</t>
+    <t xml:space="preserve">22.1776447296143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6358642578125</t>
   </si>
   <si>
     <t xml:space="preserve">23.0024337768555</t>
@@ -1448,16 +1448,16 @@
     <t xml:space="preserve">23.0940780639648</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1021499633789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.285436630249</t>
+    <t xml:space="preserve">24.1021537780762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2854385375977</t>
   </si>
   <si>
     <t xml:space="preserve">24.9269428253174</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2099456787109</t>
+    <t xml:space="preserve">26.2099437713623</t>
   </si>
   <si>
     <t xml:space="preserve">26.8514461517334</t>
@@ -1466,31 +1466,31 @@
     <t xml:space="preserve">26.6681613922119</t>
   </si>
   <si>
-    <t xml:space="preserve">27.309663772583</t>
+    <t xml:space="preserve">27.3096618652344</t>
   </si>
   <si>
     <t xml:space="preserve">26.4848747253418</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7598056793213</t>
+    <t xml:space="preserve">26.7598037719727</t>
   </si>
   <si>
     <t xml:space="preserve">26.5765190124512</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3015899658203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5684432983398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0347309112549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1425247192383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4093799591064</t>
+    <t xml:space="preserve">26.3015880584717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5684413909912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0347328186035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1425228118896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4093818664551</t>
   </si>
   <si>
     <t xml:space="preserve">28.1344509124756</t>
@@ -1505,19 +1505,19 @@
     <t xml:space="preserve">28.4570770263672</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0875034332275</t>
+    <t xml:space="preserve">28.0875053405762</t>
   </si>
   <si>
     <t xml:space="preserve">27.9951114654541</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9027214050293</t>
+    <t xml:space="preserve">27.9027194976807</t>
   </si>
   <si>
     <t xml:space="preserve">27.7179317474365</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1038303375244</t>
+    <t xml:space="preserve">29.1038284301758</t>
   </si>
   <si>
     <t xml:space="preserve">29.9353694915771</t>
@@ -1526,19 +1526,19 @@
     <t xml:space="preserve">29.750581741333</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3810081481934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8266525268555</t>
+    <t xml:space="preserve">29.3810062408447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8266506195068</t>
   </si>
   <si>
     <t xml:space="preserve">28.9190444946289</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7342567443848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0114364624023</t>
+    <t xml:space="preserve">28.7342548370361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0114345550537</t>
   </si>
   <si>
     <t xml:space="preserve">29.8429718017578</t>
@@ -1547,28 +1547,28 @@
     <t xml:space="preserve">30.1201515197754</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2125453948975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0277633666992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3973331451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1364765167236</t>
+    <t xml:space="preserve">30.2125492095947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0277614593506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3973369598389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1364822387695</t>
   </si>
   <si>
     <t xml:space="preserve">30.859302520752</t>
   </si>
   <si>
-    <t xml:space="preserve">31.0440807342529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6745128631592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4897270202637</t>
+    <t xml:space="preserve">31.0440845489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6745109558105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4897232055664</t>
   </si>
   <si>
     <t xml:space="preserve">29.2886161804199</t>
@@ -1577,37 +1577,37 @@
     <t xml:space="preserve">29.4734001159668</t>
   </si>
   <si>
-    <t xml:space="preserve">32.8919448852539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.3539123535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.5550193786621</t>
+    <t xml:space="preserve">32.8919486999512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.3539085388184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.5550231933594</t>
   </si>
   <si>
     <t xml:space="preserve">34.0930595397949</t>
   </si>
   <si>
-    <t xml:space="preserve">35.8485298156738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.4192047119141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.0986137390137</t>
+    <t xml:space="preserve">35.8485260009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.4192085266113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.0986099243164</t>
   </si>
   <si>
     <t xml:space="preserve">37.2344207763672</t>
   </si>
   <si>
-    <t xml:space="preserve">37.881175994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.1583518981934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.6039924621582</t>
+    <t xml:space="preserve">37.8811721801758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.1583557128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.6039962768555</t>
   </si>
   <si>
     <t xml:space="preserve">37.6963882446289</t>
@@ -1616,31 +1616,31 @@
     <t xml:space="preserve">37.7887840270996</t>
   </si>
   <si>
-    <t xml:space="preserve">37.142032623291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.5279273986816</t>
+    <t xml:space="preserve">37.1420288085938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.5279312133789</t>
   </si>
   <si>
     <t xml:space="preserve">38.3431396484375</t>
   </si>
   <si>
-    <t xml:space="preserve">36.4952812194824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.9409217834473</t>
+    <t xml:space="preserve">36.4952774047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.9409255981445</t>
   </si>
   <si>
     <t xml:space="preserve">36.4028854370117</t>
   </si>
   <si>
-    <t xml:space="preserve">36.6800727844238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.9735679626465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.0659599304199</t>
+    <t xml:space="preserve">36.6800651550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.9735641479492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.0659561157227</t>
   </si>
   <si>
     <t xml:space="preserve">38.4355316162109</t>
@@ -1649,10 +1649,10 @@
     <t xml:space="preserve">38.8051071166992</t>
   </si>
   <si>
-    <t xml:space="preserve">39.3594665527344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.8214263916016</t>
+    <t xml:space="preserve">39.3594627380371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.8214302062988</t>
   </si>
   <si>
     <t xml:space="preserve">40.006217956543</t>
@@ -1661,13 +1661,13 @@
     <t xml:space="preserve">40.5605773925781</t>
   </si>
   <si>
-    <t xml:space="preserve">40.6529693603516</t>
+    <t xml:space="preserve">40.6529655456543</t>
   </si>
   <si>
     <t xml:space="preserve">41.9464721679688</t>
   </si>
   <si>
-    <t xml:space="preserve">41.114933013916</t>
+    <t xml:space="preserve">41.1149368286133</t>
   </si>
   <si>
     <t xml:space="preserve">40.9301452636719</t>
@@ -1679,19 +1679,19 @@
     <t xml:space="preserve">43.5171508789062</t>
   </si>
   <si>
-    <t xml:space="preserve">44.0715141296387</t>
+    <t xml:space="preserve">44.0715103149414</t>
   </si>
   <si>
     <t xml:space="preserve">43.8867263793945</t>
   </si>
   <si>
-    <t xml:space="preserve">43.7019424438477</t>
+    <t xml:space="preserve">43.7019386291504</t>
   </si>
   <si>
     <t xml:space="preserve">43.979118347168</t>
   </si>
   <si>
-    <t xml:space="preserve">44.348690032959</t>
+    <t xml:space="preserve">44.3486938476562</t>
   </si>
   <si>
     <t xml:space="preserve">44.9954452514648</t>
@@ -1700,7 +1700,7 @@
     <t xml:space="preserve">44.8106575012207</t>
   </si>
   <si>
-    <t xml:space="preserve">44.5334777832031</t>
+    <t xml:space="preserve">44.5334815979004</t>
   </si>
   <si>
     <t xml:space="preserve">43.7943344116211</t>
@@ -1709,10 +1709,10 @@
     <t xml:space="preserve">43.1475791931152</t>
   </si>
   <si>
-    <t xml:space="preserve">41.3921127319336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.854076385498</t>
+    <t xml:space="preserve">41.3921089172363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.8540802001953</t>
   </si>
   <si>
     <t xml:space="preserve">41.5769004821777</t>
@@ -1721,10 +1721,10 @@
     <t xml:space="preserve">41.2073249816895</t>
   </si>
   <si>
-    <t xml:space="preserve">40.1910057067871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.4518585205078</t>
+    <t xml:space="preserve">40.1910018920898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.4518547058105</t>
   </si>
   <si>
     <t xml:space="preserve">38.9898910522461</t>
@@ -1745,7 +1745,7 @@
     <t xml:space="preserve">39.7290382385254</t>
   </si>
   <si>
-    <t xml:space="preserve">39.9138221740723</t>
+    <t xml:space="preserve">39.9138259887695</t>
   </si>
   <si>
     <t xml:space="preserve">40.4681816101074</t>
@@ -1760,7 +1760,7 @@
     <t xml:space="preserve">39.2670745849609</t>
   </si>
   <si>
-    <t xml:space="preserve">37.3268203735352</t>
+    <t xml:space="preserve">37.3268165588379</t>
   </si>
   <si>
     <t xml:space="preserve">38.8974952697754</t>
@@ -1769,25 +1769,25 @@
     <t xml:space="preserve">37.511604309082</t>
   </si>
   <si>
-    <t xml:space="preserve">38.7127151489258</t>
+    <t xml:space="preserve">38.712718963623</t>
   </si>
   <si>
     <t xml:space="preserve">39.0822830200195</t>
   </si>
   <si>
-    <t xml:space="preserve">36.7724533081055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.310489654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.2180976867676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.3865585327148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.0333137512207</t>
+    <t xml:space="preserve">36.7724609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.3104858398438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.2181015014648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.3865661621094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.0333099365234</t>
   </si>
   <si>
     <t xml:space="preserve">34.1854553222656</t>
@@ -1796,28 +1796,28 @@
     <t xml:space="preserve">33.7234840393066</t>
   </si>
   <si>
-    <t xml:space="preserve">33.1691284179688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6147651672363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.6310920715332</t>
+    <t xml:space="preserve">33.1691246032715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6147689819336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6310997009277</t>
   </si>
   <si>
     <t xml:space="preserve">32.707160949707</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9680137634277</t>
+    <t xml:space="preserve">31.9680156707764</t>
   </si>
   <si>
     <t xml:space="preserve">32.0604095458984</t>
   </si>
   <si>
-    <t xml:space="preserve">31.4136600494385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6908378601074</t>
+    <t xml:space="preserve">31.4136562347412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6908340454102</t>
   </si>
   <si>
     <t xml:space="preserve">32.2451972961426</t>
@@ -1826,34 +1826,34 @@
     <t xml:space="preserve">32.7995529174805</t>
   </si>
   <si>
-    <t xml:space="preserve">33.9082679748535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.1093826293945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.739803314209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.0169944763184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3375930786133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4299812316895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5223731994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5060482025146</t>
+    <t xml:space="preserve">33.9082717895508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.1093788146973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7398071289062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.0169868469238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.337589263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4299850463867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5223770141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.506046295166</t>
   </si>
   <si>
     <t xml:space="preserve">31.3212661743164</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5522441864014</t>
+    <t xml:space="preserve">31.5522518157959</t>
   </si>
   <si>
     <t xml:space="preserve">31.9218196868896</t>
@@ -1862,82 +1862,82 @@
     <t xml:space="preserve">32.1528015136719</t>
   </si>
   <si>
-    <t xml:space="preserve">33.4925003051758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.3702354431152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8620758056641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1066055297852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5359230041504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3511352539062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7804527282715</t>
+    <t xml:space="preserve">33.492504119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.3702392578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8620719909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1066017150879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.535924911499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3511371612549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7804546356201</t>
   </si>
   <si>
     <t xml:space="preserve">28.3643836975098</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3180351257324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8082180023193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7618713378906</t>
+    <t xml:space="preserve">28.3180332183838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8082160949707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7618732452393</t>
   </si>
   <si>
     <t xml:space="preserve">28.0862998962402</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9936084747314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.642463684082</t>
+    <t xml:space="preserve">27.9936065673828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6424655914307</t>
   </si>
   <si>
     <t xml:space="preserve">29.5230579376221</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1255722045898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5694046020508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.105936050415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9009132385254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7155227661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1130123138428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4641551971436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4178085327148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.186071395874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6031970977783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2324199676514</t>
+    <t xml:space="preserve">30.1255683898926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5694065093994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1059341430664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.900915145874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7155246734619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1130142211914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4641532897949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4178066253662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1860733032227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6031951904297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2324180603027</t>
   </si>
   <si>
     <t xml:space="preserve">26.556848526001</t>
@@ -1955,10 +1955,10 @@
     <t xml:space="preserve">25.2591304779053</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7029685974121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6566200256348</t>
+    <t xml:space="preserve">24.7029666900635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6566219329834</t>
   </si>
   <si>
     <t xml:space="preserve">23.9614143371582</t>
@@ -1973,22 +1973,22 @@
     <t xml:space="preserve">24.7956619262695</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2858448028564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6102733612061</t>
+    <t xml:space="preserve">24.2858467102051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6102714538574</t>
   </si>
   <si>
     <t xml:space="preserve">24.3321914672852</t>
   </si>
   <si>
-    <t xml:space="preserve">24.517578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3785381317139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4712333679199</t>
+    <t xml:space="preserve">24.5175800323486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3785362243652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4712314605713</t>
   </si>
   <si>
     <t xml:space="preserve">23.8687210083008</t>
@@ -2009,22 +2009,22 @@
     <t xml:space="preserve">23.9150676727295</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1931495666504</t>
+    <t xml:space="preserve">24.193151473999</t>
   </si>
   <si>
     <t xml:space="preserve">24.888355255127</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5835609436035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9543361663818</t>
+    <t xml:space="preserve">25.5835628509521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9543380737305</t>
   </si>
   <si>
     <t xml:space="preserve">26.6958885192871</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7885837554932</t>
+    <t xml:space="preserve">26.7885818481445</t>
   </si>
   <si>
     <t xml:space="preserve">26.7422370910645</t>
@@ -2039,16 +2039,16 @@
     <t xml:space="preserve">25.8616428375244</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1200923919678</t>
+    <t xml:space="preserve">25.1200904846191</t>
   </si>
   <si>
     <t xml:space="preserve">24.0077610015869</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4515972137451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1271686553955</t>
+    <t xml:space="preserve">23.4515953063965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1271705627441</t>
   </si>
   <si>
     <t xml:space="preserve">23.0808200836182</t>
@@ -2069,28 +2069,28 @@
     <t xml:space="preserve">23.2662105560303</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3589057922363</t>
+    <t xml:space="preserve">23.3589038848877</t>
   </si>
   <si>
     <t xml:space="preserve">22.8027381896973</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6173534393311</t>
+    <t xml:space="preserve">22.6173515319824</t>
   </si>
   <si>
     <t xml:space="preserve">23.1735153198242</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8954334259033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9684925079346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5513687133789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2732887268066</t>
+    <t xml:space="preserve">22.895435333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9684944152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5513706207275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.273286819458</t>
   </si>
   <si>
     <t xml:space="preserve">20.856164932251</t>
@@ -2105,82 +2105,82 @@
     <t xml:space="preserve">20.1609592437744</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2073020935059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8365287780762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5584468841553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.604793548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9292240142822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.068265914917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1146125793457</t>
+    <t xml:space="preserve">20.2073040008545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8365306854248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5584487915039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6047916412354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9292221069336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0682640075684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1146106719971</t>
   </si>
   <si>
     <t xml:space="preserve">20.8098182678223</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9952030181885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5780811309814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0878982543945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5977172851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.061185836792</t>
+    <t xml:space="preserve">20.9952049255371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5780830383301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0879001617432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5977153778076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0611839294434</t>
   </si>
   <si>
     <t xml:space="preserve">22.4319629669189</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3856143951416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3392677307129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6833324432373</t>
+    <t xml:space="preserve">22.3856163024902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3392696380615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6833343505859</t>
   </si>
   <si>
     <t xml:space="preserve">24.5639266967773</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4248847961426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1664390563965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2127838134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.842004776001</t>
+    <t xml:space="preserve">24.4248867034912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1664371490479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2127857208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8420085906982</t>
   </si>
   <si>
     <t xml:space="preserve">25.7689476013184</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7226009368896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3518257141113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5372142791748</t>
+    <t xml:space="preserve">25.7226028442383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.35182762146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5372123718262</t>
   </si>
   <si>
     <t xml:space="preserve">25.305477142334</t>
@@ -2189,13 +2189,13 @@
     <t xml:space="preserve">25.6762542724609</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4908695220947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6691799163818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2057075500488</t>
+    <t xml:space="preserve">25.4908657073975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6691780090332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2057056427002</t>
   </si>
   <si>
     <t xml:space="preserve">27.4837894439697</t>
@@ -2204,37 +2204,37 @@
     <t xml:space="preserve">27.2984027862549</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5764846801758</t>
+    <t xml:space="preserve">27.5764827728271</t>
   </si>
   <si>
     <t xml:space="preserve">28.0399551391602</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1789932250977</t>
+    <t xml:space="preserve">28.1789951324463</t>
   </si>
   <si>
     <t xml:space="preserve">28.2716884613037</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1326484680176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4374408721924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5301361083984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.093376159668</t>
+    <t xml:space="preserve">28.1326465606689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.437442779541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5301380157471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0933780670166</t>
   </si>
   <si>
     <t xml:space="preserve">25.39817237854</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9417819976807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2002296447754</t>
+    <t xml:space="preserve">22.941780090332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2002277374268</t>
   </si>
   <si>
     <t xml:space="preserve">22.153881072998</t>
@@ -2246,64 +2246,64 @@
     <t xml:space="preserve">22.7100448608398</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9881267547607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2198600769043</t>
+    <t xml:space="preserve">22.9881248474121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2198619842529</t>
   </si>
   <si>
     <t xml:space="preserve">21.8294506072998</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6244277954102</t>
+    <t xml:space="preserve">20.6244297027588</t>
   </si>
   <si>
     <t xml:space="preserve">20.6707744598389</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4853897094727</t>
+    <t xml:space="preserve">20.485387802124</t>
   </si>
   <si>
     <t xml:space="preserve">20.2536525726318</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5317344665527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1342449188232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7831058502197</t>
+    <t xml:space="preserve">20.5317325592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1342430114746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7831039428711</t>
   </si>
   <si>
     <t xml:space="preserve">21.6440620422363</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2269401550293</t>
+    <t xml:space="preserve">21.2269420623779</t>
   </si>
   <si>
     <t xml:space="preserve">21.3196334838867</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8757972717285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1805953979492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9025115966797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6679420471191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4127311706543</t>
+    <t xml:space="preserve">21.8757991790771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1805934906006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9025096893311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6679439544678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4127330780029</t>
   </si>
   <si>
     <t xml:space="preserve">20.6213912963867</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5748443603516</t>
+    <t xml:space="preserve">20.5748424530029</t>
   </si>
   <si>
     <t xml:space="preserve">20.3886451721191</t>
@@ -2312,7 +2312,7 @@
     <t xml:space="preserve">21.3661842346191</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9937877655029</t>
+    <t xml:space="preserve">20.9937858581543</t>
   </si>
   <si>
     <t xml:space="preserve">20.9006900787354</t>
@@ -2321,22 +2321,22 @@
     <t xml:space="preserve">21.0403366088867</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1799850463867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2265338897705</t>
+    <t xml:space="preserve">21.1799869537354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2265319824219</t>
   </si>
   <si>
     <t xml:space="preserve">20.9472389221191</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4817447662354</t>
+    <t xml:space="preserve">20.4817428588867</t>
   </si>
   <si>
     <t xml:space="preserve">20.3420963287354</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2489986419678</t>
+    <t xml:space="preserve">20.2489967346191</t>
   </si>
   <si>
     <t xml:space="preserve">20.1558990478516</t>
@@ -2348,7 +2348,7 @@
     <t xml:space="preserve">19.6904029846191</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6438541412354</t>
+    <t xml:space="preserve">19.643856048584</t>
   </si>
   <si>
     <t xml:space="preserve">19.7835025787354</t>
@@ -2369,25 +2369,25 @@
     <t xml:space="preserve">19.3180084228516</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5507564544678</t>
+    <t xml:space="preserve">19.5507545471191</t>
   </si>
   <si>
     <t xml:space="preserve">20.2024478912354</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4351959228516</t>
+    <t xml:space="preserve">20.4351978302002</t>
   </si>
   <si>
     <t xml:space="preserve">19.4576568603516</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0387134552002</t>
+    <t xml:space="preserve">19.0387115478516</t>
   </si>
   <si>
     <t xml:space="preserve">19.9696998596191</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9231510162354</t>
+    <t xml:space="preserve">19.923152923584</t>
   </si>
   <si>
     <t xml:space="preserve">19.3645572662354</t>
@@ -2402,10 +2402,10 @@
     <t xml:space="preserve">19.1318111419678</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6197662353516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8525123596191</t>
+    <t xml:space="preserve">18.6197681427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8525142669678</t>
   </si>
   <si>
     <t xml:space="preserve">18.7128677368164</t>
@@ -2423,7 +2423,7 @@
     <t xml:space="preserve">18.4708099365234</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3963317871094</t>
+    <t xml:space="preserve">18.3963298797607</t>
   </si>
   <si>
     <t xml:space="preserve">18.3404712677002</t>
@@ -2432,10 +2432,10 @@
     <t xml:space="preserve">18.2287540435791</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2101306915283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.968074798584</t>
+    <t xml:space="preserve">18.210132598877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9680767059326</t>
   </si>
   <si>
     <t xml:space="preserve">17.6701583862305</t>
@@ -2465,16 +2465,16 @@
     <t xml:space="preserve">17.2232856750488</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3350028991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.409481048584</t>
+    <t xml:space="preserve">17.3350048065186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4094829559326</t>
   </si>
   <si>
     <t xml:space="preserve">17.6515369415283</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7260189056396</t>
+    <t xml:space="preserve">17.7260208129883</t>
   </si>
   <si>
     <t xml:space="preserve">17.7073993682861</t>
@@ -2495,13 +2495,13 @@
     <t xml:space="preserve">16.5529727935791</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0929470062256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9253673553467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2736759185791</t>
+    <t xml:space="preserve">17.092945098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9253692626953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2736778259277</t>
   </si>
   <si>
     <t xml:space="preserve">16.0130004882812</t>
@@ -2510,16 +2510,16 @@
     <t xml:space="preserve">15.9757604598999</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2364387512207</t>
+    <t xml:space="preserve">16.2364368438721</t>
   </si>
   <si>
     <t xml:space="preserve">16.2922973632812</t>
   </si>
   <si>
-    <t xml:space="preserve">17.037088394165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.813648223877</t>
+    <t xml:space="preserve">17.0370864868164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8136501312256</t>
   </si>
   <si>
     <t xml:space="preserve">16.404016494751</t>
@@ -2543,7 +2543,7 @@
     <t xml:space="preserve">15.7709436416626</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7337017059326</t>
+    <t xml:space="preserve">15.7337036132812</t>
   </si>
   <si>
     <t xml:space="preserve">15.8826608657837</t>
@@ -2567,10 +2567,10 @@
     <t xml:space="preserve">16.8695106506348</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1115665435791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0184669494629</t>
+    <t xml:space="preserve">17.1115646362305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0184688568115</t>
   </si>
   <si>
     <t xml:space="preserve">17.0557060241699</t>
@@ -2582,16 +2582,16 @@
     <t xml:space="preserve">17.3536224365234</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3722438812256</t>
+    <t xml:space="preserve">17.372241973877</t>
   </si>
   <si>
     <t xml:space="preserve">16.9998474121094</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0743255615234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6833114624023</t>
+    <t xml:space="preserve">17.0743274688721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.683313369751</t>
   </si>
   <si>
     <t xml:space="preserve">16.8881282806396</t>
@@ -2600,10 +2600,10 @@
     <t xml:space="preserve">16.6646919250488</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7205505371094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8322696685791</t>
+    <t xml:space="preserve">16.7205486297607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8322677612305</t>
   </si>
   <si>
     <t xml:space="preserve">16.7391700744629</t>
@@ -2612,7 +2612,7 @@
     <t xml:space="preserve">16.5902118682861</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3481559753418</t>
+    <t xml:space="preserve">16.3481540679932</t>
   </si>
   <si>
     <t xml:space="preserve">16.3109169006348</t>
@@ -2624,7 +2624,7 @@
     <t xml:space="preserve">16.6088333129883</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0502376556396</t>
+    <t xml:space="preserve">16.0502395629883</t>
   </si>
   <si>
     <t xml:space="preserve">16.2550563812256</t>
@@ -2636,10 +2636,10 @@
     <t xml:space="preserve">17.1674251556396</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0053157806396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9122161865234</t>
+    <t xml:space="preserve">18.005313873291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9122142791748</t>
   </si>
   <si>
     <t xml:space="preserve">17.4653434753418</t>
@@ -2657,13 +2657,13 @@
     <t xml:space="preserve">17.5491313934326</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3629341125488</t>
+    <t xml:space="preserve">17.3629322052002</t>
   </si>
   <si>
     <t xml:space="preserve">17.5025787353516</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4560317993164</t>
+    <t xml:space="preserve">17.456033706665</t>
   </si>
   <si>
     <t xml:space="preserve">18.1542739868164</t>
@@ -19181,7 +19181,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G610" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -19233,7 +19233,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G612" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -19285,7 +19285,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G614" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -19311,7 +19311,7 @@
         <v>12.75</v>
       </c>
       <c r="G615" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -19337,7 +19337,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G616" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -19389,7 +19389,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G618" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -19415,7 +19415,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G619" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -19441,7 +19441,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G620" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -19467,7 +19467,7 @@
         <v>12.75</v>
       </c>
       <c r="G621" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -19493,7 +19493,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G622" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -19519,7 +19519,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G623" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -19545,7 +19545,7 @@
         <v>13</v>
       </c>
       <c r="G624" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -19571,7 +19571,7 @@
         <v>13</v>
       </c>
       <c r="G625" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -19597,7 +19597,7 @@
         <v>12.75</v>
       </c>
       <c r="G626" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -19623,7 +19623,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G627" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="H627" t="s">
         <v>9</v>
@@ -19649,7 +19649,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G628" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H628" t="s">
         <v>9</v>
@@ -19675,7 +19675,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G629" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="H629" t="s">
         <v>9</v>
@@ -19701,7 +19701,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G630" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="H630" t="s">
         <v>9</v>
@@ -19727,7 +19727,7 @@
         <v>12.75</v>
       </c>
       <c r="G631" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="H631" t="s">
         <v>9</v>
@@ -19753,7 +19753,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G632" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="H632" t="s">
         <v>9</v>
@@ -19779,7 +19779,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G633" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="H633" t="s">
         <v>9</v>
@@ -19805,7 +19805,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G634" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="H634" t="s">
         <v>9</v>
@@ -19831,7 +19831,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G635" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="H635" t="s">
         <v>9</v>
@@ -19857,7 +19857,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G636" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="H636" t="s">
         <v>9</v>
@@ -19883,7 +19883,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G637" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="H637" t="s">
         <v>9</v>
@@ -19909,7 +19909,7 @@
         <v>12.25</v>
       </c>
       <c r="G638" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="H638" t="s">
         <v>9</v>
@@ -19935,7 +19935,7 @@
         <v>12.25</v>
       </c>
       <c r="G639" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="H639" t="s">
         <v>9</v>
@@ -19961,7 +19961,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G640" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="H640" t="s">
         <v>9</v>
@@ -19987,7 +19987,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G641" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="H641" t="s">
         <v>9</v>
@@ -20013,7 +20013,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G642" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="H642" t="s">
         <v>9</v>
@@ -20039,7 +20039,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G643" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="H643" t="s">
         <v>9</v>
@@ -20065,7 +20065,7 @@
         <v>12.5</v>
       </c>
       <c r="G644" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="H644" t="s">
         <v>9</v>
@@ -20091,7 +20091,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G645" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="H645" t="s">
         <v>9</v>
@@ -20117,7 +20117,7 @@
         <v>12.5</v>
       </c>
       <c r="G646" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="H646" t="s">
         <v>9</v>
@@ -20143,7 +20143,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G647" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="H647" t="s">
         <v>9</v>
@@ -20169,7 +20169,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G648" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="H648" t="s">
         <v>9</v>
@@ -20195,7 +20195,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G649" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="H649" t="s">
         <v>9</v>
@@ -20221,7 +20221,7 @@
         <v>12.5</v>
       </c>
       <c r="G650" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="H650" t="s">
         <v>9</v>
@@ -20247,7 +20247,7 @@
         <v>12.5</v>
       </c>
       <c r="G651" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="H651" t="s">
         <v>9</v>
@@ -20273,7 +20273,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G652" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="H652" t="s">
         <v>9</v>
@@ -20299,7 +20299,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G653" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="H653" t="s">
         <v>9</v>
@@ -20325,7 +20325,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G654" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="H654" t="s">
         <v>9</v>
@@ -20351,7 +20351,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G655" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="H655" t="s">
         <v>9</v>
@@ -20377,7 +20377,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G656" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H656" t="s">
         <v>9</v>
@@ -20403,7 +20403,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G657" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H657" t="s">
         <v>9</v>
@@ -20429,7 +20429,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G658" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="H658" t="s">
         <v>9</v>
@@ -20455,7 +20455,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G659" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="H659" t="s">
         <v>9</v>
@@ -20481,7 +20481,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G660" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="H660" t="s">
         <v>9</v>
@@ -20507,7 +20507,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G661" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="H661" t="s">
         <v>9</v>
@@ -20533,7 +20533,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G662" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="H662" t="s">
         <v>9</v>
@@ -20559,7 +20559,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G663" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="H663" t="s">
         <v>9</v>
@@ -20585,7 +20585,7 @@
         <v>12.75</v>
       </c>
       <c r="G664" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -20611,7 +20611,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G665" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="H665" t="s">
         <v>9</v>
@@ -20637,7 +20637,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G666" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="H666" t="s">
         <v>9</v>
@@ -20663,7 +20663,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G667" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="H667" t="s">
         <v>9</v>
@@ -20689,7 +20689,7 @@
         <v>12.25</v>
       </c>
       <c r="G668" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="H668" t="s">
         <v>9</v>
@@ -20715,7 +20715,7 @@
         <v>12.25</v>
       </c>
       <c r="G669" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="H669" t="s">
         <v>9</v>
@@ -20741,7 +20741,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G670" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="H670" t="s">
         <v>9</v>
@@ -20767,7 +20767,7 @@
         <v>12.5</v>
       </c>
       <c r="G671" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="H671" t="s">
         <v>9</v>
@@ -20793,7 +20793,7 @@
         <v>12.5</v>
       </c>
       <c r="G672" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="H672" t="s">
         <v>9</v>
@@ -20819,7 +20819,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G673" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="H673" t="s">
         <v>9</v>
@@ -20845,7 +20845,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G674" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="H674" t="s">
         <v>9</v>
@@ -20871,7 +20871,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G675" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="H675" t="s">
         <v>9</v>
@@ -20897,7 +20897,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G676" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="H676" t="s">
         <v>9</v>
@@ -20923,7 +20923,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G677" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="H677" t="s">
         <v>9</v>
@@ -20949,7 +20949,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G678" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="H678" t="s">
         <v>9</v>
@@ -20975,7 +20975,7 @@
         <v>12.25</v>
       </c>
       <c r="G679" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="H679" t="s">
         <v>9</v>
@@ -21001,7 +21001,7 @@
         <v>12.25</v>
       </c>
       <c r="G680" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="H680" t="s">
         <v>9</v>
@@ -21027,7 +21027,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G681" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="H681" t="s">
         <v>9</v>
@@ -21053,7 +21053,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G682" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="H682" t="s">
         <v>9</v>
@@ -21079,7 +21079,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G683" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="H683" t="s">
         <v>9</v>
@@ -21105,7 +21105,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G684" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="H684" t="s">
         <v>9</v>
@@ -21131,7 +21131,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G685" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="H685" t="s">
         <v>9</v>
@@ -21157,7 +21157,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G686" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="H686" t="s">
         <v>9</v>
@@ -21183,7 +21183,7 @@
         <v>12.5</v>
       </c>
       <c r="G687" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="H687" t="s">
         <v>9</v>
@@ -21209,7 +21209,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G688" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="H688" t="s">
         <v>9</v>
@@ -21235,7 +21235,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G689" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="H689" t="s">
         <v>9</v>
@@ -21261,7 +21261,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G690" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="H690" t="s">
         <v>9</v>
@@ -21287,7 +21287,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G691" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="H691" t="s">
         <v>9</v>
@@ -21313,7 +21313,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G692" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="H692" t="s">
         <v>9</v>
@@ -21339,7 +21339,7 @@
         <v>12.75</v>
       </c>
       <c r="G693" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="H693" t="s">
         <v>9</v>
@@ -21365,7 +21365,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G694" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -21391,7 +21391,7 @@
         <v>13.25</v>
       </c>
       <c r="G695" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="H695" t="s">
         <v>9</v>
@@ -21417,7 +21417,7 @@
         <v>13</v>
       </c>
       <c r="G696" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="H696" t="s">
         <v>9</v>
@@ -21443,7 +21443,7 @@
         <v>13</v>
       </c>
       <c r="G697" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="H697" t="s">
         <v>9</v>
@@ -21469,7 +21469,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G698" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="H698" t="s">
         <v>9</v>
@@ -21495,7 +21495,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G699" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H699" t="s">
         <v>9</v>
@@ -21521,7 +21521,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G700" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H700" t="s">
         <v>9</v>
@@ -21547,7 +21547,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G701" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="H701" t="s">
         <v>9</v>
@@ -21573,7 +21573,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G702" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="H702" t="s">
         <v>9</v>
@@ -21599,7 +21599,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G703" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="H703" t="s">
         <v>9</v>
@@ -21625,7 +21625,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G704" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="H704" t="s">
         <v>9</v>
@@ -21651,7 +21651,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G705" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="H705" t="s">
         <v>9</v>
@@ -21677,7 +21677,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G706" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="H706" t="s">
         <v>9</v>
@@ -21703,7 +21703,7 @@
         <v>13.25</v>
       </c>
       <c r="G707" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="H707" t="s">
         <v>9</v>
@@ -21729,7 +21729,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G708" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H708" t="s">
         <v>9</v>
@@ -21755,7 +21755,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G709" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H709" t="s">
         <v>9</v>
@@ -21781,7 +21781,7 @@
         <v>13</v>
       </c>
       <c r="G710" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="H710" t="s">
         <v>9</v>
@@ -21807,7 +21807,7 @@
         <v>13</v>
       </c>
       <c r="G711" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="H711" t="s">
         <v>9</v>
@@ -21833,7 +21833,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G712" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H712" t="s">
         <v>9</v>
@@ -21859,7 +21859,7 @@
         <v>13</v>
       </c>
       <c r="G713" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="H713" t="s">
         <v>9</v>
@@ -21885,7 +21885,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G714" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="H714" t="s">
         <v>9</v>
@@ -21911,7 +21911,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G715" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H715" t="s">
         <v>9</v>
@@ -21937,7 +21937,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G716" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="H716" t="s">
         <v>9</v>
@@ -21963,7 +21963,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G717" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="H717" t="s">
         <v>9</v>
@@ -21989,7 +21989,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G718" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="H718" t="s">
         <v>9</v>
@@ -22015,7 +22015,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G719" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="H719" t="s">
         <v>9</v>
@@ -22041,7 +22041,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G720" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="H720" t="s">
         <v>9</v>
@@ -22067,7 +22067,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G721" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="H721" t="s">
         <v>9</v>
@@ -22093,7 +22093,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G722" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="H722" t="s">
         <v>9</v>
@@ -22119,7 +22119,7 @@
         <v>12.5</v>
       </c>
       <c r="G723" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="H723" t="s">
         <v>9</v>
@@ -22145,7 +22145,7 @@
         <v>13</v>
       </c>
       <c r="G724" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="H724" t="s">
         <v>9</v>
@@ -22171,7 +22171,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G725" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="H725" t="s">
         <v>9</v>
@@ -22197,7 +22197,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G726" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="H726" t="s">
         <v>9</v>
@@ -22223,7 +22223,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G727" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="H727" t="s">
         <v>9</v>
@@ -22249,7 +22249,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G728" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="H728" t="s">
         <v>9</v>
@@ -22275,7 +22275,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G729" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="H729" t="s">
         <v>9</v>
@@ -22301,7 +22301,7 @@
         <v>12.5</v>
       </c>
       <c r="G730" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="H730" t="s">
         <v>9</v>
@@ -22327,7 +22327,7 @@
         <v>12.25</v>
       </c>
       <c r="G731" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="H731" t="s">
         <v>9</v>
@@ -22353,7 +22353,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G732" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H732" t="s">
         <v>9</v>
@@ -22379,7 +22379,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G733" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="H733" t="s">
         <v>9</v>
@@ -22405,7 +22405,7 @@
         <v>12</v>
       </c>
       <c r="G734" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="H734" t="s">
         <v>9</v>
@@ -22431,7 +22431,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G735" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="H735" t="s">
         <v>9</v>
@@ -22457,7 +22457,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G736" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="H736" t="s">
         <v>9</v>
@@ -22483,7 +22483,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G737" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="H737" t="s">
         <v>9</v>
@@ -22509,7 +22509,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G738" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="H738" t="s">
         <v>9</v>
@@ -22535,7 +22535,7 @@
         <v>11.5</v>
       </c>
       <c r="G739" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="H739" t="s">
         <v>9</v>
@@ -22561,7 +22561,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G740" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="H740" t="s">
         <v>9</v>
@@ -22587,7 +22587,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G741" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="H741" t="s">
         <v>9</v>
@@ -22613,7 +22613,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G742" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="H742" t="s">
         <v>9</v>
@@ -22639,7 +22639,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G743" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="H743" t="s">
         <v>9</v>
@@ -22665,7 +22665,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G744" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="H744" t="s">
         <v>9</v>
@@ -22691,7 +22691,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G745" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="H745" t="s">
         <v>9</v>
@@ -22717,7 +22717,7 @@
         <v>11.5</v>
       </c>
       <c r="G746" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="H746" t="s">
         <v>9</v>
@@ -22743,7 +22743,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G747" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="H747" t="s">
         <v>9</v>
@@ -22769,7 +22769,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G748" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="H748" t="s">
         <v>9</v>
@@ -22795,7 +22795,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G749" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="H749" t="s">
         <v>9</v>
@@ -22821,7 +22821,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G750" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="H750" t="s">
         <v>9</v>
@@ -22847,7 +22847,7 @@
         <v>10.25</v>
       </c>
       <c r="G751" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="H751" t="s">
         <v>9</v>
@@ -22873,7 +22873,7 @@
         <v>10.25</v>
       </c>
       <c r="G752" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="H752" t="s">
         <v>9</v>
@@ -22899,7 +22899,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G753" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="H753" t="s">
         <v>9</v>
@@ -22925,7 +22925,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G754" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="H754" t="s">
         <v>9</v>
@@ -22951,7 +22951,7 @@
         <v>10.5</v>
       </c>
       <c r="G755" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="H755" t="s">
         <v>9</v>
@@ -22977,7 +22977,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G756" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="H756" t="s">
         <v>9</v>
@@ -23003,7 +23003,7 @@
         <v>10.5</v>
       </c>
       <c r="G757" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="H757" t="s">
         <v>9</v>
@@ -23029,7 +23029,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G758" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="H758" t="s">
         <v>9</v>
@@ -23055,7 +23055,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G759" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="H759" t="s">
         <v>9</v>
@@ -23081,7 +23081,7 @@
         <v>10.75</v>
       </c>
       <c r="G760" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="H760" t="s">
         <v>9</v>
@@ -23107,7 +23107,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G761" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="H761" t="s">
         <v>9</v>
@@ -23133,7 +23133,7 @@
         <v>11.5</v>
       </c>
       <c r="G762" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="H762" t="s">
         <v>9</v>
@@ -23159,7 +23159,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G763" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="H763" t="s">
         <v>9</v>
@@ -23185,7 +23185,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G764" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="H764" t="s">
         <v>9</v>
@@ -23211,7 +23211,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G765" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="H765" t="s">
         <v>9</v>
@@ -23237,7 +23237,7 @@
         <v>11.5</v>
       </c>
       <c r="G766" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="H766" t="s">
         <v>9</v>
@@ -23263,7 +23263,7 @@
         <v>11.5</v>
       </c>
       <c r="G767" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="H767" t="s">
         <v>9</v>
@@ -23289,7 +23289,7 @@
         <v>11.75</v>
       </c>
       <c r="G768" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="H768" t="s">
         <v>9</v>
@@ -23315,7 +23315,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G769" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="H769" t="s">
         <v>9</v>
@@ -23341,7 +23341,7 @@
         <v>12</v>
       </c>
       <c r="G770" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="H770" t="s">
         <v>9</v>
@@ -23367,7 +23367,7 @@
         <v>11.75</v>
       </c>
       <c r="G771" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="H771" t="s">
         <v>9</v>
@@ -23393,7 +23393,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G772" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="H772" t="s">
         <v>9</v>
@@ -23419,7 +23419,7 @@
         <v>11.5</v>
       </c>
       <c r="G773" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="H773" t="s">
         <v>9</v>
@@ -23445,7 +23445,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G774" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="H774" t="s">
         <v>9</v>
@@ -23471,7 +23471,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G775" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="H775" t="s">
         <v>9</v>
@@ -23497,7 +23497,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G776" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="H776" t="s">
         <v>9</v>
@@ -23523,7 +23523,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G777" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="H777" t="s">
         <v>9</v>
@@ -23549,7 +23549,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G778" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="H778" t="s">
         <v>9</v>
@@ -23575,7 +23575,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G779" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="H779" t="s">
         <v>9</v>
@@ -23601,7 +23601,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G780" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="H780" t="s">
         <v>9</v>
@@ -23627,7 +23627,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G781" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="H781" t="s">
         <v>9</v>
@@ -23653,7 +23653,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G782" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="H782" t="s">
         <v>9</v>
@@ -23679,7 +23679,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G783" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="H783" t="s">
         <v>9</v>
@@ -23705,7 +23705,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G784" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="H784" t="s">
         <v>9</v>
@@ -23731,7 +23731,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G785" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="H785" t="s">
         <v>9</v>
@@ -23757,7 +23757,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G786" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="H786" t="s">
         <v>9</v>
@@ -23783,7 +23783,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G787" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="H787" t="s">
         <v>9</v>
@@ -23809,7 +23809,7 @@
         <v>11.5</v>
       </c>
       <c r="G788" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="H788" t="s">
         <v>9</v>
@@ -23835,7 +23835,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G789" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="H789" t="s">
         <v>9</v>
@@ -23861,7 +23861,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G790" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="H790" t="s">
         <v>9</v>
@@ -23887,7 +23887,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G791" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="H791" t="s">
         <v>9</v>
@@ -23913,7 +23913,7 @@
         <v>11.5</v>
       </c>
       <c r="G792" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="H792" t="s">
         <v>9</v>
@@ -23939,7 +23939,7 @@
         <v>11.25</v>
       </c>
       <c r="G793" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="H793" t="s">
         <v>9</v>
@@ -23965,7 +23965,7 @@
         <v>11.25</v>
       </c>
       <c r="G794" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="H794" t="s">
         <v>9</v>
@@ -23991,7 +23991,7 @@
         <v>11.5</v>
       </c>
       <c r="G795" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="H795" t="s">
         <v>9</v>
@@ -24017,7 +24017,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G796" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="H796" t="s">
         <v>9</v>
@@ -24043,7 +24043,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G797" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="H797" t="s">
         <v>9</v>
@@ -24069,7 +24069,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G798" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="H798" t="s">
         <v>9</v>
@@ -24095,7 +24095,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G799" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="H799" t="s">
         <v>9</v>
@@ -24121,7 +24121,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G800" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="H800" t="s">
         <v>9</v>
@@ -24147,7 +24147,7 @@
         <v>11</v>
       </c>
       <c r="G801" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="H801" t="s">
         <v>9</v>
@@ -24173,7 +24173,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G802" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="H802" t="s">
         <v>9</v>
@@ -24199,7 +24199,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G803" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="H803" t="s">
         <v>9</v>
@@ -24225,7 +24225,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G804" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="H804" t="s">
         <v>9</v>
@@ -24251,7 +24251,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G805" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="H805" t="s">
         <v>9</v>
@@ -24277,7 +24277,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G806" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="H806" t="s">
         <v>9</v>
@@ -24303,7 +24303,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G807" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="H807" t="s">
         <v>9</v>
@@ -24329,7 +24329,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G808" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="H808" t="s">
         <v>9</v>
@@ -24355,7 +24355,7 @@
         <v>11</v>
       </c>
       <c r="G809" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="H809" t="s">
         <v>9</v>
@@ -24381,7 +24381,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G810" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="H810" t="s">
         <v>9</v>
@@ -24407,7 +24407,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G811" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="H811" t="s">
         <v>9</v>
@@ -24433,7 +24433,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G812" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="H812" t="s">
         <v>9</v>
@@ -24459,7 +24459,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G813" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="H813" t="s">
         <v>9</v>
@@ -24485,7 +24485,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G814" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="H814" t="s">
         <v>9</v>
@@ -24511,7 +24511,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G815" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="H815" t="s">
         <v>9</v>
@@ -24537,7 +24537,7 @@
         <v>10.75</v>
       </c>
       <c r="G816" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="H816" t="s">
         <v>9</v>
@@ -24563,7 +24563,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G817" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="H817" t="s">
         <v>9</v>
@@ -24589,7 +24589,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G818" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="H818" t="s">
         <v>9</v>
@@ -24615,7 +24615,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G819" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="H819" t="s">
         <v>9</v>
@@ -24641,7 +24641,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G820" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="H820" t="s">
         <v>9</v>
@@ -24667,7 +24667,7 @@
         <v>11.25</v>
       </c>
       <c r="G821" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="H821" t="s">
         <v>9</v>
@@ -24693,7 +24693,7 @@
         <v>11.25</v>
       </c>
       <c r="G822" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="H822" t="s">
         <v>9</v>
@@ -24719,7 +24719,7 @@
         <v>11.25</v>
       </c>
       <c r="G823" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="H823" t="s">
         <v>9</v>
@@ -24745,7 +24745,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G824" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="H824" t="s">
         <v>9</v>
@@ -24771,7 +24771,7 @@
         <v>11.5</v>
       </c>
       <c r="G825" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="H825" t="s">
         <v>9</v>
@@ -24797,7 +24797,7 @@
         <v>11.5</v>
       </c>
       <c r="G826" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="H826" t="s">
         <v>9</v>
@@ -24823,7 +24823,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G827" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="H827" t="s">
         <v>9</v>
@@ -24849,7 +24849,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G828" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="H828" t="s">
         <v>9</v>
@@ -24875,7 +24875,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G829" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="H829" t="s">
         <v>9</v>
@@ -24901,7 +24901,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G830" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="H830" t="s">
         <v>9</v>
@@ -24927,7 +24927,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G831" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="H831" t="s">
         <v>9</v>
@@ -24953,7 +24953,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G832" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="H832" t="s">
         <v>9</v>
@@ -24979,7 +24979,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G833" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="H833" t="s">
         <v>9</v>
@@ -25005,7 +25005,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G834" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="H834" t="s">
         <v>9</v>
@@ -25031,7 +25031,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G835" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="H835" t="s">
         <v>9</v>
@@ -25057,7 +25057,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G836" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="H836" t="s">
         <v>9</v>
@@ -25083,7 +25083,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G837" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="H837" t="s">
         <v>9</v>
@@ -25109,7 +25109,7 @@
         <v>11.5</v>
       </c>
       <c r="G838" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="H838" t="s">
         <v>9</v>
@@ -25135,7 +25135,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G839" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="H839" t="s">
         <v>9</v>
@@ -25161,7 +25161,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G840" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="H840" t="s">
         <v>9</v>
@@ -25187,7 +25187,7 @@
         <v>11.5</v>
       </c>
       <c r="G841" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="H841" t="s">
         <v>9</v>
@@ -25213,7 +25213,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G842" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="H842" t="s">
         <v>9</v>
@@ -25239,7 +25239,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G843" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="H843" t="s">
         <v>9</v>
@@ -25265,7 +25265,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G844" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="H844" t="s">
         <v>9</v>
@@ -25291,7 +25291,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G845" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="H845" t="s">
         <v>9</v>
@@ -25317,7 +25317,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G846" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="H846" t="s">
         <v>9</v>
@@ -25343,7 +25343,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G847" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -25369,7 +25369,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G848" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="H848" t="s">
         <v>9</v>
@@ -25395,7 +25395,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G849" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="H849" t="s">
         <v>9</v>
@@ -25421,7 +25421,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G850" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="H850" t="s">
         <v>9</v>
@@ -25447,7 +25447,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G851" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -25473,7 +25473,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G852" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="H852" t="s">
         <v>9</v>
@@ -25499,7 +25499,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G853" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -25525,7 +25525,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G854" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="H854" t="s">
         <v>9</v>
@@ -25551,7 +25551,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G855" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -25577,7 +25577,7 @@
         <v>11.5</v>
       </c>
       <c r="G856" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -25603,7 +25603,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G857" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="H857" t="s">
         <v>9</v>
@@ -25629,7 +25629,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G858" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -25655,7 +25655,7 @@
         <v>11.5</v>
       </c>
       <c r="G859" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="H859" t="s">
         <v>9</v>
@@ -25681,7 +25681,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G860" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="H860" t="s">
         <v>9</v>
@@ -25707,7 +25707,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G861" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -25733,7 +25733,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G862" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="H862" t="s">
         <v>9</v>
@@ -25759,7 +25759,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G863" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="H863" t="s">
         <v>9</v>
@@ -25785,7 +25785,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G864" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="H864" t="s">
         <v>9</v>
@@ -25811,7 +25811,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G865" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="H865" t="s">
         <v>9</v>
@@ -25837,7 +25837,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G866" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="H866" t="s">
         <v>9</v>
@@ -25863,7 +25863,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G867" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="H867" t="s">
         <v>9</v>
@@ -25889,7 +25889,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G868" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="H868" t="s">
         <v>9</v>
@@ -25915,7 +25915,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G869" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="H869" t="s">
         <v>9</v>
@@ -25941,7 +25941,7 @@
         <v>12</v>
       </c>
       <c r="G870" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="H870" t="s">
         <v>9</v>
@@ -25967,7 +25967,7 @@
         <v>12</v>
       </c>
       <c r="G871" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="H871" t="s">
         <v>9</v>
@@ -25993,7 +25993,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G872" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="H872" t="s">
         <v>9</v>
@@ -26019,7 +26019,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G873" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="H873" t="s">
         <v>9</v>
@@ -26045,7 +26045,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G874" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="H874" t="s">
         <v>9</v>
@@ -26071,7 +26071,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G875" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="H875" t="s">
         <v>9</v>
@@ -26097,7 +26097,7 @@
         <v>12</v>
       </c>
       <c r="G876" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="H876" t="s">
         <v>9</v>
@@ -26123,7 +26123,7 @@
         <v>12</v>
       </c>
       <c r="G877" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="H877" t="s">
         <v>9</v>
@@ -26149,7 +26149,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G878" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="H878" t="s">
         <v>9</v>
@@ -26175,7 +26175,7 @@
         <v>12</v>
       </c>
       <c r="G879" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="H879" t="s">
         <v>9</v>
@@ -26201,7 +26201,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G880" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="H880" t="s">
         <v>9</v>
@@ -26227,7 +26227,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G881" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="H881" t="s">
         <v>9</v>
@@ -26253,7 +26253,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G882" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="H882" t="s">
         <v>9</v>
@@ -26279,7 +26279,7 @@
         <v>12</v>
       </c>
       <c r="G883" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="H883" t="s">
         <v>9</v>
@@ -26305,7 +26305,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G884" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="H884" t="s">
         <v>9</v>
@@ -26331,7 +26331,7 @@
         <v>12.25</v>
       </c>
       <c r="G885" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="H885" t="s">
         <v>9</v>
@@ -26357,7 +26357,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G886" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="H886" t="s">
         <v>9</v>
@@ -26383,7 +26383,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G887" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="H887" t="s">
         <v>9</v>
@@ -26409,7 +26409,7 @@
         <v>12.25</v>
       </c>
       <c r="G888" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="H888" t="s">
         <v>9</v>
@@ -26435,7 +26435,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G889" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="H889" t="s">
         <v>9</v>
@@ -26461,7 +26461,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G890" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="H890" t="s">
         <v>9</v>
@@ -26487,7 +26487,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G891" t="s">
-        <v>326</v>
+        <v>252</v>
       </c>
       <c r="H891" t="s">
         <v>9</v>
@@ -26513,7 +26513,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G892" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H892" t="s">
         <v>9</v>
@@ -26539,7 +26539,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G893" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H893" t="s">
         <v>9</v>
@@ -26565,7 +26565,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G894" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H894" t="s">
         <v>9</v>
@@ -26591,7 +26591,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G895" t="s">
-        <v>326</v>
+        <v>252</v>
       </c>
       <c r="H895" t="s">
         <v>9</v>
@@ -26617,7 +26617,7 @@
         <v>12.5</v>
       </c>
       <c r="G896" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H896" t="s">
         <v>9</v>
@@ -26643,7 +26643,7 @@
         <v>12.5</v>
       </c>
       <c r="G897" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H897" t="s">
         <v>9</v>
@@ -26669,7 +26669,7 @@
         <v>12.5</v>
       </c>
       <c r="G898" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H898" t="s">
         <v>9</v>
@@ -26695,7 +26695,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G899" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H899" t="s">
         <v>9</v>
@@ -26721,7 +26721,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G900" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H900" t="s">
         <v>9</v>
@@ -26747,7 +26747,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G901" t="s">
-        <v>326</v>
+        <v>252</v>
       </c>
       <c r="H901" t="s">
         <v>9</v>
@@ -26773,7 +26773,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G902" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H902" t="s">
         <v>9</v>
@@ -26799,7 +26799,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G903" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H903" t="s">
         <v>9</v>
@@ -26825,7 +26825,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G904" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H904" t="s">
         <v>9</v>
@@ -26851,7 +26851,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G905" t="s">
-        <v>326</v>
+        <v>252</v>
       </c>
       <c r="H905" t="s">
         <v>9</v>
@@ -26877,7 +26877,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G906" t="s">
-        <v>326</v>
+        <v>252</v>
       </c>
       <c r="H906" t="s">
         <v>9</v>
@@ -26903,7 +26903,7 @@
         <v>12.75</v>
       </c>
       <c r="G907" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H907" t="s">
         <v>9</v>
@@ -26929,7 +26929,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G908" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H908" t="s">
         <v>9</v>
@@ -26955,7 +26955,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G909" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H909" t="s">
         <v>9</v>
@@ -26981,7 +26981,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G910" t="s">
-        <v>326</v>
+        <v>252</v>
       </c>
       <c r="H910" t="s">
         <v>9</v>
@@ -27007,7 +27007,7 @@
         <v>12.5</v>
       </c>
       <c r="G911" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H911" t="s">
         <v>9</v>
@@ -27033,7 +27033,7 @@
         <v>12.5</v>
       </c>
       <c r="G912" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H912" t="s">
         <v>9</v>
@@ -27059,7 +27059,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G913" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="H913" t="s">
         <v>9</v>
@@ -27085,7 +27085,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G914" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H914" t="s">
         <v>9</v>
@@ -27111,7 +27111,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G915" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H915" t="s">
         <v>9</v>
@@ -27137,7 +27137,7 @@
         <v>12.5</v>
       </c>
       <c r="G916" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H916" t="s">
         <v>9</v>
@@ -27163,7 +27163,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G917" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H917" t="s">
         <v>9</v>
@@ -27189,7 +27189,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G918" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="H918" t="s">
         <v>9</v>
@@ -27215,7 +27215,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G919" t="s">
-        <v>326</v>
+        <v>252</v>
       </c>
       <c r="H919" t="s">
         <v>9</v>
@@ -27241,7 +27241,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G920" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H920" t="s">
         <v>9</v>
@@ -27267,7 +27267,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G921" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H921" t="s">
         <v>9</v>
@@ -27293,7 +27293,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G922" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="H922" t="s">
         <v>9</v>
@@ -27319,7 +27319,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G923" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="H923" t="s">
         <v>9</v>
@@ -27345,7 +27345,7 @@
         <v>12.5</v>
       </c>
       <c r="G924" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H924" t="s">
         <v>9</v>
@@ -27371,7 +27371,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G925" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H925" t="s">
         <v>9</v>
@@ -27397,7 +27397,7 @@
         <v>12.5</v>
       </c>
       <c r="G926" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H926" t="s">
         <v>9</v>
@@ -27423,7 +27423,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G927" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H927" t="s">
         <v>9</v>
@@ -27449,7 +27449,7 @@
         <v>12.5</v>
       </c>
       <c r="G928" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H928" t="s">
         <v>9</v>
@@ -27475,7 +27475,7 @@
         <v>12.5</v>
       </c>
       <c r="G929" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H929" t="s">
         <v>9</v>
@@ -27501,7 +27501,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G930" t="s">
-        <v>326</v>
+        <v>252</v>
       </c>
       <c r="H930" t="s">
         <v>9</v>
@@ -27527,7 +27527,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G931" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H931" t="s">
         <v>9</v>
@@ -27553,7 +27553,7 @@
         <v>13</v>
       </c>
       <c r="G932" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H932" t="s">
         <v>9</v>
@@ -27579,7 +27579,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G933" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H933" t="s">
         <v>9</v>
@@ -27605,7 +27605,7 @@
         <v>13</v>
       </c>
       <c r="G934" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H934" t="s">
         <v>9</v>
@@ -27631,7 +27631,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G935" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H935" t="s">
         <v>9</v>
@@ -27657,7 +27657,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G936" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H936" t="s">
         <v>9</v>
@@ -27683,7 +27683,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G937" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H937" t="s">
         <v>9</v>
@@ -27709,7 +27709,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G938" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H938" t="s">
         <v>9</v>
@@ -27735,7 +27735,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G939" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H939" t="s">
         <v>9</v>
@@ -27761,7 +27761,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G940" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H940" t="s">
         <v>9</v>
@@ -27787,7 +27787,7 @@
         <v>13.25</v>
       </c>
       <c r="G941" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H941" t="s">
         <v>9</v>
@@ -27813,7 +27813,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G942" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H942" t="s">
         <v>9</v>
@@ -27839,7 +27839,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G943" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H943" t="s">
         <v>9</v>
@@ -27865,7 +27865,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G944" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H944" t="s">
         <v>9</v>
@@ -27891,7 +27891,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G945" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H945" t="s">
         <v>9</v>
@@ -27917,7 +27917,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G946" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H946" t="s">
         <v>9</v>
@@ -27943,7 +27943,7 @@
         <v>12.75</v>
       </c>
       <c r="G947" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H947" t="s">
         <v>9</v>
@@ -27969,7 +27969,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G948" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H948" t="s">
         <v>9</v>
@@ -27995,7 +27995,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G949" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H949" t="s">
         <v>9</v>
@@ -28021,7 +28021,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G950" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H950" t="s">
         <v>9</v>
@@ -28047,7 +28047,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G951" t="s">
-        <v>326</v>
+        <v>252</v>
       </c>
       <c r="H951" t="s">
         <v>9</v>
@@ -28073,7 +28073,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G952" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H952" t="s">
         <v>9</v>
@@ -28099,7 +28099,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G953" t="s">
-        <v>326</v>
+        <v>252</v>
       </c>
       <c r="H953" t="s">
         <v>9</v>
@@ -28125,7 +28125,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G954" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H954" t="s">
         <v>9</v>
@@ -28151,7 +28151,7 @@
         <v>12.5</v>
       </c>
       <c r="G955" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H955" t="s">
         <v>9</v>
@@ -28177,7 +28177,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G956" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="H956" t="s">
         <v>9</v>
@@ -28203,7 +28203,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G957" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="H957" t="s">
         <v>9</v>
@@ -28229,7 +28229,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G958" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="H958" t="s">
         <v>9</v>
@@ -28255,7 +28255,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G959" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="H959" t="s">
         <v>9</v>
@@ -28281,7 +28281,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G960" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="H960" t="s">
         <v>9</v>
@@ -28307,7 +28307,7 @@
         <v>11.75</v>
       </c>
       <c r="G961" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H961" t="s">
         <v>9</v>
@@ -28333,7 +28333,7 @@
         <v>11.5</v>
       </c>
       <c r="G962" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="H962" t="s">
         <v>9</v>
@@ -28359,7 +28359,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G963" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="H963" t="s">
         <v>9</v>
@@ -28385,7 +28385,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G964" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="H964" t="s">
         <v>9</v>
@@ -28411,7 +28411,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G965" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="H965" t="s">
         <v>9</v>
@@ -28437,7 +28437,7 @@
         <v>12.25</v>
       </c>
       <c r="G966" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="H966" t="s">
         <v>9</v>
@@ -28463,7 +28463,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G967" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="H967" t="s">
         <v>9</v>
@@ -28489,7 +28489,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G968" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="H968" t="s">
         <v>9</v>
@@ -28515,7 +28515,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G969" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H969" t="s">
         <v>9</v>
@@ -28541,7 +28541,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G970" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="H970" t="s">
         <v>9</v>
@@ -28567,7 +28567,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G971" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H971" t="s">
         <v>9</v>
@@ -28593,7 +28593,7 @@
         <v>12.25</v>
       </c>
       <c r="G972" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="H972" t="s">
         <v>9</v>
@@ -28619,7 +28619,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G973" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="H973" t="s">
         <v>9</v>
@@ -28645,7 +28645,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G974" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="H974" t="s">
         <v>9</v>
@@ -28671,7 +28671,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G975" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="H975" t="s">
         <v>9</v>
@@ -28697,7 +28697,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G976" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H976" t="s">
         <v>9</v>
@@ -28723,7 +28723,7 @@
         <v>12.5</v>
       </c>
       <c r="G977" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H977" t="s">
         <v>9</v>
@@ -28749,7 +28749,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G978" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="H978" t="s">
         <v>9</v>
@@ -28775,7 +28775,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G979" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H979" t="s">
         <v>9</v>
@@ -28801,7 +28801,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G980" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="H980" t="s">
         <v>9</v>
@@ -28827,7 +28827,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G981" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H981" t="s">
         <v>9</v>
@@ -28853,7 +28853,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G982" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H982" t="s">
         <v>9</v>
@@ -28879,7 +28879,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G983" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="H983" t="s">
         <v>9</v>
@@ -28905,7 +28905,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G984" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H984" t="s">
         <v>9</v>
@@ -28931,7 +28931,7 @@
         <v>12.25</v>
       </c>
       <c r="G985" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="H985" t="s">
         <v>9</v>
@@ -28957,7 +28957,7 @@
         <v>12.25</v>
       </c>
       <c r="G986" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="H986" t="s">
         <v>9</v>
@@ -28983,7 +28983,7 @@
         <v>12.25</v>
       </c>
       <c r="G987" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="H987" t="s">
         <v>9</v>
@@ -29009,7 +29009,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G988" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="H988" t="s">
         <v>9</v>
@@ -29035,7 +29035,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G989" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="H989" t="s">
         <v>9</v>
@@ -29061,7 +29061,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G990" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="H990" t="s">
         <v>9</v>
@@ -29087,7 +29087,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G991" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="H991" t="s">
         <v>9</v>
@@ -29113,7 +29113,7 @@
         <v>11.75</v>
       </c>
       <c r="G992" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H992" t="s">
         <v>9</v>
@@ -29139,7 +29139,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G993" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="H993" t="s">
         <v>9</v>
@@ -29165,7 +29165,7 @@
         <v>12</v>
       </c>
       <c r="G994" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="H994" t="s">
         <v>9</v>
@@ -29191,7 +29191,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G995" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="H995" t="s">
         <v>9</v>
@@ -29217,7 +29217,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G996" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="H996" t="s">
         <v>9</v>
@@ -29243,7 +29243,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G997" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="H997" t="s">
         <v>9</v>
@@ -29269,7 +29269,7 @@
         <v>12.25</v>
       </c>
       <c r="G998" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="H998" t="s">
         <v>9</v>
@@ -29295,7 +29295,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G999" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H999" t="s">
         <v>9</v>
@@ -29321,7 +29321,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1000" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H1000" t="s">
         <v>9</v>
@@ -29347,7 +29347,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G1001" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="H1001" t="s">
         <v>9</v>
@@ -29373,7 +29373,7 @@
         <v>12</v>
       </c>
       <c r="G1002" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="H1002" t="s">
         <v>9</v>
@@ -29399,7 +29399,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1003" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H1003" t="s">
         <v>9</v>
@@ -29425,7 +29425,7 @@
         <v>12.25</v>
       </c>
       <c r="G1004" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="H1004" t="s">
         <v>9</v>
@@ -29451,7 +29451,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G1005" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="H1005" t="s">
         <v>9</v>
@@ -29477,7 +29477,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G1006" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="H1006" t="s">
         <v>9</v>
@@ -29503,7 +29503,7 @@
         <v>12.25</v>
       </c>
       <c r="G1007" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="H1007" t="s">
         <v>9</v>
@@ -29529,7 +29529,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G1008" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H1008" t="s">
         <v>9</v>
@@ -29555,7 +29555,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G1009" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="H1009" t="s">
         <v>9</v>
@@ -29581,7 +29581,7 @@
         <v>12.5</v>
       </c>
       <c r="G1010" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H1010" t="s">
         <v>9</v>
@@ -29607,7 +29607,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G1011" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="H1011" t="s">
         <v>9</v>
@@ -29633,7 +29633,7 @@
         <v>12.5</v>
       </c>
       <c r="G1012" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H1012" t="s">
         <v>9</v>
@@ -29659,7 +29659,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1013" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H1013" t="s">
         <v>9</v>
@@ -29685,7 +29685,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1014" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H1014" t="s">
         <v>9</v>
@@ -29711,7 +29711,7 @@
         <v>12.75</v>
       </c>
       <c r="G1015" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H1015" t="s">
         <v>9</v>
@@ -29737,7 +29737,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G1016" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H1016" t="s">
         <v>9</v>
@@ -29763,7 +29763,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1017" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H1017" t="s">
         <v>9</v>
@@ -29789,7 +29789,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1018" t="s">
-        <v>326</v>
+        <v>252</v>
       </c>
       <c r="H1018" t="s">
         <v>9</v>
@@ -29815,7 +29815,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1019" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H1019" t="s">
         <v>9</v>
@@ -29841,7 +29841,7 @@
         <v>13.25</v>
       </c>
       <c r="G1020" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H1020" t="s">
         <v>9</v>
@@ -29867,7 +29867,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1021" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H1021" t="s">
         <v>9</v>
@@ -29893,7 +29893,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G1022" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H1022" t="s">
         <v>9</v>
@@ -29919,7 +29919,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1023" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H1023" t="s">
         <v>9</v>
@@ -29945,7 +29945,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G1024" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H1024" t="s">
         <v>9</v>
@@ -29971,7 +29971,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1025" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H1025" t="s">
         <v>9</v>
@@ -29997,7 +29997,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1026" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H1026" t="s">
         <v>9</v>
@@ -30023,7 +30023,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G1027" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H1027" t="s">
         <v>9</v>
@@ -30049,7 +30049,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1028" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H1028" t="s">
         <v>9</v>
@@ -30075,7 +30075,7 @@
         <v>13.5</v>
       </c>
       <c r="G1029" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H1029" t="s">
         <v>9</v>
@@ -30101,7 +30101,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G1030" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H1030" t="s">
         <v>9</v>
@@ -30127,7 +30127,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G1031" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H1031" t="s">
         <v>9</v>
@@ -30153,7 +30153,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G1032" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H1032" t="s">
         <v>9</v>
@@ -30179,7 +30179,7 @@
         <v>13.5</v>
       </c>
       <c r="G1033" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H1033" t="s">
         <v>9</v>
@@ -30205,7 +30205,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1034" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H1034" t="s">
         <v>9</v>
@@ -30231,7 +30231,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1035" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H1035" t="s">
         <v>9</v>
@@ -30257,7 +30257,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1036" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H1036" t="s">
         <v>9</v>
@@ -30283,7 +30283,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1037" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H1037" t="s">
         <v>9</v>
@@ -30309,7 +30309,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G1038" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H1038" t="s">
         <v>9</v>
@@ -30335,7 +30335,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1039" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H1039" t="s">
         <v>9</v>
@@ -30361,7 +30361,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G1040" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H1040" t="s">
         <v>9</v>
@@ -30387,7 +30387,7 @@
         <v>13.5</v>
       </c>
       <c r="G1041" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H1041" t="s">
         <v>9</v>
@@ -30413,7 +30413,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1042" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H1042" t="s">
         <v>9</v>
@@ -30439,7 +30439,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G1043" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H1043" t="s">
         <v>9</v>
@@ -30465,7 +30465,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G1044" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H1044" t="s">
         <v>9</v>
@@ -30491,7 +30491,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G1045" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H1045" t="s">
         <v>9</v>
@@ -30517,7 +30517,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G1046" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H1046" t="s">
         <v>9</v>
@@ -30543,7 +30543,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1047" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H1047" t="s">
         <v>9</v>
@@ -30569,7 +30569,7 @@
         <v>13.8500003814697</v>
       </c>
       <c r="G1048" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H1048" t="s">
         <v>9</v>
@@ -30595,7 +30595,7 @@
         <v>13.75</v>
       </c>
       <c r="G1049" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H1049" t="s">
         <v>9</v>
@@ -30621,7 +30621,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1050" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H1050" t="s">
         <v>9</v>
@@ -30647,7 +30647,7 @@
         <v>13.75</v>
       </c>
       <c r="G1051" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H1051" t="s">
         <v>9</v>
@@ -30673,7 +30673,7 @@
         <v>13.8500003814697</v>
       </c>
       <c r="G1052" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H1052" t="s">
         <v>9</v>
@@ -30699,7 +30699,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G1053" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H1053" t="s">
         <v>9</v>
@@ -30725,7 +30725,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G1054" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H1054" t="s">
         <v>9</v>
@@ -30751,7 +30751,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1055" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H1055" t="s">
         <v>9</v>
@@ -30777,7 +30777,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1056" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H1056" t="s">
         <v>9</v>
@@ -30803,7 +30803,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1057" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H1057" t="s">
         <v>9</v>
@@ -30829,7 +30829,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1058" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H1058" t="s">
         <v>9</v>
@@ -30855,7 +30855,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G1059" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H1059" t="s">
         <v>9</v>
@@ -30881,7 +30881,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1060" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H1060" t="s">
         <v>9</v>
@@ -30907,7 +30907,7 @@
         <v>14.0500001907349</v>
       </c>
       <c r="G1061" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H1061" t="s">
         <v>9</v>
@@ -30933,7 +30933,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1062" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H1062" t="s">
         <v>9</v>
@@ -30959,7 +30959,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1063" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H1063" t="s">
         <v>9</v>
@@ -30985,7 +30985,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G1064" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H1064" t="s">
         <v>9</v>
@@ -31011,7 +31011,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1065" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="H1065" t="s">
         <v>9</v>
@@ -31037,7 +31037,7 @@
         <v>12</v>
       </c>
       <c r="G1066" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="H1066" t="s">
         <v>9</v>
@@ -31063,7 +31063,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1067" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="H1067" t="s">
         <v>9</v>
@@ -31089,7 +31089,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G1068" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="H1068" t="s">
         <v>9</v>
@@ -31115,7 +31115,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G1069" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H1069" t="s">
         <v>9</v>
@@ -31141,7 +31141,7 @@
         <v>10.75</v>
       </c>
       <c r="G1070" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H1070" t="s">
         <v>9</v>
@@ -31167,7 +31167,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1071" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="H1071" t="s">
         <v>9</v>
@@ -31193,7 +31193,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1072" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="H1072" t="s">
         <v>9</v>
@@ -31219,7 +31219,7 @@
         <v>11.75</v>
       </c>
       <c r="G1073" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H1073" t="s">
         <v>9</v>
@@ -31245,7 +31245,7 @@
         <v>11.25</v>
       </c>
       <c r="G1074" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H1074" t="s">
         <v>9</v>
@@ -31271,7 +31271,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1075" t="s">
-        <v>361</v>
+        <v>280</v>
       </c>
       <c r="H1075" t="s">
         <v>9</v>
@@ -31297,7 +31297,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G1076" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="H1076" t="s">
         <v>9</v>
@@ -31323,7 +31323,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1077" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="H1077" t="s">
         <v>9</v>
@@ -31349,7 +31349,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1078" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="H1078" t="s">
         <v>9</v>
@@ -31375,7 +31375,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G1079" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="H1079" t="s">
         <v>9</v>
@@ -31401,7 +31401,7 @@
         <v>11.75</v>
       </c>
       <c r="G1080" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H1080" t="s">
         <v>9</v>
@@ -31427,7 +31427,7 @@
         <v>11.75</v>
       </c>
       <c r="G1081" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H1081" t="s">
         <v>9</v>
@@ -31453,7 +31453,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G1082" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="H1082" t="s">
         <v>9</v>
@@ -31479,7 +31479,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1083" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H1083" t="s">
         <v>9</v>
@@ -31505,7 +31505,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G1084" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="H1084" t="s">
         <v>9</v>
@@ -31531,7 +31531,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1085" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H1085" t="s">
         <v>9</v>
@@ -31557,7 +31557,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G1086" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H1086" t="s">
         <v>9</v>
@@ -31583,7 +31583,7 @@
         <v>12</v>
       </c>
       <c r="G1087" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="H1087" t="s">
         <v>9</v>
@@ -31609,7 +31609,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1088" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="H1088" t="s">
         <v>9</v>
@@ -31635,7 +31635,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1089" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="H1089" t="s">
         <v>9</v>
@@ -31661,7 +31661,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1090" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="H1090" t="s">
         <v>9</v>
@@ -31687,7 +31687,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G1091" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="H1091" t="s">
         <v>9</v>
@@ -31713,7 +31713,7 @@
         <v>12</v>
       </c>
       <c r="G1092" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="H1092" t="s">
         <v>9</v>
@@ -31739,7 +31739,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1093" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H1093" t="s">
         <v>9</v>
@@ -31765,7 +31765,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1094" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H1094" t="s">
         <v>9</v>
@@ -31791,7 +31791,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1095" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="H1095" t="s">
         <v>9</v>
@@ -31817,7 +31817,7 @@
         <v>12.5</v>
       </c>
       <c r="G1096" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H1096" t="s">
         <v>9</v>
@@ -31843,7 +31843,7 @@
         <v>13.5</v>
       </c>
       <c r="G1097" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H1097" t="s">
         <v>9</v>
@@ -31869,7 +31869,7 @@
         <v>13.75</v>
       </c>
       <c r="G1098" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H1098" t="s">
         <v>9</v>
@@ -31921,7 +31921,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G1100" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H1100" t="s">
         <v>9</v>
@@ -31947,7 +31947,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G1101" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H1101" t="s">
         <v>9</v>
@@ -31973,7 +31973,7 @@
         <v>13.5</v>
       </c>
       <c r="G1102" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H1102" t="s">
         <v>9</v>
@@ -31999,7 +31999,7 @@
         <v>13.5</v>
       </c>
       <c r="G1103" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H1103" t="s">
         <v>9</v>
@@ -32025,7 +32025,7 @@
         <v>13.25</v>
       </c>
       <c r="G1104" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H1104" t="s">
         <v>9</v>
@@ -32051,7 +32051,7 @@
         <v>13.5</v>
       </c>
       <c r="G1105" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H1105" t="s">
         <v>9</v>
@@ -32077,7 +32077,7 @@
         <v>13.5</v>
       </c>
       <c r="G1106" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H1106" t="s">
         <v>9</v>
@@ -32103,7 +32103,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1107" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H1107" t="s">
         <v>9</v>
@@ -32129,7 +32129,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G1108" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H1108" t="s">
         <v>9</v>
@@ -32181,7 +32181,7 @@
         <v>13.75</v>
       </c>
       <c r="G1110" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H1110" t="s">
         <v>9</v>
@@ -32207,7 +32207,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G1111" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H1111" t="s">
         <v>9</v>
@@ -32233,7 +32233,7 @@
         <v>13.8500003814697</v>
       </c>
       <c r="G1112" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H1112" t="s">
         <v>9</v>
@@ -32259,7 +32259,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G1113" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H1113" t="s">
         <v>9</v>
@@ -32285,7 +32285,7 @@
         <v>13.8500003814697</v>
       </c>
       <c r="G1114" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H1114" t="s">
         <v>9</v>
@@ -33013,7 +33013,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1142" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="H1142" t="s">
         <v>9</v>
@@ -33039,7 +33039,7 @@
         <v>14.75</v>
       </c>
       <c r="G1143" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H1143" t="s">
         <v>9</v>
@@ -33065,7 +33065,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1144" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H1144" t="s">
         <v>9</v>
@@ -33091,7 +33091,7 @@
         <v>14.5</v>
       </c>
       <c r="G1145" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1145" t="s">
         <v>9</v>
@@ -33117,7 +33117,7 @@
         <v>14.5</v>
       </c>
       <c r="G1146" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1146" t="s">
         <v>9</v>
@@ -33143,7 +33143,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1147" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1147" t="s">
         <v>9</v>
@@ -33169,7 +33169,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1148" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1148" t="s">
         <v>9</v>
@@ -33195,7 +33195,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G1149" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1149" t="s">
         <v>9</v>
@@ -33221,7 +33221,7 @@
         <v>14</v>
       </c>
       <c r="G1150" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1150" t="s">
         <v>9</v>
@@ -33247,7 +33247,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1151" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1151" t="s">
         <v>9</v>
@@ -33273,7 +33273,7 @@
         <v>14.5</v>
       </c>
       <c r="G1152" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1152" t="s">
         <v>9</v>
@@ -33299,7 +33299,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1153" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H1153" t="s">
         <v>9</v>
@@ -33325,7 +33325,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G1154" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H1154" t="s">
         <v>9</v>
@@ -33351,7 +33351,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G1155" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H1155" t="s">
         <v>9</v>
@@ -33377,7 +33377,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G1156" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H1156" t="s">
         <v>9</v>
@@ -33403,7 +33403,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1157" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H1157" t="s">
         <v>9</v>
@@ -33455,7 +33455,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1159" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H1159" t="s">
         <v>9</v>
@@ -33481,7 +33481,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1160" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H1160" t="s">
         <v>9</v>
@@ -33507,7 +33507,7 @@
         <v>14.5</v>
       </c>
       <c r="G1161" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1161" t="s">
         <v>9</v>
@@ -33533,7 +33533,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G1162" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1162" t="s">
         <v>9</v>
@@ -33559,7 +33559,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G1163" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H1163" t="s">
         <v>9</v>
@@ -33585,7 +33585,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1164" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1164" t="s">
         <v>9</v>
@@ -33611,7 +33611,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1165" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1165" t="s">
         <v>9</v>
@@ -33637,7 +33637,7 @@
         <v>14.25</v>
       </c>
       <c r="G1166" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1166" t="s">
         <v>9</v>
@@ -33663,7 +33663,7 @@
         <v>14.5</v>
       </c>
       <c r="G1167" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1167" t="s">
         <v>9</v>
@@ -33689,7 +33689,7 @@
         <v>14.5</v>
       </c>
       <c r="G1168" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1168" t="s">
         <v>9</v>
@@ -33741,7 +33741,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1170" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H1170" t="s">
         <v>9</v>
@@ -33793,7 +33793,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1172" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H1172" t="s">
         <v>9</v>
@@ -33845,7 +33845,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1174" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H1174" t="s">
         <v>9</v>
@@ -33871,7 +33871,7 @@
         <v>15.75</v>
       </c>
       <c r="G1175" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H1175" t="s">
         <v>9</v>
@@ -33897,7 +33897,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1176" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H1176" t="s">
         <v>9</v>
@@ -33923,7 +33923,7 @@
         <v>16</v>
       </c>
       <c r="G1177" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H1177" t="s">
         <v>9</v>
@@ -33949,7 +33949,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1178" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H1178" t="s">
         <v>9</v>
@@ -33975,7 +33975,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G1179" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H1179" t="s">
         <v>9</v>
@@ -34001,7 +34001,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1180" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H1180" t="s">
         <v>9</v>
@@ -34027,7 +34027,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1181" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H1181" t="s">
         <v>9</v>
@@ -34053,7 +34053,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1182" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H1182" t="s">
         <v>9</v>
@@ -34079,7 +34079,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1183" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H1183" t="s">
         <v>9</v>
@@ -34105,7 +34105,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1184" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H1184" t="s">
         <v>9</v>
@@ -34131,7 +34131,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1185" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H1185" t="s">
         <v>9</v>
@@ -34157,7 +34157,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1186" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H1186" t="s">
         <v>9</v>
@@ -34183,7 +34183,7 @@
         <v>16.5</v>
       </c>
       <c r="G1187" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H1187" t="s">
         <v>9</v>
@@ -34209,7 +34209,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1188" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H1188" t="s">
         <v>9</v>
@@ -34235,7 +34235,7 @@
         <v>16.5</v>
       </c>
       <c r="G1189" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H1189" t="s">
         <v>9</v>
@@ -34261,7 +34261,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1190" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H1190" t="s">
         <v>9</v>
@@ -34287,7 +34287,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G1191" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H1191" t="s">
         <v>9</v>
@@ -34313,7 +34313,7 @@
         <v>17</v>
       </c>
       <c r="G1192" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H1192" t="s">
         <v>9</v>
@@ -34339,7 +34339,7 @@
         <v>17</v>
       </c>
       <c r="G1193" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H1193" t="s">
         <v>9</v>
@@ -34365,7 +34365,7 @@
         <v>17</v>
       </c>
       <c r="G1194" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H1194" t="s">
         <v>9</v>
@@ -34391,7 +34391,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1195" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H1195" t="s">
         <v>9</v>
@@ -34417,7 +34417,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G1196" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H1196" t="s">
         <v>9</v>
@@ -34443,7 +34443,7 @@
         <v>18</v>
       </c>
       <c r="G1197" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H1197" t="s">
         <v>9</v>
@@ -34469,7 +34469,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1198" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H1198" t="s">
         <v>9</v>
@@ -34495,7 +34495,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1199" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H1199" t="s">
         <v>9</v>
@@ -34521,7 +34521,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1200" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H1200" t="s">
         <v>9</v>
@@ -34547,7 +34547,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G1201" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H1201" t="s">
         <v>9</v>
@@ -34573,7 +34573,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G1202" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H1202" t="s">
         <v>9</v>
@@ -34599,7 +34599,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1203" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H1203" t="s">
         <v>9</v>
@@ -34625,7 +34625,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G1204" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H1204" t="s">
         <v>9</v>
@@ -34651,7 +34651,7 @@
         <v>20</v>
       </c>
       <c r="G1205" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H1205" t="s">
         <v>9</v>
@@ -34677,7 +34677,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G1206" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H1206" t="s">
         <v>9</v>
@@ -34703,7 +34703,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G1207" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H1207" t="s">
         <v>9</v>
@@ -34729,7 +34729,7 @@
         <v>19.25</v>
       </c>
       <c r="G1208" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H1208" t="s">
         <v>9</v>
@@ -34755,7 +34755,7 @@
         <v>19.3500003814697</v>
       </c>
       <c r="G1209" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H1209" t="s">
         <v>9</v>
@@ -34781,7 +34781,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1210" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H1210" t="s">
         <v>9</v>
@@ -34807,7 +34807,7 @@
         <v>19.3500003814697</v>
       </c>
       <c r="G1211" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H1211" t="s">
         <v>9</v>
@@ -34833,7 +34833,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1212" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H1212" t="s">
         <v>9</v>
@@ -34859,7 +34859,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1213" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H1213" t="s">
         <v>9</v>
@@ -34885,7 +34885,7 @@
         <v>18.4500007629395</v>
       </c>
       <c r="G1214" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H1214" t="s">
         <v>9</v>
@@ -34911,7 +34911,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G1215" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H1215" t="s">
         <v>9</v>
@@ -34937,7 +34937,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1216" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1216" t="s">
         <v>9</v>
@@ -34963,7 +34963,7 @@
         <v>18.5</v>
       </c>
       <c r="G1217" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H1217" t="s">
         <v>9</v>
@@ -34989,7 +34989,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1218" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H1218" t="s">
         <v>9</v>
@@ -35015,7 +35015,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1219" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H1219" t="s">
         <v>9</v>
@@ -35041,7 +35041,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1220" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H1220" t="s">
         <v>9</v>
@@ -35067,7 +35067,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1221" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H1221" t="s">
         <v>9</v>
@@ -35093,7 +35093,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1222" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H1222" t="s">
         <v>9</v>
@@ -35119,7 +35119,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1223" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H1223" t="s">
         <v>9</v>
@@ -35145,7 +35145,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1224" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H1224" t="s">
         <v>9</v>
@@ -35171,7 +35171,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1225" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H1225" t="s">
         <v>9</v>
@@ -35197,7 +35197,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1226" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H1226" t="s">
         <v>9</v>
@@ -35223,7 +35223,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1227" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H1227" t="s">
         <v>9</v>
@@ -35249,7 +35249,7 @@
         <v>17.75</v>
       </c>
       <c r="G1228" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H1228" t="s">
         <v>9</v>
@@ -35275,7 +35275,7 @@
         <v>18</v>
       </c>
       <c r="G1229" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H1229" t="s">
         <v>9</v>
@@ -35301,7 +35301,7 @@
         <v>18.5</v>
       </c>
       <c r="G1230" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H1230" t="s">
         <v>9</v>
@@ -35327,7 +35327,7 @@
         <v>18.4500007629395</v>
       </c>
       <c r="G1231" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H1231" t="s">
         <v>9</v>
@@ -35353,7 +35353,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1232" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H1232" t="s">
         <v>9</v>
@@ -35379,7 +35379,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G1233" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H1233" t="s">
         <v>9</v>
@@ -35405,7 +35405,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1234" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H1234" t="s">
         <v>9</v>
@@ -35431,7 +35431,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1235" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H1235" t="s">
         <v>9</v>
@@ -35457,7 +35457,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1236" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H1236" t="s">
         <v>9</v>
@@ -35483,7 +35483,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G1237" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H1237" t="s">
         <v>9</v>
@@ -35509,7 +35509,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G1238" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H1238" t="s">
         <v>9</v>
@@ -35535,7 +35535,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G1239" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H1239" t="s">
         <v>9</v>
@@ -35561,7 +35561,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1240" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1240" t="s">
         <v>9</v>
@@ -35587,7 +35587,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1241" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H1241" t="s">
         <v>9</v>
@@ -35613,7 +35613,7 @@
         <v>18.5</v>
       </c>
       <c r="G1242" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H1242" t="s">
         <v>9</v>
@@ -35639,7 +35639,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1243" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H1243" t="s">
         <v>9</v>
@@ -35665,7 +35665,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G1244" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H1244" t="s">
         <v>9</v>
@@ -35691,7 +35691,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G1245" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H1245" t="s">
         <v>9</v>
@@ -35717,7 +35717,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1246" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H1246" t="s">
         <v>9</v>
@@ -35743,7 +35743,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1247" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H1247" t="s">
         <v>9</v>
@@ -35769,7 +35769,7 @@
         <v>17.75</v>
       </c>
       <c r="G1248" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H1248" t="s">
         <v>9</v>
@@ -35795,7 +35795,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1249" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H1249" t="s">
         <v>9</v>
@@ -35821,7 +35821,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1250" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H1250" t="s">
         <v>9</v>
@@ -35847,7 +35847,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1251" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H1251" t="s">
         <v>9</v>
@@ -35873,7 +35873,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G1252" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H1252" t="s">
         <v>9</v>
@@ -35899,7 +35899,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1253" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H1253" t="s">
         <v>9</v>
@@ -35925,7 +35925,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1254" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H1254" t="s">
         <v>9</v>
@@ -35951,7 +35951,7 @@
         <v>18.0499992370605</v>
       </c>
       <c r="G1255" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H1255" t="s">
         <v>9</v>
@@ -35977,7 +35977,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1256" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H1256" t="s">
         <v>9</v>
@@ -36003,7 +36003,7 @@
         <v>18</v>
       </c>
       <c r="G1257" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H1257" t="s">
         <v>9</v>
@@ -36029,7 +36029,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G1258" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H1258" t="s">
         <v>9</v>
@@ -36055,7 +36055,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G1259" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H1259" t="s">
         <v>9</v>
@@ -36081,7 +36081,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1260" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H1260" t="s">
         <v>9</v>
@@ -36107,7 +36107,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1261" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H1261" t="s">
         <v>9</v>
@@ -36133,7 +36133,7 @@
         <v>19</v>
       </c>
       <c r="G1262" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H1262" t="s">
         <v>9</v>
@@ -36159,7 +36159,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1263" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H1263" t="s">
         <v>9</v>
@@ -36185,7 +36185,7 @@
         <v>19.5</v>
       </c>
       <c r="G1264" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H1264" t="s">
         <v>9</v>
@@ -36211,7 +36211,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G1265" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H1265" t="s">
         <v>9</v>
@@ -36237,7 +36237,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G1266" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H1266" t="s">
         <v>9</v>
@@ -36263,7 +36263,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G1267" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H1267" t="s">
         <v>9</v>
@@ -36289,7 +36289,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G1268" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H1268" t="s">
         <v>9</v>
@@ -36315,7 +36315,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1269" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H1269" t="s">
         <v>9</v>
@@ -36341,7 +36341,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1270" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H1270" t="s">
         <v>9</v>
@@ -36367,7 +36367,7 @@
         <v>21.5</v>
       </c>
       <c r="G1271" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H1271" t="s">
         <v>9</v>
@@ -36393,7 +36393,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1272" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H1272" t="s">
         <v>9</v>
@@ -36419,7 +36419,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G1273" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H1273" t="s">
         <v>9</v>
@@ -36445,7 +36445,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1274" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H1274" t="s">
         <v>9</v>
@@ -36471,7 +36471,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G1275" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H1275" t="s">
         <v>9</v>
@@ -36497,7 +36497,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G1276" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H1276" t="s">
         <v>9</v>
@@ -36523,7 +36523,7 @@
         <v>22.5</v>
       </c>
       <c r="G1277" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H1277" t="s">
         <v>9</v>
@@ -36549,7 +36549,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G1278" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H1278" t="s">
         <v>9</v>
@@ -36575,7 +36575,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G1279" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H1279" t="s">
         <v>9</v>
@@ -36601,7 +36601,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G1280" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H1280" t="s">
         <v>9</v>
@@ -36627,7 +36627,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G1281" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H1281" t="s">
         <v>9</v>
@@ -36653,7 +36653,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1282" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H1282" t="s">
         <v>9</v>
@@ -36679,7 +36679,7 @@
         <v>23</v>
       </c>
       <c r="G1283" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H1283" t="s">
         <v>9</v>
@@ -36705,7 +36705,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G1284" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H1284" t="s">
         <v>9</v>
@@ -36731,7 +36731,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G1285" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H1285" t="s">
         <v>9</v>
@@ -36757,7 +36757,7 @@
         <v>23.5</v>
       </c>
       <c r="G1286" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H1286" t="s">
         <v>9</v>
@@ -36783,7 +36783,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G1287" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H1287" t="s">
         <v>9</v>
@@ -36835,7 +36835,7 @@
         <v>23.5</v>
       </c>
       <c r="G1289" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H1289" t="s">
         <v>9</v>
@@ -68277,7 +68277,7 @@
     </row>
     <row r="2499">
       <c r="A2499" s="1" t="n">
-        <v>45958.6909953704</v>
+        <v>45958.3333333333</v>
       </c>
       <c r="B2499" t="n">
         <v>3097</v>
@@ -68298,6 +68298,32 @@
         <v>984</v>
       </c>
       <c r="H2499" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2500">
+      <c r="A2500" s="1" t="n">
+        <v>45959.6911805556</v>
+      </c>
+      <c r="B2500" t="n">
+        <v>5573</v>
+      </c>
+      <c r="C2500" t="n">
+        <v>23.2000007629395</v>
+      </c>
+      <c r="D2500" t="n">
+        <v>22.7000007629395</v>
+      </c>
+      <c r="E2500" t="n">
+        <v>23.2000007629395</v>
+      </c>
+      <c r="F2500" t="n">
+        <v>22.8999996185303</v>
+      </c>
+      <c r="G2500" t="s">
+        <v>984</v>
+      </c>
+      <c r="H2500" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IWB.MI.xlsx
+++ b/data/IWB.MI.xlsx
@@ -38,103 +38,103 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84661674499512</t>
+    <t xml:space="preserve">7.84661531448364</t>
   </si>
   <si>
     <t xml:space="preserve">IWB.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79867267608643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8306360244751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74274063110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75073194503784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71077728271484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69479942321777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59092235565186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51101684570312</t>
+    <t xml:space="preserve">7.7986741065979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83063554763794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74274015426636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75072956085205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71077823638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69479846954346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59092378616333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51101779937744</t>
   </si>
   <si>
     <t xml:space="preserve">7.31125783920288</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44709253311157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35120868682861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29527568817139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26331329345703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29927158355713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29127979278564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27130556106567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24733304977417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37517929077148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43111515045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47106552124023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15144824981689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41513156890869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32723712921143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28728485107422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99163722991943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11149406433105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1914005279541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25532341003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41912698745728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42312335968018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63087463378906</t>
+    <t xml:space="preserve">7.44709300994873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35120820999146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29527616500854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26331424713135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29927062988281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29128074645996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27130460739136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24733257293701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3751802444458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4311146736145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47106504440308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15144634246826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41513204574585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32723808288574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28728580474854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99163913726807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11149501800537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19140100479126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25532388687134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41912841796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42312240600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63087368011475</t>
   </si>
   <si>
     <t xml:space="preserve">7.67082691192627</t>
@@ -143,58 +143,58 @@
     <t xml:space="preserve">7.49903249740601</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58293151855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89455890655518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98644781112671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91054010391235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54297971725464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82264375686646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6428599357605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62288427352905</t>
+    <t xml:space="preserve">7.58293199539185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89456033706665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98644828796387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91054058074951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54297876358032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82264518737793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64285898208618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62288331985474</t>
   </si>
   <si>
     <t xml:space="preserve">7.77470207214355</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7667121887207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79068326950073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87058877944946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96647310256958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71876955032349</t>
+    <t xml:space="preserve">7.76671409606934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79068613052368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87058734893799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96647357940674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71876907348633</t>
   </si>
   <si>
     <t xml:space="preserve">7.66283655166626</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57094573974609</t>
+    <t xml:space="preserve">7.57094669342041</t>
   </si>
   <si>
     <t xml:space="preserve">7.5589599609375</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39116048812866</t>
+    <t xml:space="preserve">7.39116144180298</t>
   </si>
   <si>
     <t xml:space="preserve">7.46307516098022</t>
@@ -203,25 +203,25 @@
     <t xml:space="preserve">7.60690307617188</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54697322845459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36719036102295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31525135040283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33123350143433</t>
+    <t xml:space="preserve">7.54697561264038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36718988418579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31525039672852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33123254776001</t>
   </si>
   <si>
     <t xml:space="preserve">7.3472146987915</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50302791595459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24333667755127</t>
+    <t xml:space="preserve">7.50302839279175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24333763122559</t>
   </si>
   <si>
     <t xml:space="preserve">7.22336196899414</t>
@@ -230,28 +230,28 @@
     <t xml:space="preserve">7.23934316635132</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45907878875732</t>
+    <t xml:space="preserve">7.45908117294312</t>
   </si>
   <si>
     <t xml:space="preserve">7.46707057952881</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10350561141968</t>
+    <t xml:space="preserve">7.10350513458252</t>
   </si>
   <si>
     <t xml:space="preserve">6.89974927902222</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91173362731934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9516863822937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00761985778809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87178134918213</t>
+    <t xml:space="preserve">6.91173410415649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95168590545654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00762033462524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8717827796936</t>
   </si>
   <si>
     <t xml:space="preserve">6.87577724456787</t>
@@ -260,64 +260,64 @@
     <t xml:space="preserve">6.87977170944214</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86778831481934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75192451477051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74393510818481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82383966445923</t>
+    <t xml:space="preserve">6.86778736114502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75192594528198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7439341545105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82384061813354</t>
   </si>
   <si>
     <t xml:space="preserve">6.66403102874756</t>
   </si>
   <si>
-    <t xml:space="preserve">6.83182954788208</t>
+    <t xml:space="preserve">6.83183002471924</t>
   </si>
   <si>
     <t xml:space="preserve">6.89575386047363</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03159141540527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07154321670532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33522701263428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25931882858276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17941427230835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2673077583313</t>
+    <t xml:space="preserve">7.0315899848938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07154417037964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33522748947144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25931930541992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17941474914551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26730918884277</t>
   </si>
   <si>
     <t xml:space="preserve">7.23135185241699</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09551429748535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18340873718262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1874041557312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20738077163696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14345645904541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12348079681396</t>
+    <t xml:space="preserve">7.09551525115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18341016769409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18740463256836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20738124847412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14345693588257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12348175048828</t>
   </si>
   <si>
     <t xml:space="preserve">7.23534774780273</t>
@@ -326,25 +326,25 @@
     <t xml:space="preserve">7.74673557281494</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83463048934937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98245429992676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92652034759521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78269100189209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63886499404907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73475074768066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07034873962402</t>
+    <t xml:space="preserve">7.834632396698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98245334625244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9265193939209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78269290924072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63886451721191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73475217819214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07034969329834</t>
   </si>
   <si>
     <t xml:space="preserve">8.21417713165283</t>
@@ -356,7 +356,7 @@
     <t xml:space="preserve">8.18221473693848</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27011013031006</t>
+    <t xml:space="preserve">8.27011108398438</t>
   </si>
   <si>
     <t xml:space="preserve">8.57374572753906</t>
@@ -365,10 +365,10 @@
     <t xml:space="preserve">8.54977512359619</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35001468658447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46987056732178</t>
+    <t xml:space="preserve">8.35001373291016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46986961364746</t>
   </si>
   <si>
     <t xml:space="preserve">8.52580451965332</t>
@@ -380,79 +380,79 @@
     <t xml:space="preserve">8.59771823883057</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60571002960205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58173751831055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64687442779541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67129993438721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61430549621582</t>
+    <t xml:space="preserve">8.60571193695068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58173561096191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64687347412109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67130088806152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61430644989014</t>
   </si>
   <si>
     <t xml:space="preserve">8.63058948516846</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75272083282471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82599830627441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87485218048096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95627307891846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74457931518555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85856628417969</t>
+    <t xml:space="preserve">8.75271987915039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82599925994873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87485122680664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95627403259277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74457740783691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85856819152832</t>
   </si>
   <si>
     <t xml:space="preserve">8.84228324890137</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91556167602539</t>
+    <t xml:space="preserve">8.91556358337402</t>
   </si>
   <si>
     <t xml:space="preserve">9.03769302368164</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00512409210205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94812965393066</t>
+    <t xml:space="preserve">9.00512599945068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94812870025635</t>
   </si>
   <si>
     <t xml:space="preserve">8.99698352813721</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12725639343262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19239234924316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11911296844482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14354038238525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98069858551025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13539886474609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16796493530273</t>
+    <t xml:space="preserve">9.1272554397583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19239139556885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11911392211914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14353942871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98070049285889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13539791107178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16796684265137</t>
   </si>
   <si>
     <t xml:space="preserve">9.15982437133789</t>
@@ -461,16 +461,16 @@
     <t xml:space="preserve">9.18424987792969</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1516809463501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07026290893555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9644136428833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92370510101318</t>
+    <t xml:space="preserve">9.15168190002441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07026100158691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96441459655762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92370319366455</t>
   </si>
   <si>
     <t xml:space="preserve">8.80157375335693</t>
@@ -479,79 +479,79 @@
     <t xml:space="preserve">8.79343128204346</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8667106628418</t>
+    <t xml:space="preserve">8.86670875549316</t>
   </si>
   <si>
     <t xml:space="preserve">8.9074182510376</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89113712310791</t>
+    <t xml:space="preserve">8.89113521575928</t>
   </si>
   <si>
     <t xml:space="preserve">9.11097049713135</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20053482055664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28195571899414</t>
+    <t xml:space="preserve">9.20053577423096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28195476531982</t>
   </si>
   <si>
     <t xml:space="preserve">9.35523414611816</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39594459533691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32266426086426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64834785461426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60763931274414</t>
+    <t xml:space="preserve">9.3959436416626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32266616821289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64834880828857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60763835906982</t>
   </si>
   <si>
     <t xml:space="preserve">9.9007511138916</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99031448364258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.120587348938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1368722915649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1775817871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1043033599854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1531553268433</t>
+    <t xml:space="preserve">9.99031543731689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1205892562866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1368732452393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1775827407837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.104302406311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1531562805176</t>
   </si>
   <si>
     <t xml:space="preserve">10.0961618423462</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94146347045898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90889263153076</t>
+    <t xml:space="preserve">9.94146251678467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90889358520508</t>
   </si>
   <si>
     <t xml:space="preserve">9.77047920227051</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83561515808105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91703605651855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79490375518799</t>
+    <t xml:space="preserve">9.83561611175537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91703701019287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79490566253662</t>
   </si>
   <si>
     <t xml:space="preserve">9.77862071990967</t>
@@ -560,7 +560,7 @@
     <t xml:space="preserve">9.78676319122314</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9577465057373</t>
+    <t xml:space="preserve">9.95774555206299</t>
   </si>
   <si>
     <t xml:space="preserve">10.0147409439087</t>
@@ -569,70 +569,70 @@
     <t xml:space="preserve">9.99845695495605</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8844690322876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86003971099854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85189914703369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89260864257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2590026855469</t>
+    <t xml:space="preserve">9.88446712493896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86004161834717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85190010070801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89260959625244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2590036392212</t>
   </si>
   <si>
     <t xml:space="preserve">10.3404226303101</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4625549316406</t>
+    <t xml:space="preserve">10.4625558853149</t>
   </si>
   <si>
     <t xml:space="preserve">10.5276908874512</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5765438079834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5439758300781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5358324050903</t>
+    <t xml:space="preserve">10.5765428543091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5439739227295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5358304977417</t>
   </si>
   <si>
     <t xml:space="preserve">10.5032644271851</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5521192550659</t>
+    <t xml:space="preserve">10.5521183013916</t>
   </si>
   <si>
     <t xml:space="preserve">10.3485651016235</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4381284713745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3241395950317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3811340332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3648509979248</t>
+    <t xml:space="preserve">10.4381265640259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3241386413574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3811330795288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3648500442505</t>
   </si>
   <si>
     <t xml:space="preserve">10.4218444824219</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4137020111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3729906082153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3892755508423</t>
+    <t xml:space="preserve">10.4137010574341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3729915618896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3892765045166</t>
   </si>
   <si>
     <t xml:space="preserve">10.2915716171265</t>
@@ -641,10 +641,10 @@
     <t xml:space="preserve">10.267144203186</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2264356613159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1938676834106</t>
+    <t xml:space="preserve">10.2264337539673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1938667297363</t>
   </si>
   <si>
     <t xml:space="preserve">10.3159980773926</t>
@@ -656,13 +656,13 @@
     <t xml:space="preserve">10.2834300994873</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4299879074097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3322820663452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2427177429199</t>
+    <t xml:space="preserve">10.4299869537354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3322811126709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2427196502686</t>
   </si>
   <si>
     <t xml:space="preserve">10.5846853256226</t>
@@ -671,49 +671,49 @@
     <t xml:space="preserve">10.6661071777344</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7068157196045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7475280761719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.788236618042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6253957748413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8696594238281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8289470672607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0324993133545</t>
+    <t xml:space="preserve">10.7068166732788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7475261688232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7882375717163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6253967285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8696584701538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8289480209351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0325002670288</t>
   </si>
   <si>
     <t xml:space="preserve">11.2360525131226</t>
   </si>
   <si>
-    <t xml:space="preserve">11.439603805542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6838626861572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0732097625732</t>
+    <t xml:space="preserve">11.4396047592163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6838645935059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0732088088989</t>
   </si>
   <si>
     <t xml:space="preserve">10.9917888641357</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1546287536621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3174705505371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.276762008667</t>
+    <t xml:space="preserve">11.1546306610107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3174734115601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2767610549927</t>
   </si>
   <si>
     <t xml:space="preserve">11.1953411102295</t>
@@ -722,7 +722,7 @@
     <t xml:space="preserve">11.3581819534302</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4839172363281</t>
+    <t xml:space="preserve">11.4839181900024</t>
   </si>
   <si>
     <t xml:space="preserve">11.5258302688599</t>
@@ -731,67 +731,67 @@
     <t xml:space="preserve">11.5677433013916</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4000940322876</t>
+    <t xml:space="preserve">11.400092124939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0228853225708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1486225128174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2324466705322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1905326843262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2743577957153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8971481323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0647964477539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.442006111145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8552360534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6875867843628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3254747390747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2822484970093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1957921981812</t>
   </si>
   <si>
     <t xml:space="preserve">11.0228843688965</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1486206054688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2324447631836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1905336380005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.274356842041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8971490859985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0647974014282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.442006111145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8552370071411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6875877380371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3254737854004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2822456359863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1957931518555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0228853225708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2390213012695</t>
+    <t xml:space="preserve">11.2390193939209</t>
   </si>
   <si>
     <t xml:space="preserve">11.1525659561157</t>
   </si>
   <si>
-    <t xml:space="preserve">10.936429977417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0661125183105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.109338760376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9796581268311</t>
+    <t xml:space="preserve">10.9364318847656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0661134719849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1093397140503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9796571731567</t>
   </si>
   <si>
     <t xml:space="preserve">10.7635231018066</t>
@@ -800,61 +800,61 @@
     <t xml:space="preserve">10.590615272522</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8499774932861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7202949523926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6770687103271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8067512512207</t>
+    <t xml:space="preserve">10.8499765396118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7202959060669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6770706176758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8067502975464</t>
   </si>
   <si>
     <t xml:space="preserve">10.8932046890259</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6338424682617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4119281768799</t>
+    <t xml:space="preserve">10.6338415145874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4119272232056</t>
   </si>
   <si>
     <t xml:space="preserve">11.4551553726196</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3687009811401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5416088104248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.62806224823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5848360061646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4609336853027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3312520980835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3744802474976</t>
+    <t xml:space="preserve">11.3687019348145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5416097640991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6280632019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5848369598389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4609346389771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3312530517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3744792938232</t>
   </si>
   <si>
     <t xml:space="preserve">10.2880258560181</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5041599273682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0286645889282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94221115112305</t>
+    <t xml:space="preserve">10.5041589736938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0286636352539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94220924377441</t>
   </si>
   <si>
     <t xml:space="preserve">9.59639358520508</t>
@@ -866,16 +866,16 @@
     <t xml:space="preserve">9.81252956390381</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85575485229492</t>
+    <t xml:space="preserve">9.85575580596924</t>
   </si>
   <si>
     <t xml:space="preserve">9.55316734313965</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03444290161133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81830883026123</t>
+    <t xml:space="preserve">9.03444194793701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81830787658691</t>
   </si>
   <si>
     <t xml:space="preserve">8.86153507232666</t>
@@ -887,7 +887,7 @@
     <t xml:space="preserve">9.07767009735107</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16412353515625</t>
+    <t xml:space="preserve">9.16412448883057</t>
   </si>
   <si>
     <t xml:space="preserve">9.25057792663574</t>
@@ -896,22 +896,22 @@
     <t xml:space="preserve">9.33703231811523</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29380416870117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2447986602783</t>
+    <t xml:space="preserve">9.2938060760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2447996139526</t>
   </si>
   <si>
     <t xml:space="preserve">9.68284797668457</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1583442687988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98543834686279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89898204803467</t>
+    <t xml:space="preserve">10.1583452224731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98543739318848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89898300170898</t>
   </si>
   <si>
     <t xml:space="preserve">9.76930236816406</t>
@@ -920,7 +920,7 @@
     <t xml:space="preserve">9.72607517242432</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46671199798584</t>
+    <t xml:space="preserve">9.46671295166016</t>
   </si>
   <si>
     <t xml:space="preserve">9.5099401473999</t>
@@ -938,16 +938,16 @@
     <t xml:space="preserve">10.0718898773193</t>
   </si>
   <si>
-    <t xml:space="preserve">10.297290802002</t>
+    <t xml:space="preserve">10.297287940979</t>
   </si>
   <si>
     <t xml:space="preserve">10.2077465057373</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1629772186279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3420610427856</t>
+    <t xml:space="preserve">10.1629781723022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3420600891113</t>
   </si>
   <si>
     <t xml:space="preserve">10.4316005706787</t>
@@ -956,34 +956,34 @@
     <t xml:space="preserve">10.3868322372437</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1182050704956</t>
+    <t xml:space="preserve">10.1182069778442</t>
   </si>
   <si>
     <t xml:space="preserve">10.2525186538696</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4763717651367</t>
+    <t xml:space="preserve">10.476372718811</t>
   </si>
   <si>
     <t xml:space="preserve">10.6554555892944</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7897691726685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7449979782104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5659141540527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7002277374268</t>
+    <t xml:space="preserve">10.7897682189941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7449970245361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5659160614014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7002267837524</t>
   </si>
   <si>
     <t xml:space="preserve">11.1031637191772</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9688529968262</t>
+    <t xml:space="preserve">10.9688520431519</t>
   </si>
   <si>
     <t xml:space="preserve">10.9240808486938</t>
@@ -995,61 +995,61 @@
     <t xml:space="preserve">11.1479349136353</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2822465896606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.237476348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4613313674927</t>
+    <t xml:space="preserve">11.2822494506836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2374753952026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4613304138184</t>
   </si>
   <si>
     <t xml:space="preserve">11.327018737793</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1927070617676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3717880249023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4165601730347</t>
+    <t xml:space="preserve">11.1927061080933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3717889785767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4165592193604</t>
   </si>
   <si>
     <t xml:space="preserve">11.0583934783936</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6404132843018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7299566268921</t>
+    <t xml:space="preserve">11.6404142379761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7299556732178</t>
   </si>
   <si>
     <t xml:space="preserve">11.6851854324341</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7747259140015</t>
+    <t xml:space="preserve">11.7747268676758</t>
   </si>
   <si>
     <t xml:space="preserve">11.8194961547852</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8642673492432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5508728027344</t>
+    <t xml:space="preserve">11.8642683029175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5508718490601</t>
   </si>
   <si>
     <t xml:space="preserve">11.5956430435181</t>
   </si>
   <si>
-    <t xml:space="preserve">10.521143913269</t>
+    <t xml:space="preserve">10.5211429595947</t>
   </si>
   <si>
     <t xml:space="preserve">11.0136222839355</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8345394134521</t>
+    <t xml:space="preserve">10.8345384597778</t>
   </si>
   <si>
     <t xml:space="preserve">11.9985799789429</t>
@@ -1058,10 +1058,10 @@
     <t xml:space="preserve">12.0881223678589</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0433511734009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1328935623169</t>
+    <t xml:space="preserve">12.0433502197266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1328916549683</t>
   </si>
   <si>
     <t xml:space="preserve">12.2224349975586</t>
@@ -1073,7 +1073,7 @@
     <t xml:space="preserve">12.3567476272583</t>
   </si>
   <si>
-    <t xml:space="preserve">12.267204284668</t>
+    <t xml:space="preserve">12.2672052383423</t>
   </si>
   <si>
     <t xml:space="preserve">12.4015188217163</t>
@@ -1085,10 +1085,10 @@
     <t xml:space="preserve">12.6701421737671</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6253709793091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5806016921997</t>
+    <t xml:space="preserve">12.6253719329834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.580602645874</t>
   </si>
   <si>
     <t xml:space="preserve">10.6106853485107</t>
@@ -1112,10 +1112,10 @@
     <t xml:space="preserve">13.6998729705811</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8789539337158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0132675170898</t>
+    <t xml:space="preserve">13.8789548873901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0132665634155</t>
   </si>
   <si>
     <t xml:space="preserve">14.1475801467896</t>
@@ -1127,25 +1127,25 @@
     <t xml:space="preserve">14.1923522949219</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9237270355225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9684982299805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7894124984741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2818918228149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8341846466064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5207901000977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4312448501587</t>
+    <t xml:space="preserve">13.9237260818481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9684963226318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7894134521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2818927764893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8341836929321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5207891464233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.431245803833</t>
   </si>
   <si>
     <t xml:space="preserve">13.5655584335327</t>
@@ -1154,13 +1154,13 @@
     <t xml:space="preserve">13.610330581665</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7004652023315</t>
+    <t xml:space="preserve">13.7004642486572</t>
   </si>
   <si>
     <t xml:space="preserve">13.7905988693237</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8356676101685</t>
+    <t xml:space="preserve">13.8356657028198</t>
   </si>
   <si>
     <t xml:space="preserve">13.6553974151611</t>
@@ -1175,13 +1175,13 @@
     <t xml:space="preserve">13.1596574783325</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0695219039917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9793872833252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7089824676514</t>
+    <t xml:space="preserve">13.069522857666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9793863296509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.708984375</t>
   </si>
   <si>
     <t xml:space="preserve">12.5737819671631</t>
@@ -1190,10 +1190,10 @@
     <t xml:space="preserve">12.6188488006592</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3399267196655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1145896911621</t>
+    <t xml:space="preserve">13.3399248123169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1145887374878</t>
   </si>
   <si>
     <t xml:space="preserve">13.4751281738281</t>
@@ -1202,7 +1202,7 @@
     <t xml:space="preserve">12.9343204498291</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7540502548218</t>
+    <t xml:space="preserve">12.7540512084961</t>
   </si>
   <si>
     <t xml:space="preserve">12.8441858291626</t>
@@ -1223,43 +1223,43 @@
     <t xml:space="preserve">14.4215412139893</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3764753341675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5116758346558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4666090011597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6018123626709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6919460296631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8722143173218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2327547073364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0074167251587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.32288646698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1876859664917</t>
+    <t xml:space="preserve">14.3764743804932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5116767883301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4666080474854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6018114089966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6919450759888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8722171783447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2327508926392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0074157714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3228883743286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1876850128174</t>
   </si>
   <si>
     <t xml:space="preserve">16.2242336273193</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9538335800171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8551788330078</t>
+    <t xml:space="preserve">15.9538288116455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8551769256592</t>
   </si>
   <si>
     <t xml:space="preserve">16.3143692016602</t>
@@ -1268,22 +1268,22 @@
     <t xml:space="preserve">16.9903793334961</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8101100921631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7565250396729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0269260406494</t>
+    <t xml:space="preserve">16.8101081848145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7565231323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0269298553467</t>
   </si>
   <si>
     <t xml:space="preserve">17.9367923736572</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3509159088135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4410533905029</t>
+    <t xml:space="preserve">17.3509178161621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4410514831543</t>
   </si>
   <si>
     <t xml:space="preserve">17.4861183166504</t>
@@ -1292,28 +1292,28 @@
     <t xml:space="preserve">17.0354461669922</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6298389434814</t>
+    <t xml:space="preserve">16.6298408508301</t>
   </si>
   <si>
     <t xml:space="preserve">16.7199745178223</t>
   </si>
   <si>
-    <t xml:space="preserve">16.404504776001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6749057769775</t>
+    <t xml:space="preserve">16.4045028686523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6749095916748</t>
   </si>
   <si>
     <t xml:space="preserve">16.9453105926514</t>
   </si>
   <si>
-    <t xml:space="preserve">16.765043258667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8636980056763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9988975524902</t>
+    <t xml:space="preserve">16.7650413513184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8636960983276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9988965988159</t>
   </si>
   <si>
     <t xml:space="preserve">16.4946384429932</t>
@@ -1322,61 +1322,61 @@
     <t xml:space="preserve">16.3594341278076</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1791648864746</t>
+    <t xml:space="preserve">16.1791687011719</t>
   </si>
   <si>
     <t xml:space="preserve">16.584774017334</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5397033691406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6834239959717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0890312194824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5932931900024</t>
+    <t xml:space="preserve">16.5397071838379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6834259033203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0890331268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5932912826538</t>
   </si>
   <si>
     <t xml:space="preserve">16.2693023681641</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1255798339844</t>
+    <t xml:space="preserve">17.125581741333</t>
   </si>
   <si>
     <t xml:space="preserve">17.5762538909912</t>
   </si>
   <si>
-    <t xml:space="preserve">17.666389465332</t>
+    <t xml:space="preserve">17.6663856506348</t>
   </si>
   <si>
     <t xml:space="preserve">17.8466548919678</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5677356719971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3874645233154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7480010986328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3789463043213</t>
+    <t xml:space="preserve">18.5677337646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3874664306641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7480030059814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3789482116699</t>
   </si>
   <si>
     <t xml:space="preserve">20.0098896026611</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5506973266602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4605617523193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.280294418335</t>
+    <t xml:space="preserve">20.5506935119629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4605598449707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2802925109863</t>
   </si>
   <si>
     <t xml:space="preserve">20.3704280853271</t>
@@ -1385,19 +1385,19 @@
     <t xml:space="preserve">20.1000232696533</t>
   </si>
   <si>
-    <t xml:space="preserve">20.640832901001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7309665679932</t>
+    <t xml:space="preserve">20.6408309936523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7309646606445</t>
   </si>
   <si>
     <t xml:space="preserve">22.4435234069824</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9027156829834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5361461639404</t>
+    <t xml:space="preserve">21.9027137756348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5361442565918</t>
   </si>
   <si>
     <t xml:space="preserve">21.1695709228516</t>
@@ -1412,10 +1412,10 @@
     <t xml:space="preserve">22.4525756835938</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2692890167236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0860023498535</t>
+    <t xml:space="preserve">22.269287109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0860004425049</t>
   </si>
   <si>
     <t xml:space="preserve">21.9943599700928</t>
@@ -1424,22 +1424,22 @@
     <t xml:space="preserve">21.6277866363525</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2773628234863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9107933044434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.727502822876</t>
+    <t xml:space="preserve">23.277364730835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9107913970947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7275047302246</t>
   </si>
   <si>
     <t xml:space="preserve">22.1776466369629</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6358604431152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0024318695068</t>
+    <t xml:space="preserve">22.6358623504639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0024337768555</t>
   </si>
   <si>
     <t xml:space="preserve">23.0940780639648</t>
@@ -1448,28 +1448,28 @@
     <t xml:space="preserve">24.1021518707275</t>
   </si>
   <si>
-    <t xml:space="preserve">24.285436630249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9269428253174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2099475860596</t>
+    <t xml:space="preserve">24.2854404449463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9269409179688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2099437713623</t>
   </si>
   <si>
     <t xml:space="preserve">26.8514461517334</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6681613922119</t>
+    <t xml:space="preserve">26.6681594848633</t>
   </si>
   <si>
     <t xml:space="preserve">27.3096618652344</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4848747253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7598056793213</t>
+    <t xml:space="preserve">26.4848728179932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7598037719727</t>
   </si>
   <si>
     <t xml:space="preserve">26.5765171051025</t>
@@ -1478,31 +1478,31 @@
     <t xml:space="preserve">26.3015880584717</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5684413909912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0347328186035</t>
+    <t xml:space="preserve">25.5684432983398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0347347259521</t>
   </si>
   <si>
     <t xml:space="preserve">29.1425247192383</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4093780517578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1344528198242</t>
+    <t xml:space="preserve">28.4093818664551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1344509124756</t>
   </si>
   <si>
     <t xml:space="preserve">28.2260932922363</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3646869659424</t>
+    <t xml:space="preserve">28.3646850585938</t>
   </si>
   <si>
     <t xml:space="preserve">28.4570770263672</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0875072479248</t>
+    <t xml:space="preserve">28.0875034332275</t>
   </si>
   <si>
     <t xml:space="preserve">27.9951114654541</t>
@@ -1514,13 +1514,13 @@
     <t xml:space="preserve">27.7179317474365</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1038284301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9353694915771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.750581741333</t>
+    <t xml:space="preserve">29.1038303375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9353675842285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7505836486816</t>
   </si>
   <si>
     <t xml:space="preserve">29.3810062408447</t>
@@ -1529,31 +1529,31 @@
     <t xml:space="preserve">28.8266525268555</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9190425872803</t>
+    <t xml:space="preserve">28.9190406799316</t>
   </si>
   <si>
     <t xml:space="preserve">28.7342567443848</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0114345550537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8429756164551</t>
+    <t xml:space="preserve">29.0114364624023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8429737091064</t>
   </si>
   <si>
     <t xml:space="preserve">30.120153427124</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2125473022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0277576446533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3973369598389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1364784240723</t>
+    <t xml:space="preserve">30.2125453948975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0277614593506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3973331451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.136474609375</t>
   </si>
   <si>
     <t xml:space="preserve">30.8592987060547</t>
@@ -1562,16 +1562,16 @@
     <t xml:space="preserve">31.0440845489502</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6745128631592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4897232055664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2886161804199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4734020233154</t>
+    <t xml:space="preserve">30.6745090484619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4897270202637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2886180877686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4734001159668</t>
   </si>
   <si>
     <t xml:space="preserve">32.8919486999512</t>
@@ -1580,7 +1580,7 @@
     <t xml:space="preserve">33.3539123535156</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5550270080566</t>
+    <t xml:space="preserve">34.5550231933594</t>
   </si>
   <si>
     <t xml:space="preserve">34.0930595397949</t>
@@ -1598,40 +1598,40 @@
     <t xml:space="preserve">37.2344207763672</t>
   </si>
   <si>
-    <t xml:space="preserve">37.8811798095703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.1583480834961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.6040000915527</t>
+    <t xml:space="preserve">37.8811721801758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.1583518981934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.6039962768555</t>
   </si>
   <si>
     <t xml:space="preserve">37.6963882446289</t>
   </si>
   <si>
-    <t xml:space="preserve">37.7887878417969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.1420288085938</t>
+    <t xml:space="preserve">37.7887840270996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.142032623291</t>
   </si>
   <si>
     <t xml:space="preserve">38.5279273986816</t>
   </si>
   <si>
-    <t xml:space="preserve">38.3431396484375</t>
+    <t xml:space="preserve">38.3431434631348</t>
   </si>
   <si>
     <t xml:space="preserve">36.4952774047852</t>
   </si>
   <si>
-    <t xml:space="preserve">35.9409217834473</t>
+    <t xml:space="preserve">35.9409255981445</t>
   </si>
   <si>
     <t xml:space="preserve">36.402889251709</t>
   </si>
   <si>
-    <t xml:space="preserve">36.6800689697266</t>
+    <t xml:space="preserve">36.6800651550293</t>
   </si>
   <si>
     <t xml:space="preserve">37.9735641479492</t>
@@ -1640,19 +1640,19 @@
     <t xml:space="preserve">38.0659599304199</t>
   </si>
   <si>
-    <t xml:space="preserve">38.4355316162109</t>
+    <t xml:space="preserve">38.4355278015137</t>
   </si>
   <si>
     <t xml:space="preserve">38.8051071166992</t>
   </si>
   <si>
-    <t xml:space="preserve">39.3594627380371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.8214263916016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.006217956543</t>
+    <t xml:space="preserve">39.3594665527344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.8214302062988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.0062141418457</t>
   </si>
   <si>
     <t xml:space="preserve">40.5605735778809</t>
@@ -1661,13 +1661,13 @@
     <t xml:space="preserve">40.6529693603516</t>
   </si>
   <si>
-    <t xml:space="preserve">41.946475982666</t>
+    <t xml:space="preserve">41.9464721679688</t>
   </si>
   <si>
     <t xml:space="preserve">41.114933013916</t>
   </si>
   <si>
-    <t xml:space="preserve">40.9301452636719</t>
+    <t xml:space="preserve">40.9301490783691</t>
   </si>
   <si>
     <t xml:space="preserve">42.3160438537598</t>
@@ -1676,19 +1676,19 @@
     <t xml:space="preserve">43.5171546936035</t>
   </si>
   <si>
-    <t xml:space="preserve">44.0715103149414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.8867225646973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.7019462585449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.979118347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.3486976623535</t>
+    <t xml:space="preserve">44.0715141296387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.8867263793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.7019386291504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.9791221618652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.348690032959</t>
   </si>
   <si>
     <t xml:space="preserve">44.9954452514648</t>
@@ -1700,10 +1700,10 @@
     <t xml:space="preserve">44.5334777832031</t>
   </si>
   <si>
-    <t xml:space="preserve">43.7943344116211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.1475830078125</t>
+    <t xml:space="preserve">43.7943382263184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.1475791931152</t>
   </si>
   <si>
     <t xml:space="preserve">41.3921127319336</t>
@@ -1712,19 +1712,19 @@
     <t xml:space="preserve">41.8540802001953</t>
   </si>
   <si>
-    <t xml:space="preserve">41.5769004821777</t>
+    <t xml:space="preserve">41.5768928527832</t>
   </si>
   <si>
     <t xml:space="preserve">41.2073249816895</t>
   </si>
   <si>
-    <t xml:space="preserve">40.1910057067871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.4518623352051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.9898948669434</t>
+    <t xml:space="preserve">40.1910018920898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.4518547058105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.9898910522461</t>
   </si>
   <si>
     <t xml:space="preserve">39.1746788024902</t>
@@ -1736,157 +1736,157 @@
     <t xml:space="preserve">40.745361328125</t>
   </si>
   <si>
-    <t xml:space="preserve">41.0225410461426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.7290344238281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.9138221740723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.4681777954102</t>
+    <t xml:space="preserve">41.0225372314453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.7290382385254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.9138259887695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.4681816101074</t>
   </si>
   <si>
     <t xml:space="preserve">39.6366424560547</t>
   </si>
   <si>
-    <t xml:space="preserve">38.6203193664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.2670707702637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.3268203735352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.8974952697754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.5115966796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.7127151489258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.0822830200195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.7724571228027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.3104858398438</t>
+    <t xml:space="preserve">38.6203155517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.2670745849609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.3268165588379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.8974990844727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.5116004943848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.7127113342285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.0822868347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.7724609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.310489654541</t>
   </si>
   <si>
     <t xml:space="preserve">36.2181015014648</t>
   </si>
   <si>
-    <t xml:space="preserve">35.3865585327148</t>
+    <t xml:space="preserve">35.3865623474121</t>
   </si>
   <si>
     <t xml:space="preserve">36.0333137512207</t>
   </si>
   <si>
-    <t xml:space="preserve">34.1854476928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.7234878540039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.1691284179688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6147651672363</t>
+    <t xml:space="preserve">34.1854515075684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.7234802246094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.1691246032715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6147689819336</t>
   </si>
   <si>
     <t xml:space="preserve">33.6310958862305</t>
   </si>
   <si>
-    <t xml:space="preserve">32.7071647644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9680156707764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0604095458984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4136524200439</t>
+    <t xml:space="preserve">32.707160949707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.968017578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0604133605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4136562347412</t>
   </si>
   <si>
     <t xml:space="preserve">31.6908378601074</t>
   </si>
   <si>
-    <t xml:space="preserve">32.2451934814453</t>
+    <t xml:space="preserve">32.2451972961426</t>
   </si>
   <si>
     <t xml:space="preserve">32.7995529174805</t>
   </si>
   <si>
-    <t xml:space="preserve">33.9082679748535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.1093788146973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7398071289062</t>
+    <t xml:space="preserve">33.9082717895508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.1093826293945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7397994995117</t>
   </si>
   <si>
     <t xml:space="preserve">35.0169906616211</t>
   </si>
   <si>
-    <t xml:space="preserve">32.3375854492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4299812316895</t>
+    <t xml:space="preserve">32.337589263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4299850463867</t>
   </si>
   <si>
     <t xml:space="preserve">32.5223770141602</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5060520172119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3212661743164</t>
+    <t xml:space="preserve">31.5060539245605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3212623596191</t>
   </si>
   <si>
     <t xml:space="preserve">31.5522480010986</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9218139648438</t>
+    <t xml:space="preserve">31.9218196868896</t>
   </si>
   <si>
     <t xml:space="preserve">32.1527976989746</t>
   </si>
   <si>
-    <t xml:space="preserve">33.4925003051758</t>
+    <t xml:space="preserve">33.492504119873</t>
   </si>
   <si>
     <t xml:space="preserve">34.3702392578125</t>
   </si>
   <si>
-    <t xml:space="preserve">33.8620758056641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1066017150879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.535924911499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3511371612549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7804527282715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3643817901611</t>
+    <t xml:space="preserve">33.8620719909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1066055297852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5359230041504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3511352539062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7804546356201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3643836975098</t>
   </si>
   <si>
     <t xml:space="preserve">28.3180332183838</t>
   </si>
   <si>
-    <t xml:space="preserve">27.808219909668</t>
+    <t xml:space="preserve">27.8082180023193</t>
   </si>
   <si>
     <t xml:space="preserve">27.7618713378906</t>
@@ -1898,25 +1898,25 @@
     <t xml:space="preserve">27.9936065673828</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6424617767334</t>
+    <t xml:space="preserve">28.6424655914307</t>
   </si>
   <si>
     <t xml:space="preserve">29.5230579376221</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1255683898926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5694065093994</t>
+    <t xml:space="preserve">30.1255702972412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5694046020508</t>
   </si>
   <si>
     <t xml:space="preserve">29.105936050415</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9009113311768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7155227661133</t>
+    <t xml:space="preserve">27.9009132385254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7155246734619</t>
   </si>
   <si>
     <t xml:space="preserve">27.1130142211914</t>
@@ -1931,16 +1931,16 @@
     <t xml:space="preserve">26.1860733032227</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6031951904297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2324199676514</t>
+    <t xml:space="preserve">26.6031932830811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2324180603027</t>
   </si>
   <si>
     <t xml:space="preserve">26.556848526001</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3251132965088</t>
+    <t xml:space="preserve">26.3251113891602</t>
   </si>
   <si>
     <t xml:space="preserve">25.8152961730957</t>
@@ -1955,7 +1955,7 @@
     <t xml:space="preserve">24.7029666900635</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6566200256348</t>
+    <t xml:space="preserve">24.6566219329834</t>
   </si>
   <si>
     <t xml:space="preserve">23.9614162445068</t>
@@ -1976,7 +1976,7 @@
     <t xml:space="preserve">24.6102714538574</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3321914672852</t>
+    <t xml:space="preserve">24.3321895599365</t>
   </si>
   <si>
     <t xml:space="preserve">24.517578125</t>
@@ -1985,13 +1985,13 @@
     <t xml:space="preserve">24.3785362243652</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4712314605713</t>
+    <t xml:space="preserve">24.4712333679199</t>
   </si>
   <si>
     <t xml:space="preserve">23.8687210083008</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5442924499512</t>
+    <t xml:space="preserve">23.5442905426025</t>
   </si>
   <si>
     <t xml:space="preserve">24.100456237793</t>
@@ -2000,22 +2000,22 @@
     <t xml:space="preserve">23.4979457855225</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8223762512207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9150657653809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1931495666504</t>
+    <t xml:space="preserve">23.8223743438721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9150676727295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.193151473999</t>
   </si>
   <si>
     <t xml:space="preserve">24.888355255127</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5835628509521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9543361663818</t>
+    <t xml:space="preserve">25.5835609436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9543380737305</t>
   </si>
   <si>
     <t xml:space="preserve">26.6958885192871</t>
@@ -2024,22 +2024,22 @@
     <t xml:space="preserve">26.7885818481445</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7422351837158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.444522857666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9810485839844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.861644744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1200923919678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0077629089355</t>
+    <t xml:space="preserve">26.7422370910645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4445209503174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.981050491333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8616409301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1200904846191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0077610015869</t>
   </si>
   <si>
     <t xml:space="preserve">23.4515972137451</t>
@@ -2060,31 +2060,31 @@
     <t xml:space="preserve">23.5906391143799</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4052505493164</t>
+    <t xml:space="preserve">23.405252456665</t>
   </si>
   <si>
     <t xml:space="preserve">23.2662105560303</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3589057922363</t>
+    <t xml:space="preserve">23.3589038848877</t>
   </si>
   <si>
     <t xml:space="preserve">22.8027381896973</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6173477172852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1735134124756</t>
+    <t xml:space="preserve">22.6173496246338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1735153198242</t>
   </si>
   <si>
     <t xml:space="preserve">22.8954334259033</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9684925079346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5513687133789</t>
+    <t xml:space="preserve">21.9684944152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5513706207275</t>
   </si>
   <si>
     <t xml:space="preserve">21.273286819458</t>
@@ -2099,16 +2099,16 @@
     <t xml:space="preserve">19.9755706787109</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1609592437744</t>
+    <t xml:space="preserve">20.1609573364258</t>
   </si>
   <si>
     <t xml:space="preserve">20.2073059082031</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8365306854248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5584487915039</t>
+    <t xml:space="preserve">19.8365287780762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5584468841553</t>
   </si>
   <si>
     <t xml:space="preserve">19.604793548584</t>
@@ -2117,22 +2117,22 @@
     <t xml:space="preserve">19.9292221069336</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0682621002197</t>
+    <t xml:space="preserve">20.0682640075684</t>
   </si>
   <si>
     <t xml:space="preserve">20.1146106719971</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8098163604736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9952030181885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5780830383301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0878982543945</t>
+    <t xml:space="preserve">20.8098182678223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9952049255371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5780811309814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0878963470459</t>
   </si>
   <si>
     <t xml:space="preserve">21.5977172851562</t>
@@ -2153,16 +2153,16 @@
     <t xml:space="preserve">23.6833343505859</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5639266967773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4248847961426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1664371490479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2127857208252</t>
+    <t xml:space="preserve">24.5639247894287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4248867034912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1664390563965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2127876281738</t>
   </si>
   <si>
     <t xml:space="preserve">24.8420066833496</t>
@@ -2180,7 +2180,7 @@
     <t xml:space="preserve">25.5372123718262</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3054790496826</t>
+    <t xml:space="preserve">25.305477142334</t>
   </si>
   <si>
     <t xml:space="preserve">25.6762561798096</t>
@@ -2189,13 +2189,13 @@
     <t xml:space="preserve">25.4908676147461</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6691799163818</t>
+    <t xml:space="preserve">27.6691780090332</t>
   </si>
   <si>
     <t xml:space="preserve">27.2057075500488</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4837913513184</t>
+    <t xml:space="preserve">27.4837894439697</t>
   </si>
   <si>
     <t xml:space="preserve">27.2984027862549</t>
@@ -2219,22 +2219,22 @@
     <t xml:space="preserve">27.437442779541</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5301361083984</t>
+    <t xml:space="preserve">27.5301380157471</t>
   </si>
   <si>
     <t xml:space="preserve">26.093376159668</t>
   </si>
   <si>
-    <t xml:space="preserve">25.39817237854</t>
+    <t xml:space="preserve">25.3981742858887</t>
   </si>
   <si>
     <t xml:space="preserve">22.941780090332</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2002296447754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1538791656494</t>
+    <t xml:space="preserve">22.2002277374268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.153881072998</t>
   </si>
   <si>
     <t xml:space="preserve">22.1075344085693</t>
@@ -2246,7 +2246,7 @@
     <t xml:space="preserve">22.9881248474121</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2198638916016</t>
+    <t xml:space="preserve">23.2198619842529</t>
   </si>
   <si>
     <t xml:space="preserve">21.8294506072998</t>
@@ -2255,55 +2255,55 @@
     <t xml:space="preserve">20.6244277954102</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6707744598389</t>
+    <t xml:space="preserve">20.6707763671875</t>
   </si>
   <si>
     <t xml:space="preserve">20.485387802124</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2536506652832</t>
+    <t xml:space="preserve">20.2536544799805</t>
   </si>
   <si>
     <t xml:space="preserve">20.5317344665527</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1342449188232</t>
+    <t xml:space="preserve">21.1342430114746</t>
   </si>
   <si>
     <t xml:space="preserve">21.7831058502197</t>
   </si>
   <si>
-    <t xml:space="preserve">21.644063949585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2269382476807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.319637298584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8757991790771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.180591583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9025096893311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6679439544678</t>
+    <t xml:space="preserve">21.6440620422363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2269401550293</t>
   </si>
   <si>
     <t xml:space="preserve">21.3196353912354</t>
   </si>
   <si>
+    <t xml:space="preserve">21.8757972717285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1805934906006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9025077819824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6679420471191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3196334838867</t>
+  </si>
+  <si>
     <t xml:space="preserve">21.4127311706543</t>
   </si>
   <si>
     <t xml:space="preserve">20.6213912963867</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5748424530029</t>
+    <t xml:space="preserve">20.5748443603516</t>
   </si>
   <si>
     <t xml:space="preserve">20.3886451721191</t>
@@ -2312,16 +2312,16 @@
     <t xml:space="preserve">21.3661842346191</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9937858581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9006881713867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0403385162354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1799869537354</t>
+    <t xml:space="preserve">20.9937877655029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9006900787354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0403366088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1799850463867</t>
   </si>
   <si>
     <t xml:space="preserve">21.2265338897705</t>
@@ -2330,13 +2330,13 @@
     <t xml:space="preserve">20.9472389221191</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4817428588867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3420944213867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2489967346191</t>
+    <t xml:space="preserve">20.4817447662354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3420963287354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2489986419678</t>
   </si>
   <si>
     <t xml:space="preserve">20.1558990478516</t>
@@ -2372,7 +2372,7 @@
     <t xml:space="preserve">19.5507564544678</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2024459838867</t>
+    <t xml:space="preserve">20.2024478912354</t>
   </si>
   <si>
     <t xml:space="preserve">20.4351959228516</t>
@@ -2381,10 +2381,10 @@
     <t xml:space="preserve">19.4576568603516</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0387115478516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9697017669678</t>
+    <t xml:space="preserve">19.0387134552002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9696998596191</t>
   </si>
   <si>
     <t xml:space="preserve">19.9231510162354</t>
@@ -2402,10 +2402,10 @@
     <t xml:space="preserve">19.1318111419678</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6197681427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8525161743164</t>
+    <t xml:space="preserve">18.6197662353516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8525123596191</t>
   </si>
   <si>
     <t xml:space="preserve">18.7128677368164</t>
@@ -2414,7 +2414,7 @@
     <t xml:space="preserve">18.6663150787354</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7594165802002</t>
+    <t xml:space="preserve">18.7594146728516</t>
   </si>
   <si>
     <t xml:space="preserve">18.5266666412354</t>
@@ -2423,16 +2423,16 @@
     <t xml:space="preserve">18.4708099365234</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3963298797607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3404731750488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2287521362305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.210132598877</t>
+    <t xml:space="preserve">18.3963317871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3404712677002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2287540435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2101306915283</t>
   </si>
   <si>
     <t xml:space="preserve">17.968074798584</t>
@@ -2462,16 +2462,16 @@
     <t xml:space="preserve">16.7577896118164</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2232837677002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3350048065186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4094829559326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.651538848877</t>
+    <t xml:space="preserve">17.2232856750488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3350028991699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.409481048584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6515369415283</t>
   </si>
   <si>
     <t xml:space="preserve">17.7260189056396</t>
@@ -2486,13 +2486,13 @@
     <t xml:space="preserve">17.2605247497559</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2419052124023</t>
+    <t xml:space="preserve">17.2419033050537</t>
   </si>
   <si>
     <t xml:space="preserve">16.5715923309326</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5529747009277</t>
+    <t xml:space="preserve">16.5529727935791</t>
   </si>
   <si>
     <t xml:space="preserve">17.0929470062256</t>
@@ -2501,7 +2501,7 @@
     <t xml:space="preserve">16.9253673553467</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2736778259277</t>
+    <t xml:space="preserve">16.2736759185791</t>
   </si>
   <si>
     <t xml:space="preserve">16.0130004882812</t>
@@ -2510,16 +2510,16 @@
     <t xml:space="preserve">15.9757604598999</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2364368438721</t>
+    <t xml:space="preserve">16.2364387512207</t>
   </si>
   <si>
     <t xml:space="preserve">16.2922973632812</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0370864868164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8136501312256</t>
+    <t xml:space="preserve">17.037088394165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.813648223877</t>
   </si>
   <si>
     <t xml:space="preserve">16.404016494751</t>
@@ -2534,19 +2534,19 @@
     <t xml:space="preserve">16.1805782318115</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3667736053467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4598731994629</t>
+    <t xml:space="preserve">16.3667755126953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4598751068115</t>
   </si>
   <si>
     <t xml:space="preserve">15.7709436416626</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7337036132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.882661819458</t>
+    <t xml:space="preserve">15.7337017059326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8826608657837</t>
   </si>
   <si>
     <t xml:space="preserve">16.161958694458</t>
@@ -2564,10 +2564,10 @@
     <t xml:space="preserve">16.6460704803467</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8695087432861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1115646362305</t>
+    <t xml:space="preserve">16.8695106506348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1115665435791</t>
   </si>
   <si>
     <t xml:space="preserve">17.0184669494629</t>
@@ -2576,22 +2576,22 @@
     <t xml:space="preserve">17.0557060241699</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4839630126953</t>
+    <t xml:space="preserve">17.4839611053467</t>
   </si>
   <si>
     <t xml:space="preserve">17.3536224365234</t>
   </si>
   <si>
-    <t xml:space="preserve">17.372241973877</t>
+    <t xml:space="preserve">17.3722438812256</t>
   </si>
   <si>
     <t xml:space="preserve">16.9998474121094</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0743274688721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.683313369751</t>
+    <t xml:space="preserve">17.0743255615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6833114624023</t>
   </si>
   <si>
     <t xml:space="preserve">16.8881282806396</t>
@@ -2600,7 +2600,7 @@
     <t xml:space="preserve">16.6646919250488</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7205486297607</t>
+    <t xml:space="preserve">16.7205505371094</t>
   </si>
   <si>
     <t xml:space="preserve">16.8322696685791</t>
@@ -2612,19 +2612,19 @@
     <t xml:space="preserve">16.5902118682861</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3481540679932</t>
+    <t xml:space="preserve">16.3481559753418</t>
   </si>
   <si>
     <t xml:space="preserve">16.3109169006348</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1991958618164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6088314056396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0502395629883</t>
+    <t xml:space="preserve">16.199197769165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6088333129883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0502376556396</t>
   </si>
   <si>
     <t xml:space="preserve">16.2550563812256</t>
@@ -2636,19 +2636,19 @@
     <t xml:space="preserve">17.1674251556396</t>
   </si>
   <si>
-    <t xml:space="preserve">18.005313873291</t>
+    <t xml:space="preserve">18.0053157806396</t>
   </si>
   <si>
     <t xml:space="preserve">17.9122161865234</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4653415679932</t>
+    <t xml:space="preserve">17.4653434753418</t>
   </si>
   <si>
     <t xml:space="preserve">17.9494571685791</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8749752044678</t>
+    <t xml:space="preserve">17.8749771118164</t>
   </si>
   <si>
     <t xml:space="preserve">17.6422309875488</t>
@@ -2657,16 +2657,16 @@
     <t xml:space="preserve">17.5491313934326</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3629322052002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5025806427002</t>
+    <t xml:space="preserve">17.3629341125488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5025787353516</t>
   </si>
   <si>
     <t xml:space="preserve">17.4560317993164</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1542720794678</t>
+    <t xml:space="preserve">18.1542739868164</t>
   </si>
   <si>
     <t xml:space="preserve">18.0611743927002</t>
@@ -68358,7 +68358,7 @@
     </row>
     <row r="2502">
       <c r="A2502" s="1" t="n">
-        <v>45961.6911226852</v>
+        <v>45961.3333333333</v>
       </c>
       <c r="B2502" t="n">
         <v>3534</v>
@@ -68379,6 +68379,32 @@
         <v>993</v>
       </c>
       <c r="H2502" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2503">
+      <c r="A2503" s="1" t="n">
+        <v>45964.6911689815</v>
+      </c>
+      <c r="B2503" t="n">
+        <v>7141</v>
+      </c>
+      <c r="C2503" t="n">
+        <v>22.7000007629395</v>
+      </c>
+      <c r="D2503" t="n">
+        <v>22.3999996185303</v>
+      </c>
+      <c r="E2503" t="n">
+        <v>22.6000003814697</v>
+      </c>
+      <c r="F2503" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="G2503" t="s">
+        <v>982</v>
+      </c>
+      <c r="H2503" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IWB.MI.xlsx
+++ b/data/IWB.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="995" uniqueCount="995">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="994" uniqueCount="994">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,25 +38,25 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84661674499512</t>
+    <t xml:space="preserve">7.84661769866943</t>
   </si>
   <si>
     <t xml:space="preserve">IWB.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79867219924927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8306360244751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74273920059204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75073003768921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71077919006348</t>
+    <t xml:space="preserve">7.79867601394653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83063507080078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7427396774292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75073051452637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71077823638916</t>
   </si>
   <si>
     <t xml:space="preserve">7.69479846954346</t>
@@ -65,7 +65,7 @@
     <t xml:space="preserve">7.59092140197754</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5110182762146</t>
+    <t xml:space="preserve">7.51101732254028</t>
   </si>
   <si>
     <t xml:space="preserve">7.31125593185425</t>
@@ -74,52 +74,52 @@
     <t xml:space="preserve">7.44709444046021</t>
   </si>
   <si>
-    <t xml:space="preserve">7.35120820999146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29527568817139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26331281661987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29927158355713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29127979278564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27130651473999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24733352661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37517881393433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4311146736145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47106504440308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1514458656311</t>
+    <t xml:space="preserve">7.35120916366577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2952766418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26331424713135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29927062988281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29128122329712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27130365371704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24733304977417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37517976760864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43111276626587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47106552124023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15144824981689</t>
   </si>
   <si>
     <t xml:space="preserve">7.41513156890869</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3272385597229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28728485107422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99163961410522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11149549484253</t>
+    <t xml:space="preserve">7.32723808288574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28728532791138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99164009094238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11149501800537</t>
   </si>
   <si>
     <t xml:space="preserve">7.19140005111694</t>
@@ -128,133 +128,133 @@
     <t xml:space="preserve">7.25532388687134</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41912889480591</t>
+    <t xml:space="preserve">7.41912698745728</t>
   </si>
   <si>
     <t xml:space="preserve">7.42312288284302</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6308741569519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67082834243774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49903297424316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58293151855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89456033706665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98644971847534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91053867340088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54297971725464</t>
+    <t xml:space="preserve">7.63087368011475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67082643508911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49903154373169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58293104171753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89455842971802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98644781112671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9105396270752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54297876358032</t>
   </si>
   <si>
     <t xml:space="preserve">7.82264471054077</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6428599357605</t>
+    <t xml:space="preserve">7.64285945892334</t>
   </si>
   <si>
     <t xml:space="preserve">7.62288427352905</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77470111846924</t>
+    <t xml:space="preserve">7.77470207214355</t>
   </si>
   <si>
     <t xml:space="preserve">7.7667121887207</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79068422317505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87058925628662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96647548675537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71876955032349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66283655166626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57094669342041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55896186828613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39116144180298</t>
+    <t xml:space="preserve">7.79068183898926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87058734893799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96647357940674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71876859664917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66283559799194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57094621658325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55896091461182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39116096496582</t>
   </si>
   <si>
     <t xml:space="preserve">7.46307563781738</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60690259933472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54697418212891</t>
+    <t xml:space="preserve">7.60690450668335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54697561264038</t>
   </si>
   <si>
     <t xml:space="preserve">7.36718940734863</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31525182723999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33123445510864</t>
+    <t xml:space="preserve">7.31525039672852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33123302459717</t>
   </si>
   <si>
     <t xml:space="preserve">7.34721374511719</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50302791595459</t>
+    <t xml:space="preserve">7.50302839279175</t>
   </si>
   <si>
     <t xml:space="preserve">7.24333810806274</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22336292266846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23934316635132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4590802192688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46707153320312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10350561141968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89974880218506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91173458099365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95168828964233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0076208114624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87178325653076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87577772140503</t>
+    <t xml:space="preserve">7.22336196899414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23934268951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45907974243164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46706962585449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10350513458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89974975585938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91173553466797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95168781280518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00762033462524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8717827796936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87577676773071</t>
   </si>
   <si>
     <t xml:space="preserve">6.8797721862793</t>
@@ -263,85 +263,85 @@
     <t xml:space="preserve">6.8677864074707</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75192499160767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74393463134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82383918762207</t>
+    <t xml:space="preserve">6.75192642211914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74393367767334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82383823394775</t>
   </si>
   <si>
     <t xml:space="preserve">6.6640305519104</t>
   </si>
   <si>
-    <t xml:space="preserve">6.83183097839355</t>
+    <t xml:space="preserve">6.83183002471924</t>
   </si>
   <si>
     <t xml:space="preserve">6.89575290679932</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0315899848938</t>
+    <t xml:space="preserve">7.03159189224243</t>
   </si>
   <si>
     <t xml:space="preserve">7.07154369354248</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33522844314575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25931739807129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17941379547119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26731014251709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23135232925415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09551572799683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18340969085693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18740510940552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20738124847412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14345693588257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1234827041626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23534870147705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74673557281494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83462953567505</t>
+    <t xml:space="preserve">7.33522796630859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25931787490845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17941331863403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26730966567993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23135089874268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09551429748535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18340826034546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1874041557312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20738220214844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14345788955688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12348175048828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23534774780273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74673652648926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83463048934937</t>
   </si>
   <si>
     <t xml:space="preserve">7.98245334625244</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92652034759521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78269290924072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63886404037476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73475217819214</t>
+    <t xml:space="preserve">7.92652130126953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78269243240356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63886451721191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73474979400635</t>
   </si>
   <si>
     <t xml:space="preserve">8.07034969329834</t>
@@ -350,46 +350,46 @@
     <t xml:space="preserve">8.21417617797852</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16623306274414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18221473693848</t>
+    <t xml:space="preserve">8.16623497009277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18221282958984</t>
   </si>
   <si>
     <t xml:space="preserve">8.27011108398438</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57374668121338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54977512359619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35001373291016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46987056732178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.525803565979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50982189178467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59771823883057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60570907592773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58173751831055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64687252044678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67129898071289</t>
+    <t xml:space="preserve">8.5737476348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54977607727051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35001468658447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46987152099609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52580261230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50982284545898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59771919250488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60570812225342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58173847198486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64687156677246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67130088806152</t>
   </si>
   <si>
     <t xml:space="preserve">8.61430644989014</t>
@@ -401,10 +401,10 @@
     <t xml:space="preserve">8.75272083282471</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82600021362305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87485122680664</t>
+    <t xml:space="preserve">8.82599830627441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87485027313232</t>
   </si>
   <si>
     <t xml:space="preserve">8.95627117156982</t>
@@ -413,40 +413,40 @@
     <t xml:space="preserve">8.74457836151123</t>
   </si>
   <si>
-    <t xml:space="preserve">8.858567237854</t>
+    <t xml:space="preserve">8.85856819152832</t>
   </si>
   <si>
     <t xml:space="preserve">8.84228324890137</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91556167602539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03769397735596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00512504577637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9481315612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99698352813721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1272554397583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19239139556885</t>
+    <t xml:space="preserve">8.91556262969971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03769302368164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00512409210205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94812965393066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99698257446289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12725639343262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19239044189453</t>
   </si>
   <si>
     <t xml:space="preserve">9.11911296844482</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14353942871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98069763183594</t>
+    <t xml:space="preserve">9.14354038238525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98069858551025</t>
   </si>
   <si>
     <t xml:space="preserve">9.13539791107178</t>
@@ -458,10 +458,10 @@
     <t xml:space="preserve">9.15982341766357</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18424892425537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15168190002441</t>
+    <t xml:space="preserve">9.184250831604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15168285369873</t>
   </si>
   <si>
     <t xml:space="preserve">9.07026195526123</t>
@@ -470,31 +470,31 @@
     <t xml:space="preserve">8.96441459655762</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92370414733887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80157375335693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79343128204346</t>
+    <t xml:space="preserve">8.92370510101318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80157279968262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79343223571777</t>
   </si>
   <si>
     <t xml:space="preserve">8.8667106628418</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90742015838623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89113712310791</t>
+    <t xml:space="preserve">8.9074182510376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89113521575928</t>
   </si>
   <si>
     <t xml:space="preserve">9.11097240447998</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20053482055664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28195285797119</t>
+    <t xml:space="preserve">9.20053291320801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28195381164551</t>
   </si>
   <si>
     <t xml:space="preserve">9.35523414611816</t>
@@ -509,31 +509,31 @@
     <t xml:space="preserve">9.64834785461426</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60763931274414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90075302124023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99031448364258</t>
+    <t xml:space="preserve">9.60763740539551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90075206756592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99031639099121</t>
   </si>
   <si>
     <t xml:space="preserve">10.120587348938</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1368722915649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1775827407837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1043043136597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1531553268433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0961608886719</t>
+    <t xml:space="preserve">10.1368732452393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.177583694458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1043033599854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1531562805176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0961599349976</t>
   </si>
   <si>
     <t xml:space="preserve">9.94146251678467</t>
@@ -542,109 +542,109 @@
     <t xml:space="preserve">9.90889453887939</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77048015594482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83561515808105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91703510284424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79490566253662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77862071990967</t>
+    <t xml:space="preserve">9.77047920227051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83561611175537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91703701019287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7949047088623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77862167358398</t>
   </si>
   <si>
     <t xml:space="preserve">9.78676414489746</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95774459838867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0147399902344</t>
+    <t xml:space="preserve">9.9577465057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0147409439087</t>
   </si>
   <si>
     <t xml:space="preserve">9.99845695495605</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88446998596191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86004257202148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85189914703369</t>
+    <t xml:space="preserve">9.88446807861328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86004161834717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85190010070801</t>
   </si>
   <si>
     <t xml:space="preserve">9.89260864257812</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2590026855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.340425491333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4625539779663</t>
+    <t xml:space="preserve">10.2590036392212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3404226303101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4625568389893</t>
   </si>
   <si>
     <t xml:space="preserve">10.5276918411255</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5765438079834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5439748764038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5358333587646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5032663345337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5521173477173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3485651016235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4381275177002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3241395950317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3811349868774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3648490905762</t>
+    <t xml:space="preserve">10.5765428543091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5439758300781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5358324050903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5032644271851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5521183013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3485670089722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4381265640259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3241386413574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3811359405518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3648500442505</t>
   </si>
   <si>
     <t xml:space="preserve">10.4218444824219</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4137020111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.372989654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3892765045166</t>
+    <t xml:space="preserve">10.4137029647827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.372992515564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3892774581909</t>
   </si>
   <si>
     <t xml:space="preserve">10.2915716171265</t>
   </si>
   <si>
-    <t xml:space="preserve">10.267144203186</t>
+    <t xml:space="preserve">10.2671432495117</t>
   </si>
   <si>
     <t xml:space="preserve">10.2264356613159</t>
   </si>
   <si>
-    <t xml:space="preserve">10.193865776062</t>
+    <t xml:space="preserve">10.1938667297363</t>
   </si>
   <si>
     <t xml:space="preserve">10.3159971237183</t>
@@ -653,109 +653,109 @@
     <t xml:space="preserve">10.2182931900024</t>
   </si>
   <si>
-    <t xml:space="preserve">10.283429145813</t>
+    <t xml:space="preserve">10.2834300994873</t>
   </si>
   <si>
     <t xml:space="preserve">10.4299869537354</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3322811126709</t>
+    <t xml:space="preserve">10.3322801589966</t>
   </si>
   <si>
     <t xml:space="preserve">10.2427196502686</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5846853256226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6661081314087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7068176269531</t>
+    <t xml:space="preserve">10.5846872329712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6661062240601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7068157196045</t>
   </si>
   <si>
     <t xml:space="preserve">10.7475261688232</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7882375717163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6253967285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8696575164795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8289470672607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0324993133545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2360525131226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4396018981934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6838655471802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0732116699219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9917898178101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1546306610107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3174695968628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2767610549927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1953411102295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3581819534302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4839191436768</t>
+    <t xml:space="preserve">10.788236618042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6253938674927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8696565628052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8289480209351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0324983596802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2360506057739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.439600944519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6838636398315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0732097625732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9917888641357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1546297073364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3174715042114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.276762008667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1953420639038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3581809997559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4839181900024</t>
   </si>
   <si>
     <t xml:space="preserve">11.5258302688599</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5677423477173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4000959396362</t>
+    <t xml:space="preserve">11.567741394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4000940322876</t>
   </si>
   <si>
     <t xml:space="preserve">11.0228853225708</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1486206054688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2324447631836</t>
+    <t xml:space="preserve">11.1486196517944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2324457168579</t>
   </si>
   <si>
     <t xml:space="preserve">11.1905336380005</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2743577957153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8971481323242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0647954940796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.442006111145</t>
+    <t xml:space="preserve">11.2743558883667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8971500396729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0647964477539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4420051574707</t>
   </si>
   <si>
     <t xml:space="preserve">10.8552360534668</t>
@@ -764,7 +764,7 @@
     <t xml:space="preserve">10.6875886917114</t>
   </si>
   <si>
-    <t xml:space="preserve">11.325475692749</t>
+    <t xml:space="preserve">11.3254747390747</t>
   </si>
   <si>
     <t xml:space="preserve">11.2822465896606</t>
@@ -776,91 +776,91 @@
     <t xml:space="preserve">11.0228862762451</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2390203475952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1525650024414</t>
+    <t xml:space="preserve">11.2390213012695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.15256690979</t>
   </si>
   <si>
     <t xml:space="preserve">10.9364309310913</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0661125183105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1093406677246</t>
+    <t xml:space="preserve">11.0661115646362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1093416213989</t>
   </si>
   <si>
     <t xml:space="preserve">10.9796581268311</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7635231018066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5906133651733</t>
+    <t xml:space="preserve">10.7635221481323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5906162261963</t>
   </si>
   <si>
     <t xml:space="preserve">10.8499774932861</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7202949523926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6770687103271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8067502975464</t>
+    <t xml:space="preserve">10.7202959060669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6770706176758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.806752204895</t>
   </si>
   <si>
     <t xml:space="preserve">10.8932046890259</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6338424682617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4119262695312</t>
+    <t xml:space="preserve">10.6338415145874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4119272232056</t>
   </si>
   <si>
     <t xml:space="preserve">11.4551553726196</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3687000274658</t>
+    <t xml:space="preserve">11.3687009811401</t>
   </si>
   <si>
     <t xml:space="preserve">11.5416097640991</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6280632019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5848360061646</t>
+    <t xml:space="preserve">11.62806224823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5848369598389</t>
   </si>
   <si>
     <t xml:space="preserve">10.4609346389771</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3312530517578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3744802474976</t>
+    <t xml:space="preserve">10.3312520980835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3744812011719</t>
   </si>
   <si>
     <t xml:space="preserve">10.2880258560181</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5041618347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0286645889282</t>
+    <t xml:space="preserve">10.5041608810425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0286636352539</t>
   </si>
   <si>
     <t xml:space="preserve">9.94221115112305</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59639263153076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63961982727051</t>
+    <t xml:space="preserve">9.59639358520508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63962078094482</t>
   </si>
   <si>
     <t xml:space="preserve">9.81252956390381</t>
@@ -872,16 +872,16 @@
     <t xml:space="preserve">9.55316734313965</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03444194793701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81830787658691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86153507232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77508068084717</t>
+    <t xml:space="preserve">9.03444290161133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81830883026123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86153411865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77508163452148</t>
   </si>
   <si>
     <t xml:space="preserve">9.07767009735107</t>
@@ -896,28 +896,28 @@
     <t xml:space="preserve">9.33703327178955</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29380512237549</t>
+    <t xml:space="preserve">9.29380416870117</t>
   </si>
   <si>
     <t xml:space="preserve">10.2447996139526</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68284893035889</t>
+    <t xml:space="preserve">9.68284797668457</t>
   </si>
   <si>
     <t xml:space="preserve">10.1583452224731</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98543834686279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89898300170898</t>
+    <t xml:space="preserve">9.98543739318848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89898204803467</t>
   </si>
   <si>
     <t xml:space="preserve">9.76930141448975</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72607421875</t>
+    <t xml:space="preserve">9.72607517242432</t>
   </si>
   <si>
     <t xml:space="preserve">9.46671295166016</t>
@@ -929,115 +929,115 @@
     <t xml:space="preserve">9.3802604675293</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42348670959473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.207350730896</t>
+    <t xml:space="preserve">9.42348575592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20735168457031</t>
   </si>
   <si>
     <t xml:space="preserve">10.071891784668</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2972898483276</t>
+    <t xml:space="preserve">10.2972888946533</t>
   </si>
   <si>
     <t xml:space="preserve">10.2077465057373</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1629772186279</t>
+    <t xml:space="preserve">10.1629781723022</t>
   </si>
   <si>
     <t xml:space="preserve">10.3420610427856</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4316024780273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3868312835693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1182050704956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2525186538696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.476372718811</t>
+    <t xml:space="preserve">10.431601524353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.386830329895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1182060241699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2525177001953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4763736724854</t>
   </si>
   <si>
     <t xml:space="preserve">10.6554546356201</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7897672653198</t>
+    <t xml:space="preserve">10.7897682189941</t>
   </si>
   <si>
     <t xml:space="preserve">10.7449979782104</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5659160614014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7002277374268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1031618118286</t>
+    <t xml:space="preserve">10.5659141540527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7002286911011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1031637191772</t>
   </si>
   <si>
     <t xml:space="preserve">10.9688510894775</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9240789413452</t>
+    <t xml:space="preserve">10.9240818023682</t>
   </si>
   <si>
     <t xml:space="preserve">10.8793096542358</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1479349136353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2822484970093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2374773025513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4613313674927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.327018737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1927051544189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3717889785767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4165601730347</t>
+    <t xml:space="preserve">11.1479368209839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.282247543335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.237476348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4613304138184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3270177841187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1927061080933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.371789932251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.416561126709</t>
   </si>
   <si>
     <t xml:space="preserve">11.0583944320679</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6404123306274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7299566268921</t>
+    <t xml:space="preserve">11.6404142379761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7299556732178</t>
   </si>
   <si>
     <t xml:space="preserve">11.6851854324341</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7747249603271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8194971084595</t>
+    <t xml:space="preserve">11.7747259140015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8194961547852</t>
   </si>
   <si>
     <t xml:space="preserve">11.8642683029175</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5508718490601</t>
+    <t xml:space="preserve">11.5508728027344</t>
   </si>
   <si>
     <t xml:space="preserve">11.5956430435181</t>
@@ -1049,10 +1049,10 @@
     <t xml:space="preserve">11.0136222839355</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8345403671265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9985799789429</t>
+    <t xml:space="preserve">10.8345394134521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9985790252686</t>
   </si>
   <si>
     <t xml:space="preserve">12.0881223678589</t>
@@ -1061,16 +1061,16 @@
     <t xml:space="preserve">12.0433511734009</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1328935623169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2224359512329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1776647567749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3567485809326</t>
+    <t xml:space="preserve">12.1328945159912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2224340438843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1776628494263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.356746673584</t>
   </si>
   <si>
     <t xml:space="preserve">12.2672052383423</t>
@@ -1079,10 +1079,10 @@
     <t xml:space="preserve">12.401517868042</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3119773864746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6701421737671</t>
+    <t xml:space="preserve">12.3119764328003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6701431274414</t>
   </si>
   <si>
     <t xml:space="preserve">12.6253719329834</t>
@@ -1091,34 +1091,31 @@
     <t xml:space="preserve">12.5806016921997</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6106863021851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62572765350342</t>
+    <t xml:space="preserve">10.6106843948364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6257266998291</t>
   </si>
   <si>
     <t xml:space="preserve">10.0734357833862</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0286636352539</t>
-  </si>
-  <si>
     <t xml:space="preserve">12.491060256958</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9090375900269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1626224517822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6998720169067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8789548873901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0132684707642</t>
+    <t xml:space="preserve">11.9090394973755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1626214981079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6998710632324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8789558410645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0132665634155</t>
   </si>
   <si>
     <t xml:space="preserve">14.1475801467896</t>
@@ -1127,43 +1124,43 @@
     <t xml:space="preserve">14.2371206283569</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1923522949219</t>
+    <t xml:space="preserve">14.1923503875732</t>
   </si>
   <si>
     <t xml:space="preserve">13.9237270355225</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9684972763062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7894124984741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2818908691406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8341846466064</t>
+    <t xml:space="preserve">13.9684953689575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7894134521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2818927764893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8341836929321</t>
   </si>
   <si>
     <t xml:space="preserve">13.520788192749</t>
   </si>
   <si>
-    <t xml:space="preserve">13.431245803833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5655584335327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.610330581665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7004652023315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.790599822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8356666564941</t>
+    <t xml:space="preserve">13.4312467575073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.565559387207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6103286743164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7004632949829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7905988693237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8356657028198</t>
   </si>
   <si>
     <t xml:space="preserve">13.6553955078125</t>
@@ -1172,13 +1169,16 @@
     <t xml:space="preserve">13.5201950073242</t>
   </si>
   <si>
+    <t xml:space="preserve">13.6103296279907</t>
+  </si>
+  <si>
     <t xml:space="preserve">13.2948589324951</t>
   </si>
   <si>
     <t xml:space="preserve">13.1596574783325</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0695209503174</t>
+    <t xml:space="preserve">13.069522857666</t>
   </si>
   <si>
     <t xml:space="preserve">12.9793872833252</t>
@@ -1187,73 +1187,73 @@
     <t xml:space="preserve">12.708984375</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5737819671631</t>
+    <t xml:space="preserve">12.5737829208374</t>
   </si>
   <si>
     <t xml:space="preserve">12.6188497543335</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3399267196655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1145915985107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4751272201538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9343204498291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7540512084961</t>
+    <t xml:space="preserve">13.3399257659912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1145887374878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4751281738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9343214035034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7540502548218</t>
   </si>
   <si>
     <t xml:space="preserve">12.8441858291626</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0610036849976</t>
+    <t xml:space="preserve">14.0610027313232</t>
   </si>
   <si>
     <t xml:space="preserve">13.8807325363159</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1962051391602</t>
+    <t xml:space="preserve">14.1962060928345</t>
   </si>
   <si>
     <t xml:space="preserve">14.3314065933228</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4215421676636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3764734268188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5116767883301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.466607093811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6018114089966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6919441223145</t>
+    <t xml:space="preserve">14.4215412139893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3764743804932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5116777420044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4666080474854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6018123626709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6919450759888</t>
   </si>
   <si>
     <t xml:space="preserve">14.8722143173218</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2327518463135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0074157714844</t>
+    <t xml:space="preserve">15.2327527999878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0074167251587</t>
   </si>
   <si>
     <t xml:space="preserve">15.3228855133057</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1876850128174</t>
+    <t xml:space="preserve">15.1876859664917</t>
   </si>
   <si>
     <t xml:space="preserve">16.224235534668</t>
@@ -1265,31 +1265,31 @@
     <t xml:space="preserve">16.8551769256592</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3143711090088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9903774261475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8101100921631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7565231323242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0269260406494</t>
+    <t xml:space="preserve">16.3143672943115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9903812408447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8101081848145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7565212249756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0269241333008</t>
   </si>
   <si>
     <t xml:space="preserve">17.9367923736572</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3509178161621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4410533905029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.486120223999</t>
+    <t xml:space="preserve">17.3509159088135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4410552978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4861183166504</t>
   </si>
   <si>
     <t xml:space="preserve">17.0354442596436</t>
@@ -1301,10 +1301,10 @@
     <t xml:space="preserve">16.7199745178223</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4045028686523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6749076843262</t>
+    <t xml:space="preserve">16.404504776001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6749057769775</t>
   </si>
   <si>
     <t xml:space="preserve">16.9453105926514</t>
@@ -1313,55 +1313,55 @@
     <t xml:space="preserve">16.7650413513184</t>
   </si>
   <si>
-    <t xml:space="preserve">15.863697052002</t>
+    <t xml:space="preserve">15.8636951446533</t>
   </si>
   <si>
     <t xml:space="preserve">15.9988975524902</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4946365356445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3594360351562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1791687011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5847721099854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5397033691406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6834268569946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0890312194824</t>
+    <t xml:space="preserve">16.4946384429932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3594341278076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1791706085205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5847702026367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5397052764893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6834287643433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0890331268311</t>
   </si>
   <si>
     <t xml:space="preserve">15.5932912826538</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2693004608154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.125581741333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5762538909912</t>
+    <t xml:space="preserve">16.2693023681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1255798339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5762519836426</t>
   </si>
   <si>
     <t xml:space="preserve">17.666389465332</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8466567993164</t>
+    <t xml:space="preserve">17.8466548919678</t>
   </si>
   <si>
     <t xml:space="preserve">18.5677337646484</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3874664306641</t>
+    <t xml:space="preserve">18.3874683380127</t>
   </si>
   <si>
     <t xml:space="preserve">18.7480030059814</t>
@@ -1373,46 +1373,46 @@
     <t xml:space="preserve">20.0098876953125</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5506935119629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4605598449707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2802925109863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3704261779785</t>
+    <t xml:space="preserve">20.5506954193115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4605617523193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.280294418335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3704280853271</t>
   </si>
   <si>
     <t xml:space="preserve">20.1000213623047</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6408309936523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7309665679932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4435234069824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.902717590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5361461639404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1695709228516</t>
+    <t xml:space="preserve">20.6408290863037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7309646606445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4435253143311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9027156829834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5361442565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1695728302002</t>
   </si>
   <si>
     <t xml:space="preserve">21.7194328308105</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3609313964844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4525737762451</t>
+    <t xml:space="preserve">22.360933303833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4525756835938</t>
   </si>
   <si>
     <t xml:space="preserve">22.2692890167236</t>
@@ -1421,13 +1421,13 @@
     <t xml:space="preserve">22.0860042572021</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9943599700928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6277885437012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.277364730835</t>
+    <t xml:space="preserve">21.9943580627441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6277866363525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2773628234863</t>
   </si>
   <si>
     <t xml:space="preserve">22.9107894897461</t>
@@ -1448,28 +1448,28 @@
     <t xml:space="preserve">23.0940799713135</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1021518707275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2854385375977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9269409179688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2099437713623</t>
+    <t xml:space="preserve">24.1021499633789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.285436630249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9269390106201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2099456787109</t>
   </si>
   <si>
     <t xml:space="preserve">26.851448059082</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6681613922119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.309663772583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4848728179932</t>
+    <t xml:space="preserve">26.6681594848633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3096618652344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4848709106445</t>
   </si>
   <si>
     <t xml:space="preserve">26.7598037719727</t>
@@ -1478,34 +1478,34 @@
     <t xml:space="preserve">26.5765171051025</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3015899658203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5684432983398</t>
+    <t xml:space="preserve">26.3015880584717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5684413909912</t>
   </si>
   <si>
     <t xml:space="preserve">27.0347328186035</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1425266265869</t>
+    <t xml:space="preserve">29.1425247192383</t>
   </si>
   <si>
     <t xml:space="preserve">28.4093818664551</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1344509124756</t>
+    <t xml:space="preserve">28.1344528198242</t>
   </si>
   <si>
     <t xml:space="preserve">28.2260932922363</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3646831512451</t>
+    <t xml:space="preserve">28.3646850585938</t>
   </si>
   <si>
     <t xml:space="preserve">28.4570770263672</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0875034332275</t>
+    <t xml:space="preserve">28.0875053405762</t>
   </si>
   <si>
     <t xml:space="preserve">27.9951114654541</t>
@@ -1526,10 +1526,10 @@
     <t xml:space="preserve">29.750581741333</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3810081481934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8266506195068</t>
+    <t xml:space="preserve">29.3810062408447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8266525268555</t>
   </si>
   <si>
     <t xml:space="preserve">28.9190425872803</t>
@@ -1538,37 +1538,37 @@
     <t xml:space="preserve">28.7342567443848</t>
   </si>
   <si>
-    <t xml:space="preserve">29.011438369751</t>
+    <t xml:space="preserve">29.0114364624023</t>
   </si>
   <si>
     <t xml:space="preserve">29.8429737091064</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1201496124268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2125473022461</t>
+    <t xml:space="preserve">30.1201515197754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2125453948975</t>
   </si>
   <si>
     <t xml:space="preserve">30.027759552002</t>
   </si>
   <si>
-    <t xml:space="preserve">30.397331237793</t>
+    <t xml:space="preserve">30.3973331451416</t>
   </si>
   <si>
     <t xml:space="preserve">31.136474609375</t>
   </si>
   <si>
-    <t xml:space="preserve">30.8592987060547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0440807342529</t>
+    <t xml:space="preserve">30.8592967987061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0440826416016</t>
   </si>
   <si>
     <t xml:space="preserve">30.6745109558105</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4897270202637</t>
+    <t xml:space="preserve">30.489725112915</t>
   </si>
   <si>
     <t xml:space="preserve">29.2886180877686</t>
@@ -1583,10 +1583,10 @@
     <t xml:space="preserve">33.3539123535156</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5550231933594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0930595397949</t>
+    <t xml:space="preserve">34.5550193786621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0930557250977</t>
   </si>
   <si>
     <t xml:space="preserve">35.8485260009766</t>
@@ -1598,13 +1598,13 @@
     <t xml:space="preserve">40.0986099243164</t>
   </si>
   <si>
-    <t xml:space="preserve">37.2344169616699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.881175994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.1583557128906</t>
+    <t xml:space="preserve">37.2344245910645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.8811721801758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.1583518981934</t>
   </si>
   <si>
     <t xml:space="preserve">37.6039924621582</t>
@@ -1619,10 +1619,10 @@
     <t xml:space="preserve">37.1420288085938</t>
   </si>
   <si>
-    <t xml:space="preserve">38.5279273986816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.3431396484375</t>
+    <t xml:space="preserve">38.5279235839844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.3431358337402</t>
   </si>
   <si>
     <t xml:space="preserve">36.4952774047852</t>
@@ -1631,7 +1631,7 @@
     <t xml:space="preserve">35.9409217834473</t>
   </si>
   <si>
-    <t xml:space="preserve">36.4028854370117</t>
+    <t xml:space="preserve">36.402889251709</t>
   </si>
   <si>
     <t xml:space="preserve">36.6800651550293</t>
@@ -1640,7 +1640,7 @@
     <t xml:space="preserve">37.9735641479492</t>
   </si>
   <si>
-    <t xml:space="preserve">38.0659637451172</t>
+    <t xml:space="preserve">38.0659599304199</t>
   </si>
   <si>
     <t xml:space="preserve">38.4355316162109</t>
@@ -1673,13 +1673,13 @@
     <t xml:space="preserve">40.9301452636719</t>
   </si>
   <si>
-    <t xml:space="preserve">42.3160400390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.5171546936035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.0715179443359</t>
+    <t xml:space="preserve">42.3160438537598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.5171508789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.0715141296387</t>
   </si>
   <si>
     <t xml:space="preserve">43.8867263793945</t>
@@ -1703,10 +1703,10 @@
     <t xml:space="preserve">44.5334815979004</t>
   </si>
   <si>
-    <t xml:space="preserve">43.7943382263184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.1475868225098</t>
+    <t xml:space="preserve">43.7943344116211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.1475830078125</t>
   </si>
   <si>
     <t xml:space="preserve">41.3921089172363</t>
@@ -1715,10 +1715,10 @@
     <t xml:space="preserve">41.8540725708008</t>
   </si>
   <si>
-    <t xml:space="preserve">41.5769004821777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.2073249816895</t>
+    <t xml:space="preserve">41.5768966674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.2073287963867</t>
   </si>
   <si>
     <t xml:space="preserve">40.1910018920898</t>
@@ -1736,13 +1736,13 @@
     <t xml:space="preserve">39.5442543029785</t>
   </si>
   <si>
-    <t xml:space="preserve">40.7453575134277</t>
+    <t xml:space="preserve">40.745361328125</t>
   </si>
   <si>
     <t xml:space="preserve">41.0225410461426</t>
   </si>
   <si>
-    <t xml:space="preserve">39.7290344238281</t>
+    <t xml:space="preserve">39.7290382385254</t>
   </si>
   <si>
     <t xml:space="preserve">39.9138259887695</t>
@@ -1751,13 +1751,13 @@
     <t xml:space="preserve">40.4681777954102</t>
   </si>
   <si>
-    <t xml:space="preserve">39.636646270752</t>
+    <t xml:space="preserve">39.6366424560547</t>
   </si>
   <si>
     <t xml:space="preserve">38.6203193664551</t>
   </si>
   <si>
-    <t xml:space="preserve">39.2670707702637</t>
+    <t xml:space="preserve">39.2670745849609</t>
   </si>
   <si>
     <t xml:space="preserve">37.3268165588379</t>
@@ -1766,16 +1766,16 @@
     <t xml:space="preserve">38.8974990844727</t>
   </si>
   <si>
-    <t xml:space="preserve">37.5115966796875</t>
+    <t xml:space="preserve">37.5116004943848</t>
   </si>
   <si>
     <t xml:space="preserve">38.7127151489258</t>
   </si>
   <si>
-    <t xml:space="preserve">39.0822906494141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.7724533081055</t>
+    <t xml:space="preserve">39.0822868347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.7724571228027</t>
   </si>
   <si>
     <t xml:space="preserve">36.310489654541</t>
@@ -1796,16 +1796,16 @@
     <t xml:space="preserve">33.7234840393066</t>
   </si>
   <si>
-    <t xml:space="preserve">33.169132232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6147689819336</t>
+    <t xml:space="preserve">33.1691284179688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6147651672363</t>
   </si>
   <si>
     <t xml:space="preserve">33.6310958862305</t>
   </si>
   <si>
-    <t xml:space="preserve">32.707160949707</t>
+    <t xml:space="preserve">32.7071647644043</t>
   </si>
   <si>
     <t xml:space="preserve">31.9680156707764</t>
@@ -1817,10 +1817,10 @@
     <t xml:space="preserve">31.4136543273926</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6908378601074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2451934814453</t>
+    <t xml:space="preserve">31.6908340454102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2451972961426</t>
   </si>
   <si>
     <t xml:space="preserve">32.7995567321777</t>
@@ -1832,7 +1832,7 @@
     <t xml:space="preserve">35.1093826293945</t>
   </si>
   <si>
-    <t xml:space="preserve">34.739803314209</t>
+    <t xml:space="preserve">34.7398071289062</t>
   </si>
   <si>
     <t xml:space="preserve">35.0169868469238</t>
@@ -1841,13 +1841,13 @@
     <t xml:space="preserve">32.337589263916</t>
   </si>
   <si>
-    <t xml:space="preserve">32.4299774169922</t>
+    <t xml:space="preserve">32.4299812316895</t>
   </si>
   <si>
     <t xml:space="preserve">32.5223731994629</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5060482025146</t>
+    <t xml:space="preserve">31.5060520172119</t>
   </si>
   <si>
     <t xml:space="preserve">31.3212623596191</t>
@@ -1856,13 +1856,13 @@
     <t xml:space="preserve">31.5522480010986</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9218196868896</t>
+    <t xml:space="preserve">31.9218158721924</t>
   </si>
   <si>
     <t xml:space="preserve">32.1528015136719</t>
   </si>
   <si>
-    <t xml:space="preserve">33.4925003051758</t>
+    <t xml:space="preserve">33.492504119873</t>
   </si>
   <si>
     <t xml:space="preserve">34.3702354431152</t>
@@ -1880,10 +1880,10 @@
     <t xml:space="preserve">30.3511352539062</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7804527282715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3643836975098</t>
+    <t xml:space="preserve">28.7804546356201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3643817901611</t>
   </si>
   <si>
     <t xml:space="preserve">28.3180351257324</t>
@@ -1895,22 +1895,22 @@
     <t xml:space="preserve">27.7618713378906</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0863018035889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9936065673828</t>
+    <t xml:space="preserve">28.0862998962402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9936084747314</t>
   </si>
   <si>
     <t xml:space="preserve">28.642463684082</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5230579376221</t>
+    <t xml:space="preserve">29.5230598449707</t>
   </si>
   <si>
     <t xml:space="preserve">30.1255683898926</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5694046020508</t>
+    <t xml:space="preserve">29.5694065093994</t>
   </si>
   <si>
     <t xml:space="preserve">29.105936050415</t>
@@ -1922,16 +1922,16 @@
     <t xml:space="preserve">27.7155227661133</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1130123138428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4641532897949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4178066253662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.186071395874</t>
+    <t xml:space="preserve">27.1130142211914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4641551971436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4178085327148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1860733032227</t>
   </si>
   <si>
     <t xml:space="preserve">26.6031951904297</t>
@@ -1940,16 +1940,16 @@
     <t xml:space="preserve">26.2324180603027</t>
   </si>
   <si>
-    <t xml:space="preserve">26.556848526001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3251113891602</t>
+    <t xml:space="preserve">26.5568466186523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3251132965088</t>
   </si>
   <si>
     <t xml:space="preserve">25.8152961730957</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6299076080322</t>
+    <t xml:space="preserve">25.6299095153809</t>
   </si>
   <si>
     <t xml:space="preserve">25.2591323852539</t>
@@ -1961,7 +1961,7 @@
     <t xml:space="preserve">24.6566200256348</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9614162445068</t>
+    <t xml:space="preserve">23.9614143371582</t>
   </si>
   <si>
     <t xml:space="preserve">23.729679107666</t>
@@ -1985,7 +1985,7 @@
     <t xml:space="preserve">24.517578125</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3785381317139</t>
+    <t xml:space="preserve">24.3785362243652</t>
   </si>
   <si>
     <t xml:space="preserve">24.4712314605713</t>
@@ -2009,22 +2009,22 @@
     <t xml:space="preserve">23.9150676727295</t>
   </si>
   <si>
-    <t xml:space="preserve">24.193151473999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8883533477783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5835609436035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9543380737305</t>
+    <t xml:space="preserve">24.1931495666504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.888355255127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5835628509521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9543361663818</t>
   </si>
   <si>
     <t xml:space="preserve">26.6958885192871</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7885837554932</t>
+    <t xml:space="preserve">26.7885818481445</t>
   </si>
   <si>
     <t xml:space="preserve">26.7422370910645</t>
@@ -2033,7 +2033,7 @@
     <t xml:space="preserve">25.4445209503174</t>
   </si>
   <si>
-    <t xml:space="preserve">24.981050491333</t>
+    <t xml:space="preserve">24.9810485839844</t>
   </si>
   <si>
     <t xml:space="preserve">25.8616428375244</t>
@@ -2042,7 +2042,7 @@
     <t xml:space="preserve">25.1200923919678</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0077610015869</t>
+    <t xml:space="preserve">24.0077629089355</t>
   </si>
   <si>
     <t xml:space="preserve">23.4515972137451</t>
@@ -2054,7 +2054,7 @@
     <t xml:space="preserve">23.0808200836182</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3125553131104</t>
+    <t xml:space="preserve">23.312557220459</t>
   </si>
   <si>
     <t xml:space="preserve">23.6369876861572</t>
@@ -2063,7 +2063,7 @@
     <t xml:space="preserve">23.5906410217285</t>
   </si>
   <si>
-    <t xml:space="preserve">23.405252456665</t>
+    <t xml:space="preserve">23.4052505493164</t>
   </si>
   <si>
     <t xml:space="preserve">23.2662086486816</t>
@@ -2075,7 +2075,7 @@
     <t xml:space="preserve">22.8027400970459</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6173515319824</t>
+    <t xml:space="preserve">22.6173496246338</t>
   </si>
   <si>
     <t xml:space="preserve">23.1735153198242</t>
@@ -2084,13 +2084,13 @@
     <t xml:space="preserve">22.8954334259033</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9684944152832</t>
+    <t xml:space="preserve">21.9684925079346</t>
   </si>
   <si>
     <t xml:space="preserve">21.5513706207275</t>
   </si>
   <si>
-    <t xml:space="preserve">21.273286819458</t>
+    <t xml:space="preserve">21.2732849121094</t>
   </si>
   <si>
     <t xml:space="preserve">20.8561611175537</t>
@@ -2105,10 +2105,10 @@
     <t xml:space="preserve">20.1609573364258</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2073059082031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8365287780762</t>
+    <t xml:space="preserve">20.2073040008545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8365306854248</t>
   </si>
   <si>
     <t xml:space="preserve">19.5584487915039</t>
@@ -2120,16 +2120,16 @@
     <t xml:space="preserve">19.9292240142822</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0682621002197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1146106719971</t>
+    <t xml:space="preserve">20.0682640075684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1146125793457</t>
   </si>
   <si>
     <t xml:space="preserve">20.8098182678223</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9952049255371</t>
+    <t xml:space="preserve">20.9952030181885</t>
   </si>
   <si>
     <t xml:space="preserve">20.5780811309814</t>
@@ -2153,7 +2153,7 @@
     <t xml:space="preserve">22.3392696380615</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6833324432373</t>
+    <t xml:space="preserve">23.6833305358887</t>
   </si>
   <si>
     <t xml:space="preserve">24.5639247894287</t>
@@ -2165,7 +2165,7 @@
     <t xml:space="preserve">25.1664390563965</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2127876281738</t>
+    <t xml:space="preserve">25.2127857208252</t>
   </si>
   <si>
     <t xml:space="preserve">24.8420066833496</t>
@@ -2174,16 +2174,16 @@
     <t xml:space="preserve">25.768949508667</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7226028442383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3518257141113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5372123718262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.305477142334</t>
+    <t xml:space="preserve">25.7226009368896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.35182762146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5372142791748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3054790496826</t>
   </si>
   <si>
     <t xml:space="preserve">25.6762542724609</t>
@@ -2198,7 +2198,7 @@
     <t xml:space="preserve">27.2057075500488</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4837894439697</t>
+    <t xml:space="preserve">27.4837875366211</t>
   </si>
   <si>
     <t xml:space="preserve">27.2984027862549</t>
@@ -2210,13 +2210,13 @@
     <t xml:space="preserve">28.0399532318115</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1789932250977</t>
+    <t xml:space="preserve">28.1789951324463</t>
   </si>
   <si>
     <t xml:space="preserve">28.2716884613037</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1326484680176</t>
+    <t xml:space="preserve">28.1326465606689</t>
   </si>
   <si>
     <t xml:space="preserve">27.437442779541</t>
@@ -2231,7 +2231,7 @@
     <t xml:space="preserve">25.39817237854</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9417781829834</t>
+    <t xml:space="preserve">22.941780090332</t>
   </si>
   <si>
     <t xml:space="preserve">22.2002277374268</t>
@@ -2240,7 +2240,7 @@
     <t xml:space="preserve">22.1538791656494</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1075344085693</t>
+    <t xml:space="preserve">22.1075325012207</t>
   </si>
   <si>
     <t xml:space="preserve">22.7100448608398</t>
@@ -2249,16 +2249,16 @@
     <t xml:space="preserve">22.9881248474121</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2198619842529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8294525146484</t>
+    <t xml:space="preserve">23.2198638916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8294506072998</t>
   </si>
   <si>
     <t xml:space="preserve">20.6244277954102</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6707744598389</t>
+    <t xml:space="preserve">20.6707763671875</t>
   </si>
   <si>
     <t xml:space="preserve">20.485387802124</t>
@@ -2276,13 +2276,13 @@
     <t xml:space="preserve">21.7831058502197</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6440620422363</t>
+    <t xml:space="preserve">21.644063949585</t>
   </si>
   <si>
     <t xml:space="preserve">21.2269401550293</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3196353912354</t>
+    <t xml:space="preserve">21.3196334838867</t>
   </si>
   <si>
     <t xml:space="preserve">21.8757991790771</t>
@@ -2291,22 +2291,19 @@
     <t xml:space="preserve">21.1805934906006</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9025077819824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6679420471191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3196334838867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4127311706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6213932037354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5748443603516</t>
+    <t xml:space="preserve">20.9025096893311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6679439544678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4127330780029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6213912963867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5748424530029</t>
   </si>
   <si>
     <t xml:space="preserve">20.3886451721191</t>
@@ -2315,13 +2312,13 @@
     <t xml:space="preserve">21.3661842346191</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9937877655029</t>
+    <t xml:space="preserve">20.9937858581543</t>
   </si>
   <si>
     <t xml:space="preserve">20.9006900787354</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0403366088867</t>
+    <t xml:space="preserve">21.0403385162354</t>
   </si>
   <si>
     <t xml:space="preserve">21.1799850463867</t>
@@ -2333,22 +2330,22 @@
     <t xml:space="preserve">20.9472389221191</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4817428588867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3420944213867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2489986419678</t>
+    <t xml:space="preserve">20.4817447662354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3420963287354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2489967346191</t>
   </si>
   <si>
     <t xml:space="preserve">20.1558990478516</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0162487030029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6904048919678</t>
+    <t xml:space="preserve">20.0162506103516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6904029846191</t>
   </si>
   <si>
     <t xml:space="preserve">19.6438541412354</t>
@@ -2357,10 +2354,10 @@
     <t xml:space="preserve">19.7835025787354</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7369537353516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5973033905029</t>
+    <t xml:space="preserve">19.7369556427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5973052978516</t>
   </si>
   <si>
     <t xml:space="preserve">19.4111080169678</t>
@@ -2378,7 +2375,7 @@
     <t xml:space="preserve">20.2024478912354</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4351959228516</t>
+    <t xml:space="preserve">20.4351940155029</t>
   </si>
   <si>
     <t xml:space="preserve">19.4576568603516</t>
@@ -2390,7 +2387,7 @@
     <t xml:space="preserve">19.9697017669678</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9231491088867</t>
+    <t xml:space="preserve">19.9231510162354</t>
   </si>
   <si>
     <t xml:space="preserve">19.3645572662354</t>
@@ -2402,13 +2399,13 @@
     <t xml:space="preserve">18.8990631103516</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1318111419678</t>
+    <t xml:space="preserve">19.1318092346191</t>
   </si>
   <si>
     <t xml:space="preserve">18.6197681427002</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8525142669678</t>
+    <t xml:space="preserve">18.8525161743164</t>
   </si>
   <si>
     <t xml:space="preserve">18.7128677368164</t>
@@ -2417,13 +2414,13 @@
     <t xml:space="preserve">18.6663150787354</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7594165802002</t>
+    <t xml:space="preserve">18.7594146728516</t>
   </si>
   <si>
     <t xml:space="preserve">18.5266666412354</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4708080291748</t>
+    <t xml:space="preserve">18.4708099365234</t>
   </si>
   <si>
     <t xml:space="preserve">18.3963298797607</t>
@@ -2438,13 +2435,13 @@
     <t xml:space="preserve">18.210132598877</t>
   </si>
   <si>
-    <t xml:space="preserve">17.968074798584</t>
+    <t xml:space="preserve">17.9680728912354</t>
   </si>
   <si>
     <t xml:space="preserve">17.6701583862305</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5770606994629</t>
+    <t xml:space="preserve">17.5770587921143</t>
   </si>
   <si>
     <t xml:space="preserve">17.6887798309326</t>
@@ -2459,25 +2456,25 @@
     <t xml:space="preserve">17.3163833618164</t>
   </si>
   <si>
-    <t xml:space="preserve">17.130184173584</t>
+    <t xml:space="preserve">17.1301860809326</t>
   </si>
   <si>
     <t xml:space="preserve">16.7577896118164</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2232856750488</t>
+    <t xml:space="preserve">17.2232837677002</t>
   </si>
   <si>
     <t xml:space="preserve">17.3350048065186</t>
   </si>
   <si>
-    <t xml:space="preserve">17.409481048584</t>
+    <t xml:space="preserve">17.4094829559326</t>
   </si>
   <si>
     <t xml:space="preserve">17.651538848877</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7260189056396</t>
+    <t xml:space="preserve">17.7260208129883</t>
   </si>
   <si>
     <t xml:space="preserve">17.7073993682861</t>
@@ -2495,16 +2492,16 @@
     <t xml:space="preserve">16.5715923309326</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5529727935791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0929470062256</t>
+    <t xml:space="preserve">16.5529747009277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.092945098877</t>
   </si>
   <si>
     <t xml:space="preserve">16.9253673553467</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2736759185791</t>
+    <t xml:space="preserve">16.2736778259277</t>
   </si>
   <si>
     <t xml:space="preserve">16.0130004882812</t>
@@ -2516,13 +2513,13 @@
     <t xml:space="preserve">16.2364387512207</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2922973632812</t>
+    <t xml:space="preserve">16.2922954559326</t>
   </si>
   <si>
     <t xml:space="preserve">17.0370864868164</t>
   </si>
   <si>
-    <t xml:space="preserve">16.813648223877</t>
+    <t xml:space="preserve">16.8136501312256</t>
   </si>
   <si>
     <t xml:space="preserve">16.404016494751</t>
@@ -2534,16 +2531,16 @@
     <t xml:space="preserve">16.3295364379883</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1805782318115</t>
+    <t xml:space="preserve">16.1805763244629</t>
   </si>
   <si>
     <t xml:space="preserve">16.3667736053467</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4598751068115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7709445953369</t>
+    <t xml:space="preserve">16.4598731994629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7709426879883</t>
   </si>
   <si>
     <t xml:space="preserve">15.7337017059326</t>
@@ -2561,7 +2558,7 @@
     <t xml:space="preserve">16.5157337188721</t>
   </si>
   <si>
-    <t xml:space="preserve">16.478494644165</t>
+    <t xml:space="preserve">16.4784927368164</t>
   </si>
   <si>
     <t xml:space="preserve">16.6460704803467</t>
@@ -2576,13 +2573,13 @@
     <t xml:space="preserve">17.0184669494629</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0557079315186</t>
+    <t xml:space="preserve">17.0557060241699</t>
   </si>
   <si>
     <t xml:space="preserve">17.4839611053467</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3536205291748</t>
+    <t xml:space="preserve">17.3536224365234</t>
   </si>
   <si>
     <t xml:space="preserve">17.372241973877</t>
@@ -2615,7 +2612,7 @@
     <t xml:space="preserve">16.5902118682861</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3481559753418</t>
+    <t xml:space="preserve">16.3481540679932</t>
   </si>
   <si>
     <t xml:space="preserve">16.3109149932861</t>
@@ -2630,7 +2627,7 @@
     <t xml:space="preserve">16.0502395629883</t>
   </si>
   <si>
-    <t xml:space="preserve">16.255054473877</t>
+    <t xml:space="preserve">16.2550563812256</t>
   </si>
   <si>
     <t xml:space="preserve">16.1060981750488</t>
@@ -2648,7 +2645,7 @@
     <t xml:space="preserve">17.4653415679932</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9494571685791</t>
+    <t xml:space="preserve">17.9494552612305</t>
   </si>
   <si>
     <t xml:space="preserve">17.8749771118164</t>
@@ -2660,7 +2657,7 @@
     <t xml:space="preserve">17.5491313934326</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3629341125488</t>
+    <t xml:space="preserve">17.3629322052002</t>
   </si>
   <si>
     <t xml:space="preserve">17.5025806427002</t>
@@ -2675,7 +2672,7 @@
     <t xml:space="preserve">18.0611743927002</t>
   </si>
   <si>
-    <t xml:space="preserve">17.828426361084</t>
+    <t xml:space="preserve">17.8284282684326</t>
   </si>
   <si>
     <t xml:space="preserve">18.3981628417969</t>
@@ -31277,7 +31274,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1075" t="s">
-        <v>362</v>
+        <v>279</v>
       </c>
       <c r="H1075" t="s">
         <v>9</v>
@@ -31901,7 +31898,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G1099" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H1099" t="s">
         <v>9</v>
@@ -32161,7 +32158,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1109" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H1109" t="s">
         <v>9</v>
@@ -32317,7 +32314,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1115" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1115" t="s">
         <v>9</v>
@@ -32343,7 +32340,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1116" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1116" t="s">
         <v>9</v>
@@ -32369,7 +32366,7 @@
         <v>15.5</v>
       </c>
       <c r="G1117" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1117" t="s">
         <v>9</v>
@@ -32395,7 +32392,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G1118" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1118" t="s">
         <v>9</v>
@@ -32421,7 +32418,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1119" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1119" t="s">
         <v>9</v>
@@ -32447,7 +32444,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1120" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1120" t="s">
         <v>9</v>
@@ -32473,7 +32470,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1121" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1121" t="s">
         <v>9</v>
@@ -32499,7 +32496,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G1122" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1122" t="s">
         <v>9</v>
@@ -32525,7 +32522,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G1123" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1123" t="s">
         <v>9</v>
@@ -32551,7 +32548,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G1124" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1124" t="s">
         <v>9</v>
@@ -32577,7 +32574,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1125" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H1125" t="s">
         <v>9</v>
@@ -32603,7 +32600,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1126" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H1126" t="s">
         <v>9</v>
@@ -32629,7 +32626,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G1127" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H1127" t="s">
         <v>9</v>
@@ -32655,7 +32652,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G1128" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H1128" t="s">
         <v>9</v>
@@ -32681,7 +32678,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1129" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H1129" t="s">
         <v>9</v>
@@ -32707,7 +32704,7 @@
         <v>15</v>
       </c>
       <c r="G1130" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H1130" t="s">
         <v>9</v>
@@ -32733,7 +32730,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G1131" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H1131" t="s">
         <v>9</v>
@@ -32759,7 +32756,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1132" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H1132" t="s">
         <v>9</v>
@@ -32785,7 +32782,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1133" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H1133" t="s">
         <v>9</v>
@@ -32811,7 +32808,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1134" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H1134" t="s">
         <v>9</v>
@@ -32837,7 +32834,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1135" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H1135" t="s">
         <v>9</v>
@@ -32863,7 +32860,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1136" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H1136" t="s">
         <v>9</v>
@@ -32889,7 +32886,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1137" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H1137" t="s">
         <v>9</v>
@@ -32915,7 +32912,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1138" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H1138" t="s">
         <v>9</v>
@@ -32941,7 +32938,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G1139" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H1139" t="s">
         <v>9</v>
@@ -32967,7 +32964,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G1140" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H1140" t="s">
         <v>9</v>
@@ -32993,7 +32990,7 @@
         <v>15</v>
       </c>
       <c r="G1141" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H1141" t="s">
         <v>9</v>
@@ -33019,7 +33016,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1142" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="H1142" t="s">
         <v>9</v>
@@ -33435,7 +33432,7 @@
         <v>15</v>
       </c>
       <c r="G1158" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H1158" t="s">
         <v>9</v>
@@ -33721,7 +33718,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1169" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H1169" t="s">
         <v>9</v>
@@ -33773,7 +33770,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1171" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H1171" t="s">
         <v>9</v>
@@ -33825,7 +33822,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G1173" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H1173" t="s">
         <v>9</v>
@@ -51895,7 +51892,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1868" t="s">
-        <v>761</v>
+        <v>756</v>
       </c>
       <c r="H1868" t="s">
         <v>9</v>
@@ -51921,7 +51918,7 @@
         <v>23</v>
       </c>
       <c r="G1869" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="H1869" t="s">
         <v>9</v>
@@ -51947,7 +51944,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1870" t="s">
-        <v>761</v>
+        <v>756</v>
       </c>
       <c r="H1870" t="s">
         <v>9</v>
@@ -51973,7 +51970,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G1871" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="H1871" t="s">
         <v>9</v>
@@ -51999,7 +51996,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G1872" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="H1872" t="s">
         <v>9</v>
@@ -52025,7 +52022,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1873" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="H1873" t="s">
         <v>9</v>
@@ -52051,7 +52048,7 @@
         <v>22.9500007629395</v>
       </c>
       <c r="G1874" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="H1874" t="s">
         <v>9</v>
@@ -52077,7 +52074,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1875" t="s">
-        <v>761</v>
+        <v>756</v>
       </c>
       <c r="H1875" t="s">
         <v>9</v>
@@ -52103,7 +52100,7 @@
         <v>22.9500007629395</v>
       </c>
       <c r="G1876" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="H1876" t="s">
         <v>9</v>
@@ -52129,7 +52126,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1877" t="s">
-        <v>761</v>
+        <v>756</v>
       </c>
       <c r="H1877" t="s">
         <v>9</v>
@@ -52155,7 +52152,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1878" t="s">
-        <v>761</v>
+        <v>756</v>
       </c>
       <c r="H1878" t="s">
         <v>9</v>
@@ -52181,7 +52178,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G1879" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="H1879" t="s">
         <v>9</v>
@@ -52207,7 +52204,7 @@
         <v>22.5499992370605</v>
       </c>
       <c r="G1880" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="H1880" t="s">
         <v>9</v>
@@ -52233,7 +52230,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G1881" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="H1881" t="s">
         <v>9</v>
@@ -52259,7 +52256,7 @@
         <v>23</v>
       </c>
       <c r="G1882" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="H1882" t="s">
         <v>9</v>
@@ -52285,7 +52282,7 @@
         <v>22.9500007629395</v>
       </c>
       <c r="G1883" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="H1883" t="s">
         <v>9</v>
@@ -52311,7 +52308,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G1884" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="H1884" t="s">
         <v>9</v>
@@ -52337,7 +52334,7 @@
         <v>22.75</v>
       </c>
       <c r="G1885" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="H1885" t="s">
         <v>9</v>
@@ -52363,7 +52360,7 @@
         <v>23</v>
       </c>
       <c r="G1886" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="H1886" t="s">
         <v>9</v>
@@ -52389,7 +52386,7 @@
         <v>22.9500007629395</v>
       </c>
       <c r="G1887" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="H1887" t="s">
         <v>9</v>
@@ -52415,7 +52412,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G1888" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="H1888" t="s">
         <v>9</v>
@@ -52441,7 +52438,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1889" t="s">
-        <v>761</v>
+        <v>756</v>
       </c>
       <c r="H1889" t="s">
         <v>9</v>
@@ -52467,7 +52464,7 @@
         <v>22.5</v>
       </c>
       <c r="G1890" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="H1890" t="s">
         <v>9</v>
@@ -52493,7 +52490,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1891" t="s">
-        <v>761</v>
+        <v>756</v>
       </c>
       <c r="H1891" t="s">
         <v>9</v>
@@ -52519,7 +52516,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1892" t="s">
-        <v>761</v>
+        <v>756</v>
       </c>
       <c r="H1892" t="s">
         <v>9</v>
@@ -52597,7 +52594,7 @@
         <v>22</v>
       </c>
       <c r="G1895" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="H1895" t="s">
         <v>9</v>
@@ -52623,7 +52620,7 @@
         <v>21.8500003814697</v>
       </c>
       <c r="G1896" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="H1896" t="s">
         <v>9</v>
@@ -52649,7 +52646,7 @@
         <v>22</v>
       </c>
       <c r="G1897" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="H1897" t="s">
         <v>9</v>
@@ -52675,7 +52672,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G1898" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="H1898" t="s">
         <v>9</v>
@@ -52701,7 +52698,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G1899" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="H1899" t="s">
         <v>9</v>
@@ -52753,7 +52750,7 @@
         <v>21.75</v>
       </c>
       <c r="G1901" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="H1901" t="s">
         <v>9</v>
@@ -52779,7 +52776,7 @@
         <v>21.75</v>
       </c>
       <c r="G1902" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="H1902" t="s">
         <v>9</v>
@@ -52805,7 +52802,7 @@
         <v>21.6499996185303</v>
       </c>
       <c r="G1903" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="H1903" t="s">
         <v>9</v>
@@ -52831,7 +52828,7 @@
         <v>21.5</v>
       </c>
       <c r="G1904" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="H1904" t="s">
         <v>9</v>
@@ -52857,7 +52854,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G1905" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="H1905" t="s">
         <v>9</v>
@@ -52883,7 +52880,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G1906" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="H1906" t="s">
         <v>9</v>
@@ -52909,7 +52906,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1907" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="H1907" t="s">
         <v>9</v>
@@ -52935,7 +52932,7 @@
         <v>21.25</v>
       </c>
       <c r="G1908" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="H1908" t="s">
         <v>9</v>
@@ -52961,7 +52958,7 @@
         <v>21.25</v>
       </c>
       <c r="G1909" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="H1909" t="s">
         <v>9</v>
@@ -52987,7 +52984,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G1910" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="H1910" t="s">
         <v>9</v>
@@ -53013,7 +53010,7 @@
         <v>21.0499992370605</v>
       </c>
       <c r="G1911" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="H1911" t="s">
         <v>9</v>
@@ -53039,7 +53036,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G1912" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="H1912" t="s">
         <v>9</v>
@@ -53065,7 +53062,7 @@
         <v>20.6499996185303</v>
       </c>
       <c r="G1913" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="H1913" t="s">
         <v>9</v>
@@ -53091,7 +53088,7 @@
         <v>20.75</v>
       </c>
       <c r="G1914" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="H1914" t="s">
         <v>9</v>
@@ -53117,7 +53114,7 @@
         <v>21</v>
       </c>
       <c r="G1915" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="H1915" t="s">
         <v>9</v>
@@ -53143,7 +53140,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G1916" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="H1916" t="s">
         <v>9</v>
@@ -53169,7 +53166,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1917" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="H1917" t="s">
         <v>9</v>
@@ -53195,7 +53192,7 @@
         <v>21.9500007629395</v>
       </c>
       <c r="G1918" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="H1918" t="s">
         <v>9</v>
@@ -53221,7 +53218,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1919" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="H1919" t="s">
         <v>9</v>
@@ -53247,7 +53244,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G1920" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="H1920" t="s">
         <v>9</v>
@@ -53273,7 +53270,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G1921" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="H1921" t="s">
         <v>9</v>
@@ -53299,7 +53296,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1922" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="H1922" t="s">
         <v>9</v>
@@ -53325,7 +53322,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G1923" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="H1923" t="s">
         <v>9</v>
@@ -53351,7 +53348,7 @@
         <v>20.6499996185303</v>
       </c>
       <c r="G1924" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="H1924" t="s">
         <v>9</v>
@@ -53377,7 +53374,7 @@
         <v>21.4500007629395</v>
       </c>
       <c r="G1925" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="H1925" t="s">
         <v>9</v>
@@ -53403,7 +53400,7 @@
         <v>21.5</v>
       </c>
       <c r="G1926" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="H1926" t="s">
         <v>9</v>
@@ -53429,7 +53426,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1927" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="H1927" t="s">
         <v>9</v>
@@ -53455,7 +53452,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1928" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="H1928" t="s">
         <v>9</v>
@@ -53481,7 +53478,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1929" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="H1929" t="s">
         <v>9</v>
@@ -53507,7 +53504,7 @@
         <v>21.25</v>
       </c>
       <c r="G1930" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="H1930" t="s">
         <v>9</v>
@@ -53533,7 +53530,7 @@
         <v>20.75</v>
       </c>
       <c r="G1931" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="H1931" t="s">
         <v>9</v>
@@ -53559,7 +53556,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1932" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="H1932" t="s">
         <v>9</v>
@@ -53585,7 +53582,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G1933" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="H1933" t="s">
         <v>9</v>
@@ -53611,7 +53608,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1934" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="H1934" t="s">
         <v>9</v>
@@ -53637,7 +53634,7 @@
         <v>20.5499992370605</v>
       </c>
       <c r="G1935" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="H1935" t="s">
         <v>9</v>
@@ -53663,7 +53660,7 @@
         <v>20</v>
       </c>
       <c r="G1936" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="H1936" t="s">
         <v>9</v>
@@ -53689,7 +53686,7 @@
         <v>20.25</v>
       </c>
       <c r="G1937" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="H1937" t="s">
         <v>9</v>
@@ -53715,7 +53712,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1938" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="H1938" t="s">
         <v>9</v>
@@ -53741,7 +53738,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1939" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="H1939" t="s">
         <v>9</v>
@@ -53767,7 +53764,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1940" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="H1940" t="s">
         <v>9</v>
@@ -53793,7 +53790,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G1941" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="H1941" t="s">
         <v>9</v>
@@ -53819,7 +53816,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G1942" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="H1942" t="s">
         <v>9</v>
@@ -53845,7 +53842,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1943" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="H1943" t="s">
         <v>9</v>
@@ -53871,7 +53868,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G1944" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="H1944" t="s">
         <v>9</v>
@@ -53897,7 +53894,7 @@
         <v>19.8400001525879</v>
       </c>
       <c r="G1945" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="H1945" t="s">
         <v>9</v>
@@ -53923,7 +53920,7 @@
         <v>19.7600002288818</v>
       </c>
       <c r="G1946" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="H1946" t="s">
         <v>9</v>
@@ -53949,7 +53946,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G1947" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="H1947" t="s">
         <v>9</v>
@@ -53975,7 +53972,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G1948" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="H1948" t="s">
         <v>9</v>
@@ -54001,7 +53998,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G1949" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="H1949" t="s">
         <v>9</v>
@@ -54027,7 +54024,7 @@
         <v>19.5799999237061</v>
       </c>
       <c r="G1950" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="H1950" t="s">
         <v>9</v>
@@ -54053,7 +54050,7 @@
         <v>19.5599994659424</v>
       </c>
       <c r="G1951" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="H1951" t="s">
         <v>9</v>
@@ -54079,7 +54076,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1952" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="H1952" t="s">
         <v>9</v>
@@ -54105,7 +54102,7 @@
         <v>18.9799995422363</v>
       </c>
       <c r="G1953" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="H1953" t="s">
         <v>9</v>
@@ -54131,7 +54128,7 @@
         <v>18.8799991607666</v>
       </c>
       <c r="G1954" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="H1954" t="s">
         <v>9</v>
@@ -54157,7 +54154,7 @@
         <v>19</v>
       </c>
       <c r="G1955" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="H1955" t="s">
         <v>9</v>
@@ -54183,7 +54180,7 @@
         <v>19</v>
       </c>
       <c r="G1956" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="H1956" t="s">
         <v>9</v>
@@ -54209,7 +54206,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1957" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="H1957" t="s">
         <v>9</v>
@@ -54235,7 +54232,7 @@
         <v>18.6800003051758</v>
       </c>
       <c r="G1958" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="H1958" t="s">
         <v>9</v>
@@ -54261,7 +54258,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1959" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="H1959" t="s">
         <v>9</v>
@@ -54287,7 +54284,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1960" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="H1960" t="s">
         <v>9</v>
@@ -54313,7 +54310,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1961" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="H1961" t="s">
         <v>9</v>
@@ -54339,7 +54336,7 @@
         <v>18</v>
       </c>
       <c r="G1962" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="H1962" t="s">
         <v>9</v>
@@ -54365,7 +54362,7 @@
         <v>18.5</v>
       </c>
       <c r="G1963" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="H1963" t="s">
         <v>9</v>
@@ -54391,7 +54388,7 @@
         <v>19</v>
       </c>
       <c r="G1964" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="H1964" t="s">
         <v>9</v>
@@ -54417,7 +54414,7 @@
         <v>18.6200008392334</v>
       </c>
       <c r="G1965" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="H1965" t="s">
         <v>9</v>
@@ -54443,7 +54440,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1966" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="H1966" t="s">
         <v>9</v>
@@ -54469,7 +54466,7 @@
         <v>18.9599990844727</v>
       </c>
       <c r="G1967" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="H1967" t="s">
         <v>9</v>
@@ -54495,7 +54492,7 @@
         <v>19</v>
       </c>
       <c r="G1968" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="H1968" t="s">
         <v>9</v>
@@ -54521,7 +54518,7 @@
         <v>18.9599990844727</v>
       </c>
       <c r="G1969" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="H1969" t="s">
         <v>9</v>
@@ -54547,7 +54544,7 @@
         <v>18.9599990844727</v>
       </c>
       <c r="G1970" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="H1970" t="s">
         <v>9</v>
@@ -54573,7 +54570,7 @@
         <v>19.0400009155273</v>
       </c>
       <c r="G1971" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="H1971" t="s">
         <v>9</v>
@@ -54599,7 +54596,7 @@
         <v>19.0200004577637</v>
       </c>
       <c r="G1972" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="H1972" t="s">
         <v>9</v>
@@ -54625,7 +54622,7 @@
         <v>19</v>
       </c>
       <c r="G1973" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="H1973" t="s">
         <v>9</v>
@@ -54651,7 +54648,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1974" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="H1974" t="s">
         <v>9</v>
@@ -54677,7 +54674,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1975" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="H1975" t="s">
         <v>9</v>
@@ -54703,7 +54700,7 @@
         <v>18.7399997711182</v>
       </c>
       <c r="G1976" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="H1976" t="s">
         <v>9</v>
@@ -54729,7 +54726,7 @@
         <v>18.5400009155273</v>
       </c>
       <c r="G1977" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="H1977" t="s">
         <v>9</v>
@@ -54755,7 +54752,7 @@
         <v>18.5400009155273</v>
       </c>
       <c r="G1978" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="H1978" t="s">
         <v>9</v>
@@ -54781,7 +54778,7 @@
         <v>18.5</v>
       </c>
       <c r="G1979" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="H1979" t="s">
         <v>9</v>
@@ -54807,7 +54804,7 @@
         <v>18.5200004577637</v>
       </c>
       <c r="G1980" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="H1980" t="s">
         <v>9</v>
@@ -54833,7 +54830,7 @@
         <v>18</v>
       </c>
       <c r="G1981" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="H1981" t="s">
         <v>9</v>
@@ -54859,7 +54856,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1982" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="H1982" t="s">
         <v>9</v>
@@ -54885,7 +54882,7 @@
         <v>17.7800006866455</v>
       </c>
       <c r="G1983" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="H1983" t="s">
         <v>9</v>
@@ -54911,7 +54908,7 @@
         <v>17.7800006866455</v>
       </c>
       <c r="G1984" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="H1984" t="s">
         <v>9</v>
@@ -54937,7 +54934,7 @@
         <v>17.7800006866455</v>
       </c>
       <c r="G1985" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="H1985" t="s">
         <v>9</v>
@@ -54963,7 +54960,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1986" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="H1986" t="s">
         <v>9</v>
@@ -54989,7 +54986,7 @@
         <v>18.3600006103516</v>
       </c>
       <c r="G1987" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="H1987" t="s">
         <v>9</v>
@@ -55015,7 +55012,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1988" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="H1988" t="s">
         <v>9</v>
@@ -55041,7 +55038,7 @@
         <v>18.5</v>
       </c>
       <c r="G1989" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="H1989" t="s">
         <v>9</v>
@@ -55067,7 +55064,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1990" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="H1990" t="s">
         <v>9</v>
@@ -55093,7 +55090,7 @@
         <v>18.1800003051758</v>
       </c>
       <c r="G1991" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="H1991" t="s">
         <v>9</v>
@@ -55119,7 +55116,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G1992" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="H1992" t="s">
         <v>9</v>
@@ -55145,7 +55142,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1993" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="H1993" t="s">
         <v>9</v>
@@ -55171,7 +55168,7 @@
         <v>17.1599998474121</v>
       </c>
       <c r="G1994" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="H1994" t="s">
         <v>9</v>
@@ -55197,7 +55194,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G1995" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="H1995" t="s">
         <v>9</v>
@@ -55223,7 +55220,7 @@
         <v>17.5</v>
       </c>
       <c r="G1996" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="H1996" t="s">
         <v>9</v>
@@ -55249,7 +55246,7 @@
         <v>18</v>
       </c>
       <c r="G1997" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="H1997" t="s">
         <v>9</v>
@@ -55275,7 +55272,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1998" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="H1998" t="s">
         <v>9</v>
@@ -55301,7 +55298,7 @@
         <v>18</v>
       </c>
       <c r="G1999" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="H1999" t="s">
         <v>9</v>
@@ -55327,7 +55324,7 @@
         <v>18</v>
       </c>
       <c r="G2000" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="H2000" t="s">
         <v>9</v>
@@ -55353,7 +55350,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G2001" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="H2001" t="s">
         <v>9</v>
@@ -55379,7 +55376,7 @@
         <v>18</v>
       </c>
       <c r="G2002" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="H2002" t="s">
         <v>9</v>
@@ -55405,7 +55402,7 @@
         <v>18</v>
       </c>
       <c r="G2003" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="H2003" t="s">
         <v>9</v>
@@ -55431,7 +55428,7 @@
         <v>17.6200008392334</v>
       </c>
       <c r="G2004" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="H2004" t="s">
         <v>9</v>
@@ -55457,7 +55454,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G2005" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="H2005" t="s">
         <v>9</v>
@@ -55483,7 +55480,7 @@
         <v>17.5</v>
       </c>
       <c r="G2006" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="H2006" t="s">
         <v>9</v>
@@ -55509,7 +55506,7 @@
         <v>17.7199993133545</v>
       </c>
       <c r="G2007" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="H2007" t="s">
         <v>9</v>
@@ -55535,7 +55532,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G2008" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="H2008" t="s">
         <v>9</v>
@@ -55561,7 +55558,7 @@
         <v>17.3799991607666</v>
       </c>
       <c r="G2009" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="H2009" t="s">
         <v>9</v>
@@ -55587,7 +55584,7 @@
         <v>17.5</v>
       </c>
       <c r="G2010" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="H2010" t="s">
         <v>9</v>
@@ -55613,7 +55610,7 @@
         <v>17.5</v>
       </c>
       <c r="G2011" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="H2011" t="s">
         <v>9</v>
@@ -55639,7 +55636,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G2012" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="H2012" t="s">
         <v>9</v>
@@ -55665,7 +55662,7 @@
         <v>17.6800003051758</v>
       </c>
       <c r="G2013" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="H2013" t="s">
         <v>9</v>
@@ -55691,7 +55688,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G2014" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="H2014" t="s">
         <v>9</v>
@@ -55717,7 +55714,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G2015" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="H2015" t="s">
         <v>9</v>
@@ -55743,7 +55740,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G2016" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="H2016" t="s">
         <v>9</v>
@@ -55769,7 +55766,7 @@
         <v>17.1599998474121</v>
       </c>
       <c r="G2017" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="H2017" t="s">
         <v>9</v>
@@ -55795,7 +55792,7 @@
         <v>17.0599994659424</v>
       </c>
       <c r="G2018" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="H2018" t="s">
         <v>9</v>
@@ -55821,7 +55818,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G2019" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="H2019" t="s">
         <v>9</v>
@@ -55847,7 +55844,7 @@
         <v>17.1599998474121</v>
       </c>
       <c r="G2020" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="H2020" t="s">
         <v>9</v>
@@ -55873,7 +55870,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G2021" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="H2021" t="s">
         <v>9</v>
@@ -55899,7 +55896,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G2022" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="H2022" t="s">
         <v>9</v>
@@ -55925,7 +55922,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G2023" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="H2023" t="s">
         <v>9</v>
@@ -55951,7 +55948,7 @@
         <v>17.5</v>
       </c>
       <c r="G2024" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="H2024" t="s">
         <v>9</v>
@@ -55977,7 +55974,7 @@
         <v>17.6800003051758</v>
       </c>
       <c r="G2025" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="H2025" t="s">
         <v>9</v>
@@ -56003,7 +56000,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G2026" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="H2026" t="s">
         <v>9</v>
@@ -56029,7 +56026,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G2027" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="H2027" t="s">
         <v>9</v>
@@ -56055,7 +56052,7 @@
         <v>17.8799991607666</v>
       </c>
       <c r="G2028" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="H2028" t="s">
         <v>9</v>
@@ -56081,7 +56078,7 @@
         <v>18.1200008392334</v>
       </c>
       <c r="G2029" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="H2029" t="s">
         <v>9</v>
@@ -56107,7 +56104,7 @@
         <v>18.3799991607666</v>
       </c>
       <c r="G2030" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="H2030" t="s">
         <v>9</v>
@@ -56133,7 +56130,7 @@
         <v>18.2800006866455</v>
       </c>
       <c r="G2031" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="H2031" t="s">
         <v>9</v>
@@ -56159,7 +56156,7 @@
         <v>18.3600006103516</v>
       </c>
       <c r="G2032" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="H2032" t="s">
         <v>9</v>
@@ -56185,7 +56182,7 @@
         <v>18.3199996948242</v>
       </c>
       <c r="G2033" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="H2033" t="s">
         <v>9</v>
@@ -56211,7 +56208,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G2034" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="H2034" t="s">
         <v>9</v>
@@ -56237,7 +56234,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G2035" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="H2035" t="s">
         <v>9</v>
@@ -56263,7 +56260,7 @@
         <v>18.9799995422363</v>
       </c>
       <c r="G2036" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="H2036" t="s">
         <v>9</v>
@@ -56289,7 +56286,7 @@
         <v>18.7800006866455</v>
       </c>
       <c r="G2037" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="H2037" t="s">
         <v>9</v>
@@ -56315,7 +56312,7 @@
         <v>18.6399993896484</v>
       </c>
       <c r="G2038" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="H2038" t="s">
         <v>9</v>
@@ -56341,7 +56338,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G2039" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="H2039" t="s">
         <v>9</v>
@@ -56367,7 +56364,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G2040" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="H2040" t="s">
         <v>9</v>
@@ -56393,7 +56390,7 @@
         <v>18.6800003051758</v>
       </c>
       <c r="G2041" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="H2041" t="s">
         <v>9</v>
@@ -56419,7 +56416,7 @@
         <v>18.6800003051758</v>
       </c>
       <c r="G2042" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="H2042" t="s">
         <v>9</v>
@@ -56445,7 +56442,7 @@
         <v>18.6599998474121</v>
       </c>
       <c r="G2043" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="H2043" t="s">
         <v>9</v>
@@ -56471,7 +56468,7 @@
         <v>18.6399993896484</v>
       </c>
       <c r="G2044" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="H2044" t="s">
         <v>9</v>
@@ -56497,7 +56494,7 @@
         <v>18.6599998474121</v>
       </c>
       <c r="G2045" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="H2045" t="s">
         <v>9</v>
@@ -56523,7 +56520,7 @@
         <v>18.6599998474121</v>
       </c>
       <c r="G2046" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="H2046" t="s">
         <v>9</v>
@@ -56549,7 +56546,7 @@
         <v>18.6599998474121</v>
       </c>
       <c r="G2047" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="H2047" t="s">
         <v>9</v>
@@ -56575,7 +56572,7 @@
         <v>18.2800006866455</v>
       </c>
       <c r="G2048" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="H2048" t="s">
         <v>9</v>
@@ -56601,7 +56598,7 @@
         <v>18.2600002288818</v>
       </c>
       <c r="G2049" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="H2049" t="s">
         <v>9</v>
@@ -56627,7 +56624,7 @@
         <v>18.3400001525879</v>
       </c>
       <c r="G2050" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="H2050" t="s">
         <v>9</v>
@@ -56653,7 +56650,7 @@
         <v>18.3799991607666</v>
       </c>
       <c r="G2051" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="H2051" t="s">
         <v>9</v>
@@ -56679,7 +56676,7 @@
         <v>18.3799991607666</v>
       </c>
       <c r="G2052" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="H2052" t="s">
         <v>9</v>
@@ -56705,7 +56702,7 @@
         <v>17.9200000762939</v>
       </c>
       <c r="G2053" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="H2053" t="s">
         <v>9</v>
@@ -56731,7 +56728,7 @@
         <v>17.8799991607666</v>
       </c>
       <c r="G2054" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="H2054" t="s">
         <v>9</v>
@@ -56757,7 +56754,7 @@
         <v>17.8799991607666</v>
       </c>
       <c r="G2055" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="H2055" t="s">
         <v>9</v>
@@ -56783,7 +56780,7 @@
         <v>18.1399993896484</v>
       </c>
       <c r="G2056" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="H2056" t="s">
         <v>9</v>
@@ -56809,7 +56806,7 @@
         <v>18</v>
       </c>
       <c r="G2057" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="H2057" t="s">
         <v>9</v>
@@ -56835,7 +56832,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G2058" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="H2058" t="s">
         <v>9</v>
@@ -56861,7 +56858,7 @@
         <v>17.7800006866455</v>
       </c>
       <c r="G2059" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="H2059" t="s">
         <v>9</v>
@@ -56887,7 +56884,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G2060" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="H2060" t="s">
         <v>9</v>
@@ -56913,7 +56910,7 @@
         <v>17.9599990844727</v>
       </c>
       <c r="G2061" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="H2061" t="s">
         <v>9</v>
@@ -56939,7 +56936,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G2062" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="H2062" t="s">
         <v>9</v>
@@ -56965,7 +56962,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G2063" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="H2063" t="s">
         <v>9</v>
@@ -56991,7 +56988,7 @@
         <v>17.9799995422363</v>
       </c>
       <c r="G2064" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="H2064" t="s">
         <v>9</v>
@@ -57017,7 +57014,7 @@
         <v>17.8199996948242</v>
       </c>
       <c r="G2065" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="H2065" t="s">
         <v>9</v>
@@ -57043,7 +57040,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G2066" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="H2066" t="s">
         <v>9</v>
@@ -57069,7 +57066,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G2067" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="H2067" t="s">
         <v>9</v>
@@ -57095,7 +57092,7 @@
         <v>17.5200004577637</v>
       </c>
       <c r="G2068" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="H2068" t="s">
         <v>9</v>
@@ -57121,7 +57118,7 @@
         <v>17.5</v>
       </c>
       <c r="G2069" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="H2069" t="s">
         <v>9</v>
@@ -57147,7 +57144,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G2070" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="H2070" t="s">
         <v>9</v>
@@ -57173,7 +57170,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G2071" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="H2071" t="s">
         <v>9</v>
@@ -57199,7 +57196,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G2072" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="H2072" t="s">
         <v>9</v>
@@ -57225,7 +57222,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G2073" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="H2073" t="s">
         <v>9</v>
@@ -57251,7 +57248,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G2074" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="H2074" t="s">
         <v>9</v>
@@ -57277,7 +57274,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G2075" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="H2075" t="s">
         <v>9</v>
@@ -57303,7 +57300,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G2076" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="H2076" t="s">
         <v>9</v>
@@ -57329,7 +57326,7 @@
         <v>17.9799995422363</v>
       </c>
       <c r="G2077" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="H2077" t="s">
         <v>9</v>
@@ -57355,7 +57352,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G2078" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="H2078" t="s">
         <v>9</v>
@@ -57381,7 +57378,7 @@
         <v>17.5200004577637</v>
       </c>
       <c r="G2079" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="H2079" t="s">
         <v>9</v>
@@ -57407,7 +57404,7 @@
         <v>17.2399997711182</v>
       </c>
       <c r="G2080" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="H2080" t="s">
         <v>9</v>
@@ -57433,7 +57430,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G2081" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="H2081" t="s">
         <v>9</v>
@@ -57459,7 +57456,7 @@
         <v>17.2399997711182</v>
       </c>
       <c r="G2082" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="H2082" t="s">
         <v>9</v>
@@ -57485,7 +57482,7 @@
         <v>17.5</v>
       </c>
       <c r="G2083" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="H2083" t="s">
         <v>9</v>
@@ -57511,7 +57508,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G2084" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="H2084" t="s">
         <v>9</v>
@@ -57537,7 +57534,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G2085" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="H2085" t="s">
         <v>9</v>
@@ -57563,7 +57560,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G2086" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="H2086" t="s">
         <v>9</v>
@@ -57589,7 +57586,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G2087" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="H2087" t="s">
         <v>9</v>
@@ -57615,7 +57612,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G2088" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="H2088" t="s">
         <v>9</v>
@@ -57641,7 +57638,7 @@
         <v>17.3799991607666</v>
       </c>
       <c r="G2089" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="H2089" t="s">
         <v>9</v>
@@ -57667,7 +57664,7 @@
         <v>17.3799991607666</v>
       </c>
       <c r="G2090" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="H2090" t="s">
         <v>9</v>
@@ -57693,7 +57690,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G2091" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="H2091" t="s">
         <v>9</v>
@@ -57719,7 +57716,7 @@
         <v>18.4400005340576</v>
       </c>
       <c r="G2092" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="H2092" t="s">
         <v>9</v>
@@ -57745,7 +57742,7 @@
         <v>19.3400001525879</v>
       </c>
       <c r="G2093" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="H2093" t="s">
         <v>9</v>
@@ -57771,7 +57768,7 @@
         <v>19.2399997711182</v>
       </c>
       <c r="G2094" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="H2094" t="s">
         <v>9</v>
@@ -57797,7 +57794,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G2095" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="H2095" t="s">
         <v>9</v>
@@ -57823,7 +57820,7 @@
         <v>18.7600002288818</v>
       </c>
       <c r="G2096" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="H2096" t="s">
         <v>9</v>
@@ -57849,7 +57846,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G2097" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="H2097" t="s">
         <v>9</v>
@@ -57875,7 +57872,7 @@
         <v>18.8799991607666</v>
       </c>
       <c r="G2098" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="H2098" t="s">
         <v>9</v>
@@ -57901,7 +57898,7 @@
         <v>19.2800006866455</v>
       </c>
       <c r="G2099" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="H2099" t="s">
         <v>9</v>
@@ -57927,7 +57924,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G2100" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="H2100" t="s">
         <v>9</v>
@@ -57953,7 +57950,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G2101" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="H2101" t="s">
         <v>9</v>
@@ -57979,7 +57976,7 @@
         <v>19</v>
       </c>
       <c r="G2102" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="H2102" t="s">
         <v>9</v>
@@ -58005,7 +58002,7 @@
         <v>19</v>
       </c>
       <c r="G2103" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="H2103" t="s">
         <v>9</v>
@@ -58031,7 +58028,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G2104" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="H2104" t="s">
         <v>9</v>
@@ -58057,7 +58054,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G2105" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="H2105" t="s">
         <v>9</v>
@@ -58083,7 +58080,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G2106" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="H2106" t="s">
         <v>9</v>
@@ -58109,7 +58106,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G2107" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="H2107" t="s">
         <v>9</v>
@@ -58135,7 +58132,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G2108" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="H2108" t="s">
         <v>9</v>
@@ -58161,7 +58158,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G2109" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H2109" t="s">
         <v>9</v>
@@ -58187,7 +58184,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G2110" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="H2110" t="s">
         <v>9</v>
@@ -58213,7 +58210,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G2111" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="H2111" t="s">
         <v>9</v>
@@ -58239,7 +58236,7 @@
         <v>18.75</v>
       </c>
       <c r="G2112" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="H2112" t="s">
         <v>9</v>
@@ -58265,7 +58262,7 @@
         <v>19</v>
       </c>
       <c r="G2113" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="H2113" t="s">
         <v>9</v>
@@ -58291,7 +58288,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G2114" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="H2114" t="s">
         <v>9</v>
@@ -58317,7 +58314,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G2115" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="H2115" t="s">
         <v>9</v>
@@ -58343,7 +58340,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G2116" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="H2116" t="s">
         <v>9</v>
@@ -58369,7 +58366,7 @@
         <v>19</v>
       </c>
       <c r="G2117" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="H2117" t="s">
         <v>9</v>
@@ -58395,7 +58392,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G2118" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="H2118" t="s">
         <v>9</v>
@@ -58421,7 +58418,7 @@
         <v>19.5</v>
       </c>
       <c r="G2119" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="H2119" t="s">
         <v>9</v>
@@ -58447,7 +58444,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G2120" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="H2120" t="s">
         <v>9</v>
@@ -58473,7 +58470,7 @@
         <v>19.1499996185303</v>
       </c>
       <c r="G2121" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="H2121" t="s">
         <v>9</v>
@@ -58499,7 +58496,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G2122" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="H2122" t="s">
         <v>9</v>
@@ -58525,7 +58522,7 @@
         <v>19.25</v>
       </c>
       <c r="G2123" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="H2123" t="s">
         <v>9</v>
@@ -58551,7 +58548,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G2124" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="H2124" t="s">
         <v>9</v>
@@ -58577,7 +58574,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G2125" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="H2125" t="s">
         <v>9</v>
@@ -58603,7 +58600,7 @@
         <v>19.5</v>
       </c>
       <c r="G2126" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H2126" t="s">
         <v>9</v>
@@ -58629,7 +58626,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G2127" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="H2127" t="s">
         <v>9</v>
@@ -58655,7 +58652,7 @@
         <v>20</v>
       </c>
       <c r="G2128" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="H2128" t="s">
         <v>9</v>
@@ -58681,7 +58678,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G2129" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="H2129" t="s">
         <v>9</v>
@@ -58707,7 +58704,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G2130" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="H2130" t="s">
         <v>9</v>
@@ -58733,7 +58730,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G2131" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="H2131" t="s">
         <v>9</v>
@@ -58759,7 +58756,7 @@
         <v>21</v>
       </c>
       <c r="G2132" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="H2132" t="s">
         <v>9</v>
@@ -58785,7 +58782,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G2133" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="H2133" t="s">
         <v>9</v>
@@ -58811,7 +58808,7 @@
         <v>22</v>
       </c>
       <c r="G2134" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="H2134" t="s">
         <v>9</v>
@@ -58837,7 +58834,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G2135" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="H2135" t="s">
         <v>9</v>
@@ -58863,7 +58860,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G2136" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="H2136" t="s">
         <v>9</v>
@@ -58889,7 +58886,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G2137" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="H2137" t="s">
         <v>9</v>
@@ -58915,7 +58912,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G2138" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="H2138" t="s">
         <v>9</v>
@@ -58941,7 +58938,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G2139" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="H2139" t="s">
         <v>9</v>
@@ -58967,7 +58964,7 @@
         <v>21.5</v>
       </c>
       <c r="G2140" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="H2140" t="s">
         <v>9</v>
@@ -58993,7 +58990,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G2141" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="H2141" t="s">
         <v>9</v>
@@ -59019,7 +59016,7 @@
         <v>21.5</v>
       </c>
       <c r="G2142" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="H2142" t="s">
         <v>9</v>
@@ -59045,7 +59042,7 @@
         <v>22</v>
       </c>
       <c r="G2143" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="H2143" t="s">
         <v>9</v>
@@ -59071,7 +59068,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G2144" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="H2144" t="s">
         <v>9</v>
@@ -59097,7 +59094,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G2145" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="H2145" t="s">
         <v>9</v>
@@ -59123,7 +59120,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G2146" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="H2146" t="s">
         <v>9</v>
@@ -59149,7 +59146,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G2147" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="H2147" t="s">
         <v>9</v>
@@ -59175,7 +59172,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G2148" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="H2148" t="s">
         <v>9</v>
@@ -59201,7 +59198,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G2149" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="H2149" t="s">
         <v>9</v>
@@ -59227,7 +59224,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G2150" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="H2150" t="s">
         <v>9</v>
@@ -59253,7 +59250,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G2151" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="H2151" t="s">
         <v>9</v>
@@ -59279,7 +59276,7 @@
         <v>21</v>
       </c>
       <c r="G2152" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="H2152" t="s">
         <v>9</v>
@@ -59305,7 +59302,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G2153" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="H2153" t="s">
         <v>9</v>
@@ -59331,7 +59328,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G2154" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="H2154" t="s">
         <v>9</v>
@@ -59357,7 +59354,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G2155" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="H2155" t="s">
         <v>9</v>
@@ -59383,7 +59380,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G2156" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="H2156" t="s">
         <v>9</v>
@@ -59409,7 +59406,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G2157" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="H2157" t="s">
         <v>9</v>
@@ -59435,7 +59432,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G2158" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="H2158" t="s">
         <v>9</v>
@@ -59461,7 +59458,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G2159" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="H2159" t="s">
         <v>9</v>
@@ -59487,7 +59484,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G2160" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="H2160" t="s">
         <v>9</v>
@@ -59513,7 +59510,7 @@
         <v>21.5</v>
       </c>
       <c r="G2161" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="H2161" t="s">
         <v>9</v>
@@ -59539,7 +59536,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G2162" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="H2162" t="s">
         <v>9</v>
@@ -59565,7 +59562,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G2163" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="H2163" t="s">
         <v>9</v>
@@ -59591,7 +59588,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G2164" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="H2164" t="s">
         <v>9</v>
@@ -59617,7 +59614,7 @@
         <v>21.5</v>
       </c>
       <c r="G2165" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="H2165" t="s">
         <v>9</v>
@@ -59643,7 +59640,7 @@
         <v>22</v>
       </c>
       <c r="G2166" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="H2166" t="s">
         <v>9</v>
@@ -59669,7 +59666,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G2167" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="H2167" t="s">
         <v>9</v>
@@ -59695,7 +59692,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G2168" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="H2168" t="s">
         <v>9</v>
@@ -59721,7 +59718,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G2169" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="H2169" t="s">
         <v>9</v>
@@ -59747,7 +59744,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G2170" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="H2170" t="s">
         <v>9</v>
@@ -59773,7 +59770,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G2171" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="H2171" t="s">
         <v>9</v>
@@ -59799,7 +59796,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G2172" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="H2172" t="s">
         <v>9</v>
@@ -59825,7 +59822,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G2173" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="H2173" t="s">
         <v>9</v>
@@ -59851,7 +59848,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G2174" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="H2174" t="s">
         <v>9</v>
@@ -59877,7 +59874,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G2175" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="H2175" t="s">
         <v>9</v>
@@ -59903,7 +59900,7 @@
         <v>22</v>
       </c>
       <c r="G2176" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="H2176" t="s">
         <v>9</v>
@@ -59929,7 +59926,7 @@
         <v>22</v>
       </c>
       <c r="G2177" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="H2177" t="s">
         <v>9</v>
@@ -59955,7 +59952,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G2178" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="H2178" t="s">
         <v>9</v>
@@ -59981,7 +59978,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G2179" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="H2179" t="s">
         <v>9</v>
@@ -60007,7 +60004,7 @@
         <v>22</v>
       </c>
       <c r="G2180" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -60033,7 +60030,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G2181" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="H2181" t="s">
         <v>9</v>
@@ -60059,7 +60056,7 @@
         <v>22</v>
       </c>
       <c r="G2182" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -60085,7 +60082,7 @@
         <v>22</v>
       </c>
       <c r="G2183" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="H2183" t="s">
         <v>9</v>
@@ -60111,7 +60108,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G2184" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="H2184" t="s">
         <v>9</v>
@@ -60137,7 +60134,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G2185" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="H2185" t="s">
         <v>9</v>
@@ -60163,7 +60160,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G2186" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="H2186" t="s">
         <v>9</v>
@@ -60189,7 +60186,7 @@
         <v>22</v>
       </c>
       <c r="G2187" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -60215,7 +60212,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G2188" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -60241,7 +60238,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G2189" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -60267,7 +60264,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G2190" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -60293,7 +60290,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G2191" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="H2191" t="s">
         <v>9</v>
@@ -60319,7 +60316,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G2192" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -60345,7 +60342,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G2193" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -60371,7 +60368,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G2194" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="H2194" t="s">
         <v>9</v>
@@ -60397,7 +60394,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G2195" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="H2195" t="s">
         <v>9</v>
@@ -60423,7 +60420,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G2196" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="H2196" t="s">
         <v>9</v>
@@ -60449,7 +60446,7 @@
         <v>21</v>
       </c>
       <c r="G2197" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="H2197" t="s">
         <v>9</v>
@@ -60475,7 +60472,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G2198" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="H2198" t="s">
         <v>9</v>
@@ -60501,7 +60498,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G2199" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="H2199" t="s">
         <v>9</v>
@@ -60527,7 +60524,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G2200" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="H2200" t="s">
         <v>9</v>
@@ -60553,7 +60550,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G2201" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="H2201" t="s">
         <v>9</v>
@@ -60579,7 +60576,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G2202" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="H2202" t="s">
         <v>9</v>
@@ -60605,7 +60602,7 @@
         <v>21.5</v>
       </c>
       <c r="G2203" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="H2203" t="s">
         <v>9</v>
@@ -60631,7 +60628,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G2204" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="H2204" t="s">
         <v>9</v>
@@ -60657,7 +60654,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G2205" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="H2205" t="s">
         <v>9</v>
@@ -60683,7 +60680,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G2206" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -60709,7 +60706,7 @@
         <v>22</v>
       </c>
       <c r="G2207" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -60735,7 +60732,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G2208" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -60761,7 +60758,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G2209" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="H2209" t="s">
         <v>9</v>
@@ -60787,7 +60784,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G2210" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -60813,7 +60810,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G2211" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -60839,7 +60836,7 @@
         <v>22</v>
       </c>
       <c r="G2212" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -60865,7 +60862,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G2213" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -60891,7 +60888,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G2214" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -60917,7 +60914,7 @@
         <v>22</v>
       </c>
       <c r="G2215" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="H2215" t="s">
         <v>9</v>
@@ -60943,7 +60940,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G2216" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -60969,7 +60966,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G2217" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="H2217" t="s">
         <v>9</v>
@@ -60995,7 +60992,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G2218" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="H2218" t="s">
         <v>9</v>
@@ -61021,7 +61018,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G2219" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="H2219" t="s">
         <v>9</v>
@@ -61047,7 +61044,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G2220" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="H2220" t="s">
         <v>9</v>
@@ -61073,7 +61070,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G2221" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="H2221" t="s">
         <v>9</v>
@@ -61099,7 +61096,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G2222" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -61125,7 +61122,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G2223" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="H2223" t="s">
         <v>9</v>
@@ -61151,7 +61148,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G2224" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -61177,7 +61174,7 @@
         <v>22</v>
       </c>
       <c r="G2225" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -61203,7 +61200,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G2226" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -61229,7 +61226,7 @@
         <v>22</v>
       </c>
       <c r="G2227" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="H2227" t="s">
         <v>9</v>
@@ -61255,7 +61252,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G2228" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -61281,7 +61278,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G2229" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="H2229" t="s">
         <v>9</v>
@@ -61307,7 +61304,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G2230" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -61333,7 +61330,7 @@
         <v>22</v>
       </c>
       <c r="G2231" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="H2231" t="s">
         <v>9</v>
@@ -61359,7 +61356,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G2232" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="H2232" t="s">
         <v>9</v>
@@ -61385,7 +61382,7 @@
         <v>22.5</v>
       </c>
       <c r="G2233" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="H2233" t="s">
         <v>9</v>
@@ -61411,7 +61408,7 @@
         <v>22.5</v>
       </c>
       <c r="G2234" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="H2234" t="s">
         <v>9</v>
@@ -61437,7 +61434,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G2235" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="H2235" t="s">
         <v>9</v>
@@ -61463,7 +61460,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G2236" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -61489,7 +61486,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G2237" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="H2237" t="s">
         <v>9</v>
@@ -61515,7 +61512,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G2238" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="H2238" t="s">
         <v>9</v>
@@ -61541,7 +61538,7 @@
         <v>24</v>
       </c>
       <c r="G2239" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="H2239" t="s">
         <v>9</v>
@@ -61567,7 +61564,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G2240" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -61593,7 +61590,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G2241" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="H2241" t="s">
         <v>9</v>
@@ -61619,7 +61616,7 @@
         <v>24</v>
       </c>
       <c r="G2242" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="H2242" t="s">
         <v>9</v>
@@ -61645,7 +61642,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G2243" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="H2243" t="s">
         <v>9</v>
@@ -61671,7 +61668,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G2244" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="H2244" t="s">
         <v>9</v>
@@ -61697,7 +61694,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G2245" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="H2245" t="s">
         <v>9</v>
@@ -61723,7 +61720,7 @@
         <v>23.5</v>
       </c>
       <c r="G2246" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="H2246" t="s">
         <v>9</v>
@@ -61749,7 +61746,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G2247" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -61775,7 +61772,7 @@
         <v>23</v>
       </c>
       <c r="G2248" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="H2248" t="s">
         <v>9</v>
@@ -61801,7 +61798,7 @@
         <v>22.5</v>
       </c>
       <c r="G2249" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="H2249" t="s">
         <v>9</v>
@@ -61827,7 +61824,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G2250" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -61853,7 +61850,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G2251" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -61879,7 +61876,7 @@
         <v>24</v>
       </c>
       <c r="G2252" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -61905,7 +61902,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G2253" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="H2253" t="s">
         <v>9</v>
@@ -61931,7 +61928,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G2254" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="H2254" t="s">
         <v>9</v>
@@ -61957,7 +61954,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G2255" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="H2255" t="s">
         <v>9</v>
@@ -61983,7 +61980,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G2256" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -62009,7 +62006,7 @@
         <v>22.5</v>
       </c>
       <c r="G2257" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -62035,7 +62032,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G2258" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="H2258" t="s">
         <v>9</v>
@@ -62061,7 +62058,7 @@
         <v>23</v>
       </c>
       <c r="G2259" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="H2259" t="s">
         <v>9</v>
@@ -62087,7 +62084,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G2260" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="H2260" t="s">
         <v>9</v>
@@ -62113,7 +62110,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G2261" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -62139,7 +62136,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G2262" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="H2262" t="s">
         <v>9</v>
@@ -62165,7 +62162,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G2263" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -62191,7 +62188,7 @@
         <v>23</v>
       </c>
       <c r="G2264" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="H2264" t="s">
         <v>9</v>
@@ -62217,7 +62214,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G2265" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -62243,7 +62240,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G2266" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -62269,7 +62266,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G2267" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="H2267" t="s">
         <v>9</v>
@@ -62295,7 +62292,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G2268" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -62321,7 +62318,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G2269" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -62347,7 +62344,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G2270" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -62373,7 +62370,7 @@
         <v>23.5</v>
       </c>
       <c r="G2271" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -62399,7 +62396,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G2272" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -62425,7 +62422,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G2273" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -62451,7 +62448,7 @@
         <v>23.5</v>
       </c>
       <c r="G2274" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -62477,7 +62474,7 @@
         <v>23.5</v>
       </c>
       <c r="G2275" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -62503,7 +62500,7 @@
         <v>23.5</v>
       </c>
       <c r="G2276" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -62529,7 +62526,7 @@
         <v>23.5</v>
       </c>
       <c r="G2277" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -62555,7 +62552,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G2278" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -62581,7 +62578,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G2279" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -62607,7 +62604,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G2280" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -62633,7 +62630,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G2281" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -62659,7 +62656,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G2282" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -62685,7 +62682,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G2283" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -62711,7 +62708,7 @@
         <v>23.5</v>
       </c>
       <c r="G2284" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -62737,7 +62734,7 @@
         <v>23.5</v>
       </c>
       <c r="G2285" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -62763,7 +62760,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G2286" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -62789,7 +62786,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G2287" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="H2287" t="s">
         <v>9</v>
@@ -62815,7 +62812,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G2288" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -62841,7 +62838,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G2289" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -62867,7 +62864,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G2290" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -62893,7 +62890,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G2291" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="H2291" t="s">
         <v>9</v>
@@ -62919,7 +62916,7 @@
         <v>23.5</v>
       </c>
       <c r="G2292" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -62945,7 +62942,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G2293" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -62971,7 +62968,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G2294" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -62997,7 +62994,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G2295" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -63023,7 +63020,7 @@
         <v>23</v>
       </c>
       <c r="G2296" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -63049,7 +63046,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G2297" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -63075,7 +63072,7 @@
         <v>22.5</v>
       </c>
       <c r="G2298" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -63101,7 +63098,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G2299" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -63127,7 +63124,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G2300" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -63153,7 +63150,7 @@
         <v>22</v>
       </c>
       <c r="G2301" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -63179,7 +63176,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G2302" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -63205,7 +63202,7 @@
         <v>22.5</v>
       </c>
       <c r="G2303" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -63231,7 +63228,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G2304" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -63257,7 +63254,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G2305" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -63283,7 +63280,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G2306" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -63309,7 +63306,7 @@
         <v>23</v>
       </c>
       <c r="G2307" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -63335,7 +63332,7 @@
         <v>23</v>
       </c>
       <c r="G2308" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -63361,7 +63358,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G2309" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -63387,7 +63384,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G2310" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -63413,7 +63410,7 @@
         <v>23.5</v>
       </c>
       <c r="G2311" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -63439,7 +63436,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G2312" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -63465,7 +63462,7 @@
         <v>23.5</v>
       </c>
       <c r="G2313" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -63491,7 +63488,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G2314" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -63517,7 +63514,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G2315" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -63543,7 +63540,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G2316" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -63569,7 +63566,7 @@
         <v>23</v>
       </c>
       <c r="G2317" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -63595,7 +63592,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G2318" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -63621,7 +63618,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G2319" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -63647,7 +63644,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G2320" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -63673,7 +63670,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G2321" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -63699,7 +63696,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G2322" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -63725,7 +63722,7 @@
         <v>22.5</v>
       </c>
       <c r="G2323" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -63751,7 +63748,7 @@
         <v>22.5</v>
       </c>
       <c r="G2324" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -63777,7 +63774,7 @@
         <v>22.5</v>
       </c>
       <c r="G2325" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -63803,7 +63800,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G2326" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -63829,7 +63826,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G2327" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -63855,7 +63852,7 @@
         <v>22.5</v>
       </c>
       <c r="G2328" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -63881,7 +63878,7 @@
         <v>22.5</v>
       </c>
       <c r="G2329" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -63907,7 +63904,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G2330" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -63933,7 +63930,7 @@
         <v>22.5</v>
       </c>
       <c r="G2331" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -63959,7 +63956,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G2332" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -63985,7 +63982,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G2333" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -64011,7 +64008,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G2334" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -64037,7 +64034,7 @@
         <v>21</v>
       </c>
       <c r="G2335" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -64063,7 +64060,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G2336" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -64089,7 +64086,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G2337" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -64115,7 +64112,7 @@
         <v>21</v>
       </c>
       <c r="G2338" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -64141,7 +64138,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G2339" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -64167,7 +64164,7 @@
         <v>20.5</v>
       </c>
       <c r="G2340" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -64193,7 +64190,7 @@
         <v>20.5</v>
       </c>
       <c r="G2341" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -64219,7 +64216,7 @@
         <v>20.5</v>
       </c>
       <c r="G2342" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -64245,7 +64242,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G2343" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -64271,7 +64268,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G2344" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -64297,7 +64294,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G2345" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -64323,7 +64320,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G2346" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -64349,7 +64346,7 @@
         <v>22</v>
       </c>
       <c r="G2347" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -64375,7 +64372,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G2348" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -64401,7 +64398,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G2349" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -64427,7 +64424,7 @@
         <v>21.5</v>
       </c>
       <c r="G2350" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -64453,7 +64450,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G2351" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -64479,7 +64476,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G2352" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -64505,7 +64502,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G2353" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -64531,7 +64528,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G2354" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -64557,7 +64554,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G2355" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -64583,7 +64580,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G2356" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -64609,7 +64606,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G2357" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -64635,7 +64632,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G2358" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -64661,7 +64658,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G2359" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -64687,7 +64684,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G2360" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -64713,7 +64710,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G2361" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -64739,7 +64736,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G2362" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -64765,7 +64762,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G2363" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -64791,7 +64788,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G2364" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -64817,7 +64814,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G2365" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -64843,7 +64840,7 @@
         <v>21</v>
       </c>
       <c r="G2366" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -64869,7 +64866,7 @@
         <v>21</v>
       </c>
       <c r="G2367" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -64895,7 +64892,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G2368" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -64921,7 +64918,7 @@
         <v>21</v>
       </c>
       <c r="G2369" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -64947,7 +64944,7 @@
         <v>21</v>
       </c>
       <c r="G2370" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -64973,7 +64970,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G2371" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -64999,7 +64996,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G2372" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -65025,7 +65022,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G2373" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -65051,7 +65048,7 @@
         <v>20.5</v>
       </c>
       <c r="G2374" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -65077,7 +65074,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G2375" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -65103,7 +65100,7 @@
         <v>19.9500007629395</v>
       </c>
       <c r="G2376" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -65129,7 +65126,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G2377" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -65155,7 +65152,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G2378" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -65181,7 +65178,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G2379" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -65207,7 +65204,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G2380" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -65233,7 +65230,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G2381" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -65259,7 +65256,7 @@
         <v>21.5</v>
       </c>
       <c r="G2382" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -65285,7 +65282,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G2383" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -65311,7 +65308,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G2384" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -65337,7 +65334,7 @@
         <v>21.5</v>
       </c>
       <c r="G2385" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -65363,7 +65360,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G2386" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -65389,7 +65386,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G2387" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -65415,7 +65412,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G2388" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -65441,7 +65438,7 @@
         <v>21</v>
       </c>
       <c r="G2389" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -65467,7 +65464,7 @@
         <v>21</v>
       </c>
       <c r="G2390" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -65493,7 +65490,7 @@
         <v>21</v>
       </c>
       <c r="G2391" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -65519,7 +65516,7 @@
         <v>21</v>
       </c>
       <c r="G2392" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -65545,7 +65542,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G2393" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -65571,7 +65568,7 @@
         <v>21</v>
       </c>
       <c r="G2394" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -65597,7 +65594,7 @@
         <v>21</v>
       </c>
       <c r="G2395" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -65623,7 +65620,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G2396" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -65649,7 +65646,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G2397" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -65675,7 +65672,7 @@
         <v>21.5</v>
       </c>
       <c r="G2398" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -65701,7 +65698,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G2399" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -65727,7 +65724,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G2400" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -65753,7 +65750,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G2401" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -65779,7 +65776,7 @@
         <v>21.5</v>
       </c>
       <c r="G2402" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -65805,7 +65802,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G2403" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -65831,7 +65828,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G2404" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -65857,7 +65854,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G2405" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -65883,7 +65880,7 @@
         <v>21</v>
       </c>
       <c r="G2406" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -65909,7 +65906,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G2407" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -65935,7 +65932,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G2408" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -65961,7 +65958,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G2409" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -65987,7 +65984,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G2410" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -66013,7 +66010,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G2411" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -66039,7 +66036,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G2412" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -66065,7 +66062,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G2413" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -66091,7 +66088,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G2414" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -66117,7 +66114,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G2415" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -66143,7 +66140,7 @@
         <v>20.5</v>
       </c>
       <c r="G2416" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -66169,7 +66166,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G2417" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -66195,7 +66192,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G2418" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -66221,7 +66218,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G2419" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -66247,7 +66244,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G2420" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -66273,7 +66270,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G2421" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -66299,7 +66296,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G2422" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -66325,7 +66322,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G2423" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -66351,7 +66348,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G2424" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -66377,7 +66374,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G2425" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -66403,7 +66400,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G2426" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -66429,7 +66426,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G2427" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -66455,7 +66452,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G2428" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -66481,7 +66478,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G2429" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -66507,7 +66504,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G2430" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -66533,7 +66530,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G2431" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -66559,7 +66556,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G2432" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -66585,7 +66582,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G2433" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -66611,7 +66608,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G2434" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -66637,7 +66634,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G2435" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -66663,7 +66660,7 @@
         <v>20.5</v>
       </c>
       <c r="G2436" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -66689,7 +66686,7 @@
         <v>20.5</v>
       </c>
       <c r="G2437" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -66715,7 +66712,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G2438" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -66741,7 +66738,7 @@
         <v>20.5</v>
       </c>
       <c r="G2439" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -66767,7 +66764,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G2440" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -66793,7 +66790,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G2441" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -66819,7 +66816,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G2442" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -66845,7 +66842,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G2443" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -66871,7 +66868,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G2444" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -66897,7 +66894,7 @@
         <v>20.5</v>
       </c>
       <c r="G2445" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -66923,7 +66920,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G2446" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -66949,7 +66946,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G2447" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -66975,7 +66972,7 @@
         <v>20.5</v>
       </c>
       <c r="G2448" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -67001,7 +66998,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G2449" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -67027,7 +67024,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G2450" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -67053,7 +67050,7 @@
         <v>21</v>
       </c>
       <c r="G2451" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -67079,7 +67076,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G2452" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -67105,7 +67102,7 @@
         <v>22</v>
       </c>
       <c r="G2453" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -67131,7 +67128,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G2454" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -67157,7 +67154,7 @@
         <v>22</v>
       </c>
       <c r="G2455" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -67183,7 +67180,7 @@
         <v>22</v>
       </c>
       <c r="G2456" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -67209,7 +67206,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G2457" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -67235,7 +67232,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G2458" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -67261,7 +67258,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G2459" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -67287,7 +67284,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G2460" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -67313,7 +67310,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G2461" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -67339,7 +67336,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G2462" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -67365,7 +67362,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G2463" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -67391,7 +67388,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G2464" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -67417,7 +67414,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G2465" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -67443,7 +67440,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G2466" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -67469,7 +67466,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G2467" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -67495,7 +67492,7 @@
         <v>22.5</v>
       </c>
       <c r="G2468" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -67521,7 +67518,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G2469" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -67547,7 +67544,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G2470" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -67573,7 +67570,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G2471" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -67599,7 +67596,7 @@
         <v>22.5</v>
       </c>
       <c r="G2472" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -67625,7 +67622,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G2473" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -67651,7 +67648,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G2474" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -67677,7 +67674,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G2475" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -67703,7 +67700,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G2476" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -67729,7 +67726,7 @@
         <v>22.5</v>
       </c>
       <c r="G2477" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -67755,7 +67752,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G2478" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -67781,7 +67778,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G2479" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -67807,7 +67804,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G2480" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -67833,7 +67830,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G2481" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -67859,7 +67856,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G2482" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -67885,7 +67882,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G2483" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -67911,7 +67908,7 @@
         <v>23.5</v>
       </c>
       <c r="G2484" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -67937,7 +67934,7 @@
         <v>23</v>
       </c>
       <c r="G2485" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -67963,7 +67960,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G2486" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -67989,7 +67986,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G2487" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -68015,7 +68012,7 @@
         <v>23.5</v>
       </c>
       <c r="G2488" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -68041,7 +68038,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G2489" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -68067,7 +68064,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G2490" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -68093,7 +68090,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G2491" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -68119,7 +68116,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G2492" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -68145,7 +68142,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G2493" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -68171,7 +68168,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G2494" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="H2494" t="s">
         <v>9</v>
@@ -68197,7 +68194,7 @@
         <v>23</v>
       </c>
       <c r="G2495" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="H2495" t="s">
         <v>9</v>
@@ -68223,7 +68220,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G2496" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="H2496" t="s">
         <v>9</v>
@@ -68249,7 +68246,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G2497" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="H2497" t="s">
         <v>9</v>
@@ -68275,7 +68272,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G2498" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="H2498" t="s">
         <v>9</v>
@@ -68301,7 +68298,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G2499" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="H2499" t="s">
         <v>9</v>
@@ -68327,7 +68324,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G2500" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="H2500" t="s">
         <v>9</v>
@@ -68353,7 +68350,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G2501" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="H2501" t="s">
         <v>9</v>
@@ -68379,7 +68376,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G2502" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="H2502" t="s">
         <v>9</v>
@@ -68405,7 +68402,7 @@
         <v>22.5</v>
       </c>
       <c r="G2503" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="H2503" t="s">
         <v>9</v>
@@ -68413,7 +68410,7 @@
     </row>
     <row r="2504">
       <c r="A2504" s="1" t="n">
-        <v>45965.6910300926</v>
+        <v>45965.3333333333</v>
       </c>
       <c r="B2504" t="n">
         <v>8746</v>
@@ -68431,9 +68428,35 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G2504" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="H2504" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2505">
+      <c r="A2505" s="1" t="n">
+        <v>45966.6910416667</v>
+      </c>
+      <c r="B2505" t="n">
+        <v>8442</v>
+      </c>
+      <c r="C2505" t="n">
+        <v>22.2000007629395</v>
+      </c>
+      <c r="D2505" t="n">
+        <v>21.7000007629395</v>
+      </c>
+      <c r="E2505" t="n">
+        <v>22</v>
+      </c>
+      <c r="F2505" t="n">
+        <v>21.8999996185303</v>
+      </c>
+      <c r="G2505" t="s">
+        <v>979</v>
+      </c>
+      <c r="H2505" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IWB.MI.xlsx
+++ b/data/IWB.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="996" uniqueCount="996">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="997" uniqueCount="997">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,28 +38,28 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84661722183228</t>
+    <t xml:space="preserve">7.8466157913208</t>
   </si>
   <si>
     <t xml:space="preserve">IWB.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79867506027222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83063411712646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7427396774292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75073099136353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71077966690063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69479751586914</t>
+    <t xml:space="preserve">7.79867458343506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83063507080078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74274015426636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75073194503784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71077823638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6947979927063</t>
   </si>
   <si>
     <t xml:space="preserve">7.5909218788147</t>
@@ -68,7 +68,7 @@
     <t xml:space="preserve">7.51101732254028</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31125640869141</t>
+    <t xml:space="preserve">7.31125736236572</t>
   </si>
   <si>
     <t xml:space="preserve">7.44709396362305</t>
@@ -77,136 +77,136 @@
     <t xml:space="preserve">7.35120964050293</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29527616500854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26331329345703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29927110671997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29128217697144</t>
+    <t xml:space="preserve">7.29527568817139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26331472396851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29927062988281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29127979278564</t>
   </si>
   <si>
     <t xml:space="preserve">7.27130460739136</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24733257293701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37518167495728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43111324310303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47106695175171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15144777297974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41513252258301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32723808288574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28728532791138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99163913726807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11149549484253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19139957427979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25532245635986</t>
+    <t xml:space="preserve">7.24733352661133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37518119812012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4311146736145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47106504440308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1514458656311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41513204574585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32723760604858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28728485107422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99163818359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11149501800537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19140100479126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25532388687134</t>
   </si>
   <si>
     <t xml:space="preserve">7.41912698745728</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42312383651733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63087558746338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67082500457764</t>
+    <t xml:space="preserve">7.42312240600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6308741569519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67082643508911</t>
   </si>
   <si>
     <t xml:space="preserve">7.49903249740601</t>
   </si>
   <si>
-    <t xml:space="preserve">7.582932472229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89455890655518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98644876480103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91053915023804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54297828674316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82264518737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64286136627197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62288379669189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77470254898071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7667121887207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79068231582642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87058925628662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96647500991821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71876907348633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66283655166626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57094764709473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55896091461182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39116191864014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46307563781738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60690450668335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54697465896606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36719131469727</t>
+    <t xml:space="preserve">7.58293199539185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89455986022949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98644971847534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91053867340088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54297924041748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82264566421509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6428599357605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62288331985474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77470207214355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76671266555786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79068422317505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8705883026123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96647357940674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7187705039978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66283559799194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57094526290894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5589599609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39116096496582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46307468414307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60690259933472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54697513580322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36719036102295</t>
   </si>
   <si>
     <t xml:space="preserve">7.31525087356567</t>
@@ -215,37 +215,37 @@
     <t xml:space="preserve">7.33123207092285</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34721279144287</t>
+    <t xml:space="preserve">7.34721422195435</t>
   </si>
   <si>
     <t xml:space="preserve">7.50302696228027</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2433385848999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22336149215698</t>
+    <t xml:space="preserve">7.24333667755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22336053848267</t>
   </si>
   <si>
     <t xml:space="preserve">7.23934268951416</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4590802192688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46707057952881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10350608825684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89974927902222</t>
+    <t xml:space="preserve">7.45907878875732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46707153320312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10350465774536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89974880218506</t>
   </si>
   <si>
     <t xml:space="preserve">6.91173410415649</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9516863822937</t>
+    <t xml:space="preserve">6.95168590545654</t>
   </si>
   <si>
     <t xml:space="preserve">7.00761985778809</t>
@@ -254,133 +254,133 @@
     <t xml:space="preserve">6.8717827796936</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87577724456787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8797721862793</t>
+    <t xml:space="preserve">6.87577676773071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87977266311646</t>
   </si>
   <si>
     <t xml:space="preserve">6.86778783798218</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75192594528198</t>
+    <t xml:space="preserve">6.75192546844482</t>
   </si>
   <si>
     <t xml:space="preserve">6.74393558502197</t>
   </si>
   <si>
-    <t xml:space="preserve">6.82383918762207</t>
+    <t xml:space="preserve">6.82383871078491</t>
   </si>
   <si>
     <t xml:space="preserve">6.6640305519104</t>
   </si>
   <si>
-    <t xml:space="preserve">6.83182954788208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89575481414795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03159141540527</t>
+    <t xml:space="preserve">6.83183002471924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89575290679932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03159093856812</t>
   </si>
   <si>
     <t xml:space="preserve">7.07154417037964</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33522796630859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25931978225708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17941427230835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26731014251709</t>
+    <t xml:space="preserve">7.33522844314575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25931930541992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17941379547119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26730918884277</t>
   </si>
   <si>
     <t xml:space="preserve">7.23135185241699</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09551477432251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18340969085693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18740510940552</t>
+    <t xml:space="preserve">7.09551382064819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18340826034546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18740463256836</t>
   </si>
   <si>
     <t xml:space="preserve">7.20738077163696</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14345598220825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12347984313965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23534870147705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74673557281494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83463096618652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98245477676392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92652177810669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78269195556641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63886547088623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73474931716919</t>
+    <t xml:space="preserve">7.14345741271973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12348127365112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23534727096558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74673509597778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83463001251221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98245429992676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92652082443237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78269243240356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63886404037476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73474979400635</t>
   </si>
   <si>
     <t xml:space="preserve">8.07034873962402</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21417713165283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16623497009277</t>
+    <t xml:space="preserve">8.2141752243042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16623401641846</t>
   </si>
   <si>
     <t xml:space="preserve">8.18221569061279</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27010917663574</t>
+    <t xml:space="preserve">8.27011013031006</t>
   </si>
   <si>
     <t xml:space="preserve">8.57374572753906</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54977607727051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35001468658447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46987152099609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.525803565979</t>
+    <t xml:space="preserve">8.54977416992188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35001373291016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46987056732178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52580261230469</t>
   </si>
   <si>
     <t xml:space="preserve">8.5098237991333</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59771919250488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60570907592773</t>
+    <t xml:space="preserve">8.59771728515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60571002960205</t>
   </si>
   <si>
     <t xml:space="preserve">8.58173751831055</t>
@@ -389,13 +389,13 @@
     <t xml:space="preserve">8.64687442779541</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67130088806152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61430644989014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63059043884277</t>
+    <t xml:space="preserve">8.67129993438721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61430358886719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63058948516846</t>
   </si>
   <si>
     <t xml:space="preserve">8.75272083282471</t>
@@ -404,10 +404,10 @@
     <t xml:space="preserve">8.82600021362305</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87485218048096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95627212524414</t>
+    <t xml:space="preserve">8.87485027313232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95627307891846</t>
   </si>
   <si>
     <t xml:space="preserve">8.74457836151123</t>
@@ -419,109 +419,109 @@
     <t xml:space="preserve">8.84228420257568</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91556072235107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03769302368164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00512599945068</t>
+    <t xml:space="preserve">8.91556262969971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03769397735596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00512504577637</t>
   </si>
   <si>
     <t xml:space="preserve">8.94813060760498</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99698257446289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1272554397583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19239330291748</t>
+    <t xml:space="preserve">8.99698352813721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12725448608398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19239139556885</t>
   </si>
   <si>
     <t xml:space="preserve">9.11911296844482</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14354038238525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98069763183594</t>
+    <t xml:space="preserve">9.14353942871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98069858551025</t>
   </si>
   <si>
     <t xml:space="preserve">9.13539791107178</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16796779632568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15982437133789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.184250831604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15168285369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07026100158691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9644136428833</t>
+    <t xml:space="preserve">9.16796684265137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15982341766357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18424987792969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15167999267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07026195526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96441459655762</t>
   </si>
   <si>
     <t xml:space="preserve">8.92370414733887</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80157279968262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79343032836914</t>
+    <t xml:space="preserve">8.80157375335693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79343223571777</t>
   </si>
   <si>
     <t xml:space="preserve">8.8667106628418</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90741920471191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89113616943359</t>
+    <t xml:space="preserve">8.90742015838623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89113712310791</t>
   </si>
   <si>
     <t xml:space="preserve">9.11097145080566</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20053482055664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28195285797119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35523319244385</t>
+    <t xml:space="preserve">9.20053386688232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28195476531982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35523414611816</t>
   </si>
   <si>
     <t xml:space="preserve">9.3959436416626</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32266426086426</t>
+    <t xml:space="preserve">9.32266521453857</t>
   </si>
   <si>
     <t xml:space="preserve">9.64834880828857</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60763645172119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90075206756592</t>
+    <t xml:space="preserve">9.60763740539551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9007511138916</t>
   </si>
   <si>
     <t xml:space="preserve">9.99031448364258</t>
   </si>
   <si>
-    <t xml:space="preserve">10.120587348938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1368722915649</t>
+    <t xml:space="preserve">10.1205892562866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1368713378906</t>
   </si>
   <si>
     <t xml:space="preserve">10.1775817871094</t>
@@ -530,7 +530,7 @@
     <t xml:space="preserve">10.1043043136597</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1531562805176</t>
+    <t xml:space="preserve">10.1531572341919</t>
   </si>
   <si>
     <t xml:space="preserve">10.0961608886719</t>
@@ -539,34 +539,34 @@
     <t xml:space="preserve">9.94146251678467</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90889453887939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77047824859619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83561515808105</t>
+    <t xml:space="preserve">9.90889358520508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77047920227051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83561611175537</t>
   </si>
   <si>
     <t xml:space="preserve">9.91703605651855</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7949047088623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7786226272583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78676509857178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9577465057373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0147399902344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99845790863037</t>
+    <t xml:space="preserve">9.79490566253662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77862071990967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78676319122314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95774555206299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.014741897583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99845600128174</t>
   </si>
   <si>
     <t xml:space="preserve">9.88446807861328</t>
@@ -575,61 +575,61 @@
     <t xml:space="preserve">9.86004161834717</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85190010070801</t>
+    <t xml:space="preserve">9.85189914703369</t>
   </si>
   <si>
     <t xml:space="preserve">9.89260959625244</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2590026855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3404235839844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4625549316406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5276918411255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5765447616577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5439758300781</t>
+    <t xml:space="preserve">10.2590045928955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3404245376587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4625558853149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5276908874512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5765419006348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5439748764038</t>
   </si>
   <si>
     <t xml:space="preserve">10.5358324050903</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5032634735107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.552116394043</t>
+    <t xml:space="preserve">10.5032644271851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5521173477173</t>
   </si>
   <si>
     <t xml:space="preserve">10.3485670089722</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4381284713745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3241395950317</t>
+    <t xml:space="preserve">10.4381275177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3241386413574</t>
   </si>
   <si>
     <t xml:space="preserve">10.3811340332031</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3648500442505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4218435287476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4137020111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3729906082153</t>
+    <t xml:space="preserve">10.3648490905762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4218454360962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4137029647827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3729934692383</t>
   </si>
   <si>
     <t xml:space="preserve">10.3892765045166</t>
@@ -638,37 +638,37 @@
     <t xml:space="preserve">10.2915725708008</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2671451568604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2264347076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1938676834106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3159971237183</t>
+    <t xml:space="preserve">10.267144203186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2264356613159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.193868637085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3159980773926</t>
   </si>
   <si>
     <t xml:space="preserve">10.2182922363281</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2834300994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.429986000061</t>
+    <t xml:space="preserve">10.2834310531616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4299879074097</t>
   </si>
   <si>
     <t xml:space="preserve">10.3322820663452</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2427196502686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5846853256226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6661071777344</t>
+    <t xml:space="preserve">10.2427206039429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5846862792969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6661062240601</t>
   </si>
   <si>
     <t xml:space="preserve">10.7068166732788</t>
@@ -677,25 +677,25 @@
     <t xml:space="preserve">10.7475261688232</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7882375717163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6253957748413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8696584701538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8289489746094</t>
+    <t xml:space="preserve">10.788236618042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.625394821167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8696575164795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8289480209351</t>
   </si>
   <si>
     <t xml:space="preserve">11.0324983596802</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2360515594482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4396028518677</t>
+    <t xml:space="preserve">11.2360496520996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4396018981934</t>
   </si>
   <si>
     <t xml:space="preserve">11.6838645935059</t>
@@ -707,79 +707,76 @@
     <t xml:space="preserve">10.9917888641357</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1546287536621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3174715042114</t>
+    <t xml:space="preserve">11.1546297073364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3174724578857</t>
   </si>
   <si>
     <t xml:space="preserve">11.2767610549927</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1953401565552</t>
+    <t xml:space="preserve">11.1953411102295</t>
   </si>
   <si>
     <t xml:space="preserve">11.3581809997559</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4839181900024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5258302688599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5677423477173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4000949859619</t>
+    <t xml:space="preserve">11.4839172363281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5258312225342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.567741394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4000959396362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0228843688965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1486215591431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2324447631836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1905345916748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.274356842041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8971490859985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0647964477539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4420042037964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8552360534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6875886917114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3254737854004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.282247543335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1957941055298</t>
   </si>
   <si>
     <t xml:space="preserve">11.0228853225708</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1486215591431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2324447631836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1905336380005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.274356842041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8971481323242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0647964477539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3581819534302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4420051574707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8552370071411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6875877380371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3254747390747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2822484970093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1957931518555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0228862762451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2390184402466</t>
+    <t xml:space="preserve">11.2390203475952</t>
   </si>
   <si>
     <t xml:space="preserve">11.15256690979</t>
@@ -788,22 +785,22 @@
     <t xml:space="preserve">10.9364309310913</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0661125183105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.109338760376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9796581268311</t>
+    <t xml:space="preserve">11.0661115646362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1093397140503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9796571731567</t>
   </si>
   <si>
     <t xml:space="preserve">10.7635231018066</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5906143188477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8499765396118</t>
+    <t xml:space="preserve">10.5906171798706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8499774932861</t>
   </si>
   <si>
     <t xml:space="preserve">10.7202949523926</t>
@@ -812,13 +809,13 @@
     <t xml:space="preserve">10.6770696640015</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8067502975464</t>
+    <t xml:space="preserve">10.8067512512207</t>
   </si>
   <si>
     <t xml:space="preserve">10.8932056427002</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6338424682617</t>
+    <t xml:space="preserve">10.6338415145874</t>
   </si>
   <si>
     <t xml:space="preserve">11.4119281768799</t>
@@ -827,316 +824,319 @@
     <t xml:space="preserve">11.4551544189453</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3687009811401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5416107177734</t>
+    <t xml:space="preserve">11.3687000274658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5416088104248</t>
   </si>
   <si>
     <t xml:space="preserve">11.62806224823</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5848360061646</t>
+    <t xml:space="preserve">11.5848340988159</t>
   </si>
   <si>
     <t xml:space="preserve">10.4609336853027</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3312530517578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3744792938232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2880268096924</t>
+    <t xml:space="preserve">10.3312540054321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3744783401489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2880258560181</t>
   </si>
   <si>
     <t xml:space="preserve">10.5041608810425</t>
   </si>
   <si>
+    <t xml:space="preserve">10.0286655426025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94221019744873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59639549255371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63962078094482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81252861022949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85575580596924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55316734313965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03444290161133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81830978393555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86153411865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77508068084717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07767105102539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16412448883057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25057697296143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33703327178955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2938060760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2447996139526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68284702301025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1583442687988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98543739318848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89898204803467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76930141448975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72607517242432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46671199798584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50993919372559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3802604675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42348766326904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20734977722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.071891784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.297290802002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2077465057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1629772186279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3420600891113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4315996170044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3868312835693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1182050704956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2525177001953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.476372718811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6554555892944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7897691726685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7449960708618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5659151077271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7002267837524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1031637191772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9688529968262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9240808486938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8793096542358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1479339599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2822494506836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.237476348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4613313674927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.327018737793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1927061080933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3717889785767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4165601730347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0583934783936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6404142379761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7299547195435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6851835250854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7747259140015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8194980621338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8642683029175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5508718490601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5956439971924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5211429595947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0136232376099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8345394134521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9985790252686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0881214141846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0433502197266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1328935623169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2224349975586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1776638031006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.356746673584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2672061920166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.401517868042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3119764328003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6701431274414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6253728866577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5806016921997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6106853485107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6257266998291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0734348297119</t>
+  </si>
+  <si>
     <t xml:space="preserve">10.0286645889282</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94220924377441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59639453887939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63961982727051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81253051757812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85575485229492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55316829681396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03444385528564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81830883026123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86153507232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77507972717285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07767009735107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16412353515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25057792663574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33703422546387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29380416870117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2447996139526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68284893035889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1583452224731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98543739318848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89898300170898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76930236816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72607517242432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46671295166016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50993919372559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38025951385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42348480224609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.207350730896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0718908309937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2972888946533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2077474594116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1629762649536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3420610427856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.431601524353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3868322372437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1182060241699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2525177001953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4763717651367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6554565429688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7897691726685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7449979782104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5659151077271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7002277374268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1031637191772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9688510894775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9240808486938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8793096542358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1479358673096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.237476348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4613304138184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3270177841187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1927070617676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3717889785767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.416561126709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0583934783936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6404142379761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7299556732178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6851863861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7747259140015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8194971084595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8642663955688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5508737564087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5956430435181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5211429595947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0136213302612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8345403671265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9985809326172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0881223678589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0433502197266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1328935623169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.22243309021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1776647567749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.356746673584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2672052383423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4015197753906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3119745254517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6701431274414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6253719329834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5806007385254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6106843948364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62572574615479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0734357833862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0286626815796</t>
-  </si>
-  <si>
     <t xml:space="preserve">12.4910593032837</t>
   </si>
   <si>
     <t xml:space="preserve">11.9090385437012</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1626214981079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6998739242554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8789548873901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0132675170898</t>
+    <t xml:space="preserve">13.1626224517822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6998720169067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8789539337158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0132665634155</t>
   </si>
   <si>
     <t xml:space="preserve">14.1475801467896</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2371215820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1923522949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9237260818481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9684982299805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7894124984741</t>
+    <t xml:space="preserve">14.2371225357056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1923503875732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9237270355225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9684972763062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7894134521484</t>
   </si>
   <si>
     <t xml:space="preserve">14.2818918228149</t>
@@ -1148,37 +1148,40 @@
     <t xml:space="preserve">13.5207891464233</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4312467575073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5655584335327</t>
+    <t xml:space="preserve">13.4312477111816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5655574798584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6103296279907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7004642486572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7905988693237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8356666564941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6553955078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5201950073242</t>
   </si>
   <si>
     <t xml:space="preserve">13.610330581665</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7004652023315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7906007766724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8356666564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6553964614868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5201950073242</t>
-  </si>
-  <si>
     <t xml:space="preserve">13.2948589324951</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1596565246582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0695219039917</t>
+    <t xml:space="preserve">13.1596574783325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.069522857666</t>
   </si>
   <si>
     <t xml:space="preserve">12.9793872833252</t>
@@ -1190,7 +1193,7 @@
     <t xml:space="preserve">12.5737810134888</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6188488006592</t>
+    <t xml:space="preserve">12.6188497543335</t>
   </si>
   <si>
     <t xml:space="preserve">13.3399257659912</t>
@@ -1202,7 +1205,7 @@
     <t xml:space="preserve">13.4751281738281</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9343204498291</t>
+    <t xml:space="preserve">12.9343214035034</t>
   </si>
   <si>
     <t xml:space="preserve">12.7540512084961</t>
@@ -1211,130 +1214,130 @@
     <t xml:space="preserve">12.8441858291626</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0610046386719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8807325363159</t>
+    <t xml:space="preserve">14.0610036849976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8807344436646</t>
   </si>
   <si>
     <t xml:space="preserve">14.1962060928345</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3314065933228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4215412139893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3764734268188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5116758346558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.466609954834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6018123626709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6919441223145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8722162246704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2327518463135</t>
+    <t xml:space="preserve">14.3314075469971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4215421676636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3764743804932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5116777420044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4666080474854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6018104553223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6919450759888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8722152709961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2327537536621</t>
   </si>
   <si>
     <t xml:space="preserve">15.0074167251587</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3228893280029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.187686920166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2242336273193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9538326263428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8551788330078</t>
+    <t xml:space="preserve">15.3228883743286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1876850128174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.224235534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9538297653198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8551769256592</t>
   </si>
   <si>
     <t xml:space="preserve">16.3143711090088</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9903793334961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8101081848145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7565212249756</t>
+    <t xml:space="preserve">16.9903774261475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8101119995117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7565250396729</t>
   </si>
   <si>
     <t xml:space="preserve">18.0269260406494</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9367904663086</t>
+    <t xml:space="preserve">17.9367923736572</t>
   </si>
   <si>
     <t xml:space="preserve">17.3509159088135</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4410533905029</t>
+    <t xml:space="preserve">17.4410572052002</t>
   </si>
   <si>
     <t xml:space="preserve">17.4861183166504</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0354442596436</t>
+    <t xml:space="preserve">17.0354461669922</t>
   </si>
   <si>
     <t xml:space="preserve">16.6298408508301</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7199745178223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.404504776001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6749076843262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9453105926514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.765043258667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8636980056763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9988965988159</t>
+    <t xml:space="preserve">16.7199726104736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4045028686523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6749057769775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7650413513184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.863697052002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9988956451416</t>
   </si>
   <si>
     <t xml:space="preserve">16.4946365356445</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3594360351562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1791667938232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5847721099854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5397033691406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6834259033203</t>
+    <t xml:space="preserve">16.3594341278076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1791706085205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5847702026367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5397071838379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6834278106689</t>
   </si>
   <si>
     <t xml:space="preserve">16.0890312194824</t>
@@ -1343,46 +1346,46 @@
     <t xml:space="preserve">15.5932922363281</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2693004608154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1255798339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5762538909912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6663875579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.846658706665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5677337646484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3874664306641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7480030059814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3789443969727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0098915100098</t>
+    <t xml:space="preserve">16.2693023681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.125581741333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5762557983398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.666389465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8466548919678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5677356719971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3874645233154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7480049133301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3789463043213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0098876953125</t>
   </si>
   <si>
     <t xml:space="preserve">20.5506954193115</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4605617523193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.280294418335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3704280853271</t>
+    <t xml:space="preserve">20.460563659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2802925109863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3704261779785</t>
   </si>
   <si>
     <t xml:space="preserve">20.1000232696533</t>
@@ -1391,52 +1394,49 @@
     <t xml:space="preserve">20.6408290863037</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7309646606445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4435253143311</t>
+    <t xml:space="preserve">20.7309665679932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4435234069824</t>
   </si>
   <si>
     <t xml:space="preserve">21.9027156829834</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5361423492432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.902717590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1695709228516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7194290161133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.360933303833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4525737762451</t>
+    <t xml:space="preserve">21.5361442565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1695690155029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7194328308105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3609294891357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4525756835938</t>
   </si>
   <si>
     <t xml:space="preserve">22.269287109375</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0860042572021</t>
+    <t xml:space="preserve">22.0860004425049</t>
   </si>
   <si>
     <t xml:space="preserve">21.9943599700928</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6277885437012</t>
+    <t xml:space="preserve">21.6277866363525</t>
   </si>
   <si>
     <t xml:space="preserve">23.2773628234863</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9107933044434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7275047302246</t>
+    <t xml:space="preserve">22.9107894897461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.727502822876</t>
   </si>
   <si>
     <t xml:space="preserve">22.1776466369629</t>
@@ -1451,19 +1451,19 @@
     <t xml:space="preserve">23.0940780639648</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1021518707275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.285436630249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.926944732666</t>
+    <t xml:space="preserve">24.1021499633789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2854385375977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9269428253174</t>
   </si>
   <si>
     <t xml:space="preserve">26.2099437713623</t>
   </si>
   <si>
-    <t xml:space="preserve">26.851448059082</t>
+    <t xml:space="preserve">26.8514461517334</t>
   </si>
   <si>
     <t xml:space="preserve">26.6681613922119</t>
@@ -1481,40 +1481,40 @@
     <t xml:space="preserve">26.5765171051025</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3015880584717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5684413909912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0347366333008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1425228118896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4093799591064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1344509124756</t>
+    <t xml:space="preserve">26.3015899658203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5684432983398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0347328186035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1425247192383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4093818664551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1344547271729</t>
   </si>
   <si>
     <t xml:space="preserve">28.2260913848877</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3646869659424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4570770263672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0875053405762</t>
+    <t xml:space="preserve">28.364688873291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4570751190186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0875072479248</t>
   </si>
   <si>
     <t xml:space="preserve">27.9951114654541</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9027194976807</t>
+    <t xml:space="preserve">27.9027214050293</t>
   </si>
   <si>
     <t xml:space="preserve">27.7179317474365</t>
@@ -1526,10 +1526,10 @@
     <t xml:space="preserve">29.9353694915771</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7505798339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3810062408447</t>
+    <t xml:space="preserve">29.750581741333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3810081481934</t>
   </si>
   <si>
     <t xml:space="preserve">28.8266506195068</t>
@@ -1541,22 +1541,22 @@
     <t xml:space="preserve">28.7342567443848</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0114345550537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8429756164551</t>
+    <t xml:space="preserve">29.0114364624023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8429737091064</t>
   </si>
   <si>
     <t xml:space="preserve">30.120153427124</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2125492095947</t>
+    <t xml:space="preserve">30.2125473022461</t>
   </si>
   <si>
     <t xml:space="preserve">30.027759552002</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3973350524902</t>
+    <t xml:space="preserve">30.3973331451416</t>
   </si>
   <si>
     <t xml:space="preserve">31.1364784240723</t>
@@ -1565,49 +1565,49 @@
     <t xml:space="preserve">30.8592987060547</t>
   </si>
   <si>
-    <t xml:space="preserve">31.0440845489502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6745109558105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4897212982178</t>
+    <t xml:space="preserve">31.0440826416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6745128631592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4897232055664</t>
   </si>
   <si>
     <t xml:space="preserve">29.2886161804199</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4734020233154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.8919486999512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.3539123535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.5550270080566</t>
+    <t xml:space="preserve">29.4734039306641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.8919448852539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.3539085388184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.5550231933594</t>
   </si>
   <si>
     <t xml:space="preserve">34.0930595397949</t>
   </si>
   <si>
-    <t xml:space="preserve">35.8485221862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.4192085266113</t>
+    <t xml:space="preserve">35.8485260009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.4192047119141</t>
   </si>
   <si>
     <t xml:space="preserve">40.0986099243164</t>
   </si>
   <si>
-    <t xml:space="preserve">37.2344169616699</t>
+    <t xml:space="preserve">37.2344207763672</t>
   </si>
   <si>
     <t xml:space="preserve">37.881175994873</t>
   </si>
   <si>
-    <t xml:space="preserve">38.1583557128906</t>
+    <t xml:space="preserve">38.1583518981934</t>
   </si>
   <si>
     <t xml:space="preserve">37.6039962768555</t>
@@ -1622,16 +1622,16 @@
     <t xml:space="preserve">37.1420288085938</t>
   </si>
   <si>
-    <t xml:space="preserve">38.5279312133789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.3431434631348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.4952735900879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.9409255981445</t>
+    <t xml:space="preserve">38.5279273986816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.3431358337402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.4952774047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.9409217834473</t>
   </si>
   <si>
     <t xml:space="preserve">36.4028854370117</t>
@@ -1646,10 +1646,10 @@
     <t xml:space="preserve">38.0659599304199</t>
   </si>
   <si>
-    <t xml:space="preserve">38.4355316162109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.805103302002</t>
+    <t xml:space="preserve">38.4355354309082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.8051071166992</t>
   </si>
   <si>
     <t xml:space="preserve">39.3594627380371</t>
@@ -1658,25 +1658,25 @@
     <t xml:space="preserve">39.8214263916016</t>
   </si>
   <si>
-    <t xml:space="preserve">40.0062141418457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.5605735778809</t>
+    <t xml:space="preserve">40.006217956543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.5605773925781</t>
   </si>
   <si>
     <t xml:space="preserve">40.6529693603516</t>
   </si>
   <si>
-    <t xml:space="preserve">41.9464721679688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.1149368286133</t>
+    <t xml:space="preserve">41.946475982666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.1149291992188</t>
   </si>
   <si>
     <t xml:space="preserve">40.9301452636719</t>
   </si>
   <si>
-    <t xml:space="preserve">42.3160400390625</t>
+    <t xml:space="preserve">42.3160438537598</t>
   </si>
   <si>
     <t xml:space="preserve">43.5171546936035</t>
@@ -1685,13 +1685,13 @@
     <t xml:space="preserve">44.0715141296387</t>
   </si>
   <si>
-    <t xml:space="preserve">43.8867263793945</t>
+    <t xml:space="preserve">43.8867225646973</t>
   </si>
   <si>
     <t xml:space="preserve">43.7019424438477</t>
   </si>
   <si>
-    <t xml:space="preserve">43.979118347168</t>
+    <t xml:space="preserve">43.9791221618652</t>
   </si>
   <si>
     <t xml:space="preserve">44.3486938476562</t>
@@ -1700,19 +1700,19 @@
     <t xml:space="preserve">44.9954452514648</t>
   </si>
   <si>
-    <t xml:space="preserve">44.810661315918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.5334777832031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.7943344116211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.1475791931152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.3921089172363</t>
+    <t xml:space="preserve">44.8106575012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.5334739685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.7943382263184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.1475830078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.3921165466309</t>
   </si>
   <si>
     <t xml:space="preserve">41.8540802001953</t>
@@ -1724,46 +1724,46 @@
     <t xml:space="preserve">41.2073249816895</t>
   </si>
   <si>
-    <t xml:space="preserve">40.1910018920898</t>
+    <t xml:space="preserve">40.1909980773926</t>
   </si>
   <si>
     <t xml:space="preserve">39.4518585205078</t>
   </si>
   <si>
-    <t xml:space="preserve">38.9898948669434</t>
+    <t xml:space="preserve">38.9898910522461</t>
   </si>
   <si>
     <t xml:space="preserve">39.1746788024902</t>
   </si>
   <si>
-    <t xml:space="preserve">39.5442504882812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.7453575134277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.0225372314453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.7290382385254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.9138259887695</t>
+    <t xml:space="preserve">39.5442543029785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.745361328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.0225448608398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.7290344238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.9138221740723</t>
   </si>
   <si>
     <t xml:space="preserve">40.4681816101074</t>
   </si>
   <si>
-    <t xml:space="preserve">39.6366424560547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.6203193664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.2670745849609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.3268165588379</t>
+    <t xml:space="preserve">39.636646270752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.6203155517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.2670669555664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.3268203735352</t>
   </si>
   <si>
     <t xml:space="preserve">38.8974990844727</t>
@@ -1772,7 +1772,7 @@
     <t xml:space="preserve">37.5116004943848</t>
   </si>
   <si>
-    <t xml:space="preserve">38.712718963623</t>
+    <t xml:space="preserve">38.7127113342285</t>
   </si>
   <si>
     <t xml:space="preserve">39.0822868347168</t>
@@ -1781,10 +1781,10 @@
     <t xml:space="preserve">36.7724571228027</t>
   </si>
   <si>
-    <t xml:space="preserve">36.3104858398438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.2181015014648</t>
+    <t xml:space="preserve">36.310489654541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.2180976867676</t>
   </si>
   <si>
     <t xml:space="preserve">35.3865623474121</t>
@@ -1796,10 +1796,10 @@
     <t xml:space="preserve">34.1854515075684</t>
   </si>
   <si>
-    <t xml:space="preserve">33.7234878540039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.1691284179688</t>
+    <t xml:space="preserve">33.7234840393066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.169132232666</t>
   </si>
   <si>
     <t xml:space="preserve">32.6147689819336</t>
@@ -1811,19 +1811,19 @@
     <t xml:space="preserve">32.707160949707</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9680156707764</t>
+    <t xml:space="preserve">31.9680118560791</t>
   </si>
   <si>
     <t xml:space="preserve">32.0604095458984</t>
   </si>
   <si>
-    <t xml:space="preserve">31.4136524200439</t>
+    <t xml:space="preserve">31.4136562347412</t>
   </si>
   <si>
     <t xml:space="preserve">31.6908378601074</t>
   </si>
   <si>
-    <t xml:space="preserve">32.2451972961426</t>
+    <t xml:space="preserve">32.2451934814453</t>
   </si>
   <si>
     <t xml:space="preserve">32.7995529174805</t>
@@ -1832,7 +1832,7 @@
     <t xml:space="preserve">33.9082717895508</t>
   </si>
   <si>
-    <t xml:space="preserve">35.1093788146973</t>
+    <t xml:space="preserve">35.1093826293945</t>
   </si>
   <si>
     <t xml:space="preserve">34.7398071289062</t>
@@ -1847,25 +1847,25 @@
     <t xml:space="preserve">32.4299812316895</t>
   </si>
   <si>
-    <t xml:space="preserve">32.5223731994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5060501098633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3212623596191</t>
+    <t xml:space="preserve">32.5223770141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5060482025146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3212661743164</t>
   </si>
   <si>
     <t xml:space="preserve">31.5522480010986</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9218158721924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1527938842773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.492504119873</t>
+    <t xml:space="preserve">31.9218196868896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1528015136719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.4925003051758</t>
   </si>
   <si>
     <t xml:space="preserve">34.3702392578125</t>
@@ -1877,7 +1877,7 @@
     <t xml:space="preserve">32.1066017150879</t>
   </si>
   <si>
-    <t xml:space="preserve">30.535924911499</t>
+    <t xml:space="preserve">30.5359210968018</t>
   </si>
   <si>
     <t xml:space="preserve">30.3511352539062</t>
@@ -1886,22 +1886,22 @@
     <t xml:space="preserve">28.7804527282715</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3643836975098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3180332183838</t>
+    <t xml:space="preserve">28.3643817901611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3180351257324</t>
   </si>
   <si>
     <t xml:space="preserve">27.8082180023193</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7618713378906</t>
+    <t xml:space="preserve">27.7618732452393</t>
   </si>
   <si>
     <t xml:space="preserve">28.0862998962402</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9936065673828</t>
+    <t xml:space="preserve">27.9936084747314</t>
   </si>
   <si>
     <t xml:space="preserve">28.6424655914307</t>
@@ -1913,7 +1913,7 @@
     <t xml:space="preserve">30.1255702972412</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5694046020508</t>
+    <t xml:space="preserve">29.5694065093994</t>
   </si>
   <si>
     <t xml:space="preserve">29.105936050415</t>
@@ -1925,52 +1925,52 @@
     <t xml:space="preserve">27.7155246734619</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1130142211914</t>
+    <t xml:space="preserve">27.1130123138428</t>
   </si>
   <si>
     <t xml:space="preserve">26.4641532897949</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4178066253662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1860733032227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6031932830811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2324180603027</t>
+    <t xml:space="preserve">26.4178085327148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.186071395874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6031951904297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2324199676514</t>
   </si>
   <si>
     <t xml:space="preserve">26.556848526001</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3251113891602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8152961730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6299076080322</t>
+    <t xml:space="preserve">26.3251132965088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8152980804443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6299095153809</t>
   </si>
   <si>
     <t xml:space="preserve">25.2591323852539</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7029666900635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6566219329834</t>
+    <t xml:space="preserve">24.7029685974121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6566181182861</t>
   </si>
   <si>
     <t xml:space="preserve">23.9614162445068</t>
   </si>
   <si>
-    <t xml:space="preserve">23.729679107666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0273971557617</t>
+    <t xml:space="preserve">23.7296772003174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0273952484131</t>
   </si>
   <si>
     <t xml:space="preserve">24.7956600189209</t>
@@ -1982,16 +1982,16 @@
     <t xml:space="preserve">24.6102714538574</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3321895599365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.517578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3785362243652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4712333679199</t>
+    <t xml:space="preserve">24.3321914672852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5175800323486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3785381317139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4712314605713</t>
   </si>
   <si>
     <t xml:space="preserve">23.8687210083008</t>
@@ -2000,7 +2000,7 @@
     <t xml:space="preserve">23.5442905426025</t>
   </si>
   <si>
-    <t xml:space="preserve">24.100456237793</t>
+    <t xml:space="preserve">24.1004543304443</t>
   </si>
   <si>
     <t xml:space="preserve">23.4979457855225</t>
@@ -2009,25 +2009,25 @@
     <t xml:space="preserve">23.8223743438721</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9150676727295</t>
+    <t xml:space="preserve">23.9150657653809</t>
   </si>
   <si>
     <t xml:space="preserve">24.193151473999</t>
   </si>
   <si>
-    <t xml:space="preserve">24.888355255127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5835609436035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9543380737305</t>
+    <t xml:space="preserve">24.8883571624756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5835590362549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9543361663818</t>
   </si>
   <si>
     <t xml:space="preserve">26.6958885192871</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7885818481445</t>
+    <t xml:space="preserve">26.7885837554932</t>
   </si>
   <si>
     <t xml:space="preserve">26.7422370910645</t>
@@ -2039,25 +2039,25 @@
     <t xml:space="preserve">24.981050491333</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8616409301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1200904846191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0077610015869</t>
+    <t xml:space="preserve">25.861644744873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1200923919678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0077629089355</t>
   </si>
   <si>
     <t xml:space="preserve">23.4515972137451</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1271686553955</t>
+    <t xml:space="preserve">23.1271705627441</t>
   </si>
   <si>
     <t xml:space="preserve">23.0808200836182</t>
   </si>
   <si>
-    <t xml:space="preserve">23.312557220459</t>
+    <t xml:space="preserve">23.3125553131104</t>
   </si>
   <si>
     <t xml:space="preserve">23.6369857788086</t>
@@ -2066,7 +2066,7 @@
     <t xml:space="preserve">23.5906391143799</t>
   </si>
   <si>
-    <t xml:space="preserve">23.405252456665</t>
+    <t xml:space="preserve">23.4052505493164</t>
   </si>
   <si>
     <t xml:space="preserve">23.2662105560303</t>
@@ -2075,34 +2075,34 @@
     <t xml:space="preserve">23.3589038848877</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8027381896973</t>
+    <t xml:space="preserve">22.8027362823486</t>
   </si>
   <si>
     <t xml:space="preserve">22.6173496246338</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1735153198242</t>
+    <t xml:space="preserve">23.1735134124756</t>
   </si>
   <si>
     <t xml:space="preserve">22.8954334259033</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9684944152832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5513706207275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.273286819458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8561630249023</t>
+    <t xml:space="preserve">21.9684925079346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5513687133789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2732887268066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.856164932251</t>
   </si>
   <si>
     <t xml:space="preserve">20.7171230316162</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9755706787109</t>
+    <t xml:space="preserve">19.9755687713623</t>
   </si>
   <si>
     <t xml:space="preserve">20.1609573364258</t>
@@ -2111,16 +2111,16 @@
     <t xml:space="preserve">20.2073059082031</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8365287780762</t>
+    <t xml:space="preserve">19.8365306854248</t>
   </si>
   <si>
     <t xml:space="preserve">19.5584468841553</t>
   </si>
   <si>
-    <t xml:space="preserve">19.604793548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9292221069336</t>
+    <t xml:space="preserve">19.6047916412354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9292240142822</t>
   </si>
   <si>
     <t xml:space="preserve">20.0682640075684</t>
@@ -2129,19 +2129,19 @@
     <t xml:space="preserve">20.1146106719971</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8098182678223</t>
+    <t xml:space="preserve">20.8098163604736</t>
   </si>
   <si>
     <t xml:space="preserve">20.9952049255371</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5780811309814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0878963470459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5977172851562</t>
+    <t xml:space="preserve">20.5780849456787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0878982543945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5977153778076</t>
   </si>
   <si>
     <t xml:space="preserve">22.061185836792</t>
@@ -2150,34 +2150,34 @@
     <t xml:space="preserve">22.4319629669189</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3856163024902</t>
+    <t xml:space="preserve">22.3856143951416</t>
   </si>
   <si>
     <t xml:space="preserve">22.3392696380615</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6833343505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5639247894287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4248867034912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1664390563965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2127876281738</t>
+    <t xml:space="preserve">23.6833324432373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5639266967773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4248847961426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1664352416992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2127857208252</t>
   </si>
   <si>
     <t xml:space="preserve">24.8420066833496</t>
   </si>
   <si>
-    <t xml:space="preserve">25.768949508667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7226028442383</t>
+    <t xml:space="preserve">25.7689476013184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7226009368896</t>
   </si>
   <si>
     <t xml:space="preserve">25.3518257141113</t>
@@ -2186,7 +2186,7 @@
     <t xml:space="preserve">25.5372123718262</t>
   </si>
   <si>
-    <t xml:space="preserve">25.305477142334</t>
+    <t xml:space="preserve">25.3054790496826</t>
   </si>
   <si>
     <t xml:space="preserve">25.6762561798096</t>
@@ -2204,7 +2204,7 @@
     <t xml:space="preserve">27.4837894439697</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2984027862549</t>
+    <t xml:space="preserve">27.2984008789062</t>
   </si>
   <si>
     <t xml:space="preserve">27.5764827728271</t>
@@ -2213,7 +2213,7 @@
     <t xml:space="preserve">28.0399532318115</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1789932250977</t>
+    <t xml:space="preserve">28.1789951324463</t>
   </si>
   <si>
     <t xml:space="preserve">28.2716884613037</t>
@@ -2222,25 +2222,25 @@
     <t xml:space="preserve">28.1326484680176</t>
   </si>
   <si>
-    <t xml:space="preserve">27.437442779541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5301380157471</t>
+    <t xml:space="preserve">27.4374408721924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5301361083984</t>
   </si>
   <si>
     <t xml:space="preserve">26.093376159668</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3981742858887</t>
+    <t xml:space="preserve">25.39817237854</t>
   </si>
   <si>
     <t xml:space="preserve">22.941780090332</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2002277374268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.153881072998</t>
+    <t xml:space="preserve">22.2002296447754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1538791656494</t>
   </si>
   <si>
     <t xml:space="preserve">22.1075344085693</t>
@@ -2261,55 +2261,55 @@
     <t xml:space="preserve">20.6244277954102</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6707763671875</t>
+    <t xml:space="preserve">20.6707744598389</t>
   </si>
   <si>
     <t xml:space="preserve">20.485387802124</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2536544799805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5317344665527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1342430114746</t>
+    <t xml:space="preserve">20.2536525726318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5317325592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1342468261719</t>
   </si>
   <si>
     <t xml:space="preserve">21.7831058502197</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6440620422363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2269401550293</t>
+    <t xml:space="preserve">21.644063949585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2269382476807</t>
   </si>
   <si>
     <t xml:space="preserve">21.3196353912354</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8757972717285</t>
+    <t xml:space="preserve">21.8757991790771</t>
   </si>
   <si>
     <t xml:space="preserve">21.1805934906006</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9025077819824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6679420471191</t>
+    <t xml:space="preserve">20.9025096893311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6679439544678</t>
   </si>
   <si>
     <t xml:space="preserve">21.3196334838867</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4127311706543</t>
+    <t xml:space="preserve">21.4127330780029</t>
   </si>
   <si>
     <t xml:space="preserve">20.6213912963867</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5748443603516</t>
+    <t xml:space="preserve">20.5748424530029</t>
   </si>
   <si>
     <t xml:space="preserve">20.3886451721191</t>
@@ -2318,22 +2318,22 @@
     <t xml:space="preserve">21.3661842346191</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9937877655029</t>
+    <t xml:space="preserve">20.9937858581543</t>
   </si>
   <si>
     <t xml:space="preserve">20.9006900787354</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0403366088867</t>
+    <t xml:space="preserve">21.0403385162354</t>
   </si>
   <si>
     <t xml:space="preserve">21.1799850463867</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2265338897705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9472389221191</t>
+    <t xml:space="preserve">21.2265357971191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9472370147705</t>
   </si>
   <si>
     <t xml:space="preserve">20.4817447662354</t>
@@ -2342,7 +2342,7 @@
     <t xml:space="preserve">20.3420963287354</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2489986419678</t>
+    <t xml:space="preserve">20.2489948272705</t>
   </si>
   <si>
     <t xml:space="preserve">20.1558990478516</t>
@@ -2381,16 +2381,16 @@
     <t xml:space="preserve">20.2024478912354</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4351959228516</t>
+    <t xml:space="preserve">20.4351940155029</t>
   </si>
   <si>
     <t xml:space="preserve">19.4576568603516</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0387134552002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9696998596191</t>
+    <t xml:space="preserve">19.0387115478516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9697017669678</t>
   </si>
   <si>
     <t xml:space="preserve">19.9231510162354</t>
@@ -2399,22 +2399,22 @@
     <t xml:space="preserve">19.3645572662354</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1783599853516</t>
+    <t xml:space="preserve">19.1783618927002</t>
   </si>
   <si>
     <t xml:space="preserve">18.8990631103516</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1318111419678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6197662353516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8525123596191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7128677368164</t>
+    <t xml:space="preserve">19.1318092346191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6197681427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8525142669678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7128658294678</t>
   </si>
   <si>
     <t xml:space="preserve">18.6663150787354</t>
@@ -2435,10 +2435,10 @@
     <t xml:space="preserve">18.3404712677002</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2287540435791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2101306915283</t>
+    <t xml:space="preserve">18.2287521362305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.210132598877</t>
   </si>
   <si>
     <t xml:space="preserve">17.968074798584</t>
@@ -2468,16 +2468,16 @@
     <t xml:space="preserve">16.7577896118164</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2232856750488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3350028991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.409481048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6515369415283</t>
+    <t xml:space="preserve">17.2232837677002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3350048065186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4094829559326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.651538848877</t>
   </si>
   <si>
     <t xml:space="preserve">17.7260189056396</t>
@@ -2492,7 +2492,7 @@
     <t xml:space="preserve">17.2605247497559</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2419033050537</t>
+    <t xml:space="preserve">17.2419052124023</t>
   </si>
   <si>
     <t xml:space="preserve">16.5715923309326</t>
@@ -2507,7 +2507,7 @@
     <t xml:space="preserve">16.9253673553467</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2736759185791</t>
+    <t xml:space="preserve">16.2736778259277</t>
   </si>
   <si>
     <t xml:space="preserve">16.0130004882812</t>
@@ -2519,13 +2519,13 @@
     <t xml:space="preserve">16.2364387512207</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2922973632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.037088394165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.813648223877</t>
+    <t xml:space="preserve">16.2922954559326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0370864868164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8136501312256</t>
   </si>
   <si>
     <t xml:space="preserve">16.404016494751</t>
@@ -2543,7 +2543,7 @@
     <t xml:space="preserve">16.3667755126953</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4598751068115</t>
+    <t xml:space="preserve">16.4598731994629</t>
   </si>
   <si>
     <t xml:space="preserve">15.7709436416626</t>
@@ -2552,16 +2552,16 @@
     <t xml:space="preserve">15.7337017059326</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8826608657837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.161958694458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1433391571045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5157337188721</t>
+    <t xml:space="preserve">15.882661819458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1619567871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1433372497559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5157318115234</t>
   </si>
   <si>
     <t xml:space="preserve">16.478494644165</t>
@@ -2570,10 +2570,10 @@
     <t xml:space="preserve">16.6460704803467</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8695106506348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1115665435791</t>
+    <t xml:space="preserve">16.8695087432861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1115646362305</t>
   </si>
   <si>
     <t xml:space="preserve">17.0184669494629</t>
@@ -2582,7 +2582,7 @@
     <t xml:space="preserve">17.0557060241699</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4839611053467</t>
+    <t xml:space="preserve">17.4839630126953</t>
   </si>
   <si>
     <t xml:space="preserve">17.3536224365234</t>
@@ -2591,7 +2591,7 @@
     <t xml:space="preserve">17.3722438812256</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9998474121094</t>
+    <t xml:space="preserve">16.999849319458</t>
   </si>
   <si>
     <t xml:space="preserve">17.0743255615234</t>
@@ -2603,10 +2603,10 @@
     <t xml:space="preserve">16.8881282806396</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6646919250488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7205505371094</t>
+    <t xml:space="preserve">16.6646900177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7205486297607</t>
   </si>
   <si>
     <t xml:space="preserve">16.8322696685791</t>
@@ -2615,13 +2615,13 @@
     <t xml:space="preserve">16.7391700744629</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5902118682861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3481559753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3109169006348</t>
+    <t xml:space="preserve">16.5902137756348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3481540679932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3109149932861</t>
   </si>
   <si>
     <t xml:space="preserve">16.199197769165</t>
@@ -2630,13 +2630,13 @@
     <t xml:space="preserve">16.6088333129883</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0502376556396</t>
+    <t xml:space="preserve">16.0502395629883</t>
   </si>
   <si>
     <t xml:space="preserve">16.2550563812256</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1060981750488</t>
+    <t xml:space="preserve">16.1060962677002</t>
   </si>
   <si>
     <t xml:space="preserve">17.1674251556396</t>
@@ -2648,10 +2648,10 @@
     <t xml:space="preserve">17.9122161865234</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4653434753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9494571685791</t>
+    <t xml:space="preserve">17.4653415679932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9494552612305</t>
   </si>
   <si>
     <t xml:space="preserve">17.8749771118164</t>
@@ -2663,16 +2663,16 @@
     <t xml:space="preserve">17.5491313934326</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3629341125488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5025787353516</t>
+    <t xml:space="preserve">17.3629322052002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5025806427002</t>
   </si>
   <si>
     <t xml:space="preserve">17.4560317993164</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1542739868164</t>
+    <t xml:space="preserve">18.1542720794678</t>
   </si>
   <si>
     <t xml:space="preserve">18.0611743927002</t>
@@ -2690,7 +2690,7 @@
     <t xml:space="preserve">18.6370983123779</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8282508850098</t>
+    <t xml:space="preserve">18.8282489776611</t>
   </si>
   <si>
     <t xml:space="preserve">19.1149749755859</t>
@@ -2699,7 +2699,7 @@
     <t xml:space="preserve">18.9716129302979</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2105503082275</t>
+    <t xml:space="preserve">19.2105484008789</t>
   </si>
   <si>
     <t xml:space="preserve">20.0707225799561</t>
@@ -2708,7 +2708,7 @@
     <t xml:space="preserve">20.8353214263916</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0264701843262</t>
+    <t xml:space="preserve">21.0264720916748</t>
   </si>
   <si>
     <t xml:space="preserve">20.9308967590332</t>
@@ -2732,7 +2732,7 @@
     <t xml:space="preserve">21.217622756958</t>
   </si>
   <si>
-    <t xml:space="preserve">20.73974609375</t>
+    <t xml:space="preserve">20.7397480010986</t>
   </si>
   <si>
     <t xml:space="preserve">21.1220455169678</t>
@@ -2741,7 +2741,7 @@
     <t xml:space="preserve">19.8795719146729</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7840003967285</t>
+    <t xml:space="preserve">19.7839984893799</t>
   </si>
   <si>
     <t xml:space="preserve">20.3574466705322</t>
@@ -2750,22 +2750,22 @@
     <t xml:space="preserve">19.9751472473145</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6884231567383</t>
+    <t xml:space="preserve">19.6884250640869</t>
   </si>
   <si>
     <t xml:space="preserve">21.3131942749023</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4087696075439</t>
+    <t xml:space="preserve">21.4087715148926</t>
   </si>
   <si>
     <t xml:space="preserve">21.5999221801758</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5043468475342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.886646270752</t>
+    <t xml:space="preserve">21.5043449401855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8866443634033</t>
   </si>
   <si>
     <t xml:space="preserve">22.5556697845459</t>
@@ -2774,10 +2774,10 @@
     <t xml:space="preserve">22.7468185424805</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9379692077637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8423919677734</t>
+    <t xml:space="preserve">22.937967300415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8423938751221</t>
   </si>
   <si>
     <t xml:space="preserve">23.1291179656982</t>
@@ -2789,7 +2789,7 @@
     <t xml:space="preserve">22.0777950286865</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9822196960449</t>
+    <t xml:space="preserve">21.9822216033936</t>
   </si>
   <si>
     <t xml:space="preserve">22.1733722686768</t>
@@ -2798,7 +2798,7 @@
     <t xml:space="preserve">21.6954956054688</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7910690307617</t>
+    <t xml:space="preserve">21.7910709381104</t>
   </si>
   <si>
     <t xml:space="preserve">22.6512451171875</t>
@@ -3000,6 +3000,9 @@
   </si>
   <si>
     <t xml:space="preserve">22.6000003814697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7000007629395</t>
   </si>
 </sst>
 </file>
@@ -19190,7 +19193,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G610" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -19242,7 +19245,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G612" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -19294,7 +19297,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G614" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -19320,7 +19323,7 @@
         <v>12.75</v>
       </c>
       <c r="G615" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -19346,7 +19349,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G616" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -19398,7 +19401,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G618" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -19424,7 +19427,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G619" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -19450,7 +19453,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G620" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -19476,7 +19479,7 @@
         <v>12.75</v>
       </c>
       <c r="G621" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -19502,7 +19505,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G622" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -19528,7 +19531,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G623" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -19554,7 +19557,7 @@
         <v>13</v>
       </c>
       <c r="G624" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -19580,7 +19583,7 @@
         <v>13</v>
       </c>
       <c r="G625" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -19606,7 +19609,7 @@
         <v>12.75</v>
       </c>
       <c r="G626" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -19632,7 +19635,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G627" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H627" t="s">
         <v>9</v>
@@ -19658,7 +19661,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G628" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H628" t="s">
         <v>9</v>
@@ -19684,7 +19687,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G629" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H629" t="s">
         <v>9</v>
@@ -19710,7 +19713,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G630" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H630" t="s">
         <v>9</v>
@@ -19736,7 +19739,7 @@
         <v>12.75</v>
       </c>
       <c r="G631" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H631" t="s">
         <v>9</v>
@@ -19762,7 +19765,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G632" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H632" t="s">
         <v>9</v>
@@ -19788,7 +19791,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G633" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H633" t="s">
         <v>9</v>
@@ -19814,7 +19817,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G634" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H634" t="s">
         <v>9</v>
@@ -19840,7 +19843,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G635" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H635" t="s">
         <v>9</v>
@@ -19866,7 +19869,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G636" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H636" t="s">
         <v>9</v>
@@ -19892,7 +19895,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G637" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H637" t="s">
         <v>9</v>
@@ -19918,7 +19921,7 @@
         <v>12.25</v>
       </c>
       <c r="G638" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H638" t="s">
         <v>9</v>
@@ -19944,7 +19947,7 @@
         <v>12.25</v>
       </c>
       <c r="G639" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H639" t="s">
         <v>9</v>
@@ -19970,7 +19973,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G640" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H640" t="s">
         <v>9</v>
@@ -19996,7 +19999,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G641" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H641" t="s">
         <v>9</v>
@@ -20022,7 +20025,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G642" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H642" t="s">
         <v>9</v>
@@ -20048,7 +20051,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G643" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H643" t="s">
         <v>9</v>
@@ -20074,7 +20077,7 @@
         <v>12.5</v>
       </c>
       <c r="G644" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H644" t="s">
         <v>9</v>
@@ -20100,7 +20103,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G645" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H645" t="s">
         <v>9</v>
@@ -20126,7 +20129,7 @@
         <v>12.5</v>
       </c>
       <c r="G646" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H646" t="s">
         <v>9</v>
@@ -20152,7 +20155,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G647" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H647" t="s">
         <v>9</v>
@@ -20178,7 +20181,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G648" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H648" t="s">
         <v>9</v>
@@ -20204,7 +20207,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G649" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H649" t="s">
         <v>9</v>
@@ -20230,7 +20233,7 @@
         <v>12.5</v>
       </c>
       <c r="G650" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H650" t="s">
         <v>9</v>
@@ -20256,7 +20259,7 @@
         <v>12.5</v>
       </c>
       <c r="G651" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H651" t="s">
         <v>9</v>
@@ -20282,7 +20285,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G652" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H652" t="s">
         <v>9</v>
@@ -20308,7 +20311,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G653" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H653" t="s">
         <v>9</v>
@@ -20334,7 +20337,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G654" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H654" t="s">
         <v>9</v>
@@ -20360,7 +20363,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G655" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H655" t="s">
         <v>9</v>
@@ -20386,7 +20389,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G656" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H656" t="s">
         <v>9</v>
@@ -20412,7 +20415,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G657" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H657" t="s">
         <v>9</v>
@@ -20438,7 +20441,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G658" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H658" t="s">
         <v>9</v>
@@ -20464,7 +20467,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G659" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H659" t="s">
         <v>9</v>
@@ -20490,7 +20493,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G660" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H660" t="s">
         <v>9</v>
@@ -20516,7 +20519,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G661" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H661" t="s">
         <v>9</v>
@@ -20542,7 +20545,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G662" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H662" t="s">
         <v>9</v>
@@ -20568,7 +20571,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G663" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H663" t="s">
         <v>9</v>
@@ -20594,7 +20597,7 @@
         <v>12.75</v>
       </c>
       <c r="G664" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -20620,7 +20623,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G665" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H665" t="s">
         <v>9</v>
@@ -20646,7 +20649,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G666" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H666" t="s">
         <v>9</v>
@@ -20672,7 +20675,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G667" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H667" t="s">
         <v>9</v>
@@ -20698,7 +20701,7 @@
         <v>12.25</v>
       </c>
       <c r="G668" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H668" t="s">
         <v>9</v>
@@ -20724,7 +20727,7 @@
         <v>12.25</v>
       </c>
       <c r="G669" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H669" t="s">
         <v>9</v>
@@ -20750,7 +20753,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G670" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H670" t="s">
         <v>9</v>
@@ -20776,7 +20779,7 @@
         <v>12.5</v>
       </c>
       <c r="G671" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H671" t="s">
         <v>9</v>
@@ -20802,7 +20805,7 @@
         <v>12.5</v>
       </c>
       <c r="G672" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H672" t="s">
         <v>9</v>
@@ -20828,7 +20831,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G673" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H673" t="s">
         <v>9</v>
@@ -20854,7 +20857,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G674" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H674" t="s">
         <v>9</v>
@@ -20880,7 +20883,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G675" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H675" t="s">
         <v>9</v>
@@ -20906,7 +20909,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G676" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H676" t="s">
         <v>9</v>
@@ -20932,7 +20935,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G677" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H677" t="s">
         <v>9</v>
@@ -20958,7 +20961,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G678" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H678" t="s">
         <v>9</v>
@@ -20984,7 +20987,7 @@
         <v>12.25</v>
       </c>
       <c r="G679" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H679" t="s">
         <v>9</v>
@@ -21010,7 +21013,7 @@
         <v>12.25</v>
       </c>
       <c r="G680" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H680" t="s">
         <v>9</v>
@@ -21036,7 +21039,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G681" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H681" t="s">
         <v>9</v>
@@ -21062,7 +21065,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G682" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H682" t="s">
         <v>9</v>
@@ -21088,7 +21091,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G683" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H683" t="s">
         <v>9</v>
@@ -21114,7 +21117,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G684" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H684" t="s">
         <v>9</v>
@@ -21140,7 +21143,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G685" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H685" t="s">
         <v>9</v>
@@ -21166,7 +21169,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G686" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H686" t="s">
         <v>9</v>
@@ -21192,7 +21195,7 @@
         <v>12.5</v>
       </c>
       <c r="G687" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H687" t="s">
         <v>9</v>
@@ -21218,7 +21221,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G688" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H688" t="s">
         <v>9</v>
@@ -21244,7 +21247,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G689" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H689" t="s">
         <v>9</v>
@@ -21270,7 +21273,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G690" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H690" t="s">
         <v>9</v>
@@ -21296,7 +21299,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G691" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H691" t="s">
         <v>9</v>
@@ -21322,7 +21325,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G692" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H692" t="s">
         <v>9</v>
@@ -21348,7 +21351,7 @@
         <v>12.75</v>
       </c>
       <c r="G693" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H693" t="s">
         <v>9</v>
@@ -21374,7 +21377,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G694" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -21400,7 +21403,7 @@
         <v>13.25</v>
       </c>
       <c r="G695" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H695" t="s">
         <v>9</v>
@@ -21426,7 +21429,7 @@
         <v>13</v>
       </c>
       <c r="G696" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H696" t="s">
         <v>9</v>
@@ -21452,7 +21455,7 @@
         <v>13</v>
       </c>
       <c r="G697" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H697" t="s">
         <v>9</v>
@@ -21478,7 +21481,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G698" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H698" t="s">
         <v>9</v>
@@ -21504,7 +21507,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G699" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H699" t="s">
         <v>9</v>
@@ -21530,7 +21533,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G700" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H700" t="s">
         <v>9</v>
@@ -21556,7 +21559,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G701" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H701" t="s">
         <v>9</v>
@@ -21582,7 +21585,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G702" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H702" t="s">
         <v>9</v>
@@ -21608,7 +21611,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G703" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H703" t="s">
         <v>9</v>
@@ -21634,7 +21637,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G704" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H704" t="s">
         <v>9</v>
@@ -21660,7 +21663,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G705" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H705" t="s">
         <v>9</v>
@@ -21686,7 +21689,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G706" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H706" t="s">
         <v>9</v>
@@ -21712,7 +21715,7 @@
         <v>13.25</v>
       </c>
       <c r="G707" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H707" t="s">
         <v>9</v>
@@ -21738,7 +21741,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G708" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H708" t="s">
         <v>9</v>
@@ -21764,7 +21767,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G709" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H709" t="s">
         <v>9</v>
@@ -21790,7 +21793,7 @@
         <v>13</v>
       </c>
       <c r="G710" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H710" t="s">
         <v>9</v>
@@ -21816,7 +21819,7 @@
         <v>13</v>
       </c>
       <c r="G711" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H711" t="s">
         <v>9</v>
@@ -21842,7 +21845,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G712" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H712" t="s">
         <v>9</v>
@@ -21868,7 +21871,7 @@
         <v>13</v>
       </c>
       <c r="G713" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H713" t="s">
         <v>9</v>
@@ -21894,7 +21897,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G714" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H714" t="s">
         <v>9</v>
@@ -21920,7 +21923,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G715" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H715" t="s">
         <v>9</v>
@@ -21946,7 +21949,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G716" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H716" t="s">
         <v>9</v>
@@ -21972,7 +21975,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G717" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H717" t="s">
         <v>9</v>
@@ -21998,7 +22001,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G718" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H718" t="s">
         <v>9</v>
@@ -22024,7 +22027,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G719" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H719" t="s">
         <v>9</v>
@@ -22050,7 +22053,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G720" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H720" t="s">
         <v>9</v>
@@ -22076,7 +22079,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G721" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H721" t="s">
         <v>9</v>
@@ -22102,7 +22105,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G722" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H722" t="s">
         <v>9</v>
@@ -22128,7 +22131,7 @@
         <v>12.5</v>
       </c>
       <c r="G723" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H723" t="s">
         <v>9</v>
@@ -22154,7 +22157,7 @@
         <v>13</v>
       </c>
       <c r="G724" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H724" t="s">
         <v>9</v>
@@ -22180,7 +22183,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G725" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H725" t="s">
         <v>9</v>
@@ -22206,7 +22209,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G726" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H726" t="s">
         <v>9</v>
@@ -22232,7 +22235,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G727" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H727" t="s">
         <v>9</v>
@@ -22258,7 +22261,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G728" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H728" t="s">
         <v>9</v>
@@ -22284,7 +22287,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G729" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H729" t="s">
         <v>9</v>
@@ -22310,7 +22313,7 @@
         <v>12.5</v>
       </c>
       <c r="G730" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H730" t="s">
         <v>9</v>
@@ -22336,7 +22339,7 @@
         <v>12.25</v>
       </c>
       <c r="G731" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H731" t="s">
         <v>9</v>
@@ -22362,7 +22365,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G732" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H732" t="s">
         <v>9</v>
@@ -22388,7 +22391,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G733" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H733" t="s">
         <v>9</v>
@@ -22414,7 +22417,7 @@
         <v>12</v>
       </c>
       <c r="G734" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H734" t="s">
         <v>9</v>
@@ -22440,7 +22443,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G735" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H735" t="s">
         <v>9</v>
@@ -22466,7 +22469,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G736" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H736" t="s">
         <v>9</v>
@@ -22492,7 +22495,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G737" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H737" t="s">
         <v>9</v>
@@ -22518,7 +22521,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G738" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H738" t="s">
         <v>9</v>
@@ -22544,7 +22547,7 @@
         <v>11.5</v>
       </c>
       <c r="G739" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H739" t="s">
         <v>9</v>
@@ -22570,7 +22573,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G740" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H740" t="s">
         <v>9</v>
@@ -22596,7 +22599,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G741" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H741" t="s">
         <v>9</v>
@@ -22622,7 +22625,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G742" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H742" t="s">
         <v>9</v>
@@ -22648,7 +22651,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G743" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H743" t="s">
         <v>9</v>
@@ -22674,7 +22677,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G744" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H744" t="s">
         <v>9</v>
@@ -22700,7 +22703,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G745" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H745" t="s">
         <v>9</v>
@@ -22726,7 +22729,7 @@
         <v>11.5</v>
       </c>
       <c r="G746" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H746" t="s">
         <v>9</v>
@@ -22752,7 +22755,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G747" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H747" t="s">
         <v>9</v>
@@ -22778,7 +22781,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G748" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H748" t="s">
         <v>9</v>
@@ -22804,7 +22807,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G749" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H749" t="s">
         <v>9</v>
@@ -22830,7 +22833,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G750" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H750" t="s">
         <v>9</v>
@@ -22856,7 +22859,7 @@
         <v>10.25</v>
       </c>
       <c r="G751" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H751" t="s">
         <v>9</v>
@@ -22882,7 +22885,7 @@
         <v>10.25</v>
       </c>
       <c r="G752" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H752" t="s">
         <v>9</v>
@@ -22908,7 +22911,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G753" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H753" t="s">
         <v>9</v>
@@ -22934,7 +22937,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G754" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H754" t="s">
         <v>9</v>
@@ -22960,7 +22963,7 @@
         <v>10.5</v>
       </c>
       <c r="G755" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H755" t="s">
         <v>9</v>
@@ -22986,7 +22989,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G756" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H756" t="s">
         <v>9</v>
@@ -23012,7 +23015,7 @@
         <v>10.5</v>
       </c>
       <c r="G757" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H757" t="s">
         <v>9</v>
@@ -23038,7 +23041,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G758" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H758" t="s">
         <v>9</v>
@@ -23064,7 +23067,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G759" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H759" t="s">
         <v>9</v>
@@ -23090,7 +23093,7 @@
         <v>10.75</v>
       </c>
       <c r="G760" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H760" t="s">
         <v>9</v>
@@ -23116,7 +23119,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G761" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H761" t="s">
         <v>9</v>
@@ -23142,7 +23145,7 @@
         <v>11.5</v>
       </c>
       <c r="G762" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H762" t="s">
         <v>9</v>
@@ -23168,7 +23171,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G763" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H763" t="s">
         <v>9</v>
@@ -23194,7 +23197,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G764" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H764" t="s">
         <v>9</v>
@@ -23220,7 +23223,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G765" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H765" t="s">
         <v>9</v>
@@ -23246,7 +23249,7 @@
         <v>11.5</v>
       </c>
       <c r="G766" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H766" t="s">
         <v>9</v>
@@ -23272,7 +23275,7 @@
         <v>11.5</v>
       </c>
       <c r="G767" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H767" t="s">
         <v>9</v>
@@ -23298,7 +23301,7 @@
         <v>11.75</v>
       </c>
       <c r="G768" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H768" t="s">
         <v>9</v>
@@ -23324,7 +23327,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G769" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H769" t="s">
         <v>9</v>
@@ -23350,7 +23353,7 @@
         <v>12</v>
       </c>
       <c r="G770" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H770" t="s">
         <v>9</v>
@@ -23376,7 +23379,7 @@
         <v>11.75</v>
       </c>
       <c r="G771" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H771" t="s">
         <v>9</v>
@@ -23402,7 +23405,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G772" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H772" t="s">
         <v>9</v>
@@ -23428,7 +23431,7 @@
         <v>11.5</v>
       </c>
       <c r="G773" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H773" t="s">
         <v>9</v>
@@ -23454,7 +23457,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G774" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H774" t="s">
         <v>9</v>
@@ -23480,7 +23483,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G775" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H775" t="s">
         <v>9</v>
@@ -23506,7 +23509,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G776" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H776" t="s">
         <v>9</v>
@@ -23532,7 +23535,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G777" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H777" t="s">
         <v>9</v>
@@ -23558,7 +23561,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G778" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H778" t="s">
         <v>9</v>
@@ -23584,7 +23587,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G779" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H779" t="s">
         <v>9</v>
@@ -23610,7 +23613,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G780" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H780" t="s">
         <v>9</v>
@@ -23636,7 +23639,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G781" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H781" t="s">
         <v>9</v>
@@ -23662,7 +23665,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G782" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H782" t="s">
         <v>9</v>
@@ -23688,7 +23691,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G783" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H783" t="s">
         <v>9</v>
@@ -23714,7 +23717,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G784" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H784" t="s">
         <v>9</v>
@@ -23740,7 +23743,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G785" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H785" t="s">
         <v>9</v>
@@ -23766,7 +23769,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G786" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H786" t="s">
         <v>9</v>
@@ -23792,7 +23795,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G787" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H787" t="s">
         <v>9</v>
@@ -23818,7 +23821,7 @@
         <v>11.5</v>
       </c>
       <c r="G788" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H788" t="s">
         <v>9</v>
@@ -23844,7 +23847,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G789" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H789" t="s">
         <v>9</v>
@@ -23870,7 +23873,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G790" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H790" t="s">
         <v>9</v>
@@ -23896,7 +23899,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G791" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H791" t="s">
         <v>9</v>
@@ -23922,7 +23925,7 @@
         <v>11.5</v>
       </c>
       <c r="G792" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H792" t="s">
         <v>9</v>
@@ -23948,7 +23951,7 @@
         <v>11.25</v>
       </c>
       <c r="G793" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H793" t="s">
         <v>9</v>
@@ -23974,7 +23977,7 @@
         <v>11.25</v>
       </c>
       <c r="G794" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H794" t="s">
         <v>9</v>
@@ -24000,7 +24003,7 @@
         <v>11.5</v>
       </c>
       <c r="G795" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H795" t="s">
         <v>9</v>
@@ -24026,7 +24029,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G796" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H796" t="s">
         <v>9</v>
@@ -24052,7 +24055,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G797" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H797" t="s">
         <v>9</v>
@@ -24078,7 +24081,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G798" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H798" t="s">
         <v>9</v>
@@ -24104,7 +24107,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G799" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H799" t="s">
         <v>9</v>
@@ -24130,7 +24133,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G800" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H800" t="s">
         <v>9</v>
@@ -24156,7 +24159,7 @@
         <v>11</v>
       </c>
       <c r="G801" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H801" t="s">
         <v>9</v>
@@ -24182,7 +24185,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G802" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H802" t="s">
         <v>9</v>
@@ -24208,7 +24211,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G803" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H803" t="s">
         <v>9</v>
@@ -24234,7 +24237,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G804" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H804" t="s">
         <v>9</v>
@@ -24260,7 +24263,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G805" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H805" t="s">
         <v>9</v>
@@ -24286,7 +24289,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G806" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H806" t="s">
         <v>9</v>
@@ -24312,7 +24315,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G807" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H807" t="s">
         <v>9</v>
@@ -24338,7 +24341,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G808" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H808" t="s">
         <v>9</v>
@@ -24364,7 +24367,7 @@
         <v>11</v>
       </c>
       <c r="G809" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H809" t="s">
         <v>9</v>
@@ -24390,7 +24393,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G810" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H810" t="s">
         <v>9</v>
@@ -24416,7 +24419,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G811" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H811" t="s">
         <v>9</v>
@@ -24442,7 +24445,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G812" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H812" t="s">
         <v>9</v>
@@ -24468,7 +24471,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G813" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H813" t="s">
         <v>9</v>
@@ -24494,7 +24497,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G814" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H814" t="s">
         <v>9</v>
@@ -24520,7 +24523,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G815" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H815" t="s">
         <v>9</v>
@@ -24546,7 +24549,7 @@
         <v>10.75</v>
       </c>
       <c r="G816" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H816" t="s">
         <v>9</v>
@@ -24572,7 +24575,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G817" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H817" t="s">
         <v>9</v>
@@ -24598,7 +24601,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G818" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H818" t="s">
         <v>9</v>
@@ -24624,7 +24627,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G819" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H819" t="s">
         <v>9</v>
@@ -24650,7 +24653,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G820" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H820" t="s">
         <v>9</v>
@@ -24676,7 +24679,7 @@
         <v>11.25</v>
       </c>
       <c r="G821" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H821" t="s">
         <v>9</v>
@@ -24702,7 +24705,7 @@
         <v>11.25</v>
       </c>
       <c r="G822" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H822" t="s">
         <v>9</v>
@@ -24728,7 +24731,7 @@
         <v>11.25</v>
       </c>
       <c r="G823" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H823" t="s">
         <v>9</v>
@@ -24754,7 +24757,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G824" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H824" t="s">
         <v>9</v>
@@ -24780,7 +24783,7 @@
         <v>11.5</v>
       </c>
       <c r="G825" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H825" t="s">
         <v>9</v>
@@ -24806,7 +24809,7 @@
         <v>11.5</v>
       </c>
       <c r="G826" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H826" t="s">
         <v>9</v>
@@ -24832,7 +24835,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G827" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H827" t="s">
         <v>9</v>
@@ -24858,7 +24861,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G828" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H828" t="s">
         <v>9</v>
@@ -24884,7 +24887,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G829" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H829" t="s">
         <v>9</v>
@@ -24910,7 +24913,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G830" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H830" t="s">
         <v>9</v>
@@ -24936,7 +24939,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G831" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H831" t="s">
         <v>9</v>
@@ -24962,7 +24965,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G832" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H832" t="s">
         <v>9</v>
@@ -24988,7 +24991,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G833" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H833" t="s">
         <v>9</v>
@@ -25014,7 +25017,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G834" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H834" t="s">
         <v>9</v>
@@ -25040,7 +25043,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G835" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H835" t="s">
         <v>9</v>
@@ -25066,7 +25069,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G836" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H836" t="s">
         <v>9</v>
@@ -25092,7 +25095,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G837" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H837" t="s">
         <v>9</v>
@@ -25118,7 +25121,7 @@
         <v>11.5</v>
       </c>
       <c r="G838" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H838" t="s">
         <v>9</v>
@@ -25144,7 +25147,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G839" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H839" t="s">
         <v>9</v>
@@ -25170,7 +25173,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G840" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H840" t="s">
         <v>9</v>
@@ -25196,7 +25199,7 @@
         <v>11.5</v>
       </c>
       <c r="G841" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H841" t="s">
         <v>9</v>
@@ -25222,7 +25225,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G842" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H842" t="s">
         <v>9</v>
@@ -25248,7 +25251,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G843" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H843" t="s">
         <v>9</v>
@@ -25274,7 +25277,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G844" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H844" t="s">
         <v>9</v>
@@ -25300,7 +25303,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G845" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H845" t="s">
         <v>9</v>
@@ -25326,7 +25329,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G846" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H846" t="s">
         <v>9</v>
@@ -25352,7 +25355,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G847" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -25378,7 +25381,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G848" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H848" t="s">
         <v>9</v>
@@ -25404,7 +25407,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G849" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H849" t="s">
         <v>9</v>
@@ -25430,7 +25433,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G850" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H850" t="s">
         <v>9</v>
@@ -25456,7 +25459,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G851" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -25482,7 +25485,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G852" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H852" t="s">
         <v>9</v>
@@ -25508,7 +25511,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G853" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -25534,7 +25537,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G854" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H854" t="s">
         <v>9</v>
@@ -25560,7 +25563,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G855" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -25586,7 +25589,7 @@
         <v>11.5</v>
       </c>
       <c r="G856" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -25612,7 +25615,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G857" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H857" t="s">
         <v>9</v>
@@ -25638,7 +25641,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G858" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -25664,7 +25667,7 @@
         <v>11.5</v>
       </c>
       <c r="G859" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H859" t="s">
         <v>9</v>
@@ -25690,7 +25693,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G860" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H860" t="s">
         <v>9</v>
@@ -25716,7 +25719,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G861" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -25742,7 +25745,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G862" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H862" t="s">
         <v>9</v>
@@ -25768,7 +25771,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G863" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H863" t="s">
         <v>9</v>
@@ -25794,7 +25797,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G864" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H864" t="s">
         <v>9</v>
@@ -25820,7 +25823,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G865" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H865" t="s">
         <v>9</v>
@@ -25846,7 +25849,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G866" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H866" t="s">
         <v>9</v>
@@ -25872,7 +25875,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G867" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H867" t="s">
         <v>9</v>
@@ -25898,7 +25901,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G868" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H868" t="s">
         <v>9</v>
@@ -25924,7 +25927,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G869" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H869" t="s">
         <v>9</v>
@@ -25950,7 +25953,7 @@
         <v>12</v>
       </c>
       <c r="G870" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H870" t="s">
         <v>9</v>
@@ -25976,7 +25979,7 @@
         <v>12</v>
       </c>
       <c r="G871" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H871" t="s">
         <v>9</v>
@@ -26002,7 +26005,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G872" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H872" t="s">
         <v>9</v>
@@ -26028,7 +26031,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G873" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H873" t="s">
         <v>9</v>
@@ -26054,7 +26057,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G874" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H874" t="s">
         <v>9</v>
@@ -26080,7 +26083,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G875" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H875" t="s">
         <v>9</v>
@@ -26106,7 +26109,7 @@
         <v>12</v>
       </c>
       <c r="G876" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H876" t="s">
         <v>9</v>
@@ -26132,7 +26135,7 @@
         <v>12</v>
       </c>
       <c r="G877" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H877" t="s">
         <v>9</v>
@@ -26158,7 +26161,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G878" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H878" t="s">
         <v>9</v>
@@ -26184,7 +26187,7 @@
         <v>12</v>
       </c>
       <c r="G879" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H879" t="s">
         <v>9</v>
@@ -26210,7 +26213,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G880" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H880" t="s">
         <v>9</v>
@@ -26236,7 +26239,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G881" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H881" t="s">
         <v>9</v>
@@ -26262,7 +26265,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G882" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H882" t="s">
         <v>9</v>
@@ -26288,7 +26291,7 @@
         <v>12</v>
       </c>
       <c r="G883" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H883" t="s">
         <v>9</v>
@@ -26314,7 +26317,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G884" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H884" t="s">
         <v>9</v>
@@ -26340,7 +26343,7 @@
         <v>12.25</v>
       </c>
       <c r="G885" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H885" t="s">
         <v>9</v>
@@ -26366,7 +26369,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G886" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H886" t="s">
         <v>9</v>
@@ -26392,7 +26395,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G887" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H887" t="s">
         <v>9</v>
@@ -26418,7 +26421,7 @@
         <v>12.25</v>
       </c>
       <c r="G888" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H888" t="s">
         <v>9</v>
@@ -26444,7 +26447,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G889" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H889" t="s">
         <v>9</v>
@@ -26470,7 +26473,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G890" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H890" t="s">
         <v>9</v>
@@ -26496,7 +26499,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G891" t="s">
-        <v>252</v>
+        <v>327</v>
       </c>
       <c r="H891" t="s">
         <v>9</v>
@@ -26600,7 +26603,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G895" t="s">
-        <v>252</v>
+        <v>327</v>
       </c>
       <c r="H895" t="s">
         <v>9</v>
@@ -26756,7 +26759,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G901" t="s">
-        <v>252</v>
+        <v>327</v>
       </c>
       <c r="H901" t="s">
         <v>9</v>
@@ -26860,7 +26863,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G905" t="s">
-        <v>252</v>
+        <v>327</v>
       </c>
       <c r="H905" t="s">
         <v>9</v>
@@ -26886,7 +26889,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G906" t="s">
-        <v>252</v>
+        <v>327</v>
       </c>
       <c r="H906" t="s">
         <v>9</v>
@@ -26990,7 +26993,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G910" t="s">
-        <v>252</v>
+        <v>327</v>
       </c>
       <c r="H910" t="s">
         <v>9</v>
@@ -27068,7 +27071,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G913" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H913" t="s">
         <v>9</v>
@@ -27198,7 +27201,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G918" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H918" t="s">
         <v>9</v>
@@ -27224,7 +27227,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G919" t="s">
-        <v>252</v>
+        <v>327</v>
       </c>
       <c r="H919" t="s">
         <v>9</v>
@@ -27302,7 +27305,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G922" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H922" t="s">
         <v>9</v>
@@ -27328,7 +27331,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G923" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H923" t="s">
         <v>9</v>
@@ -27510,7 +27513,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G930" t="s">
-        <v>252</v>
+        <v>327</v>
       </c>
       <c r="H930" t="s">
         <v>9</v>
@@ -28056,7 +28059,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G951" t="s">
-        <v>252</v>
+        <v>327</v>
       </c>
       <c r="H951" t="s">
         <v>9</v>
@@ -28108,7 +28111,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G953" t="s">
-        <v>252</v>
+        <v>327</v>
       </c>
       <c r="H953" t="s">
         <v>9</v>
@@ -28186,7 +28189,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G956" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H956" t="s">
         <v>9</v>
@@ -28212,7 +28215,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G957" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H957" t="s">
         <v>9</v>
@@ -28238,7 +28241,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G958" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H958" t="s">
         <v>9</v>
@@ -28264,7 +28267,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G959" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H959" t="s">
         <v>9</v>
@@ -28290,7 +28293,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G960" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H960" t="s">
         <v>9</v>
@@ -28342,7 +28345,7 @@
         <v>11.5</v>
       </c>
       <c r="G962" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H962" t="s">
         <v>9</v>
@@ -28368,7 +28371,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G963" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H963" t="s">
         <v>9</v>
@@ -28394,7 +28397,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G964" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H964" t="s">
         <v>9</v>
@@ -28420,7 +28423,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G965" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H965" t="s">
         <v>9</v>
@@ -28446,7 +28449,7 @@
         <v>12.25</v>
       </c>
       <c r="G966" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H966" t="s">
         <v>9</v>
@@ -28472,7 +28475,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G967" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H967" t="s">
         <v>9</v>
@@ -28498,7 +28501,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G968" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H968" t="s">
         <v>9</v>
@@ -28550,7 +28553,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G970" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H970" t="s">
         <v>9</v>
@@ -28602,7 +28605,7 @@
         <v>12.25</v>
       </c>
       <c r="G972" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H972" t="s">
         <v>9</v>
@@ -28628,7 +28631,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G973" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H973" t="s">
         <v>9</v>
@@ -28654,7 +28657,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G974" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H974" t="s">
         <v>9</v>
@@ -28680,7 +28683,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G975" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H975" t="s">
         <v>9</v>
@@ -28758,7 +28761,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G978" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H978" t="s">
         <v>9</v>
@@ -28810,7 +28813,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G980" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H980" t="s">
         <v>9</v>
@@ -28888,7 +28891,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G983" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H983" t="s">
         <v>9</v>
@@ -28940,7 +28943,7 @@
         <v>12.25</v>
       </c>
       <c r="G985" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H985" t="s">
         <v>9</v>
@@ -28966,7 +28969,7 @@
         <v>12.25</v>
       </c>
       <c r="G986" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H986" t="s">
         <v>9</v>
@@ -28992,7 +28995,7 @@
         <v>12.25</v>
       </c>
       <c r="G987" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H987" t="s">
         <v>9</v>
@@ -29018,7 +29021,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G988" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H988" t="s">
         <v>9</v>
@@ -29044,7 +29047,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G989" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H989" t="s">
         <v>9</v>
@@ -29070,7 +29073,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G990" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H990" t="s">
         <v>9</v>
@@ -29096,7 +29099,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G991" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H991" t="s">
         <v>9</v>
@@ -29148,7 +29151,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G993" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H993" t="s">
         <v>9</v>
@@ -29174,7 +29177,7 @@
         <v>12</v>
       </c>
       <c r="G994" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H994" t="s">
         <v>9</v>
@@ -29200,7 +29203,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G995" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H995" t="s">
         <v>9</v>
@@ -29226,7 +29229,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G996" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H996" t="s">
         <v>9</v>
@@ -29252,7 +29255,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G997" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H997" t="s">
         <v>9</v>
@@ -29278,7 +29281,7 @@
         <v>12.25</v>
       </c>
       <c r="G998" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H998" t="s">
         <v>9</v>
@@ -29356,7 +29359,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G1001" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H1001" t="s">
         <v>9</v>
@@ -29382,7 +29385,7 @@
         <v>12</v>
       </c>
       <c r="G1002" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H1002" t="s">
         <v>9</v>
@@ -29434,7 +29437,7 @@
         <v>12.25</v>
       </c>
       <c r="G1004" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H1004" t="s">
         <v>9</v>
@@ -29460,7 +29463,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G1005" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H1005" t="s">
         <v>9</v>
@@ -29486,7 +29489,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G1006" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H1006" t="s">
         <v>9</v>
@@ -29512,7 +29515,7 @@
         <v>12.25</v>
       </c>
       <c r="G1007" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H1007" t="s">
         <v>9</v>
@@ -29564,7 +29567,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G1009" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H1009" t="s">
         <v>9</v>
@@ -29616,7 +29619,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G1011" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H1011" t="s">
         <v>9</v>
@@ -29798,7 +29801,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1018" t="s">
-        <v>252</v>
+        <v>327</v>
       </c>
       <c r="H1018" t="s">
         <v>9</v>
@@ -31020,7 +31023,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1065" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H1065" t="s">
         <v>9</v>
@@ -31046,7 +31049,7 @@
         <v>12</v>
       </c>
       <c r="G1066" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H1066" t="s">
         <v>9</v>
@@ -31072,7 +31075,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1067" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H1067" t="s">
         <v>9</v>
@@ -31098,7 +31101,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G1068" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H1068" t="s">
         <v>9</v>
@@ -31176,7 +31179,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1071" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H1071" t="s">
         <v>9</v>
@@ -31202,7 +31205,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1072" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H1072" t="s">
         <v>9</v>
@@ -31306,7 +31309,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G1076" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H1076" t="s">
         <v>9</v>
@@ -31332,7 +31335,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1077" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H1077" t="s">
         <v>9</v>
@@ -31358,7 +31361,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1078" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H1078" t="s">
         <v>9</v>
@@ -31384,7 +31387,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G1079" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H1079" t="s">
         <v>9</v>
@@ -31462,7 +31465,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G1082" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H1082" t="s">
         <v>9</v>
@@ -31514,7 +31517,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G1084" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H1084" t="s">
         <v>9</v>
@@ -31592,7 +31595,7 @@
         <v>12</v>
       </c>
       <c r="G1087" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H1087" t="s">
         <v>9</v>
@@ -31618,7 +31621,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1088" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H1088" t="s">
         <v>9</v>
@@ -31644,7 +31647,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1089" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H1089" t="s">
         <v>9</v>
@@ -31670,7 +31673,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1090" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H1090" t="s">
         <v>9</v>
@@ -31696,7 +31699,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G1091" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H1091" t="s">
         <v>9</v>
@@ -31722,7 +31725,7 @@
         <v>12</v>
       </c>
       <c r="G1092" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H1092" t="s">
         <v>9</v>
@@ -31800,7 +31803,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1095" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H1095" t="s">
         <v>9</v>
@@ -33022,7 +33025,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1142" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="H1142" t="s">
         <v>9</v>
@@ -33048,7 +33051,7 @@
         <v>14.75</v>
       </c>
       <c r="G1143" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H1143" t="s">
         <v>9</v>
@@ -33074,7 +33077,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1144" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H1144" t="s">
         <v>9</v>
@@ -33100,7 +33103,7 @@
         <v>14.5</v>
       </c>
       <c r="G1145" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H1145" t="s">
         <v>9</v>
@@ -33126,7 +33129,7 @@
         <v>14.5</v>
       </c>
       <c r="G1146" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H1146" t="s">
         <v>9</v>
@@ -33152,7 +33155,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1147" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1147" t="s">
         <v>9</v>
@@ -33178,7 +33181,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1148" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1148" t="s">
         <v>9</v>
@@ -33204,7 +33207,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G1149" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H1149" t="s">
         <v>9</v>
@@ -33230,7 +33233,7 @@
         <v>14</v>
       </c>
       <c r="G1150" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H1150" t="s">
         <v>9</v>
@@ -33256,7 +33259,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1151" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1151" t="s">
         <v>9</v>
@@ -33282,7 +33285,7 @@
         <v>14.5</v>
       </c>
       <c r="G1152" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H1152" t="s">
         <v>9</v>
@@ -33308,7 +33311,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1153" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H1153" t="s">
         <v>9</v>
@@ -33334,7 +33337,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G1154" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H1154" t="s">
         <v>9</v>
@@ -33360,7 +33363,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G1155" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H1155" t="s">
         <v>9</v>
@@ -33386,7 +33389,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G1156" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H1156" t="s">
         <v>9</v>
@@ -33412,7 +33415,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1157" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H1157" t="s">
         <v>9</v>
@@ -33464,7 +33467,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1159" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H1159" t="s">
         <v>9</v>
@@ -33490,7 +33493,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1160" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H1160" t="s">
         <v>9</v>
@@ -33516,7 +33519,7 @@
         <v>14.5</v>
       </c>
       <c r="G1161" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H1161" t="s">
         <v>9</v>
@@ -33542,7 +33545,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G1162" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H1162" t="s">
         <v>9</v>
@@ -33568,7 +33571,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G1163" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H1163" t="s">
         <v>9</v>
@@ -33594,7 +33597,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1164" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1164" t="s">
         <v>9</v>
@@ -33620,7 +33623,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1165" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1165" t="s">
         <v>9</v>
@@ -33646,7 +33649,7 @@
         <v>14.25</v>
       </c>
       <c r="G1166" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H1166" t="s">
         <v>9</v>
@@ -33672,7 +33675,7 @@
         <v>14.5</v>
       </c>
       <c r="G1167" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H1167" t="s">
         <v>9</v>
@@ -33698,7 +33701,7 @@
         <v>14.5</v>
       </c>
       <c r="G1168" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H1168" t="s">
         <v>9</v>
@@ -33750,7 +33753,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1170" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H1170" t="s">
         <v>9</v>
@@ -33802,7 +33805,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1172" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H1172" t="s">
         <v>9</v>
@@ -33854,7 +33857,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1174" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H1174" t="s">
         <v>9</v>
@@ -33880,7 +33883,7 @@
         <v>15.75</v>
       </c>
       <c r="G1175" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H1175" t="s">
         <v>9</v>
@@ -33906,7 +33909,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1176" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H1176" t="s">
         <v>9</v>
@@ -33932,7 +33935,7 @@
         <v>16</v>
       </c>
       <c r="G1177" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H1177" t="s">
         <v>9</v>
@@ -33958,7 +33961,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1178" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H1178" t="s">
         <v>9</v>
@@ -33984,7 +33987,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G1179" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H1179" t="s">
         <v>9</v>
@@ -34010,7 +34013,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1180" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H1180" t="s">
         <v>9</v>
@@ -34036,7 +34039,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1181" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H1181" t="s">
         <v>9</v>
@@ -34062,7 +34065,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1182" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H1182" t="s">
         <v>9</v>
@@ -34088,7 +34091,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1183" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H1183" t="s">
         <v>9</v>
@@ -34114,7 +34117,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1184" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H1184" t="s">
         <v>9</v>
@@ -34140,7 +34143,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1185" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H1185" t="s">
         <v>9</v>
@@ -34166,7 +34169,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1186" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H1186" t="s">
         <v>9</v>
@@ -34192,7 +34195,7 @@
         <v>16.5</v>
       </c>
       <c r="G1187" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H1187" t="s">
         <v>9</v>
@@ -34218,7 +34221,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1188" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H1188" t="s">
         <v>9</v>
@@ -34244,7 +34247,7 @@
         <v>16.5</v>
       </c>
       <c r="G1189" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H1189" t="s">
         <v>9</v>
@@ -34270,7 +34273,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1190" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H1190" t="s">
         <v>9</v>
@@ -34296,7 +34299,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G1191" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H1191" t="s">
         <v>9</v>
@@ -34322,7 +34325,7 @@
         <v>17</v>
       </c>
       <c r="G1192" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H1192" t="s">
         <v>9</v>
@@ -34348,7 +34351,7 @@
         <v>17</v>
       </c>
       <c r="G1193" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H1193" t="s">
         <v>9</v>
@@ -34374,7 +34377,7 @@
         <v>17</v>
       </c>
       <c r="G1194" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H1194" t="s">
         <v>9</v>
@@ -34400,7 +34403,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1195" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H1195" t="s">
         <v>9</v>
@@ -34426,7 +34429,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G1196" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H1196" t="s">
         <v>9</v>
@@ -34452,7 +34455,7 @@
         <v>18</v>
       </c>
       <c r="G1197" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H1197" t="s">
         <v>9</v>
@@ -34478,7 +34481,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1198" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H1198" t="s">
         <v>9</v>
@@ -34504,7 +34507,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1199" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H1199" t="s">
         <v>9</v>
@@ -34530,7 +34533,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1200" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H1200" t="s">
         <v>9</v>
@@ -34556,7 +34559,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G1201" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H1201" t="s">
         <v>9</v>
@@ -34582,7 +34585,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G1202" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H1202" t="s">
         <v>9</v>
@@ -34608,7 +34611,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1203" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H1203" t="s">
         <v>9</v>
@@ -34634,7 +34637,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G1204" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H1204" t="s">
         <v>9</v>
@@ -34660,7 +34663,7 @@
         <v>20</v>
       </c>
       <c r="G1205" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H1205" t="s">
         <v>9</v>
@@ -34686,7 +34689,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G1206" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H1206" t="s">
         <v>9</v>
@@ -34712,7 +34715,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G1207" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H1207" t="s">
         <v>9</v>
@@ -34738,7 +34741,7 @@
         <v>19.25</v>
       </c>
       <c r="G1208" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H1208" t="s">
         <v>9</v>
@@ -34764,7 +34767,7 @@
         <v>19.3500003814697</v>
       </c>
       <c r="G1209" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H1209" t="s">
         <v>9</v>
@@ -34790,7 +34793,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1210" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H1210" t="s">
         <v>9</v>
@@ -34816,7 +34819,7 @@
         <v>19.3500003814697</v>
       </c>
       <c r="G1211" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H1211" t="s">
         <v>9</v>
@@ -34842,7 +34845,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1212" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H1212" t="s">
         <v>9</v>
@@ -34868,7 +34871,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1213" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H1213" t="s">
         <v>9</v>
@@ -34894,7 +34897,7 @@
         <v>18.4500007629395</v>
       </c>
       <c r="G1214" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H1214" t="s">
         <v>9</v>
@@ -34920,7 +34923,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G1215" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H1215" t="s">
         <v>9</v>
@@ -34946,7 +34949,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1216" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H1216" t="s">
         <v>9</v>
@@ -34972,7 +34975,7 @@
         <v>18.5</v>
       </c>
       <c r="G1217" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H1217" t="s">
         <v>9</v>
@@ -34998,7 +35001,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1218" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H1218" t="s">
         <v>9</v>
@@ -35024,7 +35027,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1219" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H1219" t="s">
         <v>9</v>
@@ -35050,7 +35053,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1220" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H1220" t="s">
         <v>9</v>
@@ -35076,7 +35079,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1221" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H1221" t="s">
         <v>9</v>
@@ -35102,7 +35105,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1222" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H1222" t="s">
         <v>9</v>
@@ -35128,7 +35131,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1223" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H1223" t="s">
         <v>9</v>
@@ -35154,7 +35157,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1224" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H1224" t="s">
         <v>9</v>
@@ -35180,7 +35183,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1225" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H1225" t="s">
         <v>9</v>
@@ -35206,7 +35209,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1226" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H1226" t="s">
         <v>9</v>
@@ -35232,7 +35235,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1227" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H1227" t="s">
         <v>9</v>
@@ -35258,7 +35261,7 @@
         <v>17.75</v>
       </c>
       <c r="G1228" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H1228" t="s">
         <v>9</v>
@@ -35284,7 +35287,7 @@
         <v>18</v>
       </c>
       <c r="G1229" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H1229" t="s">
         <v>9</v>
@@ -35310,7 +35313,7 @@
         <v>18.5</v>
       </c>
       <c r="G1230" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H1230" t="s">
         <v>9</v>
@@ -35336,7 +35339,7 @@
         <v>18.4500007629395</v>
       </c>
       <c r="G1231" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H1231" t="s">
         <v>9</v>
@@ -35362,7 +35365,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1232" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H1232" t="s">
         <v>9</v>
@@ -35388,7 +35391,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G1233" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H1233" t="s">
         <v>9</v>
@@ -35414,7 +35417,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1234" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H1234" t="s">
         <v>9</v>
@@ -35440,7 +35443,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1235" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H1235" t="s">
         <v>9</v>
@@ -35466,7 +35469,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1236" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H1236" t="s">
         <v>9</v>
@@ -35492,7 +35495,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G1237" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H1237" t="s">
         <v>9</v>
@@ -35518,7 +35521,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G1238" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H1238" t="s">
         <v>9</v>
@@ -35544,7 +35547,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G1239" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H1239" t="s">
         <v>9</v>
@@ -35570,7 +35573,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1240" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H1240" t="s">
         <v>9</v>
@@ -35596,7 +35599,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1241" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H1241" t="s">
         <v>9</v>
@@ -35622,7 +35625,7 @@
         <v>18.5</v>
       </c>
       <c r="G1242" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H1242" t="s">
         <v>9</v>
@@ -35648,7 +35651,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1243" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H1243" t="s">
         <v>9</v>
@@ -35674,7 +35677,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G1244" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H1244" t="s">
         <v>9</v>
@@ -35700,7 +35703,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G1245" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H1245" t="s">
         <v>9</v>
@@ -35726,7 +35729,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1246" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H1246" t="s">
         <v>9</v>
@@ -35752,7 +35755,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1247" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H1247" t="s">
         <v>9</v>
@@ -35778,7 +35781,7 @@
         <v>17.75</v>
       </c>
       <c r="G1248" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H1248" t="s">
         <v>9</v>
@@ -35804,7 +35807,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1249" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H1249" t="s">
         <v>9</v>
@@ -35830,7 +35833,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1250" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H1250" t="s">
         <v>9</v>
@@ -35856,7 +35859,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1251" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H1251" t="s">
         <v>9</v>
@@ -35882,7 +35885,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G1252" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H1252" t="s">
         <v>9</v>
@@ -35908,7 +35911,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1253" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H1253" t="s">
         <v>9</v>
@@ -35934,7 +35937,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1254" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H1254" t="s">
         <v>9</v>
@@ -35960,7 +35963,7 @@
         <v>18.0499992370605</v>
       </c>
       <c r="G1255" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H1255" t="s">
         <v>9</v>
@@ -35986,7 +35989,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1256" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H1256" t="s">
         <v>9</v>
@@ -36012,7 +36015,7 @@
         <v>18</v>
       </c>
       <c r="G1257" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H1257" t="s">
         <v>9</v>
@@ -36038,7 +36041,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G1258" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H1258" t="s">
         <v>9</v>
@@ -36064,7 +36067,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G1259" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H1259" t="s">
         <v>9</v>
@@ -36090,7 +36093,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1260" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H1260" t="s">
         <v>9</v>
@@ -36116,7 +36119,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1261" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H1261" t="s">
         <v>9</v>
@@ -36142,7 +36145,7 @@
         <v>19</v>
       </c>
       <c r="G1262" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H1262" t="s">
         <v>9</v>
@@ -36168,7 +36171,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1263" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H1263" t="s">
         <v>9</v>
@@ -36194,7 +36197,7 @@
         <v>19.5</v>
       </c>
       <c r="G1264" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H1264" t="s">
         <v>9</v>
@@ -36220,7 +36223,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G1265" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H1265" t="s">
         <v>9</v>
@@ -36246,7 +36249,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G1266" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H1266" t="s">
         <v>9</v>
@@ -36272,7 +36275,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G1267" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H1267" t="s">
         <v>9</v>
@@ -36298,7 +36301,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G1268" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H1268" t="s">
         <v>9</v>
@@ -36324,7 +36327,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1269" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H1269" t="s">
         <v>9</v>
@@ -36350,7 +36353,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1270" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H1270" t="s">
         <v>9</v>
@@ -36376,7 +36379,7 @@
         <v>21.5</v>
       </c>
       <c r="G1271" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H1271" t="s">
         <v>9</v>
@@ -36402,7 +36405,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1272" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H1272" t="s">
         <v>9</v>
@@ -36428,7 +36431,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G1273" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H1273" t="s">
         <v>9</v>
@@ -36454,7 +36457,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1274" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H1274" t="s">
         <v>9</v>
@@ -36480,7 +36483,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G1275" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H1275" t="s">
         <v>9</v>
@@ -36506,7 +36509,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G1276" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H1276" t="s">
         <v>9</v>
@@ -36532,7 +36535,7 @@
         <v>22.5</v>
       </c>
       <c r="G1277" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H1277" t="s">
         <v>9</v>
@@ -36558,7 +36561,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G1278" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H1278" t="s">
         <v>9</v>
@@ -36584,7 +36587,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G1279" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H1279" t="s">
         <v>9</v>
@@ -36610,7 +36613,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G1280" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H1280" t="s">
         <v>9</v>
@@ -36636,7 +36639,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G1281" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H1281" t="s">
         <v>9</v>
@@ -36662,7 +36665,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1282" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H1282" t="s">
         <v>9</v>
@@ -36688,7 +36691,7 @@
         <v>23</v>
       </c>
       <c r="G1283" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H1283" t="s">
         <v>9</v>
@@ -36714,7 +36717,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G1284" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H1284" t="s">
         <v>9</v>
@@ -36740,7 +36743,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G1285" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H1285" t="s">
         <v>9</v>
@@ -36766,7 +36769,7 @@
         <v>23.5</v>
       </c>
       <c r="G1286" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H1286" t="s">
         <v>9</v>
@@ -36792,7 +36795,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G1287" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H1287" t="s">
         <v>9</v>
@@ -36844,7 +36847,7 @@
         <v>23.5</v>
       </c>
       <c r="G1289" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H1289" t="s">
         <v>9</v>
@@ -68624,7 +68627,7 @@
     </row>
     <row r="2512">
       <c r="A2512" s="1" t="n">
-        <v>45975.6911921296</v>
+        <v>45975.3333333333</v>
       </c>
       <c r="B2512" t="n">
         <v>1231</v>
@@ -68645,6 +68648,32 @@
         <v>980</v>
       </c>
       <c r="H2512" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2513">
+      <c r="A2513" s="1" t="n">
+        <v>45978.6911689815</v>
+      </c>
+      <c r="B2513" t="n">
+        <v>5027</v>
+      </c>
+      <c r="C2513" t="n">
+        <v>22.1000003814697</v>
+      </c>
+      <c r="D2513" t="n">
+        <v>21.7000007629395</v>
+      </c>
+      <c r="E2513" t="n">
+        <v>22</v>
+      </c>
+      <c r="F2513" t="n">
+        <v>21.7000007629395</v>
+      </c>
+      <c r="G2513" t="s">
+        <v>996</v>
+      </c>
+      <c r="H2513" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IWB.MI.xlsx
+++ b/data/IWB.MI.xlsx
@@ -38,223 +38,223 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8466157913208</t>
+    <t xml:space="preserve">7.84661483764648</t>
   </si>
   <si>
     <t xml:space="preserve">IWB.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79867458343506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83063507080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74274015426636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75073194503784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71077823638916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6947979927063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5909218788147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51101732254028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31125736236572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44709396362305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35120964050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29527568817139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26331472396851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29927062988281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29127979278564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27130460739136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24733352661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37518119812012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4311146736145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47106504440308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1514458656311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41513204574585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32723760604858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28728485107422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99163818359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11149501800537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19140100479126</t>
+    <t xml:space="preserve">7.7986741065979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83063650131226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74274063110352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75073099136353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71077871322632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69479846954346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59092235565186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51101684570312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31125593185425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44709300994873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35120868682861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29527521133423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26331424713135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29926872253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29128074645996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27130508422852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24733209609985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3751802444458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43111371994019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47106599807739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15144824981689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41513252258301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3272385597229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28728580474854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99163913726807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11149549484253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19139957427979</t>
   </si>
   <si>
     <t xml:space="preserve">7.25532388687134</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41912698745728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42312240600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6308741569519</t>
+    <t xml:space="preserve">7.41912746429443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42312288284302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63087463378906</t>
   </si>
   <si>
     <t xml:space="preserve">7.67082643508911</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49903249740601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58293199539185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89455986022949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98644971847534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91053867340088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54297924041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82264566421509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6428599357605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62288331985474</t>
+    <t xml:space="preserve">7.49903154373169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.582932472229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89456081390381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98645067214966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91054010391235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54297971725464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82264471054077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64286088943481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62288427352905</t>
   </si>
   <si>
     <t xml:space="preserve">7.77470207214355</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76671266555786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79068422317505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8705883026123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96647357940674</t>
+    <t xml:space="preserve">7.7667121887207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79068231582642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87058734893799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96647262573242</t>
   </si>
   <si>
     <t xml:space="preserve">7.7187705039978</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66283559799194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57094526290894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5589599609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39116096496582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46307468414307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60690259933472</t>
+    <t xml:space="preserve">7.6628360748291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57094669342041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55896139144897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39116144180298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46307420730591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60690450668335</t>
   </si>
   <si>
     <t xml:space="preserve">7.54697513580322</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36719036102295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31525087356567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33123207092285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34721422195435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50302696228027</t>
+    <t xml:space="preserve">7.36718940734863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31525182723999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33123302459717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34721326828003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50302791595459</t>
   </si>
   <si>
     <t xml:space="preserve">7.24333667755127</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22336053848267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23934268951416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45907878875732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46707153320312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10350465774536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89974880218506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91173410415649</t>
+    <t xml:space="preserve">7.22336101531982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23934364318848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45907926559448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46707010269165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10350608825684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89974927902222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91173458099365</t>
   </si>
   <si>
     <t xml:space="preserve">6.95168590545654</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00761985778809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8717827796936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87577676773071</t>
+    <t xml:space="preserve">7.00761938095093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87178325653076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87577772140503</t>
   </si>
   <si>
     <t xml:space="preserve">6.87977266311646</t>
@@ -266,10 +266,10 @@
     <t xml:space="preserve">6.75192546844482</t>
   </si>
   <si>
-    <t xml:space="preserve">6.74393558502197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82383871078491</t>
+    <t xml:space="preserve">6.74393463134766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82383966445923</t>
   </si>
   <si>
     <t xml:space="preserve">6.6640305519104</t>
@@ -281,52 +281,52 @@
     <t xml:space="preserve">6.89575290679932</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03159093856812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07154417037964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33522844314575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25931930541992</t>
+    <t xml:space="preserve">7.03159189224243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07154273986816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33522701263428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25931835174561</t>
   </si>
   <si>
     <t xml:space="preserve">7.17941379547119</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26730918884277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23135185241699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09551382064819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18340826034546</t>
+    <t xml:space="preserve">7.26731014251709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23135137557983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09551429748535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18340969085693</t>
   </si>
   <si>
     <t xml:space="preserve">7.18740463256836</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20738077163696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14345741271973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12348127365112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23534727096558</t>
+    <t xml:space="preserve">7.20738124847412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14345645904541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12348079681396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23534774780273</t>
   </si>
   <si>
     <t xml:space="preserve">7.74673509597778</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83463001251221</t>
+    <t xml:space="preserve">7.83462953567505</t>
   </si>
   <si>
     <t xml:space="preserve">7.98245429992676</t>
@@ -338,52 +338,52 @@
     <t xml:space="preserve">7.78269243240356</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63886404037476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73474979400635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07034873962402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2141752243042</t>
+    <t xml:space="preserve">7.63886451721191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73475027084351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07034969329834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21417617797852</t>
   </si>
   <si>
     <t xml:space="preserve">8.16623401641846</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18221569061279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27011013031006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57374572753906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54977416992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35001373291016</t>
+    <t xml:space="preserve">8.18221378326416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27011203765869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57374668121338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54977607727051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35001468658447</t>
   </si>
   <si>
     <t xml:space="preserve">8.46987056732178</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52580261230469</t>
+    <t xml:space="preserve">8.52580547332764</t>
   </si>
   <si>
     <t xml:space="preserve">8.5098237991333</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59771728515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60571002960205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58173751831055</t>
+    <t xml:space="preserve">8.59771823883057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6057071685791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58173656463623</t>
   </si>
   <si>
     <t xml:space="preserve">8.64687442779541</t>
@@ -392,7 +392,7 @@
     <t xml:space="preserve">8.67129993438721</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61430358886719</t>
+    <t xml:space="preserve">8.61430549621582</t>
   </si>
   <si>
     <t xml:space="preserve">8.63058948516846</t>
@@ -401,19 +401,19 @@
     <t xml:space="preserve">8.75272083282471</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82600021362305</t>
+    <t xml:space="preserve">8.82600116729736</t>
   </si>
   <si>
     <t xml:space="preserve">8.87485027313232</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95627307891846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74457836151123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85856819152832</t>
+    <t xml:space="preserve">8.95627212524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74457740783691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.858567237854</t>
   </si>
   <si>
     <t xml:space="preserve">8.84228420257568</t>
@@ -422,91 +422,91 @@
     <t xml:space="preserve">8.91556262969971</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03769397735596</t>
+    <t xml:space="preserve">9.03769493103027</t>
   </si>
   <si>
     <t xml:space="preserve">9.00512504577637</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94813060760498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99698352813721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12725448608398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19239139556885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11911296844482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14353942871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98069858551025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13539791107178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16796684265137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15982341766357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18424987792969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15167999267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07026195526123</t>
+    <t xml:space="preserve">8.9481315612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99698257446289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1272554397583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19239234924316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11911392211914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14353847503662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98069953918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13539695739746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16796493530273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15982437133789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18424892425537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15168190002441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07026100158691</t>
   </si>
   <si>
     <t xml:space="preserve">8.96441459655762</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92370414733887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80157375335693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79343223571777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8667106628418</t>
+    <t xml:space="preserve">8.92370319366455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80157279968262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79343032836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86671161651611</t>
   </si>
   <si>
     <t xml:space="preserve">8.90742015838623</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89113712310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11097145080566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20053386688232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28195476531982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35523414611816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3959436416626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32266521453857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64834880828857</t>
+    <t xml:space="preserve">8.89113616943359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11097049713135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20053482055664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28195381164551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35523223876953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39594459533691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32266616821289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64834976196289</t>
   </si>
   <si>
     <t xml:space="preserve">9.60763740539551</t>
@@ -518,7 +518,7 @@
     <t xml:space="preserve">9.99031448364258</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1205892562866</t>
+    <t xml:space="preserve">10.1205883026123</t>
   </si>
   <si>
     <t xml:space="preserve">10.1368713378906</t>
@@ -527,16 +527,16 @@
     <t xml:space="preserve">10.1775817871094</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1043043136597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1531572341919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0961608886719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94146251678467</t>
+    <t xml:space="preserve">10.1043033599854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1531553268433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0961599349976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94146347045898</t>
   </si>
   <si>
     <t xml:space="preserve">9.90889358520508</t>
@@ -545,28 +545,28 @@
     <t xml:space="preserve">9.77047920227051</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83561611175537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91703605651855</t>
+    <t xml:space="preserve">9.83561420440674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91703701019287</t>
   </si>
   <si>
     <t xml:space="preserve">9.79490566253662</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77862071990967</t>
+    <t xml:space="preserve">9.77862167358398</t>
   </si>
   <si>
     <t xml:space="preserve">9.78676319122314</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95774555206299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.014741897583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99845600128174</t>
+    <t xml:space="preserve">9.95774459838867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0147399902344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99845695495605</t>
   </si>
   <si>
     <t xml:space="preserve">9.88446807861328</t>
@@ -578,58 +578,58 @@
     <t xml:space="preserve">9.85189914703369</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89260959625244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2590045928955</t>
+    <t xml:space="preserve">9.89260768890381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2590026855469</t>
   </si>
   <si>
     <t xml:space="preserve">10.3404245376587</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4625558853149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5276908874512</t>
+    <t xml:space="preserve">10.4625539779663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5276918411255</t>
   </si>
   <si>
     <t xml:space="preserve">10.5765419006348</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5439748764038</t>
+    <t xml:space="preserve">10.5439758300781</t>
   </si>
   <si>
     <t xml:space="preserve">10.5358324050903</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5032644271851</t>
+    <t xml:space="preserve">10.5032653808594</t>
   </si>
   <si>
     <t xml:space="preserve">10.5521173477173</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3485670089722</t>
+    <t xml:space="preserve">10.3485660552979</t>
   </si>
   <si>
     <t xml:space="preserve">10.4381275177002</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3241386413574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3811340332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3648490905762</t>
+    <t xml:space="preserve">10.3241395950317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3811330795288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3648500442505</t>
   </si>
   <si>
     <t xml:space="preserve">10.4218454360962</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4137029647827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3729934692383</t>
+    <t xml:space="preserve">10.4137020111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3729915618896</t>
   </si>
   <si>
     <t xml:space="preserve">10.3892765045166</t>
@@ -638,31 +638,31 @@
     <t xml:space="preserve">10.2915725708008</t>
   </si>
   <si>
-    <t xml:space="preserve">10.267144203186</t>
+    <t xml:space="preserve">10.2671451568604</t>
   </si>
   <si>
     <t xml:space="preserve">10.2264356613159</t>
   </si>
   <si>
-    <t xml:space="preserve">10.193868637085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3159980773926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2182922363281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2834310531616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4299879074097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3322820663452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2427206039429</t>
+    <t xml:space="preserve">10.1938667297363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3159971237183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2182931900024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2834300994873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4299869537354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3322811126709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2427177429199</t>
   </si>
   <si>
     <t xml:space="preserve">10.5846862792969</t>
@@ -674,391 +674,391 @@
     <t xml:space="preserve">10.7068166732788</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7475261688232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.788236618042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.625394821167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8696575164795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8289480209351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0324983596802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2360496520996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4396018981934</t>
+    <t xml:space="preserve">10.7475252151489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7882394790649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6253976821899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8696594238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8289489746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0324993133545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2360506057739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4396028518677</t>
   </si>
   <si>
     <t xml:space="preserve">11.6838645935059</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0732107162476</t>
+    <t xml:space="preserve">11.0732116699219</t>
   </si>
   <si>
     <t xml:space="preserve">10.9917888641357</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1546297073364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3174724578857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2767610549927</t>
+    <t xml:space="preserve">11.1546306610107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3174705505371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.276762008667</t>
   </si>
   <si>
     <t xml:space="preserve">11.1953411102295</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3581809997559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4839172363281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5258312225342</t>
+    <t xml:space="preserve">11.3581819534302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4839162826538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5258302688599</t>
   </si>
   <si>
     <t xml:space="preserve">11.567741394043</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4000959396362</t>
+    <t xml:space="preserve">11.4000949859619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0228834152222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1486206054688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2324466705322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1905345916748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2743577957153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8971481323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0647964477539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.442006111145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8552370071411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6875867843628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.325475692749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2822484970093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1957931518555</t>
   </si>
   <si>
     <t xml:space="preserve">11.0228843688965</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1486215591431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2324447631836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1905345916748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.274356842041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8971490859985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0647964477539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4420042037964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8552360534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6875886917114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3254737854004</t>
+    <t xml:space="preserve">11.2390213012695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1525659561157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9364309310913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0661115646362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1093397140503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9796581268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7635221481323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.590615272522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8499765396118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7202968597412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6770696640015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8067502975464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8932046890259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6338415145874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4119281768799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4551553726196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3687000274658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5416088104248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6280632019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5848360061646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4609346389771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3312520980835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3744802474976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2880249023438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5041618347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0286655426025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94221115112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59639453887939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63961982727051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81252956390381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85575485229492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55316638946533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03444194793701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81830883026123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86153507232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77508068084717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07767009735107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16412353515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25057697296143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33703136444092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29380512237549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2447996139526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68284797668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1583442687988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98543643951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89898204803467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76930141448975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72607707977295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46671295166016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50994110107422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38025951385498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42348670959473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20735168457031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.071891784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2972898483276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2077474594116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1629772186279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.342059135437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.431601524353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3868312835693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1182060241699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2525186538696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.476372718811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6554546356201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7897691726685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7449970245361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5659151077271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7002267837524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1031646728516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9688510894775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9240808486938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8793096542358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1479349136353</t>
   </si>
   <si>
     <t xml:space="preserve">11.282247543335</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1957941055298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0228853225708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2390203475952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.15256690979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9364309310913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0661115646362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1093397140503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9796571731567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7635231018066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5906171798706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8499774932861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7202949523926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6770696640015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8067512512207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8932056427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6338415145874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4119281768799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4551544189453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3687000274658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5416088104248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.62806224823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5848340988159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4609336853027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3312540054321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3744783401489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2880258560181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5041608810425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0286655426025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94221019744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59639549255371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63962078094482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81252861022949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85575580596924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55316734313965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03444290161133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81830978393555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86153411865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77508068084717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07767105102539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16412448883057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25057697296143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33703327178955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2938060760498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2447996139526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68284702301025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1583442687988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98543739318848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89898204803467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76930141448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72607517242432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46671199798584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50993919372559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3802604675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42348766326904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20734977722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.071891784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.297290802002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2077465057373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1629772186279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3420600891113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4315996170044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3868312835693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1182050704956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2525177001953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.476372718811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6554555892944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7897691726685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7449960708618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5659151077271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7002267837524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1031637191772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9688529968262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9240808486938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8793096542358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1479339599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2822494506836</t>
-  </si>
-  <si>
     <t xml:space="preserve">11.237476348877</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4613313674927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.327018737793</t>
+    <t xml:space="preserve">11.4613304138184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3270168304443</t>
   </si>
   <si>
     <t xml:space="preserve">11.1927061080933</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3717889785767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4165601730347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0583934783936</t>
+    <t xml:space="preserve">11.371789932251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.416558265686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0583944320679</t>
   </si>
   <si>
     <t xml:space="preserve">11.6404142379761</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7299547195435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6851835250854</t>
+    <t xml:space="preserve">11.7299566268921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6851854324341</t>
   </si>
   <si>
     <t xml:space="preserve">11.7747259140015</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8194980621338</t>
+    <t xml:space="preserve">11.8194971084595</t>
   </si>
   <si>
     <t xml:space="preserve">11.8642683029175</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5508718490601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5956439971924</t>
+    <t xml:space="preserve">11.5508737564087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5956430435181</t>
   </si>
   <si>
     <t xml:space="preserve">10.5211429595947</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0136232376099</t>
+    <t xml:space="preserve">11.0136222839355</t>
   </si>
   <si>
     <t xml:space="preserve">10.8345394134521</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9985790252686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0881214141846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0433502197266</t>
+    <t xml:space="preserve">11.9985809326172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0881223678589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0433511734009</t>
   </si>
   <si>
     <t xml:space="preserve">12.1328935623169</t>
@@ -1073,19 +1073,19 @@
     <t xml:space="preserve">12.356746673584</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2672061920166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.401517868042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3119764328003</t>
+    <t xml:space="preserve">12.267204284668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4015188217163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.311975479126</t>
   </si>
   <si>
     <t xml:space="preserve">12.6701431274414</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6253728866577</t>
+    <t xml:space="preserve">12.6253719329834</t>
   </si>
   <si>
     <t xml:space="preserve">12.5806016921997</t>
@@ -1094,19 +1094,19 @@
     <t xml:space="preserve">10.6106853485107</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6257266998291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0734348297119</t>
+    <t xml:space="preserve">9.62572765350342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0734357833862</t>
   </si>
   <si>
     <t xml:space="preserve">10.0286645889282</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4910593032837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9090385437012</t>
+    <t xml:space="preserve">12.491060256958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9090375900269</t>
   </si>
   <si>
     <t xml:space="preserve">13.1626224517822</t>
@@ -1115,49 +1115,49 @@
     <t xml:space="preserve">13.6998720169067</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8789539337158</t>
+    <t xml:space="preserve">13.8789548873901</t>
   </si>
   <si>
     <t xml:space="preserve">14.0132665634155</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1475801467896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2371225357056</t>
+    <t xml:space="preserve">14.1475811004639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2371215820312</t>
   </si>
   <si>
     <t xml:space="preserve">14.1923503875732</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9237270355225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9684972763062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7894134521484</t>
+    <t xml:space="preserve">13.9237260818481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9684982299805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7894124984741</t>
   </si>
   <si>
     <t xml:space="preserve">14.2818918228149</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8341846466064</t>
+    <t xml:space="preserve">13.8341836929321</t>
   </si>
   <si>
     <t xml:space="preserve">13.5207891464233</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4312477111816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5655574798584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6103296279907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7004642486572</t>
+    <t xml:space="preserve">13.4312467575073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5655584335327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.610330581665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7004652023315</t>
   </si>
   <si>
     <t xml:space="preserve">13.7905988693237</t>
@@ -1169,16 +1169,13 @@
     <t xml:space="preserve">13.6553955078125</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5201950073242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.610330581665</t>
+    <t xml:space="preserve">13.5201940536499</t>
   </si>
   <si>
     <t xml:space="preserve">13.2948589324951</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1596574783325</t>
+    <t xml:space="preserve">13.1596565246582</t>
   </si>
   <si>
     <t xml:space="preserve">13.069522857666</t>
@@ -1187,10 +1184,10 @@
     <t xml:space="preserve">12.9793872833252</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7089834213257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5737810134888</t>
+    <t xml:space="preserve">12.7089824676514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5737819671631</t>
   </si>
   <si>
     <t xml:space="preserve">12.6188497543335</t>
@@ -1199,22 +1196,22 @@
     <t xml:space="preserve">13.3399257659912</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1145896911621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4751281738281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9343214035034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7540512084961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8441858291626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0610036849976</t>
+    <t xml:space="preserve">13.1145906448364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4751272201538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9343204498291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7540521621704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8441848754883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0610046386719</t>
   </si>
   <si>
     <t xml:space="preserve">13.8807344436646</t>
@@ -1223,25 +1220,25 @@
     <t xml:space="preserve">14.1962060928345</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3314075469971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4215421676636</t>
+    <t xml:space="preserve">14.3314065933228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4215412139893</t>
   </si>
   <si>
     <t xml:space="preserve">14.3764743804932</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5116777420044</t>
+    <t xml:space="preserve">14.5116767883301</t>
   </si>
   <si>
     <t xml:space="preserve">14.4666080474854</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6018104553223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6919450759888</t>
+    <t xml:space="preserve">14.6018114089966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6919460296631</t>
   </si>
   <si>
     <t xml:space="preserve">14.8722152709961</t>
@@ -1253,67 +1250,67 @@
     <t xml:space="preserve">15.0074167251587</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3228883743286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1876850128174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.224235534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9538297653198</t>
+    <t xml:space="preserve">15.3228874206543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.187686920166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2242317199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9538316726685</t>
   </si>
   <si>
     <t xml:space="preserve">16.8551769256592</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3143711090088</t>
+    <t xml:space="preserve">16.3143692016602</t>
   </si>
   <si>
     <t xml:space="preserve">16.9903774261475</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8101119995117</t>
+    <t xml:space="preserve">16.8101100921631</t>
   </si>
   <si>
     <t xml:space="preserve">17.7565250396729</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0269260406494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9367923736572</t>
+    <t xml:space="preserve">18.026927947998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.93678855896</t>
   </si>
   <si>
     <t xml:space="preserve">17.3509159088135</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4410572052002</t>
+    <t xml:space="preserve">17.4410514831543</t>
   </si>
   <si>
     <t xml:space="preserve">17.4861183166504</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0354461669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6298408508301</t>
+    <t xml:space="preserve">17.0354480743408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6298427581787</t>
   </si>
   <si>
     <t xml:space="preserve">16.7199726104736</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4045028686523</t>
+    <t xml:space="preserve">16.4045066833496</t>
   </si>
   <si>
     <t xml:space="preserve">16.6749057769775</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7650413513184</t>
+    <t xml:space="preserve">16.9453105926514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.765043258667</t>
   </si>
   <si>
     <t xml:space="preserve">15.863697052002</t>
@@ -1343,61 +1340,61 @@
     <t xml:space="preserve">16.0890312194824</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5932922363281</t>
+    <t xml:space="preserve">15.5932912826538</t>
   </si>
   <si>
     <t xml:space="preserve">16.2693023681641</t>
   </si>
   <si>
-    <t xml:space="preserve">17.125581741333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5762557983398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.666389465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8466548919678</t>
+    <t xml:space="preserve">17.1255836486816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5762538909912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6663875579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8466567993164</t>
   </si>
   <si>
     <t xml:space="preserve">18.5677356719971</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3874645233154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7480049133301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3789463043213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0098876953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5506954193115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.460563659668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2802925109863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3704261779785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1000232696533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6408290863037</t>
+    <t xml:space="preserve">18.3874664306641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7480030059814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3789443969727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0098915100098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5506935119629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4605617523193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.280294418335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3704280853271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1000213623047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6408309936523</t>
   </si>
   <si>
     <t xml:space="preserve">20.7309665679932</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4435234069824</t>
+    <t xml:space="preserve">22.4435253143311</t>
   </si>
   <si>
     <t xml:space="preserve">21.9027156829834</t>
@@ -1406,46 +1403,49 @@
     <t xml:space="preserve">21.5361442565918</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1695690155029</t>
+    <t xml:space="preserve">21.9027137756348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1695709228516</t>
   </si>
   <si>
     <t xml:space="preserve">21.7194328308105</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3609294891357</t>
+    <t xml:space="preserve">22.3609313964844</t>
   </si>
   <si>
     <t xml:space="preserve">22.4525756835938</t>
   </si>
   <si>
-    <t xml:space="preserve">22.269287109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0860004425049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9943599700928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6277866363525</t>
+    <t xml:space="preserve">22.2692890167236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0860023498535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9943580627441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6277885437012</t>
   </si>
   <si>
     <t xml:space="preserve">23.2773628234863</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9107894897461</t>
+    <t xml:space="preserve">22.9107913970947</t>
   </si>
   <si>
     <t xml:space="preserve">22.727502822876</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1776466369629</t>
+    <t xml:space="preserve">22.1776447296143</t>
   </si>
   <si>
     <t xml:space="preserve">22.6358623504639</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0024337768555</t>
+    <t xml:space="preserve">23.0024356842041</t>
   </si>
   <si>
     <t xml:space="preserve">23.0940780639648</t>
@@ -1460,7 +1460,7 @@
     <t xml:space="preserve">24.9269428253174</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2099437713623</t>
+    <t xml:space="preserve">26.2099456787109</t>
   </si>
   <si>
     <t xml:space="preserve">26.8514461517334</t>
@@ -1469,7 +1469,7 @@
     <t xml:space="preserve">26.6681613922119</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3096599578857</t>
+    <t xml:space="preserve">27.3096618652344</t>
   </si>
   <si>
     <t xml:space="preserve">26.4848747253418</t>
@@ -1478,13 +1478,13 @@
     <t xml:space="preserve">26.7598037719727</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5765171051025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3015899658203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5684432983398</t>
+    <t xml:space="preserve">26.5765190124512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3015880584717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5684413909912</t>
   </si>
   <si>
     <t xml:space="preserve">27.0347328186035</t>
@@ -1496,25 +1496,25 @@
     <t xml:space="preserve">28.4093818664551</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1344547271729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2260913848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.364688873291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4570751190186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0875072479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9951114654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9027214050293</t>
+    <t xml:space="preserve">28.1344528198242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2260932922363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3646869659424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4570770263672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0875053405762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9951095581055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9027194976807</t>
   </si>
   <si>
     <t xml:space="preserve">27.7179317474365</t>
@@ -1523,10 +1523,10 @@
     <t xml:space="preserve">29.1038303375244</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9353694915771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.750581741333</t>
+    <t xml:space="preserve">29.9353675842285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7505836486816</t>
   </si>
   <si>
     <t xml:space="preserve">29.3810081481934</t>
@@ -1538,13 +1538,13 @@
     <t xml:space="preserve">28.9190425872803</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7342567443848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0114364624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8429737091064</t>
+    <t xml:space="preserve">28.7342548370361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0114345550537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8429756164551</t>
   </si>
   <si>
     <t xml:space="preserve">30.120153427124</t>
@@ -1556,7 +1556,7 @@
     <t xml:space="preserve">30.027759552002</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3973331451416</t>
+    <t xml:space="preserve">30.397331237793</t>
   </si>
   <si>
     <t xml:space="preserve">31.1364784240723</t>
@@ -1565,19 +1565,19 @@
     <t xml:space="preserve">30.8592987060547</t>
   </si>
   <si>
-    <t xml:space="preserve">31.0440826416016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6745128631592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4897232055664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2886161804199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4734039306641</t>
+    <t xml:space="preserve">31.0440845489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6745109558105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4897270202637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2886142730713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4734020233154</t>
   </si>
   <si>
     <t xml:space="preserve">32.8919448852539</t>
@@ -1595,7 +1595,7 @@
     <t xml:space="preserve">35.8485260009766</t>
   </si>
   <si>
-    <t xml:space="preserve">37.4192047119141</t>
+    <t xml:space="preserve">37.4192085266113</t>
   </si>
   <si>
     <t xml:space="preserve">40.0986099243164</t>
@@ -1604,10 +1604,10 @@
     <t xml:space="preserve">37.2344207763672</t>
   </si>
   <si>
-    <t xml:space="preserve">37.881175994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.1583518981934</t>
+    <t xml:space="preserve">37.8811721801758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.1583557128906</t>
   </si>
   <si>
     <t xml:space="preserve">37.6039962768555</t>
@@ -1616,64 +1616,64 @@
     <t xml:space="preserve">37.6963882446289</t>
   </si>
   <si>
-    <t xml:space="preserve">37.7887840270996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.1420288085938</t>
+    <t xml:space="preserve">37.7887802124023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.142032623291</t>
   </si>
   <si>
     <t xml:space="preserve">38.5279273986816</t>
   </si>
   <si>
-    <t xml:space="preserve">38.3431358337402</t>
+    <t xml:space="preserve">38.3431396484375</t>
   </si>
   <si>
     <t xml:space="preserve">36.4952774047852</t>
   </si>
   <si>
-    <t xml:space="preserve">35.9409217834473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.4028854370117</t>
+    <t xml:space="preserve">35.9409255981445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.402889251709</t>
   </si>
   <si>
     <t xml:space="preserve">36.6800651550293</t>
   </si>
   <si>
-    <t xml:space="preserve">37.9735641479492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.0659599304199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.4355354309082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.8051071166992</t>
+    <t xml:space="preserve">37.9735717773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.0659637451172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.4355316162109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.805103302002</t>
   </si>
   <si>
     <t xml:space="preserve">39.3594627380371</t>
   </si>
   <si>
-    <t xml:space="preserve">39.8214263916016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.006217956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.5605773925781</t>
+    <t xml:space="preserve">39.8214225769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.0062141418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.5605812072754</t>
   </si>
   <si>
     <t xml:space="preserve">40.6529693603516</t>
   </si>
   <si>
-    <t xml:space="preserve">41.946475982666</t>
+    <t xml:space="preserve">41.9464721679688</t>
   </si>
   <si>
     <t xml:space="preserve">41.1149291992188</t>
   </si>
   <si>
-    <t xml:space="preserve">40.9301452636719</t>
+    <t xml:space="preserve">40.9301490783691</t>
   </si>
   <si>
     <t xml:space="preserve">42.3160438537598</t>
@@ -1682,46 +1682,46 @@
     <t xml:space="preserve">43.5171546936035</t>
   </si>
   <si>
-    <t xml:space="preserve">44.0715141296387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.8867225646973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.7019424438477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.9791221618652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.3486938476562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.9954452514648</t>
+    <t xml:space="preserve">44.0715103149414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.8867301940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.7019386291504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.979118347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.348690032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.9954490661621</t>
   </si>
   <si>
     <t xml:space="preserve">44.8106575012207</t>
   </si>
   <si>
-    <t xml:space="preserve">44.5334739685059</t>
+    <t xml:space="preserve">44.5334777832031</t>
   </si>
   <si>
     <t xml:space="preserve">43.7943382263184</t>
   </si>
   <si>
-    <t xml:space="preserve">43.1475830078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.3921165466309</t>
+    <t xml:space="preserve">43.1475791931152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.3921089172363</t>
   </si>
   <si>
     <t xml:space="preserve">41.8540802001953</t>
   </si>
   <si>
-    <t xml:space="preserve">41.5768966674805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.2073249816895</t>
+    <t xml:space="preserve">41.5769004821777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.2073211669922</t>
   </si>
   <si>
     <t xml:space="preserve">40.1909980773926</t>
@@ -1730,7 +1730,7 @@
     <t xml:space="preserve">39.4518585205078</t>
   </si>
   <si>
-    <t xml:space="preserve">38.9898910522461</t>
+    <t xml:space="preserve">38.9898948669434</t>
   </si>
   <si>
     <t xml:space="preserve">39.1746788024902</t>
@@ -1751,19 +1751,19 @@
     <t xml:space="preserve">39.9138221740723</t>
   </si>
   <si>
-    <t xml:space="preserve">40.4681816101074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.636646270752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.6203155517578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.2670669555664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.3268203735352</t>
+    <t xml:space="preserve">40.4681854248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.6366386413574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.6203193664551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.2670745849609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.3268165588379</t>
   </si>
   <si>
     <t xml:space="preserve">38.8974990844727</t>
@@ -1772,22 +1772,22 @@
     <t xml:space="preserve">37.5116004943848</t>
   </si>
   <si>
-    <t xml:space="preserve">38.7127113342285</t>
+    <t xml:space="preserve">38.7127151489258</t>
   </si>
   <si>
     <t xml:space="preserve">39.0822868347168</t>
   </si>
   <si>
-    <t xml:space="preserve">36.7724571228027</t>
+    <t xml:space="preserve">36.7724533081055</t>
   </si>
   <si>
     <t xml:space="preserve">36.310489654541</t>
   </si>
   <si>
-    <t xml:space="preserve">36.2180976867676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.3865623474121</t>
+    <t xml:space="preserve">36.2181015014648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.3865585327148</t>
   </si>
   <si>
     <t xml:space="preserve">36.0333137512207</t>
@@ -1799,22 +1799,22 @@
     <t xml:space="preserve">33.7234840393066</t>
   </si>
   <si>
-    <t xml:space="preserve">33.169132232666</t>
+    <t xml:space="preserve">33.1691246032715</t>
   </si>
   <si>
     <t xml:space="preserve">32.6147689819336</t>
   </si>
   <si>
-    <t xml:space="preserve">33.6310958862305</t>
+    <t xml:space="preserve">33.6310997009277</t>
   </si>
   <si>
     <t xml:space="preserve">32.707160949707</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9680118560791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0604095458984</t>
+    <t xml:space="preserve">31.9680156707764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0604133605957</t>
   </si>
   <si>
     <t xml:space="preserve">31.4136562347412</t>
@@ -1823,7 +1823,7 @@
     <t xml:space="preserve">31.6908378601074</t>
   </si>
   <si>
-    <t xml:space="preserve">32.2451934814453</t>
+    <t xml:space="preserve">32.2451972961426</t>
   </si>
   <si>
     <t xml:space="preserve">32.7995529174805</t>
@@ -1835,28 +1835,28 @@
     <t xml:space="preserve">35.1093826293945</t>
   </si>
   <si>
-    <t xml:space="preserve">34.7398071289062</t>
+    <t xml:space="preserve">34.739803314209</t>
   </si>
   <si>
     <t xml:space="preserve">35.0169906616211</t>
   </si>
   <si>
-    <t xml:space="preserve">32.3375854492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4299812316895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5223770141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5060482025146</t>
+    <t xml:space="preserve">32.337589263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4299774169922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5223731994629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5060501098633</t>
   </si>
   <si>
     <t xml:space="preserve">31.3212661743164</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5522480010986</t>
+    <t xml:space="preserve">31.5522441864014</t>
   </si>
   <si>
     <t xml:space="preserve">31.9218196868896</t>
@@ -1865,19 +1865,19 @@
     <t xml:space="preserve">32.1528015136719</t>
   </si>
   <si>
-    <t xml:space="preserve">33.4925003051758</t>
+    <t xml:space="preserve">33.492504119873</t>
   </si>
   <si>
     <t xml:space="preserve">34.3702392578125</t>
   </si>
   <si>
-    <t xml:space="preserve">33.8620758056641</t>
+    <t xml:space="preserve">33.8620719909668</t>
   </si>
   <si>
     <t xml:space="preserve">32.1066017150879</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5359210968018</t>
+    <t xml:space="preserve">30.5359230041504</t>
   </si>
   <si>
     <t xml:space="preserve">30.3511352539062</t>
@@ -1889,10 +1889,10 @@
     <t xml:space="preserve">28.3643817901611</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3180351257324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8082180023193</t>
+    <t xml:space="preserve">28.3180332183838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8082160949707</t>
   </si>
   <si>
     <t xml:space="preserve">27.7618732452393</t>
@@ -1916,7 +1916,7 @@
     <t xml:space="preserve">29.5694065093994</t>
   </si>
   <si>
-    <t xml:space="preserve">29.105936050415</t>
+    <t xml:space="preserve">29.1059341430664</t>
   </si>
   <si>
     <t xml:space="preserve">27.9009132385254</t>
@@ -1925,22 +1925,22 @@
     <t xml:space="preserve">27.7155246734619</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1130123138428</t>
+    <t xml:space="preserve">27.1130142211914</t>
   </si>
   <si>
     <t xml:space="preserve">26.4641532897949</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4178085327148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.186071395874</t>
+    <t xml:space="preserve">26.4178066253662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1860733032227</t>
   </si>
   <si>
     <t xml:space="preserve">26.6031951904297</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2324199676514</t>
+    <t xml:space="preserve">26.2324180603027</t>
   </si>
   <si>
     <t xml:space="preserve">26.556848526001</t>
@@ -1949,34 +1949,34 @@
     <t xml:space="preserve">26.3251132965088</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8152980804443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6299095153809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2591323852539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7029685974121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6566181182861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9614162445068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7296772003174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0273952484131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7956600189209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2858448028564</t>
+    <t xml:space="preserve">25.8152961730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6299076080322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2591304779053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7029666900635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6566219329834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9614143371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.729679107666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0273971557617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7956619262695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2858467102051</t>
   </si>
   <si>
     <t xml:space="preserve">24.6102714538574</t>
@@ -1988,7 +1988,7 @@
     <t xml:space="preserve">24.5175800323486</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3785381317139</t>
+    <t xml:space="preserve">24.3785362243652</t>
   </si>
   <si>
     <t xml:space="preserve">24.4712314605713</t>
@@ -1997,10 +1997,10 @@
     <t xml:space="preserve">23.8687210083008</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5442905426025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1004543304443</t>
+    <t xml:space="preserve">23.5442924499512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.100456237793</t>
   </si>
   <si>
     <t xml:space="preserve">23.4979457855225</t>
@@ -2009,28 +2009,28 @@
     <t xml:space="preserve">23.8223743438721</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9150657653809</t>
+    <t xml:space="preserve">23.9150676727295</t>
   </si>
   <si>
     <t xml:space="preserve">24.193151473999</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8883571624756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5835590362549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9543361663818</t>
+    <t xml:space="preserve">24.888355255127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5835609436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9543380737305</t>
   </si>
   <si>
     <t xml:space="preserve">26.6958885192871</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7885837554932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7422370910645</t>
+    <t xml:space="preserve">26.7885818481445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7422389984131</t>
   </si>
   <si>
     <t xml:space="preserve">25.4445209503174</t>
@@ -2039,31 +2039,31 @@
     <t xml:space="preserve">24.981050491333</t>
   </si>
   <si>
-    <t xml:space="preserve">25.861644744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1200923919678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0077629089355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4515972137451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1271705627441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0808200836182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3125553131104</t>
+    <t xml:space="preserve">25.8616428375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1200885772705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0077610015869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4515953063965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1271686553955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0808219909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.312557220459</t>
   </si>
   <si>
     <t xml:space="preserve">23.6369857788086</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5906391143799</t>
+    <t xml:space="preserve">23.5906372070312</t>
   </si>
   <si>
     <t xml:space="preserve">23.4052505493164</t>
@@ -2072,31 +2072,31 @@
     <t xml:space="preserve">23.2662105560303</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3589038848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8027362823486</t>
+    <t xml:space="preserve">23.3589019775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8027381896973</t>
   </si>
   <si>
     <t xml:space="preserve">22.6173496246338</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1735134124756</t>
+    <t xml:space="preserve">23.1735153198242</t>
   </si>
   <si>
     <t xml:space="preserve">22.8954334259033</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9684925079346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5513687133789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2732887268066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.856164932251</t>
+    <t xml:space="preserve">21.9684944152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5513706207275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.273286819458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8561668395996</t>
   </si>
   <si>
     <t xml:space="preserve">20.7171230316162</t>
@@ -2117,31 +2117,31 @@
     <t xml:space="preserve">19.5584468841553</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6047916412354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9292240142822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0682640075684</t>
+    <t xml:space="preserve">19.604793548584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9292221069336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.068265914917</t>
   </si>
   <si>
     <t xml:space="preserve">20.1146106719971</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8098163604736</t>
+    <t xml:space="preserve">20.8098182678223</t>
   </si>
   <si>
     <t xml:space="preserve">20.9952049255371</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5780849456787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0878982543945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5977153778076</t>
+    <t xml:space="preserve">20.5780830383301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0879001617432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5977172851562</t>
   </si>
   <si>
     <t xml:space="preserve">22.061185836792</t>
@@ -2150,7 +2150,7 @@
     <t xml:space="preserve">22.4319629669189</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3856143951416</t>
+    <t xml:space="preserve">22.3856163024902</t>
   </si>
   <si>
     <t xml:space="preserve">22.3392696380615</t>
@@ -2162,40 +2162,40 @@
     <t xml:space="preserve">24.5639266967773</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4248847961426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1664352416992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2127857208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8420066833496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7689476013184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7226009368896</t>
+    <t xml:space="preserve">24.4248867034912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1664371490479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2127876281738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8420085906982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.768949508667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7226028442383</t>
   </si>
   <si>
     <t xml:space="preserve">25.3518257141113</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5372123718262</t>
+    <t xml:space="preserve">25.5372142791748</t>
   </si>
   <si>
     <t xml:space="preserve">25.3054790496826</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6762561798096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4908676147461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6691780090332</t>
+    <t xml:space="preserve">25.6762542724609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4908657073975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6691799163818</t>
   </si>
   <si>
     <t xml:space="preserve">27.2057075500488</t>
@@ -2207,7 +2207,7 @@
     <t xml:space="preserve">27.2984008789062</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5764827728271</t>
+    <t xml:space="preserve">27.5764808654785</t>
   </si>
   <si>
     <t xml:space="preserve">28.0399532318115</t>
@@ -2216,19 +2216,19 @@
     <t xml:space="preserve">28.1789951324463</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2716884613037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1326484680176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4374408721924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5301361083984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.093376159668</t>
+    <t xml:space="preserve">28.2716903686523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1326465606689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.437442779541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5301380157471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0933780670166</t>
   </si>
   <si>
     <t xml:space="preserve">25.39817237854</t>
@@ -2237,7 +2237,7 @@
     <t xml:space="preserve">22.941780090332</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2002296447754</t>
+    <t xml:space="preserve">22.2002277374268</t>
   </si>
   <si>
     <t xml:space="preserve">22.1538791656494</t>
@@ -2249,7 +2249,7 @@
     <t xml:space="preserve">22.7100448608398</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9881248474121</t>
+    <t xml:space="preserve">22.9881267547607</t>
   </si>
   <si>
     <t xml:space="preserve">23.2198619842529</t>
@@ -2264,25 +2264,25 @@
     <t xml:space="preserve">20.6707744598389</t>
   </si>
   <si>
-    <t xml:space="preserve">20.485387802124</t>
+    <t xml:space="preserve">20.4853858947754</t>
   </si>
   <si>
     <t xml:space="preserve">20.2536525726318</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5317325592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1342468261719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7831058502197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.644063949585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2269382476807</t>
+    <t xml:space="preserve">20.5317344665527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1342430114746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7831039428711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6440620422363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2269401550293</t>
   </si>
   <si>
     <t xml:space="preserve">21.3196353912354</t>
@@ -2294,7 +2294,7 @@
     <t xml:space="preserve">21.1805934906006</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9025096893311</t>
+    <t xml:space="preserve">20.9025077819824</t>
   </si>
   <si>
     <t xml:space="preserve">20.6679439544678</t>
@@ -2324,25 +2324,25 @@
     <t xml:space="preserve">20.9006900787354</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0403385162354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1799850463867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2265357971191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9472370147705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4817447662354</t>
+    <t xml:space="preserve">21.0403366088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1799869537354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2265319824219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9472389221191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4817428588867</t>
   </si>
   <si>
     <t xml:space="preserve">20.3420963287354</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2489948272705</t>
+    <t xml:space="preserve">20.2489967346191</t>
   </si>
   <si>
     <t xml:space="preserve">20.1558990478516</t>
@@ -2354,7 +2354,7 @@
     <t xml:space="preserve">19.6904029846191</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6438541412354</t>
+    <t xml:space="preserve">19.643856048584</t>
   </si>
   <si>
     <t xml:space="preserve">19.7835025787354</t>
@@ -2375,13 +2375,13 @@
     <t xml:space="preserve">19.3180084228516</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5507564544678</t>
+    <t xml:space="preserve">19.5507545471191</t>
   </si>
   <si>
     <t xml:space="preserve">20.2024478912354</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4351940155029</t>
+    <t xml:space="preserve">20.4351978302002</t>
   </si>
   <si>
     <t xml:space="preserve">19.4576568603516</t>
@@ -2390,22 +2390,22 @@
     <t xml:space="preserve">19.0387115478516</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9697017669678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9231510162354</t>
+    <t xml:space="preserve">19.9696998596191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.923152923584</t>
   </si>
   <si>
     <t xml:space="preserve">19.3645572662354</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1783618927002</t>
+    <t xml:space="preserve">19.1783599853516</t>
   </si>
   <si>
     <t xml:space="preserve">18.8990631103516</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1318092346191</t>
+    <t xml:space="preserve">19.1318111419678</t>
   </si>
   <si>
     <t xml:space="preserve">18.6197681427002</t>
@@ -2414,7 +2414,7 @@
     <t xml:space="preserve">18.8525142669678</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7128658294678</t>
+    <t xml:space="preserve">18.7128677368164</t>
   </si>
   <si>
     <t xml:space="preserve">18.6663150787354</t>
@@ -2429,19 +2429,19 @@
     <t xml:space="preserve">18.4708099365234</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3963317871094</t>
+    <t xml:space="preserve">18.3963298797607</t>
   </si>
   <si>
     <t xml:space="preserve">18.3404712677002</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2287521362305</t>
+    <t xml:space="preserve">18.2287540435791</t>
   </si>
   <si>
     <t xml:space="preserve">18.210132598877</t>
   </si>
   <si>
-    <t xml:space="preserve">17.968074798584</t>
+    <t xml:space="preserve">17.9680767059326</t>
   </si>
   <si>
     <t xml:space="preserve">17.6701583862305</t>
@@ -2468,7 +2468,7 @@
     <t xml:space="preserve">16.7577896118164</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2232837677002</t>
+    <t xml:space="preserve">17.2232856750488</t>
   </si>
   <si>
     <t xml:space="preserve">17.3350048065186</t>
@@ -2477,10 +2477,10 @@
     <t xml:space="preserve">17.4094829559326</t>
   </si>
   <si>
-    <t xml:space="preserve">17.651538848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7260189056396</t>
+    <t xml:space="preserve">17.6515369415283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7260208129883</t>
   </si>
   <si>
     <t xml:space="preserve">17.7073993682861</t>
@@ -2492,7 +2492,7 @@
     <t xml:space="preserve">17.2605247497559</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2419052124023</t>
+    <t xml:space="preserve">17.2419033050537</t>
   </si>
   <si>
     <t xml:space="preserve">16.5715923309326</t>
@@ -2501,10 +2501,10 @@
     <t xml:space="preserve">16.5529727935791</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0929470062256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9253673553467</t>
+    <t xml:space="preserve">17.092945098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9253692626953</t>
   </si>
   <si>
     <t xml:space="preserve">16.2736778259277</t>
@@ -2516,10 +2516,10 @@
     <t xml:space="preserve">15.9757604598999</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2364387512207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2922954559326</t>
+    <t xml:space="preserve">16.2364368438721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2922973632812</t>
   </si>
   <si>
     <t xml:space="preserve">17.0370864868164</t>
@@ -2543,25 +2543,25 @@
     <t xml:space="preserve">16.3667755126953</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4598731994629</t>
+    <t xml:space="preserve">16.4598751068115</t>
   </si>
   <si>
     <t xml:space="preserve">15.7709436416626</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7337017059326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.882661819458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1619567871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1433372497559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5157318115234</t>
+    <t xml:space="preserve">15.7337036132812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8826608657837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.161958694458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1433391571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5157337188721</t>
   </si>
   <si>
     <t xml:space="preserve">16.478494644165</t>
@@ -2570,58 +2570,58 @@
     <t xml:space="preserve">16.6460704803467</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8695087432861</t>
+    <t xml:space="preserve">16.8695106506348</t>
   </si>
   <si>
     <t xml:space="preserve">17.1115646362305</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0184669494629</t>
+    <t xml:space="preserve">17.0184688568115</t>
   </si>
   <si>
     <t xml:space="preserve">17.0557060241699</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4839630126953</t>
+    <t xml:space="preserve">17.4839611053467</t>
   </si>
   <si>
     <t xml:space="preserve">17.3536224365234</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3722438812256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.999849319458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0743255615234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6833114624023</t>
+    <t xml:space="preserve">17.372241973877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9998474121094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0743274688721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.683313369751</t>
   </si>
   <si>
     <t xml:space="preserve">16.8881282806396</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6646900177002</t>
+    <t xml:space="preserve">16.6646919250488</t>
   </si>
   <si>
     <t xml:space="preserve">16.7205486297607</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8322696685791</t>
+    <t xml:space="preserve">16.8322677612305</t>
   </si>
   <si>
     <t xml:space="preserve">16.7391700744629</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5902137756348</t>
+    <t xml:space="preserve">16.5902118682861</t>
   </si>
   <si>
     <t xml:space="preserve">16.3481540679932</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3109149932861</t>
+    <t xml:space="preserve">16.3109169006348</t>
   </si>
   <si>
     <t xml:space="preserve">16.199197769165</t>
@@ -2636,22 +2636,22 @@
     <t xml:space="preserve">16.2550563812256</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1060962677002</t>
+    <t xml:space="preserve">16.1060981750488</t>
   </si>
   <si>
     <t xml:space="preserve">17.1674251556396</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0053157806396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9122161865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4653415679932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9494552612305</t>
+    <t xml:space="preserve">18.005313873291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9122142791748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4653434753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9494571685791</t>
   </si>
   <si>
     <t xml:space="preserve">17.8749771118164</t>
@@ -2666,13 +2666,13 @@
     <t xml:space="preserve">17.3629322052002</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5025806427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4560317993164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1542720794678</t>
+    <t xml:space="preserve">17.5025787353516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.456033706665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1542739868164</t>
   </si>
   <si>
     <t xml:space="preserve">18.0611743927002</t>
@@ -2690,7 +2690,7 @@
     <t xml:space="preserve">18.6370983123779</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8282489776611</t>
+    <t xml:space="preserve">18.8282508850098</t>
   </si>
   <si>
     <t xml:space="preserve">19.1149749755859</t>
@@ -2699,7 +2699,7 @@
     <t xml:space="preserve">18.9716129302979</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2105484008789</t>
+    <t xml:space="preserve">19.2105503082275</t>
   </si>
   <si>
     <t xml:space="preserve">20.0707225799561</t>
@@ -2708,7 +2708,7 @@
     <t xml:space="preserve">20.8353214263916</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0264720916748</t>
+    <t xml:space="preserve">21.0264701843262</t>
   </si>
   <si>
     <t xml:space="preserve">20.9308967590332</t>
@@ -2732,7 +2732,7 @@
     <t xml:space="preserve">21.217622756958</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7397480010986</t>
+    <t xml:space="preserve">20.73974609375</t>
   </si>
   <si>
     <t xml:space="preserve">21.1220455169678</t>
@@ -2741,7 +2741,7 @@
     <t xml:space="preserve">19.8795719146729</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7839984893799</t>
+    <t xml:space="preserve">19.7840003967285</t>
   </si>
   <si>
     <t xml:space="preserve">20.3574466705322</t>
@@ -2750,22 +2750,22 @@
     <t xml:space="preserve">19.9751472473145</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6884250640869</t>
+    <t xml:space="preserve">19.6884231567383</t>
   </si>
   <si>
     <t xml:space="preserve">21.3131942749023</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4087715148926</t>
+    <t xml:space="preserve">21.4087696075439</t>
   </si>
   <si>
     <t xml:space="preserve">21.5999221801758</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5043449401855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8866443634033</t>
+    <t xml:space="preserve">21.5043468475342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.886646270752</t>
   </si>
   <si>
     <t xml:space="preserve">22.5556697845459</t>
@@ -2774,10 +2774,10 @@
     <t xml:space="preserve">22.7468185424805</t>
   </si>
   <si>
-    <t xml:space="preserve">22.937967300415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8423938751221</t>
+    <t xml:space="preserve">22.9379692077637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8423919677734</t>
   </si>
   <si>
     <t xml:space="preserve">23.1291179656982</t>
@@ -2789,7 +2789,7 @@
     <t xml:space="preserve">22.0777950286865</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9822216033936</t>
+    <t xml:space="preserve">21.9822196960449</t>
   </si>
   <si>
     <t xml:space="preserve">22.1733722686768</t>
@@ -2798,7 +2798,7 @@
     <t xml:space="preserve">21.6954956054688</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7910709381104</t>
+    <t xml:space="preserve">21.7910690307617</t>
   </si>
   <si>
     <t xml:space="preserve">22.6512451171875</t>
@@ -33025,7 +33025,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1142" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="H1142" t="s">
         <v>9</v>
@@ -33051,7 +33051,7 @@
         <v>14.75</v>
       </c>
       <c r="G1143" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H1143" t="s">
         <v>9</v>
@@ -33077,7 +33077,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1144" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1144" t="s">
         <v>9</v>
@@ -33103,7 +33103,7 @@
         <v>14.5</v>
       </c>
       <c r="G1145" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1145" t="s">
         <v>9</v>
@@ -33129,7 +33129,7 @@
         <v>14.5</v>
       </c>
       <c r="G1146" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1146" t="s">
         <v>9</v>
@@ -33155,7 +33155,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1147" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1147" t="s">
         <v>9</v>
@@ -33181,7 +33181,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1148" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1148" t="s">
         <v>9</v>
@@ -33207,7 +33207,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G1149" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1149" t="s">
         <v>9</v>
@@ -33233,7 +33233,7 @@
         <v>14</v>
       </c>
       <c r="G1150" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H1150" t="s">
         <v>9</v>
@@ -33259,7 +33259,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1151" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1151" t="s">
         <v>9</v>
@@ -33285,7 +33285,7 @@
         <v>14.5</v>
       </c>
       <c r="G1152" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1152" t="s">
         <v>9</v>
@@ -33311,7 +33311,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1153" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H1153" t="s">
         <v>9</v>
@@ -33337,7 +33337,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G1154" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H1154" t="s">
         <v>9</v>
@@ -33363,7 +33363,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G1155" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H1155" t="s">
         <v>9</v>
@@ -33389,7 +33389,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G1156" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H1156" t="s">
         <v>9</v>
@@ -33415,7 +33415,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1157" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H1157" t="s">
         <v>9</v>
@@ -33467,7 +33467,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1159" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1159" t="s">
         <v>9</v>
@@ -33493,7 +33493,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1160" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1160" t="s">
         <v>9</v>
@@ -33519,7 +33519,7 @@
         <v>14.5</v>
       </c>
       <c r="G1161" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1161" t="s">
         <v>9</v>
@@ -33545,7 +33545,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G1162" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H1162" t="s">
         <v>9</v>
@@ -33571,7 +33571,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G1163" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1163" t="s">
         <v>9</v>
@@ -33597,7 +33597,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1164" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1164" t="s">
         <v>9</v>
@@ -33623,7 +33623,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1165" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1165" t="s">
         <v>9</v>
@@ -33649,7 +33649,7 @@
         <v>14.25</v>
       </c>
       <c r="G1166" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H1166" t="s">
         <v>9</v>
@@ -33675,7 +33675,7 @@
         <v>14.5</v>
       </c>
       <c r="G1167" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1167" t="s">
         <v>9</v>
@@ -33701,7 +33701,7 @@
         <v>14.5</v>
       </c>
       <c r="G1168" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1168" t="s">
         <v>9</v>
@@ -33753,7 +33753,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1170" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H1170" t="s">
         <v>9</v>
@@ -33805,7 +33805,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1172" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H1172" t="s">
         <v>9</v>
@@ -33857,7 +33857,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1174" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H1174" t="s">
         <v>9</v>
@@ -33883,7 +33883,7 @@
         <v>15.75</v>
       </c>
       <c r="G1175" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H1175" t="s">
         <v>9</v>
@@ -33909,7 +33909,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1176" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H1176" t="s">
         <v>9</v>
@@ -33935,7 +33935,7 @@
         <v>16</v>
       </c>
       <c r="G1177" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H1177" t="s">
         <v>9</v>
@@ -33961,7 +33961,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1178" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H1178" t="s">
         <v>9</v>
@@ -33987,7 +33987,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G1179" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H1179" t="s">
         <v>9</v>
@@ -34013,7 +34013,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1180" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H1180" t="s">
         <v>9</v>
@@ -34039,7 +34039,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1181" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H1181" t="s">
         <v>9</v>
@@ -34065,7 +34065,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1182" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H1182" t="s">
         <v>9</v>
@@ -34091,7 +34091,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1183" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H1183" t="s">
         <v>9</v>
@@ -34117,7 +34117,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1184" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H1184" t="s">
         <v>9</v>
@@ -34143,7 +34143,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1185" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H1185" t="s">
         <v>9</v>
@@ -34169,7 +34169,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1186" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H1186" t="s">
         <v>9</v>
@@ -34195,7 +34195,7 @@
         <v>16.5</v>
       </c>
       <c r="G1187" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H1187" t="s">
         <v>9</v>
@@ -34221,7 +34221,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1188" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H1188" t="s">
         <v>9</v>
@@ -34247,7 +34247,7 @@
         <v>16.5</v>
       </c>
       <c r="G1189" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H1189" t="s">
         <v>9</v>
@@ -34273,7 +34273,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1190" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H1190" t="s">
         <v>9</v>
@@ -34299,7 +34299,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G1191" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H1191" t="s">
         <v>9</v>
@@ -34325,7 +34325,7 @@
         <v>17</v>
       </c>
       <c r="G1192" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H1192" t="s">
         <v>9</v>
@@ -34351,7 +34351,7 @@
         <v>17</v>
       </c>
       <c r="G1193" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H1193" t="s">
         <v>9</v>
@@ -34377,7 +34377,7 @@
         <v>17</v>
       </c>
       <c r="G1194" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H1194" t="s">
         <v>9</v>
@@ -34403,7 +34403,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1195" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H1195" t="s">
         <v>9</v>
@@ -34429,7 +34429,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G1196" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H1196" t="s">
         <v>9</v>
@@ -34455,7 +34455,7 @@
         <v>18</v>
       </c>
       <c r="G1197" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H1197" t="s">
         <v>9</v>
@@ -34481,7 +34481,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1198" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H1198" t="s">
         <v>9</v>
@@ -34507,7 +34507,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1199" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H1199" t="s">
         <v>9</v>
@@ -34533,7 +34533,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1200" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H1200" t="s">
         <v>9</v>
@@ -34559,7 +34559,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G1201" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H1201" t="s">
         <v>9</v>
@@ -34585,7 +34585,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G1202" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H1202" t="s">
         <v>9</v>
@@ -34611,7 +34611,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1203" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H1203" t="s">
         <v>9</v>
@@ -34637,7 +34637,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G1204" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H1204" t="s">
         <v>9</v>
@@ -34663,7 +34663,7 @@
         <v>20</v>
       </c>
       <c r="G1205" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H1205" t="s">
         <v>9</v>
@@ -34689,7 +34689,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G1206" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H1206" t="s">
         <v>9</v>
@@ -34715,7 +34715,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G1207" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H1207" t="s">
         <v>9</v>
@@ -34741,7 +34741,7 @@
         <v>19.25</v>
       </c>
       <c r="G1208" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H1208" t="s">
         <v>9</v>
@@ -34767,7 +34767,7 @@
         <v>19.3500003814697</v>
       </c>
       <c r="G1209" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H1209" t="s">
         <v>9</v>
@@ -34793,7 +34793,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1210" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H1210" t="s">
         <v>9</v>
@@ -34819,7 +34819,7 @@
         <v>19.3500003814697</v>
       </c>
       <c r="G1211" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H1211" t="s">
         <v>9</v>
@@ -34845,7 +34845,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1212" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H1212" t="s">
         <v>9</v>
@@ -34871,7 +34871,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1213" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H1213" t="s">
         <v>9</v>
@@ -34897,7 +34897,7 @@
         <v>18.4500007629395</v>
       </c>
       <c r="G1214" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H1214" t="s">
         <v>9</v>
@@ -34923,7 +34923,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G1215" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1215" t="s">
         <v>9</v>
@@ -34949,7 +34949,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1216" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H1216" t="s">
         <v>9</v>
@@ -34975,7 +34975,7 @@
         <v>18.5</v>
       </c>
       <c r="G1217" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H1217" t="s">
         <v>9</v>
@@ -35001,7 +35001,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1218" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H1218" t="s">
         <v>9</v>
@@ -35027,7 +35027,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1219" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H1219" t="s">
         <v>9</v>
@@ -35053,7 +35053,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1220" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H1220" t="s">
         <v>9</v>
@@ -35079,7 +35079,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1221" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H1221" t="s">
         <v>9</v>
@@ -35105,7 +35105,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1222" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H1222" t="s">
         <v>9</v>
@@ -35131,7 +35131,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1223" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H1223" t="s">
         <v>9</v>
@@ -35157,7 +35157,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1224" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H1224" t="s">
         <v>9</v>
@@ -35183,7 +35183,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1225" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H1225" t="s">
         <v>9</v>
@@ -35209,7 +35209,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1226" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H1226" t="s">
         <v>9</v>
@@ -35235,7 +35235,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1227" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H1227" t="s">
         <v>9</v>
@@ -35261,7 +35261,7 @@
         <v>17.75</v>
       </c>
       <c r="G1228" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H1228" t="s">
         <v>9</v>
@@ -35287,7 +35287,7 @@
         <v>18</v>
       </c>
       <c r="G1229" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H1229" t="s">
         <v>9</v>
@@ -35313,7 +35313,7 @@
         <v>18.5</v>
       </c>
       <c r="G1230" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H1230" t="s">
         <v>9</v>
@@ -35339,7 +35339,7 @@
         <v>18.4500007629395</v>
       </c>
       <c r="G1231" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H1231" t="s">
         <v>9</v>
@@ -35365,7 +35365,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1232" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H1232" t="s">
         <v>9</v>
@@ -35391,7 +35391,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G1233" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H1233" t="s">
         <v>9</v>
@@ -35417,7 +35417,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1234" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H1234" t="s">
         <v>9</v>
@@ -35443,7 +35443,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1235" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H1235" t="s">
         <v>9</v>
@@ -35469,7 +35469,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1236" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H1236" t="s">
         <v>9</v>
@@ -35495,7 +35495,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G1237" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H1237" t="s">
         <v>9</v>
@@ -35521,7 +35521,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G1238" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H1238" t="s">
         <v>9</v>
@@ -35547,7 +35547,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G1239" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H1239" t="s">
         <v>9</v>
@@ -35573,7 +35573,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1240" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H1240" t="s">
         <v>9</v>
@@ -35599,7 +35599,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1241" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H1241" t="s">
         <v>9</v>
@@ -35625,7 +35625,7 @@
         <v>18.5</v>
       </c>
       <c r="G1242" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H1242" t="s">
         <v>9</v>
@@ -35651,7 +35651,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1243" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H1243" t="s">
         <v>9</v>
@@ -35677,7 +35677,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G1244" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H1244" t="s">
         <v>9</v>
@@ -35703,7 +35703,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G1245" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H1245" t="s">
         <v>9</v>
@@ -35729,7 +35729,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1246" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H1246" t="s">
         <v>9</v>
@@ -35755,7 +35755,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1247" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H1247" t="s">
         <v>9</v>
@@ -35781,7 +35781,7 @@
         <v>17.75</v>
       </c>
       <c r="G1248" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H1248" t="s">
         <v>9</v>
@@ -35807,7 +35807,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1249" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H1249" t="s">
         <v>9</v>
@@ -35833,7 +35833,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1250" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H1250" t="s">
         <v>9</v>
@@ -35859,7 +35859,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1251" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H1251" t="s">
         <v>9</v>
@@ -35885,7 +35885,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G1252" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H1252" t="s">
         <v>9</v>
@@ -35911,7 +35911,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1253" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H1253" t="s">
         <v>9</v>
@@ -35937,7 +35937,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1254" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H1254" t="s">
         <v>9</v>
@@ -35963,7 +35963,7 @@
         <v>18.0499992370605</v>
       </c>
       <c r="G1255" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H1255" t="s">
         <v>9</v>
@@ -35989,7 +35989,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1256" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H1256" t="s">
         <v>9</v>
@@ -36015,7 +36015,7 @@
         <v>18</v>
       </c>
       <c r="G1257" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H1257" t="s">
         <v>9</v>
@@ -36041,7 +36041,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G1258" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H1258" t="s">
         <v>9</v>
@@ -36067,7 +36067,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G1259" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H1259" t="s">
         <v>9</v>
@@ -36093,7 +36093,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1260" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H1260" t="s">
         <v>9</v>
@@ -36119,7 +36119,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1261" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H1261" t="s">
         <v>9</v>
@@ -36145,7 +36145,7 @@
         <v>19</v>
       </c>
       <c r="G1262" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H1262" t="s">
         <v>9</v>
@@ -36171,7 +36171,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1263" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H1263" t="s">
         <v>9</v>
@@ -36197,7 +36197,7 @@
         <v>19.5</v>
       </c>
       <c r="G1264" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H1264" t="s">
         <v>9</v>
@@ -36223,7 +36223,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G1265" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H1265" t="s">
         <v>9</v>
@@ -36249,7 +36249,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G1266" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H1266" t="s">
         <v>9</v>
@@ -36275,7 +36275,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G1267" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H1267" t="s">
         <v>9</v>
@@ -36301,7 +36301,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G1268" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H1268" t="s">
         <v>9</v>
@@ -36327,7 +36327,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1269" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H1269" t="s">
         <v>9</v>
@@ -36353,7 +36353,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1270" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H1270" t="s">
         <v>9</v>
@@ -36379,7 +36379,7 @@
         <v>21.5</v>
       </c>
       <c r="G1271" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H1271" t="s">
         <v>9</v>
@@ -36405,7 +36405,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1272" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H1272" t="s">
         <v>9</v>
@@ -36431,7 +36431,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G1273" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H1273" t="s">
         <v>9</v>
@@ -36457,7 +36457,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1274" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H1274" t="s">
         <v>9</v>
@@ -36483,7 +36483,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G1275" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H1275" t="s">
         <v>9</v>
@@ -36509,7 +36509,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G1276" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H1276" t="s">
         <v>9</v>
@@ -36535,7 +36535,7 @@
         <v>22.5</v>
       </c>
       <c r="G1277" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H1277" t="s">
         <v>9</v>
@@ -36561,7 +36561,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G1278" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H1278" t="s">
         <v>9</v>
@@ -36587,7 +36587,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G1279" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H1279" t="s">
         <v>9</v>
@@ -36613,7 +36613,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G1280" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H1280" t="s">
         <v>9</v>
@@ -36639,7 +36639,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G1281" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H1281" t="s">
         <v>9</v>
@@ -36665,7 +36665,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1282" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H1282" t="s">
         <v>9</v>
@@ -36691,7 +36691,7 @@
         <v>23</v>
       </c>
       <c r="G1283" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H1283" t="s">
         <v>9</v>
@@ -36717,7 +36717,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G1284" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H1284" t="s">
         <v>9</v>
@@ -36743,7 +36743,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G1285" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H1285" t="s">
         <v>9</v>
@@ -36769,7 +36769,7 @@
         <v>23.5</v>
       </c>
       <c r="G1286" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H1286" t="s">
         <v>9</v>
@@ -36795,7 +36795,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G1287" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H1287" t="s">
         <v>9</v>
@@ -36847,7 +36847,7 @@
         <v>23.5</v>
       </c>
       <c r="G1289" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H1289" t="s">
         <v>9</v>
@@ -68653,7 +68653,7 @@
     </row>
     <row r="2513">
       <c r="A2513" s="1" t="n">
-        <v>45978.6911689815</v>
+        <v>45978.3333333333</v>
       </c>
       <c r="B2513" t="n">
         <v>5027</v>
@@ -68674,6 +68674,32 @@
         <v>996</v>
       </c>
       <c r="H2513" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2514">
+      <c r="A2514" s="1" t="n">
+        <v>45979.6909953704</v>
+      </c>
+      <c r="B2514" t="n">
+        <v>2951</v>
+      </c>
+      <c r="C2514" t="n">
+        <v>21.8999996185303</v>
+      </c>
+      <c r="D2514" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="E2514" t="n">
+        <v>21.7999992370605</v>
+      </c>
+      <c r="F2514" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="G2514" t="s">
+        <v>963</v>
+      </c>
+      <c r="H2514" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IWB.MI.xlsx
+++ b/data/IWB.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84661722183228</t>
+    <t xml:space="preserve">7.84661626815796</t>
   </si>
   <si>
     <t xml:space="preserve">IWB.MI</t>
@@ -53,100 +53,100 @@
     <t xml:space="preserve">7.74274015426636</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75073099136353</t>
+    <t xml:space="preserve">7.75073146820068</t>
   </si>
   <si>
     <t xml:space="preserve">7.71077871322632</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69479751586914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59092283248901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51101636886597</t>
+    <t xml:space="preserve">7.69479703903198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59092140197754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51101732254028</t>
   </si>
   <si>
     <t xml:space="preserve">7.31125688552856</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44709300994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35120820999146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29527521133423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26331520080566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29927062988281</t>
+    <t xml:space="preserve">7.44709444046021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35120868682861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29527616500854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26331472396851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29927015304565</t>
   </si>
   <si>
     <t xml:space="preserve">7.2912802696228</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2713041305542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24733114242554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37518072128296</t>
+    <t xml:space="preserve">7.27130556106567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24733352661133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3751802444458</t>
   </si>
   <si>
     <t xml:space="preserve">7.43111419677734</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47106599807739</t>
+    <t xml:space="preserve">7.47106552124023</t>
   </si>
   <si>
     <t xml:space="preserve">7.15144824981689</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41513204574585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32723760604858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28728532791138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99163913726807</t>
+    <t xml:space="preserve">7.41513252258301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32723665237427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28728437423706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99163722991943</t>
   </si>
   <si>
     <t xml:space="preserve">7.11149597167969</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19140100479126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25532484054565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41912841796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42312145233154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63087511062622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67082738876343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49903297424316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58293151855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89455842971802</t>
+    <t xml:space="preserve">7.19140005111694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2553243637085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41912651062012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42312335968018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6308741569519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67082691192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49903154373169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58293199539185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89455938339233</t>
   </si>
   <si>
     <t xml:space="preserve">7.98644828796387</t>
@@ -155,76 +155,76 @@
     <t xml:space="preserve">7.9105396270752</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54297924041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82264614105225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64285850524902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62288284301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77470111846924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76671314239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79068326950073</t>
+    <t xml:space="preserve">7.54297876358032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82264566421509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64285898208618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62288475036621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77470064163208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76671266555786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79068279266357</t>
   </si>
   <si>
     <t xml:space="preserve">7.8705883026123</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96647262573242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71877002716064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66283702850342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57094621658325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55896043777466</t>
+    <t xml:space="preserve">7.96647357940674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71876955032349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66283750534058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57094812393188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55896139144897</t>
   </si>
   <si>
     <t xml:space="preserve">7.3911600112915</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46307468414307</t>
+    <t xml:space="preserve">7.46307516098022</t>
   </si>
   <si>
     <t xml:space="preserve">7.60690355300903</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54697465896606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36718893051147</t>
+    <t xml:space="preserve">7.54697513580322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36718988418579</t>
   </si>
   <si>
     <t xml:space="preserve">7.31525182723999</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33123302459717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34721326828003</t>
+    <t xml:space="preserve">7.33123254776001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34721517562866</t>
   </si>
   <si>
     <t xml:space="preserve">7.50302696228027</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24333715438843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22336101531982</t>
+    <t xml:space="preserve">7.24333763122559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2233624458313</t>
   </si>
   <si>
     <t xml:space="preserve">7.23934316635132</t>
@@ -233,13 +233,13 @@
     <t xml:space="preserve">7.45907926559448</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46707010269165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10350656509399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89974880218506</t>
+    <t xml:space="preserve">7.46706962585449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10350513458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89974927902222</t>
   </si>
   <si>
     <t xml:space="preserve">6.91173410415649</t>
@@ -248,70 +248,70 @@
     <t xml:space="preserve">6.95168685913086</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00761985778809</t>
+    <t xml:space="preserve">7.00762128829956</t>
   </si>
   <si>
     <t xml:space="preserve">6.8717827796936</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87577724456787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87977313995361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86778783798218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75192499160767</t>
+    <t xml:space="preserve">6.87577772140503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87977266311646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86778688430786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75192642211914</t>
   </si>
   <si>
     <t xml:space="preserve">6.7439341545105</t>
   </si>
   <si>
-    <t xml:space="preserve">6.82384014129639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66403102874756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83183097839355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89575386047363</t>
+    <t xml:space="preserve">6.82383966445923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6640305519104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83183002471924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89575338363647</t>
   </si>
   <si>
     <t xml:space="preserve">7.03159141540527</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07154273986816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33522796630859</t>
+    <t xml:space="preserve">7.07154417037964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33522844314575</t>
   </si>
   <si>
     <t xml:space="preserve">7.25931835174561</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17941331863403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26731061935425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23135375976562</t>
+    <t xml:space="preserve">7.17941427230835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26730823516846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23135280609131</t>
   </si>
   <si>
     <t xml:space="preserve">7.09551429748535</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18340921401978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18740463256836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20738172531128</t>
+    <t xml:space="preserve">7.18340826034546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1874041557312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20738220214844</t>
   </si>
   <si>
     <t xml:space="preserve">7.14345598220825</t>
@@ -320,58 +320,58 @@
     <t xml:space="preserve">7.12348222732544</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23534822463989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7467360496521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83462953567505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98245334625244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9265193939209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78269195556641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63886451721191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73474931716919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07034778594971</t>
+    <t xml:space="preserve">7.23534727096558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74673557281494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.834632396698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98245429992676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92652034759521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78269100189209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63886547088623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73474979400635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07034969329834</t>
   </si>
   <si>
     <t xml:space="preserve">8.21417713165283</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16623306274414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18221473693848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27011013031006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57374477386475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54977703094482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35001277923584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46986961364746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.525803565979</t>
+    <t xml:space="preserve">8.16623497009277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18221378326416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27011203765869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57374572753906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54977512359619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35001373291016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46987152099609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52580451965332</t>
   </si>
   <si>
     <t xml:space="preserve">8.50982284545898</t>
@@ -380,49 +380,49 @@
     <t xml:space="preserve">8.59771919250488</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60570907592773</t>
+    <t xml:space="preserve">8.60571002960205</t>
   </si>
   <si>
     <t xml:space="preserve">8.58173751831055</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64687442779541</t>
+    <t xml:space="preserve">8.64687156677246</t>
   </si>
   <si>
     <t xml:space="preserve">8.67129993438721</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6143045425415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63058948516846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75272274017334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82599925994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87485122680664</t>
+    <t xml:space="preserve">8.61430644989014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63059139251709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75272083282471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82599830627441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87485218048096</t>
   </si>
   <si>
     <t xml:space="preserve">8.95627212524414</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74457931518555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.858567237854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84228229522705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91556262969971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03769397735596</t>
+    <t xml:space="preserve">8.74457836151123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85856819152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84228420257568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91556358337402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03769302368164</t>
   </si>
   <si>
     <t xml:space="preserve">9.00512599945068</t>
@@ -431,16 +431,16 @@
     <t xml:space="preserve">8.94812965393066</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99698257446289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12725448608398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19239139556885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11911487579346</t>
+    <t xml:space="preserve">8.99698352813721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1272554397583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19239234924316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11911392211914</t>
   </si>
   <si>
     <t xml:space="preserve">9.14354038238525</t>
@@ -455,154 +455,154 @@
     <t xml:space="preserve">9.16796684265137</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15982437133789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18424987792969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15168285369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07026100158691</t>
+    <t xml:space="preserve">9.15982532501221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.184250831604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1516809463501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07026290893555</t>
   </si>
   <si>
     <t xml:space="preserve">8.96441459655762</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92370510101318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80157375335693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79343223571777</t>
+    <t xml:space="preserve">8.92370414733887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8015718460083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79343128204346</t>
   </si>
   <si>
     <t xml:space="preserve">8.86670970916748</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9074182510376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89113616943359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11096954345703</t>
+    <t xml:space="preserve">8.90742015838623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89113426208496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11097049713135</t>
   </si>
   <si>
     <t xml:space="preserve">9.20053482055664</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28195571899414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35523223876953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39594268798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32266616821289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64834880828857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60763931274414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9007511138916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99031448364258</t>
+    <t xml:space="preserve">9.28195476531982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35523319244385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39594459533691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32266521453857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64834785461426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60763740539551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90075206756592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99031543731689</t>
   </si>
   <si>
     <t xml:space="preserve">10.1205883026123</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1368713378906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.177583694458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1043033599854</t>
+    <t xml:space="preserve">10.1368732452393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1775827407837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1043014526367</t>
   </si>
   <si>
     <t xml:space="preserve">10.1531562805176</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0961618423462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94146156311035</t>
+    <t xml:space="preserve">10.0961627960205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94146251678467</t>
   </si>
   <si>
     <t xml:space="preserve">9.90889358520508</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77047920227051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83561515808105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91703701019287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79490566253662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7786226272583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78676223754883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95774555206299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0147399902344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99845695495605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88446998596191</t>
+    <t xml:space="preserve">9.77048110961914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83561611175537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91703510284424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7949047088623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77862167358398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78676319122314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9577465057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.014741897583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99845790863037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88446712493896</t>
   </si>
   <si>
     <t xml:space="preserve">9.86004161834717</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85190105438232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89261054992676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2590026855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3404245376587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4625539779663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5276918411255</t>
+    <t xml:space="preserve">9.85190010070801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89260959625244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2590036392212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3404235839844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4625558853149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5276908874512</t>
   </si>
   <si>
     <t xml:space="preserve">10.5765428543091</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5439748764038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5358324050903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5032653808594</t>
+    <t xml:space="preserve">10.5439767837524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5358333587646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5032634735107</t>
   </si>
   <si>
     <t xml:space="preserve">10.5521173477173</t>
@@ -614,82 +614,82 @@
     <t xml:space="preserve">10.4381284713745</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3241405487061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3811359405518</t>
+    <t xml:space="preserve">10.3241395950317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3811349868774</t>
   </si>
   <si>
     <t xml:space="preserve">10.3648490905762</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4218454360962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4137020111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3729906082153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.389274597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2915716171265</t>
+    <t xml:space="preserve">10.4218444824219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4137010574341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3729915618896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3892765045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2915706634521</t>
   </si>
   <si>
     <t xml:space="preserve">10.267144203186</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2264347076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1938667297363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3159980773926</t>
+    <t xml:space="preserve">10.2264366149902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1938676834106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3159971237183</t>
   </si>
   <si>
     <t xml:space="preserve">10.2182922363281</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2834300994873</t>
+    <t xml:space="preserve">10.283429145813</t>
   </si>
   <si>
     <t xml:space="preserve">10.4299869537354</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3322811126709</t>
+    <t xml:space="preserve">10.3322830200195</t>
   </si>
   <si>
     <t xml:space="preserve">10.2427186965942</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5846843719482</t>
+    <t xml:space="preserve">10.5846862792969</t>
   </si>
   <si>
     <t xml:space="preserve">10.6661071777344</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7068157196045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7475261688232</t>
+    <t xml:space="preserve">10.7068166732788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7475280761719</t>
   </si>
   <si>
     <t xml:space="preserve">10.7882375717163</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6253976821899</t>
+    <t xml:space="preserve">10.6253967285156</t>
   </si>
   <si>
     <t xml:space="preserve">10.8696584701538</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8289489746094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0324993133545</t>
+    <t xml:space="preserve">10.8289470672607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0325002670288</t>
   </si>
   <si>
     <t xml:space="preserve">11.2360515594482</t>
@@ -698,31 +698,31 @@
     <t xml:space="preserve">11.4396018981934</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6838655471802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0732097625732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9917879104614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1546297073364</t>
+    <t xml:space="preserve">11.6838665008545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0732107162476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9917898178101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1546287536621</t>
   </si>
   <si>
     <t xml:space="preserve">11.3174705505371</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2767610549927</t>
+    <t xml:space="preserve">11.276762008667</t>
   </si>
   <si>
     <t xml:space="preserve">11.1953411102295</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3581829071045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4839181900024</t>
+    <t xml:space="preserve">11.3581809997559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4839172363281</t>
   </si>
   <si>
     <t xml:space="preserve">11.5258293151855</t>
@@ -740,267 +740,267 @@
     <t xml:space="preserve">11.1486215591431</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2324457168579</t>
+    <t xml:space="preserve">11.2324438095093</t>
   </si>
   <si>
     <t xml:space="preserve">11.1905336380005</t>
   </si>
   <si>
-    <t xml:space="preserve">11.274356842041</t>
+    <t xml:space="preserve">11.2743577957153</t>
   </si>
   <si>
     <t xml:space="preserve">10.8971481323242</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0647983551025</t>
+    <t xml:space="preserve">11.0647974014282</t>
   </si>
   <si>
     <t xml:space="preserve">11.3581819534302</t>
   </si>
   <si>
-    <t xml:space="preserve">11.442006111145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8552360534668</t>
+    <t xml:space="preserve">11.4420051574707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8552370071411</t>
   </si>
   <si>
     <t xml:space="preserve">10.6875896453857</t>
   </si>
   <si>
-    <t xml:space="preserve">11.325475692749</t>
+    <t xml:space="preserve">11.3254747390747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2822465896606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1957931518555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0228862762451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2390203475952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1525659561157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.936429977417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0661134719849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1093397140503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9796571731567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.763524055481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5906162261963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8499774932861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7202959060669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6770696640015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8067512512207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8932046890259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6338415145874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4119291305542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4551563262939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3687000274658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5416097640991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6280632019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5848350524902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4609355926514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3312530517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3744802474976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2880258560181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5041608810425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0286636352539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94221115112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59639453887939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63962173461914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81252861022949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85575580596924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55316734313965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03444385528564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81830883026123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86153507232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77508068084717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07766914367676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16412544250488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25057888031006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33703231811523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29380512237549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2447986602783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68284797668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1583452224731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98543739318848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89898204803467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76930236816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72607517242432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46671390533447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50993919372559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38025951385498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42348480224609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.207350730896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0718908309937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2972898483276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2077465057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1629772186279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3420600891113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4316005706787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.386830329895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1182060241699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2525186538696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.476372718811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6554546356201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7897691726685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7449979782104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5659141540527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7002267837524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1031637191772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9688520431519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9240798950195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8793106079102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1479349136353</t>
   </si>
   <si>
     <t xml:space="preserve">11.282247543335</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1957921981812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0228853225708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2390203475952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1525659561157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9364309310913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0661125183105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.109338760376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9796590805054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7635231018066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.590615272522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8499765396118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7202949523926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6770706176758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8067502975464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8932046890259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6338424682617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4119272232056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4551544189453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3687019348145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5416088104248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6280632019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5848350524902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4609346389771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3312530517578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3744802474976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2880258560181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5041608810425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0286645889282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94221019744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59639453887939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63962173461914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81252956390381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85575580596924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55316638946533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03444385528564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81830883026123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86153507232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77508068084717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07767009735107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16412448883057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25057983398438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33703231811523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2938060760498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2447986602783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68284797668457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1583442687988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98543739318848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89898300170898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76930236816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72607517242432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46671390533447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5099401473999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3802604675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42348575592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.207350730896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0718908309937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2972898483276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2077465057373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1629781723022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3420600891113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.431601524353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3868322372437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1182060241699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2525196075439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4763717651367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6554565429688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7897691726685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7449979782104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5659160614014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7002267837524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1031627655029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9688520431519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9240808486938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8793106079102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1479349136353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2822484970093</t>
-  </si>
-  <si>
     <t xml:space="preserve">11.237476348877</t>
   </si>
   <si>
@@ -1013,58 +1013,58 @@
     <t xml:space="preserve">11.1927061080933</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3717908859253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4165601730347</t>
+    <t xml:space="preserve">11.371789932251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.416561126709</t>
   </si>
   <si>
     <t xml:space="preserve">11.0583944320679</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6404142379761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7299575805664</t>
+    <t xml:space="preserve">11.6404151916504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7299556732178</t>
   </si>
   <si>
     <t xml:space="preserve">11.6851854324341</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7747278213501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8194961547852</t>
+    <t xml:space="preserve">11.7747259140015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8194971084595</t>
   </si>
   <si>
     <t xml:space="preserve">11.8642683029175</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5508718490601</t>
+    <t xml:space="preserve">11.5508708953857</t>
   </si>
   <si>
     <t xml:space="preserve">11.5956430435181</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5211429595947</t>
+    <t xml:space="preserve">10.521143913269</t>
   </si>
   <si>
     <t xml:space="preserve">11.0136232376099</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8345394134521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9985799789429</t>
+    <t xml:space="preserve">10.8345403671265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9985809326172</t>
   </si>
   <si>
     <t xml:space="preserve">12.0881223678589</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0433511734009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1328916549683</t>
+    <t xml:space="preserve">12.0433502197266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1328926086426</t>
   </si>
   <si>
     <t xml:space="preserve">12.2224340438843</t>
@@ -1073,7 +1073,7 @@
     <t xml:space="preserve">12.1776647567749</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3567476272583</t>
+    <t xml:space="preserve">12.356746673584</t>
   </si>
   <si>
     <t xml:space="preserve">12.2672052383423</t>
@@ -1082,28 +1082,25 @@
     <t xml:space="preserve">12.401517868042</t>
   </si>
   <si>
-    <t xml:space="preserve">12.311975479126</t>
+    <t xml:space="preserve">12.3119764328003</t>
   </si>
   <si>
     <t xml:space="preserve">12.6701421737671</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6253719329834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5806007385254</t>
+    <t xml:space="preserve">12.6253728866577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5806016921997</t>
   </si>
   <si>
     <t xml:space="preserve">10.6106853485107</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6257266998291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0734348297119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0286636352539</t>
+    <t xml:space="preserve">9.62572574615479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0734357833862</t>
   </si>
   <si>
     <t xml:space="preserve">12.4910593032837</t>
@@ -1115,13 +1112,13 @@
     <t xml:space="preserve">13.1626214981079</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6998729705811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8789539337158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0132675170898</t>
+    <t xml:space="preserve">13.6998710632324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8789558410645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0132665634155</t>
   </si>
   <si>
     <t xml:space="preserve">14.1475811004639</t>
@@ -1130,22 +1127,22 @@
     <t xml:space="preserve">14.2371206283569</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1923503875732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9237251281738</t>
+    <t xml:space="preserve">14.1923513412476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9237260818481</t>
   </si>
   <si>
     <t xml:space="preserve">13.9684963226318</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7894144058228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2818927764893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8341836929321</t>
+    <t xml:space="preserve">13.7894134521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2818908691406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8341846466064</t>
   </si>
   <si>
     <t xml:space="preserve">13.520788192749</t>
@@ -1157,43 +1154,46 @@
     <t xml:space="preserve">13.5655584335327</t>
   </si>
   <si>
+    <t xml:space="preserve">13.610330581665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7004632949829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.790599822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8356666564941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6553964614868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5201950073242</t>
+  </si>
+  <si>
     <t xml:space="preserve">13.6103296279907</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7004642486572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7906007766724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8356666564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6553964614868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5201940536499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2948579788208</t>
+    <t xml:space="preserve">13.2948589324951</t>
   </si>
   <si>
     <t xml:space="preserve">13.1596574783325</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0695219039917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9793863296509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7089834213257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5737819671631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6188497543335</t>
+    <t xml:space="preserve">13.069522857666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9793872833252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.708984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5737810134888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6188488006592</t>
   </si>
   <si>
     <t xml:space="preserve">13.3399267196655</t>
@@ -1202,22 +1202,22 @@
     <t xml:space="preserve">13.1145896911621</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4751272201538</t>
+    <t xml:space="preserve">13.4751281738281</t>
   </si>
   <si>
     <t xml:space="preserve">12.9343214035034</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7540512084961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8441858291626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0610027313232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8807334899902</t>
+    <t xml:space="preserve">12.7540502548218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8441867828369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0610036849976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8807325363159</t>
   </si>
   <si>
     <t xml:space="preserve">14.1962051391602</t>
@@ -1226,25 +1226,25 @@
     <t xml:space="preserve">14.3314065933228</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4215421676636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3764743804932</t>
+    <t xml:space="preserve">14.4215412139893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3764734268188</t>
   </si>
   <si>
     <t xml:space="preserve">14.5116758346558</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4666080474854</t>
+    <t xml:space="preserve">14.4666090011597</t>
   </si>
   <si>
     <t xml:space="preserve">14.6018123626709</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6919441223145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8722152709961</t>
+    <t xml:space="preserve">14.6919450759888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8722143173218</t>
   </si>
   <si>
     <t xml:space="preserve">15.2327527999878</t>
@@ -1253,13 +1253,13 @@
     <t xml:space="preserve">15.0074148178101</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3228893280029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1876859664917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2242317199707</t>
+    <t xml:space="preserve">15.3228883743286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.187686920166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.224235534668</t>
   </si>
   <si>
     <t xml:space="preserve">15.9538307189941</t>
@@ -1268,13 +1268,13 @@
     <t xml:space="preserve">16.8551788330078</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3143672943115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9903774261475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8101100921631</t>
+    <t xml:space="preserve">16.3143692016602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9903812408447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8101081848145</t>
   </si>
   <si>
     <t xml:space="preserve">17.7565250396729</t>
@@ -1283,34 +1283,34 @@
     <t xml:space="preserve">18.026927947998</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9367904663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3509159088135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4410514831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4861183166504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0354461669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6298389434814</t>
+    <t xml:space="preserve">17.9367923736572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3509197235107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4410533905029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.486120223999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0354442596436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6298427581787</t>
   </si>
   <si>
     <t xml:space="preserve">16.7199726104736</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4045066833496</t>
+    <t xml:space="preserve">16.404504776001</t>
   </si>
   <si>
     <t xml:space="preserve">16.6749057769775</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9453125</t>
+    <t xml:space="preserve">16.9453086853027</t>
   </si>
   <si>
     <t xml:space="preserve">16.7650413513184</t>
@@ -1322,22 +1322,22 @@
     <t xml:space="preserve">15.9988985061646</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4946384429932</t>
+    <t xml:space="preserve">16.4946365356445</t>
   </si>
   <si>
     <t xml:space="preserve">16.3594360351562</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1791648864746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5847702026367</t>
+    <t xml:space="preserve">16.1791687011719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5847721099854</t>
   </si>
   <si>
     <t xml:space="preserve">16.5397071838379</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6834278106689</t>
+    <t xml:space="preserve">15.6834259033203</t>
   </si>
   <si>
     <t xml:space="preserve">16.0890331268311</t>
@@ -1349,22 +1349,22 @@
     <t xml:space="preserve">16.2693004608154</t>
   </si>
   <si>
-    <t xml:space="preserve">17.125581741333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5762538909912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6663913726807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8466548919678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5677337646484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3874683380127</t>
+    <t xml:space="preserve">17.1255798339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5762519836426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6663875579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.846658706665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5677356719971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3874664306641</t>
   </si>
   <si>
     <t xml:space="preserve">18.7480030059814</t>
@@ -1376,22 +1376,22 @@
     <t xml:space="preserve">20.0098896026611</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5506954193115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4605617523193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2802906036377</t>
+    <t xml:space="preserve">20.5506935119629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.460563659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2802925109863</t>
   </si>
   <si>
     <t xml:space="preserve">20.3704280853271</t>
   </si>
   <si>
-    <t xml:space="preserve">20.100025177002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.640832901001</t>
+    <t xml:space="preserve">20.1000232696533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6408309936523</t>
   </si>
   <si>
     <t xml:space="preserve">20.7309665679932</t>
@@ -1400,73 +1400,70 @@
     <t xml:space="preserve">22.4435234069824</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9027156829834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5361404418945</t>
-  </si>
-  <si>
     <t xml:space="preserve">21.9027137756348</t>
   </si>
   <si>
+    <t xml:space="preserve">21.5361442565918</t>
+  </si>
+  <si>
     <t xml:space="preserve">21.1695709228516</t>
   </si>
   <si>
     <t xml:space="preserve">21.7194290161133</t>
   </si>
   <si>
-    <t xml:space="preserve">22.360933303833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4525756835938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.269287109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0860042572021</t>
+    <t xml:space="preserve">22.3609313964844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4525737762451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2692890167236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0860023498535</t>
   </si>
   <si>
     <t xml:space="preserve">21.9943599700928</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6277885437012</t>
+    <t xml:space="preserve">21.6277866363525</t>
   </si>
   <si>
     <t xml:space="preserve">23.277364730835</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9107913970947</t>
+    <t xml:space="preserve">22.9107894897461</t>
   </si>
   <si>
     <t xml:space="preserve">22.727502822876</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1776466369629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6358623504639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0024337768555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0940780639648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1021518707275</t>
+    <t xml:space="preserve">22.1776447296143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6358604431152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0024356842041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0940799713135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1021480560303</t>
   </si>
   <si>
     <t xml:space="preserve">24.2854385375977</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9269428253174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2099437713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.851448059082</t>
+    <t xml:space="preserve">24.9269409179688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2099456787109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8514442443848</t>
   </si>
   <si>
     <t xml:space="preserve">26.6681613922119</t>
@@ -1475,7 +1472,7 @@
     <t xml:space="preserve">27.3096618652344</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4848728179932</t>
+    <t xml:space="preserve">26.4848747253418</t>
   </si>
   <si>
     <t xml:space="preserve">26.7598037719727</t>
@@ -1484,19 +1481,19 @@
     <t xml:space="preserve">26.5765151977539</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3015880584717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5684413909912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0347328186035</t>
+    <t xml:space="preserve">26.3015899658203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5684432983398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0347347259521</t>
   </si>
   <si>
     <t xml:space="preserve">29.1425247192383</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4093818664551</t>
+    <t xml:space="preserve">28.4093799591064</t>
   </si>
   <si>
     <t xml:space="preserve">28.1344528198242</t>
@@ -1508,13 +1505,13 @@
     <t xml:space="preserve">28.3646850585938</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4570770263672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0875053405762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9951114654541</t>
+    <t xml:space="preserve">28.4570789337158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0875034332275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9951133728027</t>
   </si>
   <si>
     <t xml:space="preserve">27.9027194976807</t>
@@ -1523,7 +1520,7 @@
     <t xml:space="preserve">27.7179317474365</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1038303375244</t>
+    <t xml:space="preserve">29.1038284301758</t>
   </si>
   <si>
     <t xml:space="preserve">29.9353694915771</t>
@@ -1541,28 +1538,28 @@
     <t xml:space="preserve">28.9190425872803</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7342548370361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0114345550537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8429737091064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1201515197754</t>
+    <t xml:space="preserve">28.7342586517334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0114364624023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8429718017578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.120153427124</t>
   </si>
   <si>
     <t xml:space="preserve">30.2125473022461</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0277614593506</t>
+    <t xml:space="preserve">30.027759552002</t>
   </si>
   <si>
     <t xml:space="preserve">30.3973331451416</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1364784240723</t>
+    <t xml:space="preserve">31.1364765167236</t>
   </si>
   <si>
     <t xml:space="preserve">30.8592987060547</t>
@@ -1571,13 +1568,13 @@
     <t xml:space="preserve">31.0440845489502</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6745109558105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4897270202637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2886142730713</t>
+    <t xml:space="preserve">30.6745090484619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.489725112915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2886161804199</t>
   </si>
   <si>
     <t xml:space="preserve">29.4734020233154</t>
@@ -1586,7 +1583,7 @@
     <t xml:space="preserve">32.8919486999512</t>
   </si>
   <si>
-    <t xml:space="preserve">33.3539085388184</t>
+    <t xml:space="preserve">33.3539123535156</t>
   </si>
   <si>
     <t xml:space="preserve">34.5550231933594</t>
@@ -1610,7 +1607,7 @@
     <t xml:space="preserve">37.8811721801758</t>
   </si>
   <si>
-    <t xml:space="preserve">38.1583557128906</t>
+    <t xml:space="preserve">38.1583518981934</t>
   </si>
   <si>
     <t xml:space="preserve">37.6039962768555</t>
@@ -1619,7 +1616,7 @@
     <t xml:space="preserve">37.6963882446289</t>
   </si>
   <si>
-    <t xml:space="preserve">37.7887802124023</t>
+    <t xml:space="preserve">37.7887840270996</t>
   </si>
   <si>
     <t xml:space="preserve">37.142032623291</t>
@@ -1628,46 +1625,46 @@
     <t xml:space="preserve">38.5279273986816</t>
   </si>
   <si>
-    <t xml:space="preserve">38.3431396484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.4952735900879</t>
+    <t xml:space="preserve">38.3431434631348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.4952774047852</t>
   </si>
   <si>
     <t xml:space="preserve">35.9409255981445</t>
   </si>
   <si>
-    <t xml:space="preserve">36.4028854370117</t>
+    <t xml:space="preserve">36.402889251709</t>
   </si>
   <si>
     <t xml:space="preserve">36.6800651550293</t>
   </si>
   <si>
-    <t xml:space="preserve">37.9735679626465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.0659561157227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.4355316162109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.8051071166992</t>
+    <t xml:space="preserve">37.9735641479492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.0659637451172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.4355278015137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.805103302002</t>
   </si>
   <si>
     <t xml:space="preserve">39.3594627380371</t>
   </si>
   <si>
-    <t xml:space="preserve">39.8214263916016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.006217956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.5605773925781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.6529655456543</t>
+    <t xml:space="preserve">39.8214302062988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.0062141418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.5605735778809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.6529693603516</t>
   </si>
   <si>
     <t xml:space="preserve">41.9464721679688</t>
@@ -1682,22 +1679,22 @@
     <t xml:space="preserve">42.3160438537598</t>
   </si>
   <si>
-    <t xml:space="preserve">43.5171508789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.0715103149414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.8867263793945</t>
+    <t xml:space="preserve">43.5171546936035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.0715141296387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.8867225646973</t>
   </si>
   <si>
     <t xml:space="preserve">43.7019386291504</t>
   </si>
   <si>
-    <t xml:space="preserve">43.979118347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.3486938476562</t>
+    <t xml:space="preserve">43.9791221618652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.348690032959</t>
   </si>
   <si>
     <t xml:space="preserve">44.9954452514648</t>
@@ -1706,43 +1703,43 @@
     <t xml:space="preserve">44.8106575012207</t>
   </si>
   <si>
-    <t xml:space="preserve">44.5334815979004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.7943344116211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.1475791931152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.3921089172363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.8540802001953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.5769004821777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.2073249816895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.1910018920898</t>
+    <t xml:space="preserve">44.5334777832031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.7943382263184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.1475830078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.3921127319336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.854076385498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.5768966674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.2073211669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.1910057067871</t>
   </si>
   <si>
     <t xml:space="preserve">39.4518547058105</t>
   </si>
   <si>
-    <t xml:space="preserve">38.9898910522461</t>
+    <t xml:space="preserve">38.9898948669434</t>
   </si>
   <si>
     <t xml:space="preserve">39.1746788024902</t>
   </si>
   <si>
-    <t xml:space="preserve">39.5442504882812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.7453575134277</t>
+    <t xml:space="preserve">39.5442543029785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.745361328125</t>
   </si>
   <si>
     <t xml:space="preserve">41.0225410461426</t>
@@ -1754,13 +1751,13 @@
     <t xml:space="preserve">39.9138259887695</t>
   </si>
   <si>
-    <t xml:space="preserve">40.4681816101074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.636646270752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.6203193664551</t>
+    <t xml:space="preserve">40.4681854248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.6366424560547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.6203155517578</t>
   </si>
   <si>
     <t xml:space="preserve">39.2670745849609</t>
@@ -1769,16 +1766,16 @@
     <t xml:space="preserve">37.3268165588379</t>
   </si>
   <si>
-    <t xml:space="preserve">38.8974952697754</t>
+    <t xml:space="preserve">38.8974990844727</t>
   </si>
   <si>
     <t xml:space="preserve">37.5116004943848</t>
   </si>
   <si>
-    <t xml:space="preserve">38.712718963623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.0822830200195</t>
+    <t xml:space="preserve">38.7127151489258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.0822868347168</t>
   </si>
   <si>
     <t xml:space="preserve">36.7724571228027</t>
@@ -1790,31 +1787,31 @@
     <t xml:space="preserve">36.2181015014648</t>
   </si>
   <si>
-    <t xml:space="preserve">35.3865661621094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.0333099365234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.1854515075684</t>
+    <t xml:space="preserve">35.3865585327148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.0333137512207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.1854476928711</t>
   </si>
   <si>
     <t xml:space="preserve">33.7234840393066</t>
   </si>
   <si>
-    <t xml:space="preserve">33.1691207885742</t>
+    <t xml:space="preserve">33.1691284179688</t>
   </si>
   <si>
     <t xml:space="preserve">32.6147689819336</t>
   </si>
   <si>
-    <t xml:space="preserve">33.6310997009277</t>
+    <t xml:space="preserve">33.6310920715332</t>
   </si>
   <si>
     <t xml:space="preserve">32.707160949707</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9680156707764</t>
+    <t xml:space="preserve">31.968017578125</t>
   </si>
   <si>
     <t xml:space="preserve">32.0604095458984</t>
@@ -1823,7 +1820,7 @@
     <t xml:space="preserve">31.4136562347412</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6908340454102</t>
+    <t xml:space="preserve">31.6908416748047</t>
   </si>
   <si>
     <t xml:space="preserve">32.2452011108398</t>
@@ -1832,19 +1829,19 @@
     <t xml:space="preserve">32.7995529174805</t>
   </si>
   <si>
-    <t xml:space="preserve">33.908275604248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.1093788146973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7398071289062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.0169868469238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.337589263916</t>
+    <t xml:space="preserve">33.9082679748535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.1093826293945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.739803314209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.0169906616211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3375854492188</t>
   </si>
   <si>
     <t xml:space="preserve">32.4299812316895</t>
@@ -1853,10 +1850,10 @@
     <t xml:space="preserve">32.5223770141602</t>
   </si>
   <si>
-    <t xml:space="preserve">31.506046295166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3212699890137</t>
+    <t xml:space="preserve">31.5060501098633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3212661743164</t>
   </si>
   <si>
     <t xml:space="preserve">31.5522480010986</t>
@@ -1865,7 +1862,7 @@
     <t xml:space="preserve">31.9218196868896</t>
   </si>
   <si>
-    <t xml:space="preserve">32.1528015136719</t>
+    <t xml:space="preserve">32.1527976989746</t>
   </si>
   <si>
     <t xml:space="preserve">33.4925079345703</t>
@@ -1877,37 +1874,37 @@
     <t xml:space="preserve">33.8620719909668</t>
   </si>
   <si>
-    <t xml:space="preserve">32.1066017150879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5359210968018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3511371612549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7804546356201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3643836975098</t>
+    <t xml:space="preserve">32.1066055297852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5359191894531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3511352539062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7804527282715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3643817901611</t>
   </si>
   <si>
     <t xml:space="preserve">28.3180332183838</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8082160949707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7618732452393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0862998962402</t>
+    <t xml:space="preserve">27.8082180023193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7618713378906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0863018035889</t>
   </si>
   <si>
     <t xml:space="preserve">27.9936065673828</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6424655914307</t>
+    <t xml:space="preserve">28.642463684082</t>
   </si>
   <si>
     <t xml:space="preserve">29.5230579376221</t>
@@ -1919,10 +1916,10 @@
     <t xml:space="preserve">29.5694065093994</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1059341430664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.900915145874</t>
+    <t xml:space="preserve">29.105936050415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9009132385254</t>
   </si>
   <si>
     <t xml:space="preserve">27.7155246734619</t>
@@ -1964,19 +1961,19 @@
     <t xml:space="preserve">24.7029666900635</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6566219329834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9614143371582</t>
+    <t xml:space="preserve">24.6566200256348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9614162445068</t>
   </si>
   <si>
     <t xml:space="preserve">23.729679107666</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0273971557617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7956619262695</t>
+    <t xml:space="preserve">25.0273990631104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7956600189209</t>
   </si>
   <si>
     <t xml:space="preserve">24.2858467102051</t>
@@ -1985,10 +1982,10 @@
     <t xml:space="preserve">24.6102714538574</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3321914672852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5175800323486</t>
+    <t xml:space="preserve">24.3321895599365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.517578125</t>
   </si>
   <si>
     <t xml:space="preserve">24.3785362243652</t>
@@ -2003,19 +2000,19 @@
     <t xml:space="preserve">23.5442905426025</t>
   </si>
   <si>
-    <t xml:space="preserve">24.100456237793</t>
+    <t xml:space="preserve">24.1004581451416</t>
   </si>
   <si>
     <t xml:space="preserve">23.4979457855225</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8223743438721</t>
+    <t xml:space="preserve">23.8223762512207</t>
   </si>
   <si>
     <t xml:space="preserve">23.9150676727295</t>
   </si>
   <si>
-    <t xml:space="preserve">24.193151473999</t>
+    <t xml:space="preserve">24.1931495666504</t>
   </si>
   <si>
     <t xml:space="preserve">24.888355255127</t>
@@ -2033,7 +2030,7 @@
     <t xml:space="preserve">26.7885818481445</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7422370910645</t>
+    <t xml:space="preserve">26.7422351837158</t>
   </si>
   <si>
     <t xml:space="preserve">25.4445209503174</t>
@@ -2051,16 +2048,16 @@
     <t xml:space="preserve">24.0077610015869</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4515953063965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1271705627441</t>
+    <t xml:space="preserve">23.4515972137451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1271686553955</t>
   </si>
   <si>
     <t xml:space="preserve">23.0808200836182</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3125553131104</t>
+    <t xml:space="preserve">23.312557220459</t>
   </si>
   <si>
     <t xml:space="preserve">23.6369857788086</t>
@@ -2075,19 +2072,19 @@
     <t xml:space="preserve">23.2662105560303</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3589038848877</t>
+    <t xml:space="preserve">23.3589057922363</t>
   </si>
   <si>
     <t xml:space="preserve">22.8027381896973</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6173515319824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1735153198242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.895435333252</t>
+    <t xml:space="preserve">22.6173496246338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1735134124756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8954334259033</t>
   </si>
   <si>
     <t xml:space="preserve">21.9684944152832</t>
@@ -2096,7 +2093,7 @@
     <t xml:space="preserve">21.5513706207275</t>
   </si>
   <si>
-    <t xml:space="preserve">21.273286819458</t>
+    <t xml:space="preserve">21.2732849121094</t>
   </si>
   <si>
     <t xml:space="preserve">20.856164932251</t>
@@ -2105,7 +2102,7 @@
     <t xml:space="preserve">20.7171230316162</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9755687713623</t>
+    <t xml:space="preserve">19.9755706787109</t>
   </si>
   <si>
     <t xml:space="preserve">20.1609592437744</t>
@@ -2120,7 +2117,7 @@
     <t xml:space="preserve">19.5584487915039</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6047916412354</t>
+    <t xml:space="preserve">19.604793548584</t>
   </si>
   <si>
     <t xml:space="preserve">19.9292221069336</t>
@@ -2132,22 +2129,22 @@
     <t xml:space="preserve">20.1146106719971</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8098182678223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9952049255371</t>
+    <t xml:space="preserve">20.8098163604736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9952030181885</t>
   </si>
   <si>
     <t xml:space="preserve">20.5780830383301</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0879001617432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5977153778076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0611839294434</t>
+    <t xml:space="preserve">21.0878982543945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5977172851562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.061185836792</t>
   </si>
   <si>
     <t xml:space="preserve">22.4319629669189</t>
@@ -2168,7 +2165,7 @@
     <t xml:space="preserve">24.4248867034912</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1664371490479</t>
+    <t xml:space="preserve">25.1664390563965</t>
   </si>
   <si>
     <t xml:space="preserve">25.2127857208252</t>
@@ -2177,7 +2174,7 @@
     <t xml:space="preserve">24.8420085906982</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7689476013184</t>
+    <t xml:space="preserve">25.768949508667</t>
   </si>
   <si>
     <t xml:space="preserve">25.7226028442383</t>
@@ -2189,22 +2186,22 @@
     <t xml:space="preserve">25.5372123718262</t>
   </si>
   <si>
-    <t xml:space="preserve">25.305477142334</t>
+    <t xml:space="preserve">25.3054790496826</t>
   </si>
   <si>
     <t xml:space="preserve">25.6762542724609</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4908657073975</t>
+    <t xml:space="preserve">25.4908676147461</t>
   </si>
   <si>
     <t xml:space="preserve">27.6691780090332</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2057056427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4837894439697</t>
+    <t xml:space="preserve">27.2057075500488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4837913513184</t>
   </si>
   <si>
     <t xml:space="preserve">27.2984027862549</t>
@@ -2213,10 +2210,10 @@
     <t xml:space="preserve">27.5764827728271</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0399551391602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1789951324463</t>
+    <t xml:space="preserve">28.0399532318115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1789932250977</t>
   </si>
   <si>
     <t xml:space="preserve">28.2716884613037</t>
@@ -2255,7 +2252,7 @@
     <t xml:space="preserve">22.9881248474121</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2198619842529</t>
+    <t xml:space="preserve">23.2198638916016</t>
   </si>
   <si>
     <t xml:space="preserve">21.8294506072998</t>
@@ -2279,28 +2276,31 @@
     <t xml:space="preserve">21.1342430114746</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7831039428711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6440620422363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2269420623779</t>
+    <t xml:space="preserve">21.7831058502197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.644063949585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2269401550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3196353912354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8757972717285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1805934906006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9025096893311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6679439544678</t>
   </si>
   <si>
     <t xml:space="preserve">21.3196334838867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8757991790771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1805934906006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9025096893311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6679439544678</t>
   </si>
   <si>
     <t xml:space="preserve">21.4127330780029</t>
@@ -31283,7 +31283,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1075" t="s">
-        <v>363</v>
+        <v>280</v>
       </c>
       <c r="H1075" t="s">
         <v>9</v>
@@ -31907,7 +31907,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G1099" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H1099" t="s">
         <v>9</v>
@@ -32167,7 +32167,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1109" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1109" t="s">
         <v>9</v>
@@ -32323,7 +32323,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1115" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1115" t="s">
         <v>9</v>
@@ -32349,7 +32349,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1116" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1116" t="s">
         <v>9</v>
@@ -32375,7 +32375,7 @@
         <v>15.5</v>
       </c>
       <c r="G1117" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1117" t="s">
         <v>9</v>
@@ -32401,7 +32401,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G1118" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1118" t="s">
         <v>9</v>
@@ -32427,7 +32427,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1119" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1119" t="s">
         <v>9</v>
@@ -32453,7 +32453,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1120" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1120" t="s">
         <v>9</v>
@@ -32479,7 +32479,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1121" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1121" t="s">
         <v>9</v>
@@ -32505,7 +32505,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G1122" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1122" t="s">
         <v>9</v>
@@ -32531,7 +32531,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G1123" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1123" t="s">
         <v>9</v>
@@ -32557,7 +32557,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G1124" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H1124" t="s">
         <v>9</v>
@@ -32583,7 +32583,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1125" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H1125" t="s">
         <v>9</v>
@@ -32609,7 +32609,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1126" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H1126" t="s">
         <v>9</v>
@@ -32635,7 +32635,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G1127" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H1127" t="s">
         <v>9</v>
@@ -32661,7 +32661,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G1128" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H1128" t="s">
         <v>9</v>
@@ -32687,7 +32687,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1129" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H1129" t="s">
         <v>9</v>
@@ -32713,7 +32713,7 @@
         <v>15</v>
       </c>
       <c r="G1130" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H1130" t="s">
         <v>9</v>
@@ -32739,7 +32739,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G1131" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H1131" t="s">
         <v>9</v>
@@ -32765,7 +32765,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1132" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H1132" t="s">
         <v>9</v>
@@ -32791,7 +32791,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1133" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H1133" t="s">
         <v>9</v>
@@ -32817,7 +32817,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1134" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H1134" t="s">
         <v>9</v>
@@ -32843,7 +32843,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1135" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H1135" t="s">
         <v>9</v>
@@ -32869,7 +32869,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1136" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H1136" t="s">
         <v>9</v>
@@ -32895,7 +32895,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1137" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H1137" t="s">
         <v>9</v>
@@ -32921,7 +32921,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1138" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H1138" t="s">
         <v>9</v>
@@ -32947,7 +32947,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G1139" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H1139" t="s">
         <v>9</v>
@@ -32973,7 +32973,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G1140" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H1140" t="s">
         <v>9</v>
@@ -32999,7 +32999,7 @@
         <v>15</v>
       </c>
       <c r="G1141" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H1141" t="s">
         <v>9</v>
@@ -33025,7 +33025,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1142" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="H1142" t="s">
         <v>9</v>
@@ -33441,7 +33441,7 @@
         <v>15</v>
       </c>
       <c r="G1158" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H1158" t="s">
         <v>9</v>
@@ -33727,7 +33727,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1169" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H1169" t="s">
         <v>9</v>
@@ -33779,7 +33779,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1171" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H1171" t="s">
         <v>9</v>
@@ -33831,7 +33831,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G1173" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H1173" t="s">
         <v>9</v>
@@ -36795,7 +36795,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G1287" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="H1287" t="s">
         <v>9</v>
@@ -36821,7 +36821,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1288" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H1288" t="s">
         <v>9</v>
@@ -36873,7 +36873,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G1290" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H1290" t="s">
         <v>9</v>
@@ -36899,7 +36899,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G1291" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1291" t="s">
         <v>9</v>
@@ -36925,7 +36925,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G1292" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1292" t="s">
         <v>9</v>
@@ -36951,7 +36951,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G1293" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1293" t="s">
         <v>9</v>
@@ -36977,7 +36977,7 @@
         <v>24.5</v>
       </c>
       <c r="G1294" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1294" t="s">
         <v>9</v>
@@ -37003,7 +37003,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G1295" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1295" t="s">
         <v>9</v>
@@ -37029,7 +37029,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G1296" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1296" t="s">
         <v>9</v>
@@ -37055,7 +37055,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G1297" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1297" t="s">
         <v>9</v>
@@ -37081,7 +37081,7 @@
         <v>24</v>
       </c>
       <c r="G1298" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1298" t="s">
         <v>9</v>
@@ -37107,7 +37107,7 @@
         <v>24</v>
       </c>
       <c r="G1299" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1299" t="s">
         <v>9</v>
@@ -37133,7 +37133,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1300" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1300" t="s">
         <v>9</v>
@@ -37159,7 +37159,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G1301" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H1301" t="s">
         <v>9</v>
@@ -37185,7 +37185,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G1302" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H1302" t="s">
         <v>9</v>
@@ -37211,7 +37211,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G1303" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H1303" t="s">
         <v>9</v>
@@ -37237,7 +37237,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1304" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1304" t="s">
         <v>9</v>
@@ -37263,7 +37263,7 @@
         <v>24</v>
       </c>
       <c r="G1305" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1305" t="s">
         <v>9</v>
@@ -37289,7 +37289,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G1306" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1306" t="s">
         <v>9</v>
@@ -37315,7 +37315,7 @@
         <v>25</v>
       </c>
       <c r="G1307" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H1307" t="s">
         <v>9</v>
@@ -37341,7 +37341,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G1308" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1308" t="s">
         <v>9</v>
@@ -37367,7 +37367,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G1309" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1309" t="s">
         <v>9</v>
@@ -37393,7 +37393,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G1310" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1310" t="s">
         <v>9</v>
@@ -37419,7 +37419,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G1311" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1311" t="s">
         <v>9</v>
@@ -37445,7 +37445,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G1312" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1312" t="s">
         <v>9</v>
@@ -37471,7 +37471,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G1313" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H1313" t="s">
         <v>9</v>
@@ -37497,7 +37497,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G1314" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1314" t="s">
         <v>9</v>
@@ -37523,7 +37523,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G1315" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1315" t="s">
         <v>9</v>
@@ -37549,7 +37549,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G1316" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1316" t="s">
         <v>9</v>
@@ -37575,7 +37575,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G1317" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1317" t="s">
         <v>9</v>
@@ -37601,7 +37601,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G1318" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H1318" t="s">
         <v>9</v>
@@ -37627,7 +37627,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G1319" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1319" t="s">
         <v>9</v>
@@ -37653,7 +37653,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G1320" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1320" t="s">
         <v>9</v>
@@ -37679,7 +37679,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G1321" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1321" t="s">
         <v>9</v>
@@ -37705,7 +37705,7 @@
         <v>24.5</v>
       </c>
       <c r="G1322" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1322" t="s">
         <v>9</v>
@@ -37731,7 +37731,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G1323" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H1323" t="s">
         <v>9</v>
@@ -37757,7 +37757,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G1324" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H1324" t="s">
         <v>9</v>
@@ -37783,7 +37783,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G1325" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1325" t="s">
         <v>9</v>
@@ -37809,7 +37809,7 @@
         <v>26.5</v>
       </c>
       <c r="G1326" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H1326" t="s">
         <v>9</v>
@@ -37835,7 +37835,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1327" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H1327" t="s">
         <v>9</v>
@@ -37861,7 +37861,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1328" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H1328" t="s">
         <v>9</v>
@@ -37887,7 +37887,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G1329" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H1329" t="s">
         <v>9</v>
@@ -37913,7 +37913,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1330" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H1330" t="s">
         <v>9</v>
@@ -37939,7 +37939,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G1331" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H1331" t="s">
         <v>9</v>
@@ -37965,7 +37965,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1332" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H1332" t="s">
         <v>9</v>
@@ -37991,7 +37991,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1333" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H1333" t="s">
         <v>9</v>
@@ -38017,7 +38017,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1334" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H1334" t="s">
         <v>9</v>
@@ -38043,7 +38043,7 @@
         <v>29</v>
       </c>
       <c r="G1335" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H1335" t="s">
         <v>9</v>
@@ -38069,7 +38069,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1336" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H1336" t="s">
         <v>9</v>
@@ -38095,7 +38095,7 @@
         <v>29</v>
       </c>
       <c r="G1337" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H1337" t="s">
         <v>9</v>
@@ -38121,7 +38121,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1338" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H1338" t="s">
         <v>9</v>
@@ -38147,7 +38147,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G1339" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H1339" t="s">
         <v>9</v>
@@ -38173,7 +38173,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1340" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H1340" t="s">
         <v>9</v>
@@ -38199,7 +38199,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1341" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H1341" t="s">
         <v>9</v>
@@ -38225,7 +38225,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1342" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H1342" t="s">
         <v>9</v>
@@ -38251,7 +38251,7 @@
         <v>29.5</v>
       </c>
       <c r="G1343" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H1343" t="s">
         <v>9</v>
@@ -38277,7 +38277,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G1344" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H1344" t="s">
         <v>9</v>
@@ -38303,7 +38303,7 @@
         <v>31</v>
       </c>
       <c r="G1345" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H1345" t="s">
         <v>9</v>
@@ -38329,7 +38329,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G1346" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H1346" t="s">
         <v>9</v>
@@ -38355,7 +38355,7 @@
         <v>31</v>
       </c>
       <c r="G1347" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H1347" t="s">
         <v>9</v>
@@ -38381,7 +38381,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G1348" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H1348" t="s">
         <v>9</v>
@@ -38407,7 +38407,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G1349" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H1349" t="s">
         <v>9</v>
@@ -38433,7 +38433,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G1350" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H1350" t="s">
         <v>9</v>
@@ -38459,7 +38459,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G1351" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1351" t="s">
         <v>9</v>
@@ -38485,7 +38485,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G1352" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1352" t="s">
         <v>9</v>
@@ -38511,7 +38511,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1353" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H1353" t="s">
         <v>9</v>
@@ -38537,7 +38537,7 @@
         <v>30</v>
       </c>
       <c r="G1354" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H1354" t="s">
         <v>9</v>
@@ -38563,7 +38563,7 @@
         <v>30</v>
       </c>
       <c r="G1355" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H1355" t="s">
         <v>9</v>
@@ -38589,7 +38589,7 @@
         <v>31.5</v>
       </c>
       <c r="G1356" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H1356" t="s">
         <v>9</v>
@@ -38615,7 +38615,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G1357" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1357" t="s">
         <v>9</v>
@@ -38641,7 +38641,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1358" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H1358" t="s">
         <v>9</v>
@@ -38667,7 +38667,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G1359" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H1359" t="s">
         <v>9</v>
@@ -38693,7 +38693,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G1360" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H1360" t="s">
         <v>9</v>
@@ -38719,7 +38719,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G1361" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H1361" t="s">
         <v>9</v>
@@ -38745,7 +38745,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1362" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H1362" t="s">
         <v>9</v>
@@ -38771,7 +38771,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G1363" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H1363" t="s">
         <v>9</v>
@@ -38797,7 +38797,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1364" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H1364" t="s">
         <v>9</v>
@@ -38823,7 +38823,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G1365" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H1365" t="s">
         <v>9</v>
@@ -38849,7 +38849,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G1366" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H1366" t="s">
         <v>9</v>
@@ -38875,7 +38875,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G1367" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H1367" t="s">
         <v>9</v>
@@ -38901,7 +38901,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1368" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H1368" t="s">
         <v>9</v>
@@ -38927,7 +38927,7 @@
         <v>32.5</v>
       </c>
       <c r="G1369" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H1369" t="s">
         <v>9</v>
@@ -38953,7 +38953,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G1370" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H1370" t="s">
         <v>9</v>
@@ -38979,7 +38979,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G1371" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H1371" t="s">
         <v>9</v>
@@ -39005,7 +39005,7 @@
         <v>33.7000007629395</v>
       </c>
       <c r="G1372" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H1372" t="s">
         <v>9</v>
@@ -39031,7 +39031,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G1373" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H1373" t="s">
         <v>9</v>
@@ -39057,7 +39057,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G1374" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H1374" t="s">
         <v>9</v>
@@ -39083,7 +39083,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1375" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H1375" t="s">
         <v>9</v>
@@ -39109,7 +39109,7 @@
         <v>33</v>
       </c>
       <c r="G1376" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H1376" t="s">
         <v>9</v>
@@ -39135,7 +39135,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1377" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H1377" t="s">
         <v>9</v>
@@ -39161,7 +39161,7 @@
         <v>32.5</v>
       </c>
       <c r="G1378" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H1378" t="s">
         <v>9</v>
@@ -39187,7 +39187,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G1379" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1379" t="s">
         <v>9</v>
@@ -39213,7 +39213,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G1380" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1380" t="s">
         <v>9</v>
@@ -39239,7 +39239,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G1381" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1381" t="s">
         <v>9</v>
@@ -39265,7 +39265,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G1382" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H1382" t="s">
         <v>9</v>
@@ -39291,7 +39291,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1383" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H1383" t="s">
         <v>9</v>
@@ -39317,7 +39317,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G1384" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H1384" t="s">
         <v>9</v>
@@ -39343,7 +39343,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G1385" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1385" t="s">
         <v>9</v>
@@ -39369,7 +39369,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G1386" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1386" t="s">
         <v>9</v>
@@ -39395,7 +39395,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G1387" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H1387" t="s">
         <v>9</v>
@@ -39421,7 +39421,7 @@
         <v>35.5999984741211</v>
       </c>
       <c r="G1388" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H1388" t="s">
         <v>9</v>
@@ -39447,7 +39447,7 @@
         <v>36.0999984741211</v>
       </c>
       <c r="G1389" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H1389" t="s">
         <v>9</v>
@@ -39473,7 +39473,7 @@
         <v>37.4000015258789</v>
       </c>
       <c r="G1390" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="H1390" t="s">
         <v>9</v>
@@ -39499,7 +39499,7 @@
         <v>36.9000015258789</v>
       </c>
       <c r="G1391" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="H1391" t="s">
         <v>9</v>
@@ -39525,7 +39525,7 @@
         <v>38.7999992370605</v>
       </c>
       <c r="G1392" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="H1392" t="s">
         <v>9</v>
@@ -39551,7 +39551,7 @@
         <v>40.5</v>
       </c>
       <c r="G1393" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H1393" t="s">
         <v>9</v>
@@ -39577,7 +39577,7 @@
         <v>43.4000015258789</v>
       </c>
       <c r="G1394" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H1394" t="s">
         <v>9</v>
@@ -39603,7 +39603,7 @@
         <v>40.2999992370605</v>
       </c>
       <c r="G1395" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H1395" t="s">
         <v>9</v>
@@ -39629,7 +39629,7 @@
         <v>41</v>
       </c>
       <c r="G1396" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H1396" t="s">
         <v>9</v>
@@ -39655,7 +39655,7 @@
         <v>41.2999992370605</v>
       </c>
       <c r="G1397" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H1397" t="s">
         <v>9</v>
@@ -39681,7 +39681,7 @@
         <v>40.7000007629395</v>
       </c>
       <c r="G1398" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H1398" t="s">
         <v>9</v>
@@ -39707,7 +39707,7 @@
         <v>40.5</v>
       </c>
       <c r="G1399" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H1399" t="s">
         <v>9</v>
@@ -39733,7 +39733,7 @@
         <v>41</v>
       </c>
       <c r="G1400" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H1400" t="s">
         <v>9</v>
@@ -39759,7 +39759,7 @@
         <v>40.7999992370605</v>
       </c>
       <c r="G1401" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H1401" t="s">
         <v>9</v>
@@ -39785,7 +39785,7 @@
         <v>40.9000015258789</v>
       </c>
       <c r="G1402" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H1402" t="s">
         <v>9</v>
@@ -39811,7 +39811,7 @@
         <v>40.2000007629395</v>
       </c>
       <c r="G1403" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H1403" t="s">
         <v>9</v>
@@ -39837,7 +39837,7 @@
         <v>40.9000015258789</v>
       </c>
       <c r="G1404" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H1404" t="s">
         <v>9</v>
@@ -39863,7 +39863,7 @@
         <v>41.7000007629395</v>
       </c>
       <c r="G1405" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H1405" t="s">
         <v>9</v>
@@ -39889,7 +39889,7 @@
         <v>41.5</v>
       </c>
       <c r="G1406" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H1406" t="s">
         <v>9</v>
@@ -39915,7 +39915,7 @@
         <v>40.7000007629395</v>
       </c>
       <c r="G1407" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H1407" t="s">
         <v>9</v>
@@ -39941,7 +39941,7 @@
         <v>39.5</v>
       </c>
       <c r="G1408" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H1408" t="s">
         <v>9</v>
@@ -39967,7 +39967,7 @@
         <v>38.9000015258789</v>
       </c>
       <c r="G1409" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H1409" t="s">
         <v>9</v>
@@ -39993,7 +39993,7 @@
         <v>39.4000015258789</v>
       </c>
       <c r="G1410" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H1410" t="s">
         <v>9</v>
@@ -40019,7 +40019,7 @@
         <v>39.7000007629395</v>
       </c>
       <c r="G1411" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1411" t="s">
         <v>9</v>
@@ -40045,7 +40045,7 @@
         <v>40.9000015258789</v>
       </c>
       <c r="G1412" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H1412" t="s">
         <v>9</v>
@@ -40071,7 +40071,7 @@
         <v>41.0999984741211</v>
       </c>
       <c r="G1413" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H1413" t="s">
         <v>9</v>
@@ -40097,7 +40097,7 @@
         <v>41.2000007629395</v>
       </c>
       <c r="G1414" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H1414" t="s">
         <v>9</v>
@@ -40123,7 +40123,7 @@
         <v>41.2000007629395</v>
       </c>
       <c r="G1415" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H1415" t="s">
         <v>9</v>
@@ -40149,7 +40149,7 @@
         <v>40.2999992370605</v>
       </c>
       <c r="G1416" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H1416" t="s">
         <v>9</v>
@@ -40175,7 +40175,7 @@
         <v>41.0999984741211</v>
       </c>
       <c r="G1417" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H1417" t="s">
         <v>9</v>
@@ -40201,7 +40201,7 @@
         <v>41.2000007629395</v>
       </c>
       <c r="G1418" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H1418" t="s">
         <v>9</v>
@@ -40227,7 +40227,7 @@
         <v>41.0999984741211</v>
       </c>
       <c r="G1419" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H1419" t="s">
         <v>9</v>
@@ -40253,7 +40253,7 @@
         <v>40.7999992370605</v>
       </c>
       <c r="G1420" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H1420" t="s">
         <v>9</v>
@@ -40279,7 +40279,7 @@
         <v>41.0999984741211</v>
       </c>
       <c r="G1421" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H1421" t="s">
         <v>9</v>
@@ -40305,7 +40305,7 @@
         <v>41</v>
       </c>
       <c r="G1422" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H1422" t="s">
         <v>9</v>
@@ -40331,7 +40331,7 @@
         <v>41.5999984741211</v>
       </c>
       <c r="G1423" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H1423" t="s">
         <v>9</v>
@@ -40357,7 +40357,7 @@
         <v>42</v>
       </c>
       <c r="G1424" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H1424" t="s">
         <v>9</v>
@@ -40383,7 +40383,7 @@
         <v>42.5999984741211</v>
       </c>
       <c r="G1425" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H1425" t="s">
         <v>9</v>
@@ -40409,7 +40409,7 @@
         <v>43.0999984741211</v>
       </c>
       <c r="G1426" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H1426" t="s">
         <v>9</v>
@@ -40435,7 +40435,7 @@
         <v>43.2999992370605</v>
       </c>
       <c r="G1427" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H1427" t="s">
         <v>9</v>
@@ -40461,7 +40461,7 @@
         <v>43.9000015258789</v>
       </c>
       <c r="G1428" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H1428" t="s">
         <v>9</v>
@@ -40487,7 +40487,7 @@
         <v>44</v>
       </c>
       <c r="G1429" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="H1429" t="s">
         <v>9</v>
@@ -40513,7 +40513,7 @@
         <v>44</v>
       </c>
       <c r="G1430" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="H1430" t="s">
         <v>9</v>
@@ -40539,7 +40539,7 @@
         <v>45.4000015258789</v>
       </c>
       <c r="G1431" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H1431" t="s">
         <v>9</v>
@@ -40565,7 +40565,7 @@
         <v>44.5</v>
       </c>
       <c r="G1432" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H1432" t="s">
         <v>9</v>
@@ -40591,7 +40591,7 @@
         <v>44.2999992370605</v>
       </c>
       <c r="G1433" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="H1433" t="s">
         <v>9</v>
@@ -40617,7 +40617,7 @@
         <v>45.7999992370605</v>
       </c>
       <c r="G1434" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H1434" t="s">
         <v>9</v>
@@ -40643,7 +40643,7 @@
         <v>47.0999984741211</v>
       </c>
       <c r="G1435" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H1435" t="s">
         <v>9</v>
@@ -40669,7 +40669,7 @@
         <v>47.7000007629395</v>
       </c>
       <c r="G1436" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="H1436" t="s">
         <v>9</v>
@@ -40695,7 +40695,7 @@
         <v>47.5</v>
       </c>
       <c r="G1437" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="H1437" t="s">
         <v>9</v>
@@ -40721,7 +40721,7 @@
         <v>47.2999992370605</v>
       </c>
       <c r="G1438" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H1438" t="s">
         <v>9</v>
@@ -40747,7 +40747,7 @@
         <v>47.5999984741211</v>
       </c>
       <c r="G1439" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H1439" t="s">
         <v>9</v>
@@ -40773,7 +40773,7 @@
         <v>47.2999992370605</v>
       </c>
       <c r="G1440" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H1440" t="s">
         <v>9</v>
@@ -40799,7 +40799,7 @@
         <v>47.5</v>
       </c>
       <c r="G1441" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="H1441" t="s">
         <v>9</v>
@@ -40825,7 +40825,7 @@
         <v>48</v>
       </c>
       <c r="G1442" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="H1442" t="s">
         <v>9</v>
@@ -40851,7 +40851,7 @@
         <v>48</v>
       </c>
       <c r="G1443" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="H1443" t="s">
         <v>9</v>
@@ -40877,7 +40877,7 @@
         <v>48.7000007629395</v>
       </c>
       <c r="G1444" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H1444" t="s">
         <v>9</v>
@@ -40903,7 +40903,7 @@
         <v>48.5</v>
       </c>
       <c r="G1445" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H1445" t="s">
         <v>9</v>
@@ -40929,7 +40929,7 @@
         <v>48.2000007629395</v>
       </c>
       <c r="G1446" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H1446" t="s">
         <v>9</v>
@@ -40955,7 +40955,7 @@
         <v>47.5999984741211</v>
       </c>
       <c r="G1447" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H1447" t="s">
         <v>9</v>
@@ -40981,7 +40981,7 @@
         <v>47.4000015258789</v>
       </c>
       <c r="G1448" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H1448" t="s">
         <v>9</v>
@@ -41007,7 +41007,7 @@
         <v>46.7000007629395</v>
       </c>
       <c r="G1449" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H1449" t="s">
         <v>9</v>
@@ -41033,7 +41033,7 @@
         <v>48</v>
       </c>
       <c r="G1450" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="H1450" t="s">
         <v>9</v>
@@ -41059,7 +41059,7 @@
         <v>46.7000007629395</v>
       </c>
       <c r="G1451" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H1451" t="s">
         <v>9</v>
@@ -41085,7 +41085,7 @@
         <v>45.7999992370605</v>
       </c>
       <c r="G1452" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H1452" t="s">
         <v>9</v>
@@ -41111,7 +41111,7 @@
         <v>44.7999992370605</v>
       </c>
       <c r="G1453" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H1453" t="s">
         <v>9</v>
@@ -41137,7 +41137,7 @@
         <v>44.7999992370605</v>
       </c>
       <c r="G1454" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H1454" t="s">
         <v>9</v>
@@ -41163,7 +41163,7 @@
         <v>45.2999992370605</v>
       </c>
       <c r="G1455" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H1455" t="s">
         <v>9</v>
@@ -41189,7 +41189,7 @@
         <v>45.2999992370605</v>
       </c>
       <c r="G1456" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H1456" t="s">
         <v>9</v>
@@ -41215,7 +41215,7 @@
         <v>45.2999992370605</v>
       </c>
       <c r="G1457" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H1457" t="s">
         <v>9</v>
@@ -41241,7 +41241,7 @@
         <v>45</v>
       </c>
       <c r="G1458" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="H1458" t="s">
         <v>9</v>
@@ -41267,7 +41267,7 @@
         <v>44.5999984741211</v>
       </c>
       <c r="G1459" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H1459" t="s">
         <v>9</v>
@@ -41293,7 +41293,7 @@
         <v>43.5</v>
       </c>
       <c r="G1460" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H1460" t="s">
         <v>9</v>
@@ -41319,7 +41319,7 @@
         <v>41.5</v>
       </c>
       <c r="G1461" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H1461" t="s">
         <v>9</v>
@@ -41345,7 +41345,7 @@
         <v>40.9000015258789</v>
       </c>
       <c r="G1462" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H1462" t="s">
         <v>9</v>
@@ -41371,7 +41371,7 @@
         <v>40.2999992370605</v>
       </c>
       <c r="G1463" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H1463" t="s">
         <v>9</v>
@@ -41397,7 +41397,7 @@
         <v>41.5</v>
       </c>
       <c r="G1464" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H1464" t="s">
         <v>9</v>
@@ -41423,7 +41423,7 @@
         <v>42.7000007629395</v>
       </c>
       <c r="G1465" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="H1465" t="s">
         <v>9</v>
@@ -41449,7 +41449,7 @@
         <v>42</v>
       </c>
       <c r="G1466" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H1466" t="s">
         <v>9</v>
@@ -41475,7 +41475,7 @@
         <v>41.5999984741211</v>
       </c>
       <c r="G1467" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H1467" t="s">
         <v>9</v>
@@ -41501,7 +41501,7 @@
         <v>42.2000007629395</v>
       </c>
       <c r="G1468" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H1468" t="s">
         <v>9</v>
@@ -41527,7 +41527,7 @@
         <v>42.5999984741211</v>
       </c>
       <c r="G1469" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H1469" t="s">
         <v>9</v>
@@ -41553,7 +41553,7 @@
         <v>42.4000015258789</v>
       </c>
       <c r="G1470" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H1470" t="s">
         <v>9</v>
@@ -41579,7 +41579,7 @@
         <v>42.4000015258789</v>
       </c>
       <c r="G1471" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H1471" t="s">
         <v>9</v>
@@ -41605,7 +41605,7 @@
         <v>42.7999992370605</v>
       </c>
       <c r="G1472" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H1472" t="s">
         <v>9</v>
@@ -41631,7 +41631,7 @@
         <v>43.0999984741211</v>
       </c>
       <c r="G1473" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H1473" t="s">
         <v>9</v>
@@ -41657,7 +41657,7 @@
         <v>43.5</v>
       </c>
       <c r="G1474" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H1474" t="s">
         <v>9</v>
@@ -41683,7 +41683,7 @@
         <v>44.0999984741211</v>
       </c>
       <c r="G1475" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H1475" t="s">
         <v>9</v>
@@ -41709,7 +41709,7 @@
         <v>44.4000015258789</v>
       </c>
       <c r="G1476" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H1476" t="s">
         <v>9</v>
@@ -41735,7 +41735,7 @@
         <v>44.0999984741211</v>
       </c>
       <c r="G1477" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H1477" t="s">
         <v>9</v>
@@ -41761,7 +41761,7 @@
         <v>44.5</v>
       </c>
       <c r="G1478" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H1478" t="s">
         <v>9</v>
@@ -41787,7 +41787,7 @@
         <v>44.5999984741211</v>
       </c>
       <c r="G1479" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H1479" t="s">
         <v>9</v>
@@ -41813,7 +41813,7 @@
         <v>44.0999984741211</v>
       </c>
       <c r="G1480" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H1480" t="s">
         <v>9</v>
@@ -41839,7 +41839,7 @@
         <v>42.5999984741211</v>
       </c>
       <c r="G1481" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H1481" t="s">
         <v>9</v>
@@ -41865,7 +41865,7 @@
         <v>42.5999984741211</v>
       </c>
       <c r="G1482" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H1482" t="s">
         <v>9</v>
@@ -41891,7 +41891,7 @@
         <v>42.5999984741211</v>
       </c>
       <c r="G1483" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H1483" t="s">
         <v>9</v>
@@ -41917,7 +41917,7 @@
         <v>42.7999992370605</v>
       </c>
       <c r="G1484" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H1484" t="s">
         <v>9</v>
@@ -41943,7 +41943,7 @@
         <v>43</v>
       </c>
       <c r="G1485" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H1485" t="s">
         <v>9</v>
@@ -41969,7 +41969,7 @@
         <v>43.2000007629395</v>
       </c>
       <c r="G1486" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H1486" t="s">
         <v>9</v>
@@ -41995,7 +41995,7 @@
         <v>43.2000007629395</v>
       </c>
       <c r="G1487" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H1487" t="s">
         <v>9</v>
@@ -42021,7 +42021,7 @@
         <v>43.7999992370605</v>
       </c>
       <c r="G1488" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H1488" t="s">
         <v>9</v>
@@ -42047,7 +42047,7 @@
         <v>44.2999992370605</v>
       </c>
       <c r="G1489" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="H1489" t="s">
         <v>9</v>
@@ -42073,7 +42073,7 @@
         <v>44.4000015258789</v>
       </c>
       <c r="G1490" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H1490" t="s">
         <v>9</v>
@@ -42099,7 +42099,7 @@
         <v>43.2000007629395</v>
       </c>
       <c r="G1491" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H1491" t="s">
         <v>9</v>
@@ -42125,7 +42125,7 @@
         <v>43.0999984741211</v>
       </c>
       <c r="G1492" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H1492" t="s">
         <v>9</v>
@@ -42151,7 +42151,7 @@
         <v>42.5999984741211</v>
       </c>
       <c r="G1493" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H1493" t="s">
         <v>9</v>
@@ -42177,7 +42177,7 @@
         <v>43</v>
       </c>
       <c r="G1494" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H1494" t="s">
         <v>9</v>
@@ -42203,7 +42203,7 @@
         <v>42.9000015258789</v>
       </c>
       <c r="G1495" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H1495" t="s">
         <v>9</v>
@@ -42229,7 +42229,7 @@
         <v>43.0999984741211</v>
       </c>
       <c r="G1496" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H1496" t="s">
         <v>9</v>
@@ -42255,7 +42255,7 @@
         <v>43</v>
       </c>
       <c r="G1497" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H1497" t="s">
         <v>9</v>
@@ -42281,7 +42281,7 @@
         <v>42.7999992370605</v>
       </c>
       <c r="G1498" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H1498" t="s">
         <v>9</v>
@@ -42307,7 +42307,7 @@
         <v>42.5999984741211</v>
       </c>
       <c r="G1499" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H1499" t="s">
         <v>9</v>
@@ -42333,7 +42333,7 @@
         <v>43.5</v>
       </c>
       <c r="G1500" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H1500" t="s">
         <v>9</v>
@@ -42359,7 +42359,7 @@
         <v>43.0999984741211</v>
       </c>
       <c r="G1501" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H1501" t="s">
         <v>9</v>
@@ -42385,7 +42385,7 @@
         <v>41.7999992370605</v>
       </c>
       <c r="G1502" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H1502" t="s">
         <v>9</v>
@@ -42411,7 +42411,7 @@
         <v>43</v>
       </c>
       <c r="G1503" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H1503" t="s">
         <v>9</v>
@@ -42437,7 +42437,7 @@
         <v>42.5</v>
       </c>
       <c r="G1504" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H1504" t="s">
         <v>9</v>
@@ -42463,7 +42463,7 @@
         <v>43.2000007629395</v>
       </c>
       <c r="G1505" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H1505" t="s">
         <v>9</v>
@@ -42489,7 +42489,7 @@
         <v>42.9000015258789</v>
       </c>
       <c r="G1506" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H1506" t="s">
         <v>9</v>
@@ -42515,7 +42515,7 @@
         <v>42.9000015258789</v>
       </c>
       <c r="G1507" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H1507" t="s">
         <v>9</v>
@@ -42541,7 +42541,7 @@
         <v>42.7000007629395</v>
       </c>
       <c r="G1508" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="H1508" t="s">
         <v>9</v>
@@ -42567,7 +42567,7 @@
         <v>42.5999984741211</v>
       </c>
       <c r="G1509" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H1509" t="s">
         <v>9</v>
@@ -42593,7 +42593,7 @@
         <v>43.2000007629395</v>
       </c>
       <c r="G1510" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H1510" t="s">
         <v>9</v>
@@ -42619,7 +42619,7 @@
         <v>42.5</v>
       </c>
       <c r="G1511" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H1511" t="s">
         <v>9</v>
@@ -42645,7 +42645,7 @@
         <v>43</v>
       </c>
       <c r="G1512" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H1512" t="s">
         <v>9</v>
@@ -42671,7 +42671,7 @@
         <v>42.5999984741211</v>
       </c>
       <c r="G1513" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H1513" t="s">
         <v>9</v>
@@ -42697,7 +42697,7 @@
         <v>41.5</v>
       </c>
       <c r="G1514" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H1514" t="s">
         <v>9</v>
@@ -42723,7 +42723,7 @@
         <v>41.2999992370605</v>
       </c>
       <c r="G1515" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H1515" t="s">
         <v>9</v>
@@ -42749,7 +42749,7 @@
         <v>41.2999992370605</v>
       </c>
       <c r="G1516" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H1516" t="s">
         <v>9</v>
@@ -42775,7 +42775,7 @@
         <v>40.7999992370605</v>
       </c>
       <c r="G1517" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H1517" t="s">
         <v>9</v>
@@ -42801,7 +42801,7 @@
         <v>41.2999992370605</v>
       </c>
       <c r="G1518" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H1518" t="s">
         <v>9</v>
@@ -42827,7 +42827,7 @@
         <v>41.5</v>
       </c>
       <c r="G1519" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H1519" t="s">
         <v>9</v>
@@ -42853,7 +42853,7 @@
         <v>40.5</v>
       </c>
       <c r="G1520" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H1520" t="s">
         <v>9</v>
@@ -42879,7 +42879,7 @@
         <v>40.4000015258789</v>
       </c>
       <c r="G1521" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H1521" t="s">
         <v>9</v>
@@ -42905,7 +42905,7 @@
         <v>40.4000015258789</v>
       </c>
       <c r="G1522" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H1522" t="s">
         <v>9</v>
@@ -42931,7 +42931,7 @@
         <v>40.5</v>
       </c>
       <c r="G1523" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H1523" t="s">
         <v>9</v>
@@ -42957,7 +42957,7 @@
         <v>40.5</v>
       </c>
       <c r="G1524" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H1524" t="s">
         <v>9</v>
@@ -42983,7 +42983,7 @@
         <v>41</v>
       </c>
       <c r="G1525" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H1525" t="s">
         <v>9</v>
@@ -43009,7 +43009,7 @@
         <v>41.5</v>
       </c>
       <c r="G1526" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H1526" t="s">
         <v>9</v>
@@ -43035,7 +43035,7 @@
         <v>42.5999984741211</v>
       </c>
       <c r="G1527" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H1527" t="s">
         <v>9</v>
@@ -43061,7 +43061,7 @@
         <v>42.4000015258789</v>
       </c>
       <c r="G1528" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H1528" t="s">
         <v>9</v>
@@ -43087,7 +43087,7 @@
         <v>42.0999984741211</v>
       </c>
       <c r="G1529" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H1529" t="s">
         <v>9</v>
@@ -43113,7 +43113,7 @@
         <v>41.2999992370605</v>
       </c>
       <c r="G1530" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H1530" t="s">
         <v>9</v>
@@ -43139,7 +43139,7 @@
         <v>41.7999992370605</v>
       </c>
       <c r="G1531" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H1531" t="s">
         <v>9</v>
@@ -43165,7 +43165,7 @@
         <v>40.5</v>
       </c>
       <c r="G1532" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H1532" t="s">
         <v>9</v>
@@ -43191,7 +43191,7 @@
         <v>40.5999984741211</v>
       </c>
       <c r="G1533" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H1533" t="s">
         <v>9</v>
@@ -43217,7 +43217,7 @@
         <v>42.5999984741211</v>
       </c>
       <c r="G1534" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H1534" t="s">
         <v>9</v>
@@ -43243,7 +43243,7 @@
         <v>41.5999984741211</v>
       </c>
       <c r="G1535" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H1535" t="s">
         <v>9</v>
@@ -43269,7 +43269,7 @@
         <v>41.5</v>
       </c>
       <c r="G1536" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H1536" t="s">
         <v>9</v>
@@ -43295,7 +43295,7 @@
         <v>42.5999984741211</v>
       </c>
       <c r="G1537" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H1537" t="s">
         <v>9</v>
@@ -43321,7 +43321,7 @@
         <v>42.7000007629395</v>
       </c>
       <c r="G1538" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="H1538" t="s">
         <v>9</v>
@@ -43347,7 +43347,7 @@
         <v>42.5</v>
       </c>
       <c r="G1539" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H1539" t="s">
         <v>9</v>
@@ -43373,7 +43373,7 @@
         <v>41.9000015258789</v>
       </c>
       <c r="G1540" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H1540" t="s">
         <v>9</v>
@@ -43399,7 +43399,7 @@
         <v>42.2999992370605</v>
       </c>
       <c r="G1541" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H1541" t="s">
         <v>9</v>
@@ -43425,7 +43425,7 @@
         <v>40.2000007629395</v>
       </c>
       <c r="G1542" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H1542" t="s">
         <v>9</v>
@@ -43451,7 +43451,7 @@
         <v>40.4000015258789</v>
       </c>
       <c r="G1543" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H1543" t="s">
         <v>9</v>
@@ -43477,7 +43477,7 @@
         <v>40.5</v>
       </c>
       <c r="G1544" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H1544" t="s">
         <v>9</v>
@@ -43503,7 +43503,7 @@
         <v>40.5</v>
       </c>
       <c r="G1545" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H1545" t="s">
         <v>9</v>
@@ -43529,7 +43529,7 @@
         <v>40.2999992370605</v>
       </c>
       <c r="G1546" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H1546" t="s">
         <v>9</v>
@@ -43555,7 +43555,7 @@
         <v>42</v>
       </c>
       <c r="G1547" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H1547" t="s">
         <v>9</v>
@@ -43581,7 +43581,7 @@
         <v>41.7999992370605</v>
       </c>
       <c r="G1548" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H1548" t="s">
         <v>9</v>
@@ -43607,7 +43607,7 @@
         <v>41.5999984741211</v>
       </c>
       <c r="G1549" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H1549" t="s">
         <v>9</v>
@@ -43633,7 +43633,7 @@
         <v>41.5</v>
       </c>
       <c r="G1550" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H1550" t="s">
         <v>9</v>
@@ -43659,7 +43659,7 @@
         <v>41.2999992370605</v>
       </c>
       <c r="G1551" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H1551" t="s">
         <v>9</v>
@@ -43685,7 +43685,7 @@
         <v>41</v>
       </c>
       <c r="G1552" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H1552" t="s">
         <v>9</v>
@@ -43711,7 +43711,7 @@
         <v>40.7999992370605</v>
       </c>
       <c r="G1553" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H1553" t="s">
         <v>9</v>
@@ -43737,7 +43737,7 @@
         <v>41.0999984741211</v>
       </c>
       <c r="G1554" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H1554" t="s">
         <v>9</v>
@@ -43763,7 +43763,7 @@
         <v>41</v>
       </c>
       <c r="G1555" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H1555" t="s">
         <v>9</v>
@@ -43789,7 +43789,7 @@
         <v>40.7000007629395</v>
       </c>
       <c r="G1556" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H1556" t="s">
         <v>9</v>
@@ -43815,7 +43815,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G1557" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="H1557" t="s">
         <v>9</v>
@@ -43841,7 +43841,7 @@
         <v>39.2999992370605</v>
       </c>
       <c r="G1558" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H1558" t="s">
         <v>9</v>
@@ -43867,7 +43867,7 @@
         <v>39.2000007629395</v>
       </c>
       <c r="G1559" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H1559" t="s">
         <v>9</v>
@@ -43893,7 +43893,7 @@
         <v>38.2999992370605</v>
       </c>
       <c r="G1560" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H1560" t="s">
         <v>9</v>
@@ -43919,7 +43919,7 @@
         <v>39</v>
       </c>
       <c r="G1561" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H1561" t="s">
         <v>9</v>
@@ -43945,7 +43945,7 @@
         <v>37</v>
       </c>
       <c r="G1562" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="H1562" t="s">
         <v>9</v>
@@ -43971,7 +43971,7 @@
         <v>36.5</v>
       </c>
       <c r="G1563" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="H1563" t="s">
         <v>9</v>
@@ -43997,7 +43997,7 @@
         <v>35.9000015258789</v>
       </c>
       <c r="G1564" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H1564" t="s">
         <v>9</v>
@@ -44023,7 +44023,7 @@
         <v>35.2999992370605</v>
       </c>
       <c r="G1565" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="H1565" t="s">
         <v>9</v>
@@ -44049,7 +44049,7 @@
         <v>36.4000015258789</v>
       </c>
       <c r="G1566" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="H1566" t="s">
         <v>9</v>
@@ -44075,7 +44075,7 @@
         <v>35.9000015258789</v>
       </c>
       <c r="G1567" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H1567" t="s">
         <v>9</v>
@@ -44101,7 +44101,7 @@
         <v>35.4000015258789</v>
       </c>
       <c r="G1568" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H1568" t="s">
         <v>9</v>
@@ -44127,7 +44127,7 @@
         <v>34.5999984741211</v>
       </c>
       <c r="G1569" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="H1569" t="s">
         <v>9</v>
@@ -44153,7 +44153,7 @@
         <v>34.7000007629395</v>
       </c>
       <c r="G1570" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="H1570" t="s">
         <v>9</v>
@@ -44179,7 +44179,7 @@
         <v>34</v>
       </c>
       <c r="G1571" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="H1571" t="s">
         <v>9</v>
@@ -44205,7 +44205,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1572" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H1572" t="s">
         <v>9</v>
@@ -44231,7 +44231,7 @@
         <v>33</v>
       </c>
       <c r="G1573" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H1573" t="s">
         <v>9</v>
@@ -44257,7 +44257,7 @@
         <v>34.5999984741211</v>
       </c>
       <c r="G1574" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="H1574" t="s">
         <v>9</v>
@@ -44283,7 +44283,7 @@
         <v>34.2999992370605</v>
       </c>
       <c r="G1575" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="H1575" t="s">
         <v>9</v>
@@ -44309,7 +44309,7 @@
         <v>35.9000015258789</v>
       </c>
       <c r="G1576" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H1576" t="s">
         <v>9</v>
@@ -44335,7 +44335,7 @@
         <v>35.4000015258789</v>
       </c>
       <c r="G1577" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H1577" t="s">
         <v>9</v>
@@ -44361,7 +44361,7 @@
         <v>34.9000015258789</v>
       </c>
       <c r="G1578" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="H1578" t="s">
         <v>9</v>
@@ -44387,7 +44387,7 @@
         <v>35.5</v>
       </c>
       <c r="G1579" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="H1579" t="s">
         <v>9</v>
@@ -44413,7 +44413,7 @@
         <v>36.7000007629395</v>
       </c>
       <c r="G1580" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="H1580" t="s">
         <v>9</v>
@@ -44439,7 +44439,7 @@
         <v>38</v>
       </c>
       <c r="G1581" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="H1581" t="s">
         <v>9</v>
@@ -44465,7 +44465,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G1582" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H1582" t="s">
         <v>9</v>
@@ -44491,7 +44491,7 @@
         <v>37.4000015258789</v>
       </c>
       <c r="G1583" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="H1583" t="s">
         <v>9</v>
@@ -44517,7 +44517,7 @@
         <v>37.9000015258789</v>
       </c>
       <c r="G1584" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="H1584" t="s">
         <v>9</v>
@@ -44543,7 +44543,7 @@
         <v>35.9000015258789</v>
       </c>
       <c r="G1585" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H1585" t="s">
         <v>9</v>
@@ -44569,7 +44569,7 @@
         <v>35</v>
       </c>
       <c r="G1586" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="H1586" t="s">
         <v>9</v>
@@ -44595,7 +44595,7 @@
         <v>35.0999984741211</v>
       </c>
       <c r="G1587" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="H1587" t="s">
         <v>9</v>
@@ -44621,7 +44621,7 @@
         <v>35.2000007629395</v>
       </c>
       <c r="G1588" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="H1588" t="s">
         <v>9</v>
@@ -44647,7 +44647,7 @@
         <v>35</v>
       </c>
       <c r="G1589" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="H1589" t="s">
         <v>9</v>
@@ -44673,7 +44673,7 @@
         <v>34.0999984741211</v>
       </c>
       <c r="G1590" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="H1590" t="s">
         <v>9</v>
@@ -44699,7 +44699,7 @@
         <v>33.9000015258789</v>
       </c>
       <c r="G1591" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="H1591" t="s">
         <v>9</v>
@@ -44725,7 +44725,7 @@
         <v>33.9000015258789</v>
       </c>
       <c r="G1592" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="H1592" t="s">
         <v>9</v>
@@ -44751,7 +44751,7 @@
         <v>35</v>
       </c>
       <c r="G1593" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="H1593" t="s">
         <v>9</v>
@@ -44777,7 +44777,7 @@
         <v>34.1500015258789</v>
       </c>
       <c r="G1594" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="H1594" t="s">
         <v>9</v>
@@ -44803,7 +44803,7 @@
         <v>34.5499992370605</v>
       </c>
       <c r="G1595" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="H1595" t="s">
         <v>9</v>
@@ -44829,7 +44829,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G1596" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="H1596" t="s">
         <v>9</v>
@@ -44855,7 +44855,7 @@
         <v>36.25</v>
       </c>
       <c r="G1597" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="H1597" t="s">
         <v>9</v>
@@ -44881,7 +44881,7 @@
         <v>36.5</v>
       </c>
       <c r="G1598" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="H1598" t="s">
         <v>9</v>
@@ -44907,7 +44907,7 @@
         <v>37.4000015258789</v>
       </c>
       <c r="G1599" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="H1599" t="s">
         <v>9</v>
@@ -44933,7 +44933,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G1600" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="H1600" t="s">
         <v>9</v>
@@ -44959,7 +44959,7 @@
         <v>36.6500015258789</v>
       </c>
       <c r="G1601" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="H1601" t="s">
         <v>9</v>
@@ -44985,7 +44985,7 @@
         <v>34.75</v>
       </c>
       <c r="G1602" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="H1602" t="s">
         <v>9</v>
@@ -45011,7 +45011,7 @@
         <v>33.9000015258789</v>
       </c>
       <c r="G1603" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="H1603" t="s">
         <v>9</v>
@@ -45037,7 +45037,7 @@
         <v>33.0499992370605</v>
       </c>
       <c r="G1604" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="H1604" t="s">
         <v>9</v>
@@ -45063,7 +45063,7 @@
         <v>32.8499984741211</v>
       </c>
       <c r="G1605" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H1605" t="s">
         <v>9</v>
@@ -45089,7 +45089,7 @@
         <v>32.5</v>
       </c>
       <c r="G1606" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H1606" t="s">
         <v>9</v>
@@ -45115,7 +45115,7 @@
         <v>31.1499996185303</v>
       </c>
       <c r="G1607" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="H1607" t="s">
         <v>9</v>
@@ -45141,7 +45141,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G1608" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1608" t="s">
         <v>9</v>
@@ -45167,7 +45167,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G1609" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H1609" t="s">
         <v>9</v>
@@ -45193,7 +45193,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1610" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="H1610" t="s">
         <v>9</v>
@@ -45219,7 +45219,7 @@
         <v>30.5499992370605</v>
       </c>
       <c r="G1611" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="H1611" t="s">
         <v>9</v>
@@ -45245,7 +45245,7 @@
         <v>30</v>
       </c>
       <c r="G1612" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="H1612" t="s">
         <v>9</v>
@@ -45271,7 +45271,7 @@
         <v>29.9500007629395</v>
       </c>
       <c r="G1613" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="H1613" t="s">
         <v>9</v>
@@ -45297,7 +45297,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G1614" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="H1614" t="s">
         <v>9</v>
@@ -45323,7 +45323,7 @@
         <v>29.9500007629395</v>
       </c>
       <c r="G1615" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="H1615" t="s">
         <v>9</v>
@@ -45349,7 +45349,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1616" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H1616" t="s">
         <v>9</v>
@@ -45375,7 +45375,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G1617" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="H1617" t="s">
         <v>9</v>
@@ -45401,7 +45401,7 @@
         <v>31.8500003814697</v>
       </c>
       <c r="G1618" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="H1618" t="s">
         <v>9</v>
@@ -45427,7 +45427,7 @@
         <v>32.5</v>
       </c>
       <c r="G1619" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="H1619" t="s">
         <v>9</v>
@@ -45453,7 +45453,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G1620" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="H1620" t="s">
         <v>9</v>
@@ -45479,7 +45479,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G1621" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="H1621" t="s">
         <v>9</v>
@@ -45505,7 +45505,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G1622" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H1622" t="s">
         <v>9</v>
@@ -45531,7 +45531,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G1623" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="H1623" t="s">
         <v>9</v>
@@ -45557,7 +45557,7 @@
         <v>29.25</v>
       </c>
       <c r="G1624" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="H1624" t="s">
         <v>9</v>
@@ -45583,7 +45583,7 @@
         <v>28.5499992370605</v>
       </c>
       <c r="G1625" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="H1625" t="s">
         <v>9</v>
@@ -45609,7 +45609,7 @@
         <v>28.5</v>
       </c>
       <c r="G1626" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="H1626" t="s">
         <v>9</v>
@@ -45635,7 +45635,7 @@
         <v>28.5</v>
       </c>
       <c r="G1627" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="H1627" t="s">
         <v>9</v>
@@ -45661,7 +45661,7 @@
         <v>28.25</v>
       </c>
       <c r="G1628" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="H1628" t="s">
         <v>9</v>
@@ -45687,7 +45687,7 @@
         <v>28.25</v>
       </c>
       <c r="G1629" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="H1629" t="s">
         <v>9</v>
@@ -45713,7 +45713,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G1630" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="H1630" t="s">
         <v>9</v>
@@ -45739,7 +45739,7 @@
         <v>28.25</v>
       </c>
       <c r="G1631" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="H1631" t="s">
         <v>9</v>
@@ -45765,7 +45765,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G1632" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="H1632" t="s">
         <v>9</v>
@@ -45791,7 +45791,7 @@
         <v>28.6499996185303</v>
       </c>
       <c r="G1633" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="H1633" t="s">
         <v>9</v>
@@ -45817,7 +45817,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G1634" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="H1634" t="s">
         <v>9</v>
@@ -45843,7 +45843,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1635" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H1635" t="s">
         <v>9</v>
@@ -45869,7 +45869,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1636" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H1636" t="s">
         <v>9</v>
@@ -45895,7 +45895,7 @@
         <v>27.8500003814697</v>
       </c>
       <c r="G1637" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H1637" t="s">
         <v>9</v>
@@ -45921,7 +45921,7 @@
         <v>27.6499996185303</v>
       </c>
       <c r="G1638" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H1638" t="s">
         <v>9</v>
@@ -45947,7 +45947,7 @@
         <v>27.25</v>
       </c>
       <c r="G1639" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H1639" t="s">
         <v>9</v>
@@ -45973,7 +45973,7 @@
         <v>26.6499996185303</v>
       </c>
       <c r="G1640" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -45999,7 +45999,7 @@
         <v>26.6499996185303</v>
       </c>
       <c r="G1641" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H1641" t="s">
         <v>9</v>
@@ -46025,7 +46025,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1642" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -46051,7 +46051,7 @@
         <v>25.8500003814697</v>
       </c>
       <c r="G1643" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="H1643" t="s">
         <v>9</v>
@@ -46077,7 +46077,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G1644" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="H1644" t="s">
         <v>9</v>
@@ -46103,7 +46103,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G1645" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="H1645" t="s">
         <v>9</v>
@@ -46129,7 +46129,7 @@
         <v>27</v>
       </c>
       <c r="G1646" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="H1646" t="s">
         <v>9</v>
@@ -46155,7 +46155,7 @@
         <v>26.75</v>
       </c>
       <c r="G1647" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="H1647" t="s">
         <v>9</v>
@@ -46181,7 +46181,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G1648" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="H1648" t="s">
         <v>9</v>
@@ -46207,7 +46207,7 @@
         <v>26.75</v>
       </c>
       <c r="G1649" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="H1649" t="s">
         <v>9</v>
@@ -46233,7 +46233,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1650" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H1650" t="s">
         <v>9</v>
@@ -46259,7 +46259,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1651" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H1651" t="s">
         <v>9</v>
@@ -46285,7 +46285,7 @@
         <v>26.5499992370605</v>
       </c>
       <c r="G1652" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="H1652" t="s">
         <v>9</v>
@@ -46311,7 +46311,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1653" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H1653" t="s">
         <v>9</v>
@@ -46337,7 +46337,7 @@
         <v>26.25</v>
       </c>
       <c r="G1654" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="H1654" t="s">
         <v>9</v>
@@ -46363,7 +46363,7 @@
         <v>26.4500007629395</v>
       </c>
       <c r="G1655" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="H1655" t="s">
         <v>9</v>
@@ -46389,7 +46389,7 @@
         <v>26.4500007629395</v>
       </c>
       <c r="G1656" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="H1656" t="s">
         <v>9</v>
@@ -46415,7 +46415,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G1657" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -46441,7 +46441,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G1658" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="H1658" t="s">
         <v>9</v>
@@ -46467,7 +46467,7 @@
         <v>25.75</v>
       </c>
       <c r="G1659" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="H1659" t="s">
         <v>9</v>
@@ -46493,7 +46493,7 @@
         <v>25.8500003814697</v>
       </c>
       <c r="G1660" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="H1660" t="s">
         <v>9</v>
@@ -46519,7 +46519,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G1661" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -46545,7 +46545,7 @@
         <v>26</v>
       </c>
       <c r="G1662" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -46571,7 +46571,7 @@
         <v>25.3500003814697</v>
       </c>
       <c r="G1663" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="H1663" t="s">
         <v>9</v>
@@ -46597,7 +46597,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G1664" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="H1664" t="s">
         <v>9</v>
@@ -46623,7 +46623,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G1665" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="H1665" t="s">
         <v>9</v>
@@ -46649,7 +46649,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G1666" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -46675,7 +46675,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G1667" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="H1667" t="s">
         <v>9</v>
@@ -46701,7 +46701,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G1668" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="H1668" t="s">
         <v>9</v>
@@ -46727,7 +46727,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G1669" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="H1669" t="s">
         <v>9</v>
@@ -46753,7 +46753,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G1670" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="H1670" t="s">
         <v>9</v>
@@ -46779,7 +46779,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G1671" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="H1671" t="s">
         <v>9</v>
@@ -46805,7 +46805,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G1672" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="H1672" t="s">
         <v>9</v>
@@ -46831,7 +46831,7 @@
         <v>26.8500003814697</v>
       </c>
       <c r="G1673" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="H1673" t="s">
         <v>9</v>
@@ -46857,7 +46857,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1674" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H1674" t="s">
         <v>9</v>
@@ -46883,7 +46883,7 @@
         <v>28</v>
       </c>
       <c r="G1675" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="H1675" t="s">
         <v>9</v>
@@ -46909,7 +46909,7 @@
         <v>28.5</v>
       </c>
       <c r="G1676" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="H1676" t="s">
         <v>9</v>
@@ -46935,7 +46935,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1677" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="H1677" t="s">
         <v>9</v>
@@ -46961,7 +46961,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1678" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H1678" t="s">
         <v>9</v>
@@ -46987,7 +46987,7 @@
         <v>28.8500003814697</v>
       </c>
       <c r="G1679" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="H1679" t="s">
         <v>9</v>
@@ -47013,7 +47013,7 @@
         <v>28</v>
       </c>
       <c r="G1680" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="H1680" t="s">
         <v>9</v>
@@ -47039,7 +47039,7 @@
         <v>27.4500007629395</v>
       </c>
       <c r="G1681" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -47065,7 +47065,7 @@
         <v>26.9500007629395</v>
       </c>
       <c r="G1682" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="H1682" t="s">
         <v>9</v>
@@ -47091,7 +47091,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1683" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H1683" t="s">
         <v>9</v>
@@ -47117,7 +47117,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1684" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="H1684" t="s">
         <v>9</v>
@@ -47143,7 +47143,7 @@
         <v>27.6499996185303</v>
       </c>
       <c r="G1685" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H1685" t="s">
         <v>9</v>
@@ -47169,7 +47169,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G1686" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="H1686" t="s">
         <v>9</v>
@@ -47195,7 +47195,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G1687" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="H1687" t="s">
         <v>9</v>
@@ -47221,7 +47221,7 @@
         <v>25.8500003814697</v>
       </c>
       <c r="G1688" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="H1688" t="s">
         <v>9</v>
@@ -47247,7 +47247,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G1689" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="H1689" t="s">
         <v>9</v>
@@ -47273,7 +47273,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G1690" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="H1690" t="s">
         <v>9</v>
@@ -47299,7 +47299,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G1691" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="H1691" t="s">
         <v>9</v>
@@ -47325,7 +47325,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G1692" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="H1692" t="s">
         <v>9</v>
@@ -47351,7 +47351,7 @@
         <v>24.9500007629395</v>
       </c>
       <c r="G1693" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="H1693" t="s">
         <v>9</v>
@@ -47377,7 +47377,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G1694" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -47403,7 +47403,7 @@
         <v>25.1499996185303</v>
       </c>
       <c r="G1695" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="H1695" t="s">
         <v>9</v>
@@ -47429,7 +47429,7 @@
         <v>25.75</v>
       </c>
       <c r="G1696" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="H1696" t="s">
         <v>9</v>
@@ -47455,7 +47455,7 @@
         <v>25.5</v>
       </c>
       <c r="G1697" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="H1697" t="s">
         <v>9</v>
@@ -47481,7 +47481,7 @@
         <v>25.4500007629395</v>
       </c>
       <c r="G1698" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="H1698" t="s">
         <v>9</v>
@@ -47507,7 +47507,7 @@
         <v>25.25</v>
       </c>
       <c r="G1699" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="H1699" t="s">
         <v>9</v>
@@ -47533,7 +47533,7 @@
         <v>25.1499996185303</v>
       </c>
       <c r="G1700" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="H1700" t="s">
         <v>9</v>
@@ -47559,7 +47559,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G1701" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="H1701" t="s">
         <v>9</v>
@@ -47585,7 +47585,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G1702" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="H1702" t="s">
         <v>9</v>
@@ -47611,7 +47611,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G1703" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="H1703" t="s">
         <v>9</v>
@@ -47637,7 +47637,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G1704" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="H1704" t="s">
         <v>9</v>
@@ -47663,7 +47663,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G1705" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="H1705" t="s">
         <v>9</v>
@@ -47689,7 +47689,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G1706" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="H1706" t="s">
         <v>9</v>
@@ -47715,7 +47715,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G1707" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="H1707" t="s">
         <v>9</v>
@@ -47741,7 +47741,7 @@
         <v>26</v>
       </c>
       <c r="G1708" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="H1708" t="s">
         <v>9</v>
@@ -47767,7 +47767,7 @@
         <v>25.4500007629395</v>
       </c>
       <c r="G1709" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="H1709" t="s">
         <v>9</v>
@@ -47793,7 +47793,7 @@
         <v>25</v>
       </c>
       <c r="G1710" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="H1710" t="s">
         <v>9</v>
@@ -47819,7 +47819,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G1711" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="H1711" t="s">
         <v>9</v>
@@ -47845,7 +47845,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G1712" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="H1712" t="s">
         <v>9</v>
@@ -47871,7 +47871,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G1713" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="H1713" t="s">
         <v>9</v>
@@ -47897,7 +47897,7 @@
         <v>23.25</v>
       </c>
       <c r="G1714" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="H1714" t="s">
         <v>9</v>
@@ -47923,7 +47923,7 @@
         <v>22.9500007629395</v>
       </c>
       <c r="G1715" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="H1715" t="s">
         <v>9</v>
@@ -47949,7 +47949,7 @@
         <v>22.5</v>
       </c>
       <c r="G1716" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="H1716" t="s">
         <v>9</v>
@@ -47975,7 +47975,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G1717" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H1717" t="s">
         <v>9</v>
@@ -48001,7 +48001,7 @@
         <v>21.5499992370605</v>
       </c>
       <c r="G1718" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="H1718" t="s">
         <v>9</v>
@@ -48027,7 +48027,7 @@
         <v>21.75</v>
       </c>
       <c r="G1719" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="H1719" t="s">
         <v>9</v>
@@ -48053,7 +48053,7 @@
         <v>21.75</v>
       </c>
       <c r="G1720" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="H1720" t="s">
         <v>9</v>
@@ -48079,7 +48079,7 @@
         <v>21.75</v>
       </c>
       <c r="G1721" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="H1721" t="s">
         <v>9</v>
@@ -48105,7 +48105,7 @@
         <v>21.75</v>
       </c>
       <c r="G1722" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="H1722" t="s">
         <v>9</v>
@@ -48131,7 +48131,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G1723" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="H1723" t="s">
         <v>9</v>
@@ -48157,7 +48157,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G1724" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="H1724" t="s">
         <v>9</v>
@@ -48183,7 +48183,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1725" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="H1725" t="s">
         <v>9</v>
@@ -48209,7 +48209,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1726" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H1726" t="s">
         <v>9</v>
@@ -48235,7 +48235,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G1727" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="H1727" t="s">
         <v>9</v>
@@ -48261,7 +48261,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1728" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="H1728" t="s">
         <v>9</v>
@@ -48287,7 +48287,7 @@
         <v>21.5</v>
       </c>
       <c r="G1729" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="H1729" t="s">
         <v>9</v>
@@ -48313,7 +48313,7 @@
         <v>21.6499996185303</v>
       </c>
       <c r="G1730" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="H1730" t="s">
         <v>9</v>
@@ -48339,7 +48339,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1731" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="H1731" t="s">
         <v>9</v>
@@ -48365,7 +48365,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G1732" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="H1732" t="s">
         <v>9</v>
@@ -48391,7 +48391,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G1733" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="H1733" t="s">
         <v>9</v>
@@ -48417,7 +48417,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G1734" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="H1734" t="s">
         <v>9</v>
@@ -48443,7 +48443,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1735" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="H1735" t="s">
         <v>9</v>
@@ -48469,7 +48469,7 @@
         <v>22.75</v>
       </c>
       <c r="G1736" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="H1736" t="s">
         <v>9</v>
@@ -48495,7 +48495,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1737" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="H1737" t="s">
         <v>9</v>
@@ -48521,7 +48521,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G1738" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="H1738" t="s">
         <v>9</v>
@@ -48547,7 +48547,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G1739" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="H1739" t="s">
         <v>9</v>
@@ -48573,7 +48573,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G1740" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="H1740" t="s">
         <v>9</v>
@@ -48599,7 +48599,7 @@
         <v>24.1499996185303</v>
       </c>
       <c r="G1741" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="H1741" t="s">
         <v>9</v>
@@ -48625,7 +48625,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G1742" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="H1742" t="s">
         <v>9</v>
@@ -48651,7 +48651,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G1743" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="H1743" t="s">
         <v>9</v>
@@ -48677,7 +48677,7 @@
         <v>25</v>
       </c>
       <c r="G1744" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="H1744" t="s">
         <v>9</v>
@@ -48703,7 +48703,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G1745" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="H1745" t="s">
         <v>9</v>
@@ -48729,7 +48729,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G1746" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="H1746" t="s">
         <v>9</v>
@@ -48755,7 +48755,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G1747" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="H1747" t="s">
         <v>9</v>
@@ -48781,7 +48781,7 @@
         <v>25.5499992370605</v>
       </c>
       <c r="G1748" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="H1748" t="s">
         <v>9</v>
@@ -48807,7 +48807,7 @@
         <v>26.5</v>
       </c>
       <c r="G1749" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="H1749" t="s">
         <v>9</v>
@@ -48833,7 +48833,7 @@
         <v>26.3500003814697</v>
       </c>
       <c r="G1750" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="H1750" t="s">
         <v>9</v>
@@ -48859,7 +48859,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G1751" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="H1751" t="s">
         <v>9</v>
@@ -48885,7 +48885,7 @@
         <v>25</v>
       </c>
       <c r="G1752" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="H1752" t="s">
         <v>9</v>
@@ -48911,7 +48911,7 @@
         <v>25.25</v>
       </c>
       <c r="G1753" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="H1753" t="s">
         <v>9</v>
@@ -48937,7 +48937,7 @@
         <v>25.5499992370605</v>
       </c>
       <c r="G1754" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="H1754" t="s">
         <v>9</v>
@@ -48963,7 +48963,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G1755" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="H1755" t="s">
         <v>9</v>
@@ -48989,7 +48989,7 @@
         <v>27.1499996185303</v>
       </c>
       <c r="G1756" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="H1756" t="s">
         <v>9</v>
@@ -49015,7 +49015,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1757" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="H1757" t="s">
         <v>9</v>
@@ -49041,7 +49041,7 @@
         <v>26.8500003814697</v>
       </c>
       <c r="G1758" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="H1758" t="s">
         <v>9</v>
@@ -49067,7 +49067,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1759" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H1759" t="s">
         <v>9</v>
@@ -49093,7 +49093,7 @@
         <v>26</v>
       </c>
       <c r="G1760" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="H1760" t="s">
         <v>9</v>
@@ -49119,7 +49119,7 @@
         <v>26.5</v>
       </c>
       <c r="G1761" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="H1761" t="s">
         <v>9</v>
@@ -49145,7 +49145,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1762" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="H1762" t="s">
         <v>9</v>
@@ -49171,7 +49171,7 @@
         <v>27</v>
       </c>
       <c r="G1763" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="H1763" t="s">
         <v>9</v>
@@ -49197,7 +49197,7 @@
         <v>26.9500007629395</v>
       </c>
       <c r="G1764" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="H1764" t="s">
         <v>9</v>
@@ -49223,7 +49223,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G1765" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="H1765" t="s">
         <v>9</v>
@@ -49249,7 +49249,7 @@
         <v>27.25</v>
       </c>
       <c r="G1766" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H1766" t="s">
         <v>9</v>
@@ -49275,7 +49275,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1767" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="H1767" t="s">
         <v>9</v>
@@ -49301,7 +49301,7 @@
         <v>27.6499996185303</v>
       </c>
       <c r="G1768" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H1768" t="s">
         <v>9</v>
@@ -49327,7 +49327,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1769" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="H1769" t="s">
         <v>9</v>
@@ -49353,7 +49353,7 @@
         <v>27.75</v>
       </c>
       <c r="G1770" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="H1770" t="s">
         <v>9</v>
@@ -49379,7 +49379,7 @@
         <v>27</v>
       </c>
       <c r="G1771" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="H1771" t="s">
         <v>9</v>
@@ -49405,7 +49405,7 @@
         <v>27.3500003814697</v>
       </c>
       <c r="G1772" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="H1772" t="s">
         <v>9</v>
@@ -49431,7 +49431,7 @@
         <v>27.1499996185303</v>
       </c>
       <c r="G1773" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="H1773" t="s">
         <v>9</v>
@@ -49457,7 +49457,7 @@
         <v>27.4500007629395</v>
       </c>
       <c r="G1774" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="H1774" t="s">
         <v>9</v>
@@ -49483,7 +49483,7 @@
         <v>27.5499992370605</v>
       </c>
       <c r="G1775" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="H1775" t="s">
         <v>9</v>
@@ -49509,7 +49509,7 @@
         <v>27.1499996185303</v>
       </c>
       <c r="G1776" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="H1776" t="s">
         <v>9</v>
@@ -49535,7 +49535,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G1777" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H1777" t="s">
         <v>9</v>
@@ -49561,7 +49561,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1778" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H1778" t="s">
         <v>9</v>
@@ -49587,7 +49587,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1779" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="H1779" t="s">
         <v>9</v>
@@ -49613,7 +49613,7 @@
         <v>27.5</v>
       </c>
       <c r="G1780" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="H1780" t="s">
         <v>9</v>
@@ -49639,7 +49639,7 @@
         <v>27.5</v>
       </c>
       <c r="G1781" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="H1781" t="s">
         <v>9</v>
@@ -49665,7 +49665,7 @@
         <v>27.4500007629395</v>
       </c>
       <c r="G1782" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="H1782" t="s">
         <v>9</v>
@@ -49691,7 +49691,7 @@
         <v>27.6499996185303</v>
       </c>
       <c r="G1783" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H1783" t="s">
         <v>9</v>
@@ -49717,7 +49717,7 @@
         <v>27.5</v>
       </c>
       <c r="G1784" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="H1784" t="s">
         <v>9</v>
@@ -49743,7 +49743,7 @@
         <v>29.8500003814697</v>
       </c>
       <c r="G1785" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="H1785" t="s">
         <v>9</v>
@@ -49769,7 +49769,7 @@
         <v>29.3500003814697</v>
       </c>
       <c r="G1786" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="H1786" t="s">
         <v>9</v>
@@ -49795,7 +49795,7 @@
         <v>29.6499996185303</v>
       </c>
       <c r="G1787" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H1787" t="s">
         <v>9</v>
@@ -49821,7 +49821,7 @@
         <v>29.4500007629395</v>
       </c>
       <c r="G1788" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="H1788" t="s">
         <v>9</v>
@@ -49847,7 +49847,7 @@
         <v>29.75</v>
       </c>
       <c r="G1789" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="H1789" t="s">
         <v>9</v>
@@ -49873,7 +49873,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G1790" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H1790" t="s">
         <v>9</v>
@@ -49899,7 +49899,7 @@
         <v>30.25</v>
       </c>
       <c r="G1791" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="H1791" t="s">
         <v>9</v>
@@ -49925,7 +49925,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G1792" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H1792" t="s">
         <v>9</v>
@@ -49951,7 +49951,7 @@
         <v>30.25</v>
       </c>
       <c r="G1793" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="H1793" t="s">
         <v>9</v>
@@ -49977,7 +49977,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G1794" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H1794" t="s">
         <v>9</v>
@@ -50003,7 +50003,7 @@
         <v>30.5</v>
       </c>
       <c r="G1795" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="H1795" t="s">
         <v>9</v>
@@ -50029,7 +50029,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G1796" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="H1796" t="s">
         <v>9</v>
@@ -50055,7 +50055,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G1797" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H1797" t="s">
         <v>9</v>
@@ -50081,7 +50081,7 @@
         <v>30.3500003814697</v>
       </c>
       <c r="G1798" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H1798" t="s">
         <v>9</v>
@@ -50107,7 +50107,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G1799" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="H1799" t="s">
         <v>9</v>
@@ -50133,7 +50133,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G1800" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="H1800" t="s">
         <v>9</v>
@@ -50159,7 +50159,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G1801" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H1801" t="s">
         <v>9</v>
@@ -50185,7 +50185,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G1802" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="H1802" t="s">
         <v>9</v>
@@ -50211,7 +50211,7 @@
         <v>29.75</v>
       </c>
       <c r="G1803" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="H1803" t="s">
         <v>9</v>
@@ -50237,7 +50237,7 @@
         <v>28.1499996185303</v>
       </c>
       <c r="G1804" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="H1804" t="s">
         <v>9</v>
@@ -50263,7 +50263,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1805" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="H1805" t="s">
         <v>9</v>
@@ -50289,7 +50289,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1806" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H1806" t="s">
         <v>9</v>
@@ -50315,7 +50315,7 @@
         <v>27.6499996185303</v>
       </c>
       <c r="G1807" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H1807" t="s">
         <v>9</v>
@@ -50341,7 +50341,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1808" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H1808" t="s">
         <v>9</v>
@@ -50367,7 +50367,7 @@
         <v>27.5</v>
       </c>
       <c r="G1809" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="H1809" t="s">
         <v>9</v>
@@ -50393,7 +50393,7 @@
         <v>27.3500003814697</v>
       </c>
       <c r="G1810" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="H1810" t="s">
         <v>9</v>
@@ -50419,7 +50419,7 @@
         <v>26.9500007629395</v>
       </c>
       <c r="G1811" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="H1811" t="s">
         <v>9</v>
@@ -50445,7 +50445,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G1812" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="H1812" t="s">
         <v>9</v>
@@ -50471,7 +50471,7 @@
         <v>26</v>
       </c>
       <c r="G1813" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="H1813" t="s">
         <v>9</v>
@@ -50497,7 +50497,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G1814" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="H1814" t="s">
         <v>9</v>
@@ -50523,7 +50523,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G1815" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="H1815" t="s">
         <v>9</v>
@@ -50549,7 +50549,7 @@
         <v>24.75</v>
       </c>
       <c r="G1816" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="H1816" t="s">
         <v>9</v>
@@ -50575,7 +50575,7 @@
         <v>23.9500007629395</v>
       </c>
       <c r="G1817" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="H1817" t="s">
         <v>9</v>
@@ -50601,7 +50601,7 @@
         <v>24.1499996185303</v>
       </c>
       <c r="G1818" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="H1818" t="s">
         <v>9</v>
@@ -50627,7 +50627,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G1819" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="H1819" t="s">
         <v>9</v>
@@ -50653,7 +50653,7 @@
         <v>23.8500003814697</v>
       </c>
       <c r="G1820" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="H1820" t="s">
         <v>9</v>
@@ -50679,7 +50679,7 @@
         <v>23.9500007629395</v>
       </c>
       <c r="G1821" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="H1821" t="s">
         <v>9</v>
@@ -50705,7 +50705,7 @@
         <v>24.5</v>
       </c>
       <c r="G1822" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="H1822" t="s">
         <v>9</v>
@@ -50731,7 +50731,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G1823" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="H1823" t="s">
         <v>9</v>
@@ -50757,7 +50757,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G1824" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="H1824" t="s">
         <v>9</v>
@@ -50783,7 +50783,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G1825" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="H1825" t="s">
         <v>9</v>
@@ -50809,7 +50809,7 @@
         <v>25.0499992370605</v>
       </c>
       <c r="G1826" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="H1826" t="s">
         <v>9</v>
@@ -50835,7 +50835,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G1827" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="H1827" t="s">
         <v>9</v>
@@ -50861,7 +50861,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G1828" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="H1828" t="s">
         <v>9</v>
@@ -50887,7 +50887,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G1829" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="H1829" t="s">
         <v>9</v>
@@ -50913,7 +50913,7 @@
         <v>25.25</v>
       </c>
       <c r="G1830" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="H1830" t="s">
         <v>9</v>
@@ -50939,7 +50939,7 @@
         <v>25.3500003814697</v>
       </c>
       <c r="G1831" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="H1831" t="s">
         <v>9</v>
@@ -50965,7 +50965,7 @@
         <v>25.25</v>
       </c>
       <c r="G1832" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="H1832" t="s">
         <v>9</v>
@@ -50991,7 +50991,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G1833" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="H1833" t="s">
         <v>9</v>
@@ -51017,7 +51017,7 @@
         <v>25.5499992370605</v>
       </c>
       <c r="G1834" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="H1834" t="s">
         <v>9</v>
@@ -51043,7 +51043,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G1835" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="H1835" t="s">
         <v>9</v>
@@ -51069,7 +51069,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G1836" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="H1836" t="s">
         <v>9</v>
@@ -51095,7 +51095,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G1837" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="H1837" t="s">
         <v>9</v>
@@ -51121,7 +51121,7 @@
         <v>22.25</v>
       </c>
       <c r="G1838" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="H1838" t="s">
         <v>9</v>
@@ -51147,7 +51147,7 @@
         <v>22.25</v>
       </c>
       <c r="G1839" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="H1839" t="s">
         <v>9</v>
@@ -51173,7 +51173,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G1840" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="H1840" t="s">
         <v>9</v>
@@ -51199,7 +51199,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G1841" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="H1841" t="s">
         <v>9</v>
@@ -51225,7 +51225,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G1842" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="H1842" t="s">
         <v>9</v>
@@ -51251,7 +51251,7 @@
         <v>21.8500003814697</v>
       </c>
       <c r="G1843" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="H1843" t="s">
         <v>9</v>
@@ -51277,7 +51277,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G1844" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H1844" t="s">
         <v>9</v>
@@ -51303,7 +51303,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G1845" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="H1845" t="s">
         <v>9</v>
@@ -51329,7 +51329,7 @@
         <v>23.5</v>
       </c>
       <c r="G1846" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="H1846" t="s">
         <v>9</v>
@@ -51355,7 +51355,7 @@
         <v>23.8500003814697</v>
       </c>
       <c r="G1847" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="H1847" t="s">
         <v>9</v>
@@ -51381,7 +51381,7 @@
         <v>24.5</v>
       </c>
       <c r="G1848" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="H1848" t="s">
         <v>9</v>
@@ -51407,7 +51407,7 @@
         <v>24.9500007629395</v>
       </c>
       <c r="G1849" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="H1849" t="s">
         <v>9</v>
@@ -51433,7 +51433,7 @@
         <v>23.8500003814697</v>
       </c>
       <c r="G1850" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="H1850" t="s">
         <v>9</v>
@@ -51459,7 +51459,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1851" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="H1851" t="s">
         <v>9</v>
@@ -51485,7 +51485,7 @@
         <v>23.3500003814697</v>
       </c>
       <c r="G1852" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="H1852" t="s">
         <v>9</v>
@@ -51511,7 +51511,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1853" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H1853" t="s">
         <v>9</v>
@@ -51537,7 +51537,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G1854" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="H1854" t="s">
         <v>9</v>
@@ -51563,7 +51563,7 @@
         <v>23</v>
       </c>
       <c r="G1855" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="H1855" t="s">
         <v>9</v>
@@ -51589,7 +51589,7 @@
         <v>23</v>
       </c>
       <c r="G1856" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="H1856" t="s">
         <v>9</v>
@@ -51615,7 +51615,7 @@
         <v>23.3500003814697</v>
       </c>
       <c r="G1857" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="H1857" t="s">
         <v>9</v>
@@ -51641,7 +51641,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1858" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="H1858" t="s">
         <v>9</v>
@@ -51667,7 +51667,7 @@
         <v>23</v>
       </c>
       <c r="G1859" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="H1859" t="s">
         <v>9</v>
@@ -51693,7 +51693,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G1860" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="H1860" t="s">
         <v>9</v>
@@ -51719,7 +51719,7 @@
         <v>23</v>
       </c>
       <c r="G1861" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="H1861" t="s">
         <v>9</v>
@@ -51745,7 +51745,7 @@
         <v>22.9500007629395</v>
       </c>
       <c r="G1862" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="H1862" t="s">
         <v>9</v>
@@ -51771,7 +51771,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G1863" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="H1863" t="s">
         <v>9</v>
@@ -51797,7 +51797,7 @@
         <v>22.5499992370605</v>
       </c>
       <c r="G1864" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="H1864" t="s">
         <v>9</v>
@@ -51823,7 +51823,7 @@
         <v>23</v>
       </c>
       <c r="G1865" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="H1865" t="s">
         <v>9</v>
@@ -51849,7 +51849,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1866" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="H1866" t="s">
         <v>9</v>
@@ -51875,7 +51875,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1867" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="H1867" t="s">
         <v>9</v>
@@ -51901,7 +51901,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1868" t="s">
-        <v>758</v>
+        <v>762</v>
       </c>
       <c r="H1868" t="s">
         <v>9</v>
@@ -51953,7 +51953,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1870" t="s">
-        <v>758</v>
+        <v>762</v>
       </c>
       <c r="H1870" t="s">
         <v>9</v>
@@ -52083,7 +52083,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1875" t="s">
-        <v>758</v>
+        <v>762</v>
       </c>
       <c r="H1875" t="s">
         <v>9</v>
@@ -52135,7 +52135,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1877" t="s">
-        <v>758</v>
+        <v>762</v>
       </c>
       <c r="H1877" t="s">
         <v>9</v>
@@ -52161,7 +52161,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1878" t="s">
-        <v>758</v>
+        <v>762</v>
       </c>
       <c r="H1878" t="s">
         <v>9</v>
@@ -52447,7 +52447,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1889" t="s">
-        <v>758</v>
+        <v>762</v>
       </c>
       <c r="H1889" t="s">
         <v>9</v>
@@ -52499,7 +52499,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1891" t="s">
-        <v>758</v>
+        <v>762</v>
       </c>
       <c r="H1891" t="s">
         <v>9</v>
@@ -52525,7 +52525,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1892" t="s">
-        <v>758</v>
+        <v>762</v>
       </c>
       <c r="H1892" t="s">
         <v>9</v>
@@ -52551,7 +52551,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1893" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="H1893" t="s">
         <v>9</v>
@@ -52577,7 +52577,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1894" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="H1894" t="s">
         <v>9</v>
@@ -52733,7 +52733,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1900" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="H1900" t="s">
         <v>9</v>
@@ -68731,7 +68731,7 @@
     </row>
     <row r="2516">
       <c r="A2516" s="1" t="n">
-        <v>45981.6911921296</v>
+        <v>45981.3333333333</v>
       </c>
       <c r="B2516" t="n">
         <v>10302</v>
@@ -68752,6 +68752,32 @@
         <v>970</v>
       </c>
       <c r="H2516" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2517">
+      <c r="A2517" s="1" t="n">
+        <v>45982.6912962963</v>
+      </c>
+      <c r="B2517" t="n">
+        <v>5128</v>
+      </c>
+      <c r="C2517" t="n">
+        <v>21.8999996185303</v>
+      </c>
+      <c r="D2517" t="n">
+        <v>21.6000003814697</v>
+      </c>
+      <c r="E2517" t="n">
+        <v>21.6000003814697</v>
+      </c>
+      <c r="F2517" t="n">
+        <v>21.7999992370605</v>
+      </c>
+      <c r="G2517" t="s">
+        <v>980</v>
+      </c>
+      <c r="H2517" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IWB.MI.xlsx
+++ b/data/IWB.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84661531448364</t>
+    <t xml:space="preserve">7.8466157913208</t>
   </si>
   <si>
     <t xml:space="preserve">IWB.MI</t>
@@ -47,235 +47,235 @@
     <t xml:space="preserve">7.7986741065979</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83063459396362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7427396774292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75072956085205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71077823638916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69479846954346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59092235565186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51101589202881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31125640869141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44709396362305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35120916366577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29527473449707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26331424713135</t>
+    <t xml:space="preserve">7.83063507080078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74274158477783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75073003768921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71077871322632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69479703903198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59092283248901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5110182762146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31125736236572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44709491729736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35120820999146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29527568817139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26331377029419</t>
   </si>
   <si>
     <t xml:space="preserve">7.29927062988281</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29128122329712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2713041305542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24733114242554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37517881393433</t>
+    <t xml:space="preserve">7.29127979278564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27130508422852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24733400344849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3751802444458</t>
   </si>
   <si>
     <t xml:space="preserve">7.43111371994019</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47106552124023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15144681930542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41513204574585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32723808288574</t>
+    <t xml:space="preserve">7.47106409072876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15144729614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41513156890869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32723665237427</t>
   </si>
   <si>
     <t xml:space="preserve">7.28728532791138</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99163866043091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11149454116821</t>
+    <t xml:space="preserve">6.99163913726807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11149406433105</t>
   </si>
   <si>
     <t xml:space="preserve">7.1914005279541</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25532293319702</t>
+    <t xml:space="preserve">7.25532341003418</t>
   </si>
   <si>
     <t xml:space="preserve">7.41912746429443</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42312288284302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6308741569519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67082738876343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49903106689453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58293199539185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89455986022949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98644924163818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91054058074951</t>
+    <t xml:space="preserve">7.42312431335449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63087368011475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67082691192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49903249740601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58293056488037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89455842971802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98644971847534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9105396270752</t>
   </si>
   <si>
     <t xml:space="preserve">7.54297876358032</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82264471054077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64285898208618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62288475036621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77470302581787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7667121887207</t>
+    <t xml:space="preserve">7.82264566421509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64286041259766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62288379669189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77470254898071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76671171188354</t>
   </si>
   <si>
     <t xml:space="preserve">7.79068326950073</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87058877944946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96647214889526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7187705039978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66283512115479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57094717025757</t>
+    <t xml:space="preserve">7.8705883026123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96647357940674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71876859664917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66283798217773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57094764709473</t>
   </si>
   <si>
     <t xml:space="preserve">7.5589599609375</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39115953445435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46307611465454</t>
+    <t xml:space="preserve">7.39116191864014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46307516098022</t>
   </si>
   <si>
     <t xml:space="preserve">7.60690402984619</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54697513580322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36718988418579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31525087356567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33123207092285</t>
+    <t xml:space="preserve">7.54697370529175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36719036102295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31525182723999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33123302459717</t>
   </si>
   <si>
     <t xml:space="preserve">7.34721326828003</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50302791595459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24333667755127</t>
+    <t xml:space="preserve">7.50302839279175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24333763122559</t>
   </si>
   <si>
     <t xml:space="preserve">7.22336149215698</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23934268951416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45907878875732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46707201004028</t>
+    <t xml:space="preserve">7.23934316635132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4590802192688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46707153320312</t>
   </si>
   <si>
     <t xml:space="preserve">7.10350513458252</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89974880218506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91173410415649</t>
+    <t xml:space="preserve">6.89974784851074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91173458099365</t>
   </si>
   <si>
     <t xml:space="preserve">6.95168733596802</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00761938095093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87178182601929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87577724456787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87977266311646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86778736114502</t>
+    <t xml:space="preserve">7.0076208114624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8717827796936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87577676773071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8797721862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86778783798218</t>
   </si>
   <si>
     <t xml:space="preserve">6.75192451477051</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7439341545105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82383966445923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66403150558472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8318305015564</t>
+    <t xml:space="preserve">6.74393463134766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82383918762207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66403102874756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83183145523071</t>
   </si>
   <si>
     <t xml:space="preserve">6.89575338363647</t>
@@ -284,61 +284,61 @@
     <t xml:space="preserve">7.03159093856812</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07154417037964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33522891998291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25931787490845</t>
+    <t xml:space="preserve">7.07154369354248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33522796630859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25931835174561</t>
   </si>
   <si>
     <t xml:space="preserve">7.17941427230835</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26730918884277</t>
+    <t xml:space="preserve">7.26730966567993</t>
   </si>
   <si>
     <t xml:space="preserve">7.23135232925415</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09551477432251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18340921401978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18740510940552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20738124847412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14345741271973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12347984313965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23534774780273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74673652648926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83463048934937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98245239257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92652034759521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78269100189209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63886594772339</t>
+    <t xml:space="preserve">7.09551525115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18340826034546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18740463256836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20738172531128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14345693588257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12348031997681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23534822463989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7467360496521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83463191986084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98245334625244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92652225494385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78269195556641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63886451721191</t>
   </si>
   <si>
     <t xml:space="preserve">7.73475027084351</t>
@@ -347,37 +347,37 @@
     <t xml:space="preserve">8.07035064697266</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21417617797852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16623497009277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18221473693848</t>
+    <t xml:space="preserve">8.21417713165283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16623306274414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18221569061279</t>
   </si>
   <si>
     <t xml:space="preserve">8.27011108398438</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57374668121338</t>
+    <t xml:space="preserve">8.5737476348877</t>
   </si>
   <si>
     <t xml:space="preserve">8.54977512359619</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35001373291016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46986961364746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52580451965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50982475280762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59771823883057</t>
+    <t xml:space="preserve">8.35001564025879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46987152099609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.525803565979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50982189178467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59771728515625</t>
   </si>
   <si>
     <t xml:space="preserve">8.60571002960205</t>
@@ -386,49 +386,49 @@
     <t xml:space="preserve">8.58173751831055</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64687442779541</t>
+    <t xml:space="preserve">8.64687538146973</t>
   </si>
   <si>
     <t xml:space="preserve">8.67130088806152</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61430644989014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63059139251709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75272178649902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82599925994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87485122680664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95627117156982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74457836151123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.858567237854</t>
+    <t xml:space="preserve">8.6143045425415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63058948516846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75272083282471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82599830627441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87485218048096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95627212524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74457931518555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85856819152832</t>
   </si>
   <si>
     <t xml:space="preserve">8.84228324890137</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91556262969971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03769397735596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00512409210205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94812870025635</t>
+    <t xml:space="preserve">8.91556167602539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03769302368164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00512504577637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94813060760498</t>
   </si>
   <si>
     <t xml:space="preserve">8.99698257446289</t>
@@ -440,7 +440,7 @@
     <t xml:space="preserve">9.19239139556885</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11911487579346</t>
+    <t xml:space="preserve">9.11911201477051</t>
   </si>
   <si>
     <t xml:space="preserve">9.14354038238525</t>
@@ -449,73 +449,73 @@
     <t xml:space="preserve">8.98069763183594</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13539791107178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16796779632568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15982437133789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18424987792969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1516809463501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07026195526123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96441555023193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92370223999023</t>
+    <t xml:space="preserve">9.13539695739746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16796684265137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15982341766357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.184250831604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15168285369873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07026290893555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96441459655762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92370414733887</t>
   </si>
   <si>
     <t xml:space="preserve">8.8015718460083</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79343032836914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8667106628418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90742015838623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89113616943359</t>
+    <t xml:space="preserve">8.79343223571777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86670875549316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90741920471191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89113712310791</t>
   </si>
   <si>
     <t xml:space="preserve">9.11097145080566</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20053291320801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28195571899414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35523223876953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3959436416626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32266426086426</t>
+    <t xml:space="preserve">9.20053482055664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28195381164551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35523319244385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39594554901123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32266712188721</t>
   </si>
   <si>
     <t xml:space="preserve">9.64834880828857</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60763835906982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9007511138916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99031448364258</t>
+    <t xml:space="preserve">9.60763931274414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90075302124023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99031639099121</t>
   </si>
   <si>
     <t xml:space="preserve">10.1205883026123</t>
@@ -524,13 +524,13 @@
     <t xml:space="preserve">10.1368722915649</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1775817871094</t>
+    <t xml:space="preserve">10.1775827407837</t>
   </si>
   <si>
     <t xml:space="preserve">10.1043043136597</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1531562805176</t>
+    <t xml:space="preserve">10.1531581878662</t>
   </si>
   <si>
     <t xml:space="preserve">10.0961608886719</t>
@@ -539,34 +539,34 @@
     <t xml:space="preserve">9.94146156311035</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90889358520508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77047824859619</t>
+    <t xml:space="preserve">9.90889263153076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77047920227051</t>
   </si>
   <si>
     <t xml:space="preserve">9.83561515808105</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91703701019287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79490375518799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77862167358398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78676223754883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9577465057373</t>
+    <t xml:space="preserve">9.91703796386719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7949047088623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77862358093262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78676319122314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95774555206299</t>
   </si>
   <si>
     <t xml:space="preserve">10.0147409439087</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99845600128174</t>
+    <t xml:space="preserve">9.99845790863037</t>
   </si>
   <si>
     <t xml:space="preserve">9.88446807861328</t>
@@ -575,19 +575,19 @@
     <t xml:space="preserve">9.86004161834717</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85190105438232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89260864257812</t>
+    <t xml:space="preserve">9.85190010070801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89260959625244</t>
   </si>
   <si>
     <t xml:space="preserve">10.2590036392212</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3404226303101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4625549316406</t>
+    <t xml:space="preserve">10.3404245376587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4625539779663</t>
   </si>
   <si>
     <t xml:space="preserve">10.5276918411255</t>
@@ -602,37 +602,37 @@
     <t xml:space="preserve">10.5358324050903</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5032653808594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5521173477173</t>
+    <t xml:space="preserve">10.5032644271851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5521183013916</t>
   </si>
   <si>
     <t xml:space="preserve">10.3485651016235</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4381284713745</t>
+    <t xml:space="preserve">10.4381275177002</t>
   </si>
   <si>
     <t xml:space="preserve">10.3241405487061</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3811340332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3648490905762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4218444824219</t>
+    <t xml:space="preserve">10.3811330795288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3648481369019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4218454360962</t>
   </si>
   <si>
     <t xml:space="preserve">10.4137029647827</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3729915618896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3892755508423</t>
+    <t xml:space="preserve">10.3729906082153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3892765045166</t>
   </si>
   <si>
     <t xml:space="preserve">10.2915706634521</t>
@@ -641,7 +641,7 @@
     <t xml:space="preserve">10.267144203186</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2264347076416</t>
+    <t xml:space="preserve">10.2264337539673</t>
   </si>
   <si>
     <t xml:space="preserve">10.1938667297363</t>
@@ -653,49 +653,49 @@
     <t xml:space="preserve">10.2182922363281</t>
   </si>
   <si>
-    <t xml:space="preserve">10.283429145813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4299879074097</t>
+    <t xml:space="preserve">10.2834300994873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.429986000061</t>
   </si>
   <si>
     <t xml:space="preserve">10.3322811126709</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2427196502686</t>
+    <t xml:space="preserve">10.2427186965942</t>
   </si>
   <si>
     <t xml:space="preserve">10.5846843719482</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6661071777344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7068157196045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7475280761719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.788236618042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.625394821167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8696594238281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8289480209351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0324993133545</t>
+    <t xml:space="preserve">10.6661062240601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7068176269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7475261688232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7882375717163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6253967285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8696584701538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8289470672607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0325002670288</t>
   </si>
   <si>
     <t xml:space="preserve">11.2360515594482</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4396028518677</t>
+    <t xml:space="preserve">11.4396018981934</t>
   </si>
   <si>
     <t xml:space="preserve">11.6838645935059</t>
@@ -704,13 +704,13 @@
     <t xml:space="preserve">11.0732097625732</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9917888641357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1546297073364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3174705505371</t>
+    <t xml:space="preserve">10.9917898178101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1546316146851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3174686431885</t>
   </si>
   <si>
     <t xml:space="preserve">11.2767610549927</t>
@@ -722,49 +722,52 @@
     <t xml:space="preserve">11.3581829071045</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4839181900024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5258283615112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5677404403687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4000940322876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0228843688965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1486186981201</t>
+    <t xml:space="preserve">11.4839191436768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5258293151855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5677433013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4000949859619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0228853225708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1486206054688</t>
   </si>
   <si>
     <t xml:space="preserve">11.2324447631836</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1905336380005</t>
+    <t xml:space="preserve">11.1905326843262</t>
   </si>
   <si>
     <t xml:space="preserve">11.2743577957153</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8971500396729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0647954940796</t>
+    <t xml:space="preserve">10.8971481323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0647964477539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3581838607788</t>
   </si>
   <si>
     <t xml:space="preserve">11.442006111145</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8552370071411</t>
+    <t xml:space="preserve">10.8552360534668</t>
   </si>
   <si>
     <t xml:space="preserve">10.6875867843628</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3254747390747</t>
+    <t xml:space="preserve">11.3254766464233</t>
   </si>
   <si>
     <t xml:space="preserve">11.282247543335</t>
@@ -773,10 +776,13 @@
     <t xml:space="preserve">11.1957931518555</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2390213012695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1525650024414</t>
+    <t xml:space="preserve">11.0228862762451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2390203475952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1525659561157</t>
   </si>
   <si>
     <t xml:space="preserve">10.9364309310913</t>
@@ -788,7 +794,7 @@
     <t xml:space="preserve">11.1093397140503</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9796590805054</t>
+    <t xml:space="preserve">10.9796581268311</t>
   </si>
   <si>
     <t xml:space="preserve">10.7635231018066</t>
@@ -797,13 +803,13 @@
     <t xml:space="preserve">10.590615272522</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8499774932861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7202968597412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6770696640015</t>
+    <t xml:space="preserve">10.8499784469604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7202959060669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6770677566528</t>
   </si>
   <si>
     <t xml:space="preserve">10.8067512512207</t>
@@ -812,13 +818,13 @@
     <t xml:space="preserve">10.8932046890259</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6338424682617</t>
+    <t xml:space="preserve">10.6338405609131</t>
   </si>
   <si>
     <t xml:space="preserve">11.4119281768799</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4551544189453</t>
+    <t xml:space="preserve">11.4551553726196</t>
   </si>
   <si>
     <t xml:space="preserve">11.3687009811401</t>
@@ -827,67 +833,67 @@
     <t xml:space="preserve">11.5416088104248</t>
   </si>
   <si>
-    <t xml:space="preserve">11.62806224823</t>
+    <t xml:space="preserve">11.6280632019043</t>
   </si>
   <si>
     <t xml:space="preserve">11.5848350524902</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4609346389771</t>
+    <t xml:space="preserve">10.4609327316284</t>
   </si>
   <si>
     <t xml:space="preserve">10.3312530517578</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3744812011719</t>
+    <t xml:space="preserve">10.3744792938232</t>
   </si>
   <si>
     <t xml:space="preserve">10.2880258560181</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5041599273682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0286645889282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94221115112305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59639358520508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63962173461914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81252861022949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85575485229492</t>
+    <t xml:space="preserve">10.5041608810425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0286636352539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94220924377441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59639453887939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63961982727051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81252956390381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85575580596924</t>
   </si>
   <si>
     <t xml:space="preserve">9.55316734313965</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03444194793701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81830883026123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86153507232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7750825881958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07767009735107</t>
+    <t xml:space="preserve">9.03444385528564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8183069229126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86153411865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77508163452148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07767105102539</t>
   </si>
   <si>
     <t xml:space="preserve">9.16412448883057</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25057888031006</t>
+    <t xml:space="preserve">9.25057983398438</t>
   </si>
   <si>
     <t xml:space="preserve">9.33703327178955</t>
@@ -896,49 +902,49 @@
     <t xml:space="preserve">9.2938060760498</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2447996139526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68284702301025</t>
+    <t xml:space="preserve">10.244800567627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68284797668457</t>
   </si>
   <si>
     <t xml:space="preserve">10.1583452224731</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98543834686279</t>
+    <t xml:space="preserve">9.98543739318848</t>
   </si>
   <si>
     <t xml:space="preserve">9.89898204803467</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76930141448975</t>
+    <t xml:space="preserve">9.76930236816406</t>
   </si>
   <si>
     <t xml:space="preserve">9.72607517242432</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46671295166016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5099401473999</t>
+    <t xml:space="preserve">9.46671199798584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50994110107422</t>
   </si>
   <si>
     <t xml:space="preserve">9.38025951385498</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42348575592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20735168457031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.071891784668</t>
+    <t xml:space="preserve">9.42348480224609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.207350730896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0718908309937</t>
   </si>
   <si>
     <t xml:space="preserve">10.2972898483276</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2077474594116</t>
+    <t xml:space="preserve">10.2077465057373</t>
   </si>
   <si>
     <t xml:space="preserve">10.1629772186279</t>
@@ -947,37 +953,37 @@
     <t xml:space="preserve">10.3420610427856</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4316024780273</t>
+    <t xml:space="preserve">10.431601524353</t>
   </si>
   <si>
     <t xml:space="preserve">10.3868312835693</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1182060241699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2525177001953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.476372718811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6554555892944</t>
+    <t xml:space="preserve">10.1182069778442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2525186538696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4763717651367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6554546356201</t>
   </si>
   <si>
     <t xml:space="preserve">10.7897682189941</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7449989318848</t>
+    <t xml:space="preserve">10.7449979782104</t>
   </si>
   <si>
     <t xml:space="preserve">10.5659141540527</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7002267837524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1031646728516</t>
+    <t xml:space="preserve">10.7002258300781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1031627655029</t>
   </si>
   <si>
     <t xml:space="preserve">10.9688520431519</t>
@@ -986,28 +992,25 @@
     <t xml:space="preserve">10.9240818023682</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8793096542358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1479349136353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2822484970093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2374773025513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4613313674927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.327018737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1927070617676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3717908859253</t>
+    <t xml:space="preserve">10.8793087005615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1479358673096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.237476348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4613304138184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3270177841187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1927061080933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3717889785767</t>
   </si>
   <si>
     <t xml:space="preserve">11.4165592193604</t>
@@ -1016,13 +1019,13 @@
     <t xml:space="preserve">11.0583934783936</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6404151916504</t>
+    <t xml:space="preserve">11.6404142379761</t>
   </si>
   <si>
     <t xml:space="preserve">11.7299566268921</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6851854324341</t>
+    <t xml:space="preserve">11.6851844787598</t>
   </si>
   <si>
     <t xml:space="preserve">11.7747259140015</t>
@@ -1031,7 +1034,7 @@
     <t xml:space="preserve">11.8194971084595</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8642673492432</t>
+    <t xml:space="preserve">11.8642683029175</t>
   </si>
   <si>
     <t xml:space="preserve">11.5508718490601</t>
@@ -1040,13 +1043,13 @@
     <t xml:space="preserve">11.5956439971924</t>
   </si>
   <si>
-    <t xml:space="preserve">10.521143913269</t>
+    <t xml:space="preserve">10.5211448669434</t>
   </si>
   <si>
     <t xml:space="preserve">11.0136222839355</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8345403671265</t>
+    <t xml:space="preserve">10.8345394134521</t>
   </si>
   <si>
     <t xml:space="preserve">11.9985799789429</t>
@@ -1058,13 +1061,13 @@
     <t xml:space="preserve">12.0433511734009</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1328945159912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2224359512329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1776638031006</t>
+    <t xml:space="preserve">12.1328926086426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.22243309021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1776657104492</t>
   </si>
   <si>
     <t xml:space="preserve">12.356746673584</t>
@@ -1073,19 +1076,19 @@
     <t xml:space="preserve">12.2672061920166</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4015188217163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.311975479126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6701440811157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6253728866577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.580602645874</t>
+    <t xml:space="preserve">12.4015197753906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3119773864746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6701421737671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6253719329834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5806016921997</t>
   </si>
   <si>
     <t xml:space="preserve">10.6106863021851</t>
@@ -1097,70 +1100,67 @@
     <t xml:space="preserve">10.0734357833862</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0286636352539</t>
-  </si>
-  <si>
     <t xml:space="preserve">12.491060256958</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9090375900269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1626224517822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6998710632324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8789567947388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0132675170898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1475801467896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2371206283569</t>
+    <t xml:space="preserve">11.9090385437012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1626205444336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6998720169067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8789539337158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0132684707642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1475811004639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2371215820312</t>
   </si>
   <si>
     <t xml:space="preserve">14.1923513412476</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9237270355225</t>
+    <t xml:space="preserve">13.9237279891968</t>
   </si>
   <si>
     <t xml:space="preserve">13.9684972763062</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7894134521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2818937301636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8341846466064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5207901000977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4312477111816</t>
+    <t xml:space="preserve">13.7894124984741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2818918228149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8341836929321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5207891464233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.431245803833</t>
   </si>
   <si>
     <t xml:space="preserve">13.565559387207</t>
   </si>
   <si>
-    <t xml:space="preserve">13.610330581665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7004632949829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7905979156494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8356666564941</t>
+    <t xml:space="preserve">13.6103296279907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7004652023315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7905988693237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8356647491455</t>
   </si>
   <si>
     <t xml:space="preserve">13.6553974151611</t>
@@ -1169,28 +1169,25 @@
     <t xml:space="preserve">13.5201950073242</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6103315353394</t>
-  </si>
-  <si>
     <t xml:space="preserve">13.2948589324951</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1596584320068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.069522857666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9793872833252</t>
+    <t xml:space="preserve">13.1596574783325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0695219039917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9793863296509</t>
   </si>
   <si>
     <t xml:space="preserve">12.708984375</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5737819671631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6188497543335</t>
+    <t xml:space="preserve">12.5737810134888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6188488006592</t>
   </si>
   <si>
     <t xml:space="preserve">13.3399257659912</t>
@@ -1202,13 +1199,13 @@
     <t xml:space="preserve">13.4751281738281</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9343204498291</t>
+    <t xml:space="preserve">12.9343194961548</t>
   </si>
   <si>
     <t xml:space="preserve">12.7540502548218</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8441858291626</t>
+    <t xml:space="preserve">12.8441848754883</t>
   </si>
   <si>
     <t xml:space="preserve">14.0610036849976</t>
@@ -1223,43 +1220,43 @@
     <t xml:space="preserve">14.3314056396484</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4215421676636</t>
+    <t xml:space="preserve">14.4215412139893</t>
   </si>
   <si>
     <t xml:space="preserve">14.3764734268188</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5116777420044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4666090011597</t>
+    <t xml:space="preserve">14.5116758346558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4666080474854</t>
   </si>
   <si>
     <t xml:space="preserve">14.6018114089966</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6919441223145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8722152709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2327547073364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0074148178101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3228893280029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.187686920166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.224235534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9538316726685</t>
+    <t xml:space="preserve">14.6919460296631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8722143173218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2327527999878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0074157714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.32288646698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1876859664917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2242336273193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9538345336914</t>
   </si>
   <si>
     <t xml:space="preserve">16.8551788330078</t>
@@ -1268,22 +1265,22 @@
     <t xml:space="preserve">16.3143692016602</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9903812408447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8101081848145</t>
+    <t xml:space="preserve">16.9903793334961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8101100921631</t>
   </si>
   <si>
     <t xml:space="preserve">17.7565231323242</t>
   </si>
   <si>
-    <t xml:space="preserve">18.026927947998</t>
+    <t xml:space="preserve">18.0269260406494</t>
   </si>
   <si>
     <t xml:space="preserve">17.9367923736572</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3509159088135</t>
+    <t xml:space="preserve">17.3509178161621</t>
   </si>
   <si>
     <t xml:space="preserve">17.4410533905029</t>
@@ -1292,16 +1289,16 @@
     <t xml:space="preserve">17.4861183166504</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0354423522949</t>
+    <t xml:space="preserve">17.0354461669922</t>
   </si>
   <si>
     <t xml:space="preserve">16.6298408508301</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7199726104736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4045028686523</t>
+    <t xml:space="preserve">16.7199745178223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4045066833496</t>
   </si>
   <si>
     <t xml:space="preserve">16.6749076843262</t>
@@ -1310,46 +1307,46 @@
     <t xml:space="preserve">16.9453105926514</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7650413513184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.863697052002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9988985061646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4946346282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3594379425049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1791687011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5847702026367</t>
+    <t xml:space="preserve">16.765043258667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8636989593506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9988956451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4946365356445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3594360351562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1791667938232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5847721099854</t>
   </si>
   <si>
     <t xml:space="preserve">16.5397052764893</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6834278106689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0890350341797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5932922363281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2693023681641</t>
+    <t xml:space="preserve">15.6834239959717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0890312194824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5932903289795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2693004608154</t>
   </si>
   <si>
     <t xml:space="preserve">17.1255798339844</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5762538909912</t>
+    <t xml:space="preserve">17.5762519836426</t>
   </si>
   <si>
     <t xml:space="preserve">17.666389465332</t>
@@ -1358,43 +1355,43 @@
     <t xml:space="preserve">17.8466567993164</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5677356719971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3874645233154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7480030059814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3789482116699</t>
+    <t xml:space="preserve">18.5677337646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3874664306641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7480049133301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3789463043213</t>
   </si>
   <si>
     <t xml:space="preserve">20.0098896026611</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5506954193115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4605598449707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2802925109863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3704261779785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1000232696533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6408309936523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7309665679932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4435253143311</t>
+    <t xml:space="preserve">20.5506935119629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.460563659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.280294418335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3704280853271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1000213623047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6408290863037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7309646606445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4435234069824</t>
   </si>
   <si>
     <t xml:space="preserve">21.902717590332</t>
@@ -1403,7 +1400,10 @@
     <t xml:space="preserve">21.5361442565918</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1695690155029</t>
+    <t xml:space="preserve">21.9027194976807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1695709228516</t>
   </si>
   <si>
     <t xml:space="preserve">21.7194309234619</t>
@@ -1412,13 +1412,13 @@
     <t xml:space="preserve">22.360933303833</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4525756835938</t>
+    <t xml:space="preserve">22.4525737762451</t>
   </si>
   <si>
     <t xml:space="preserve">22.269287109375</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0860023498535</t>
+    <t xml:space="preserve">22.0860042572021</t>
   </si>
   <si>
     <t xml:space="preserve">21.9943599700928</t>
@@ -1427,25 +1427,25 @@
     <t xml:space="preserve">21.6277866363525</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2773628234863</t>
+    <t xml:space="preserve">23.277364730835</t>
   </si>
   <si>
     <t xml:space="preserve">22.9107913970947</t>
   </si>
   <si>
-    <t xml:space="preserve">22.727502822876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1776447296143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6358604431152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0024356842041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0940780639648</t>
+    <t xml:space="preserve">22.7275047302246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1776466369629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6358623504639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0024337768555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0940761566162</t>
   </si>
   <si>
     <t xml:space="preserve">24.1021518707275</t>
@@ -1454,13 +1454,13 @@
     <t xml:space="preserve">24.2854385375977</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9269409179688</t>
+    <t xml:space="preserve">24.9269428253174</t>
   </si>
   <si>
     <t xml:space="preserve">26.2099456787109</t>
   </si>
   <si>
-    <t xml:space="preserve">26.851448059082</t>
+    <t xml:space="preserve">26.8514461517334</t>
   </si>
   <si>
     <t xml:space="preserve">26.6681594848633</t>
@@ -1472,94 +1472,94 @@
     <t xml:space="preserve">26.4848747253418</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7598037719727</t>
+    <t xml:space="preserve">26.759801864624</t>
   </si>
   <si>
     <t xml:space="preserve">26.5765171051025</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3015899658203</t>
+    <t xml:space="preserve">26.301586151123</t>
   </si>
   <si>
     <t xml:space="preserve">25.5684413909912</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0347309112549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1425266265869</t>
+    <t xml:space="preserve">27.0347328186035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1425247192383</t>
   </si>
   <si>
     <t xml:space="preserve">28.4093818664551</t>
   </si>
   <si>
-    <t xml:space="preserve">28.134449005127</t>
+    <t xml:space="preserve">28.1344528198242</t>
   </si>
   <si>
     <t xml:space="preserve">28.2260932922363</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3646831512451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4570770263672</t>
+    <t xml:space="preserve">28.3646850585938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4570789337158</t>
   </si>
   <si>
     <t xml:space="preserve">28.0875053405762</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9951095581055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9027214050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7179336547852</t>
+    <t xml:space="preserve">27.9951114654541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9027194976807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7179317474365</t>
   </si>
   <si>
     <t xml:space="preserve">29.1038303375244</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9353694915771</t>
+    <t xml:space="preserve">29.9353675842285</t>
   </si>
   <si>
     <t xml:space="preserve">29.7505798339844</t>
   </si>
   <si>
-    <t xml:space="preserve">29.381010055542</t>
+    <t xml:space="preserve">29.3810081481934</t>
   </si>
   <si>
     <t xml:space="preserve">28.8266525268555</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9190425872803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7342548370361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.011438369751</t>
+    <t xml:space="preserve">28.9190406799316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7342567443848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0114345550537</t>
   </si>
   <si>
     <t xml:space="preserve">29.8429737091064</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1201496124268</t>
+    <t xml:space="preserve">30.1201553344727</t>
   </si>
   <si>
     <t xml:space="preserve">30.2125473022461</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0277633666992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3973331451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1364765167236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8593006134033</t>
+    <t xml:space="preserve">30.0277614593506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3973350524902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1364803314209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8592967987061</t>
   </si>
   <si>
     <t xml:space="preserve">31.0440826416016</t>
@@ -1571,7 +1571,7 @@
     <t xml:space="preserve">30.489725112915</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2886161804199</t>
+    <t xml:space="preserve">29.2886180877686</t>
   </si>
   <si>
     <t xml:space="preserve">29.4734020233154</t>
@@ -1583,70 +1583,70 @@
     <t xml:space="preserve">33.3539085388184</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5550193786621</t>
+    <t xml:space="preserve">34.5550270080566</t>
   </si>
   <si>
     <t xml:space="preserve">34.0930557250977</t>
   </si>
   <si>
-    <t xml:space="preserve">35.8485260009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.4192047119141</t>
+    <t xml:space="preserve">35.8485221862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.4192085266113</t>
   </si>
   <si>
     <t xml:space="preserve">40.0986099243164</t>
   </si>
   <si>
-    <t xml:space="preserve">37.2344207763672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.881175994873</t>
+    <t xml:space="preserve">37.2344169616699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.8811798095703</t>
   </si>
   <si>
     <t xml:space="preserve">38.1583518981934</t>
   </si>
   <si>
-    <t xml:space="preserve">37.6039924621582</t>
+    <t xml:space="preserve">37.6039962768555</t>
   </si>
   <si>
     <t xml:space="preserve">37.6963882446289</t>
   </si>
   <si>
-    <t xml:space="preserve">37.7887840270996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.1420364379883</t>
+    <t xml:space="preserve">37.7887878417969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.1420249938965</t>
   </si>
   <si>
     <t xml:space="preserve">38.5279273986816</t>
   </si>
   <si>
-    <t xml:space="preserve">38.3431434631348</t>
+    <t xml:space="preserve">38.3431396484375</t>
   </si>
   <si>
     <t xml:space="preserve">36.4952812194824</t>
   </si>
   <si>
-    <t xml:space="preserve">35.9409217834473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.402889251709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.6800689697266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.9735679626465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.0659599304199</t>
+    <t xml:space="preserve">35.94091796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.4028854370117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.680061340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.9735641479492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.0659637451172</t>
   </si>
   <si>
     <t xml:space="preserve">38.4355316162109</t>
   </si>
   <si>
-    <t xml:space="preserve">38.8051071166992</t>
+    <t xml:space="preserve">38.805103302002</t>
   </si>
   <si>
     <t xml:space="preserve">39.3594665527344</t>
@@ -1658,22 +1658,22 @@
     <t xml:space="preserve">40.006217956543</t>
   </si>
   <si>
-    <t xml:space="preserve">40.5605773925781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.6529693603516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.9464721679688</t>
+    <t xml:space="preserve">40.5605735778809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.6529655456543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.946475982666</t>
   </si>
   <si>
     <t xml:space="preserve">41.114933013916</t>
   </si>
   <si>
-    <t xml:space="preserve">40.9301452636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.3160438537598</t>
+    <t xml:space="preserve">40.9301490783691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.3160400390625</t>
   </si>
   <si>
     <t xml:space="preserve">43.5171546936035</t>
@@ -1682,7 +1682,7 @@
     <t xml:space="preserve">44.0715141296387</t>
   </si>
   <si>
-    <t xml:space="preserve">43.8867263793945</t>
+    <t xml:space="preserve">43.8867225646973</t>
   </si>
   <si>
     <t xml:space="preserve">43.7019424438477</t>
@@ -1694,13 +1694,13 @@
     <t xml:space="preserve">44.3486938476562</t>
   </si>
   <si>
-    <t xml:space="preserve">44.9954414367676</t>
+    <t xml:space="preserve">44.9954490661621</t>
   </si>
   <si>
     <t xml:space="preserve">44.8106575012207</t>
   </si>
   <si>
-    <t xml:space="preserve">44.5334777832031</t>
+    <t xml:space="preserve">44.5334815979004</t>
   </si>
   <si>
     <t xml:space="preserve">43.7943344116211</t>
@@ -1712,43 +1712,43 @@
     <t xml:space="preserve">41.3921127319336</t>
   </si>
   <si>
-    <t xml:space="preserve">41.8540802001953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.5769004821777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.2073249816895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.1910057067871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.4518585205078</t>
+    <t xml:space="preserve">41.854076385498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.5768966674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.2073287963867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.1910018920898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.4518623352051</t>
   </si>
   <si>
     <t xml:space="preserve">38.9898910522461</t>
   </si>
   <si>
-    <t xml:space="preserve">39.1746788024902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.5442504882812</t>
+    <t xml:space="preserve">39.174674987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.5442543029785</t>
   </si>
   <si>
     <t xml:space="preserve">40.7453575134277</t>
   </si>
   <si>
-    <t xml:space="preserve">41.0225410461426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.7290382385254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.9138221740723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.4681816101074</t>
+    <t xml:space="preserve">41.0225448608398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.7290344238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.9138259887695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.4681777954102</t>
   </si>
   <si>
     <t xml:space="preserve">39.6366424560547</t>
@@ -1760,7 +1760,7 @@
     <t xml:space="preserve">39.2670707702637</t>
   </si>
   <si>
-    <t xml:space="preserve">37.3268203735352</t>
+    <t xml:space="preserve">37.3268165588379</t>
   </si>
   <si>
     <t xml:space="preserve">38.8974952697754</t>
@@ -1769,10 +1769,10 @@
     <t xml:space="preserve">37.5116004943848</t>
   </si>
   <si>
-    <t xml:space="preserve">38.712718963623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.0822830200195</t>
+    <t xml:space="preserve">38.7127151489258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.0822868347168</t>
   </si>
   <si>
     <t xml:space="preserve">36.7724571228027</t>
@@ -1787,7 +1787,7 @@
     <t xml:space="preserve">35.3865585327148</t>
   </si>
   <si>
-    <t xml:space="preserve">36.0333137512207</t>
+    <t xml:space="preserve">36.033317565918</t>
   </si>
   <si>
     <t xml:space="preserve">34.1854515075684</t>
@@ -1796,52 +1796,52 @@
     <t xml:space="preserve">33.7234840393066</t>
   </si>
   <si>
-    <t xml:space="preserve">33.1691284179688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6147651672363</t>
+    <t xml:space="preserve">33.169132232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6147689819336</t>
   </si>
   <si>
     <t xml:space="preserve">33.6310958862305</t>
   </si>
   <si>
-    <t xml:space="preserve">32.707160949707</t>
+    <t xml:space="preserve">32.7071647644043</t>
   </si>
   <si>
     <t xml:space="preserve">31.9680156707764</t>
   </si>
   <si>
-    <t xml:space="preserve">32.0604133605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4136600494385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6908359527588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2451972961426</t>
+    <t xml:space="preserve">32.0604095458984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4136581420898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6908378601074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2451934814453</t>
   </si>
   <si>
     <t xml:space="preserve">32.7995529174805</t>
   </si>
   <si>
-    <t xml:space="preserve">33.9082679748535</t>
+    <t xml:space="preserve">33.9082717895508</t>
   </si>
   <si>
     <t xml:space="preserve">35.1093826293945</t>
   </si>
   <si>
-    <t xml:space="preserve">34.739803314209</t>
+    <t xml:space="preserve">34.7398071289062</t>
   </si>
   <si>
     <t xml:space="preserve">35.0169906616211</t>
   </si>
   <si>
-    <t xml:space="preserve">32.337589263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4299812316895</t>
+    <t xml:space="preserve">32.3375854492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4299774169922</t>
   </si>
   <si>
     <t xml:space="preserve">32.5223731994629</t>
@@ -1850,13 +1850,13 @@
     <t xml:space="preserve">31.5060482025146</t>
   </si>
   <si>
-    <t xml:space="preserve">31.3212642669678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.55224609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9218215942383</t>
+    <t xml:space="preserve">31.3212661743164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5522480010986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9218196868896</t>
   </si>
   <si>
     <t xml:space="preserve">32.1528015136719</t>
@@ -1880,10 +1880,10 @@
     <t xml:space="preserve">30.3511352539062</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7804508209229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3643836975098</t>
+    <t xml:space="preserve">28.7804527282715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3643817901611</t>
   </si>
   <si>
     <t xml:space="preserve">28.3180351257324</t>
@@ -1892,25 +1892,25 @@
     <t xml:space="preserve">27.8082180023193</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7618713378906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0862998962402</t>
+    <t xml:space="preserve">27.7618732452393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0863018035889</t>
   </si>
   <si>
     <t xml:space="preserve">27.9936084747314</t>
   </si>
   <si>
-    <t xml:space="preserve">28.642463684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5230579376221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1255722045898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5694046020508</t>
+    <t xml:space="preserve">28.6424655914307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5230598449707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1255683898926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5694065093994</t>
   </si>
   <si>
     <t xml:space="preserve">29.105936050415</t>
@@ -1934,13 +1934,13 @@
     <t xml:space="preserve">26.186071395874</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6031970977783</t>
+    <t xml:space="preserve">26.6031951904297</t>
   </si>
   <si>
     <t xml:space="preserve">26.2324199676514</t>
   </si>
   <si>
-    <t xml:space="preserve">26.556848526001</t>
+    <t xml:space="preserve">26.5568466186523</t>
   </si>
   <si>
     <t xml:space="preserve">26.3251132965088</t>
@@ -1949,10 +1949,10 @@
     <t xml:space="preserve">25.8152980804443</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6299076080322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2591304779053</t>
+    <t xml:space="preserve">25.6299095153809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2591323852539</t>
   </si>
   <si>
     <t xml:space="preserve">24.7029685974121</t>
@@ -1961,13 +1961,13 @@
     <t xml:space="preserve">24.6566200256348</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9614143371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.729679107666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0273971557617</t>
+    <t xml:space="preserve">23.9614162445068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7296772003174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0273952484131</t>
   </si>
   <si>
     <t xml:space="preserve">24.7956619262695</t>
@@ -1976,43 +1976,43 @@
     <t xml:space="preserve">24.2858448028564</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6102733612061</t>
+    <t xml:space="preserve">24.6102714538574</t>
   </si>
   <si>
     <t xml:space="preserve">24.3321914672852</t>
   </si>
   <si>
-    <t xml:space="preserve">24.517578125</t>
+    <t xml:space="preserve">24.5175800323486</t>
   </si>
   <si>
     <t xml:space="preserve">24.3785381317139</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4712333679199</t>
+    <t xml:space="preserve">24.4712314605713</t>
   </si>
   <si>
     <t xml:space="preserve">23.8687210083008</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5442905426025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.100456237793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4979457855225</t>
+    <t xml:space="preserve">23.5442924499512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1004543304443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4979438781738</t>
   </si>
   <si>
     <t xml:space="preserve">23.8223743438721</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9150676727295</t>
+    <t xml:space="preserve">23.9150657653809</t>
   </si>
   <si>
     <t xml:space="preserve">24.1931495666504</t>
   </si>
   <si>
-    <t xml:space="preserve">24.888355255127</t>
+    <t xml:space="preserve">24.8883571624756</t>
   </si>
   <si>
     <t xml:space="preserve">25.5835609436035</t>
@@ -2042,13 +2042,13 @@
     <t xml:space="preserve">25.1200923919678</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0077610015869</t>
+    <t xml:space="preserve">24.0077629089355</t>
   </si>
   <si>
     <t xml:space="preserve">23.4515972137451</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1271686553955</t>
+    <t xml:space="preserve">23.1271705627441</t>
   </si>
   <si>
     <t xml:space="preserve">23.0808200836182</t>
@@ -2060,22 +2060,22 @@
     <t xml:space="preserve">23.6369857788086</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5906391143799</t>
+    <t xml:space="preserve">23.5906410217285</t>
   </si>
   <si>
     <t xml:space="preserve">23.4052505493164</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2662105560303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3589057922363</t>
+    <t xml:space="preserve">23.2662086486816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3589038848877</t>
   </si>
   <si>
     <t xml:space="preserve">22.8027381896973</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6173534393311</t>
+    <t xml:space="preserve">22.6173496246338</t>
   </si>
   <si>
     <t xml:space="preserve">23.1735153198242</t>
@@ -2087,13 +2087,13 @@
     <t xml:space="preserve">21.9684925079346</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5513687133789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2732887268066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.856164932251</t>
+    <t xml:space="preserve">21.5513706207275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.273286819458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8561630249023</t>
   </si>
   <si>
     <t xml:space="preserve">20.7171230316162</t>
@@ -2102,16 +2102,16 @@
     <t xml:space="preserve">19.9755687713623</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1609592437744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2073020935059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8365287780762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5584468841553</t>
+    <t xml:space="preserve">20.1609573364258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2073040008545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8365306854248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5584487915039</t>
   </si>
   <si>
     <t xml:space="preserve">19.604793548584</t>
@@ -2120,19 +2120,19 @@
     <t xml:space="preserve">19.9292240142822</t>
   </si>
   <si>
-    <t xml:space="preserve">20.068265914917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1146125793457</t>
+    <t xml:space="preserve">20.0682640075684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1146106719971</t>
   </si>
   <si>
     <t xml:space="preserve">20.8098182678223</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9952030181885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5780811309814</t>
+    <t xml:space="preserve">20.9952049255371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5780830383301</t>
   </si>
   <si>
     <t xml:space="preserve">21.0878982543945</t>
@@ -2150,25 +2150,25 @@
     <t xml:space="preserve">22.3856143951416</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3392677307129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6833324432373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5639266967773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4248847961426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1664390563965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2127838134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.842004776001</t>
+    <t xml:space="preserve">22.3392696380615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6833305358887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5639247894287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4248867034912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1664371490479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2127857208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8420066833496</t>
   </si>
   <si>
     <t xml:space="preserve">25.7689476013184</t>
@@ -2183,46 +2183,46 @@
     <t xml:space="preserve">25.5372142791748</t>
   </si>
   <si>
-    <t xml:space="preserve">25.305477142334</t>
+    <t xml:space="preserve">25.3054790496826</t>
   </si>
   <si>
     <t xml:space="preserve">25.6762542724609</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4908695220947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6691799163818</t>
+    <t xml:space="preserve">25.4908657073975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6691780090332</t>
   </si>
   <si>
     <t xml:space="preserve">27.2057075500488</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4837894439697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2984027862549</t>
+    <t xml:space="preserve">27.4837875366211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2984008789062</t>
   </si>
   <si>
     <t xml:space="preserve">27.5764846801758</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0399551391602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1789932250977</t>
+    <t xml:space="preserve">28.0399532318115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1789951324463</t>
   </si>
   <si>
     <t xml:space="preserve">28.2716884613037</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1326484680176</t>
+    <t xml:space="preserve">28.1326465606689</t>
   </si>
   <si>
     <t xml:space="preserve">27.4374408721924</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5301361083984</t>
+    <t xml:space="preserve">27.5301380157471</t>
   </si>
   <si>
     <t xml:space="preserve">26.093376159668</t>
@@ -2231,13 +2231,13 @@
     <t xml:space="preserve">25.39817237854</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9417819976807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2002296447754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.153881072998</t>
+    <t xml:space="preserve">22.941780090332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2002277374268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1538791656494</t>
   </si>
   <si>
     <t xml:space="preserve">22.1075344085693</t>
@@ -2246,10 +2246,10 @@
     <t xml:space="preserve">22.7100448608398</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9881267547607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2198600769043</t>
+    <t xml:space="preserve">22.9881248474121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2198619842529</t>
   </si>
   <si>
     <t xml:space="preserve">21.8294506072998</t>
@@ -2258,19 +2258,19 @@
     <t xml:space="preserve">20.6244277954102</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6707744598389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4853897094727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2536525726318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5317344665527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1342449188232</t>
+    <t xml:space="preserve">20.6707763671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.485387802124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2536544799805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5317325592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1342468261719</t>
   </si>
   <si>
     <t xml:space="preserve">21.7831058502197</t>
@@ -2285,25 +2285,25 @@
     <t xml:space="preserve">21.3196334838867</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8757972717285</t>
+    <t xml:space="preserve">21.8757991790771</t>
   </si>
   <si>
     <t xml:space="preserve">21.1805953979492</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9025115966797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6679420471191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4127311706543</t>
+    <t xml:space="preserve">20.9025096893311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6679439544678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4127330780029</t>
   </si>
   <si>
     <t xml:space="preserve">20.6213912963867</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5748443603516</t>
+    <t xml:space="preserve">20.5748424530029</t>
   </si>
   <si>
     <t xml:space="preserve">20.3886451721191</t>
@@ -2312,19 +2312,19 @@
     <t xml:space="preserve">21.3661842346191</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9937877655029</t>
+    <t xml:space="preserve">20.9937858581543</t>
   </si>
   <si>
     <t xml:space="preserve">20.9006900787354</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0403366088867</t>
+    <t xml:space="preserve">21.0403385162354</t>
   </si>
   <si>
     <t xml:space="preserve">21.1799850463867</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2265338897705</t>
+    <t xml:space="preserve">21.2265357971191</t>
   </si>
   <si>
     <t xml:space="preserve">20.9472389221191</t>
@@ -2336,7 +2336,7 @@
     <t xml:space="preserve">20.3420963287354</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2489986419678</t>
+    <t xml:space="preserve">20.2489967346191</t>
   </si>
   <si>
     <t xml:space="preserve">20.1558990478516</t>
@@ -2354,10 +2354,10 @@
     <t xml:space="preserve">19.7835025787354</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7369537353516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5973033905029</t>
+    <t xml:space="preserve">19.7369556427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5973052978516</t>
   </si>
   <si>
     <t xml:space="preserve">19.4111080169678</t>
@@ -2375,7 +2375,7 @@
     <t xml:space="preserve">20.2024478912354</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4351959228516</t>
+    <t xml:space="preserve">20.4351940155029</t>
   </si>
   <si>
     <t xml:space="preserve">19.4576568603516</t>
@@ -2384,7 +2384,7 @@
     <t xml:space="preserve">19.0387134552002</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9696998596191</t>
+    <t xml:space="preserve">19.9697017669678</t>
   </si>
   <si>
     <t xml:space="preserve">19.9231510162354</t>
@@ -2393,19 +2393,19 @@
     <t xml:space="preserve">19.3645572662354</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1783599853516</t>
+    <t xml:space="preserve">19.1783618927002</t>
   </si>
   <si>
     <t xml:space="preserve">18.8990631103516</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1318111419678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6197662353516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8525123596191</t>
+    <t xml:space="preserve">19.1318092346191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6197681427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8525161743164</t>
   </si>
   <si>
     <t xml:space="preserve">18.7128677368164</t>
@@ -2423,19 +2423,19 @@
     <t xml:space="preserve">18.4708099365234</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3963317871094</t>
+    <t xml:space="preserve">18.3963298797607</t>
   </si>
   <si>
     <t xml:space="preserve">18.3404712677002</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2287540435791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2101306915283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.968074798584</t>
+    <t xml:space="preserve">18.2287521362305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.210132598877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9680728912354</t>
   </si>
   <si>
     <t xml:space="preserve">17.6701583862305</t>
@@ -2462,19 +2462,19 @@
     <t xml:space="preserve">16.7577896118164</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2232856750488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3350028991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.409481048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6515369415283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7260189056396</t>
+    <t xml:space="preserve">17.2232837677002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3350048065186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4094829559326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.651538848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7260208129883</t>
   </si>
   <si>
     <t xml:space="preserve">17.7073993682861</t>
@@ -2492,16 +2492,16 @@
     <t xml:space="preserve">16.5715923309326</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5529727935791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0929470062256</t>
+    <t xml:space="preserve">16.5529747009277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.092945098877</t>
   </si>
   <si>
     <t xml:space="preserve">16.9253673553467</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2736759185791</t>
+    <t xml:space="preserve">16.2736778259277</t>
   </si>
   <si>
     <t xml:space="preserve">16.0130004882812</t>
@@ -2513,13 +2513,13 @@
     <t xml:space="preserve">16.2364387512207</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2922973632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.037088394165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.813648223877</t>
+    <t xml:space="preserve">16.2922954559326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0370864868164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8136501312256</t>
   </si>
   <si>
     <t xml:space="preserve">16.404016494751</t>
@@ -2531,40 +2531,40 @@
     <t xml:space="preserve">16.3295364379883</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1805782318115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3667755126953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4598751068115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7709436416626</t>
+    <t xml:space="preserve">16.1805763244629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3667736053467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4598731994629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7709426879883</t>
   </si>
   <si>
     <t xml:space="preserve">15.7337017059326</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8826608657837</t>
+    <t xml:space="preserve">15.882661819458</t>
   </si>
   <si>
     <t xml:space="preserve">16.161958694458</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1433391571045</t>
+    <t xml:space="preserve">16.1433372497559</t>
   </si>
   <si>
     <t xml:space="preserve">16.5157337188721</t>
   </si>
   <si>
-    <t xml:space="preserve">16.478494644165</t>
+    <t xml:space="preserve">16.4784927368164</t>
   </si>
   <si>
     <t xml:space="preserve">16.6460704803467</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8695106506348</t>
+    <t xml:space="preserve">16.8695087432861</t>
   </si>
   <si>
     <t xml:space="preserve">17.1115665435791</t>
@@ -2582,10 +2582,10 @@
     <t xml:space="preserve">17.3536224365234</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3722438812256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9998474121094</t>
+    <t xml:space="preserve">17.372241973877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.999849319458</t>
   </si>
   <si>
     <t xml:space="preserve">17.0743255615234</t>
@@ -2612,19 +2612,19 @@
     <t xml:space="preserve">16.5902118682861</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3481559753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3109169006348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.199197769165</t>
+    <t xml:space="preserve">16.3481540679932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3109149932861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1991958618164</t>
   </si>
   <si>
     <t xml:space="preserve">16.6088333129883</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0502376556396</t>
+    <t xml:space="preserve">16.0502395629883</t>
   </si>
   <si>
     <t xml:space="preserve">16.2550563812256</t>
@@ -2633,7 +2633,7 @@
     <t xml:space="preserve">16.1060981750488</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1674251556396</t>
+    <t xml:space="preserve">17.1674270629883</t>
   </si>
   <si>
     <t xml:space="preserve">18.0053157806396</t>
@@ -2642,10 +2642,10 @@
     <t xml:space="preserve">17.9122161865234</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4653434753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9494571685791</t>
+    <t xml:space="preserve">17.4653415679932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9494552612305</t>
   </si>
   <si>
     <t xml:space="preserve">17.8749771118164</t>
@@ -2657,10 +2657,10 @@
     <t xml:space="preserve">17.5491313934326</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3629341125488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5025787353516</t>
+    <t xml:space="preserve">17.3629322052002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5025806427002</t>
   </si>
   <si>
     <t xml:space="preserve">17.4560317993164</t>
@@ -2672,7 +2672,7 @@
     <t xml:space="preserve">18.0611743927002</t>
   </si>
   <si>
-    <t xml:space="preserve">17.828426361084</t>
+    <t xml:space="preserve">17.8284282684326</t>
   </si>
   <si>
     <t xml:space="preserve">18.3981628417969</t>
@@ -2684,7 +2684,7 @@
     <t xml:space="preserve">18.6370983123779</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8282508850098</t>
+    <t xml:space="preserve">18.8282489776611</t>
   </si>
   <si>
     <t xml:space="preserve">19.1149749755859</t>
@@ -2693,7 +2693,7 @@
     <t xml:space="preserve">18.9716129302979</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2105503082275</t>
+    <t xml:space="preserve">19.2105484008789</t>
   </si>
   <si>
     <t xml:space="preserve">20.0707225799561</t>
@@ -2702,7 +2702,7 @@
     <t xml:space="preserve">20.8353214263916</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0264701843262</t>
+    <t xml:space="preserve">21.0264720916748</t>
   </si>
   <si>
     <t xml:space="preserve">20.9308967590332</t>
@@ -2726,7 +2726,7 @@
     <t xml:space="preserve">21.217622756958</t>
   </si>
   <si>
-    <t xml:space="preserve">20.73974609375</t>
+    <t xml:space="preserve">20.7397480010986</t>
   </si>
   <si>
     <t xml:space="preserve">21.1220455169678</t>
@@ -2735,7 +2735,7 @@
     <t xml:space="preserve">19.8795719146729</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7840003967285</t>
+    <t xml:space="preserve">19.7839984893799</t>
   </si>
   <si>
     <t xml:space="preserve">20.3574466705322</t>
@@ -2744,22 +2744,22 @@
     <t xml:space="preserve">19.9751472473145</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6884231567383</t>
+    <t xml:space="preserve">19.6884250640869</t>
   </si>
   <si>
     <t xml:space="preserve">21.3131942749023</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4087696075439</t>
+    <t xml:space="preserve">21.4087715148926</t>
   </si>
   <si>
     <t xml:space="preserve">21.5999221801758</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5043468475342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.886646270752</t>
+    <t xml:space="preserve">21.5043449401855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8866443634033</t>
   </si>
   <si>
     <t xml:space="preserve">22.5556697845459</t>
@@ -2768,10 +2768,10 @@
     <t xml:space="preserve">22.7468185424805</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9379692077637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8423919677734</t>
+    <t xml:space="preserve">22.937967300415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8423938751221</t>
   </si>
   <si>
     <t xml:space="preserve">23.1291179656982</t>
@@ -2783,7 +2783,7 @@
     <t xml:space="preserve">22.0777950286865</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9822196960449</t>
+    <t xml:space="preserve">21.9822216033936</t>
   </si>
   <si>
     <t xml:space="preserve">22.1733722686768</t>
@@ -2792,7 +2792,7 @@
     <t xml:space="preserve">21.6954956054688</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7910690307617</t>
+    <t xml:space="preserve">21.7910709381104</t>
   </si>
   <si>
     <t xml:space="preserve">22.6512451171875</t>
@@ -19187,7 +19187,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G610" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -19239,7 +19239,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G612" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -19291,7 +19291,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G614" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -19317,7 +19317,7 @@
         <v>12.75</v>
       </c>
       <c r="G615" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -19343,7 +19343,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G616" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -19395,7 +19395,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G618" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -19421,7 +19421,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G619" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -19447,7 +19447,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G620" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -19473,7 +19473,7 @@
         <v>12.75</v>
       </c>
       <c r="G621" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -19499,7 +19499,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G622" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -19525,7 +19525,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G623" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -19551,7 +19551,7 @@
         <v>13</v>
       </c>
       <c r="G624" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -19577,7 +19577,7 @@
         <v>13</v>
       </c>
       <c r="G625" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -19603,7 +19603,7 @@
         <v>12.75</v>
       </c>
       <c r="G626" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -19629,7 +19629,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G627" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="H627" t="s">
         <v>9</v>
@@ -19655,7 +19655,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G628" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H628" t="s">
         <v>9</v>
@@ -19681,7 +19681,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G629" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="H629" t="s">
         <v>9</v>
@@ -19707,7 +19707,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G630" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="H630" t="s">
         <v>9</v>
@@ -19733,7 +19733,7 @@
         <v>12.75</v>
       </c>
       <c r="G631" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="H631" t="s">
         <v>9</v>
@@ -19759,7 +19759,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G632" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="H632" t="s">
         <v>9</v>
@@ -19785,7 +19785,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G633" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="H633" t="s">
         <v>9</v>
@@ -19811,7 +19811,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G634" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="H634" t="s">
         <v>9</v>
@@ -19837,7 +19837,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G635" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="H635" t="s">
         <v>9</v>
@@ -19863,7 +19863,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G636" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="H636" t="s">
         <v>9</v>
@@ -19889,7 +19889,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G637" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="H637" t="s">
         <v>9</v>
@@ -19915,7 +19915,7 @@
         <v>12.25</v>
       </c>
       <c r="G638" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="H638" t="s">
         <v>9</v>
@@ -19941,7 +19941,7 @@
         <v>12.25</v>
       </c>
       <c r="G639" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="H639" t="s">
         <v>9</v>
@@ -19967,7 +19967,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G640" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="H640" t="s">
         <v>9</v>
@@ -19993,7 +19993,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G641" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="H641" t="s">
         <v>9</v>
@@ -20019,7 +20019,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G642" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="H642" t="s">
         <v>9</v>
@@ -20045,7 +20045,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G643" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="H643" t="s">
         <v>9</v>
@@ -20071,7 +20071,7 @@
         <v>12.5</v>
       </c>
       <c r="G644" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="H644" t="s">
         <v>9</v>
@@ -20097,7 +20097,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G645" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="H645" t="s">
         <v>9</v>
@@ -20123,7 +20123,7 @@
         <v>12.5</v>
       </c>
       <c r="G646" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="H646" t="s">
         <v>9</v>
@@ -20149,7 +20149,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G647" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="H647" t="s">
         <v>9</v>
@@ -20175,7 +20175,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G648" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="H648" t="s">
         <v>9</v>
@@ -20201,7 +20201,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G649" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="H649" t="s">
         <v>9</v>
@@ -20227,7 +20227,7 @@
         <v>12.5</v>
       </c>
       <c r="G650" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="H650" t="s">
         <v>9</v>
@@ -20253,7 +20253,7 @@
         <v>12.5</v>
       </c>
       <c r="G651" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="H651" t="s">
         <v>9</v>
@@ -20279,7 +20279,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G652" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="H652" t="s">
         <v>9</v>
@@ -20305,7 +20305,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G653" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="H653" t="s">
         <v>9</v>
@@ -20331,7 +20331,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G654" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="H654" t="s">
         <v>9</v>
@@ -20357,7 +20357,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G655" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="H655" t="s">
         <v>9</v>
@@ -20383,7 +20383,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G656" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H656" t="s">
         <v>9</v>
@@ -20409,7 +20409,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G657" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H657" t="s">
         <v>9</v>
@@ -20435,7 +20435,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G658" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="H658" t="s">
         <v>9</v>
@@ -20461,7 +20461,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G659" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="H659" t="s">
         <v>9</v>
@@ -20487,7 +20487,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G660" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="H660" t="s">
         <v>9</v>
@@ -20513,7 +20513,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G661" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="H661" t="s">
         <v>9</v>
@@ -20539,7 +20539,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G662" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="H662" t="s">
         <v>9</v>
@@ -20565,7 +20565,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G663" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="H663" t="s">
         <v>9</v>
@@ -20591,7 +20591,7 @@
         <v>12.75</v>
       </c>
       <c r="G664" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -20617,7 +20617,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G665" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="H665" t="s">
         <v>9</v>
@@ -20643,7 +20643,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G666" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="H666" t="s">
         <v>9</v>
@@ -20669,7 +20669,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G667" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="H667" t="s">
         <v>9</v>
@@ -20695,7 +20695,7 @@
         <v>12.25</v>
       </c>
       <c r="G668" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="H668" t="s">
         <v>9</v>
@@ -20721,7 +20721,7 @@
         <v>12.25</v>
       </c>
       <c r="G669" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="H669" t="s">
         <v>9</v>
@@ -20747,7 +20747,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G670" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="H670" t="s">
         <v>9</v>
@@ -20773,7 +20773,7 @@
         <v>12.5</v>
       </c>
       <c r="G671" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="H671" t="s">
         <v>9</v>
@@ -20799,7 +20799,7 @@
         <v>12.5</v>
       </c>
       <c r="G672" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="H672" t="s">
         <v>9</v>
@@ -20825,7 +20825,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G673" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="H673" t="s">
         <v>9</v>
@@ -20851,7 +20851,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G674" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="H674" t="s">
         <v>9</v>
@@ -20877,7 +20877,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G675" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="H675" t="s">
         <v>9</v>
@@ -20903,7 +20903,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G676" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="H676" t="s">
         <v>9</v>
@@ -20929,7 +20929,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G677" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="H677" t="s">
         <v>9</v>
@@ -20955,7 +20955,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G678" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="H678" t="s">
         <v>9</v>
@@ -20981,7 +20981,7 @@
         <v>12.25</v>
       </c>
       <c r="G679" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="H679" t="s">
         <v>9</v>
@@ -21007,7 +21007,7 @@
         <v>12.25</v>
       </c>
       <c r="G680" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="H680" t="s">
         <v>9</v>
@@ -21033,7 +21033,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G681" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="H681" t="s">
         <v>9</v>
@@ -21059,7 +21059,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G682" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="H682" t="s">
         <v>9</v>
@@ -21085,7 +21085,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G683" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="H683" t="s">
         <v>9</v>
@@ -21111,7 +21111,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G684" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="H684" t="s">
         <v>9</v>
@@ -21137,7 +21137,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G685" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="H685" t="s">
         <v>9</v>
@@ -21163,7 +21163,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G686" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="H686" t="s">
         <v>9</v>
@@ -21189,7 +21189,7 @@
         <v>12.5</v>
       </c>
       <c r="G687" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="H687" t="s">
         <v>9</v>
@@ -21215,7 +21215,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G688" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="H688" t="s">
         <v>9</v>
@@ -21241,7 +21241,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G689" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="H689" t="s">
         <v>9</v>
@@ -21267,7 +21267,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G690" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="H690" t="s">
         <v>9</v>
@@ -21293,7 +21293,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G691" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="H691" t="s">
         <v>9</v>
@@ -21319,7 +21319,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G692" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="H692" t="s">
         <v>9</v>
@@ -21345,7 +21345,7 @@
         <v>12.75</v>
       </c>
       <c r="G693" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="H693" t="s">
         <v>9</v>
@@ -21371,7 +21371,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G694" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -21397,7 +21397,7 @@
         <v>13.25</v>
       </c>
       <c r="G695" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="H695" t="s">
         <v>9</v>
@@ -21423,7 +21423,7 @@
         <v>13</v>
       </c>
       <c r="G696" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="H696" t="s">
         <v>9</v>
@@ -21449,7 +21449,7 @@
         <v>13</v>
       </c>
       <c r="G697" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="H697" t="s">
         <v>9</v>
@@ -21475,7 +21475,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G698" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="H698" t="s">
         <v>9</v>
@@ -21501,7 +21501,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G699" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H699" t="s">
         <v>9</v>
@@ -21527,7 +21527,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G700" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H700" t="s">
         <v>9</v>
@@ -21553,7 +21553,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G701" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="H701" t="s">
         <v>9</v>
@@ -21579,7 +21579,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G702" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="H702" t="s">
         <v>9</v>
@@ -21605,7 +21605,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G703" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="H703" t="s">
         <v>9</v>
@@ -21631,7 +21631,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G704" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="H704" t="s">
         <v>9</v>
@@ -21657,7 +21657,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G705" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="H705" t="s">
         <v>9</v>
@@ -21683,7 +21683,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G706" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="H706" t="s">
         <v>9</v>
@@ -21709,7 +21709,7 @@
         <v>13.25</v>
       </c>
       <c r="G707" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="H707" t="s">
         <v>9</v>
@@ -21735,7 +21735,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G708" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H708" t="s">
         <v>9</v>
@@ -21761,7 +21761,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G709" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H709" t="s">
         <v>9</v>
@@ -21787,7 +21787,7 @@
         <v>13</v>
       </c>
       <c r="G710" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="H710" t="s">
         <v>9</v>
@@ -21813,7 +21813,7 @@
         <v>13</v>
       </c>
       <c r="G711" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="H711" t="s">
         <v>9</v>
@@ -21839,7 +21839,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G712" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H712" t="s">
         <v>9</v>
@@ -21865,7 +21865,7 @@
         <v>13</v>
       </c>
       <c r="G713" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="H713" t="s">
         <v>9</v>
@@ -21891,7 +21891,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G714" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="H714" t="s">
         <v>9</v>
@@ -21917,7 +21917,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G715" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H715" t="s">
         <v>9</v>
@@ -21943,7 +21943,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G716" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="H716" t="s">
         <v>9</v>
@@ -21969,7 +21969,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G717" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="H717" t="s">
         <v>9</v>
@@ -21995,7 +21995,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G718" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="H718" t="s">
         <v>9</v>
@@ -22021,7 +22021,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G719" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="H719" t="s">
         <v>9</v>
@@ -22047,7 +22047,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G720" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="H720" t="s">
         <v>9</v>
@@ -22073,7 +22073,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G721" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="H721" t="s">
         <v>9</v>
@@ -22099,7 +22099,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G722" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="H722" t="s">
         <v>9</v>
@@ -22125,7 +22125,7 @@
         <v>12.5</v>
       </c>
       <c r="G723" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="H723" t="s">
         <v>9</v>
@@ -22151,7 +22151,7 @@
         <v>13</v>
       </c>
       <c r="G724" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="H724" t="s">
         <v>9</v>
@@ -22177,7 +22177,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G725" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="H725" t="s">
         <v>9</v>
@@ -22203,7 +22203,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G726" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="H726" t="s">
         <v>9</v>
@@ -22229,7 +22229,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G727" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="H727" t="s">
         <v>9</v>
@@ -22255,7 +22255,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G728" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="H728" t="s">
         <v>9</v>
@@ -22281,7 +22281,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G729" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="H729" t="s">
         <v>9</v>
@@ -22307,7 +22307,7 @@
         <v>12.5</v>
       </c>
       <c r="G730" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="H730" t="s">
         <v>9</v>
@@ -22333,7 +22333,7 @@
         <v>12.25</v>
       </c>
       <c r="G731" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="H731" t="s">
         <v>9</v>
@@ -22359,7 +22359,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G732" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H732" t="s">
         <v>9</v>
@@ -22385,7 +22385,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G733" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="H733" t="s">
         <v>9</v>
@@ -22411,7 +22411,7 @@
         <v>12</v>
       </c>
       <c r="G734" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="H734" t="s">
         <v>9</v>
@@ -22437,7 +22437,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G735" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="H735" t="s">
         <v>9</v>
@@ -22463,7 +22463,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G736" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="H736" t="s">
         <v>9</v>
@@ -22489,7 +22489,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G737" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="H737" t="s">
         <v>9</v>
@@ -22515,7 +22515,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G738" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="H738" t="s">
         <v>9</v>
@@ -22541,7 +22541,7 @@
         <v>11.5</v>
       </c>
       <c r="G739" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="H739" t="s">
         <v>9</v>
@@ -22567,7 +22567,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G740" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="H740" t="s">
         <v>9</v>
@@ -22593,7 +22593,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G741" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="H741" t="s">
         <v>9</v>
@@ -22619,7 +22619,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G742" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="H742" t="s">
         <v>9</v>
@@ -22645,7 +22645,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G743" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="H743" t="s">
         <v>9</v>
@@ -22671,7 +22671,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G744" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="H744" t="s">
         <v>9</v>
@@ -22697,7 +22697,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G745" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="H745" t="s">
         <v>9</v>
@@ -22723,7 +22723,7 @@
         <v>11.5</v>
       </c>
       <c r="G746" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="H746" t="s">
         <v>9</v>
@@ -22749,7 +22749,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G747" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="H747" t="s">
         <v>9</v>
@@ -22775,7 +22775,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G748" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="H748" t="s">
         <v>9</v>
@@ -22801,7 +22801,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G749" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="H749" t="s">
         <v>9</v>
@@ -22827,7 +22827,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G750" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="H750" t="s">
         <v>9</v>
@@ -22853,7 +22853,7 @@
         <v>10.25</v>
       </c>
       <c r="G751" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="H751" t="s">
         <v>9</v>
@@ -22879,7 +22879,7 @@
         <v>10.25</v>
       </c>
       <c r="G752" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="H752" t="s">
         <v>9</v>
@@ -22905,7 +22905,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G753" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="H753" t="s">
         <v>9</v>
@@ -22931,7 +22931,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G754" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="H754" t="s">
         <v>9</v>
@@ -22957,7 +22957,7 @@
         <v>10.5</v>
       </c>
       <c r="G755" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="H755" t="s">
         <v>9</v>
@@ -22983,7 +22983,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G756" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="H756" t="s">
         <v>9</v>
@@ -23009,7 +23009,7 @@
         <v>10.5</v>
       </c>
       <c r="G757" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="H757" t="s">
         <v>9</v>
@@ -23035,7 +23035,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G758" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="H758" t="s">
         <v>9</v>
@@ -23061,7 +23061,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G759" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="H759" t="s">
         <v>9</v>
@@ -23087,7 +23087,7 @@
         <v>10.75</v>
       </c>
       <c r="G760" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="H760" t="s">
         <v>9</v>
@@ -23113,7 +23113,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G761" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="H761" t="s">
         <v>9</v>
@@ -23139,7 +23139,7 @@
         <v>11.5</v>
       </c>
       <c r="G762" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="H762" t="s">
         <v>9</v>
@@ -23165,7 +23165,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G763" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="H763" t="s">
         <v>9</v>
@@ -23191,7 +23191,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G764" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="H764" t="s">
         <v>9</v>
@@ -23217,7 +23217,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G765" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="H765" t="s">
         <v>9</v>
@@ -23243,7 +23243,7 @@
         <v>11.5</v>
       </c>
       <c r="G766" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="H766" t="s">
         <v>9</v>
@@ -23269,7 +23269,7 @@
         <v>11.5</v>
       </c>
       <c r="G767" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="H767" t="s">
         <v>9</v>
@@ -23295,7 +23295,7 @@
         <v>11.75</v>
       </c>
       <c r="G768" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="H768" t="s">
         <v>9</v>
@@ -23321,7 +23321,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G769" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="H769" t="s">
         <v>9</v>
@@ -23347,7 +23347,7 @@
         <v>12</v>
       </c>
       <c r="G770" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="H770" t="s">
         <v>9</v>
@@ -23373,7 +23373,7 @@
         <v>11.75</v>
       </c>
       <c r="G771" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="H771" t="s">
         <v>9</v>
@@ -23399,7 +23399,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G772" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="H772" t="s">
         <v>9</v>
@@ -23425,7 +23425,7 @@
         <v>11.5</v>
       </c>
       <c r="G773" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="H773" t="s">
         <v>9</v>
@@ -23451,7 +23451,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G774" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="H774" t="s">
         <v>9</v>
@@ -23477,7 +23477,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G775" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="H775" t="s">
         <v>9</v>
@@ -23503,7 +23503,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G776" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="H776" t="s">
         <v>9</v>
@@ -23529,7 +23529,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G777" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="H777" t="s">
         <v>9</v>
@@ -23555,7 +23555,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G778" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="H778" t="s">
         <v>9</v>
@@ -23581,7 +23581,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G779" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="H779" t="s">
         <v>9</v>
@@ -23607,7 +23607,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G780" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="H780" t="s">
         <v>9</v>
@@ -23633,7 +23633,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G781" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="H781" t="s">
         <v>9</v>
@@ -23659,7 +23659,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G782" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="H782" t="s">
         <v>9</v>
@@ -23685,7 +23685,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G783" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="H783" t="s">
         <v>9</v>
@@ -23711,7 +23711,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G784" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="H784" t="s">
         <v>9</v>
@@ -23737,7 +23737,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G785" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="H785" t="s">
         <v>9</v>
@@ -23763,7 +23763,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G786" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="H786" t="s">
         <v>9</v>
@@ -23789,7 +23789,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G787" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="H787" t="s">
         <v>9</v>
@@ -23815,7 +23815,7 @@
         <v>11.5</v>
       </c>
       <c r="G788" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="H788" t="s">
         <v>9</v>
@@ -23841,7 +23841,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G789" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="H789" t="s">
         <v>9</v>
@@ -23867,7 +23867,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G790" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="H790" t="s">
         <v>9</v>
@@ -23893,7 +23893,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G791" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="H791" t="s">
         <v>9</v>
@@ -23919,7 +23919,7 @@
         <v>11.5</v>
       </c>
       <c r="G792" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="H792" t="s">
         <v>9</v>
@@ -23945,7 +23945,7 @@
         <v>11.25</v>
       </c>
       <c r="G793" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="H793" t="s">
         <v>9</v>
@@ -23971,7 +23971,7 @@
         <v>11.25</v>
       </c>
       <c r="G794" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="H794" t="s">
         <v>9</v>
@@ -23997,7 +23997,7 @@
         <v>11.5</v>
       </c>
       <c r="G795" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="H795" t="s">
         <v>9</v>
@@ -24023,7 +24023,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G796" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="H796" t="s">
         <v>9</v>
@@ -24049,7 +24049,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G797" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="H797" t="s">
         <v>9</v>
@@ -24075,7 +24075,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G798" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="H798" t="s">
         <v>9</v>
@@ -24101,7 +24101,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G799" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="H799" t="s">
         <v>9</v>
@@ -24127,7 +24127,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G800" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="H800" t="s">
         <v>9</v>
@@ -24153,7 +24153,7 @@
         <v>11</v>
       </c>
       <c r="G801" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="H801" t="s">
         <v>9</v>
@@ -24179,7 +24179,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G802" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="H802" t="s">
         <v>9</v>
@@ -24205,7 +24205,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G803" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="H803" t="s">
         <v>9</v>
@@ -24231,7 +24231,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G804" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="H804" t="s">
         <v>9</v>
@@ -24257,7 +24257,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G805" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="H805" t="s">
         <v>9</v>
@@ -24283,7 +24283,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G806" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="H806" t="s">
         <v>9</v>
@@ -24309,7 +24309,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G807" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="H807" t="s">
         <v>9</v>
@@ -24335,7 +24335,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G808" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="H808" t="s">
         <v>9</v>
@@ -24361,7 +24361,7 @@
         <v>11</v>
       </c>
       <c r="G809" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="H809" t="s">
         <v>9</v>
@@ -24387,7 +24387,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G810" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="H810" t="s">
         <v>9</v>
@@ -24413,7 +24413,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G811" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="H811" t="s">
         <v>9</v>
@@ -24439,7 +24439,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G812" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="H812" t="s">
         <v>9</v>
@@ -24465,7 +24465,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G813" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="H813" t="s">
         <v>9</v>
@@ -24491,7 +24491,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G814" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="H814" t="s">
         <v>9</v>
@@ -24517,7 +24517,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G815" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="H815" t="s">
         <v>9</v>
@@ -24543,7 +24543,7 @@
         <v>10.75</v>
       </c>
       <c r="G816" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="H816" t="s">
         <v>9</v>
@@ -24569,7 +24569,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G817" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="H817" t="s">
         <v>9</v>
@@ -24595,7 +24595,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G818" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="H818" t="s">
         <v>9</v>
@@ -24621,7 +24621,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G819" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="H819" t="s">
         <v>9</v>
@@ -24647,7 +24647,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G820" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="H820" t="s">
         <v>9</v>
@@ -24673,7 +24673,7 @@
         <v>11.25</v>
       </c>
       <c r="G821" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="H821" t="s">
         <v>9</v>
@@ -24699,7 +24699,7 @@
         <v>11.25</v>
       </c>
       <c r="G822" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="H822" t="s">
         <v>9</v>
@@ -24725,7 +24725,7 @@
         <v>11.25</v>
       </c>
       <c r="G823" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="H823" t="s">
         <v>9</v>
@@ -24751,7 +24751,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G824" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="H824" t="s">
         <v>9</v>
@@ -24777,7 +24777,7 @@
         <v>11.5</v>
       </c>
       <c r="G825" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="H825" t="s">
         <v>9</v>
@@ -24803,7 +24803,7 @@
         <v>11.5</v>
       </c>
       <c r="G826" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="H826" t="s">
         <v>9</v>
@@ -24829,7 +24829,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G827" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="H827" t="s">
         <v>9</v>
@@ -24855,7 +24855,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G828" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="H828" t="s">
         <v>9</v>
@@ -24881,7 +24881,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G829" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="H829" t="s">
         <v>9</v>
@@ -24907,7 +24907,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G830" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="H830" t="s">
         <v>9</v>
@@ -24933,7 +24933,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G831" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="H831" t="s">
         <v>9</v>
@@ -24959,7 +24959,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G832" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="H832" t="s">
         <v>9</v>
@@ -24985,7 +24985,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G833" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="H833" t="s">
         <v>9</v>
@@ -25011,7 +25011,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G834" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="H834" t="s">
         <v>9</v>
@@ -25037,7 +25037,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G835" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="H835" t="s">
         <v>9</v>
@@ -25063,7 +25063,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G836" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="H836" t="s">
         <v>9</v>
@@ -25089,7 +25089,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G837" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="H837" t="s">
         <v>9</v>
@@ -25115,7 +25115,7 @@
         <v>11.5</v>
       </c>
       <c r="G838" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="H838" t="s">
         <v>9</v>
@@ -25141,7 +25141,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G839" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="H839" t="s">
         <v>9</v>
@@ -25167,7 +25167,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G840" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="H840" t="s">
         <v>9</v>
@@ -25193,7 +25193,7 @@
         <v>11.5</v>
       </c>
       <c r="G841" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="H841" t="s">
         <v>9</v>
@@ -25219,7 +25219,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G842" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="H842" t="s">
         <v>9</v>
@@ -25245,7 +25245,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G843" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="H843" t="s">
         <v>9</v>
@@ -25271,7 +25271,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G844" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="H844" t="s">
         <v>9</v>
@@ -25297,7 +25297,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G845" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="H845" t="s">
         <v>9</v>
@@ -25323,7 +25323,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G846" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="H846" t="s">
         <v>9</v>
@@ -25349,7 +25349,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G847" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -25375,7 +25375,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G848" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="H848" t="s">
         <v>9</v>
@@ -25401,7 +25401,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G849" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="H849" t="s">
         <v>9</v>
@@ -25427,7 +25427,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G850" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="H850" t="s">
         <v>9</v>
@@ -25453,7 +25453,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G851" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -25479,7 +25479,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G852" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="H852" t="s">
         <v>9</v>
@@ -25505,7 +25505,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G853" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -25531,7 +25531,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G854" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="H854" t="s">
         <v>9</v>
@@ -25557,7 +25557,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G855" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -25583,7 +25583,7 @@
         <v>11.5</v>
       </c>
       <c r="G856" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -25609,7 +25609,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G857" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="H857" t="s">
         <v>9</v>
@@ -25635,7 +25635,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G858" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -25661,7 +25661,7 @@
         <v>11.5</v>
       </c>
       <c r="G859" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="H859" t="s">
         <v>9</v>
@@ -25687,7 +25687,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G860" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="H860" t="s">
         <v>9</v>
@@ -25713,7 +25713,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G861" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -25739,7 +25739,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G862" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="H862" t="s">
         <v>9</v>
@@ -25765,7 +25765,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G863" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="H863" t="s">
         <v>9</v>
@@ -25791,7 +25791,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G864" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="H864" t="s">
         <v>9</v>
@@ -25817,7 +25817,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G865" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="H865" t="s">
         <v>9</v>
@@ -25843,7 +25843,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G866" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="H866" t="s">
         <v>9</v>
@@ -25869,7 +25869,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G867" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="H867" t="s">
         <v>9</v>
@@ -25895,7 +25895,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G868" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="H868" t="s">
         <v>9</v>
@@ -25921,7 +25921,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G869" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="H869" t="s">
         <v>9</v>
@@ -25947,7 +25947,7 @@
         <v>12</v>
       </c>
       <c r="G870" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="H870" t="s">
         <v>9</v>
@@ -25973,7 +25973,7 @@
         <v>12</v>
       </c>
       <c r="G871" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="H871" t="s">
         <v>9</v>
@@ -25999,7 +25999,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G872" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="H872" t="s">
         <v>9</v>
@@ -26025,7 +26025,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G873" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="H873" t="s">
         <v>9</v>
@@ -26051,7 +26051,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G874" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="H874" t="s">
         <v>9</v>
@@ -26077,7 +26077,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G875" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="H875" t="s">
         <v>9</v>
@@ -26103,7 +26103,7 @@
         <v>12</v>
       </c>
       <c r="G876" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="H876" t="s">
         <v>9</v>
@@ -26129,7 +26129,7 @@
         <v>12</v>
       </c>
       <c r="G877" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="H877" t="s">
         <v>9</v>
@@ -26155,7 +26155,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G878" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="H878" t="s">
         <v>9</v>
@@ -26181,7 +26181,7 @@
         <v>12</v>
       </c>
       <c r="G879" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="H879" t="s">
         <v>9</v>
@@ -26207,7 +26207,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G880" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="H880" t="s">
         <v>9</v>
@@ -26233,7 +26233,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G881" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="H881" t="s">
         <v>9</v>
@@ -26259,7 +26259,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G882" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="H882" t="s">
         <v>9</v>
@@ -26285,7 +26285,7 @@
         <v>12</v>
       </c>
       <c r="G883" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="H883" t="s">
         <v>9</v>
@@ -26311,7 +26311,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G884" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="H884" t="s">
         <v>9</v>
@@ -26337,7 +26337,7 @@
         <v>12.25</v>
       </c>
       <c r="G885" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="H885" t="s">
         <v>9</v>
@@ -26363,7 +26363,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G886" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="H886" t="s">
         <v>9</v>
@@ -26389,7 +26389,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G887" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="H887" t="s">
         <v>9</v>
@@ -26415,7 +26415,7 @@
         <v>12.25</v>
       </c>
       <c r="G888" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="H888" t="s">
         <v>9</v>
@@ -26441,7 +26441,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G889" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="H889" t="s">
         <v>9</v>
@@ -26467,7 +26467,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G890" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="H890" t="s">
         <v>9</v>
@@ -26493,7 +26493,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G891" t="s">
-        <v>326</v>
+        <v>252</v>
       </c>
       <c r="H891" t="s">
         <v>9</v>
@@ -26519,7 +26519,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G892" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H892" t="s">
         <v>9</v>
@@ -26545,7 +26545,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G893" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H893" t="s">
         <v>9</v>
@@ -26571,7 +26571,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G894" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H894" t="s">
         <v>9</v>
@@ -26597,7 +26597,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G895" t="s">
-        <v>326</v>
+        <v>252</v>
       </c>
       <c r="H895" t="s">
         <v>9</v>
@@ -26623,7 +26623,7 @@
         <v>12.5</v>
       </c>
       <c r="G896" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H896" t="s">
         <v>9</v>
@@ -26649,7 +26649,7 @@
         <v>12.5</v>
       </c>
       <c r="G897" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H897" t="s">
         <v>9</v>
@@ -26675,7 +26675,7 @@
         <v>12.5</v>
       </c>
       <c r="G898" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H898" t="s">
         <v>9</v>
@@ -26701,7 +26701,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G899" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H899" t="s">
         <v>9</v>
@@ -26727,7 +26727,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G900" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H900" t="s">
         <v>9</v>
@@ -26753,7 +26753,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G901" t="s">
-        <v>326</v>
+        <v>252</v>
       </c>
       <c r="H901" t="s">
         <v>9</v>
@@ -26779,7 +26779,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G902" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H902" t="s">
         <v>9</v>
@@ -26805,7 +26805,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G903" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H903" t="s">
         <v>9</v>
@@ -26831,7 +26831,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G904" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H904" t="s">
         <v>9</v>
@@ -26857,7 +26857,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G905" t="s">
-        <v>326</v>
+        <v>252</v>
       </c>
       <c r="H905" t="s">
         <v>9</v>
@@ -26883,7 +26883,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G906" t="s">
-        <v>326</v>
+        <v>252</v>
       </c>
       <c r="H906" t="s">
         <v>9</v>
@@ -26909,7 +26909,7 @@
         <v>12.75</v>
       </c>
       <c r="G907" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H907" t="s">
         <v>9</v>
@@ -26935,7 +26935,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G908" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H908" t="s">
         <v>9</v>
@@ -26961,7 +26961,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G909" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H909" t="s">
         <v>9</v>
@@ -26987,7 +26987,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G910" t="s">
-        <v>326</v>
+        <v>252</v>
       </c>
       <c r="H910" t="s">
         <v>9</v>
@@ -27013,7 +27013,7 @@
         <v>12.5</v>
       </c>
       <c r="G911" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H911" t="s">
         <v>9</v>
@@ -27039,7 +27039,7 @@
         <v>12.5</v>
       </c>
       <c r="G912" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H912" t="s">
         <v>9</v>
@@ -27065,7 +27065,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G913" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="H913" t="s">
         <v>9</v>
@@ -27091,7 +27091,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G914" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H914" t="s">
         <v>9</v>
@@ -27117,7 +27117,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G915" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H915" t="s">
         <v>9</v>
@@ -27143,7 +27143,7 @@
         <v>12.5</v>
       </c>
       <c r="G916" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H916" t="s">
         <v>9</v>
@@ -27169,7 +27169,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G917" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H917" t="s">
         <v>9</v>
@@ -27195,7 +27195,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G918" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="H918" t="s">
         <v>9</v>
@@ -27221,7 +27221,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G919" t="s">
-        <v>326</v>
+        <v>252</v>
       </c>
       <c r="H919" t="s">
         <v>9</v>
@@ -27247,7 +27247,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G920" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H920" t="s">
         <v>9</v>
@@ -27273,7 +27273,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G921" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H921" t="s">
         <v>9</v>
@@ -27299,7 +27299,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G922" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="H922" t="s">
         <v>9</v>
@@ -27325,7 +27325,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G923" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="H923" t="s">
         <v>9</v>
@@ -27351,7 +27351,7 @@
         <v>12.5</v>
       </c>
       <c r="G924" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H924" t="s">
         <v>9</v>
@@ -27377,7 +27377,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G925" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H925" t="s">
         <v>9</v>
@@ -27403,7 +27403,7 @@
         <v>12.5</v>
       </c>
       <c r="G926" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H926" t="s">
         <v>9</v>
@@ -27429,7 +27429,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G927" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H927" t="s">
         <v>9</v>
@@ -27455,7 +27455,7 @@
         <v>12.5</v>
       </c>
       <c r="G928" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H928" t="s">
         <v>9</v>
@@ -27481,7 +27481,7 @@
         <v>12.5</v>
       </c>
       <c r="G929" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H929" t="s">
         <v>9</v>
@@ -27507,7 +27507,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G930" t="s">
-        <v>326</v>
+        <v>252</v>
       </c>
       <c r="H930" t="s">
         <v>9</v>
@@ -27533,7 +27533,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G931" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H931" t="s">
         <v>9</v>
@@ -27559,7 +27559,7 @@
         <v>13</v>
       </c>
       <c r="G932" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H932" t="s">
         <v>9</v>
@@ -27585,7 +27585,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G933" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H933" t="s">
         <v>9</v>
@@ -27611,7 +27611,7 @@
         <v>13</v>
       </c>
       <c r="G934" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H934" t="s">
         <v>9</v>
@@ -27637,7 +27637,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G935" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H935" t="s">
         <v>9</v>
@@ -27663,7 +27663,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G936" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H936" t="s">
         <v>9</v>
@@ -27689,7 +27689,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G937" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H937" t="s">
         <v>9</v>
@@ -27715,7 +27715,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G938" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H938" t="s">
         <v>9</v>
@@ -27741,7 +27741,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G939" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H939" t="s">
         <v>9</v>
@@ -27767,7 +27767,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G940" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H940" t="s">
         <v>9</v>
@@ -27793,7 +27793,7 @@
         <v>13.25</v>
       </c>
       <c r="G941" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H941" t="s">
         <v>9</v>
@@ -27819,7 +27819,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G942" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H942" t="s">
         <v>9</v>
@@ -27845,7 +27845,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G943" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H943" t="s">
         <v>9</v>
@@ -27871,7 +27871,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G944" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H944" t="s">
         <v>9</v>
@@ -27897,7 +27897,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G945" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H945" t="s">
         <v>9</v>
@@ -27923,7 +27923,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G946" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H946" t="s">
         <v>9</v>
@@ -27949,7 +27949,7 @@
         <v>12.75</v>
       </c>
       <c r="G947" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H947" t="s">
         <v>9</v>
@@ -27975,7 +27975,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G948" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H948" t="s">
         <v>9</v>
@@ -28001,7 +28001,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G949" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H949" t="s">
         <v>9</v>
@@ -28027,7 +28027,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G950" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H950" t="s">
         <v>9</v>
@@ -28053,7 +28053,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G951" t="s">
-        <v>326</v>
+        <v>252</v>
       </c>
       <c r="H951" t="s">
         <v>9</v>
@@ -28079,7 +28079,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G952" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H952" t="s">
         <v>9</v>
@@ -28105,7 +28105,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G953" t="s">
-        <v>326</v>
+        <v>252</v>
       </c>
       <c r="H953" t="s">
         <v>9</v>
@@ -28131,7 +28131,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G954" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H954" t="s">
         <v>9</v>
@@ -28157,7 +28157,7 @@
         <v>12.5</v>
       </c>
       <c r="G955" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H955" t="s">
         <v>9</v>
@@ -28183,7 +28183,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G956" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="H956" t="s">
         <v>9</v>
@@ -28209,7 +28209,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G957" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="H957" t="s">
         <v>9</v>
@@ -28235,7 +28235,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G958" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="H958" t="s">
         <v>9</v>
@@ -28261,7 +28261,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G959" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="H959" t="s">
         <v>9</v>
@@ -28287,7 +28287,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G960" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="H960" t="s">
         <v>9</v>
@@ -28313,7 +28313,7 @@
         <v>11.75</v>
       </c>
       <c r="G961" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H961" t="s">
         <v>9</v>
@@ -28339,7 +28339,7 @@
         <v>11.5</v>
       </c>
       <c r="G962" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="H962" t="s">
         <v>9</v>
@@ -28365,7 +28365,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G963" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="H963" t="s">
         <v>9</v>
@@ -28391,7 +28391,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G964" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="H964" t="s">
         <v>9</v>
@@ -28417,7 +28417,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G965" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="H965" t="s">
         <v>9</v>
@@ -28443,7 +28443,7 @@
         <v>12.25</v>
       </c>
       <c r="G966" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="H966" t="s">
         <v>9</v>
@@ -28469,7 +28469,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G967" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="H967" t="s">
         <v>9</v>
@@ -28495,7 +28495,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G968" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="H968" t="s">
         <v>9</v>
@@ -28521,7 +28521,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G969" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H969" t="s">
         <v>9</v>
@@ -28547,7 +28547,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G970" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="H970" t="s">
         <v>9</v>
@@ -28573,7 +28573,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G971" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H971" t="s">
         <v>9</v>
@@ -28599,7 +28599,7 @@
         <v>12.25</v>
       </c>
       <c r="G972" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="H972" t="s">
         <v>9</v>
@@ -28625,7 +28625,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G973" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="H973" t="s">
         <v>9</v>
@@ -28651,7 +28651,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G974" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="H974" t="s">
         <v>9</v>
@@ -28677,7 +28677,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G975" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="H975" t="s">
         <v>9</v>
@@ -28703,7 +28703,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G976" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H976" t="s">
         <v>9</v>
@@ -28729,7 +28729,7 @@
         <v>12.5</v>
       </c>
       <c r="G977" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H977" t="s">
         <v>9</v>
@@ -28755,7 +28755,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G978" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="H978" t="s">
         <v>9</v>
@@ -28781,7 +28781,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G979" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H979" t="s">
         <v>9</v>
@@ -28807,7 +28807,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G980" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="H980" t="s">
         <v>9</v>
@@ -28833,7 +28833,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G981" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H981" t="s">
         <v>9</v>
@@ -28859,7 +28859,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G982" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H982" t="s">
         <v>9</v>
@@ -28885,7 +28885,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G983" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="H983" t="s">
         <v>9</v>
@@ -28911,7 +28911,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G984" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H984" t="s">
         <v>9</v>
@@ -28937,7 +28937,7 @@
         <v>12.25</v>
       </c>
       <c r="G985" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="H985" t="s">
         <v>9</v>
@@ -28963,7 +28963,7 @@
         <v>12.25</v>
       </c>
       <c r="G986" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="H986" t="s">
         <v>9</v>
@@ -28989,7 +28989,7 @@
         <v>12.25</v>
       </c>
       <c r="G987" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="H987" t="s">
         <v>9</v>
@@ -29015,7 +29015,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G988" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="H988" t="s">
         <v>9</v>
@@ -29041,7 +29041,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G989" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="H989" t="s">
         <v>9</v>
@@ -29067,7 +29067,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G990" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="H990" t="s">
         <v>9</v>
@@ -29093,7 +29093,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G991" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="H991" t="s">
         <v>9</v>
@@ -29119,7 +29119,7 @@
         <v>11.75</v>
       </c>
       <c r="G992" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H992" t="s">
         <v>9</v>
@@ -29145,7 +29145,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G993" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="H993" t="s">
         <v>9</v>
@@ -29171,7 +29171,7 @@
         <v>12</v>
       </c>
       <c r="G994" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="H994" t="s">
         <v>9</v>
@@ -29197,7 +29197,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G995" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="H995" t="s">
         <v>9</v>
@@ -29223,7 +29223,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G996" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="H996" t="s">
         <v>9</v>
@@ -29249,7 +29249,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G997" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="H997" t="s">
         <v>9</v>
@@ -29275,7 +29275,7 @@
         <v>12.25</v>
       </c>
       <c r="G998" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="H998" t="s">
         <v>9</v>
@@ -29301,7 +29301,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G999" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H999" t="s">
         <v>9</v>
@@ -29327,7 +29327,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1000" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H1000" t="s">
         <v>9</v>
@@ -29353,7 +29353,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G1001" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="H1001" t="s">
         <v>9</v>
@@ -29379,7 +29379,7 @@
         <v>12</v>
       </c>
       <c r="G1002" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="H1002" t="s">
         <v>9</v>
@@ -29405,7 +29405,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1003" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H1003" t="s">
         <v>9</v>
@@ -29431,7 +29431,7 @@
         <v>12.25</v>
       </c>
       <c r="G1004" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="H1004" t="s">
         <v>9</v>
@@ -29457,7 +29457,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G1005" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="H1005" t="s">
         <v>9</v>
@@ -29483,7 +29483,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G1006" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="H1006" t="s">
         <v>9</v>
@@ -29509,7 +29509,7 @@
         <v>12.25</v>
       </c>
       <c r="G1007" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="H1007" t="s">
         <v>9</v>
@@ -29535,7 +29535,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G1008" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H1008" t="s">
         <v>9</v>
@@ -29561,7 +29561,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G1009" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="H1009" t="s">
         <v>9</v>
@@ -29587,7 +29587,7 @@
         <v>12.5</v>
       </c>
       <c r="G1010" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H1010" t="s">
         <v>9</v>
@@ -29613,7 +29613,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G1011" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="H1011" t="s">
         <v>9</v>
@@ -29639,7 +29639,7 @@
         <v>12.5</v>
       </c>
       <c r="G1012" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H1012" t="s">
         <v>9</v>
@@ -29665,7 +29665,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1013" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H1013" t="s">
         <v>9</v>
@@ -29691,7 +29691,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1014" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H1014" t="s">
         <v>9</v>
@@ -29717,7 +29717,7 @@
         <v>12.75</v>
       </c>
       <c r="G1015" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H1015" t="s">
         <v>9</v>
@@ -29743,7 +29743,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G1016" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H1016" t="s">
         <v>9</v>
@@ -29769,7 +29769,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1017" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H1017" t="s">
         <v>9</v>
@@ -29795,7 +29795,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1018" t="s">
-        <v>326</v>
+        <v>252</v>
       </c>
       <c r="H1018" t="s">
         <v>9</v>
@@ -29821,7 +29821,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1019" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H1019" t="s">
         <v>9</v>
@@ -29847,7 +29847,7 @@
         <v>13.25</v>
       </c>
       <c r="G1020" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H1020" t="s">
         <v>9</v>
@@ -29873,7 +29873,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1021" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H1021" t="s">
         <v>9</v>
@@ -29899,7 +29899,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G1022" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H1022" t="s">
         <v>9</v>
@@ -29925,7 +29925,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1023" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H1023" t="s">
         <v>9</v>
@@ -29951,7 +29951,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G1024" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H1024" t="s">
         <v>9</v>
@@ -29977,7 +29977,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1025" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H1025" t="s">
         <v>9</v>
@@ -30003,7 +30003,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1026" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H1026" t="s">
         <v>9</v>
@@ -30029,7 +30029,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G1027" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H1027" t="s">
         <v>9</v>
@@ -30055,7 +30055,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1028" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H1028" t="s">
         <v>9</v>
@@ -30081,7 +30081,7 @@
         <v>13.5</v>
       </c>
       <c r="G1029" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H1029" t="s">
         <v>9</v>
@@ -30107,7 +30107,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G1030" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H1030" t="s">
         <v>9</v>
@@ -30133,7 +30133,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G1031" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H1031" t="s">
         <v>9</v>
@@ -30159,7 +30159,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G1032" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H1032" t="s">
         <v>9</v>
@@ -30185,7 +30185,7 @@
         <v>13.5</v>
       </c>
       <c r="G1033" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H1033" t="s">
         <v>9</v>
@@ -30211,7 +30211,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1034" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H1034" t="s">
         <v>9</v>
@@ -30237,7 +30237,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1035" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H1035" t="s">
         <v>9</v>
@@ -30263,7 +30263,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1036" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H1036" t="s">
         <v>9</v>
@@ -30289,7 +30289,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1037" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H1037" t="s">
         <v>9</v>
@@ -30315,7 +30315,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G1038" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H1038" t="s">
         <v>9</v>
@@ -30341,7 +30341,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1039" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H1039" t="s">
         <v>9</v>
@@ -30367,7 +30367,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G1040" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H1040" t="s">
         <v>9</v>
@@ -30393,7 +30393,7 @@
         <v>13.5</v>
       </c>
       <c r="G1041" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H1041" t="s">
         <v>9</v>
@@ -30419,7 +30419,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1042" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H1042" t="s">
         <v>9</v>
@@ -30445,7 +30445,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G1043" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H1043" t="s">
         <v>9</v>
@@ -30471,7 +30471,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G1044" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H1044" t="s">
         <v>9</v>
@@ -30497,7 +30497,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G1045" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H1045" t="s">
         <v>9</v>
@@ -30523,7 +30523,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G1046" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H1046" t="s">
         <v>9</v>
@@ -30549,7 +30549,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1047" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H1047" t="s">
         <v>9</v>
@@ -30575,7 +30575,7 @@
         <v>13.8500003814697</v>
       </c>
       <c r="G1048" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H1048" t="s">
         <v>9</v>
@@ -30601,7 +30601,7 @@
         <v>13.75</v>
       </c>
       <c r="G1049" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H1049" t="s">
         <v>9</v>
@@ -30627,7 +30627,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1050" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H1050" t="s">
         <v>9</v>
@@ -30653,7 +30653,7 @@
         <v>13.75</v>
       </c>
       <c r="G1051" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H1051" t="s">
         <v>9</v>
@@ -30679,7 +30679,7 @@
         <v>13.8500003814697</v>
       </c>
       <c r="G1052" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H1052" t="s">
         <v>9</v>
@@ -30705,7 +30705,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G1053" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H1053" t="s">
         <v>9</v>
@@ -30731,7 +30731,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G1054" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H1054" t="s">
         <v>9</v>
@@ -30757,7 +30757,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1055" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H1055" t="s">
         <v>9</v>
@@ -30783,7 +30783,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1056" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H1056" t="s">
         <v>9</v>
@@ -30809,7 +30809,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1057" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H1057" t="s">
         <v>9</v>
@@ -30835,7 +30835,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1058" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H1058" t="s">
         <v>9</v>
@@ -30861,7 +30861,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G1059" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H1059" t="s">
         <v>9</v>
@@ -30887,7 +30887,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1060" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H1060" t="s">
         <v>9</v>
@@ -30913,7 +30913,7 @@
         <v>14.0500001907349</v>
       </c>
       <c r="G1061" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H1061" t="s">
         <v>9</v>
@@ -30939,7 +30939,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1062" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H1062" t="s">
         <v>9</v>
@@ -30965,7 +30965,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1063" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H1063" t="s">
         <v>9</v>
@@ -30991,7 +30991,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G1064" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H1064" t="s">
         <v>9</v>
@@ -31017,7 +31017,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1065" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="H1065" t="s">
         <v>9</v>
@@ -31043,7 +31043,7 @@
         <v>12</v>
       </c>
       <c r="G1066" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="H1066" t="s">
         <v>9</v>
@@ -31069,7 +31069,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1067" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="H1067" t="s">
         <v>9</v>
@@ -31095,7 +31095,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G1068" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="H1068" t="s">
         <v>9</v>
@@ -31121,7 +31121,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G1069" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H1069" t="s">
         <v>9</v>
@@ -31147,7 +31147,7 @@
         <v>10.75</v>
       </c>
       <c r="G1070" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H1070" t="s">
         <v>9</v>
@@ -31173,7 +31173,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1071" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="H1071" t="s">
         <v>9</v>
@@ -31199,7 +31199,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1072" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="H1072" t="s">
         <v>9</v>
@@ -31225,7 +31225,7 @@
         <v>11.75</v>
       </c>
       <c r="G1073" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H1073" t="s">
         <v>9</v>
@@ -31251,7 +31251,7 @@
         <v>11.25</v>
       </c>
       <c r="G1074" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H1074" t="s">
         <v>9</v>
@@ -31277,7 +31277,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1075" t="s">
-        <v>361</v>
+        <v>280</v>
       </c>
       <c r="H1075" t="s">
         <v>9</v>
@@ -31303,7 +31303,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G1076" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="H1076" t="s">
         <v>9</v>
@@ -31329,7 +31329,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1077" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="H1077" t="s">
         <v>9</v>
@@ -31355,7 +31355,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1078" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="H1078" t="s">
         <v>9</v>
@@ -31381,7 +31381,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G1079" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="H1079" t="s">
         <v>9</v>
@@ -31407,7 +31407,7 @@
         <v>11.75</v>
       </c>
       <c r="G1080" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H1080" t="s">
         <v>9</v>
@@ -31433,7 +31433,7 @@
         <v>11.75</v>
       </c>
       <c r="G1081" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H1081" t="s">
         <v>9</v>
@@ -31459,7 +31459,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G1082" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="H1082" t="s">
         <v>9</v>
@@ -31485,7 +31485,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1083" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H1083" t="s">
         <v>9</v>
@@ -31511,7 +31511,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G1084" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="H1084" t="s">
         <v>9</v>
@@ -31537,7 +31537,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1085" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H1085" t="s">
         <v>9</v>
@@ -31563,7 +31563,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G1086" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H1086" t="s">
         <v>9</v>
@@ -31589,7 +31589,7 @@
         <v>12</v>
       </c>
       <c r="G1087" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="H1087" t="s">
         <v>9</v>
@@ -31615,7 +31615,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1088" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="H1088" t="s">
         <v>9</v>
@@ -31641,7 +31641,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1089" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="H1089" t="s">
         <v>9</v>
@@ -31667,7 +31667,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1090" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="H1090" t="s">
         <v>9</v>
@@ -31693,7 +31693,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G1091" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="H1091" t="s">
         <v>9</v>
@@ -31719,7 +31719,7 @@
         <v>12</v>
       </c>
       <c r="G1092" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="H1092" t="s">
         <v>9</v>
@@ -31745,7 +31745,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1093" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H1093" t="s">
         <v>9</v>
@@ -31771,7 +31771,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1094" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H1094" t="s">
         <v>9</v>
@@ -31797,7 +31797,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1095" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="H1095" t="s">
         <v>9</v>
@@ -31823,7 +31823,7 @@
         <v>12.5</v>
       </c>
       <c r="G1096" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H1096" t="s">
         <v>9</v>
@@ -31849,7 +31849,7 @@
         <v>13.5</v>
       </c>
       <c r="G1097" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H1097" t="s">
         <v>9</v>
@@ -31875,7 +31875,7 @@
         <v>13.75</v>
       </c>
       <c r="G1098" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H1098" t="s">
         <v>9</v>
@@ -31927,7 +31927,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G1100" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H1100" t="s">
         <v>9</v>
@@ -31953,7 +31953,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G1101" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H1101" t="s">
         <v>9</v>
@@ -31979,7 +31979,7 @@
         <v>13.5</v>
       </c>
       <c r="G1102" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H1102" t="s">
         <v>9</v>
@@ -32005,7 +32005,7 @@
         <v>13.5</v>
       </c>
       <c r="G1103" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H1103" t="s">
         <v>9</v>
@@ -32031,7 +32031,7 @@
         <v>13.25</v>
       </c>
       <c r="G1104" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H1104" t="s">
         <v>9</v>
@@ -32057,7 +32057,7 @@
         <v>13.5</v>
       </c>
       <c r="G1105" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H1105" t="s">
         <v>9</v>
@@ -32083,7 +32083,7 @@
         <v>13.5</v>
       </c>
       <c r="G1106" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H1106" t="s">
         <v>9</v>
@@ -32109,7 +32109,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1107" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H1107" t="s">
         <v>9</v>
@@ -32135,7 +32135,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G1108" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H1108" t="s">
         <v>9</v>
@@ -32187,7 +32187,7 @@
         <v>13.75</v>
       </c>
       <c r="G1110" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H1110" t="s">
         <v>9</v>
@@ -32213,7 +32213,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G1111" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H1111" t="s">
         <v>9</v>
@@ -32239,7 +32239,7 @@
         <v>13.8500003814697</v>
       </c>
       <c r="G1112" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H1112" t="s">
         <v>9</v>
@@ -32265,7 +32265,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G1113" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H1113" t="s">
         <v>9</v>
@@ -32291,7 +32291,7 @@
         <v>13.8500003814697</v>
       </c>
       <c r="G1114" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H1114" t="s">
         <v>9</v>
@@ -33019,7 +33019,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1142" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="H1142" t="s">
         <v>9</v>
@@ -33045,7 +33045,7 @@
         <v>14.75</v>
       </c>
       <c r="G1143" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H1143" t="s">
         <v>9</v>
@@ -33071,7 +33071,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1144" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H1144" t="s">
         <v>9</v>
@@ -33097,7 +33097,7 @@
         <v>14.5</v>
       </c>
       <c r="G1145" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1145" t="s">
         <v>9</v>
@@ -33123,7 +33123,7 @@
         <v>14.5</v>
       </c>
       <c r="G1146" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1146" t="s">
         <v>9</v>
@@ -33149,7 +33149,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1147" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1147" t="s">
         <v>9</v>
@@ -33175,7 +33175,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1148" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1148" t="s">
         <v>9</v>
@@ -33201,7 +33201,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G1149" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1149" t="s">
         <v>9</v>
@@ -33227,7 +33227,7 @@
         <v>14</v>
       </c>
       <c r="G1150" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1150" t="s">
         <v>9</v>
@@ -33253,7 +33253,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1151" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1151" t="s">
         <v>9</v>
@@ -33279,7 +33279,7 @@
         <v>14.5</v>
       </c>
       <c r="G1152" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1152" t="s">
         <v>9</v>
@@ -33305,7 +33305,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1153" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H1153" t="s">
         <v>9</v>
@@ -33331,7 +33331,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G1154" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H1154" t="s">
         <v>9</v>
@@ -33357,7 +33357,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G1155" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H1155" t="s">
         <v>9</v>
@@ -33383,7 +33383,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G1156" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H1156" t="s">
         <v>9</v>
@@ -33409,7 +33409,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1157" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H1157" t="s">
         <v>9</v>
@@ -33461,7 +33461,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1159" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H1159" t="s">
         <v>9</v>
@@ -33487,7 +33487,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1160" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H1160" t="s">
         <v>9</v>
@@ -33513,7 +33513,7 @@
         <v>14.5</v>
       </c>
       <c r="G1161" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1161" t="s">
         <v>9</v>
@@ -33539,7 +33539,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G1162" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1162" t="s">
         <v>9</v>
@@ -33565,7 +33565,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G1163" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H1163" t="s">
         <v>9</v>
@@ -33591,7 +33591,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1164" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1164" t="s">
         <v>9</v>
@@ -33617,7 +33617,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1165" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1165" t="s">
         <v>9</v>
@@ -33643,7 +33643,7 @@
         <v>14.25</v>
       </c>
       <c r="G1166" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1166" t="s">
         <v>9</v>
@@ -33669,7 +33669,7 @@
         <v>14.5</v>
       </c>
       <c r="G1167" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1167" t="s">
         <v>9</v>
@@ -33695,7 +33695,7 @@
         <v>14.5</v>
       </c>
       <c r="G1168" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1168" t="s">
         <v>9</v>
@@ -33747,7 +33747,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1170" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H1170" t="s">
         <v>9</v>
@@ -33799,7 +33799,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1172" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H1172" t="s">
         <v>9</v>
@@ -33851,7 +33851,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1174" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H1174" t="s">
         <v>9</v>
@@ -33877,7 +33877,7 @@
         <v>15.75</v>
       </c>
       <c r="G1175" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H1175" t="s">
         <v>9</v>
@@ -33903,7 +33903,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1176" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H1176" t="s">
         <v>9</v>
@@ -33929,7 +33929,7 @@
         <v>16</v>
       </c>
       <c r="G1177" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H1177" t="s">
         <v>9</v>
@@ -33955,7 +33955,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1178" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H1178" t="s">
         <v>9</v>
@@ -33981,7 +33981,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G1179" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H1179" t="s">
         <v>9</v>
@@ -34007,7 +34007,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1180" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H1180" t="s">
         <v>9</v>
@@ -34033,7 +34033,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1181" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H1181" t="s">
         <v>9</v>
@@ -34059,7 +34059,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1182" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H1182" t="s">
         <v>9</v>
@@ -34085,7 +34085,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1183" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H1183" t="s">
         <v>9</v>
@@ -34111,7 +34111,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1184" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H1184" t="s">
         <v>9</v>
@@ -34137,7 +34137,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1185" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H1185" t="s">
         <v>9</v>
@@ -34163,7 +34163,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1186" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H1186" t="s">
         <v>9</v>
@@ -34189,7 +34189,7 @@
         <v>16.5</v>
       </c>
       <c r="G1187" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H1187" t="s">
         <v>9</v>
@@ -34215,7 +34215,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1188" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H1188" t="s">
         <v>9</v>
@@ -34241,7 +34241,7 @@
         <v>16.5</v>
       </c>
       <c r="G1189" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H1189" t="s">
         <v>9</v>
@@ -34267,7 +34267,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1190" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H1190" t="s">
         <v>9</v>
@@ -34293,7 +34293,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G1191" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H1191" t="s">
         <v>9</v>
@@ -34319,7 +34319,7 @@
         <v>17</v>
       </c>
       <c r="G1192" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H1192" t="s">
         <v>9</v>
@@ -34345,7 +34345,7 @@
         <v>17</v>
       </c>
       <c r="G1193" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H1193" t="s">
         <v>9</v>
@@ -34371,7 +34371,7 @@
         <v>17</v>
       </c>
       <c r="G1194" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H1194" t="s">
         <v>9</v>
@@ -34397,7 +34397,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1195" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H1195" t="s">
         <v>9</v>
@@ -34423,7 +34423,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G1196" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H1196" t="s">
         <v>9</v>
@@ -34449,7 +34449,7 @@
         <v>18</v>
       </c>
       <c r="G1197" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H1197" t="s">
         <v>9</v>
@@ -34475,7 +34475,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1198" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H1198" t="s">
         <v>9</v>
@@ -34501,7 +34501,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1199" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H1199" t="s">
         <v>9</v>
@@ -34527,7 +34527,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1200" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H1200" t="s">
         <v>9</v>
@@ -34553,7 +34553,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G1201" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H1201" t="s">
         <v>9</v>
@@ -34579,7 +34579,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G1202" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H1202" t="s">
         <v>9</v>
@@ -34605,7 +34605,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1203" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H1203" t="s">
         <v>9</v>
@@ -34631,7 +34631,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G1204" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H1204" t="s">
         <v>9</v>
@@ -34657,7 +34657,7 @@
         <v>20</v>
       </c>
       <c r="G1205" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H1205" t="s">
         <v>9</v>
@@ -34683,7 +34683,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G1206" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H1206" t="s">
         <v>9</v>
@@ -34709,7 +34709,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G1207" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H1207" t="s">
         <v>9</v>
@@ -34735,7 +34735,7 @@
         <v>19.25</v>
       </c>
       <c r="G1208" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H1208" t="s">
         <v>9</v>
@@ -34761,7 +34761,7 @@
         <v>19.3500003814697</v>
       </c>
       <c r="G1209" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H1209" t="s">
         <v>9</v>
@@ -34787,7 +34787,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1210" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H1210" t="s">
         <v>9</v>
@@ -34813,7 +34813,7 @@
         <v>19.3500003814697</v>
       </c>
       <c r="G1211" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H1211" t="s">
         <v>9</v>
@@ -34839,7 +34839,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1212" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H1212" t="s">
         <v>9</v>
@@ -34865,7 +34865,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1213" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H1213" t="s">
         <v>9</v>
@@ -34891,7 +34891,7 @@
         <v>18.4500007629395</v>
       </c>
       <c r="G1214" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H1214" t="s">
         <v>9</v>
@@ -34917,7 +34917,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G1215" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H1215" t="s">
         <v>9</v>
@@ -34943,7 +34943,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1216" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1216" t="s">
         <v>9</v>
@@ -34969,7 +34969,7 @@
         <v>18.5</v>
       </c>
       <c r="G1217" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H1217" t="s">
         <v>9</v>
@@ -34995,7 +34995,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1218" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H1218" t="s">
         <v>9</v>
@@ -35021,7 +35021,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1219" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H1219" t="s">
         <v>9</v>
@@ -35047,7 +35047,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1220" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H1220" t="s">
         <v>9</v>
@@ -35073,7 +35073,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1221" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H1221" t="s">
         <v>9</v>
@@ -35099,7 +35099,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1222" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H1222" t="s">
         <v>9</v>
@@ -35125,7 +35125,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1223" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H1223" t="s">
         <v>9</v>
@@ -35151,7 +35151,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1224" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H1224" t="s">
         <v>9</v>
@@ -35177,7 +35177,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1225" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H1225" t="s">
         <v>9</v>
@@ -35203,7 +35203,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1226" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H1226" t="s">
         <v>9</v>
@@ -35229,7 +35229,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1227" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H1227" t="s">
         <v>9</v>
@@ -35255,7 +35255,7 @@
         <v>17.75</v>
       </c>
       <c r="G1228" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H1228" t="s">
         <v>9</v>
@@ -35281,7 +35281,7 @@
         <v>18</v>
       </c>
       <c r="G1229" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H1229" t="s">
         <v>9</v>
@@ -35307,7 +35307,7 @@
         <v>18.5</v>
       </c>
       <c r="G1230" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H1230" t="s">
         <v>9</v>
@@ -35333,7 +35333,7 @@
         <v>18.4500007629395</v>
       </c>
       <c r="G1231" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H1231" t="s">
         <v>9</v>
@@ -35359,7 +35359,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1232" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H1232" t="s">
         <v>9</v>
@@ -35385,7 +35385,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G1233" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H1233" t="s">
         <v>9</v>
@@ -35411,7 +35411,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1234" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H1234" t="s">
         <v>9</v>
@@ -35437,7 +35437,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1235" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H1235" t="s">
         <v>9</v>
@@ -35463,7 +35463,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1236" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H1236" t="s">
         <v>9</v>
@@ -35489,7 +35489,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G1237" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H1237" t="s">
         <v>9</v>
@@ -35515,7 +35515,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G1238" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H1238" t="s">
         <v>9</v>
@@ -35541,7 +35541,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G1239" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H1239" t="s">
         <v>9</v>
@@ -35567,7 +35567,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1240" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1240" t="s">
         <v>9</v>
@@ -35593,7 +35593,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1241" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H1241" t="s">
         <v>9</v>
@@ -35619,7 +35619,7 @@
         <v>18.5</v>
       </c>
       <c r="G1242" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H1242" t="s">
         <v>9</v>
@@ -35645,7 +35645,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1243" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H1243" t="s">
         <v>9</v>
@@ -35671,7 +35671,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G1244" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H1244" t="s">
         <v>9</v>
@@ -35697,7 +35697,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G1245" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H1245" t="s">
         <v>9</v>
@@ -35723,7 +35723,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1246" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H1246" t="s">
         <v>9</v>
@@ -35749,7 +35749,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1247" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H1247" t="s">
         <v>9</v>
@@ -35775,7 +35775,7 @@
         <v>17.75</v>
       </c>
       <c r="G1248" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H1248" t="s">
         <v>9</v>
@@ -35801,7 +35801,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1249" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H1249" t="s">
         <v>9</v>
@@ -35827,7 +35827,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1250" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H1250" t="s">
         <v>9</v>
@@ -35853,7 +35853,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1251" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H1251" t="s">
         <v>9</v>
@@ -35879,7 +35879,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G1252" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H1252" t="s">
         <v>9</v>
@@ -35905,7 +35905,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1253" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H1253" t="s">
         <v>9</v>
@@ -35931,7 +35931,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1254" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H1254" t="s">
         <v>9</v>
@@ -35957,7 +35957,7 @@
         <v>18.0499992370605</v>
       </c>
       <c r="G1255" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H1255" t="s">
         <v>9</v>
@@ -35983,7 +35983,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1256" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H1256" t="s">
         <v>9</v>
@@ -36009,7 +36009,7 @@
         <v>18</v>
       </c>
       <c r="G1257" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H1257" t="s">
         <v>9</v>
@@ -36035,7 +36035,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G1258" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H1258" t="s">
         <v>9</v>
@@ -36061,7 +36061,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G1259" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H1259" t="s">
         <v>9</v>
@@ -36087,7 +36087,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1260" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H1260" t="s">
         <v>9</v>
@@ -36113,7 +36113,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1261" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H1261" t="s">
         <v>9</v>
@@ -36139,7 +36139,7 @@
         <v>19</v>
       </c>
       <c r="G1262" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H1262" t="s">
         <v>9</v>
@@ -36165,7 +36165,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1263" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H1263" t="s">
         <v>9</v>
@@ -36191,7 +36191,7 @@
         <v>19.5</v>
       </c>
       <c r="G1264" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H1264" t="s">
         <v>9</v>
@@ -36217,7 +36217,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G1265" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H1265" t="s">
         <v>9</v>
@@ -36243,7 +36243,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G1266" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H1266" t="s">
         <v>9</v>
@@ -36269,7 +36269,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G1267" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H1267" t="s">
         <v>9</v>
@@ -36295,7 +36295,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G1268" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H1268" t="s">
         <v>9</v>
@@ -36321,7 +36321,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1269" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H1269" t="s">
         <v>9</v>
@@ -36347,7 +36347,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1270" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H1270" t="s">
         <v>9</v>
@@ -36373,7 +36373,7 @@
         <v>21.5</v>
       </c>
       <c r="G1271" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H1271" t="s">
         <v>9</v>
@@ -36399,7 +36399,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1272" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H1272" t="s">
         <v>9</v>
@@ -36425,7 +36425,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G1273" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H1273" t="s">
         <v>9</v>
@@ -36451,7 +36451,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1274" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H1274" t="s">
         <v>9</v>
@@ -36477,7 +36477,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G1275" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H1275" t="s">
         <v>9</v>
@@ -36503,7 +36503,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G1276" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H1276" t="s">
         <v>9</v>
@@ -36529,7 +36529,7 @@
         <v>22.5</v>
       </c>
       <c r="G1277" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H1277" t="s">
         <v>9</v>
@@ -36555,7 +36555,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G1278" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H1278" t="s">
         <v>9</v>
@@ -36581,7 +36581,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G1279" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H1279" t="s">
         <v>9</v>
@@ -36607,7 +36607,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G1280" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H1280" t="s">
         <v>9</v>
@@ -36633,7 +36633,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G1281" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H1281" t="s">
         <v>9</v>
@@ -36659,7 +36659,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1282" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H1282" t="s">
         <v>9</v>
@@ -36685,7 +36685,7 @@
         <v>23</v>
       </c>
       <c r="G1283" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H1283" t="s">
         <v>9</v>
@@ -36711,7 +36711,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G1284" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H1284" t="s">
         <v>9</v>
@@ -36737,7 +36737,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G1285" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H1285" t="s">
         <v>9</v>
@@ -36763,7 +36763,7 @@
         <v>23.5</v>
       </c>
       <c r="G1286" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H1286" t="s">
         <v>9</v>
@@ -36789,7 +36789,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G1287" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H1287" t="s">
         <v>9</v>
@@ -36841,7 +36841,7 @@
         <v>23.5</v>
       </c>
       <c r="G1289" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H1289" t="s">
         <v>9</v>
@@ -69739,7 +69739,7 @@
     </row>
     <row r="2555">
       <c r="A2555" s="1" t="n">
-        <v>46043.6911689815</v>
+        <v>46043.3333333333</v>
       </c>
       <c r="B2555" t="n">
         <v>2173</v>
@@ -69760,6 +69760,32 @@
         <v>965</v>
       </c>
       <c r="H2555" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2556">
+      <c r="A2556" s="1" t="n">
+        <v>46044.6911111111</v>
+      </c>
+      <c r="B2556" t="n">
+        <v>7165</v>
+      </c>
+      <c r="C2556" t="n">
+        <v>21.2000007629395</v>
+      </c>
+      <c r="D2556" t="n">
+        <v>20.8999996185303</v>
+      </c>
+      <c r="E2556" t="n">
+        <v>21.2000007629395</v>
+      </c>
+      <c r="F2556" t="n">
+        <v>21</v>
+      </c>
+      <c r="G2556" t="s">
+        <v>964</v>
+      </c>
+      <c r="H2556" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IWB.MI.xlsx
+++ b/data/IWB.MI.xlsx
@@ -44,211 +44,211 @@
     <t xml:space="preserve">IWB.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7986741065979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83063507080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74274158477783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75073003768921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71077871322632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69479703903198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59092283248901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5110182762146</t>
+    <t xml:space="preserve">7.79867458343506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83063554763794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74274063110352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75073099136353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71077823638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69479751586914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59092140197754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51101779937744</t>
   </si>
   <si>
     <t xml:space="preserve">7.31125736236572</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44709491729736</t>
+    <t xml:space="preserve">7.44709396362305</t>
   </si>
   <si>
     <t xml:space="preserve">7.35120820999146</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29527568817139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26331377029419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29927062988281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29127979278564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27130508422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24733400344849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3751802444458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43111371994019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47106409072876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15144729614258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41513156890869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32723665237427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28728532791138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99163913726807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11149406433105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1914005279541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25532341003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41912746429443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42312431335449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63087368011475</t>
+    <t xml:space="preserve">7.29527473449707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26331472396851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29927158355713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29128122329712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2713041305542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24733209609985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37517976760864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4311146736145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47106552124023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15144681930542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41513252258301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32723712921143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28728580474854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99163961410522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11149549484253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19140005111694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25532388687134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41912794113159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4231219291687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63087463378906</t>
   </si>
   <si>
     <t xml:space="preserve">7.67082691192627</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49903249740601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58293056488037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89455842971802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98644971847534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9105396270752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54297876358032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82264566421509</t>
+    <t xml:space="preserve">7.49903297424316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58293199539185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89455938339233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98644876480103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91053867340088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5429801940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82264518737793</t>
   </si>
   <si>
     <t xml:space="preserve">7.64286041259766</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62288379669189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77470254898071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76671171188354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79068326950073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8705883026123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96647357940674</t>
+    <t xml:space="preserve">7.62288427352905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77470207214355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76671028137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79068279266357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87058782577515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96647310256958</t>
   </si>
   <si>
     <t xml:space="preserve">7.71876859664917</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66283798217773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57094764709473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5589599609375</t>
+    <t xml:space="preserve">7.66283655166626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57094717025757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55896043777466</t>
   </si>
   <si>
     <t xml:space="preserve">7.39116191864014</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46307516098022</t>
+    <t xml:space="preserve">7.4630765914917</t>
   </si>
   <si>
     <t xml:space="preserve">7.60690402984619</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54697370529175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36719036102295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31525182723999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33123302459717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34721326828003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50302839279175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24333763122559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22336149215698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23934316635132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4590802192688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46707153320312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10350513458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89974784851074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91173458099365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95168733596802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0076208114624</t>
+    <t xml:space="preserve">7.54697561264038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36718988418579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31525230407715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33123207092285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34721374511719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50302696228027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24333810806274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22336101531982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23934364318848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45907926559448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46707010269165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10350465774536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89974880218506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91173362731934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95168590545654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00762033462524</t>
   </si>
   <si>
     <t xml:space="preserve">6.8717827796936</t>
@@ -257,190 +257,190 @@
     <t xml:space="preserve">6.87577676773071</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8797721862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86778783798218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75192451477051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74393463134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82383918762207</t>
+    <t xml:space="preserve">6.87977266311646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86778688430786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75192546844482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74393510818481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82383871078491</t>
   </si>
   <si>
     <t xml:space="preserve">6.66403102874756</t>
   </si>
   <si>
-    <t xml:space="preserve">6.83183145523071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89575338363647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03159093856812</t>
+    <t xml:space="preserve">6.83182954788208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89575290679932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03159046173096</t>
   </si>
   <si>
     <t xml:space="preserve">7.07154369354248</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33522796630859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25931835174561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17941427230835</t>
+    <t xml:space="preserve">7.33522987365723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25931787490845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17941474914551</t>
   </si>
   <si>
     <t xml:space="preserve">7.26730966567993</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23135232925415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09551525115967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18340826034546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18740463256836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20738172531128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14345693588257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12348031997681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23534822463989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7467360496521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83463191986084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98245334625244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92652225494385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78269195556641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63886451721191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73475027084351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07035064697266</t>
+    <t xml:space="preserve">7.23135328292847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09551429748535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18340969085693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1874041557312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20738077163696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14345645904541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12348222732544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23534774780273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74673461914062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83463001251221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98245239257812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92652177810669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78269243240356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63886547088623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73474979400635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07034969329834</t>
   </si>
   <si>
     <t xml:space="preserve">8.21417713165283</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16623306274414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18221569061279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27011108398438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5737476348877</t>
+    <t xml:space="preserve">8.16623401641846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18221473693848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27011013031006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57374668121338</t>
   </si>
   <si>
     <t xml:space="preserve">8.54977512359619</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35001564025879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46987152099609</t>
+    <t xml:space="preserve">8.35001373291016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46987056732178</t>
   </si>
   <si>
     <t xml:space="preserve">8.525803565979</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50982189178467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59771728515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60571002960205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58173751831055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64687538146973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67130088806152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6143045425415</t>
+    <t xml:space="preserve">8.50982475280762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59771919250488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60570907592773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58173847198486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64687442779541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67129993438721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61430549621582</t>
   </si>
   <si>
     <t xml:space="preserve">8.63058948516846</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75272083282471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82599830627441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87485218048096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95627212524414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74457931518555</t>
+    <t xml:space="preserve">8.75271987915039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82600021362305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87485122680664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95627117156982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74457836151123</t>
   </si>
   <si>
     <t xml:space="preserve">8.85856819152832</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84228324890137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91556167602539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03769302368164</t>
+    <t xml:space="preserve">8.84228420257568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91556072235107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03769397735596</t>
   </si>
   <si>
     <t xml:space="preserve">9.00512504577637</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94813060760498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99698257446289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12725448608398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19239139556885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11911201477051</t>
+    <t xml:space="preserve">8.9481315612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99698448181152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12725639343262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19239044189453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11911487579346</t>
   </si>
   <si>
     <t xml:space="preserve">9.14354038238525</t>
@@ -449,22 +449,22 @@
     <t xml:space="preserve">8.98069763183594</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13539695739746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16796684265137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15982341766357</t>
+    <t xml:space="preserve">9.13539791107178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16796588897705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15982246398926</t>
   </si>
   <si>
     <t xml:space="preserve">9.184250831604</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15168285369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07026290893555</t>
+    <t xml:space="preserve">9.15168190002441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07026195526123</t>
   </si>
   <si>
     <t xml:space="preserve">8.96441459655762</t>
@@ -473,91 +473,91 @@
     <t xml:space="preserve">8.92370414733887</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8015718460083</t>
+    <t xml:space="preserve">8.80157470703125</t>
   </si>
   <si>
     <t xml:space="preserve">8.79343223571777</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86670875549316</t>
+    <t xml:space="preserve">8.86670970916748</t>
   </si>
   <si>
     <t xml:space="preserve">8.90741920471191</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89113712310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11097145080566</t>
+    <t xml:space="preserve">8.89113521575928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1109733581543</t>
   </si>
   <si>
     <t xml:space="preserve">9.20053482055664</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28195381164551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35523319244385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39594554901123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32266712188721</t>
+    <t xml:space="preserve">9.28195571899414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35523414611816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39594268798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32266616821289</t>
   </si>
   <si>
     <t xml:space="preserve">9.64834880828857</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60763931274414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90075302124023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99031639099121</t>
+    <t xml:space="preserve">9.60763835906982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90075206756592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99031543731689</t>
   </si>
   <si>
     <t xml:space="preserve">10.1205883026123</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1368722915649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1775827407837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1043043136597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1531581878662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0961608886719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94146156311035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90889263153076</t>
+    <t xml:space="preserve">10.1368713378906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1775808334351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1043033599854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1531562805176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0961618423462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94146251678467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90889453887939</t>
   </si>
   <si>
     <t xml:space="preserve">9.77047920227051</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83561515808105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91703796386719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7949047088623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77862358093262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78676319122314</t>
+    <t xml:space="preserve">9.83561611175537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91703605651855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79490566253662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77862167358398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78676414489746</t>
   </si>
   <si>
     <t xml:space="preserve">9.95774555206299</t>
@@ -566,13 +566,13 @@
     <t xml:space="preserve">10.0147409439087</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99845790863037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88446807861328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86004161834717</t>
+    <t xml:space="preserve">9.99845600128174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88446998596191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8600435256958</t>
   </si>
   <si>
     <t xml:space="preserve">9.85190010070801</t>
@@ -584,16 +584,16 @@
     <t xml:space="preserve">10.2590036392212</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3404245376587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4625539779663</t>
+    <t xml:space="preserve">10.3404226303101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4625549316406</t>
   </si>
   <si>
     <t xml:space="preserve">10.5276918411255</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5765438079834</t>
+    <t xml:space="preserve">10.5765428543091</t>
   </si>
   <si>
     <t xml:space="preserve">10.5439758300781</t>
@@ -602,55 +602,55 @@
     <t xml:space="preserve">10.5358324050903</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5032644271851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5521183013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3485651016235</t>
+    <t xml:space="preserve">10.5032653808594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.552116394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3485641479492</t>
   </si>
   <si>
     <t xml:space="preserve">10.4381275177002</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3241405487061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3811330795288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3648481369019</t>
+    <t xml:space="preserve">10.3241386413574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3811349868774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3648500442505</t>
   </si>
   <si>
     <t xml:space="preserve">10.4218454360962</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4137029647827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3729906082153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3892765045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2915706634521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.267144203186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2264337539673</t>
+    <t xml:space="preserve">10.4137020111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3729944229126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3892774581909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2915725708008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2671451568604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2264356613159</t>
   </si>
   <si>
     <t xml:space="preserve">10.1938667297363</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3159980773926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2182922363281</t>
+    <t xml:space="preserve">10.3159971237183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2182931900024</t>
   </si>
   <si>
     <t xml:space="preserve">10.2834300994873</t>
@@ -659,61 +659,61 @@
     <t xml:space="preserve">10.429986000061</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3322811126709</t>
+    <t xml:space="preserve">10.3322801589966</t>
   </si>
   <si>
     <t xml:space="preserve">10.2427186965942</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5846843719482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6661062240601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7068176269531</t>
+    <t xml:space="preserve">10.5846853256226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6661071777344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7068157196045</t>
   </si>
   <si>
     <t xml:space="preserve">10.7475261688232</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7882375717163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6253967285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8696584701538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8289470672607</t>
+    <t xml:space="preserve">10.788236618042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6253957748413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8696594238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8289480209351</t>
   </si>
   <si>
     <t xml:space="preserve">11.0325002670288</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2360515594482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4396018981934</t>
+    <t xml:space="preserve">11.2360496520996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4396028518677</t>
   </si>
   <si>
     <t xml:space="preserve">11.6838645935059</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0732097625732</t>
+    <t xml:space="preserve">11.0732088088989</t>
   </si>
   <si>
     <t xml:space="preserve">10.9917898178101</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1546316146851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3174686431885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2767610549927</t>
+    <t xml:space="preserve">11.1546306610107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3174715042114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2767601013184</t>
   </si>
   <si>
     <t xml:space="preserve">11.1953401565552</t>
@@ -722,103 +722,100 @@
     <t xml:space="preserve">11.3581829071045</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4839191436768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5258293151855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5677433013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4000949859619</t>
+    <t xml:space="preserve">11.4839181900024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5258302688599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.567741394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4000930786133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0228843688965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1486215591431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2324447631836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1905345916748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.274356842041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8971481323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0647964477539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4420051574707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8552370071411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6875886917114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.325475692749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.282247543335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1957921981812</t>
   </si>
   <si>
     <t xml:space="preserve">11.0228853225708</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1486206054688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2324447631836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1905326843262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2743577957153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8971481323242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0647964477539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3581838607788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.442006111145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8552360534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6875867843628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3254766464233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.282247543335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1957931518555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0228862762451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2390203475952</t>
+    <t xml:space="preserve">11.2390213012695</t>
   </si>
   <si>
     <t xml:space="preserve">11.1525659561157</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9364309310913</t>
+    <t xml:space="preserve">10.936429977417</t>
   </si>
   <si>
     <t xml:space="preserve">11.0661125183105</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1093397140503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9796581268311</t>
+    <t xml:space="preserve">11.109338760376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9796571731567</t>
   </si>
   <si>
     <t xml:space="preserve">10.7635231018066</t>
   </si>
   <si>
-    <t xml:space="preserve">10.590615272522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8499784469604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7202959060669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6770677566528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8067512512207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8932046890259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6338405609131</t>
+    <t xml:space="preserve">10.5906162261963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8499774932861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7202949523926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6770706176758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8067502975464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8932056427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6338424682617</t>
   </si>
   <si>
     <t xml:space="preserve">11.4119281768799</t>
@@ -830,82 +827,82 @@
     <t xml:space="preserve">11.3687009811401</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5416088104248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6280632019043</t>
+    <t xml:space="preserve">11.5416097640991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6280641555786</t>
   </si>
   <si>
     <t xml:space="preserve">11.5848350524902</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4609327316284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3312530517578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3744792938232</t>
+    <t xml:space="preserve">10.4609346389771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3312540054321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3744802474976</t>
   </si>
   <si>
     <t xml:space="preserve">10.2880258560181</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5041608810425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0286636352539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94220924377441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59639453887939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63961982727051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81252956390381</t>
+    <t xml:space="preserve">10.5041589736938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0286645889282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94221019744873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59639358520508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63962078094482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81252861022949</t>
   </si>
   <si>
     <t xml:space="preserve">9.85575580596924</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55316734313965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03444385528564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8183069229126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86153411865234</t>
+    <t xml:space="preserve">9.55316925048828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03444290161133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81830787658691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86153602600098</t>
   </si>
   <si>
     <t xml:space="preserve">8.77508163452148</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07767105102539</t>
+    <t xml:space="preserve">9.07767009735107</t>
   </si>
   <si>
     <t xml:space="preserve">9.16412448883057</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25057983398438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33703327178955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2938060760498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.244800567627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68284797668457</t>
+    <t xml:space="preserve">9.25057697296143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33703231811523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29380512237549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2447996139526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68284702301025</t>
   </si>
   <si>
     <t xml:space="preserve">10.1583452224731</t>
@@ -914,7 +911,7 @@
     <t xml:space="preserve">9.98543739318848</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89898204803467</t>
+    <t xml:space="preserve">9.8989839553833</t>
   </si>
   <si>
     <t xml:space="preserve">9.76930236816406</t>
@@ -923,16 +920,16 @@
     <t xml:space="preserve">9.72607517242432</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46671199798584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50994110107422</t>
+    <t xml:space="preserve">9.46671295166016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50993919372559</t>
   </si>
   <si>
     <t xml:space="preserve">9.38025951385498</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42348480224609</t>
+    <t xml:space="preserve">9.42348575592041</t>
   </si>
   <si>
     <t xml:space="preserve">9.207350730896</t>
@@ -941,10 +938,10 @@
     <t xml:space="preserve">10.0718908309937</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2972898483276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2077465057373</t>
+    <t xml:space="preserve">10.2972888946533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2077474594116</t>
   </si>
   <si>
     <t xml:space="preserve">10.1629772186279</t>
@@ -962,28 +959,28 @@
     <t xml:space="preserve">10.1182069778442</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2525186538696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4763717651367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6554546356201</t>
+    <t xml:space="preserve">10.2525196075439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.476372718811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6554555892944</t>
   </si>
   <si>
     <t xml:space="preserve">10.7897682189941</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7449979782104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5659141540527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7002258300781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1031627655029</t>
+    <t xml:space="preserve">10.7449970245361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5659151077271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7002277374268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1031637191772</t>
   </si>
   <si>
     <t xml:space="preserve">10.9688520431519</t>
@@ -995,13 +992,16 @@
     <t xml:space="preserve">10.8793087005615</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1479358673096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.237476348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4613304138184</t>
+    <t xml:space="preserve">11.1479349136353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2822484970093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2374773025513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4613313674927</t>
   </si>
   <si>
     <t xml:space="preserve">11.3270177841187</t>
@@ -1013,10 +1013,10 @@
     <t xml:space="preserve">11.3717889785767</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4165592193604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0583934783936</t>
+    <t xml:space="preserve">11.416561126709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0583944320679</t>
   </si>
   <si>
     <t xml:space="preserve">11.6404142379761</t>
@@ -1025,169 +1025,169 @@
     <t xml:space="preserve">11.7299566268921</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6851844787598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7747259140015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8194971084595</t>
+    <t xml:space="preserve">11.6851854324341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7747268676758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8194980621338</t>
   </si>
   <si>
     <t xml:space="preserve">11.8642683029175</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5508718490601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5956439971924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5211448669434</t>
+    <t xml:space="preserve">11.5508728027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5956430435181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.521143913269</t>
   </si>
   <si>
     <t xml:space="preserve">11.0136222839355</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8345394134521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9985799789429</t>
+    <t xml:space="preserve">10.8345403671265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9985809326172</t>
   </si>
   <si>
     <t xml:space="preserve">12.0881223678589</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0433511734009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1328926086426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.22243309021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1776657104492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.356746673584</t>
+    <t xml:space="preserve">12.0433521270752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1328945159912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2224340438843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1776638031006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3567476272583</t>
   </si>
   <si>
     <t xml:space="preserve">12.2672061920166</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4015197753906</t>
+    <t xml:space="preserve">12.401517868042</t>
   </si>
   <si>
     <t xml:space="preserve">12.3119773864746</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6701421737671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6253719329834</t>
+    <t xml:space="preserve">12.6701431274414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.625373840332</t>
   </si>
   <si>
     <t xml:space="preserve">12.5806016921997</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6106863021851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62572765350342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0734357833862</t>
+    <t xml:space="preserve">10.6106872558594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6257266998291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0734348297119</t>
   </si>
   <si>
     <t xml:space="preserve">12.491060256958</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9090385437012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1626205444336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6998720169067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8789539337158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0132684707642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1475811004639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2371215820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1923513412476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9237279891968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9684972763062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7894124984741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2818918228149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8341836929321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5207891464233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.431245803833</t>
+    <t xml:space="preserve">11.9090394973755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1626224517822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6998729705811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8789558410645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0132675170898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1475801467896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2371225357056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1923522949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9237260818481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9684982299805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7894144058228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2818927764893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8341846466064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5207901000977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4312467575073</t>
   </si>
   <si>
     <t xml:space="preserve">13.565559387207</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6103296279907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7004652023315</t>
+    <t xml:space="preserve">13.610330581665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7004642486572</t>
   </si>
   <si>
     <t xml:space="preserve">13.7905988693237</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8356647491455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6553974151611</t>
+    <t xml:space="preserve">13.8356666564941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6553964614868</t>
   </si>
   <si>
     <t xml:space="preserve">13.5201950073242</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2948589324951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1596574783325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0695219039917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9793863296509</t>
+    <t xml:space="preserve">13.2948579788208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1596565246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.069522857666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9793872833252</t>
   </si>
   <si>
     <t xml:space="preserve">12.708984375</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5737810134888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6188488006592</t>
+    <t xml:space="preserve">12.5737819671631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6188478469849</t>
   </si>
   <si>
     <t xml:space="preserve">13.3399257659912</t>
@@ -1196,37 +1196,37 @@
     <t xml:space="preserve">13.1145896911621</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4751281738281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9343194961548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7540502548218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8441848754883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0610036849976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8807325363159</t>
+    <t xml:space="preserve">13.4751272201538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9343214035034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7540512084961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8441858291626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0610046386719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8807334899902</t>
   </si>
   <si>
     <t xml:space="preserve">14.1962051391602</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3314056396484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4215412139893</t>
+    <t xml:space="preserve">14.3314075469971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4215421676636</t>
   </si>
   <si>
     <t xml:space="preserve">14.3764734268188</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5116758346558</t>
+    <t xml:space="preserve">14.5116767883301</t>
   </si>
   <si>
     <t xml:space="preserve">14.4666080474854</t>
@@ -1235,31 +1235,31 @@
     <t xml:space="preserve">14.6018114089966</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6919460296631</t>
+    <t xml:space="preserve">14.6919441223145</t>
   </si>
   <si>
     <t xml:space="preserve">14.8722143173218</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2327527999878</t>
+    <t xml:space="preserve">15.2327518463135</t>
   </si>
   <si>
     <t xml:space="preserve">15.0074157714844</t>
   </si>
   <si>
-    <t xml:space="preserve">15.32288646698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1876859664917</t>
+    <t xml:space="preserve">15.3228893280029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.187686920166</t>
   </si>
   <si>
     <t xml:space="preserve">16.2242336273193</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9538345336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8551788330078</t>
+    <t xml:space="preserve">15.9538316726685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8551750183105</t>
   </si>
   <si>
     <t xml:space="preserve">16.3143692016602</t>
@@ -1271,7 +1271,7 @@
     <t xml:space="preserve">16.8101100921631</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7565231323242</t>
+    <t xml:space="preserve">17.7565212249756</t>
   </si>
   <si>
     <t xml:space="preserve">18.0269260406494</t>
@@ -1283,49 +1283,49 @@
     <t xml:space="preserve">17.3509178161621</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4410533905029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4861183166504</t>
+    <t xml:space="preserve">17.4410552978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.486120223999</t>
   </si>
   <si>
     <t xml:space="preserve">17.0354461669922</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6298408508301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7199745178223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4045066833496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6749076843262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9453105926514</t>
+    <t xml:space="preserve">16.6298389434814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7199726104736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4045028686523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6749095916748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9453086853027</t>
   </si>
   <si>
     <t xml:space="preserve">16.765043258667</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8636989593506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9988956451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4946365356445</t>
+    <t xml:space="preserve">15.863697052002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9988965988159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4946384429932</t>
   </si>
   <si>
     <t xml:space="preserve">16.3594360351562</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1791667938232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5847721099854</t>
+    <t xml:space="preserve">16.1791687011719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5847702026367</t>
   </si>
   <si>
     <t xml:space="preserve">16.5397052764893</t>
@@ -1334,28 +1334,28 @@
     <t xml:space="preserve">15.6834239959717</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0890312194824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5932903289795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2693004608154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1255798339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5762519836426</t>
+    <t xml:space="preserve">16.0890350341797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5932912826538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2692985534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1255836486816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5762538909912</t>
   </si>
   <si>
     <t xml:space="preserve">17.666389465332</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8466567993164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5677337646484</t>
+    <t xml:space="preserve">17.846658706665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5677356719971</t>
   </si>
   <si>
     <t xml:space="preserve">18.3874664306641</t>
@@ -1364,28 +1364,28 @@
     <t xml:space="preserve">18.7480049133301</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3789463043213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0098896026611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5506935119629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.460563659668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.280294418335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3704280853271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1000213623047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6408290863037</t>
+    <t xml:space="preserve">19.3789443969727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0098876953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5506954193115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4605617523193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2802906036377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3704299926758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1000232696533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6408309936523</t>
   </si>
   <si>
     <t xml:space="preserve">20.7309646606445</t>
@@ -1394,13 +1394,13 @@
     <t xml:space="preserve">22.4435234069824</t>
   </si>
   <si>
-    <t xml:space="preserve">21.902717590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5361442565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9027194976807</t>
+    <t xml:space="preserve">21.9027137756348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5361423492432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9027156829834</t>
   </si>
   <si>
     <t xml:space="preserve">21.1695709228516</t>
@@ -1412,19 +1412,19 @@
     <t xml:space="preserve">22.360933303833</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4525737762451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.269287109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0860042572021</t>
+    <t xml:space="preserve">22.4525718688965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2692852020264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0860023498535</t>
   </si>
   <si>
     <t xml:space="preserve">21.9943599700928</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6277866363525</t>
+    <t xml:space="preserve">21.6277885437012</t>
   </si>
   <si>
     <t xml:space="preserve">23.277364730835</t>
@@ -1436,25 +1436,25 @@
     <t xml:space="preserve">22.7275047302246</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1776466369629</t>
+    <t xml:space="preserve">22.1776447296143</t>
   </si>
   <si>
     <t xml:space="preserve">22.6358623504639</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0024337768555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0940761566162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1021518707275</t>
+    <t xml:space="preserve">23.0024356842041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0940780639648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1021499633789</t>
   </si>
   <si>
     <t xml:space="preserve">24.2854385375977</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9269428253174</t>
+    <t xml:space="preserve">24.9269409179688</t>
   </si>
   <si>
     <t xml:space="preserve">26.2099456787109</t>
@@ -1466,34 +1466,34 @@
     <t xml:space="preserve">26.6681594848633</t>
   </si>
   <si>
-    <t xml:space="preserve">27.309663772583</t>
+    <t xml:space="preserve">27.3096618652344</t>
   </si>
   <si>
     <t xml:space="preserve">26.4848747253418</t>
   </si>
   <si>
-    <t xml:space="preserve">26.759801864624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5765171051025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.301586151123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5684413909912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0347328186035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1425247192383</t>
+    <t xml:space="preserve">26.7598056793213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5765190124512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3015880584717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5684452056885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0347309112549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1425266265869</t>
   </si>
   <si>
     <t xml:space="preserve">28.4093818664551</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1344528198242</t>
+    <t xml:space="preserve">28.1344509124756</t>
   </si>
   <si>
     <t xml:space="preserve">28.2260932922363</t>
@@ -1502,19 +1502,19 @@
     <t xml:space="preserve">28.3646850585938</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4570789337158</t>
+    <t xml:space="preserve">28.4570770263672</t>
   </si>
   <si>
     <t xml:space="preserve">28.0875053405762</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9951114654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9027194976807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7179317474365</t>
+    <t xml:space="preserve">27.9951095581055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9027214050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7179336547852</t>
   </si>
   <si>
     <t xml:space="preserve">29.1038303375244</t>
@@ -1523,43 +1523,43 @@
     <t xml:space="preserve">29.9353675842285</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7505798339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3810081481934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8266525268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9190406799316</t>
+    <t xml:space="preserve">29.750581741333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.381010055542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8266506195068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9190425872803</t>
   </si>
   <si>
     <t xml:space="preserve">28.7342567443848</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0114345550537</t>
+    <t xml:space="preserve">29.0114364624023</t>
   </si>
   <si>
     <t xml:space="preserve">29.8429737091064</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1201553344727</t>
+    <t xml:space="preserve">30.1201496124268</t>
   </si>
   <si>
     <t xml:space="preserve">30.2125473022461</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0277614593506</t>
+    <t xml:space="preserve">30.0277633666992</t>
   </si>
   <si>
     <t xml:space="preserve">30.3973350524902</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1364803314209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8592967987061</t>
+    <t xml:space="preserve">31.1364765167236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8593006134033</t>
   </si>
   <si>
     <t xml:space="preserve">31.0440826416016</t>
@@ -1574,49 +1574,49 @@
     <t xml:space="preserve">29.2886180877686</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4734020233154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.8919486999512</t>
+    <t xml:space="preserve">29.4734001159668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.8919448852539</t>
   </si>
   <si>
     <t xml:space="preserve">33.3539085388184</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5550270080566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0930557250977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.8485221862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.4192085266113</t>
+    <t xml:space="preserve">34.5550231933594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0930595397949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.8485260009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.4192047119141</t>
   </si>
   <si>
     <t xml:space="preserve">40.0986099243164</t>
   </si>
   <si>
-    <t xml:space="preserve">37.2344169616699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.8811798095703</t>
+    <t xml:space="preserve">37.2344245910645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.881175994873</t>
   </si>
   <si>
     <t xml:space="preserve">38.1583518981934</t>
   </si>
   <si>
-    <t xml:space="preserve">37.6039962768555</t>
+    <t xml:space="preserve">37.6039924621582</t>
   </si>
   <si>
     <t xml:space="preserve">37.6963882446289</t>
   </si>
   <si>
-    <t xml:space="preserve">37.7887878417969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.1420249938965</t>
+    <t xml:space="preserve">37.7887840270996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.142032623291</t>
   </si>
   <si>
     <t xml:space="preserve">38.5279273986816</t>
@@ -1628,28 +1628,28 @@
     <t xml:space="preserve">36.4952812194824</t>
   </si>
   <si>
-    <t xml:space="preserve">35.94091796875</t>
+    <t xml:space="preserve">35.9409217834473</t>
   </si>
   <si>
     <t xml:space="preserve">36.4028854370117</t>
   </si>
   <si>
-    <t xml:space="preserve">36.680061340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.9735641479492</t>
+    <t xml:space="preserve">36.6800651550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.9735679626465</t>
   </si>
   <si>
     <t xml:space="preserve">38.0659637451172</t>
   </si>
   <si>
-    <t xml:space="preserve">38.4355316162109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.805103302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.3594665527344</t>
+    <t xml:space="preserve">38.4355354309082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.8051071166992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.3594627380371</t>
   </si>
   <si>
     <t xml:space="preserve">39.8214263916016</t>
@@ -1658,7 +1658,7 @@
     <t xml:space="preserve">40.006217956543</t>
   </si>
   <si>
-    <t xml:space="preserve">40.5605735778809</t>
+    <t xml:space="preserve">40.5605773925781</t>
   </si>
   <si>
     <t xml:space="preserve">40.6529655456543</t>
@@ -1667,25 +1667,25 @@
     <t xml:space="preserve">41.946475982666</t>
   </si>
   <si>
-    <t xml:space="preserve">41.114933013916</t>
+    <t xml:space="preserve">41.1149368286133</t>
   </si>
   <si>
     <t xml:space="preserve">40.9301490783691</t>
   </si>
   <si>
-    <t xml:space="preserve">42.3160400390625</t>
+    <t xml:space="preserve">42.316047668457</t>
   </si>
   <si>
     <t xml:space="preserve">43.5171546936035</t>
   </si>
   <si>
-    <t xml:space="preserve">44.0715141296387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.8867225646973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.7019424438477</t>
+    <t xml:space="preserve">44.0715103149414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.8867301940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.7019386291504</t>
   </si>
   <si>
     <t xml:space="preserve">43.979118347168</t>
@@ -1694,28 +1694,28 @@
     <t xml:space="preserve">44.3486938476562</t>
   </si>
   <si>
-    <t xml:space="preserve">44.9954490661621</t>
+    <t xml:space="preserve">44.9954452514648</t>
   </si>
   <si>
     <t xml:space="preserve">44.8106575012207</t>
   </si>
   <si>
-    <t xml:space="preserve">44.5334815979004</t>
+    <t xml:space="preserve">44.5334777832031</t>
   </si>
   <si>
     <t xml:space="preserve">43.7943344116211</t>
   </si>
   <si>
-    <t xml:space="preserve">43.1475791931152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.3921127319336</t>
+    <t xml:space="preserve">43.1475830078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.3921089172363</t>
   </si>
   <si>
     <t xml:space="preserve">41.854076385498</t>
   </si>
   <si>
-    <t xml:space="preserve">41.5768966674805</t>
+    <t xml:space="preserve">41.5769004821777</t>
   </si>
   <si>
     <t xml:space="preserve">41.2073287963867</t>
@@ -1724,22 +1724,22 @@
     <t xml:space="preserve">40.1910018920898</t>
   </si>
   <si>
-    <t xml:space="preserve">39.4518623352051</t>
+    <t xml:space="preserve">39.4518547058105</t>
   </si>
   <si>
     <t xml:space="preserve">38.9898910522461</t>
   </si>
   <si>
-    <t xml:space="preserve">39.174674987793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.5442543029785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.7453575134277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.0225448608398</t>
+    <t xml:space="preserve">39.1746788024902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.544246673584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.745361328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.0225372314453</t>
   </si>
   <si>
     <t xml:space="preserve">39.7290344238281</t>
@@ -1748,34 +1748,34 @@
     <t xml:space="preserve">39.9138259887695</t>
   </si>
   <si>
-    <t xml:space="preserve">40.4681777954102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.6366424560547</t>
+    <t xml:space="preserve">40.4681816101074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.636646270752</t>
   </si>
   <si>
     <t xml:space="preserve">38.6203193664551</t>
   </si>
   <si>
-    <t xml:space="preserve">39.2670707702637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.3268165588379</t>
+    <t xml:space="preserve">39.2670745849609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.3268203735352</t>
   </si>
   <si>
     <t xml:space="preserve">38.8974952697754</t>
   </si>
   <si>
-    <t xml:space="preserve">37.5116004943848</t>
+    <t xml:space="preserve">37.5115966796875</t>
   </si>
   <si>
     <t xml:space="preserve">38.7127151489258</t>
   </si>
   <si>
-    <t xml:space="preserve">39.0822868347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.7724571228027</t>
+    <t xml:space="preserve">39.0822830200195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.7724533081055</t>
   </si>
   <si>
     <t xml:space="preserve">36.310489654541</t>
@@ -1784,10 +1784,10 @@
     <t xml:space="preserve">36.2180976867676</t>
   </si>
   <si>
-    <t xml:space="preserve">35.3865585327148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.033317565918</t>
+    <t xml:space="preserve">35.3865623474121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.0333137512207</t>
   </si>
   <si>
     <t xml:space="preserve">34.1854515075684</t>
@@ -1796,13 +1796,13 @@
     <t xml:space="preserve">33.7234840393066</t>
   </si>
   <si>
-    <t xml:space="preserve">33.169132232666</t>
+    <t xml:space="preserve">33.1691246032715</t>
   </si>
   <si>
     <t xml:space="preserve">32.6147689819336</t>
   </si>
   <si>
-    <t xml:space="preserve">33.6310958862305</t>
+    <t xml:space="preserve">33.6310920715332</t>
   </si>
   <si>
     <t xml:space="preserve">32.7071647644043</t>
@@ -1811,16 +1811,16 @@
     <t xml:space="preserve">31.9680156707764</t>
   </si>
   <si>
-    <t xml:space="preserve">32.0604095458984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4136581420898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6908378601074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2451934814453</t>
+    <t xml:space="preserve">32.0604133605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4136600494385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6908359527588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2451972961426</t>
   </si>
   <si>
     <t xml:space="preserve">32.7995529174805</t>
@@ -1838,7 +1838,7 @@
     <t xml:space="preserve">35.0169906616211</t>
   </si>
   <si>
-    <t xml:space="preserve">32.3375854492188</t>
+    <t xml:space="preserve">32.337589263916</t>
   </si>
   <si>
     <t xml:space="preserve">32.4299774169922</t>
@@ -1850,25 +1850,25 @@
     <t xml:space="preserve">31.5060482025146</t>
   </si>
   <si>
-    <t xml:space="preserve">31.3212661743164</t>
+    <t xml:space="preserve">31.3212642669678</t>
   </si>
   <si>
     <t xml:space="preserve">31.5522480010986</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9218196868896</t>
+    <t xml:space="preserve">31.921817779541</t>
   </si>
   <si>
     <t xml:space="preserve">32.1528015136719</t>
   </si>
   <si>
-    <t xml:space="preserve">33.4925003051758</t>
+    <t xml:space="preserve">33.4924964904785</t>
   </si>
   <si>
     <t xml:space="preserve">34.3702354431152</t>
   </si>
   <si>
-    <t xml:space="preserve">33.8620758056641</t>
+    <t xml:space="preserve">33.8620719909668</t>
   </si>
   <si>
     <t xml:space="preserve">32.1066055297852</t>
@@ -1883,7 +1883,7 @@
     <t xml:space="preserve">28.7804527282715</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3643817901611</t>
+    <t xml:space="preserve">28.3643836975098</t>
   </si>
   <si>
     <t xml:space="preserve">28.3180351257324</t>
@@ -1892,31 +1892,31 @@
     <t xml:space="preserve">27.8082180023193</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7618732452393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0863018035889</t>
+    <t xml:space="preserve">27.761869430542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0862998962402</t>
   </si>
   <si>
     <t xml:space="preserve">27.9936084747314</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6424655914307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5230598449707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1255683898926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5694065093994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.105936050415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9009132385254</t>
+    <t xml:space="preserve">28.642463684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5230579376221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1255722045898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5694046020508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1059341430664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9009113311768</t>
   </si>
   <si>
     <t xml:space="preserve">27.7155227661133</t>
@@ -1934,40 +1934,40 @@
     <t xml:space="preserve">26.186071395874</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6031951904297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2324199676514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5568466186523</t>
+    <t xml:space="preserve">26.6031970977783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2324180603027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.556848526001</t>
   </si>
   <si>
     <t xml:space="preserve">26.3251132965088</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8152980804443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6299095153809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2591323852539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7029685974121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6566200256348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9614162445068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7296772003174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0273952484131</t>
+    <t xml:space="preserve">25.8152961730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6299076080322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2591304779053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7029666900635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6566219329834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9614143371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7296810150146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0273971557617</t>
   </si>
   <si>
     <t xml:space="preserve">24.7956619262695</t>
@@ -1976,43 +1976,43 @@
     <t xml:space="preserve">24.2858448028564</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6102714538574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3321914672852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5175800323486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3785381317139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4712314605713</t>
+    <t xml:space="preserve">24.6102733612061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3321933746338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.517578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3785362243652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4712333679199</t>
   </si>
   <si>
     <t xml:space="preserve">23.8687210083008</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5442924499512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1004543304443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4979438781738</t>
+    <t xml:space="preserve">23.5442905426025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.100456237793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4979457855225</t>
   </si>
   <si>
     <t xml:space="preserve">23.8223743438721</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9150657653809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1931495666504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8883571624756</t>
+    <t xml:space="preserve">23.9150676727295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.193151473999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.888355255127</t>
   </si>
   <si>
     <t xml:space="preserve">25.5835609436035</t>
@@ -2033,25 +2033,25 @@
     <t xml:space="preserve">25.4445209503174</t>
   </si>
   <si>
-    <t xml:space="preserve">24.981050491333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8616428375244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1200923919678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0077629089355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4515972137451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1271705627441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0808200836182</t>
+    <t xml:space="preserve">24.9810485839844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.861644744873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1200904846191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0077610015869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4515953063965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1271686553955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0808219909668</t>
   </si>
   <si>
     <t xml:space="preserve">23.3125553131104</t>
@@ -2060,40 +2060,40 @@
     <t xml:space="preserve">23.6369857788086</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5906410217285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4052505493164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2662086486816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3589038848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8027381896973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6173496246338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1735153198242</t>
+    <t xml:space="preserve">23.5906372070312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.405252456665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2662105560303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3589057922363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8027400970459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6173515319824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1735134124756</t>
   </si>
   <si>
     <t xml:space="preserve">22.8954334259033</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9684925079346</t>
+    <t xml:space="preserve">21.9684944152832</t>
   </si>
   <si>
     <t xml:space="preserve">21.5513706207275</t>
   </si>
   <si>
-    <t xml:space="preserve">21.273286819458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8561630249023</t>
+    <t xml:space="preserve">21.2732887268066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.856164932251</t>
   </si>
   <si>
     <t xml:space="preserve">20.7171230316162</t>
@@ -2102,37 +2102,37 @@
     <t xml:space="preserve">19.9755687713623</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1609573364258</t>
+    <t xml:space="preserve">20.1609592437744</t>
   </si>
   <si>
     <t xml:space="preserve">20.2073040008545</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8365306854248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5584487915039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.604793548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9292240142822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0682640075684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1146106719971</t>
+    <t xml:space="preserve">19.8365268707275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5584468841553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6047954559326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9292221069336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.068265914917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1146125793457</t>
   </si>
   <si>
     <t xml:space="preserve">20.8098182678223</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9952049255371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5780830383301</t>
+    <t xml:space="preserve">20.9952030181885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5780811309814</t>
   </si>
   <si>
     <t xml:space="preserve">21.0878982543945</t>
@@ -2150,31 +2150,31 @@
     <t xml:space="preserve">22.3856143951416</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3392696380615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6833305358887</t>
+    <t xml:space="preserve">22.3392677307129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6833324432373</t>
   </si>
   <si>
     <t xml:space="preserve">24.5639247894287</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4248867034912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1664371490479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2127857208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8420066833496</t>
+    <t xml:space="preserve">24.4248847961426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1664390563965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2127838134766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.842004776001</t>
   </si>
   <si>
     <t xml:space="preserve">25.7689476013184</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7226009368896</t>
+    <t xml:space="preserve">25.7226028442383</t>
   </si>
   <si>
     <t xml:space="preserve">25.3518257141113</t>
@@ -2183,16 +2183,16 @@
     <t xml:space="preserve">25.5372142791748</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3054790496826</t>
+    <t xml:space="preserve">25.305477142334</t>
   </si>
   <si>
     <t xml:space="preserve">25.6762542724609</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4908657073975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6691780090332</t>
+    <t xml:space="preserve">25.4908676147461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6691799163818</t>
   </si>
   <si>
     <t xml:space="preserve">27.2057075500488</t>
@@ -2201,22 +2201,22 @@
     <t xml:space="preserve">27.4837875366211</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2984008789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5764846801758</t>
+    <t xml:space="preserve">27.2984027862549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5764827728271</t>
   </si>
   <si>
     <t xml:space="preserve">28.0399532318115</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1789951324463</t>
+    <t xml:space="preserve">28.178991317749</t>
   </si>
   <si>
     <t xml:space="preserve">28.2716884613037</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1326465606689</t>
+    <t xml:space="preserve">28.1326484680176</t>
   </si>
   <si>
     <t xml:space="preserve">27.4374408721924</t>
@@ -2231,22 +2231,22 @@
     <t xml:space="preserve">25.39817237854</t>
   </si>
   <si>
-    <t xml:space="preserve">22.941780090332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2002277374268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1538791656494</t>
+    <t xml:space="preserve">22.9417819976807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2002296447754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.153881072998</t>
   </si>
   <si>
     <t xml:space="preserve">22.1075344085693</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7100448608398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9881248474121</t>
+    <t xml:space="preserve">22.7100429534912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9881267547607</t>
   </si>
   <si>
     <t xml:space="preserve">23.2198619842529</t>
@@ -2258,22 +2258,22 @@
     <t xml:space="preserve">20.6244277954102</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6707763671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.485387802124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2536544799805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5317325592041</t>
+    <t xml:space="preserve">20.6707744598389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4853897094727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2536506652832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5317363739014</t>
   </si>
   <si>
     <t xml:space="preserve">21.1342468261719</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7831058502197</t>
+    <t xml:space="preserve">21.7831039428711</t>
   </si>
   <si>
     <t xml:space="preserve">21.6440620422363</t>
@@ -2288,22 +2288,22 @@
     <t xml:space="preserve">21.8757991790771</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1805953979492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9025096893311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6679439544678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4127330780029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6213912963867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5748424530029</t>
+    <t xml:space="preserve">21.1805934906006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9025115966797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6679420471191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4127311706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6213932037354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5748443603516</t>
   </si>
   <si>
     <t xml:space="preserve">20.3886451721191</t>
@@ -2312,13 +2312,13 @@
     <t xml:space="preserve">21.3661842346191</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9937858581543</t>
+    <t xml:space="preserve">20.9937877655029</t>
   </si>
   <si>
     <t xml:space="preserve">20.9006900787354</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0403385162354</t>
+    <t xml:space="preserve">21.0403366088867</t>
   </si>
   <si>
     <t xml:space="preserve">21.1799850463867</t>
@@ -2330,22 +2330,22 @@
     <t xml:space="preserve">20.9472389221191</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4817447662354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3420963287354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2489967346191</t>
+    <t xml:space="preserve">20.4817428588867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3420944213867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2489986419678</t>
   </si>
   <si>
     <t xml:space="preserve">20.1558990478516</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0162506103516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6904029846191</t>
+    <t xml:space="preserve">20.0162487030029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6904048919678</t>
   </si>
   <si>
     <t xml:space="preserve">19.6438541412354</t>
@@ -2354,10 +2354,10 @@
     <t xml:space="preserve">19.7835025787354</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7369556427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5973052978516</t>
+    <t xml:space="preserve">19.7369537353516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5973033905029</t>
   </si>
   <si>
     <t xml:space="preserve">19.4111080169678</t>
@@ -2375,7 +2375,7 @@
     <t xml:space="preserve">20.2024478912354</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4351940155029</t>
+    <t xml:space="preserve">20.4351959228516</t>
   </si>
   <si>
     <t xml:space="preserve">19.4576568603516</t>
@@ -2387,7 +2387,7 @@
     <t xml:space="preserve">19.9697017669678</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9231510162354</t>
+    <t xml:space="preserve">19.9231491088867</t>
   </si>
   <si>
     <t xml:space="preserve">19.3645572662354</t>
@@ -2399,13 +2399,13 @@
     <t xml:space="preserve">18.8990631103516</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1318092346191</t>
+    <t xml:space="preserve">19.1318111419678</t>
   </si>
   <si>
     <t xml:space="preserve">18.6197681427002</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8525161743164</t>
+    <t xml:space="preserve">18.8525142669678</t>
   </si>
   <si>
     <t xml:space="preserve">18.7128677368164</t>
@@ -2414,13 +2414,13 @@
     <t xml:space="preserve">18.6663150787354</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7594146728516</t>
+    <t xml:space="preserve">18.7594165802002</t>
   </si>
   <si>
     <t xml:space="preserve">18.5266666412354</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4708099365234</t>
+    <t xml:space="preserve">18.4708080291748</t>
   </si>
   <si>
     <t xml:space="preserve">18.3963298797607</t>
@@ -2435,13 +2435,13 @@
     <t xml:space="preserve">18.210132598877</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9680728912354</t>
+    <t xml:space="preserve">17.968074798584</t>
   </si>
   <si>
     <t xml:space="preserve">17.6701583862305</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5770587921143</t>
+    <t xml:space="preserve">17.5770606994629</t>
   </si>
   <si>
     <t xml:space="preserve">17.6887798309326</t>
@@ -2456,25 +2456,25 @@
     <t xml:space="preserve">17.3163833618164</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1301860809326</t>
+    <t xml:space="preserve">17.130184173584</t>
   </si>
   <si>
     <t xml:space="preserve">16.7577896118164</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2232837677002</t>
+    <t xml:space="preserve">17.2232856750488</t>
   </si>
   <si>
     <t xml:space="preserve">17.3350048065186</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4094829559326</t>
+    <t xml:space="preserve">17.409481048584</t>
   </si>
   <si>
     <t xml:space="preserve">17.651538848877</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7260208129883</t>
+    <t xml:space="preserve">17.7260189056396</t>
   </si>
   <si>
     <t xml:space="preserve">17.7073993682861</t>
@@ -2492,16 +2492,16 @@
     <t xml:space="preserve">16.5715923309326</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5529747009277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.092945098877</t>
+    <t xml:space="preserve">16.5529727935791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0929470062256</t>
   </si>
   <si>
     <t xml:space="preserve">16.9253673553467</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2736778259277</t>
+    <t xml:space="preserve">16.2736759185791</t>
   </si>
   <si>
     <t xml:space="preserve">16.0130004882812</t>
@@ -2513,13 +2513,13 @@
     <t xml:space="preserve">16.2364387512207</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2922954559326</t>
+    <t xml:space="preserve">16.2922973632812</t>
   </si>
   <si>
     <t xml:space="preserve">17.0370864868164</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8136501312256</t>
+    <t xml:space="preserve">16.813648223877</t>
   </si>
   <si>
     <t xml:space="preserve">16.404016494751</t>
@@ -2531,16 +2531,16 @@
     <t xml:space="preserve">16.3295364379883</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1805763244629</t>
+    <t xml:space="preserve">16.1805782318115</t>
   </si>
   <si>
     <t xml:space="preserve">16.3667736053467</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4598731994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7709426879883</t>
+    <t xml:space="preserve">16.4598751068115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7709445953369</t>
   </si>
   <si>
     <t xml:space="preserve">15.7337017059326</t>
@@ -2558,7 +2558,7 @@
     <t xml:space="preserve">16.5157337188721</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4784927368164</t>
+    <t xml:space="preserve">16.478494644165</t>
   </si>
   <si>
     <t xml:space="preserve">16.6460704803467</t>
@@ -2573,13 +2573,13 @@
     <t xml:space="preserve">17.0184669494629</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0557060241699</t>
+    <t xml:space="preserve">17.0557079315186</t>
   </si>
   <si>
     <t xml:space="preserve">17.4839611053467</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3536224365234</t>
+    <t xml:space="preserve">17.3536205291748</t>
   </si>
   <si>
     <t xml:space="preserve">17.372241973877</t>
@@ -2612,7 +2612,7 @@
     <t xml:space="preserve">16.5902118682861</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3481540679932</t>
+    <t xml:space="preserve">16.3481559753418</t>
   </si>
   <si>
     <t xml:space="preserve">16.3109149932861</t>
@@ -2627,7 +2627,7 @@
     <t xml:space="preserve">16.0502395629883</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2550563812256</t>
+    <t xml:space="preserve">16.255054473877</t>
   </si>
   <si>
     <t xml:space="preserve">16.1060981750488</t>
@@ -2645,7 +2645,7 @@
     <t xml:space="preserve">17.4653415679932</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9494552612305</t>
+    <t xml:space="preserve">17.9494571685791</t>
   </si>
   <si>
     <t xml:space="preserve">17.8749771118164</t>
@@ -2657,7 +2657,7 @@
     <t xml:space="preserve">17.5491313934326</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3629322052002</t>
+    <t xml:space="preserve">17.3629341125488</t>
   </si>
   <si>
     <t xml:space="preserve">17.5025806427002</t>
@@ -2672,7 +2672,7 @@
     <t xml:space="preserve">18.0611743927002</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8284282684326</t>
+    <t xml:space="preserve">17.828426361084</t>
   </si>
   <si>
     <t xml:space="preserve">18.3981628417969</t>
@@ -19187,7 +19187,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G610" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -19239,7 +19239,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G612" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -19291,7 +19291,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G614" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -19317,7 +19317,7 @@
         <v>12.75</v>
       </c>
       <c r="G615" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -19343,7 +19343,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G616" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -19395,7 +19395,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G618" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -19421,7 +19421,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G619" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -19447,7 +19447,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G620" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -19473,7 +19473,7 @@
         <v>12.75</v>
       </c>
       <c r="G621" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -19499,7 +19499,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G622" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -19525,7 +19525,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G623" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -19551,7 +19551,7 @@
         <v>13</v>
       </c>
       <c r="G624" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -19577,7 +19577,7 @@
         <v>13</v>
       </c>
       <c r="G625" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -19603,7 +19603,7 @@
         <v>12.75</v>
       </c>
       <c r="G626" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -19629,7 +19629,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G627" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H627" t="s">
         <v>9</v>
@@ -19655,7 +19655,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G628" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H628" t="s">
         <v>9</v>
@@ -19681,7 +19681,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G629" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H629" t="s">
         <v>9</v>
@@ -19707,7 +19707,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G630" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H630" t="s">
         <v>9</v>
@@ -19733,7 +19733,7 @@
         <v>12.75</v>
       </c>
       <c r="G631" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H631" t="s">
         <v>9</v>
@@ -19759,7 +19759,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G632" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H632" t="s">
         <v>9</v>
@@ -19785,7 +19785,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G633" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H633" t="s">
         <v>9</v>
@@ -19811,7 +19811,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G634" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H634" t="s">
         <v>9</v>
@@ -19837,7 +19837,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G635" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H635" t="s">
         <v>9</v>
@@ -19863,7 +19863,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G636" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H636" t="s">
         <v>9</v>
@@ -19889,7 +19889,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G637" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H637" t="s">
         <v>9</v>
@@ -19915,7 +19915,7 @@
         <v>12.25</v>
       </c>
       <c r="G638" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H638" t="s">
         <v>9</v>
@@ -19941,7 +19941,7 @@
         <v>12.25</v>
       </c>
       <c r="G639" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H639" t="s">
         <v>9</v>
@@ -19967,7 +19967,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G640" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H640" t="s">
         <v>9</v>
@@ -19993,7 +19993,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G641" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H641" t="s">
         <v>9</v>
@@ -20019,7 +20019,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G642" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H642" t="s">
         <v>9</v>
@@ -20045,7 +20045,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G643" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H643" t="s">
         <v>9</v>
@@ -20071,7 +20071,7 @@
         <v>12.5</v>
       </c>
       <c r="G644" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H644" t="s">
         <v>9</v>
@@ -20097,7 +20097,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G645" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H645" t="s">
         <v>9</v>
@@ -20123,7 +20123,7 @@
         <v>12.5</v>
       </c>
       <c r="G646" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H646" t="s">
         <v>9</v>
@@ -20149,7 +20149,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G647" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H647" t="s">
         <v>9</v>
@@ -20175,7 +20175,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G648" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H648" t="s">
         <v>9</v>
@@ -20201,7 +20201,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G649" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H649" t="s">
         <v>9</v>
@@ -20227,7 +20227,7 @@
         <v>12.5</v>
       </c>
       <c r="G650" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H650" t="s">
         <v>9</v>
@@ -20253,7 +20253,7 @@
         <v>12.5</v>
       </c>
       <c r="G651" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H651" t="s">
         <v>9</v>
@@ -20279,7 +20279,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G652" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H652" t="s">
         <v>9</v>
@@ -20305,7 +20305,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G653" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H653" t="s">
         <v>9</v>
@@ -20331,7 +20331,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G654" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H654" t="s">
         <v>9</v>
@@ -20357,7 +20357,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G655" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H655" t="s">
         <v>9</v>
@@ -20383,7 +20383,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G656" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H656" t="s">
         <v>9</v>
@@ -20409,7 +20409,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G657" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H657" t="s">
         <v>9</v>
@@ -20435,7 +20435,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G658" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H658" t="s">
         <v>9</v>
@@ -20461,7 +20461,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G659" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H659" t="s">
         <v>9</v>
@@ -20487,7 +20487,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G660" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H660" t="s">
         <v>9</v>
@@ -20513,7 +20513,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G661" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H661" t="s">
         <v>9</v>
@@ -20539,7 +20539,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G662" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H662" t="s">
         <v>9</v>
@@ -20565,7 +20565,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G663" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H663" t="s">
         <v>9</v>
@@ -20591,7 +20591,7 @@
         <v>12.75</v>
       </c>
       <c r="G664" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -20617,7 +20617,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G665" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H665" t="s">
         <v>9</v>
@@ -20643,7 +20643,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G666" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H666" t="s">
         <v>9</v>
@@ -20669,7 +20669,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G667" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H667" t="s">
         <v>9</v>
@@ -20695,7 +20695,7 @@
         <v>12.25</v>
       </c>
       <c r="G668" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H668" t="s">
         <v>9</v>
@@ -20721,7 +20721,7 @@
         <v>12.25</v>
       </c>
       <c r="G669" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H669" t="s">
         <v>9</v>
@@ -20747,7 +20747,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G670" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H670" t="s">
         <v>9</v>
@@ -20773,7 +20773,7 @@
         <v>12.5</v>
       </c>
       <c r="G671" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H671" t="s">
         <v>9</v>
@@ -20799,7 +20799,7 @@
         <v>12.5</v>
       </c>
       <c r="G672" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H672" t="s">
         <v>9</v>
@@ -20825,7 +20825,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G673" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H673" t="s">
         <v>9</v>
@@ -20851,7 +20851,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G674" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H674" t="s">
         <v>9</v>
@@ -20877,7 +20877,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G675" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H675" t="s">
         <v>9</v>
@@ -20903,7 +20903,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G676" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H676" t="s">
         <v>9</v>
@@ -20929,7 +20929,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G677" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H677" t="s">
         <v>9</v>
@@ -20955,7 +20955,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G678" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H678" t="s">
         <v>9</v>
@@ -20981,7 +20981,7 @@
         <v>12.25</v>
       </c>
       <c r="G679" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H679" t="s">
         <v>9</v>
@@ -21007,7 +21007,7 @@
         <v>12.25</v>
       </c>
       <c r="G680" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H680" t="s">
         <v>9</v>
@@ -21033,7 +21033,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G681" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H681" t="s">
         <v>9</v>
@@ -21059,7 +21059,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G682" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H682" t="s">
         <v>9</v>
@@ -21085,7 +21085,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G683" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H683" t="s">
         <v>9</v>
@@ -21111,7 +21111,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G684" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H684" t="s">
         <v>9</v>
@@ -21137,7 +21137,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G685" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H685" t="s">
         <v>9</v>
@@ -21163,7 +21163,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G686" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H686" t="s">
         <v>9</v>
@@ -21189,7 +21189,7 @@
         <v>12.5</v>
       </c>
       <c r="G687" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H687" t="s">
         <v>9</v>
@@ -21215,7 +21215,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G688" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H688" t="s">
         <v>9</v>
@@ -21241,7 +21241,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G689" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H689" t="s">
         <v>9</v>
@@ -21267,7 +21267,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G690" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H690" t="s">
         <v>9</v>
@@ -21293,7 +21293,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G691" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H691" t="s">
         <v>9</v>
@@ -21319,7 +21319,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G692" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H692" t="s">
         <v>9</v>
@@ -21345,7 +21345,7 @@
         <v>12.75</v>
       </c>
       <c r="G693" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H693" t="s">
         <v>9</v>
@@ -21371,7 +21371,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G694" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -21397,7 +21397,7 @@
         <v>13.25</v>
       </c>
       <c r="G695" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H695" t="s">
         <v>9</v>
@@ -21423,7 +21423,7 @@
         <v>13</v>
       </c>
       <c r="G696" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H696" t="s">
         <v>9</v>
@@ -21449,7 +21449,7 @@
         <v>13</v>
       </c>
       <c r="G697" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H697" t="s">
         <v>9</v>
@@ -21475,7 +21475,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G698" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H698" t="s">
         <v>9</v>
@@ -21501,7 +21501,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G699" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H699" t="s">
         <v>9</v>
@@ -21527,7 +21527,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G700" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H700" t="s">
         <v>9</v>
@@ -21553,7 +21553,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G701" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H701" t="s">
         <v>9</v>
@@ -21579,7 +21579,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G702" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H702" t="s">
         <v>9</v>
@@ -21605,7 +21605,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G703" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H703" t="s">
         <v>9</v>
@@ -21631,7 +21631,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G704" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H704" t="s">
         <v>9</v>
@@ -21657,7 +21657,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G705" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H705" t="s">
         <v>9</v>
@@ -21683,7 +21683,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G706" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H706" t="s">
         <v>9</v>
@@ -21709,7 +21709,7 @@
         <v>13.25</v>
       </c>
       <c r="G707" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H707" t="s">
         <v>9</v>
@@ -21735,7 +21735,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G708" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H708" t="s">
         <v>9</v>
@@ -21761,7 +21761,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G709" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H709" t="s">
         <v>9</v>
@@ -21787,7 +21787,7 @@
         <v>13</v>
       </c>
       <c r="G710" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H710" t="s">
         <v>9</v>
@@ -21813,7 +21813,7 @@
         <v>13</v>
       </c>
       <c r="G711" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H711" t="s">
         <v>9</v>
@@ -21839,7 +21839,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G712" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H712" t="s">
         <v>9</v>
@@ -21865,7 +21865,7 @@
         <v>13</v>
       </c>
       <c r="G713" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H713" t="s">
         <v>9</v>
@@ -21891,7 +21891,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G714" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H714" t="s">
         <v>9</v>
@@ -21917,7 +21917,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G715" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H715" t="s">
         <v>9</v>
@@ -21943,7 +21943,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G716" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H716" t="s">
         <v>9</v>
@@ -21969,7 +21969,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G717" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H717" t="s">
         <v>9</v>
@@ -21995,7 +21995,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G718" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H718" t="s">
         <v>9</v>
@@ -22021,7 +22021,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G719" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H719" t="s">
         <v>9</v>
@@ -22047,7 +22047,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G720" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H720" t="s">
         <v>9</v>
@@ -22073,7 +22073,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G721" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H721" t="s">
         <v>9</v>
@@ -22099,7 +22099,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G722" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H722" t="s">
         <v>9</v>
@@ -22125,7 +22125,7 @@
         <v>12.5</v>
       </c>
       <c r="G723" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H723" t="s">
         <v>9</v>
@@ -22151,7 +22151,7 @@
         <v>13</v>
       </c>
       <c r="G724" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H724" t="s">
         <v>9</v>
@@ -22177,7 +22177,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G725" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H725" t="s">
         <v>9</v>
@@ -22203,7 +22203,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G726" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H726" t="s">
         <v>9</v>
@@ -22229,7 +22229,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G727" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H727" t="s">
         <v>9</v>
@@ -22255,7 +22255,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G728" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H728" t="s">
         <v>9</v>
@@ -22281,7 +22281,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G729" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H729" t="s">
         <v>9</v>
@@ -22307,7 +22307,7 @@
         <v>12.5</v>
       </c>
       <c r="G730" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H730" t="s">
         <v>9</v>
@@ -22333,7 +22333,7 @@
         <v>12.25</v>
       </c>
       <c r="G731" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H731" t="s">
         <v>9</v>
@@ -22359,7 +22359,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G732" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H732" t="s">
         <v>9</v>
@@ -22385,7 +22385,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G733" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H733" t="s">
         <v>9</v>
@@ -22411,7 +22411,7 @@
         <v>12</v>
       </c>
       <c r="G734" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H734" t="s">
         <v>9</v>
@@ -22437,7 +22437,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G735" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H735" t="s">
         <v>9</v>
@@ -22463,7 +22463,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G736" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H736" t="s">
         <v>9</v>
@@ -22489,7 +22489,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G737" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H737" t="s">
         <v>9</v>
@@ -22515,7 +22515,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G738" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H738" t="s">
         <v>9</v>
@@ -22541,7 +22541,7 @@
         <v>11.5</v>
       </c>
       <c r="G739" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H739" t="s">
         <v>9</v>
@@ -22567,7 +22567,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G740" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H740" t="s">
         <v>9</v>
@@ -22593,7 +22593,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G741" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H741" t="s">
         <v>9</v>
@@ -22619,7 +22619,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G742" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H742" t="s">
         <v>9</v>
@@ -22645,7 +22645,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G743" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H743" t="s">
         <v>9</v>
@@ -22671,7 +22671,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G744" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H744" t="s">
         <v>9</v>
@@ -22697,7 +22697,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G745" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H745" t="s">
         <v>9</v>
@@ -22723,7 +22723,7 @@
         <v>11.5</v>
       </c>
       <c r="G746" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H746" t="s">
         <v>9</v>
@@ -22749,7 +22749,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G747" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H747" t="s">
         <v>9</v>
@@ -22775,7 +22775,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G748" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H748" t="s">
         <v>9</v>
@@ -22801,7 +22801,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G749" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H749" t="s">
         <v>9</v>
@@ -22827,7 +22827,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G750" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H750" t="s">
         <v>9</v>
@@ -22853,7 +22853,7 @@
         <v>10.25</v>
       </c>
       <c r="G751" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H751" t="s">
         <v>9</v>
@@ -22879,7 +22879,7 @@
         <v>10.25</v>
       </c>
       <c r="G752" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H752" t="s">
         <v>9</v>
@@ -22905,7 +22905,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G753" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H753" t="s">
         <v>9</v>
@@ -22931,7 +22931,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G754" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H754" t="s">
         <v>9</v>
@@ -22957,7 +22957,7 @@
         <v>10.5</v>
       </c>
       <c r="G755" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H755" t="s">
         <v>9</v>
@@ -22983,7 +22983,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G756" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H756" t="s">
         <v>9</v>
@@ -23009,7 +23009,7 @@
         <v>10.5</v>
       </c>
       <c r="G757" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H757" t="s">
         <v>9</v>
@@ -23035,7 +23035,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G758" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H758" t="s">
         <v>9</v>
@@ -23061,7 +23061,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G759" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H759" t="s">
         <v>9</v>
@@ -23087,7 +23087,7 @@
         <v>10.75</v>
       </c>
       <c r="G760" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H760" t="s">
         <v>9</v>
@@ -23113,7 +23113,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G761" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H761" t="s">
         <v>9</v>
@@ -23139,7 +23139,7 @@
         <v>11.5</v>
       </c>
       <c r="G762" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H762" t="s">
         <v>9</v>
@@ -23165,7 +23165,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G763" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H763" t="s">
         <v>9</v>
@@ -23191,7 +23191,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G764" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H764" t="s">
         <v>9</v>
@@ -23217,7 +23217,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G765" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H765" t="s">
         <v>9</v>
@@ -23243,7 +23243,7 @@
         <v>11.5</v>
       </c>
       <c r="G766" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H766" t="s">
         <v>9</v>
@@ -23269,7 +23269,7 @@
         <v>11.5</v>
       </c>
       <c r="G767" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H767" t="s">
         <v>9</v>
@@ -23295,7 +23295,7 @@
         <v>11.75</v>
       </c>
       <c r="G768" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H768" t="s">
         <v>9</v>
@@ -23321,7 +23321,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G769" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H769" t="s">
         <v>9</v>
@@ -23347,7 +23347,7 @@
         <v>12</v>
       </c>
       <c r="G770" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H770" t="s">
         <v>9</v>
@@ -23373,7 +23373,7 @@
         <v>11.75</v>
       </c>
       <c r="G771" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H771" t="s">
         <v>9</v>
@@ -23399,7 +23399,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G772" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H772" t="s">
         <v>9</v>
@@ -23425,7 +23425,7 @@
         <v>11.5</v>
       </c>
       <c r="G773" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H773" t="s">
         <v>9</v>
@@ -23451,7 +23451,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G774" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H774" t="s">
         <v>9</v>
@@ -23477,7 +23477,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G775" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H775" t="s">
         <v>9</v>
@@ -23503,7 +23503,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G776" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H776" t="s">
         <v>9</v>
@@ -23529,7 +23529,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G777" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H777" t="s">
         <v>9</v>
@@ -23555,7 +23555,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G778" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H778" t="s">
         <v>9</v>
@@ -23581,7 +23581,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G779" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H779" t="s">
         <v>9</v>
@@ -23607,7 +23607,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G780" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H780" t="s">
         <v>9</v>
@@ -23633,7 +23633,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G781" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H781" t="s">
         <v>9</v>
@@ -23659,7 +23659,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G782" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H782" t="s">
         <v>9</v>
@@ -23685,7 +23685,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G783" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H783" t="s">
         <v>9</v>
@@ -23711,7 +23711,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G784" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H784" t="s">
         <v>9</v>
@@ -23737,7 +23737,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G785" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H785" t="s">
         <v>9</v>
@@ -23763,7 +23763,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G786" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H786" t="s">
         <v>9</v>
@@ -23789,7 +23789,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G787" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H787" t="s">
         <v>9</v>
@@ -23815,7 +23815,7 @@
         <v>11.5</v>
       </c>
       <c r="G788" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H788" t="s">
         <v>9</v>
@@ -23841,7 +23841,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G789" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H789" t="s">
         <v>9</v>
@@ -23867,7 +23867,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G790" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H790" t="s">
         <v>9</v>
@@ -23893,7 +23893,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G791" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H791" t="s">
         <v>9</v>
@@ -23919,7 +23919,7 @@
         <v>11.5</v>
       </c>
       <c r="G792" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H792" t="s">
         <v>9</v>
@@ -23945,7 +23945,7 @@
         <v>11.25</v>
       </c>
       <c r="G793" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H793" t="s">
         <v>9</v>
@@ -23971,7 +23971,7 @@
         <v>11.25</v>
       </c>
       <c r="G794" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H794" t="s">
         <v>9</v>
@@ -23997,7 +23997,7 @@
         <v>11.5</v>
       </c>
       <c r="G795" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H795" t="s">
         <v>9</v>
@@ -24023,7 +24023,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G796" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H796" t="s">
         <v>9</v>
@@ -24049,7 +24049,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G797" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H797" t="s">
         <v>9</v>
@@ -24075,7 +24075,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G798" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H798" t="s">
         <v>9</v>
@@ -24101,7 +24101,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G799" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H799" t="s">
         <v>9</v>
@@ -24127,7 +24127,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G800" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H800" t="s">
         <v>9</v>
@@ -24153,7 +24153,7 @@
         <v>11</v>
       </c>
       <c r="G801" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H801" t="s">
         <v>9</v>
@@ -24179,7 +24179,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G802" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H802" t="s">
         <v>9</v>
@@ -24205,7 +24205,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G803" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H803" t="s">
         <v>9</v>
@@ -24231,7 +24231,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G804" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H804" t="s">
         <v>9</v>
@@ -24257,7 +24257,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G805" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H805" t="s">
         <v>9</v>
@@ -24283,7 +24283,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G806" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H806" t="s">
         <v>9</v>
@@ -24309,7 +24309,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G807" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H807" t="s">
         <v>9</v>
@@ -24335,7 +24335,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G808" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H808" t="s">
         <v>9</v>
@@ -24361,7 +24361,7 @@
         <v>11</v>
       </c>
       <c r="G809" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H809" t="s">
         <v>9</v>
@@ -24387,7 +24387,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G810" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H810" t="s">
         <v>9</v>
@@ -24413,7 +24413,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G811" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H811" t="s">
         <v>9</v>
@@ -24439,7 +24439,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G812" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H812" t="s">
         <v>9</v>
@@ -24465,7 +24465,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G813" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H813" t="s">
         <v>9</v>
@@ -24491,7 +24491,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G814" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H814" t="s">
         <v>9</v>
@@ -24517,7 +24517,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G815" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H815" t="s">
         <v>9</v>
@@ -24543,7 +24543,7 @@
         <v>10.75</v>
       </c>
       <c r="G816" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H816" t="s">
         <v>9</v>
@@ -24569,7 +24569,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G817" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H817" t="s">
         <v>9</v>
@@ -24595,7 +24595,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G818" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H818" t="s">
         <v>9</v>
@@ -24621,7 +24621,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G819" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H819" t="s">
         <v>9</v>
@@ -24647,7 +24647,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G820" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H820" t="s">
         <v>9</v>
@@ -24673,7 +24673,7 @@
         <v>11.25</v>
       </c>
       <c r="G821" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H821" t="s">
         <v>9</v>
@@ -24699,7 +24699,7 @@
         <v>11.25</v>
       </c>
       <c r="G822" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H822" t="s">
         <v>9</v>
@@ -24725,7 +24725,7 @@
         <v>11.25</v>
       </c>
       <c r="G823" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H823" t="s">
         <v>9</v>
@@ -24751,7 +24751,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G824" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H824" t="s">
         <v>9</v>
@@ -24777,7 +24777,7 @@
         <v>11.5</v>
       </c>
       <c r="G825" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H825" t="s">
         <v>9</v>
@@ -24803,7 +24803,7 @@
         <v>11.5</v>
       </c>
       <c r="G826" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H826" t="s">
         <v>9</v>
@@ -24829,7 +24829,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G827" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H827" t="s">
         <v>9</v>
@@ -24855,7 +24855,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G828" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H828" t="s">
         <v>9</v>
@@ -24881,7 +24881,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G829" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H829" t="s">
         <v>9</v>
@@ -24907,7 +24907,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G830" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H830" t="s">
         <v>9</v>
@@ -24933,7 +24933,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G831" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H831" t="s">
         <v>9</v>
@@ -24959,7 +24959,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G832" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H832" t="s">
         <v>9</v>
@@ -24985,7 +24985,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G833" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H833" t="s">
         <v>9</v>
@@ -25011,7 +25011,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G834" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H834" t="s">
         <v>9</v>
@@ -25037,7 +25037,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G835" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H835" t="s">
         <v>9</v>
@@ -25063,7 +25063,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G836" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H836" t="s">
         <v>9</v>
@@ -25089,7 +25089,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G837" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H837" t="s">
         <v>9</v>
@@ -25115,7 +25115,7 @@
         <v>11.5</v>
       </c>
       <c r="G838" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H838" t="s">
         <v>9</v>
@@ -25141,7 +25141,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G839" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H839" t="s">
         <v>9</v>
@@ -25167,7 +25167,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G840" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H840" t="s">
         <v>9</v>
@@ -25193,7 +25193,7 @@
         <v>11.5</v>
       </c>
       <c r="G841" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H841" t="s">
         <v>9</v>
@@ -25219,7 +25219,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G842" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H842" t="s">
         <v>9</v>
@@ -25245,7 +25245,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G843" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H843" t="s">
         <v>9</v>
@@ -25271,7 +25271,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G844" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H844" t="s">
         <v>9</v>
@@ -25297,7 +25297,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G845" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H845" t="s">
         <v>9</v>
@@ -25323,7 +25323,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G846" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H846" t="s">
         <v>9</v>
@@ -25349,7 +25349,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G847" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -25375,7 +25375,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G848" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H848" t="s">
         <v>9</v>
@@ -25401,7 +25401,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G849" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H849" t="s">
         <v>9</v>
@@ -25427,7 +25427,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G850" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H850" t="s">
         <v>9</v>
@@ -25453,7 +25453,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G851" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -25479,7 +25479,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G852" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H852" t="s">
         <v>9</v>
@@ -25505,7 +25505,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G853" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -25531,7 +25531,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G854" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H854" t="s">
         <v>9</v>
@@ -25557,7 +25557,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G855" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -25583,7 +25583,7 @@
         <v>11.5</v>
       </c>
       <c r="G856" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -25609,7 +25609,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G857" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H857" t="s">
         <v>9</v>
@@ -25635,7 +25635,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G858" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -25661,7 +25661,7 @@
         <v>11.5</v>
       </c>
       <c r="G859" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H859" t="s">
         <v>9</v>
@@ -25687,7 +25687,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G860" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H860" t="s">
         <v>9</v>
@@ -25713,7 +25713,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G861" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -25739,7 +25739,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G862" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H862" t="s">
         <v>9</v>
@@ -25765,7 +25765,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G863" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H863" t="s">
         <v>9</v>
@@ -25791,7 +25791,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G864" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H864" t="s">
         <v>9</v>
@@ -25817,7 +25817,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G865" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H865" t="s">
         <v>9</v>
@@ -25843,7 +25843,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G866" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H866" t="s">
         <v>9</v>
@@ -25869,7 +25869,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G867" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H867" t="s">
         <v>9</v>
@@ -25895,7 +25895,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G868" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H868" t="s">
         <v>9</v>
@@ -25921,7 +25921,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G869" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H869" t="s">
         <v>9</v>
@@ -25947,7 +25947,7 @@
         <v>12</v>
       </c>
       <c r="G870" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H870" t="s">
         <v>9</v>
@@ -25973,7 +25973,7 @@
         <v>12</v>
       </c>
       <c r="G871" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H871" t="s">
         <v>9</v>
@@ -25999,7 +25999,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G872" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H872" t="s">
         <v>9</v>
@@ -26025,7 +26025,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G873" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H873" t="s">
         <v>9</v>
@@ -26051,7 +26051,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G874" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H874" t="s">
         <v>9</v>
@@ -26077,7 +26077,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G875" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H875" t="s">
         <v>9</v>
@@ -26103,7 +26103,7 @@
         <v>12</v>
       </c>
       <c r="G876" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H876" t="s">
         <v>9</v>
@@ -26129,7 +26129,7 @@
         <v>12</v>
       </c>
       <c r="G877" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H877" t="s">
         <v>9</v>
@@ -26155,7 +26155,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G878" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H878" t="s">
         <v>9</v>
@@ -26181,7 +26181,7 @@
         <v>12</v>
       </c>
       <c r="G879" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H879" t="s">
         <v>9</v>
@@ -26207,7 +26207,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G880" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H880" t="s">
         <v>9</v>
@@ -26233,7 +26233,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G881" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H881" t="s">
         <v>9</v>
@@ -26259,7 +26259,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G882" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H882" t="s">
         <v>9</v>
@@ -26285,7 +26285,7 @@
         <v>12</v>
       </c>
       <c r="G883" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H883" t="s">
         <v>9</v>
@@ -26311,7 +26311,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G884" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H884" t="s">
         <v>9</v>
@@ -26337,7 +26337,7 @@
         <v>12.25</v>
       </c>
       <c r="G885" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H885" t="s">
         <v>9</v>
@@ -26363,7 +26363,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G886" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H886" t="s">
         <v>9</v>
@@ -26389,7 +26389,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G887" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H887" t="s">
         <v>9</v>
@@ -26415,7 +26415,7 @@
         <v>12.25</v>
       </c>
       <c r="G888" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H888" t="s">
         <v>9</v>
@@ -26441,7 +26441,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G889" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H889" t="s">
         <v>9</v>
@@ -26467,7 +26467,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G890" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H890" t="s">
         <v>9</v>
@@ -26493,7 +26493,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G891" t="s">
-        <v>252</v>
+        <v>327</v>
       </c>
       <c r="H891" t="s">
         <v>9</v>
@@ -26597,7 +26597,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G895" t="s">
-        <v>252</v>
+        <v>327</v>
       </c>
       <c r="H895" t="s">
         <v>9</v>
@@ -26753,7 +26753,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G901" t="s">
-        <v>252</v>
+        <v>327</v>
       </c>
       <c r="H901" t="s">
         <v>9</v>
@@ -26857,7 +26857,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G905" t="s">
-        <v>252</v>
+        <v>327</v>
       </c>
       <c r="H905" t="s">
         <v>9</v>
@@ -26883,7 +26883,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G906" t="s">
-        <v>252</v>
+        <v>327</v>
       </c>
       <c r="H906" t="s">
         <v>9</v>
@@ -26987,7 +26987,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G910" t="s">
-        <v>252</v>
+        <v>327</v>
       </c>
       <c r="H910" t="s">
         <v>9</v>
@@ -27065,7 +27065,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G913" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H913" t="s">
         <v>9</v>
@@ -27195,7 +27195,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G918" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H918" t="s">
         <v>9</v>
@@ -27221,7 +27221,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G919" t="s">
-        <v>252</v>
+        <v>327</v>
       </c>
       <c r="H919" t="s">
         <v>9</v>
@@ -27299,7 +27299,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G922" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H922" t="s">
         <v>9</v>
@@ -27325,7 +27325,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G923" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H923" t="s">
         <v>9</v>
@@ -27507,7 +27507,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G930" t="s">
-        <v>252</v>
+        <v>327</v>
       </c>
       <c r="H930" t="s">
         <v>9</v>
@@ -28053,7 +28053,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G951" t="s">
-        <v>252</v>
+        <v>327</v>
       </c>
       <c r="H951" t="s">
         <v>9</v>
@@ -28105,7 +28105,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G953" t="s">
-        <v>252</v>
+        <v>327</v>
       </c>
       <c r="H953" t="s">
         <v>9</v>
@@ -28183,7 +28183,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G956" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H956" t="s">
         <v>9</v>
@@ -28209,7 +28209,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G957" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H957" t="s">
         <v>9</v>
@@ -28235,7 +28235,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G958" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H958" t="s">
         <v>9</v>
@@ -28261,7 +28261,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G959" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H959" t="s">
         <v>9</v>
@@ -28287,7 +28287,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G960" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H960" t="s">
         <v>9</v>
@@ -28339,7 +28339,7 @@
         <v>11.5</v>
       </c>
       <c r="G962" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H962" t="s">
         <v>9</v>
@@ -28365,7 +28365,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G963" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H963" t="s">
         <v>9</v>
@@ -28391,7 +28391,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G964" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H964" t="s">
         <v>9</v>
@@ -28417,7 +28417,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G965" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H965" t="s">
         <v>9</v>
@@ -28443,7 +28443,7 @@
         <v>12.25</v>
       </c>
       <c r="G966" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H966" t="s">
         <v>9</v>
@@ -28469,7 +28469,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G967" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H967" t="s">
         <v>9</v>
@@ -28495,7 +28495,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G968" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H968" t="s">
         <v>9</v>
@@ -28547,7 +28547,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G970" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H970" t="s">
         <v>9</v>
@@ -28599,7 +28599,7 @@
         <v>12.25</v>
       </c>
       <c r="G972" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H972" t="s">
         <v>9</v>
@@ -28625,7 +28625,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G973" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H973" t="s">
         <v>9</v>
@@ -28651,7 +28651,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G974" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H974" t="s">
         <v>9</v>
@@ -28677,7 +28677,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G975" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H975" t="s">
         <v>9</v>
@@ -28755,7 +28755,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G978" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H978" t="s">
         <v>9</v>
@@ -28807,7 +28807,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G980" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H980" t="s">
         <v>9</v>
@@ -28885,7 +28885,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G983" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H983" t="s">
         <v>9</v>
@@ -28937,7 +28937,7 @@
         <v>12.25</v>
       </c>
       <c r="G985" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H985" t="s">
         <v>9</v>
@@ -28963,7 +28963,7 @@
         <v>12.25</v>
       </c>
       <c r="G986" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H986" t="s">
         <v>9</v>
@@ -28989,7 +28989,7 @@
         <v>12.25</v>
       </c>
       <c r="G987" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H987" t="s">
         <v>9</v>
@@ -29015,7 +29015,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G988" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H988" t="s">
         <v>9</v>
@@ -29041,7 +29041,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G989" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H989" t="s">
         <v>9</v>
@@ -29067,7 +29067,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G990" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H990" t="s">
         <v>9</v>
@@ -29093,7 +29093,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G991" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H991" t="s">
         <v>9</v>
@@ -29145,7 +29145,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G993" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H993" t="s">
         <v>9</v>
@@ -29171,7 +29171,7 @@
         <v>12</v>
       </c>
       <c r="G994" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H994" t="s">
         <v>9</v>
@@ -29197,7 +29197,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G995" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H995" t="s">
         <v>9</v>
@@ -29223,7 +29223,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G996" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H996" t="s">
         <v>9</v>
@@ -29249,7 +29249,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G997" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H997" t="s">
         <v>9</v>
@@ -29275,7 +29275,7 @@
         <v>12.25</v>
       </c>
       <c r="G998" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H998" t="s">
         <v>9</v>
@@ -29353,7 +29353,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G1001" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H1001" t="s">
         <v>9</v>
@@ -29379,7 +29379,7 @@
         <v>12</v>
       </c>
       <c r="G1002" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H1002" t="s">
         <v>9</v>
@@ -29431,7 +29431,7 @@
         <v>12.25</v>
       </c>
       <c r="G1004" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H1004" t="s">
         <v>9</v>
@@ -29457,7 +29457,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G1005" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H1005" t="s">
         <v>9</v>
@@ -29483,7 +29483,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G1006" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H1006" t="s">
         <v>9</v>
@@ -29509,7 +29509,7 @@
         <v>12.25</v>
       </c>
       <c r="G1007" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H1007" t="s">
         <v>9</v>
@@ -29561,7 +29561,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G1009" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H1009" t="s">
         <v>9</v>
@@ -29613,7 +29613,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G1011" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H1011" t="s">
         <v>9</v>
@@ -29795,7 +29795,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1018" t="s">
-        <v>252</v>
+        <v>327</v>
       </c>
       <c r="H1018" t="s">
         <v>9</v>
@@ -31017,7 +31017,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1065" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H1065" t="s">
         <v>9</v>
@@ -31043,7 +31043,7 @@
         <v>12</v>
       </c>
       <c r="G1066" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H1066" t="s">
         <v>9</v>
@@ -31069,7 +31069,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1067" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H1067" t="s">
         <v>9</v>
@@ -31095,7 +31095,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G1068" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H1068" t="s">
         <v>9</v>
@@ -31173,7 +31173,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1071" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H1071" t="s">
         <v>9</v>
@@ -31199,7 +31199,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1072" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H1072" t="s">
         <v>9</v>
@@ -31277,7 +31277,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1075" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1075" t="s">
         <v>9</v>
@@ -31303,7 +31303,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G1076" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H1076" t="s">
         <v>9</v>
@@ -31329,7 +31329,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1077" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H1077" t="s">
         <v>9</v>
@@ -31355,7 +31355,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1078" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H1078" t="s">
         <v>9</v>
@@ -31381,7 +31381,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G1079" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H1079" t="s">
         <v>9</v>
@@ -31459,7 +31459,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G1082" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H1082" t="s">
         <v>9</v>
@@ -31511,7 +31511,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G1084" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H1084" t="s">
         <v>9</v>
@@ -31589,7 +31589,7 @@
         <v>12</v>
       </c>
       <c r="G1087" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H1087" t="s">
         <v>9</v>
@@ -31615,7 +31615,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1088" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H1088" t="s">
         <v>9</v>
@@ -31641,7 +31641,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1089" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H1089" t="s">
         <v>9</v>
@@ -31667,7 +31667,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1090" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H1090" t="s">
         <v>9</v>
@@ -31693,7 +31693,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G1091" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H1091" t="s">
         <v>9</v>
@@ -31719,7 +31719,7 @@
         <v>12</v>
       </c>
       <c r="G1092" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H1092" t="s">
         <v>9</v>
@@ -31797,7 +31797,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1095" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H1095" t="s">
         <v>9</v>
@@ -69765,7 +69765,7 @@
     </row>
     <row r="2556">
       <c r="A2556" s="1" t="n">
-        <v>46044.6911111111</v>
+        <v>46044.3333333333</v>
       </c>
       <c r="B2556" t="n">
         <v>7165</v>
@@ -69786,6 +69786,32 @@
         <v>964</v>
       </c>
       <c r="H2556" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2557">
+      <c r="A2557" s="1" t="n">
+        <v>46045.6910416667</v>
+      </c>
+      <c r="B2557" t="n">
+        <v>4213</v>
+      </c>
+      <c r="C2557" t="n">
+        <v>21.2000007629395</v>
+      </c>
+      <c r="D2557" t="n">
+        <v>20.7999992370605</v>
+      </c>
+      <c r="E2557" t="n">
+        <v>21.1000003814697</v>
+      </c>
+      <c r="F2557" t="n">
+        <v>21.2000007629395</v>
+      </c>
+      <c r="G2557" t="s">
+        <v>966</v>
+      </c>
+      <c r="H2557" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IWB.MI.xlsx
+++ b/data/IWB.MI.xlsx
@@ -47,175 +47,175 @@
     <t xml:space="preserve">7.79867458343506</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83063554763794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74273872375488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75073194503784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71077871322632</t>
+    <t xml:space="preserve">7.8306360244751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74273920059204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75073099136353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71077823638916</t>
   </si>
   <si>
     <t xml:space="preserve">7.6947979927063</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59092092514038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51101636886597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31125783920288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44709539413452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35120820999146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29527473449707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26331377029419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29927206039429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2912802696228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27130365371704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24733448028564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37518072128296</t>
+    <t xml:space="preserve">7.59092283248901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51101684570312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31125640869141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44709491729736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3512077331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2952766418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26331424713135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29927110671997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29128074645996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27130460739136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24733257293701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3751802444458</t>
   </si>
   <si>
     <t xml:space="preserve">7.43111371994019</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47106552124023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15144777297974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41513156890869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32723760604858</t>
+    <t xml:space="preserve">7.47106647491455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15144824981689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41513252258301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32723808288574</t>
   </si>
   <si>
     <t xml:space="preserve">7.28728437423706</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99163913726807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11149454116821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19140005111694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25532245635986</t>
+    <t xml:space="preserve">6.99163866043091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11149549484253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19139957427979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25532388687134</t>
   </si>
   <si>
     <t xml:space="preserve">7.41912841796875</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42312288284302</t>
+    <t xml:space="preserve">7.42312240600586</t>
   </si>
   <si>
     <t xml:space="preserve">7.63087368011475</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67082834243774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49903392791748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58293104171753</t>
+    <t xml:space="preserve">7.67082548141479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49903249740601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58293151855469</t>
   </si>
   <si>
     <t xml:space="preserve">7.89455938339233</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98644733428955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91054105758667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54297876358032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82264614105225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64285898208618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62288427352905</t>
+    <t xml:space="preserve">7.9864501953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91054010391235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5429801940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82264471054077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6428599357605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62288379669189</t>
   </si>
   <si>
     <t xml:space="preserve">7.77470207214355</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76671266555786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79068326950073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87058925628662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96647214889526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71876811981201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66283512115479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57094526290894</t>
+    <t xml:space="preserve">7.76671314239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79068279266357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87058877944946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96647262573242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7187705039978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66283750534058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57094669342041</t>
   </si>
   <si>
     <t xml:space="preserve">7.55896091461182</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39116239547729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4630765914917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60690402984619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54697370529175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36718893051147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31525135040283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33123111724854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3472146987915</t>
+    <t xml:space="preserve">7.39116048812866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46307516098022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60690355300903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54697418212891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36718940734863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31525087356567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33123350143433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34721422195435</t>
   </si>
   <si>
     <t xml:space="preserve">7.50302696228027</t>
@@ -224,193 +224,193 @@
     <t xml:space="preserve">7.24333715438843</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2233624458313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23934364318848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4590802192688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46707201004028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10350561141968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89974975585938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91173362731934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95168685913086</t>
+    <t xml:space="preserve">7.22336149215698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23934268951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45907926559448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46707010269165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10350656509399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8997483253479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91173410415649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9516863822937</t>
   </si>
   <si>
     <t xml:space="preserve">7.0076208114624</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87178230285645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87577676773071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87977313995361</t>
+    <t xml:space="preserve">6.8717827796936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87577724456787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87977266311646</t>
   </si>
   <si>
     <t xml:space="preserve">6.86778688430786</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75192451477051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74393558502197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8238377571106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66403102874756</t>
+    <t xml:space="preserve">6.75192546844482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74393510818481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82383918762207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66403150558472</t>
   </si>
   <si>
     <t xml:space="preserve">6.83183002471924</t>
   </si>
   <si>
-    <t xml:space="preserve">6.895751953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03159189224243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07154369354248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33522844314575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25931787490845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17941379547119</t>
+    <t xml:space="preserve">6.89575290679932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03159141540527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07154417037964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33522748947144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25931835174561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17941427230835</t>
   </si>
   <si>
     <t xml:space="preserve">7.26731061935425</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23135375976562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09551525115967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1834077835083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18740558624268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20738172531128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14345550537109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12348079681396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23534727096558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74673557281494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83463096618652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98245477676392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92652082443237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78269195556641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63886547088623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73475027084351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07035064697266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21417808532715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16623401641846</t>
+    <t xml:space="preserve">7.23135185241699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09551429748535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18340921401978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18740367889404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20738220214844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14345741271973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12348127365112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23534774780273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74673461914062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83463048934937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9824538230896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92652177810669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78269243240356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63886451721191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73475074768066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07034969329834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21417617797852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16623306274414</t>
   </si>
   <si>
     <t xml:space="preserve">8.18221378326416</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27011108398438</t>
+    <t xml:space="preserve">8.27010917663574</t>
   </si>
   <si>
     <t xml:space="preserve">8.57374572753906</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54977512359619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35001468658447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46986961364746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52580451965332</t>
+    <t xml:space="preserve">8.54977607727051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35001373291016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46987152099609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.525803565979</t>
   </si>
   <si>
     <t xml:space="preserve">8.50982284545898</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59771919250488</t>
+    <t xml:space="preserve">8.59771823883057</t>
   </si>
   <si>
     <t xml:space="preserve">8.6057071685791</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58173656463623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64687156677246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67129993438721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61430644989014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63058853149414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75272274017334</t>
+    <t xml:space="preserve">8.58173847198486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64687252044678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67129898071289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61430549621582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63058948516846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75272083282471</t>
   </si>
   <si>
     <t xml:space="preserve">8.82599925994873</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87485122680664</t>
+    <t xml:space="preserve">8.87485313415527</t>
   </si>
   <si>
     <t xml:space="preserve">8.95627212524414</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74457836151123</t>
+    <t xml:space="preserve">8.74457931518555</t>
   </si>
   <si>
     <t xml:space="preserve">8.858567237854</t>
@@ -419,34 +419,34 @@
     <t xml:space="preserve">8.84228420257568</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91556167602539</t>
+    <t xml:space="preserve">8.91556358337402</t>
   </si>
   <si>
     <t xml:space="preserve">9.03769493103027</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00512504577637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94812870025635</t>
+    <t xml:space="preserve">9.005126953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94812965393066</t>
   </si>
   <si>
     <t xml:space="preserve">8.99698257446289</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12725639343262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19239234924316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11911392211914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14353942871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98069953918457</t>
+    <t xml:space="preserve">9.1272554397583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19239330291748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11911296844482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14354038238525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98069858551025</t>
   </si>
   <si>
     <t xml:space="preserve">9.13539886474609</t>
@@ -455,79 +455,79 @@
     <t xml:space="preserve">9.16796588897705</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15982341766357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18424892425537</t>
+    <t xml:space="preserve">9.15982437133789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.184250831604</t>
   </si>
   <si>
     <t xml:space="preserve">9.15168190002441</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0702600479126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96441650390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92370319366455</t>
+    <t xml:space="preserve">9.07026100158691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96441555023193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9237060546875</t>
   </si>
   <si>
     <t xml:space="preserve">8.80157279968262</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79343032836914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86670970916748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90742111206055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89113616943359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11097145080566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20053577423096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28195571899414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35523414611816</t>
+    <t xml:space="preserve">8.79343128204346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86671161651611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90741920471191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89113712310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11097049713135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20053386688232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28195381164551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35523223876953</t>
   </si>
   <si>
     <t xml:space="preserve">9.3959436416626</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32266616821289</t>
+    <t xml:space="preserve">9.32266426086426</t>
   </si>
   <si>
     <t xml:space="preserve">9.64834880828857</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60763835906982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90075206756592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99031639099121</t>
+    <t xml:space="preserve">9.60763931274414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90075302124023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99031543731689</t>
   </si>
   <si>
     <t xml:space="preserve">10.1205883026123</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1368732452393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1775808334351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1043033599854</t>
+    <t xml:space="preserve">10.1368703842163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1775827407837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.104302406311</t>
   </si>
   <si>
     <t xml:space="preserve">10.1531562805176</t>
@@ -536,28 +536,28 @@
     <t xml:space="preserve">10.0961608886719</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94146060943604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90889358520508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77048015594482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83561611175537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91703796386719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79490375518799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77862167358398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78676223754883</t>
+    <t xml:space="preserve">9.94146251678467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90889263153076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77047920227051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83561515808105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91703701019287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7949047088623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7786226272583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78676414489746</t>
   </si>
   <si>
     <t xml:space="preserve">9.9577465057373</t>
@@ -566,7 +566,7 @@
     <t xml:space="preserve">10.0147399902344</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99845600128174</t>
+    <t xml:space="preserve">9.99845695495605</t>
   </si>
   <si>
     <t xml:space="preserve">9.88446807861328</t>
@@ -575,46 +575,46 @@
     <t xml:space="preserve">9.86004161834717</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85190010070801</t>
+    <t xml:space="preserve">9.85189914703369</t>
   </si>
   <si>
     <t xml:space="preserve">9.89261054992676</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2590055465698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3404245376587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4625539779663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5276918411255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5765428543091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5439739227295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.535831451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5032663345337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5521173477173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3485660552979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4381294250488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3241386413574</t>
+    <t xml:space="preserve">10.2590036392212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3404226303101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.462553024292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5276908874512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5765438079834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5439758300781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5358333587646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5032653808594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5521192550659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3485651016235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4381284713745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3241405487061</t>
   </si>
   <si>
     <t xml:space="preserve">10.3811340332031</t>
@@ -623,91 +623,91 @@
     <t xml:space="preserve">10.3648490905762</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4218435287476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.413703918457</t>
+    <t xml:space="preserve">10.4218444824219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4137020111084</t>
   </si>
   <si>
     <t xml:space="preserve">10.3729915618896</t>
   </si>
   <si>
-    <t xml:space="preserve">10.389274597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2915716171265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.267144203186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2264347076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1938667297363</t>
+    <t xml:space="preserve">10.3892755508423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2915725708008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2671432495117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2264337539673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.193865776062</t>
   </si>
   <si>
     <t xml:space="preserve">10.3159971237183</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2182931900024</t>
+    <t xml:space="preserve">10.2182922363281</t>
   </si>
   <si>
     <t xml:space="preserve">10.2834300994873</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4299869537354</t>
+    <t xml:space="preserve">10.429986000061</t>
   </si>
   <si>
     <t xml:space="preserve">10.3322820663452</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2427186965942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5846872329712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6661062240601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7068157196045</t>
+    <t xml:space="preserve">10.2427196502686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5846862792969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6661071777344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7068166732788</t>
   </si>
   <si>
     <t xml:space="preserve">10.7475271224976</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7882375717163</t>
+    <t xml:space="preserve">10.7882356643677</t>
   </si>
   <si>
     <t xml:space="preserve">10.6253967285156</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8696594238281</t>
+    <t xml:space="preserve">10.8696584701538</t>
   </si>
   <si>
     <t xml:space="preserve">10.8289480209351</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0324983596802</t>
+    <t xml:space="preserve">11.0324993133545</t>
   </si>
   <si>
     <t xml:space="preserve">11.2360506057739</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4396028518677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6838655471802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0732107162476</t>
+    <t xml:space="preserve">11.439603805542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6838645935059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0732088088989</t>
   </si>
   <si>
     <t xml:space="preserve">10.9917888641357</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1546306610107</t>
+    <t xml:space="preserve">11.1546297073364</t>
   </si>
   <si>
     <t xml:space="preserve">11.3174705505371</t>
@@ -716,76 +716,79 @@
     <t xml:space="preserve">11.2767610549927</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1953420639038</t>
+    <t xml:space="preserve">11.1953401565552</t>
   </si>
   <si>
     <t xml:space="preserve">11.3581819534302</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4839181900024</t>
+    <t xml:space="preserve">11.4839162826538</t>
   </si>
   <si>
     <t xml:space="preserve">11.5258302688599</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5677433013916</t>
+    <t xml:space="preserve">11.5677423477173</t>
   </si>
   <si>
     <t xml:space="preserve">11.4000949859619</t>
   </si>
   <si>
+    <t xml:space="preserve">11.0228834152222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1486215591431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2324447631836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1905326843262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2743577957153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8971481323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0647974014282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4420051574707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8552370071411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6875877380371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.325475692749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2822484970093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1957931518555</t>
+  </si>
+  <si>
     <t xml:space="preserve">11.0228843688965</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1486206054688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2324438095093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1905326843262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2743587493896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8971490859985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0647964477539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.442006111145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8552360534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6875867843628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3254747390747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2822484970093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1957921981812</t>
-  </si>
-  <si>
     <t xml:space="preserve">11.2390203475952</t>
   </si>
   <si>
     <t xml:space="preserve">11.1525659561157</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9364318847656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0661125183105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.109338760376</t>
+    <t xml:space="preserve">10.936429977417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0661115646362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1093397140503</t>
   </si>
   <si>
     <t xml:space="preserve">10.9796581268311</t>
@@ -794,13 +797,13 @@
     <t xml:space="preserve">10.7635231018066</t>
   </si>
   <si>
-    <t xml:space="preserve">10.590615272522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8499774932861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7202949523926</t>
+    <t xml:space="preserve">10.5906143188477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8499784469604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7202959060669</t>
   </si>
   <si>
     <t xml:space="preserve">10.6770696640015</t>
@@ -809,10 +812,10 @@
     <t xml:space="preserve">10.8067502975464</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8932056427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6338405609131</t>
+    <t xml:space="preserve">10.8932037353516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.633843421936</t>
   </si>
   <si>
     <t xml:space="preserve">11.4119272232056</t>
@@ -821,97 +824,97 @@
     <t xml:space="preserve">11.4551553726196</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3687009811401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5416097640991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6280641555786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5848340988159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4609355926514</t>
+    <t xml:space="preserve">11.3687000274658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5416088104248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6280632019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5848369598389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4609336853027</t>
   </si>
   <si>
     <t xml:space="preserve">10.3312530517578</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3744812011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2880258560181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5041599273682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0286655426025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94220924377441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59639549255371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63962078094482</t>
+    <t xml:space="preserve">10.3744802474976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2880268096924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5041618347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0286645889282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94221019744873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59639453887939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63962173461914</t>
   </si>
   <si>
     <t xml:space="preserve">9.81252956390381</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85575580596924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55316638946533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03444385528564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81830883026123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86153411865234</t>
+    <t xml:space="preserve">9.85575485229492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55316734313965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03444290161133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81830787658691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86153507232666</t>
   </si>
   <si>
     <t xml:space="preserve">8.77507877349854</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07767009735107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16412258148193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25057792663574</t>
+    <t xml:space="preserve">9.07766914367676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16412544250488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25057888031006</t>
   </si>
   <si>
     <t xml:space="preserve">9.33703136444092</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2938060760498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2447986602783</t>
+    <t xml:space="preserve">9.29380512237549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2447996139526</t>
   </si>
   <si>
     <t xml:space="preserve">9.68284702301025</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1583442687988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98543834686279</t>
+    <t xml:space="preserve">10.1583452224731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98543643951416</t>
   </si>
   <si>
     <t xml:space="preserve">9.89898300170898</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76930236816406</t>
+    <t xml:space="preserve">9.76930332183838</t>
   </si>
   <si>
     <t xml:space="preserve">9.72607517242432</t>
@@ -923,13 +926,13 @@
     <t xml:space="preserve">9.5099401473999</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3802604675293</t>
+    <t xml:space="preserve">9.38025856018066</t>
   </si>
   <si>
     <t xml:space="preserve">9.42348575592041</t>
   </si>
   <si>
-    <t xml:space="preserve">9.207350730896</t>
+    <t xml:space="preserve">9.20735168457031</t>
   </si>
   <si>
     <t xml:space="preserve">10.0718898773193</t>
@@ -938,19 +941,19 @@
     <t xml:space="preserve">10.2972898483276</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2077484130859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1629772186279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3420610427856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4316005706787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3868322372437</t>
+    <t xml:space="preserve">10.2077474594116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1629762649536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.342059135437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.431601524353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3868312835693</t>
   </si>
   <si>
     <t xml:space="preserve">10.1182069778442</t>
@@ -962,16 +965,16 @@
     <t xml:space="preserve">10.476372718811</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6554565429688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7897672653198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7449970245361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5659151077271</t>
+    <t xml:space="preserve">10.6554546356201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7897682189941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7449979782104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5659141540527</t>
   </si>
   <si>
     <t xml:space="preserve">10.7002267837524</t>
@@ -980,43 +983,40 @@
     <t xml:space="preserve">11.1031627655029</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9688529968262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9240808486938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8793096542358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1479349136353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2822494506836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.237476348877</t>
+    <t xml:space="preserve">10.9688520431519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9240818023682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8793106079102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1479339599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2374773025513</t>
   </si>
   <si>
     <t xml:space="preserve">11.4613313674927</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3270177841187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1927051544189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3717889785767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.416558265686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0583934783936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6404151916504</t>
+    <t xml:space="preserve">11.3270168304443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1927042007446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.371789932251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4165601730347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0583944320679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6404142379761</t>
   </si>
   <si>
     <t xml:space="preserve">11.7299556732178</t>
@@ -1025,22 +1025,22 @@
     <t xml:space="preserve">11.6851854324341</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7747259140015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8194971084595</t>
+    <t xml:space="preserve">11.7747249603271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8194961547852</t>
   </si>
   <si>
     <t xml:space="preserve">11.8642683029175</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5508718490601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5956430435181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.521143913269</t>
+    <t xml:space="preserve">11.5508728027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5956439971924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5211429595947</t>
   </si>
   <si>
     <t xml:space="preserve">11.0136222839355</t>
@@ -1049,25 +1049,25 @@
     <t xml:space="preserve">10.8345394134521</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9985799789429</t>
+    <t xml:space="preserve">11.9985809326172</t>
   </si>
   <si>
     <t xml:space="preserve">12.0881223678589</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0433502197266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1328916549683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2224340438843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1776638031006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.356746673584</t>
+    <t xml:space="preserve">12.0433521270752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1328935623169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2224349975586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1776647567749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3567476272583</t>
   </si>
   <si>
     <t xml:space="preserve">12.2672052383423</t>
@@ -1079,43 +1079,43 @@
     <t xml:space="preserve">12.3119764328003</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6701431274414</t>
+    <t xml:space="preserve">12.6701421737671</t>
   </si>
   <si>
     <t xml:space="preserve">12.6253728866577</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5806016921997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6106843948364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62572765350342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0734348297119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4910593032837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9090404510498</t>
+    <t xml:space="preserve">12.5806007385254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6106853485107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6257266998291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0734357833862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4910583496094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9090394973755</t>
   </si>
   <si>
     <t xml:space="preserve">13.1626224517822</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6998710632324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8789548873901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0132675170898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1475801467896</t>
+    <t xml:space="preserve">13.6998739242554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8789539337158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0132665634155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1475811004639</t>
   </si>
   <si>
     <t xml:space="preserve">14.2371215820312</t>
@@ -1124,19 +1124,19 @@
     <t xml:space="preserve">14.1923522949219</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9237270355225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9684972763062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7894134521484</t>
+    <t xml:space="preserve">13.9237251281738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9684963226318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7894144058228</t>
   </si>
   <si>
     <t xml:space="preserve">14.2818927764893</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8341846466064</t>
+    <t xml:space="preserve">13.8341827392578</t>
   </si>
   <si>
     <t xml:space="preserve">13.520788192749</t>
@@ -1145,19 +1145,19 @@
     <t xml:space="preserve">13.431245803833</t>
   </si>
   <si>
-    <t xml:space="preserve">13.565559387207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.610330581665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7004642486572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7905988693237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8356666564941</t>
+    <t xml:space="preserve">13.5655584335327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6103315353394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7004652023315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7906007766724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8356676101685</t>
   </si>
   <si>
     <t xml:space="preserve">13.6553974151611</t>
@@ -1166,67 +1166,64 @@
     <t xml:space="preserve">13.5201950073242</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6103296279907</t>
-  </si>
-  <si>
     <t xml:space="preserve">13.2948579788208</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1596574783325</t>
+    <t xml:space="preserve">13.1596565246582</t>
   </si>
   <si>
     <t xml:space="preserve">13.069522857666</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9793872833252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.708984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5737819671631</t>
+    <t xml:space="preserve">12.9793863296509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7089834213257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5737810134888</t>
   </si>
   <si>
     <t xml:space="preserve">12.6188478469849</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3399267196655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1145887374878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4751281738281</t>
+    <t xml:space="preserve">13.3399248123169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1145896911621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4751262664795</t>
   </si>
   <si>
     <t xml:space="preserve">12.9343204498291</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7540512084961</t>
+    <t xml:space="preserve">12.7540502548218</t>
   </si>
   <si>
     <t xml:space="preserve">12.8441858291626</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0610046386719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8807334899902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1962051391602</t>
+    <t xml:space="preserve">14.0610027313232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8807344436646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1962060928345</t>
   </si>
   <si>
     <t xml:space="preserve">14.3314065933228</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4215412139893</t>
+    <t xml:space="preserve">14.4215421676636</t>
   </si>
   <si>
     <t xml:space="preserve">14.3764743804932</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5116758346558</t>
+    <t xml:space="preserve">14.5116767883301</t>
   </si>
   <si>
     <t xml:space="preserve">14.4666080474854</t>
@@ -1235,19 +1232,19 @@
     <t xml:space="preserve">14.6018114089966</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6919450759888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8722162246704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2327508926392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0074148178101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3228893280029</t>
+    <t xml:space="preserve">14.6919441223145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8722143173218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2327537536621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0074167251587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3228874206543</t>
   </si>
   <si>
     <t xml:space="preserve">15.1876850128174</t>
@@ -1256,7 +1253,7 @@
     <t xml:space="preserve">16.224235534668</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9538307189941</t>
+    <t xml:space="preserve">15.9538297653198</t>
   </si>
   <si>
     <t xml:space="preserve">16.8551769256592</t>
@@ -1265,43 +1262,43 @@
     <t xml:space="preserve">16.3143711090088</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9903774261475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8101081848145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7565231323242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0269260406494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9367904663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3509159088135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4410514831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.486120223999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0354442596436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6298389434814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7199745178223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4045028686523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6749095916748</t>
+    <t xml:space="preserve">16.9903793334961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8101100921631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7565250396729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.026927947998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9367923736572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3509178161621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4410533905029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4861183166504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0354461669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6298427581787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7199764251709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4045085906982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6749057769775</t>
   </si>
   <si>
     <t xml:space="preserve">16.9453086853027</t>
@@ -1310,7 +1307,7 @@
     <t xml:space="preserve">16.7650413513184</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8636960983276</t>
+    <t xml:space="preserve">15.8636951446533</t>
   </si>
   <si>
     <t xml:space="preserve">15.9988965988159</t>
@@ -1322,7 +1319,7 @@
     <t xml:space="preserve">16.3594360351562</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1791667938232</t>
+    <t xml:space="preserve">16.1791648864746</t>
   </si>
   <si>
     <t xml:space="preserve">16.5847721099854</t>
@@ -1331,85 +1328,88 @@
     <t xml:space="preserve">16.5397052764893</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6834259033203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0890331268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5932903289795</t>
+    <t xml:space="preserve">15.6834268569946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0890312194824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5932893753052</t>
   </si>
   <si>
     <t xml:space="preserve">16.2693023681641</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1255779266357</t>
+    <t xml:space="preserve">17.125581741333</t>
   </si>
   <si>
     <t xml:space="preserve">17.5762538909912</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6663875579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.846658706665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5677356719971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3874664306641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7480030059814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3789482116699</t>
+    <t xml:space="preserve">17.666389465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8466567993164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5677337646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3874645233154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7480049133301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3789443969727</t>
   </si>
   <si>
     <t xml:space="preserve">20.0098915100098</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5506973266602</t>
+    <t xml:space="preserve">20.5506954193115</t>
   </si>
   <si>
     <t xml:space="preserve">20.4605617523193</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2802906036377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3704299926758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1000232696533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6408309936523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7309646606445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4435253143311</t>
+    <t xml:space="preserve">20.280294418335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3704280853271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.100025177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.640832901001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7309665679932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4435214996338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.902717590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5361423492432</t>
   </si>
   <si>
     <t xml:space="preserve">21.9027156829834</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5361423492432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1695690155029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7194290161133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3609313964844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4525756835938</t>
+    <t xml:space="preserve">21.1695709228516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7194309234619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.360933303833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4525737762451</t>
   </si>
   <si>
     <t xml:space="preserve">22.269287109375</t>
@@ -1421,40 +1421,40 @@
     <t xml:space="preserve">21.9943599700928</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6277885437012</t>
+    <t xml:space="preserve">21.6277866363525</t>
   </si>
   <si>
     <t xml:space="preserve">23.2773628234863</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9107894897461</t>
+    <t xml:space="preserve">22.9107913970947</t>
   </si>
   <si>
     <t xml:space="preserve">22.727502822876</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1776447296143</t>
+    <t xml:space="preserve">22.1776466369629</t>
   </si>
   <si>
     <t xml:space="preserve">22.6358623504639</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0024356842041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0940799713135</t>
+    <t xml:space="preserve">23.0024337768555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0940780639648</t>
   </si>
   <si>
     <t xml:space="preserve">24.1021499633789</t>
   </si>
   <si>
-    <t xml:space="preserve">24.285436630249</t>
+    <t xml:space="preserve">24.2854385375977</t>
   </si>
   <si>
     <t xml:space="preserve">24.9269428253174</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2099437713623</t>
+    <t xml:space="preserve">26.2099475860596</t>
   </si>
   <si>
     <t xml:space="preserve">26.8514461517334</t>
@@ -1463,22 +1463,22 @@
     <t xml:space="preserve">26.6681613922119</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3096599578857</t>
+    <t xml:space="preserve">27.3096618652344</t>
   </si>
   <si>
     <t xml:space="preserve">26.4848728179932</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7598056793213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5765171051025</t>
+    <t xml:space="preserve">26.7598037719727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5765190124512</t>
   </si>
   <si>
     <t xml:space="preserve">26.3015880584717</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5684432983398</t>
+    <t xml:space="preserve">25.5684413909912</t>
   </si>
   <si>
     <t xml:space="preserve">27.0347328186035</t>
@@ -1487,16 +1487,16 @@
     <t xml:space="preserve">29.1425228118896</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4093818664551</t>
+    <t xml:space="preserve">28.4093799591064</t>
   </si>
   <si>
     <t xml:space="preserve">28.1344509124756</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2260932922363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3646869659424</t>
+    <t xml:space="preserve">28.226095199585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3646850585938</t>
   </si>
   <si>
     <t xml:space="preserve">28.4570770263672</t>
@@ -1511,19 +1511,19 @@
     <t xml:space="preserve">27.9027194976807</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7179317474365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1038284301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9353694915771</t>
+    <t xml:space="preserve">27.7179298400879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1038303375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9353675842285</t>
   </si>
   <si>
     <t xml:space="preserve">29.750581741333</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3810081481934</t>
+    <t xml:space="preserve">29.3810062408447</t>
   </si>
   <si>
     <t xml:space="preserve">28.8266506195068</t>
@@ -1532,7 +1532,7 @@
     <t xml:space="preserve">28.9190425872803</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7342548370361</t>
+    <t xml:space="preserve">28.7342586517334</t>
   </si>
   <si>
     <t xml:space="preserve">29.0114345550537</t>
@@ -1541,31 +1541,31 @@
     <t xml:space="preserve">29.8429737091064</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1201496124268</t>
+    <t xml:space="preserve">30.120153427124</t>
   </si>
   <si>
     <t xml:space="preserve">30.2125473022461</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0277614593506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3973331451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1364784240723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8592987060547</t>
+    <t xml:space="preserve">30.027759552002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3973350524902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1364765167236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8593006134033</t>
   </si>
   <si>
     <t xml:space="preserve">31.0440845489502</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6745109558105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4897232055664</t>
+    <t xml:space="preserve">30.6745128631592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.489725112915</t>
   </si>
   <si>
     <t xml:space="preserve">29.2886161804199</t>
@@ -1574,43 +1574,43 @@
     <t xml:space="preserve">29.4734020233154</t>
   </si>
   <si>
-    <t xml:space="preserve">32.8919410705566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.3539085388184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.5550193786621</t>
+    <t xml:space="preserve">32.8919448852539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.3539123535156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.5550231933594</t>
   </si>
   <si>
     <t xml:space="preserve">34.0930595397949</t>
   </si>
   <si>
-    <t xml:space="preserve">35.8485221862793</t>
+    <t xml:space="preserve">35.8485298156738</t>
   </si>
   <si>
     <t xml:space="preserve">37.4192085266113</t>
   </si>
   <si>
-    <t xml:space="preserve">40.0986137390137</t>
+    <t xml:space="preserve">40.0986099243164</t>
   </si>
   <si>
     <t xml:space="preserve">37.2344207763672</t>
   </si>
   <si>
-    <t xml:space="preserve">37.881175994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.1583557128906</t>
+    <t xml:space="preserve">37.8811721801758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.1583518981934</t>
   </si>
   <si>
     <t xml:space="preserve">37.6039962768555</t>
   </si>
   <si>
-    <t xml:space="preserve">37.6963882446289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.7887802124023</t>
+    <t xml:space="preserve">37.6963920593262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.7887840270996</t>
   </si>
   <si>
     <t xml:space="preserve">37.142032623291</t>
@@ -1625,7 +1625,7 @@
     <t xml:space="preserve">36.4952774047852</t>
   </si>
   <si>
-    <t xml:space="preserve">35.9409255981445</t>
+    <t xml:space="preserve">35.9409217834473</t>
   </si>
   <si>
     <t xml:space="preserve">36.4028854370117</t>
@@ -1637,7 +1637,7 @@
     <t xml:space="preserve">37.9735679626465</t>
   </si>
   <si>
-    <t xml:space="preserve">38.0659599304199</t>
+    <t xml:space="preserve">38.0659637451172</t>
   </si>
   <si>
     <t xml:space="preserve">38.4355316162109</t>
@@ -1646,31 +1646,31 @@
     <t xml:space="preserve">38.805103302002</t>
   </si>
   <si>
-    <t xml:space="preserve">39.3594627380371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.8214302062988</t>
+    <t xml:space="preserve">39.3594589233398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.8214263916016</t>
   </si>
   <si>
     <t xml:space="preserve">40.0062141418457</t>
   </si>
   <si>
-    <t xml:space="preserve">40.5605735778809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.6529693603516</t>
+    <t xml:space="preserve">40.5605773925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.6529655456543</t>
   </si>
   <si>
     <t xml:space="preserve">41.946475982666</t>
   </si>
   <si>
-    <t xml:space="preserve">41.114933013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.9301490783691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.3160438537598</t>
+    <t xml:space="preserve">41.1149368286133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.9301414489746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.316047668457</t>
   </si>
   <si>
     <t xml:space="preserve">43.5171508789062</t>
@@ -1685,19 +1685,19 @@
     <t xml:space="preserve">43.7019386291504</t>
   </si>
   <si>
-    <t xml:space="preserve">43.979118347168</t>
+    <t xml:space="preserve">43.9791145324707</t>
   </si>
   <si>
     <t xml:space="preserve">44.348690032959</t>
   </si>
   <si>
-    <t xml:space="preserve">44.9954490661621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.810661315918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.5334739685059</t>
+    <t xml:space="preserve">44.9954452514648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.8106575012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.5334815979004</t>
   </si>
   <si>
     <t xml:space="preserve">43.7943382263184</t>
@@ -1712,16 +1712,16 @@
     <t xml:space="preserve">41.8540802001953</t>
   </si>
   <si>
-    <t xml:space="preserve">41.5768966674805</t>
+    <t xml:space="preserve">41.5769004821777</t>
   </si>
   <si>
     <t xml:space="preserve">41.2073249816895</t>
   </si>
   <si>
-    <t xml:space="preserve">40.1910018920898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.4518547058105</t>
+    <t xml:space="preserve">40.1910057067871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.4518585205078</t>
   </si>
   <si>
     <t xml:space="preserve">38.9898948669434</t>
@@ -1730,13 +1730,13 @@
     <t xml:space="preserve">39.1746788024902</t>
   </si>
   <si>
-    <t xml:space="preserve">39.544246673584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.7453575134277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.0225372314453</t>
+    <t xml:space="preserve">39.5442543029785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.745361328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.0225448608398</t>
   </si>
   <si>
     <t xml:space="preserve">39.7290344238281</t>
@@ -1751,43 +1751,43 @@
     <t xml:space="preserve">39.6366424560547</t>
   </si>
   <si>
-    <t xml:space="preserve">38.6203155517578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.2670745849609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.3268203735352</t>
+    <t xml:space="preserve">38.6203193664551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.2670783996582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.3268165588379</t>
   </si>
   <si>
     <t xml:space="preserve">38.8974990844727</t>
   </si>
   <si>
-    <t xml:space="preserve">37.5116004943848</t>
+    <t xml:space="preserve">37.5115966796875</t>
   </si>
   <si>
     <t xml:space="preserve">38.7127151489258</t>
   </si>
   <si>
-    <t xml:space="preserve">39.0822868347168</t>
+    <t xml:space="preserve">39.0822792053223</t>
   </si>
   <si>
     <t xml:space="preserve">36.7724571228027</t>
   </si>
   <si>
-    <t xml:space="preserve">36.310489654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.2181015014648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.3865623474121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.0333137512207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.1854515075684</t>
+    <t xml:space="preserve">36.3104858398438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.2181053161621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.3865585327148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.0333099365234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.1854476928711</t>
   </si>
   <si>
     <t xml:space="preserve">33.7234840393066</t>
@@ -1796,7 +1796,7 @@
     <t xml:space="preserve">33.1691246032715</t>
   </si>
   <si>
-    <t xml:space="preserve">32.6147651672363</t>
+    <t xml:space="preserve">32.6147689819336</t>
   </si>
   <si>
     <t xml:space="preserve">33.6310920715332</t>
@@ -1805,22 +1805,22 @@
     <t xml:space="preserve">32.707160949707</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9680156707764</t>
+    <t xml:space="preserve">31.9680137634277</t>
   </si>
   <si>
     <t xml:space="preserve">32.0604095458984</t>
   </si>
   <si>
-    <t xml:space="preserve">31.4136562347412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6908378601074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2452011108398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.7995529174805</t>
+    <t xml:space="preserve">31.4136581420898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6908359527588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2451934814453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.7995567321777</t>
   </si>
   <si>
     <t xml:space="preserve">33.9082717895508</t>
@@ -1829,7 +1829,7 @@
     <t xml:space="preserve">35.1093826293945</t>
   </si>
   <si>
-    <t xml:space="preserve">34.739803314209</t>
+    <t xml:space="preserve">34.7398071289062</t>
   </si>
   <si>
     <t xml:space="preserve">35.0169906616211</t>
@@ -1841,22 +1841,22 @@
     <t xml:space="preserve">32.4299812316895</t>
   </si>
   <si>
-    <t xml:space="preserve">32.5223731994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5060501098633</t>
+    <t xml:space="preserve">32.5223770141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5060482025146</t>
   </si>
   <si>
     <t xml:space="preserve">31.3212661743164</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5522480010986</t>
+    <t xml:space="preserve">31.55224609375</t>
   </si>
   <si>
     <t xml:space="preserve">31.9218196868896</t>
   </si>
   <si>
-    <t xml:space="preserve">32.1528015136719</t>
+    <t xml:space="preserve">32.1527976989746</t>
   </si>
   <si>
     <t xml:space="preserve">33.492504119873</t>
@@ -1865,19 +1865,19 @@
     <t xml:space="preserve">34.3702392578125</t>
   </si>
   <si>
-    <t xml:space="preserve">33.8620719909668</t>
+    <t xml:space="preserve">33.8620758056641</t>
   </si>
   <si>
     <t xml:space="preserve">32.1066017150879</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5359268188477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3511352539062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7804546356201</t>
+    <t xml:space="preserve">30.5359230041504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3511333465576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7804508209229</t>
   </si>
   <si>
     <t xml:space="preserve">28.3643836975098</t>
@@ -1886,16 +1886,16 @@
     <t xml:space="preserve">28.3180332183838</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8082180023193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7618713378906</t>
+    <t xml:space="preserve">27.8082160949707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7618732452393</t>
   </si>
   <si>
     <t xml:space="preserve">28.0862998962402</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9936084747314</t>
+    <t xml:space="preserve">27.9936065673828</t>
   </si>
   <si>
     <t xml:space="preserve">28.6424655914307</t>
@@ -1904,13 +1904,13 @@
     <t xml:space="preserve">29.5230579376221</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1255722045898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5694046020508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.105936050415</t>
+    <t xml:space="preserve">30.1255683898926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5694065093994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1059341430664</t>
   </si>
   <si>
     <t xml:space="preserve">27.900915145874</t>
@@ -1940,7 +1940,7 @@
     <t xml:space="preserve">26.556848526001</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3251113891602</t>
+    <t xml:space="preserve">26.3251132965088</t>
   </si>
   <si>
     <t xml:space="preserve">25.8152980804443</t>
@@ -1961,7 +1961,7 @@
     <t xml:space="preserve">23.9614143371582</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7296810150146</t>
+    <t xml:space="preserve">23.729679107666</t>
   </si>
   <si>
     <t xml:space="preserve">25.0273971557617</t>
@@ -1970,22 +1970,22 @@
     <t xml:space="preserve">24.7956619262695</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2858448028564</t>
+    <t xml:space="preserve">24.2858467102051</t>
   </si>
   <si>
     <t xml:space="preserve">24.6102714538574</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3321895599365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.517578125</t>
+    <t xml:space="preserve">24.3321914672852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5175800323486</t>
   </si>
   <si>
     <t xml:space="preserve">24.3785362243652</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4712333679199</t>
+    <t xml:space="preserve">24.4712314605713</t>
   </si>
   <si>
     <t xml:space="preserve">23.8687210083008</t>
@@ -2006,13 +2006,13 @@
     <t xml:space="preserve">23.9150676727295</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1931495666504</t>
+    <t xml:space="preserve">24.193151473999</t>
   </si>
   <si>
     <t xml:space="preserve">24.888355255127</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5835609436035</t>
+    <t xml:space="preserve">25.5835628509521</t>
   </si>
   <si>
     <t xml:space="preserve">25.9543380737305</t>
@@ -2042,16 +2042,16 @@
     <t xml:space="preserve">24.0077610015869</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4515972137451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1271686553955</t>
+    <t xml:space="preserve">23.4515953063965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1271705627441</t>
   </si>
   <si>
     <t xml:space="preserve">23.0808200836182</t>
   </si>
   <si>
-    <t xml:space="preserve">23.312557220459</t>
+    <t xml:space="preserve">23.3125553131104</t>
   </si>
   <si>
     <t xml:space="preserve">23.6369857788086</t>
@@ -2060,7 +2060,7 @@
     <t xml:space="preserve">23.5906391143799</t>
   </si>
   <si>
-    <t xml:space="preserve">23.405252456665</t>
+    <t xml:space="preserve">23.4052505493164</t>
   </si>
   <si>
     <t xml:space="preserve">23.2662105560303</t>
@@ -2072,13 +2072,13 @@
     <t xml:space="preserve">22.8027381896973</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6173496246338</t>
+    <t xml:space="preserve">22.6173515319824</t>
   </si>
   <si>
     <t xml:space="preserve">23.1735153198242</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8954334259033</t>
+    <t xml:space="preserve">22.895435333252</t>
   </si>
   <si>
     <t xml:space="preserve">21.9684944152832</t>
@@ -2099,19 +2099,19 @@
     <t xml:space="preserve">19.9755687713623</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1609573364258</t>
+    <t xml:space="preserve">20.1609592437744</t>
   </si>
   <si>
     <t xml:space="preserve">20.2073040008545</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8365268707275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5584468841553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.604793548584</t>
+    <t xml:space="preserve">19.8365306854248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5584487915039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6047916412354</t>
   </si>
   <si>
     <t xml:space="preserve">19.9292221069336</t>
@@ -2129,13 +2129,13 @@
     <t xml:space="preserve">20.9952049255371</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5780811309814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0878982543945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5977172851562</t>
+    <t xml:space="preserve">20.5780830383301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0879001617432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5977153778076</t>
   </si>
   <si>
     <t xml:space="preserve">22.0611839294434</t>
@@ -2144,55 +2144,55 @@
     <t xml:space="preserve">22.4319629669189</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3856143951416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3392677307129</t>
+    <t xml:space="preserve">22.3856163024902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3392696380615</t>
   </si>
   <si>
     <t xml:space="preserve">23.6833343505859</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5639247894287</t>
+    <t xml:space="preserve">24.5639266967773</t>
   </si>
   <si>
     <t xml:space="preserve">24.4248867034912</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1664390563965</t>
+    <t xml:space="preserve">25.1664371490479</t>
   </si>
   <si>
     <t xml:space="preserve">25.2127857208252</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8420066833496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.768949508667</t>
+    <t xml:space="preserve">24.8420085906982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7689476013184</t>
   </si>
   <si>
     <t xml:space="preserve">25.7226028442383</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3518257141113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5372142791748</t>
+    <t xml:space="preserve">25.35182762146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5372123718262</t>
   </si>
   <si>
     <t xml:space="preserve">25.305477142334</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6762561798096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4908676147461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6691799163818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2057075500488</t>
+    <t xml:space="preserve">25.6762542724609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4908657073975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6691780090332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2057056427002</t>
   </si>
   <si>
     <t xml:space="preserve">27.4837894439697</t>
@@ -2207,7 +2207,7 @@
     <t xml:space="preserve">28.0399551391602</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1789932250977</t>
+    <t xml:space="preserve">28.1789951324463</t>
   </si>
   <si>
     <t xml:space="preserve">28.2716884613037</t>
@@ -2222,13 +2222,13 @@
     <t xml:space="preserve">27.5301380157471</t>
   </si>
   <si>
-    <t xml:space="preserve">26.093376159668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3981742858887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9417819976807</t>
+    <t xml:space="preserve">26.0933780670166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.39817237854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.941780090332</t>
   </si>
   <si>
     <t xml:space="preserve">22.2002277374268</t>
@@ -2237,13 +2237,13 @@
     <t xml:space="preserve">22.153881072998</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1075325012207</t>
+    <t xml:space="preserve">22.1075344085693</t>
   </si>
   <si>
     <t xml:space="preserve">22.7100448608398</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9881267547607</t>
+    <t xml:space="preserve">22.9881248474121</t>
   </si>
   <si>
     <t xml:space="preserve">23.2198619842529</t>
@@ -2252,10 +2252,10 @@
     <t xml:space="preserve">21.8294506072998</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6244277954102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6707763671875</t>
+    <t xml:space="preserve">20.6244297027588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6707744598389</t>
   </si>
   <si>
     <t xml:space="preserve">20.485387802124</t>
@@ -2264,13 +2264,13 @@
     <t xml:space="preserve">20.2536525726318</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5317344665527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1342449188232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7831058502197</t>
+    <t xml:space="preserve">20.5317325592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1342430114746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7831039428711</t>
   </si>
   <si>
     <t xml:space="preserve">21.6440620422363</t>
@@ -2282,25 +2282,25 @@
     <t xml:space="preserve">21.3196334838867</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8757972717285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1805953979492</t>
+    <t xml:space="preserve">21.8757991790771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1805934906006</t>
   </si>
   <si>
     <t xml:space="preserve">20.9025096893311</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6679420471191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4127311706543</t>
+    <t xml:space="preserve">20.6679439544678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4127330780029</t>
   </si>
   <si>
     <t xml:space="preserve">20.6213912963867</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5748443603516</t>
+    <t xml:space="preserve">20.5748424530029</t>
   </si>
   <si>
     <t xml:space="preserve">20.3886451721191</t>
@@ -2309,7 +2309,7 @@
     <t xml:space="preserve">21.3661842346191</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9937877655029</t>
+    <t xml:space="preserve">20.9937858581543</t>
   </si>
   <si>
     <t xml:space="preserve">20.9006900787354</t>
@@ -2318,22 +2318,22 @@
     <t xml:space="preserve">21.0403366088867</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1799850463867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2265338897705</t>
+    <t xml:space="preserve">21.1799869537354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2265319824219</t>
   </si>
   <si>
     <t xml:space="preserve">20.9472389221191</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4817447662354</t>
+    <t xml:space="preserve">20.4817428588867</t>
   </si>
   <si>
     <t xml:space="preserve">20.3420963287354</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2489986419678</t>
+    <t xml:space="preserve">20.2489967346191</t>
   </si>
   <si>
     <t xml:space="preserve">20.1558990478516</t>
@@ -2345,7 +2345,7 @@
     <t xml:space="preserve">19.6904029846191</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6438541412354</t>
+    <t xml:space="preserve">19.643856048584</t>
   </si>
   <si>
     <t xml:space="preserve">19.7835025787354</t>
@@ -2366,25 +2366,25 @@
     <t xml:space="preserve">19.3180084228516</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5507564544678</t>
+    <t xml:space="preserve">19.5507545471191</t>
   </si>
   <si>
     <t xml:space="preserve">20.2024478912354</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4351959228516</t>
+    <t xml:space="preserve">20.4351978302002</t>
   </si>
   <si>
     <t xml:space="preserve">19.4576568603516</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0387134552002</t>
+    <t xml:space="preserve">19.0387115478516</t>
   </si>
   <si>
     <t xml:space="preserve">19.9696998596191</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9231510162354</t>
+    <t xml:space="preserve">19.923152923584</t>
   </si>
   <si>
     <t xml:space="preserve">19.3645572662354</t>
@@ -2399,10 +2399,10 @@
     <t xml:space="preserve">19.1318111419678</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6197662353516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8525123596191</t>
+    <t xml:space="preserve">18.6197681427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8525142669678</t>
   </si>
   <si>
     <t xml:space="preserve">18.7128677368164</t>
@@ -2420,7 +2420,7 @@
     <t xml:space="preserve">18.4708099365234</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3963317871094</t>
+    <t xml:space="preserve">18.3963298797607</t>
   </si>
   <si>
     <t xml:space="preserve">18.3404712677002</t>
@@ -2429,10 +2429,10 @@
     <t xml:space="preserve">18.2287540435791</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2101306915283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.968074798584</t>
+    <t xml:space="preserve">18.210132598877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9680767059326</t>
   </si>
   <si>
     <t xml:space="preserve">17.6701583862305</t>
@@ -2462,16 +2462,16 @@
     <t xml:space="preserve">17.2232856750488</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3350028991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.409481048584</t>
+    <t xml:space="preserve">17.3350048065186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4094829559326</t>
   </si>
   <si>
     <t xml:space="preserve">17.6515369415283</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7260189056396</t>
+    <t xml:space="preserve">17.7260208129883</t>
   </si>
   <si>
     <t xml:space="preserve">17.7073993682861</t>
@@ -2492,13 +2492,13 @@
     <t xml:space="preserve">16.5529727935791</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0929470062256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9253673553467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2736759185791</t>
+    <t xml:space="preserve">17.092945098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9253692626953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2736778259277</t>
   </si>
   <si>
     <t xml:space="preserve">16.0130004882812</t>
@@ -2507,16 +2507,16 @@
     <t xml:space="preserve">15.9757604598999</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2364387512207</t>
+    <t xml:space="preserve">16.2364368438721</t>
   </si>
   <si>
     <t xml:space="preserve">16.2922973632812</t>
   </si>
   <si>
-    <t xml:space="preserve">17.037088394165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.813648223877</t>
+    <t xml:space="preserve">17.0370864868164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8136501312256</t>
   </si>
   <si>
     <t xml:space="preserve">16.404016494751</t>
@@ -2540,7 +2540,7 @@
     <t xml:space="preserve">15.7709436416626</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7337017059326</t>
+    <t xml:space="preserve">15.7337036132812</t>
   </si>
   <si>
     <t xml:space="preserve">15.8826608657837</t>
@@ -2564,10 +2564,10 @@
     <t xml:space="preserve">16.8695106506348</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1115665435791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0184669494629</t>
+    <t xml:space="preserve">17.1115646362305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0184688568115</t>
   </si>
   <si>
     <t xml:space="preserve">17.0557060241699</t>
@@ -2579,16 +2579,16 @@
     <t xml:space="preserve">17.3536224365234</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3722438812256</t>
+    <t xml:space="preserve">17.372241973877</t>
   </si>
   <si>
     <t xml:space="preserve">16.9998474121094</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0743255615234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6833114624023</t>
+    <t xml:space="preserve">17.0743274688721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.683313369751</t>
   </si>
   <si>
     <t xml:space="preserve">16.8881282806396</t>
@@ -2597,10 +2597,10 @@
     <t xml:space="preserve">16.6646919250488</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7205505371094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8322696685791</t>
+    <t xml:space="preserve">16.7205486297607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8322677612305</t>
   </si>
   <si>
     <t xml:space="preserve">16.7391700744629</t>
@@ -2609,7 +2609,7 @@
     <t xml:space="preserve">16.5902118682861</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3481559753418</t>
+    <t xml:space="preserve">16.3481540679932</t>
   </si>
   <si>
     <t xml:space="preserve">16.3109169006348</t>
@@ -2621,7 +2621,7 @@
     <t xml:space="preserve">16.6088333129883</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0502376556396</t>
+    <t xml:space="preserve">16.0502395629883</t>
   </si>
   <si>
     <t xml:space="preserve">16.2550563812256</t>
@@ -2633,10 +2633,10 @@
     <t xml:space="preserve">17.1674251556396</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0053157806396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9122161865234</t>
+    <t xml:space="preserve">18.005313873291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9122142791748</t>
   </si>
   <si>
     <t xml:space="preserve">17.4653434753418</t>
@@ -2654,13 +2654,13 @@
     <t xml:space="preserve">17.5491313934326</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3629341125488</t>
+    <t xml:space="preserve">17.3629322052002</t>
   </si>
   <si>
     <t xml:space="preserve">17.5025787353516</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4560317993164</t>
+    <t xml:space="preserve">17.456033706665</t>
   </si>
   <si>
     <t xml:space="preserve">18.1542739868164</t>
@@ -19470,7 +19470,7 @@
         <v>12.75</v>
       </c>
       <c r="G621" t="s">
-        <v>240</v>
+        <v>253</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -19548,7 +19548,7 @@
         <v>13</v>
       </c>
       <c r="G624" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -19574,7 +19574,7 @@
         <v>13</v>
       </c>
       <c r="G625" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -19600,7 +19600,7 @@
         <v>12.75</v>
       </c>
       <c r="G626" t="s">
-        <v>240</v>
+        <v>253</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -19626,7 +19626,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G627" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H627" t="s">
         <v>9</v>
@@ -19678,7 +19678,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G629" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H629" t="s">
         <v>9</v>
@@ -19704,7 +19704,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G630" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H630" t="s">
         <v>9</v>
@@ -19730,7 +19730,7 @@
         <v>12.75</v>
       </c>
       <c r="G631" t="s">
-        <v>240</v>
+        <v>253</v>
       </c>
       <c r="H631" t="s">
         <v>9</v>
@@ -19756,7 +19756,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G632" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H632" t="s">
         <v>9</v>
@@ -19782,7 +19782,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G633" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H633" t="s">
         <v>9</v>
@@ -19808,7 +19808,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G634" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H634" t="s">
         <v>9</v>
@@ -19834,7 +19834,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G635" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H635" t="s">
         <v>9</v>
@@ -19860,7 +19860,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G636" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H636" t="s">
         <v>9</v>
@@ -19886,7 +19886,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G637" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H637" t="s">
         <v>9</v>
@@ -19912,7 +19912,7 @@
         <v>12.25</v>
       </c>
       <c r="G638" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H638" t="s">
         <v>9</v>
@@ -19938,7 +19938,7 @@
         <v>12.25</v>
       </c>
       <c r="G639" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H639" t="s">
         <v>9</v>
@@ -19964,7 +19964,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G640" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H640" t="s">
         <v>9</v>
@@ -19990,7 +19990,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G641" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H641" t="s">
         <v>9</v>
@@ -20016,7 +20016,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G642" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H642" t="s">
         <v>9</v>
@@ -20042,7 +20042,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G643" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H643" t="s">
         <v>9</v>
@@ -20068,7 +20068,7 @@
         <v>12.5</v>
       </c>
       <c r="G644" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H644" t="s">
         <v>9</v>
@@ -20094,7 +20094,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G645" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H645" t="s">
         <v>9</v>
@@ -20120,7 +20120,7 @@
         <v>12.5</v>
       </c>
       <c r="G646" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H646" t="s">
         <v>9</v>
@@ -20146,7 +20146,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G647" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H647" t="s">
         <v>9</v>
@@ -20172,7 +20172,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G648" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H648" t="s">
         <v>9</v>
@@ -20198,7 +20198,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G649" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H649" t="s">
         <v>9</v>
@@ -20224,7 +20224,7 @@
         <v>12.5</v>
       </c>
       <c r="G650" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H650" t="s">
         <v>9</v>
@@ -20250,7 +20250,7 @@
         <v>12.5</v>
       </c>
       <c r="G651" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H651" t="s">
         <v>9</v>
@@ -20276,7 +20276,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G652" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H652" t="s">
         <v>9</v>
@@ -20302,7 +20302,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G653" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H653" t="s">
         <v>9</v>
@@ -20328,7 +20328,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G654" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H654" t="s">
         <v>9</v>
@@ -20354,7 +20354,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G655" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H655" t="s">
         <v>9</v>
@@ -20432,7 +20432,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G658" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H658" t="s">
         <v>9</v>
@@ -20458,7 +20458,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G659" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H659" t="s">
         <v>9</v>
@@ -20484,7 +20484,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G660" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H660" t="s">
         <v>9</v>
@@ -20510,7 +20510,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G661" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H661" t="s">
         <v>9</v>
@@ -20536,7 +20536,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G662" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H662" t="s">
         <v>9</v>
@@ -20562,7 +20562,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G663" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H663" t="s">
         <v>9</v>
@@ -20588,7 +20588,7 @@
         <v>12.75</v>
       </c>
       <c r="G664" t="s">
-        <v>240</v>
+        <v>253</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -20614,7 +20614,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G665" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H665" t="s">
         <v>9</v>
@@ -20640,7 +20640,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G666" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H666" t="s">
         <v>9</v>
@@ -20666,7 +20666,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G667" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H667" t="s">
         <v>9</v>
@@ -20692,7 +20692,7 @@
         <v>12.25</v>
       </c>
       <c r="G668" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H668" t="s">
         <v>9</v>
@@ -20718,7 +20718,7 @@
         <v>12.25</v>
       </c>
       <c r="G669" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H669" t="s">
         <v>9</v>
@@ -20744,7 +20744,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G670" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H670" t="s">
         <v>9</v>
@@ -20770,7 +20770,7 @@
         <v>12.5</v>
       </c>
       <c r="G671" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H671" t="s">
         <v>9</v>
@@ -20796,7 +20796,7 @@
         <v>12.5</v>
       </c>
       <c r="G672" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H672" t="s">
         <v>9</v>
@@ -20822,7 +20822,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G673" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H673" t="s">
         <v>9</v>
@@ -20848,7 +20848,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G674" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H674" t="s">
         <v>9</v>
@@ -20874,7 +20874,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G675" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H675" t="s">
         <v>9</v>
@@ -20900,7 +20900,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G676" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H676" t="s">
         <v>9</v>
@@ -20926,7 +20926,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G677" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H677" t="s">
         <v>9</v>
@@ -20952,7 +20952,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G678" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H678" t="s">
         <v>9</v>
@@ -20978,7 +20978,7 @@
         <v>12.25</v>
       </c>
       <c r="G679" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H679" t="s">
         <v>9</v>
@@ -21004,7 +21004,7 @@
         <v>12.25</v>
       </c>
       <c r="G680" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H680" t="s">
         <v>9</v>
@@ -21030,7 +21030,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G681" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H681" t="s">
         <v>9</v>
@@ -21056,7 +21056,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G682" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H682" t="s">
         <v>9</v>
@@ -21082,7 +21082,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G683" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H683" t="s">
         <v>9</v>
@@ -21108,7 +21108,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G684" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H684" t="s">
         <v>9</v>
@@ -21134,7 +21134,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G685" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H685" t="s">
         <v>9</v>
@@ -21160,7 +21160,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G686" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H686" t="s">
         <v>9</v>
@@ -21186,7 +21186,7 @@
         <v>12.5</v>
       </c>
       <c r="G687" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H687" t="s">
         <v>9</v>
@@ -21212,7 +21212,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G688" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H688" t="s">
         <v>9</v>
@@ -21238,7 +21238,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G689" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H689" t="s">
         <v>9</v>
@@ -21264,7 +21264,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G690" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H690" t="s">
         <v>9</v>
@@ -21290,7 +21290,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G691" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H691" t="s">
         <v>9</v>
@@ -21316,7 +21316,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G692" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H692" t="s">
         <v>9</v>
@@ -21342,7 +21342,7 @@
         <v>12.75</v>
       </c>
       <c r="G693" t="s">
-        <v>240</v>
+        <v>253</v>
       </c>
       <c r="H693" t="s">
         <v>9</v>
@@ -21368,7 +21368,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G694" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -21394,7 +21394,7 @@
         <v>13.25</v>
       </c>
       <c r="G695" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H695" t="s">
         <v>9</v>
@@ -21420,7 +21420,7 @@
         <v>13</v>
       </c>
       <c r="G696" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H696" t="s">
         <v>9</v>
@@ -21446,7 +21446,7 @@
         <v>13</v>
       </c>
       <c r="G697" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H697" t="s">
         <v>9</v>
@@ -21472,7 +21472,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G698" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H698" t="s">
         <v>9</v>
@@ -21550,7 +21550,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G701" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H701" t="s">
         <v>9</v>
@@ -21576,7 +21576,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G702" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H702" t="s">
         <v>9</v>
@@ -21602,7 +21602,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G703" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H703" t="s">
         <v>9</v>
@@ -21628,7 +21628,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G704" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H704" t="s">
         <v>9</v>
@@ -21654,7 +21654,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G705" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H705" t="s">
         <v>9</v>
@@ -21680,7 +21680,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G706" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H706" t="s">
         <v>9</v>
@@ -21706,7 +21706,7 @@
         <v>13.25</v>
       </c>
       <c r="G707" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H707" t="s">
         <v>9</v>
@@ -21784,7 +21784,7 @@
         <v>13</v>
       </c>
       <c r="G710" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H710" t="s">
         <v>9</v>
@@ -21810,7 +21810,7 @@
         <v>13</v>
       </c>
       <c r="G711" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H711" t="s">
         <v>9</v>
@@ -21862,7 +21862,7 @@
         <v>13</v>
       </c>
       <c r="G713" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H713" t="s">
         <v>9</v>
@@ -21888,7 +21888,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G714" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H714" t="s">
         <v>9</v>
@@ -21940,7 +21940,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G716" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H716" t="s">
         <v>9</v>
@@ -21966,7 +21966,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G717" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H717" t="s">
         <v>9</v>
@@ -21992,7 +21992,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G718" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H718" t="s">
         <v>9</v>
@@ -22018,7 +22018,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G719" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H719" t="s">
         <v>9</v>
@@ -22044,7 +22044,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G720" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H720" t="s">
         <v>9</v>
@@ -22070,7 +22070,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G721" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H721" t="s">
         <v>9</v>
@@ -22096,7 +22096,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G722" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H722" t="s">
         <v>9</v>
@@ -22122,7 +22122,7 @@
         <v>12.5</v>
       </c>
       <c r="G723" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H723" t="s">
         <v>9</v>
@@ -22148,7 +22148,7 @@
         <v>13</v>
       </c>
       <c r="G724" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H724" t="s">
         <v>9</v>
@@ -22174,7 +22174,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G725" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H725" t="s">
         <v>9</v>
@@ -22200,7 +22200,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G726" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H726" t="s">
         <v>9</v>
@@ -22226,7 +22226,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G727" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H727" t="s">
         <v>9</v>
@@ -22252,7 +22252,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G728" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H728" t="s">
         <v>9</v>
@@ -22278,7 +22278,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G729" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H729" t="s">
         <v>9</v>
@@ -22304,7 +22304,7 @@
         <v>12.5</v>
       </c>
       <c r="G730" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H730" t="s">
         <v>9</v>
@@ -22330,7 +22330,7 @@
         <v>12.25</v>
       </c>
       <c r="G731" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H731" t="s">
         <v>9</v>
@@ -22356,7 +22356,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G732" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H732" t="s">
         <v>9</v>
@@ -22382,7 +22382,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G733" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H733" t="s">
         <v>9</v>
@@ -22408,7 +22408,7 @@
         <v>12</v>
       </c>
       <c r="G734" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H734" t="s">
         <v>9</v>
@@ -22434,7 +22434,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G735" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H735" t="s">
         <v>9</v>
@@ -22460,7 +22460,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G736" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H736" t="s">
         <v>9</v>
@@ -22486,7 +22486,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G737" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H737" t="s">
         <v>9</v>
@@ -22512,7 +22512,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G738" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H738" t="s">
         <v>9</v>
@@ -22538,7 +22538,7 @@
         <v>11.5</v>
       </c>
       <c r="G739" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H739" t="s">
         <v>9</v>
@@ -22564,7 +22564,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G740" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H740" t="s">
         <v>9</v>
@@ -22590,7 +22590,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G741" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H741" t="s">
         <v>9</v>
@@ -22616,7 +22616,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G742" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H742" t="s">
         <v>9</v>
@@ -22642,7 +22642,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G743" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H743" t="s">
         <v>9</v>
@@ -22668,7 +22668,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G744" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H744" t="s">
         <v>9</v>
@@ -22694,7 +22694,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G745" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H745" t="s">
         <v>9</v>
@@ -22720,7 +22720,7 @@
         <v>11.5</v>
       </c>
       <c r="G746" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H746" t="s">
         <v>9</v>
@@ -22746,7 +22746,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G747" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H747" t="s">
         <v>9</v>
@@ -22772,7 +22772,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G748" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H748" t="s">
         <v>9</v>
@@ -22798,7 +22798,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G749" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H749" t="s">
         <v>9</v>
@@ -22824,7 +22824,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G750" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H750" t="s">
         <v>9</v>
@@ -22850,7 +22850,7 @@
         <v>10.25</v>
       </c>
       <c r="G751" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H751" t="s">
         <v>9</v>
@@ -22876,7 +22876,7 @@
         <v>10.25</v>
       </c>
       <c r="G752" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H752" t="s">
         <v>9</v>
@@ -22902,7 +22902,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G753" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H753" t="s">
         <v>9</v>
@@ -22928,7 +22928,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G754" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H754" t="s">
         <v>9</v>
@@ -22954,7 +22954,7 @@
         <v>10.5</v>
       </c>
       <c r="G755" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H755" t="s">
         <v>9</v>
@@ -22980,7 +22980,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G756" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H756" t="s">
         <v>9</v>
@@ -23006,7 +23006,7 @@
         <v>10.5</v>
       </c>
       <c r="G757" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H757" t="s">
         <v>9</v>
@@ -23032,7 +23032,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G758" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H758" t="s">
         <v>9</v>
@@ -23058,7 +23058,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G759" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H759" t="s">
         <v>9</v>
@@ -23084,7 +23084,7 @@
         <v>10.75</v>
       </c>
       <c r="G760" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H760" t="s">
         <v>9</v>
@@ -23110,7 +23110,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G761" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H761" t="s">
         <v>9</v>
@@ -23136,7 +23136,7 @@
         <v>11.5</v>
       </c>
       <c r="G762" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H762" t="s">
         <v>9</v>
@@ -23162,7 +23162,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G763" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H763" t="s">
         <v>9</v>
@@ -23188,7 +23188,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G764" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H764" t="s">
         <v>9</v>
@@ -23214,7 +23214,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G765" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H765" t="s">
         <v>9</v>
@@ -23240,7 +23240,7 @@
         <v>11.5</v>
       </c>
       <c r="G766" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H766" t="s">
         <v>9</v>
@@ -23266,7 +23266,7 @@
         <v>11.5</v>
       </c>
       <c r="G767" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H767" t="s">
         <v>9</v>
@@ -23292,7 +23292,7 @@
         <v>11.75</v>
       </c>
       <c r="G768" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H768" t="s">
         <v>9</v>
@@ -23318,7 +23318,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G769" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H769" t="s">
         <v>9</v>
@@ -23344,7 +23344,7 @@
         <v>12</v>
       </c>
       <c r="G770" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H770" t="s">
         <v>9</v>
@@ -23370,7 +23370,7 @@
         <v>11.75</v>
       </c>
       <c r="G771" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H771" t="s">
         <v>9</v>
@@ -23396,7 +23396,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G772" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H772" t="s">
         <v>9</v>
@@ -23422,7 +23422,7 @@
         <v>11.5</v>
       </c>
       <c r="G773" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H773" t="s">
         <v>9</v>
@@ -23448,7 +23448,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G774" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H774" t="s">
         <v>9</v>
@@ -23474,7 +23474,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G775" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H775" t="s">
         <v>9</v>
@@ -23500,7 +23500,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G776" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H776" t="s">
         <v>9</v>
@@ -23526,7 +23526,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G777" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H777" t="s">
         <v>9</v>
@@ -23552,7 +23552,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G778" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H778" t="s">
         <v>9</v>
@@ -23578,7 +23578,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G779" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H779" t="s">
         <v>9</v>
@@ -23604,7 +23604,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G780" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H780" t="s">
         <v>9</v>
@@ -23630,7 +23630,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G781" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H781" t="s">
         <v>9</v>
@@ -23656,7 +23656,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G782" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H782" t="s">
         <v>9</v>
@@ -23682,7 +23682,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G783" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H783" t="s">
         <v>9</v>
@@ -23708,7 +23708,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G784" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H784" t="s">
         <v>9</v>
@@ -23734,7 +23734,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G785" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H785" t="s">
         <v>9</v>
@@ -23760,7 +23760,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G786" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H786" t="s">
         <v>9</v>
@@ -23786,7 +23786,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G787" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H787" t="s">
         <v>9</v>
@@ -23812,7 +23812,7 @@
         <v>11.5</v>
       </c>
       <c r="G788" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H788" t="s">
         <v>9</v>
@@ -23838,7 +23838,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G789" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H789" t="s">
         <v>9</v>
@@ -23864,7 +23864,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G790" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H790" t="s">
         <v>9</v>
@@ -23890,7 +23890,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G791" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H791" t="s">
         <v>9</v>
@@ -23916,7 +23916,7 @@
         <v>11.5</v>
       </c>
       <c r="G792" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H792" t="s">
         <v>9</v>
@@ -23942,7 +23942,7 @@
         <v>11.25</v>
       </c>
       <c r="G793" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H793" t="s">
         <v>9</v>
@@ -23968,7 +23968,7 @@
         <v>11.25</v>
       </c>
       <c r="G794" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H794" t="s">
         <v>9</v>
@@ -23994,7 +23994,7 @@
         <v>11.5</v>
       </c>
       <c r="G795" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H795" t="s">
         <v>9</v>
@@ -24020,7 +24020,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G796" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H796" t="s">
         <v>9</v>
@@ -24046,7 +24046,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G797" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H797" t="s">
         <v>9</v>
@@ -24072,7 +24072,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G798" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H798" t="s">
         <v>9</v>
@@ -24098,7 +24098,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G799" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H799" t="s">
         <v>9</v>
@@ -24124,7 +24124,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G800" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H800" t="s">
         <v>9</v>
@@ -24150,7 +24150,7 @@
         <v>11</v>
       </c>
       <c r="G801" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H801" t="s">
         <v>9</v>
@@ -24176,7 +24176,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G802" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H802" t="s">
         <v>9</v>
@@ -24202,7 +24202,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G803" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H803" t="s">
         <v>9</v>
@@ -24228,7 +24228,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G804" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H804" t="s">
         <v>9</v>
@@ -24254,7 +24254,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G805" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H805" t="s">
         <v>9</v>
@@ -24280,7 +24280,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G806" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H806" t="s">
         <v>9</v>
@@ -24306,7 +24306,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G807" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H807" t="s">
         <v>9</v>
@@ -24332,7 +24332,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G808" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H808" t="s">
         <v>9</v>
@@ -24358,7 +24358,7 @@
         <v>11</v>
       </c>
       <c r="G809" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H809" t="s">
         <v>9</v>
@@ -24384,7 +24384,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G810" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H810" t="s">
         <v>9</v>
@@ -24410,7 +24410,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G811" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H811" t="s">
         <v>9</v>
@@ -24436,7 +24436,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G812" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H812" t="s">
         <v>9</v>
@@ -24462,7 +24462,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G813" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H813" t="s">
         <v>9</v>
@@ -24488,7 +24488,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G814" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H814" t="s">
         <v>9</v>
@@ -24514,7 +24514,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G815" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H815" t="s">
         <v>9</v>
@@ -24540,7 +24540,7 @@
         <v>10.75</v>
       </c>
       <c r="G816" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H816" t="s">
         <v>9</v>
@@ -24566,7 +24566,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G817" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H817" t="s">
         <v>9</v>
@@ -24592,7 +24592,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G818" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H818" t="s">
         <v>9</v>
@@ -24618,7 +24618,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G819" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H819" t="s">
         <v>9</v>
@@ -24644,7 +24644,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G820" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H820" t="s">
         <v>9</v>
@@ -24670,7 +24670,7 @@
         <v>11.25</v>
       </c>
       <c r="G821" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H821" t="s">
         <v>9</v>
@@ -24696,7 +24696,7 @@
         <v>11.25</v>
       </c>
       <c r="G822" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H822" t="s">
         <v>9</v>
@@ -24722,7 +24722,7 @@
         <v>11.25</v>
       </c>
       <c r="G823" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H823" t="s">
         <v>9</v>
@@ -24748,7 +24748,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G824" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H824" t="s">
         <v>9</v>
@@ -24774,7 +24774,7 @@
         <v>11.5</v>
       </c>
       <c r="G825" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H825" t="s">
         <v>9</v>
@@ -24800,7 +24800,7 @@
         <v>11.5</v>
       </c>
       <c r="G826" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H826" t="s">
         <v>9</v>
@@ -24826,7 +24826,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G827" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H827" t="s">
         <v>9</v>
@@ -24852,7 +24852,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G828" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H828" t="s">
         <v>9</v>
@@ -24878,7 +24878,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G829" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H829" t="s">
         <v>9</v>
@@ -24904,7 +24904,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G830" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H830" t="s">
         <v>9</v>
@@ -24930,7 +24930,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G831" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H831" t="s">
         <v>9</v>
@@ -24956,7 +24956,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G832" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H832" t="s">
         <v>9</v>
@@ -24982,7 +24982,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G833" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H833" t="s">
         <v>9</v>
@@ -25008,7 +25008,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G834" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H834" t="s">
         <v>9</v>
@@ -25034,7 +25034,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G835" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H835" t="s">
         <v>9</v>
@@ -25060,7 +25060,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G836" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H836" t="s">
         <v>9</v>
@@ -25086,7 +25086,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G837" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H837" t="s">
         <v>9</v>
@@ -25112,7 +25112,7 @@
         <v>11.5</v>
       </c>
       <c r="G838" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H838" t="s">
         <v>9</v>
@@ -25138,7 +25138,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G839" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H839" t="s">
         <v>9</v>
@@ -25164,7 +25164,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G840" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H840" t="s">
         <v>9</v>
@@ -25190,7 +25190,7 @@
         <v>11.5</v>
       </c>
       <c r="G841" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H841" t="s">
         <v>9</v>
@@ -25216,7 +25216,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G842" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H842" t="s">
         <v>9</v>
@@ -25242,7 +25242,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G843" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H843" t="s">
         <v>9</v>
@@ -25268,7 +25268,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G844" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H844" t="s">
         <v>9</v>
@@ -25294,7 +25294,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G845" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H845" t="s">
         <v>9</v>
@@ -25320,7 +25320,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G846" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H846" t="s">
         <v>9</v>
@@ -25346,7 +25346,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G847" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -25372,7 +25372,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G848" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H848" t="s">
         <v>9</v>
@@ -25398,7 +25398,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G849" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H849" t="s">
         <v>9</v>
@@ -25424,7 +25424,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G850" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H850" t="s">
         <v>9</v>
@@ -25450,7 +25450,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G851" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -25476,7 +25476,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G852" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H852" t="s">
         <v>9</v>
@@ -25502,7 +25502,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G853" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -25528,7 +25528,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G854" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H854" t="s">
         <v>9</v>
@@ -25554,7 +25554,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G855" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -25580,7 +25580,7 @@
         <v>11.5</v>
       </c>
       <c r="G856" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -25606,7 +25606,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G857" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H857" t="s">
         <v>9</v>
@@ -25632,7 +25632,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G858" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -25658,7 +25658,7 @@
         <v>11.5</v>
       </c>
       <c r="G859" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H859" t="s">
         <v>9</v>
@@ -25684,7 +25684,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G860" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H860" t="s">
         <v>9</v>
@@ -25710,7 +25710,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G861" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -25736,7 +25736,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G862" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H862" t="s">
         <v>9</v>
@@ -25762,7 +25762,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G863" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H863" t="s">
         <v>9</v>
@@ -25788,7 +25788,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G864" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H864" t="s">
         <v>9</v>
@@ -25814,7 +25814,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G865" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H865" t="s">
         <v>9</v>
@@ -25840,7 +25840,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G866" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H866" t="s">
         <v>9</v>
@@ -25866,7 +25866,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G867" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H867" t="s">
         <v>9</v>
@@ -25892,7 +25892,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G868" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H868" t="s">
         <v>9</v>
@@ -25918,7 +25918,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G869" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H869" t="s">
         <v>9</v>
@@ -25944,7 +25944,7 @@
         <v>12</v>
       </c>
       <c r="G870" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H870" t="s">
         <v>9</v>
@@ -25970,7 +25970,7 @@
         <v>12</v>
       </c>
       <c r="G871" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H871" t="s">
         <v>9</v>
@@ -25996,7 +25996,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G872" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H872" t="s">
         <v>9</v>
@@ -26022,7 +26022,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G873" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H873" t="s">
         <v>9</v>
@@ -26048,7 +26048,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G874" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H874" t="s">
         <v>9</v>
@@ -26074,7 +26074,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G875" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H875" t="s">
         <v>9</v>
@@ -26100,7 +26100,7 @@
         <v>12</v>
       </c>
       <c r="G876" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H876" t="s">
         <v>9</v>
@@ -26126,7 +26126,7 @@
         <v>12</v>
       </c>
       <c r="G877" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H877" t="s">
         <v>9</v>
@@ -26152,7 +26152,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G878" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H878" t="s">
         <v>9</v>
@@ -26178,7 +26178,7 @@
         <v>12</v>
       </c>
       <c r="G879" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H879" t="s">
         <v>9</v>
@@ -26204,7 +26204,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G880" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H880" t="s">
         <v>9</v>
@@ -26230,7 +26230,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G881" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H881" t="s">
         <v>9</v>
@@ -26256,7 +26256,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G882" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H882" t="s">
         <v>9</v>
@@ -26282,7 +26282,7 @@
         <v>12</v>
       </c>
       <c r="G883" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H883" t="s">
         <v>9</v>
@@ -26308,7 +26308,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G884" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H884" t="s">
         <v>9</v>
@@ -26334,7 +26334,7 @@
         <v>12.25</v>
       </c>
       <c r="G885" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H885" t="s">
         <v>9</v>
@@ -26360,7 +26360,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G886" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H886" t="s">
         <v>9</v>
@@ -26386,7 +26386,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G887" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H887" t="s">
         <v>9</v>
@@ -26412,7 +26412,7 @@
         <v>12.25</v>
       </c>
       <c r="G888" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H888" t="s">
         <v>9</v>
@@ -26438,7 +26438,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G889" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H889" t="s">
         <v>9</v>
@@ -26464,7 +26464,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G890" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H890" t="s">
         <v>9</v>
@@ -26490,7 +26490,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G891" t="s">
-        <v>326</v>
+        <v>251</v>
       </c>
       <c r="H891" t="s">
         <v>9</v>
@@ -26594,7 +26594,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G895" t="s">
-        <v>326</v>
+        <v>251</v>
       </c>
       <c r="H895" t="s">
         <v>9</v>
@@ -26750,7 +26750,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G901" t="s">
-        <v>326</v>
+        <v>251</v>
       </c>
       <c r="H901" t="s">
         <v>9</v>
@@ -26854,7 +26854,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G905" t="s">
-        <v>326</v>
+        <v>251</v>
       </c>
       <c r="H905" t="s">
         <v>9</v>
@@ -26880,7 +26880,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G906" t="s">
-        <v>326</v>
+        <v>251</v>
       </c>
       <c r="H906" t="s">
         <v>9</v>
@@ -26984,7 +26984,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G910" t="s">
-        <v>326</v>
+        <v>251</v>
       </c>
       <c r="H910" t="s">
         <v>9</v>
@@ -27062,7 +27062,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G913" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H913" t="s">
         <v>9</v>
@@ -27192,7 +27192,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G918" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H918" t="s">
         <v>9</v>
@@ -27218,7 +27218,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G919" t="s">
-        <v>326</v>
+        <v>251</v>
       </c>
       <c r="H919" t="s">
         <v>9</v>
@@ -27296,7 +27296,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G922" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H922" t="s">
         <v>9</v>
@@ -27322,7 +27322,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G923" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H923" t="s">
         <v>9</v>
@@ -27504,7 +27504,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G930" t="s">
-        <v>326</v>
+        <v>251</v>
       </c>
       <c r="H930" t="s">
         <v>9</v>
@@ -28050,7 +28050,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G951" t="s">
-        <v>326</v>
+        <v>251</v>
       </c>
       <c r="H951" t="s">
         <v>9</v>
@@ -28102,7 +28102,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G953" t="s">
-        <v>326</v>
+        <v>251</v>
       </c>
       <c r="H953" t="s">
         <v>9</v>
@@ -28180,7 +28180,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G956" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H956" t="s">
         <v>9</v>
@@ -28206,7 +28206,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G957" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H957" t="s">
         <v>9</v>
@@ -28232,7 +28232,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G958" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H958" t="s">
         <v>9</v>
@@ -28258,7 +28258,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G959" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H959" t="s">
         <v>9</v>
@@ -28284,7 +28284,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G960" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H960" t="s">
         <v>9</v>
@@ -28336,7 +28336,7 @@
         <v>11.5</v>
       </c>
       <c r="G962" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H962" t="s">
         <v>9</v>
@@ -28362,7 +28362,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G963" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H963" t="s">
         <v>9</v>
@@ -28388,7 +28388,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G964" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H964" t="s">
         <v>9</v>
@@ -28414,7 +28414,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G965" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H965" t="s">
         <v>9</v>
@@ -28440,7 +28440,7 @@
         <v>12.25</v>
       </c>
       <c r="G966" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H966" t="s">
         <v>9</v>
@@ -28466,7 +28466,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G967" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H967" t="s">
         <v>9</v>
@@ -28492,7 +28492,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G968" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H968" t="s">
         <v>9</v>
@@ -28544,7 +28544,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G970" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H970" t="s">
         <v>9</v>
@@ -28596,7 +28596,7 @@
         <v>12.25</v>
       </c>
       <c r="G972" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H972" t="s">
         <v>9</v>
@@ -28622,7 +28622,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G973" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H973" t="s">
         <v>9</v>
@@ -28648,7 +28648,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G974" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H974" t="s">
         <v>9</v>
@@ -28674,7 +28674,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G975" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H975" t="s">
         <v>9</v>
@@ -28752,7 +28752,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G978" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H978" t="s">
         <v>9</v>
@@ -28804,7 +28804,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G980" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H980" t="s">
         <v>9</v>
@@ -28882,7 +28882,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G983" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H983" t="s">
         <v>9</v>
@@ -28934,7 +28934,7 @@
         <v>12.25</v>
       </c>
       <c r="G985" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H985" t="s">
         <v>9</v>
@@ -28960,7 +28960,7 @@
         <v>12.25</v>
       </c>
       <c r="G986" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H986" t="s">
         <v>9</v>
@@ -28986,7 +28986,7 @@
         <v>12.25</v>
       </c>
       <c r="G987" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H987" t="s">
         <v>9</v>
@@ -29012,7 +29012,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G988" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H988" t="s">
         <v>9</v>
@@ -29038,7 +29038,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G989" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H989" t="s">
         <v>9</v>
@@ -29064,7 +29064,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G990" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H990" t="s">
         <v>9</v>
@@ -29090,7 +29090,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G991" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H991" t="s">
         <v>9</v>
@@ -29142,7 +29142,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G993" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H993" t="s">
         <v>9</v>
@@ -29168,7 +29168,7 @@
         <v>12</v>
       </c>
       <c r="G994" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H994" t="s">
         <v>9</v>
@@ -29194,7 +29194,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G995" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H995" t="s">
         <v>9</v>
@@ -29220,7 +29220,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G996" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H996" t="s">
         <v>9</v>
@@ -29246,7 +29246,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G997" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H997" t="s">
         <v>9</v>
@@ -29272,7 +29272,7 @@
         <v>12.25</v>
       </c>
       <c r="G998" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H998" t="s">
         <v>9</v>
@@ -29350,7 +29350,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G1001" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H1001" t="s">
         <v>9</v>
@@ -29376,7 +29376,7 @@
         <v>12</v>
       </c>
       <c r="G1002" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H1002" t="s">
         <v>9</v>
@@ -29428,7 +29428,7 @@
         <v>12.25</v>
       </c>
       <c r="G1004" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H1004" t="s">
         <v>9</v>
@@ -29454,7 +29454,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G1005" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H1005" t="s">
         <v>9</v>
@@ -29480,7 +29480,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G1006" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H1006" t="s">
         <v>9</v>
@@ -29506,7 +29506,7 @@
         <v>12.25</v>
       </c>
       <c r="G1007" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H1007" t="s">
         <v>9</v>
@@ -29558,7 +29558,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G1009" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H1009" t="s">
         <v>9</v>
@@ -29610,7 +29610,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G1011" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H1011" t="s">
         <v>9</v>
@@ -29792,7 +29792,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1018" t="s">
-        <v>326</v>
+        <v>251</v>
       </c>
       <c r="H1018" t="s">
         <v>9</v>
@@ -31014,7 +31014,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1065" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H1065" t="s">
         <v>9</v>
@@ -31040,7 +31040,7 @@
         <v>12</v>
       </c>
       <c r="G1066" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H1066" t="s">
         <v>9</v>
@@ -31066,7 +31066,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1067" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H1067" t="s">
         <v>9</v>
@@ -31092,7 +31092,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G1068" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H1068" t="s">
         <v>9</v>
@@ -31170,7 +31170,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1071" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H1071" t="s">
         <v>9</v>
@@ -31196,7 +31196,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1072" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H1072" t="s">
         <v>9</v>
@@ -31274,7 +31274,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1075" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H1075" t="s">
         <v>9</v>
@@ -31300,7 +31300,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G1076" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H1076" t="s">
         <v>9</v>
@@ -31326,7 +31326,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1077" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H1077" t="s">
         <v>9</v>
@@ -31352,7 +31352,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1078" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H1078" t="s">
         <v>9</v>
@@ -31378,7 +31378,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G1079" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H1079" t="s">
         <v>9</v>
@@ -31456,7 +31456,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G1082" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H1082" t="s">
         <v>9</v>
@@ -31508,7 +31508,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G1084" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H1084" t="s">
         <v>9</v>
@@ -31586,7 +31586,7 @@
         <v>12</v>
       </c>
       <c r="G1087" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H1087" t="s">
         <v>9</v>
@@ -31612,7 +31612,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1088" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H1088" t="s">
         <v>9</v>
@@ -31638,7 +31638,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1089" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H1089" t="s">
         <v>9</v>
@@ -31664,7 +31664,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1090" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H1090" t="s">
         <v>9</v>
@@ -31690,7 +31690,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G1091" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H1091" t="s">
         <v>9</v>
@@ -31716,7 +31716,7 @@
         <v>12</v>
       </c>
       <c r="G1092" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H1092" t="s">
         <v>9</v>
@@ -31794,7 +31794,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1095" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H1095" t="s">
         <v>9</v>
@@ -33016,7 +33016,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1142" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="H1142" t="s">
         <v>9</v>
@@ -33042,7 +33042,7 @@
         <v>14.75</v>
       </c>
       <c r="G1143" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H1143" t="s">
         <v>9</v>
@@ -33068,7 +33068,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1144" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H1144" t="s">
         <v>9</v>
@@ -33094,7 +33094,7 @@
         <v>14.5</v>
       </c>
       <c r="G1145" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H1145" t="s">
         <v>9</v>
@@ -33120,7 +33120,7 @@
         <v>14.5</v>
       </c>
       <c r="G1146" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H1146" t="s">
         <v>9</v>
@@ -33146,7 +33146,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1147" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1147" t="s">
         <v>9</v>
@@ -33172,7 +33172,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1148" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1148" t="s">
         <v>9</v>
@@ -33198,7 +33198,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G1149" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1149" t="s">
         <v>9</v>
@@ -33224,7 +33224,7 @@
         <v>14</v>
       </c>
       <c r="G1150" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1150" t="s">
         <v>9</v>
@@ -33250,7 +33250,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1151" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1151" t="s">
         <v>9</v>
@@ -33276,7 +33276,7 @@
         <v>14.5</v>
       </c>
       <c r="G1152" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H1152" t="s">
         <v>9</v>
@@ -33302,7 +33302,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1153" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1153" t="s">
         <v>9</v>
@@ -33328,7 +33328,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G1154" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H1154" t="s">
         <v>9</v>
@@ -33354,7 +33354,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G1155" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H1155" t="s">
         <v>9</v>
@@ -33380,7 +33380,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G1156" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H1156" t="s">
         <v>9</v>
@@ -33406,7 +33406,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1157" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1157" t="s">
         <v>9</v>
@@ -33458,7 +33458,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1159" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H1159" t="s">
         <v>9</v>
@@ -33484,7 +33484,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1160" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H1160" t="s">
         <v>9</v>
@@ -33510,7 +33510,7 @@
         <v>14.5</v>
       </c>
       <c r="G1161" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H1161" t="s">
         <v>9</v>
@@ -33536,7 +33536,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G1162" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H1162" t="s">
         <v>9</v>
@@ -33562,7 +33562,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G1163" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1163" t="s">
         <v>9</v>
@@ -33588,7 +33588,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1164" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1164" t="s">
         <v>9</v>
@@ -33614,7 +33614,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1165" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1165" t="s">
         <v>9</v>
@@ -33640,7 +33640,7 @@
         <v>14.25</v>
       </c>
       <c r="G1166" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H1166" t="s">
         <v>9</v>
@@ -33666,7 +33666,7 @@
         <v>14.5</v>
       </c>
       <c r="G1167" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H1167" t="s">
         <v>9</v>
@@ -33692,7 +33692,7 @@
         <v>14.5</v>
       </c>
       <c r="G1168" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H1168" t="s">
         <v>9</v>
@@ -33744,7 +33744,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1170" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1170" t="s">
         <v>9</v>
@@ -33796,7 +33796,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1172" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H1172" t="s">
         <v>9</v>
@@ -33848,7 +33848,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1174" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H1174" t="s">
         <v>9</v>
@@ -33874,7 +33874,7 @@
         <v>15.75</v>
       </c>
       <c r="G1175" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H1175" t="s">
         <v>9</v>
@@ -33900,7 +33900,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1176" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H1176" t="s">
         <v>9</v>
@@ -33926,7 +33926,7 @@
         <v>16</v>
       </c>
       <c r="G1177" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H1177" t="s">
         <v>9</v>
@@ -33952,7 +33952,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1178" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H1178" t="s">
         <v>9</v>
@@ -33978,7 +33978,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G1179" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H1179" t="s">
         <v>9</v>
@@ -34004,7 +34004,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1180" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H1180" t="s">
         <v>9</v>
@@ -34030,7 +34030,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1181" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H1181" t="s">
         <v>9</v>
@@ -34056,7 +34056,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1182" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H1182" t="s">
         <v>9</v>
@@ -34082,7 +34082,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1183" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H1183" t="s">
         <v>9</v>
@@ -34108,7 +34108,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1184" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H1184" t="s">
         <v>9</v>
@@ -34134,7 +34134,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1185" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H1185" t="s">
         <v>9</v>
@@ -34160,7 +34160,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1186" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H1186" t="s">
         <v>9</v>
@@ -34186,7 +34186,7 @@
         <v>16.5</v>
       </c>
       <c r="G1187" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H1187" t="s">
         <v>9</v>
@@ -34212,7 +34212,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1188" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H1188" t="s">
         <v>9</v>
@@ -34238,7 +34238,7 @@
         <v>16.5</v>
       </c>
       <c r="G1189" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H1189" t="s">
         <v>9</v>
@@ -34264,7 +34264,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1190" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H1190" t="s">
         <v>9</v>
@@ -34290,7 +34290,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G1191" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H1191" t="s">
         <v>9</v>
@@ -34316,7 +34316,7 @@
         <v>17</v>
       </c>
       <c r="G1192" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H1192" t="s">
         <v>9</v>
@@ -34342,7 +34342,7 @@
         <v>17</v>
       </c>
       <c r="G1193" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H1193" t="s">
         <v>9</v>
@@ -34368,7 +34368,7 @@
         <v>17</v>
       </c>
       <c r="G1194" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H1194" t="s">
         <v>9</v>
@@ -34394,7 +34394,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1195" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H1195" t="s">
         <v>9</v>
@@ -34420,7 +34420,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G1196" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H1196" t="s">
         <v>9</v>
@@ -34446,7 +34446,7 @@
         <v>18</v>
       </c>
       <c r="G1197" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H1197" t="s">
         <v>9</v>
@@ -34472,7 +34472,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1198" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H1198" t="s">
         <v>9</v>
@@ -34498,7 +34498,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1199" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H1199" t="s">
         <v>9</v>
@@ -34524,7 +34524,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1200" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H1200" t="s">
         <v>9</v>
@@ -34550,7 +34550,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G1201" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H1201" t="s">
         <v>9</v>
@@ -34576,7 +34576,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G1202" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H1202" t="s">
         <v>9</v>
@@ -34602,7 +34602,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1203" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H1203" t="s">
         <v>9</v>
@@ -34628,7 +34628,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G1204" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H1204" t="s">
         <v>9</v>
@@ -34654,7 +34654,7 @@
         <v>20</v>
       </c>
       <c r="G1205" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H1205" t="s">
         <v>9</v>
@@ -34680,7 +34680,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G1206" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H1206" t="s">
         <v>9</v>
@@ -34706,7 +34706,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G1207" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H1207" t="s">
         <v>9</v>
@@ -34732,7 +34732,7 @@
         <v>19.25</v>
       </c>
       <c r="G1208" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H1208" t="s">
         <v>9</v>
@@ -34758,7 +34758,7 @@
         <v>19.3500003814697</v>
       </c>
       <c r="G1209" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H1209" t="s">
         <v>9</v>
@@ -34784,7 +34784,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1210" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H1210" t="s">
         <v>9</v>
@@ -34810,7 +34810,7 @@
         <v>19.3500003814697</v>
       </c>
       <c r="G1211" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H1211" t="s">
         <v>9</v>
@@ -34836,7 +34836,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1212" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H1212" t="s">
         <v>9</v>
@@ -34862,7 +34862,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1213" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H1213" t="s">
         <v>9</v>
@@ -34888,7 +34888,7 @@
         <v>18.4500007629395</v>
       </c>
       <c r="G1214" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H1214" t="s">
         <v>9</v>
@@ -34914,7 +34914,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G1215" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H1215" t="s">
         <v>9</v>
@@ -34940,7 +34940,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1216" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H1216" t="s">
         <v>9</v>
@@ -34966,7 +34966,7 @@
         <v>18.5</v>
       </c>
       <c r="G1217" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1217" t="s">
         <v>9</v>
@@ -34992,7 +34992,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1218" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H1218" t="s">
         <v>9</v>
@@ -35018,7 +35018,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1219" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H1219" t="s">
         <v>9</v>
@@ -35044,7 +35044,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1220" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H1220" t="s">
         <v>9</v>
@@ -35070,7 +35070,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1221" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H1221" t="s">
         <v>9</v>
@@ -35096,7 +35096,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1222" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H1222" t="s">
         <v>9</v>
@@ -35122,7 +35122,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1223" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H1223" t="s">
         <v>9</v>
@@ -35148,7 +35148,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1224" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H1224" t="s">
         <v>9</v>
@@ -35174,7 +35174,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1225" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H1225" t="s">
         <v>9</v>
@@ -35200,7 +35200,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1226" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H1226" t="s">
         <v>9</v>
@@ -35226,7 +35226,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1227" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H1227" t="s">
         <v>9</v>
@@ -35252,7 +35252,7 @@
         <v>17.75</v>
       </c>
       <c r="G1228" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H1228" t="s">
         <v>9</v>
@@ -35278,7 +35278,7 @@
         <v>18</v>
       </c>
       <c r="G1229" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H1229" t="s">
         <v>9</v>
@@ -35304,7 +35304,7 @@
         <v>18.5</v>
       </c>
       <c r="G1230" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1230" t="s">
         <v>9</v>
@@ -35330,7 +35330,7 @@
         <v>18.4500007629395</v>
       </c>
       <c r="G1231" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H1231" t="s">
         <v>9</v>
@@ -35356,7 +35356,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1232" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H1232" t="s">
         <v>9</v>
@@ -35382,7 +35382,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G1233" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H1233" t="s">
         <v>9</v>
@@ -35408,7 +35408,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1234" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H1234" t="s">
         <v>9</v>
@@ -35434,7 +35434,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1235" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H1235" t="s">
         <v>9</v>
@@ -35460,7 +35460,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1236" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H1236" t="s">
         <v>9</v>
@@ -35486,7 +35486,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G1237" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H1237" t="s">
         <v>9</v>
@@ -35512,7 +35512,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G1238" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H1238" t="s">
         <v>9</v>
@@ -35538,7 +35538,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G1239" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H1239" t="s">
         <v>9</v>
@@ -35564,7 +35564,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1240" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H1240" t="s">
         <v>9</v>
@@ -35590,7 +35590,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1241" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H1241" t="s">
         <v>9</v>
@@ -35616,7 +35616,7 @@
         <v>18.5</v>
       </c>
       <c r="G1242" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1242" t="s">
         <v>9</v>
@@ -35642,7 +35642,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1243" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H1243" t="s">
         <v>9</v>
@@ -35668,7 +35668,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G1244" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H1244" t="s">
         <v>9</v>
@@ -35694,7 +35694,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G1245" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H1245" t="s">
         <v>9</v>
@@ -35720,7 +35720,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1246" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H1246" t="s">
         <v>9</v>
@@ -35746,7 +35746,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1247" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H1247" t="s">
         <v>9</v>
@@ -35772,7 +35772,7 @@
         <v>17.75</v>
       </c>
       <c r="G1248" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H1248" t="s">
         <v>9</v>
@@ -35798,7 +35798,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1249" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H1249" t="s">
         <v>9</v>
@@ -35824,7 +35824,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1250" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H1250" t="s">
         <v>9</v>
@@ -35850,7 +35850,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1251" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H1251" t="s">
         <v>9</v>
@@ -35876,7 +35876,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G1252" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H1252" t="s">
         <v>9</v>
@@ -35902,7 +35902,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1253" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H1253" t="s">
         <v>9</v>
@@ -35928,7 +35928,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1254" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H1254" t="s">
         <v>9</v>
@@ -35954,7 +35954,7 @@
         <v>18.0499992370605</v>
       </c>
       <c r="G1255" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H1255" t="s">
         <v>9</v>
@@ -35980,7 +35980,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1256" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H1256" t="s">
         <v>9</v>
@@ -36006,7 +36006,7 @@
         <v>18</v>
       </c>
       <c r="G1257" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H1257" t="s">
         <v>9</v>
@@ -36032,7 +36032,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G1258" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H1258" t="s">
         <v>9</v>
@@ -36058,7 +36058,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G1259" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H1259" t="s">
         <v>9</v>
@@ -36084,7 +36084,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1260" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H1260" t="s">
         <v>9</v>
@@ -36110,7 +36110,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1261" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H1261" t="s">
         <v>9</v>
@@ -36136,7 +36136,7 @@
         <v>19</v>
       </c>
       <c r="G1262" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H1262" t="s">
         <v>9</v>
@@ -36162,7 +36162,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1263" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H1263" t="s">
         <v>9</v>
@@ -36188,7 +36188,7 @@
         <v>19.5</v>
       </c>
       <c r="G1264" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H1264" t="s">
         <v>9</v>
@@ -36214,7 +36214,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G1265" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H1265" t="s">
         <v>9</v>
@@ -36240,7 +36240,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G1266" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H1266" t="s">
         <v>9</v>
@@ -36266,7 +36266,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G1267" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H1267" t="s">
         <v>9</v>
@@ -36292,7 +36292,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G1268" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H1268" t="s">
         <v>9</v>
@@ -36318,7 +36318,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1269" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H1269" t="s">
         <v>9</v>
@@ -36344,7 +36344,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1270" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H1270" t="s">
         <v>9</v>
@@ -36370,7 +36370,7 @@
         <v>21.5</v>
       </c>
       <c r="G1271" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H1271" t="s">
         <v>9</v>
@@ -36396,7 +36396,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1272" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H1272" t="s">
         <v>9</v>
@@ -36422,7 +36422,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G1273" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H1273" t="s">
         <v>9</v>
@@ -36448,7 +36448,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1274" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H1274" t="s">
         <v>9</v>
@@ -36474,7 +36474,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G1275" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H1275" t="s">
         <v>9</v>
@@ -36500,7 +36500,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G1276" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H1276" t="s">
         <v>9</v>
@@ -36526,7 +36526,7 @@
         <v>22.5</v>
       </c>
       <c r="G1277" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H1277" t="s">
         <v>9</v>
@@ -36552,7 +36552,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G1278" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H1278" t="s">
         <v>9</v>
@@ -36578,7 +36578,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G1279" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H1279" t="s">
         <v>9</v>
@@ -36604,7 +36604,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G1280" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H1280" t="s">
         <v>9</v>
@@ -36630,7 +36630,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G1281" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H1281" t="s">
         <v>9</v>
@@ -36656,7 +36656,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1282" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H1282" t="s">
         <v>9</v>
@@ -36682,7 +36682,7 @@
         <v>23</v>
       </c>
       <c r="G1283" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H1283" t="s">
         <v>9</v>
@@ -36708,7 +36708,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G1284" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H1284" t="s">
         <v>9</v>
@@ -36734,7 +36734,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G1285" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H1285" t="s">
         <v>9</v>
@@ -36760,7 +36760,7 @@
         <v>23.5</v>
       </c>
       <c r="G1286" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H1286" t="s">
         <v>9</v>
@@ -36786,7 +36786,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G1287" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H1287" t="s">
         <v>9</v>
@@ -36838,7 +36838,7 @@
         <v>23.5</v>
       </c>
       <c r="G1289" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H1289" t="s">
         <v>9</v>
@@ -69814,7 +69814,7 @@
     </row>
     <row r="2558">
       <c r="A2558" s="1" t="n">
-        <v>46048.6911226852</v>
+        <v>46048.3333333333</v>
       </c>
       <c r="B2558" t="n">
         <v>6158</v>
@@ -69835,6 +69835,32 @@
         <v>963</v>
       </c>
       <c r="H2558" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2559">
+      <c r="A2559" s="1" t="n">
+        <v>46049.6910300926</v>
+      </c>
+      <c r="B2559" t="n">
+        <v>3784</v>
+      </c>
+      <c r="C2559" t="n">
+        <v>21.1000003814697</v>
+      </c>
+      <c r="D2559" t="n">
+        <v>20.8999996185303</v>
+      </c>
+      <c r="E2559" t="n">
+        <v>21</v>
+      </c>
+      <c r="F2559" t="n">
+        <v>21.1000003814697</v>
+      </c>
+      <c r="G2559" t="s">
+        <v>961</v>
+      </c>
+      <c r="H2559" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IWB.MI.xlsx
+++ b/data/IWB.MI.xlsx
@@ -38,223 +38,223 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84661531448364</t>
+    <t xml:space="preserve">7.84661722183228</t>
   </si>
   <si>
     <t xml:space="preserve">IWB.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79867506027222</t>
+    <t xml:space="preserve">7.79867362976074</t>
   </si>
   <si>
     <t xml:space="preserve">7.83063459396362</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74273872375488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75073003768921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71077871322632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69479751586914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59092235565186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51101684570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31125593185425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44709444046021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35120868682861</t>
+    <t xml:space="preserve">7.74274015426636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75073099136353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.710777759552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69479703903198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5909218788147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5110182762146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31125736236572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44709396362305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35120916366577</t>
   </si>
   <si>
     <t xml:space="preserve">7.29527616500854</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26331329345703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29927110671997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29128074645996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2713041305542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24733448028564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37517976760864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43111371994019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47106456756592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15144824981689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41513299942017</t>
+    <t xml:space="preserve">7.26331472396851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29927206039429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29128122329712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27130508422852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24733257293701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37518072128296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43111276626587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47106647491455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15144777297974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41513109207153</t>
   </si>
   <si>
     <t xml:space="preserve">7.32723712921143</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28728485107422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99163913726807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11149597167969</t>
+    <t xml:space="preserve">7.28728580474854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99163770675659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11149501800537</t>
   </si>
   <si>
     <t xml:space="preserve">7.19140005111694</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25532388687134</t>
+    <t xml:space="preserve">7.25532341003418</t>
   </si>
   <si>
     <t xml:space="preserve">7.41912746429443</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42312240600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63087558746338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67082738876343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49903202056885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58293199539185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89456033706665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98644733428955</t>
+    <t xml:space="preserve">7.42312335968018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63087368011475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67082643508911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49903154373169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58293151855469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89455938339233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98644828796387</t>
   </si>
   <si>
     <t xml:space="preserve">7.9105396270752</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54297876358032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8226466178894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6428599357605</t>
+    <t xml:space="preserve">7.5429801940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82264471054077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64285898208618</t>
   </si>
   <si>
     <t xml:space="preserve">7.62288331985474</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77470207214355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7667121887207</t>
+    <t xml:space="preserve">7.7747015953064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76671266555786</t>
   </si>
   <si>
     <t xml:space="preserve">7.79068374633789</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87058925628662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9664740562439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7187705039978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66283750534058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57094669342041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55896091461182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39116096496582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46307373046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6069016456604</t>
+    <t xml:space="preserve">7.8705883026123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96647453308105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71876907348633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66283702850342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57094717025757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55896139144897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3911600112915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46307516098022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60690259933472</t>
   </si>
   <si>
     <t xml:space="preserve">7.54697465896606</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36718988418579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31525182723999</t>
+    <t xml:space="preserve">7.36719036102295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31525087356567</t>
   </si>
   <si>
     <t xml:space="preserve">7.33123254776001</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34721422195435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50302791595459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2433385848999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2233624458313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23934412002563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45907974243164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46706914901733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10350608825684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8997483253479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91173505783081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9516863822937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00761985778809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87178182601929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87577724456787</t>
+    <t xml:space="preserve">7.34721326828003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50302839279175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24333763122559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22336149215698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23934316635132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45907926559448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46707057952881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10350561141968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89974784851074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91173410415649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95168685913086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00761938095093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87178134918213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87577676773071</t>
   </si>
   <si>
     <t xml:space="preserve">6.87977266311646</t>
@@ -263,67 +263,67 @@
     <t xml:space="preserve">6.86778736114502</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75192451477051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7439341545105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82383871078491</t>
+    <t xml:space="preserve">6.75192594528198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74393510818481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82383823394775</t>
   </si>
   <si>
     <t xml:space="preserve">6.6640305519104</t>
   </si>
   <si>
-    <t xml:space="preserve">6.83183002471924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89575338363647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03159093856812</t>
+    <t xml:space="preserve">6.8318305015564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89575433731079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03159141540527</t>
   </si>
   <si>
     <t xml:space="preserve">7.07154321670532</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33522844314575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25931882858276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17941379547119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26730918884277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23135232925415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09551477432251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18340873718262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1874041557312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20738172531128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14345693588257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12348079681396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23534679412842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74673509597778</t>
+    <t xml:space="preserve">7.33522701263428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25931978225708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17941427230835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26730871200562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23135137557983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09551572799683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18340969085693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18740510940552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20738124847412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14345788955688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12348175048828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23534727096558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7467360496521</t>
   </si>
   <si>
     <t xml:space="preserve">7.83463048934937</t>
@@ -332,16 +332,16 @@
     <t xml:space="preserve">7.98245334625244</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92652082443237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78269147872925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63886499404907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73475027084351</t>
+    <t xml:space="preserve">7.92652130126953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78269195556641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63886308670044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73474979400635</t>
   </si>
   <si>
     <t xml:space="preserve">8.07035064697266</t>
@@ -353,7 +353,7 @@
     <t xml:space="preserve">8.16623497009277</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18221378326416</t>
+    <t xml:space="preserve">8.18221473693848</t>
   </si>
   <si>
     <t xml:space="preserve">8.27011108398438</t>
@@ -365,79 +365,79 @@
     <t xml:space="preserve">8.54977512359619</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35001468658447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46986961364746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.525803565979</t>
+    <t xml:space="preserve">8.35001373291016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46987247467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52580451965332</t>
   </si>
   <si>
     <t xml:space="preserve">8.50982284545898</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59771919250488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6057071685791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58173847198486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64687538146973</t>
+    <t xml:space="preserve">8.59771823883057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60570812225342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58173561096191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64687347412109</t>
   </si>
   <si>
     <t xml:space="preserve">8.67129993438721</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61430549621582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63058948516846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75271987915039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82600021362305</t>
+    <t xml:space="preserve">8.61430644989014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63059139251709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75272083282471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82599830627441</t>
   </si>
   <si>
     <t xml:space="preserve">8.87485027313232</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95627307891846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74458026885986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85856819152832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84228229522705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91556167602539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03769207000732</t>
+    <t xml:space="preserve">8.95627212524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74457740783691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.858567237854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84228420257568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91556262969971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03769493103027</t>
   </si>
   <si>
     <t xml:space="preserve">9.00512599945068</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94813060760498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99698448181152</t>
+    <t xml:space="preserve">8.94812965393066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99698352813721</t>
   </si>
   <si>
     <t xml:space="preserve">9.1272554397583</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19239044189453</t>
+    <t xml:space="preserve">9.19239234924316</t>
   </si>
   <si>
     <t xml:space="preserve">9.11911296844482</t>
@@ -449,10 +449,10 @@
     <t xml:space="preserve">8.98069763183594</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13539695739746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16796588897705</t>
+    <t xml:space="preserve">9.13539600372314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16796493530273</t>
   </si>
   <si>
     <t xml:space="preserve">9.15982437133789</t>
@@ -461,64 +461,64 @@
     <t xml:space="preserve">9.18424987792969</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15168190002441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07026290893555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96441459655762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92370510101318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80157375335693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79343223571777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86670875549316</t>
+    <t xml:space="preserve">9.1516809463501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07026195526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9644136428833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92370223999023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80157279968262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79343128204346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8667106628418</t>
   </si>
   <si>
     <t xml:space="preserve">8.90741920471191</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89113521575928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11097240447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20053291320801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28195381164551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35523319244385</t>
+    <t xml:space="preserve">8.89113616943359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11097145080566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20053577423096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28195476531982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35523223876953</t>
   </si>
   <si>
     <t xml:space="preserve">9.39594459533691</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32266616821289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64834785461426</t>
+    <t xml:space="preserve">9.32266426086426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64834880828857</t>
   </si>
   <si>
     <t xml:space="preserve">9.60763835906982</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90075206756592</t>
+    <t xml:space="preserve">9.9007511138916</t>
   </si>
   <si>
     <t xml:space="preserve">9.99031448364258</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1205892562866</t>
+    <t xml:space="preserve">10.120587348938</t>
   </si>
   <si>
     <t xml:space="preserve">10.1368722915649</t>
@@ -527,7 +527,7 @@
     <t xml:space="preserve">10.1775827407837</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1043033599854</t>
+    <t xml:space="preserve">10.104302406311</t>
   </si>
   <si>
     <t xml:space="preserve">10.1531562805176</t>
@@ -536,70 +536,70 @@
     <t xml:space="preserve">10.0961618423462</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94146347045898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90889263153076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77047729492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83561706542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91703605651855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79490566253662</t>
+    <t xml:space="preserve">9.94146251678467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90889358520508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77047824859619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83561611175537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91703510284424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7949047088623</t>
   </si>
   <si>
     <t xml:space="preserve">9.77862167358398</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78676319122314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9577465057373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0147409439087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99845600128174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88446998596191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86004066467285</t>
+    <t xml:space="preserve">9.78676223754883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95774459838867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.014741897583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99845695495605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8844690322876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86004257202148</t>
   </si>
   <si>
     <t xml:space="preserve">9.85189914703369</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89261054992676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2590026855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3404216766357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4625549316406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5276927947998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5765409469604</t>
+    <t xml:space="preserve">9.89260959625244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2590036392212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.340425491333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4625558853149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5276918411255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5765428543091</t>
   </si>
   <si>
     <t xml:space="preserve">10.5439758300781</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5358324050903</t>
+    <t xml:space="preserve">10.535831451416</t>
   </si>
   <si>
     <t xml:space="preserve">10.5032653808594</t>
@@ -608,25 +608,25 @@
     <t xml:space="preserve">10.5521173477173</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3485660552979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4381275177002</t>
+    <t xml:space="preserve">10.3485641479492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4381294250488</t>
   </si>
   <si>
     <t xml:space="preserve">10.3241386413574</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3811349868774</t>
+    <t xml:space="preserve">10.3811340332031</t>
   </si>
   <si>
     <t xml:space="preserve">10.3648490905762</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4218444824219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4137020111084</t>
+    <t xml:space="preserve">10.4218454360962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4137010574341</t>
   </si>
   <si>
     <t xml:space="preserve">10.3729915618896</t>
@@ -635,19 +635,19 @@
     <t xml:space="preserve">10.3892765045166</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2915706634521</t>
+    <t xml:space="preserve">10.2915716171265</t>
   </si>
   <si>
     <t xml:space="preserve">10.2671451568604</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2264347076416</t>
+    <t xml:space="preserve">10.2264337539673</t>
   </si>
   <si>
     <t xml:space="preserve">10.1938667297363</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3159971237183</t>
+    <t xml:space="preserve">10.3159980773926</t>
   </si>
   <si>
     <t xml:space="preserve">10.2182931900024</t>
@@ -656,127 +656,133 @@
     <t xml:space="preserve">10.2834300994873</t>
   </si>
   <si>
-    <t xml:space="preserve">10.429986000061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3322811126709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2427186965942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5846853256226</t>
+    <t xml:space="preserve">10.4299869537354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3322801589966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2427196502686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5846862792969</t>
   </si>
   <si>
     <t xml:space="preserve">10.6661071777344</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7068176269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7475271224976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7882375717163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.625394821167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8696584701538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8289480209351</t>
+    <t xml:space="preserve">10.7068166732788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7475261688232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7882385253906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6253976821899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8696575164795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8289470672607</t>
   </si>
   <si>
     <t xml:space="preserve">11.0324993133545</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2360506057739</t>
+    <t xml:space="preserve">11.2360525131226</t>
   </si>
   <si>
     <t xml:space="preserve">11.439603805542</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6838645935059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0732088088989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9917879104614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1546287536621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3174695968628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2767610549927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1953411102295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3581819534302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4839172363281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5258312225342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5677423477173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4000940322876</t>
+    <t xml:space="preserve">11.6838665008545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0732107162476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9917888641357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1546306610107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3174705505371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.276762008667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1953392028809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3581829071045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4839181900024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5258302688599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5677433013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4000930786133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0228843688965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1486215591431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2324438095093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1905326843262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2743577957153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8971490859985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0647974014282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3581809997559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4420051574707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8552370071411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6875877380371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3254737854004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.282247543335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1957941055298</t>
   </si>
   <si>
     <t xml:space="preserve">11.0228853225708</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1486215591431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2324447631836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1905326843262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2743577957153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8971490859985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0647974014282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4420051574707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8552370071411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6875877380371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.325475692749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2822465896606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1957931518555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2390193939209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1525659561157</t>
+    <t xml:space="preserve">11.2390203475952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.15256690979</t>
   </si>
   <si>
     <t xml:space="preserve">10.936429977417</t>
@@ -788,7 +794,7 @@
     <t xml:space="preserve">11.1093397140503</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9796571731567</t>
+    <t xml:space="preserve">10.9796581268311</t>
   </si>
   <si>
     <t xml:space="preserve">10.7635231018066</t>
@@ -797,40 +803,40 @@
     <t xml:space="preserve">10.5906143188477</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8499784469604</t>
+    <t xml:space="preserve">10.8499794006348</t>
   </si>
   <si>
     <t xml:space="preserve">10.7202959060669</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6770687103271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8067502975464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8932046890259</t>
+    <t xml:space="preserve">10.6770696640015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8067512512207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8932037353516</t>
   </si>
   <si>
     <t xml:space="preserve">10.6338424682617</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4119281768799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4551544189453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3687009811401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5416097640991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6280641555786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5848340988159</t>
+    <t xml:space="preserve">11.4119262695312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4551553726196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3687000274658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5416088104248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6280632019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5848350524902</t>
   </si>
   <si>
     <t xml:space="preserve">10.4609346389771</t>
@@ -839,16 +845,16 @@
     <t xml:space="preserve">10.3312530517578</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3744792938232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2880258560181</t>
+    <t xml:space="preserve">10.3744812011719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2880249023438</t>
   </si>
   <si>
     <t xml:space="preserve">10.5041608810425</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0286655426025</t>
+    <t xml:space="preserve">10.0286645889282</t>
   </si>
   <si>
     <t xml:space="preserve">9.94220924377441</t>
@@ -857,25 +863,25 @@
     <t xml:space="preserve">9.59639453887939</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63962173461914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81253051757812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85575580596924</t>
+    <t xml:space="preserve">9.63961887359619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81252861022949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85575485229492</t>
   </si>
   <si>
     <t xml:space="preserve">9.55316734313965</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03444194793701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8183069229126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86153602600098</t>
+    <t xml:space="preserve">9.03444385528564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81830787658691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86153411865234</t>
   </si>
   <si>
     <t xml:space="preserve">8.77508068084717</t>
@@ -884,25 +890,25 @@
     <t xml:space="preserve">9.07767200469971</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16412353515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25057697296143</t>
+    <t xml:space="preserve">9.16412258148193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25057792663574</t>
   </si>
   <si>
     <t xml:space="preserve">9.33703231811523</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29380512237549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.244800567627</t>
+    <t xml:space="preserve">9.2938060760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2447986602783</t>
   </si>
   <si>
     <t xml:space="preserve">9.68284797668457</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1583442687988</t>
+    <t xml:space="preserve">10.1583461761475</t>
   </si>
   <si>
     <t xml:space="preserve">9.98543834686279</t>
@@ -911,25 +917,25 @@
     <t xml:space="preserve">9.89898300170898</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76930141448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72607421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46671199798584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5099401473999</t>
+    <t xml:space="preserve">9.76930236816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72607517242432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46671295166016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50994110107422</t>
   </si>
   <si>
     <t xml:space="preserve">9.3802604675293</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42348575592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20735168457031</t>
+    <t xml:space="preserve">9.42348670959473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.207350730896</t>
   </si>
   <si>
     <t xml:space="preserve">10.0718908309937</t>
@@ -941,25 +947,25 @@
     <t xml:space="preserve">10.2077474594116</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1629762649536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.342059135437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4316024780273</t>
+    <t xml:space="preserve">10.1629772186279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3420610427856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.431601524353</t>
   </si>
   <si>
     <t xml:space="preserve">10.3868322372437</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1182050704956</t>
+    <t xml:space="preserve">10.1182069778442</t>
   </si>
   <si>
     <t xml:space="preserve">10.2525186538696</t>
   </si>
   <si>
-    <t xml:space="preserve">10.476372718811</t>
+    <t xml:space="preserve">10.4763736724854</t>
   </si>
   <si>
     <t xml:space="preserve">10.6554555892944</t>
@@ -974,37 +980,34 @@
     <t xml:space="preserve">10.5659141540527</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7002277374268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1031627655029</t>
+    <t xml:space="preserve">10.7002258300781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1031637191772</t>
   </si>
   <si>
     <t xml:space="preserve">10.9688510894775</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9240818023682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8793096542358</t>
+    <t xml:space="preserve">10.9240808486938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8793106079102</t>
   </si>
   <si>
     <t xml:space="preserve">11.1479349136353</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2822484970093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2374773025513</t>
+    <t xml:space="preserve">11.237476348877</t>
   </si>
   <si>
     <t xml:space="preserve">11.4613304138184</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3270177841187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1927061080933</t>
+    <t xml:space="preserve">11.3270168304443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1927070617676</t>
   </si>
   <si>
     <t xml:space="preserve">11.3717889785767</t>
@@ -1013,55 +1016,55 @@
     <t xml:space="preserve">11.4165592193604</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0583925247192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6404142379761</t>
+    <t xml:space="preserve">11.0583934783936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6404132843018</t>
   </si>
   <si>
     <t xml:space="preserve">11.7299556732178</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6851844787598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7747268676758</t>
+    <t xml:space="preserve">11.6851854324341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7747259140015</t>
   </si>
   <si>
     <t xml:space="preserve">11.8194971084595</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8642673492432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5508708953857</t>
+    <t xml:space="preserve">11.8642683029175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5508728027344</t>
   </si>
   <si>
     <t xml:space="preserve">11.5956430435181</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5211429595947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0136222839355</t>
+    <t xml:space="preserve">10.5211448669434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0136232376099</t>
   </si>
   <si>
     <t xml:space="preserve">10.8345394134521</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9985790252686</t>
+    <t xml:space="preserve">11.9985799789429</t>
   </si>
   <si>
     <t xml:space="preserve">12.0881223678589</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0433511734009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1328935623169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2224349975586</t>
+    <t xml:space="preserve">12.0433502197266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1328916549683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2224340438843</t>
   </si>
   <si>
     <t xml:space="preserve">12.1776647567749</t>
@@ -1079,40 +1082,37 @@
     <t xml:space="preserve">12.311975479126</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6701440811157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.625373840332</t>
+    <t xml:space="preserve">12.6701431274414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6253728866577</t>
   </si>
   <si>
     <t xml:space="preserve">12.5806016921997</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6106853485107</t>
+    <t xml:space="preserve">10.6106843948364</t>
   </si>
   <si>
     <t xml:space="preserve">9.62572574615479</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0734338760376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0286645889282</t>
+    <t xml:space="preserve">10.0734357833862</t>
   </si>
   <si>
     <t xml:space="preserve">12.4910593032837</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9090385437012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1626234054565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6998720169067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8789558410645</t>
+    <t xml:space="preserve">11.9090394973755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1626224517822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6998729705811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8789548873901</t>
   </si>
   <si>
     <t xml:space="preserve">14.0132684707642</t>
@@ -1124,34 +1124,34 @@
     <t xml:space="preserve">14.2371215820312</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1923503875732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9237251281738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9684972763062</t>
+    <t xml:space="preserve">14.1923522949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9237260818481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9684963226318</t>
   </si>
   <si>
     <t xml:space="preserve">13.7894124984741</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2818937301636</t>
+    <t xml:space="preserve">14.2818927764893</t>
   </si>
   <si>
     <t xml:space="preserve">13.8341846466064</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5207901000977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4312477111816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5655584335327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.610330581665</t>
+    <t xml:space="preserve">13.520788192749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.431245803833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.565559387207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6103296279907</t>
   </si>
   <si>
     <t xml:space="preserve">13.7004642486572</t>
@@ -1160,55 +1160,55 @@
     <t xml:space="preserve">13.790599822998</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8356657028198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6553955078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5201959609985</t>
+    <t xml:space="preserve">13.8356666564941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6553964614868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5201950073242</t>
   </si>
   <si>
     <t xml:space="preserve">13.2948579788208</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1596565246582</t>
+    <t xml:space="preserve">13.1596574783325</t>
   </si>
   <si>
     <t xml:space="preserve">13.0695219039917</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9793882369995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.708984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5737810134888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6188478469849</t>
+    <t xml:space="preserve">12.9793872833252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7089834213257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5737819671631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6188488006592</t>
   </si>
   <si>
     <t xml:space="preserve">13.3399257659912</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1145887374878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4751272201538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9343214035034</t>
+    <t xml:space="preserve">13.1145896911621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4751281738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9343204498291</t>
   </si>
   <si>
     <t xml:space="preserve">12.7540512084961</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8441848754883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0610027313232</t>
+    <t xml:space="preserve">12.8441867828369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0610046386719</t>
   </si>
   <si>
     <t xml:space="preserve">13.8807334899902</t>
@@ -1217,22 +1217,22 @@
     <t xml:space="preserve">14.1962051391602</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3314075469971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4215421676636</t>
+    <t xml:space="preserve">14.3314065933228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4215412139893</t>
   </si>
   <si>
     <t xml:space="preserve">14.3764753341675</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5116748809814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4666090011597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6018123626709</t>
+    <t xml:space="preserve">14.5116758346558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4666080474854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6018114089966</t>
   </si>
   <si>
     <t xml:space="preserve">14.6919450759888</t>
@@ -1241,22 +1241,22 @@
     <t xml:space="preserve">14.8722152709961</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2327508926392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0074157714844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3228883743286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.187686920166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2242317199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9538326263428</t>
+    <t xml:space="preserve">15.2327518463135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0074167251587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3228893280029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1876850128174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.224235534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9538307189941</t>
   </si>
   <si>
     <t xml:space="preserve">16.8551769256592</t>
@@ -1268,16 +1268,16 @@
     <t xml:space="preserve">16.9903793334961</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8101100921631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7565250396729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0269241333008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9367904663086</t>
+    <t xml:space="preserve">16.8101081848145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7565212249756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0269260406494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9367923736572</t>
   </si>
   <si>
     <t xml:space="preserve">17.3509159088135</t>
@@ -1289,19 +1289,19 @@
     <t xml:space="preserve">17.4861183166504</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0354442596436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6298408508301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7199764251709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.404504776001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6749076843262</t>
+    <t xml:space="preserve">17.0354423522949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6298389434814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7199726104736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4045028686523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6749095916748</t>
   </si>
   <si>
     <t xml:space="preserve">16.9453086853027</t>
@@ -1310,31 +1310,31 @@
     <t xml:space="preserve">16.765043258667</t>
   </si>
   <si>
-    <t xml:space="preserve">15.863697052002</t>
+    <t xml:space="preserve">15.8636960983276</t>
   </si>
   <si>
     <t xml:space="preserve">15.9988965988159</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4946403503418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3594360351562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1791706085205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5847702026367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5397052764893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.683424949646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0890331268311</t>
+    <t xml:space="preserve">16.4946384429932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3594379425049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1791687011719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5847721099854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5397071838379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6834259033203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0890312194824</t>
   </si>
   <si>
     <t xml:space="preserve">15.5932903289795</t>
@@ -1349,7 +1349,7 @@
     <t xml:space="preserve">17.5762538909912</t>
   </si>
   <si>
-    <t xml:space="preserve">17.666389465332</t>
+    <t xml:space="preserve">17.6663856506348</t>
   </si>
   <si>
     <t xml:space="preserve">17.846658706665</t>
@@ -1361,7 +1361,7 @@
     <t xml:space="preserve">18.3874664306641</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7480049133301</t>
+    <t xml:space="preserve">18.7480030059814</t>
   </si>
   <si>
     <t xml:space="preserve">19.3789463043213</t>
@@ -1370,61 +1370,61 @@
     <t xml:space="preserve">20.0098896026611</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5506973266602</t>
+    <t xml:space="preserve">20.5506954193115</t>
   </si>
   <si>
     <t xml:space="preserve">20.4605617523193</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2802925109863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3704261779785</t>
+    <t xml:space="preserve">20.2802906036377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3704299926758</t>
   </si>
   <si>
     <t xml:space="preserve">20.1000232696533</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6408309936523</t>
+    <t xml:space="preserve">20.640832901001</t>
   </si>
   <si>
     <t xml:space="preserve">20.7309646606445</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4435234069824</t>
+    <t xml:space="preserve">22.4435253143311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9027156829834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5361442565918</t>
   </si>
   <si>
     <t xml:space="preserve">21.9027137756348</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5361442565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.902717590332</t>
-  </si>
-  <si>
     <t xml:space="preserve">21.1695690155029</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7194309234619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.360933303833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4525756835938</t>
+    <t xml:space="preserve">21.7194290161133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3609313964844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4525737762451</t>
   </si>
   <si>
     <t xml:space="preserve">22.269287109375</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0860023498535</t>
+    <t xml:space="preserve">22.0860042572021</t>
   </si>
   <si>
     <t xml:space="preserve">21.9943599700928</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6277866363525</t>
+    <t xml:space="preserve">21.6277885437012</t>
   </si>
   <si>
     <t xml:space="preserve">23.2773628234863</t>
@@ -1433,10 +1433,10 @@
     <t xml:space="preserve">22.9107913970947</t>
   </si>
   <si>
-    <t xml:space="preserve">22.727502822876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1776447296143</t>
+    <t xml:space="preserve">22.7275047302246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1776466369629</t>
   </si>
   <si>
     <t xml:space="preserve">22.6358604431152</t>
@@ -1451,73 +1451,73 @@
     <t xml:space="preserve">24.1021518707275</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2854385375977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9269409179688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2099456787109</t>
+    <t xml:space="preserve">24.285436630249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9269428253174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2099437713623</t>
   </si>
   <si>
     <t xml:space="preserve">26.851448059082</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6681594848633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.309663772583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4848747253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7598037719727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5765171051025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3015899658203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5684413909912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0347309112549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1425266265869</t>
+    <t xml:space="preserve">26.6681632995605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3096618652344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4848728179932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7598056793213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5765151977539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3015880584717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5684432983398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0347328186035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1425228118896</t>
   </si>
   <si>
     <t xml:space="preserve">28.4093818664551</t>
   </si>
   <si>
-    <t xml:space="preserve">28.134449005127</t>
+    <t xml:space="preserve">28.1344509124756</t>
   </si>
   <si>
     <t xml:space="preserve">28.2260932922363</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3646831512451</t>
+    <t xml:space="preserve">28.3646869659424</t>
   </si>
   <si>
     <t xml:space="preserve">28.4570770263672</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0875053405762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9951095581055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9027214050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7179336547852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1038303375244</t>
+    <t xml:space="preserve">28.0875072479248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9951133728027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.902717590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7179317474365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1038284301758</t>
   </si>
   <si>
     <t xml:space="preserve">29.9353694915771</t>
@@ -1526,49 +1526,49 @@
     <t xml:space="preserve">29.7505798339844</t>
   </si>
   <si>
-    <t xml:space="preserve">29.381010055542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8266525268555</t>
+    <t xml:space="preserve">29.3810062408447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8266506195068</t>
   </si>
   <si>
     <t xml:space="preserve">28.9190425872803</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7342548370361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.011438369751</t>
+    <t xml:space="preserve">28.7342567443848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0114326477051</t>
   </si>
   <si>
     <t xml:space="preserve">29.8429737091064</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1201496124268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2125473022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0277633666992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3973331451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1364765167236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8593006134033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0440826416016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6745128631592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.489725112915</t>
+    <t xml:space="preserve">30.1201515197754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2125492095947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0277614593506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3973350524902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1364784240723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8592987060547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0440845489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6745109558105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4897232055664</t>
   </si>
   <si>
     <t xml:space="preserve">29.2886161804199</t>
@@ -1577,37 +1577,37 @@
     <t xml:space="preserve">29.4734020233154</t>
   </si>
   <si>
-    <t xml:space="preserve">32.8919486999512</t>
+    <t xml:space="preserve">32.8919448852539</t>
   </si>
   <si>
     <t xml:space="preserve">33.3539085388184</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5550193786621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0930557250977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.8485260009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.4192047119141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.0986099243164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.2344207763672</t>
+    <t xml:space="preserve">34.5550231933594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0930595397949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.8485221862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.4192085266113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.0986137390137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.2344169616699</t>
   </si>
   <si>
     <t xml:space="preserve">37.881175994873</t>
   </si>
   <si>
-    <t xml:space="preserve">38.1583518981934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.6039924621582</t>
+    <t xml:space="preserve">38.1583557128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.6040000915527</t>
   </si>
   <si>
     <t xml:space="preserve">37.6963882446289</t>
@@ -1616,55 +1616,55 @@
     <t xml:space="preserve">37.7887840270996</t>
   </si>
   <si>
-    <t xml:space="preserve">37.1420364379883</t>
+    <t xml:space="preserve">37.1420288085938</t>
   </si>
   <si>
     <t xml:space="preserve">38.5279273986816</t>
   </si>
   <si>
-    <t xml:space="preserve">38.3431434631348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.4952812194824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.9409217834473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.402889251709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.6800689697266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.9735679626465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.0659599304199</t>
+    <t xml:space="preserve">38.3431396484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.4952774047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.9409255981445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.4028854370117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.6800651550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.9735641479492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.0659561157227</t>
   </si>
   <si>
     <t xml:space="preserve">38.4355316162109</t>
   </si>
   <si>
-    <t xml:space="preserve">38.8051071166992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.3594665527344</t>
+    <t xml:space="preserve">38.805103302002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.3594627380371</t>
   </si>
   <si>
     <t xml:space="preserve">39.8214263916016</t>
   </si>
   <si>
-    <t xml:space="preserve">40.006217956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.5605773925781</t>
+    <t xml:space="preserve">40.0062141418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.5605735778809</t>
   </si>
   <si>
     <t xml:space="preserve">40.6529693603516</t>
   </si>
   <si>
-    <t xml:space="preserve">41.9464721679688</t>
+    <t xml:space="preserve">41.946475982666</t>
   </si>
   <si>
     <t xml:space="preserve">41.114933013916</t>
@@ -1673,10 +1673,10 @@
     <t xml:space="preserve">40.9301452636719</t>
   </si>
   <si>
-    <t xml:space="preserve">42.3160438537598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.5171546936035</t>
+    <t xml:space="preserve">42.3160400390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.5171508789062</t>
   </si>
   <si>
     <t xml:space="preserve">44.0715141296387</t>
@@ -1691,13 +1691,13 @@
     <t xml:space="preserve">43.979118347168</t>
   </si>
   <si>
-    <t xml:space="preserve">44.3486938476562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.9954414367676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.8106575012207</t>
+    <t xml:space="preserve">44.348690032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.9954490661621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.810661315918</t>
   </si>
   <si>
     <t xml:space="preserve">44.5334777832031</t>
@@ -1715,19 +1715,19 @@
     <t xml:space="preserve">41.8540802001953</t>
   </si>
   <si>
-    <t xml:space="preserve">41.5769004821777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.2073249816895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.1910057067871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.4518585205078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.9898910522461</t>
+    <t xml:space="preserve">41.5768966674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.2073287963867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.1910018920898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.4518547058105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.9898948669434</t>
   </si>
   <si>
     <t xml:space="preserve">39.1746788024902</t>
@@ -1739,13 +1739,13 @@
     <t xml:space="preserve">40.7453575134277</t>
   </si>
   <si>
-    <t xml:space="preserve">41.0225410461426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.7290382385254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.9138221740723</t>
+    <t xml:space="preserve">41.0225372314453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.7290344238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.9138259887695</t>
   </si>
   <si>
     <t xml:space="preserve">40.4681816101074</t>
@@ -1754,37 +1754,37 @@
     <t xml:space="preserve">39.6366424560547</t>
   </si>
   <si>
-    <t xml:space="preserve">38.6203193664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.2670707702637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.3268203735352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.8974952697754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.5116004943848</t>
+    <t xml:space="preserve">38.6203155517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.2670745849609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.3268165588379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.8974990844727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.511604309082</t>
   </si>
   <si>
     <t xml:space="preserve">38.712718963623</t>
   </si>
   <si>
-    <t xml:space="preserve">39.0822830200195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.7724571228027</t>
+    <t xml:space="preserve">39.0822868347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.7724609375</t>
   </si>
   <si>
     <t xml:space="preserve">36.310489654541</t>
   </si>
   <si>
-    <t xml:space="preserve">36.2180976867676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.3865585327148</t>
+    <t xml:space="preserve">36.2181015014648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.3865661621094</t>
   </si>
   <si>
     <t xml:space="preserve">36.0333137512207</t>
@@ -1796,28 +1796,28 @@
     <t xml:space="preserve">33.7234840393066</t>
   </si>
   <si>
-    <t xml:space="preserve">33.1691284179688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6147651672363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.6310958862305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.707160949707</t>
+    <t xml:space="preserve">33.1691246032715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6147689819336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6310920715332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.7071647644043</t>
   </si>
   <si>
     <t xml:space="preserve">31.9680156707764</t>
   </si>
   <si>
-    <t xml:space="preserve">32.0604133605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4136600494385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6908359527588</t>
+    <t xml:space="preserve">32.0604095458984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4136562347412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6908378601074</t>
   </si>
   <si>
     <t xml:space="preserve">32.2451972961426</t>
@@ -1826,7 +1826,7 @@
     <t xml:space="preserve">32.7995529174805</t>
   </si>
   <si>
-    <t xml:space="preserve">33.9082679748535</t>
+    <t xml:space="preserve">33.9082717895508</t>
   </si>
   <si>
     <t xml:space="preserve">35.1093826293945</t>
@@ -1838,7 +1838,7 @@
     <t xml:space="preserve">35.0169906616211</t>
   </si>
   <si>
-    <t xml:space="preserve">32.337589263916</t>
+    <t xml:space="preserve">32.3375854492188</t>
   </si>
   <si>
     <t xml:space="preserve">32.4299812316895</t>
@@ -1847,46 +1847,46 @@
     <t xml:space="preserve">32.5223731994629</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5060482025146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3212642669678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.55224609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9218215942383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1528015136719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.4925003051758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.3702354431152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8620758056641</t>
+    <t xml:space="preserve">31.5060501098633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3212661743164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5522480010986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9218196868896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1527976989746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.492504119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.3702392578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8620719909668</t>
   </si>
   <si>
     <t xml:space="preserve">32.1066055297852</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5359210968018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3511352539062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7804508209229</t>
+    <t xml:space="preserve">30.5359230041504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3511333465576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7804546356201</t>
   </si>
   <si>
     <t xml:space="preserve">28.3643836975098</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3180351257324</t>
+    <t xml:space="preserve">28.3180332183838</t>
   </si>
   <si>
     <t xml:space="preserve">27.8082180023193</t>
@@ -1901,7 +1901,7 @@
     <t xml:space="preserve">27.9936084747314</t>
   </si>
   <si>
-    <t xml:space="preserve">28.642463684082</t>
+    <t xml:space="preserve">28.6424655914307</t>
   </si>
   <si>
     <t xml:space="preserve">29.5230579376221</t>
@@ -1916,34 +1916,34 @@
     <t xml:space="preserve">29.105936050415</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9009132385254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7155227661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1130123138428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4641551971436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4178085327148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.186071395874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6031970977783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2324199676514</t>
+    <t xml:space="preserve">27.900915145874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7155246734619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1130142211914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4641532897949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4178066253662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1860733032227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6031951904297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2324180603027</t>
   </si>
   <si>
     <t xml:space="preserve">26.556848526001</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3251132965088</t>
+    <t xml:space="preserve">26.3251113891602</t>
   </si>
   <si>
     <t xml:space="preserve">25.8152980804443</t>
@@ -1955,16 +1955,16 @@
     <t xml:space="preserve">25.2591304779053</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7029685974121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6566200256348</t>
+    <t xml:space="preserve">24.7029666900635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6566219329834</t>
   </si>
   <si>
     <t xml:space="preserve">23.9614143371582</t>
   </si>
   <si>
-    <t xml:space="preserve">23.729679107666</t>
+    <t xml:space="preserve">23.7296810150146</t>
   </si>
   <si>
     <t xml:space="preserve">25.0273971557617</t>
@@ -1976,16 +1976,16 @@
     <t xml:space="preserve">24.2858448028564</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6102733612061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3321914672852</t>
+    <t xml:space="preserve">24.6102714538574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3321895599365</t>
   </si>
   <si>
     <t xml:space="preserve">24.517578125</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3785381317139</t>
+    <t xml:space="preserve">24.3785362243652</t>
   </si>
   <si>
     <t xml:space="preserve">24.4712333679199</t>
@@ -2018,13 +2018,13 @@
     <t xml:space="preserve">25.5835609436035</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9543361663818</t>
+    <t xml:space="preserve">25.9543380737305</t>
   </si>
   <si>
     <t xml:space="preserve">26.6958885192871</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7885837554932</t>
+    <t xml:space="preserve">26.7885818481445</t>
   </si>
   <si>
     <t xml:space="preserve">26.7422370910645</t>
@@ -2039,7 +2039,7 @@
     <t xml:space="preserve">25.8616428375244</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1200923919678</t>
+    <t xml:space="preserve">25.1200904846191</t>
   </si>
   <si>
     <t xml:space="preserve">24.0077610015869</t>
@@ -2054,7 +2054,7 @@
     <t xml:space="preserve">23.0808200836182</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3125553131104</t>
+    <t xml:space="preserve">23.312557220459</t>
   </si>
   <si>
     <t xml:space="preserve">23.6369857788086</t>
@@ -2063,19 +2063,19 @@
     <t xml:space="preserve">23.5906391143799</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4052505493164</t>
+    <t xml:space="preserve">23.405252456665</t>
   </si>
   <si>
     <t xml:space="preserve">23.2662105560303</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3589057922363</t>
+    <t xml:space="preserve">23.3589038848877</t>
   </si>
   <si>
     <t xml:space="preserve">22.8027381896973</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6173534393311</t>
+    <t xml:space="preserve">22.6173496246338</t>
   </si>
   <si>
     <t xml:space="preserve">23.1735153198242</t>
@@ -2084,13 +2084,13 @@
     <t xml:space="preserve">22.8954334259033</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9684925079346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5513687133789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2732887268066</t>
+    <t xml:space="preserve">21.9684944152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5513706207275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.273286819458</t>
   </si>
   <si>
     <t xml:space="preserve">20.856164932251</t>
@@ -2102,13 +2102,13 @@
     <t xml:space="preserve">19.9755687713623</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1609592437744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2073020935059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8365287780762</t>
+    <t xml:space="preserve">20.1609573364258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2073040008545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8365268707275</t>
   </si>
   <si>
     <t xml:space="preserve">19.5584468841553</t>
@@ -2117,19 +2117,19 @@
     <t xml:space="preserve">19.604793548584</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9292240142822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.068265914917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1146125793457</t>
+    <t xml:space="preserve">19.9292221069336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0682640075684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1146106719971</t>
   </si>
   <si>
     <t xml:space="preserve">20.8098182678223</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9952030181885</t>
+    <t xml:space="preserve">20.9952049255371</t>
   </si>
   <si>
     <t xml:space="preserve">20.5780811309814</t>
@@ -2141,7 +2141,7 @@
     <t xml:space="preserve">21.5977172851562</t>
   </si>
   <si>
-    <t xml:space="preserve">22.061185836792</t>
+    <t xml:space="preserve">22.0611839294434</t>
   </si>
   <si>
     <t xml:space="preserve">22.4319629669189</t>
@@ -2153,28 +2153,28 @@
     <t xml:space="preserve">22.3392677307129</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6833324432373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5639266967773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4248847961426</t>
+    <t xml:space="preserve">23.6833343505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5639247894287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4248867034912</t>
   </si>
   <si>
     <t xml:space="preserve">25.1664390563965</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2127838134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.842004776001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7689476013184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7226009368896</t>
+    <t xml:space="preserve">25.2127857208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8420066833496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.768949508667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7226028442383</t>
   </si>
   <si>
     <t xml:space="preserve">25.3518257141113</t>
@@ -2186,10 +2186,10 @@
     <t xml:space="preserve">25.305477142334</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6762542724609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4908695220947</t>
+    <t xml:space="preserve">25.6762561798096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4908676147461</t>
   </si>
   <si>
     <t xml:space="preserve">27.6691799163818</t>
@@ -2204,7 +2204,7 @@
     <t xml:space="preserve">27.2984027862549</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5764846801758</t>
+    <t xml:space="preserve">27.5764827728271</t>
   </si>
   <si>
     <t xml:space="preserve">28.0399551391602</t>
@@ -2216,31 +2216,31 @@
     <t xml:space="preserve">28.2716884613037</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1326484680176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4374408721924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5301361083984</t>
+    <t xml:space="preserve">28.1326465606689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.437442779541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5301380157471</t>
   </si>
   <si>
     <t xml:space="preserve">26.093376159668</t>
   </si>
   <si>
-    <t xml:space="preserve">25.39817237854</t>
+    <t xml:space="preserve">25.3981742858887</t>
   </si>
   <si>
     <t xml:space="preserve">22.9417819976807</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2002296447754</t>
+    <t xml:space="preserve">22.2002277374268</t>
   </si>
   <si>
     <t xml:space="preserve">22.153881072998</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1075344085693</t>
+    <t xml:space="preserve">22.1075325012207</t>
   </si>
   <si>
     <t xml:space="preserve">22.7100448608398</t>
@@ -2249,7 +2249,7 @@
     <t xml:space="preserve">22.9881267547607</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2198600769043</t>
+    <t xml:space="preserve">23.2198619842529</t>
   </si>
   <si>
     <t xml:space="preserve">21.8294506072998</t>
@@ -2258,10 +2258,10 @@
     <t xml:space="preserve">20.6244277954102</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6707744598389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4853897094727</t>
+    <t xml:space="preserve">20.6707763671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.485387802124</t>
   </si>
   <si>
     <t xml:space="preserve">20.2536525726318</t>
@@ -2279,7 +2279,7 @@
     <t xml:space="preserve">21.6440620422363</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2269401550293</t>
+    <t xml:space="preserve">21.2269420623779</t>
   </si>
   <si>
     <t xml:space="preserve">21.3196334838867</t>
@@ -2291,7 +2291,7 @@
     <t xml:space="preserve">21.1805953979492</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9025115966797</t>
+    <t xml:space="preserve">20.9025096893311</t>
   </si>
   <si>
     <t xml:space="preserve">20.6679420471191</t>
@@ -19187,7 +19187,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G610" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -19239,7 +19239,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G612" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -19291,7 +19291,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G614" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -19317,7 +19317,7 @@
         <v>12.75</v>
       </c>
       <c r="G615" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -19343,7 +19343,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G616" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -19395,7 +19395,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G618" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -19421,7 +19421,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G619" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -19447,7 +19447,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G620" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -19473,7 +19473,7 @@
         <v>12.75</v>
       </c>
       <c r="G621" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -19499,7 +19499,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G622" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -19525,7 +19525,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G623" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -19551,7 +19551,7 @@
         <v>13</v>
       </c>
       <c r="G624" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -19577,7 +19577,7 @@
         <v>13</v>
       </c>
       <c r="G625" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -19603,7 +19603,7 @@
         <v>12.75</v>
       </c>
       <c r="G626" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -19629,7 +19629,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G627" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="H627" t="s">
         <v>9</v>
@@ -19655,7 +19655,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G628" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H628" t="s">
         <v>9</v>
@@ -19681,7 +19681,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G629" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="H629" t="s">
         <v>9</v>
@@ -19707,7 +19707,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G630" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="H630" t="s">
         <v>9</v>
@@ -19733,7 +19733,7 @@
         <v>12.75</v>
       </c>
       <c r="G631" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="H631" t="s">
         <v>9</v>
@@ -19759,7 +19759,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G632" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="H632" t="s">
         <v>9</v>
@@ -19785,7 +19785,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G633" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="H633" t="s">
         <v>9</v>
@@ -19811,7 +19811,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G634" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="H634" t="s">
         <v>9</v>
@@ -19837,7 +19837,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G635" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="H635" t="s">
         <v>9</v>
@@ -19863,7 +19863,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G636" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="H636" t="s">
         <v>9</v>
@@ -19889,7 +19889,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G637" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="H637" t="s">
         <v>9</v>
@@ -19915,7 +19915,7 @@
         <v>12.25</v>
       </c>
       <c r="G638" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="H638" t="s">
         <v>9</v>
@@ -19941,7 +19941,7 @@
         <v>12.25</v>
       </c>
       <c r="G639" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="H639" t="s">
         <v>9</v>
@@ -19967,7 +19967,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G640" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="H640" t="s">
         <v>9</v>
@@ -19993,7 +19993,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G641" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="H641" t="s">
         <v>9</v>
@@ -20019,7 +20019,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G642" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="H642" t="s">
         <v>9</v>
@@ -20045,7 +20045,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G643" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="H643" t="s">
         <v>9</v>
@@ -20071,7 +20071,7 @@
         <v>12.5</v>
       </c>
       <c r="G644" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="H644" t="s">
         <v>9</v>
@@ -20097,7 +20097,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G645" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="H645" t="s">
         <v>9</v>
@@ -20123,7 +20123,7 @@
         <v>12.5</v>
       </c>
       <c r="G646" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="H646" t="s">
         <v>9</v>
@@ -20149,7 +20149,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G647" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="H647" t="s">
         <v>9</v>
@@ -20175,7 +20175,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G648" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="H648" t="s">
         <v>9</v>
@@ -20201,7 +20201,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G649" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="H649" t="s">
         <v>9</v>
@@ -20227,7 +20227,7 @@
         <v>12.5</v>
       </c>
       <c r="G650" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="H650" t="s">
         <v>9</v>
@@ -20253,7 +20253,7 @@
         <v>12.5</v>
       </c>
       <c r="G651" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="H651" t="s">
         <v>9</v>
@@ -20279,7 +20279,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G652" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="H652" t="s">
         <v>9</v>
@@ -20305,7 +20305,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G653" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="H653" t="s">
         <v>9</v>
@@ -20331,7 +20331,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G654" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="H654" t="s">
         <v>9</v>
@@ -20357,7 +20357,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G655" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="H655" t="s">
         <v>9</v>
@@ -20383,7 +20383,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G656" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H656" t="s">
         <v>9</v>
@@ -20409,7 +20409,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G657" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H657" t="s">
         <v>9</v>
@@ -20435,7 +20435,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G658" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="H658" t="s">
         <v>9</v>
@@ -20461,7 +20461,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G659" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="H659" t="s">
         <v>9</v>
@@ -20487,7 +20487,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G660" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="H660" t="s">
         <v>9</v>
@@ -20513,7 +20513,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G661" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="H661" t="s">
         <v>9</v>
@@ -20539,7 +20539,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G662" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="H662" t="s">
         <v>9</v>
@@ -20565,7 +20565,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G663" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="H663" t="s">
         <v>9</v>
@@ -20591,7 +20591,7 @@
         <v>12.75</v>
       </c>
       <c r="G664" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -20617,7 +20617,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G665" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="H665" t="s">
         <v>9</v>
@@ -20643,7 +20643,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G666" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="H666" t="s">
         <v>9</v>
@@ -20669,7 +20669,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G667" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="H667" t="s">
         <v>9</v>
@@ -20695,7 +20695,7 @@
         <v>12.25</v>
       </c>
       <c r="G668" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="H668" t="s">
         <v>9</v>
@@ -20721,7 +20721,7 @@
         <v>12.25</v>
       </c>
       <c r="G669" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="H669" t="s">
         <v>9</v>
@@ -20747,7 +20747,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G670" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="H670" t="s">
         <v>9</v>
@@ -20773,7 +20773,7 @@
         <v>12.5</v>
       </c>
       <c r="G671" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="H671" t="s">
         <v>9</v>
@@ -20799,7 +20799,7 @@
         <v>12.5</v>
       </c>
       <c r="G672" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="H672" t="s">
         <v>9</v>
@@ -20825,7 +20825,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G673" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="H673" t="s">
         <v>9</v>
@@ -20851,7 +20851,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G674" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="H674" t="s">
         <v>9</v>
@@ -20877,7 +20877,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G675" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="H675" t="s">
         <v>9</v>
@@ -20903,7 +20903,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G676" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="H676" t="s">
         <v>9</v>
@@ -20929,7 +20929,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G677" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="H677" t="s">
         <v>9</v>
@@ -20955,7 +20955,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G678" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="H678" t="s">
         <v>9</v>
@@ -20981,7 +20981,7 @@
         <v>12.25</v>
       </c>
       <c r="G679" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="H679" t="s">
         <v>9</v>
@@ -21007,7 +21007,7 @@
         <v>12.25</v>
       </c>
       <c r="G680" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="H680" t="s">
         <v>9</v>
@@ -21033,7 +21033,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G681" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="H681" t="s">
         <v>9</v>
@@ -21059,7 +21059,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G682" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="H682" t="s">
         <v>9</v>
@@ -21085,7 +21085,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G683" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="H683" t="s">
         <v>9</v>
@@ -21111,7 +21111,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G684" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="H684" t="s">
         <v>9</v>
@@ -21137,7 +21137,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G685" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="H685" t="s">
         <v>9</v>
@@ -21163,7 +21163,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G686" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="H686" t="s">
         <v>9</v>
@@ -21189,7 +21189,7 @@
         <v>12.5</v>
       </c>
       <c r="G687" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="H687" t="s">
         <v>9</v>
@@ -21215,7 +21215,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G688" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="H688" t="s">
         <v>9</v>
@@ -21241,7 +21241,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G689" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="H689" t="s">
         <v>9</v>
@@ -21267,7 +21267,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G690" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="H690" t="s">
         <v>9</v>
@@ -21293,7 +21293,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G691" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="H691" t="s">
         <v>9</v>
@@ -21319,7 +21319,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G692" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="H692" t="s">
         <v>9</v>
@@ -21345,7 +21345,7 @@
         <v>12.75</v>
       </c>
       <c r="G693" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="H693" t="s">
         <v>9</v>
@@ -21371,7 +21371,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G694" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -21397,7 +21397,7 @@
         <v>13.25</v>
       </c>
       <c r="G695" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="H695" t="s">
         <v>9</v>
@@ -21423,7 +21423,7 @@
         <v>13</v>
       </c>
       <c r="G696" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="H696" t="s">
         <v>9</v>
@@ -21449,7 +21449,7 @@
         <v>13</v>
       </c>
       <c r="G697" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="H697" t="s">
         <v>9</v>
@@ -21475,7 +21475,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G698" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="H698" t="s">
         <v>9</v>
@@ -21501,7 +21501,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G699" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H699" t="s">
         <v>9</v>
@@ -21527,7 +21527,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G700" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H700" t="s">
         <v>9</v>
@@ -21553,7 +21553,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G701" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="H701" t="s">
         <v>9</v>
@@ -21579,7 +21579,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G702" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="H702" t="s">
         <v>9</v>
@@ -21605,7 +21605,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G703" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="H703" t="s">
         <v>9</v>
@@ -21631,7 +21631,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G704" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="H704" t="s">
         <v>9</v>
@@ -21657,7 +21657,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G705" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="H705" t="s">
         <v>9</v>
@@ -21683,7 +21683,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G706" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="H706" t="s">
         <v>9</v>
@@ -21709,7 +21709,7 @@
         <v>13.25</v>
       </c>
       <c r="G707" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="H707" t="s">
         <v>9</v>
@@ -21735,7 +21735,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G708" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H708" t="s">
         <v>9</v>
@@ -21761,7 +21761,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G709" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H709" t="s">
         <v>9</v>
@@ -21787,7 +21787,7 @@
         <v>13</v>
       </c>
       <c r="G710" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="H710" t="s">
         <v>9</v>
@@ -21813,7 +21813,7 @@
         <v>13</v>
       </c>
       <c r="G711" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="H711" t="s">
         <v>9</v>
@@ -21839,7 +21839,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G712" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H712" t="s">
         <v>9</v>
@@ -21865,7 +21865,7 @@
         <v>13</v>
       </c>
       <c r="G713" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="H713" t="s">
         <v>9</v>
@@ -21891,7 +21891,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G714" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="H714" t="s">
         <v>9</v>
@@ -21917,7 +21917,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G715" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H715" t="s">
         <v>9</v>
@@ -21943,7 +21943,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G716" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="H716" t="s">
         <v>9</v>
@@ -21969,7 +21969,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G717" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="H717" t="s">
         <v>9</v>
@@ -21995,7 +21995,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G718" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="H718" t="s">
         <v>9</v>
@@ -22021,7 +22021,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G719" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="H719" t="s">
         <v>9</v>
@@ -22047,7 +22047,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G720" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="H720" t="s">
         <v>9</v>
@@ -22073,7 +22073,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G721" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="H721" t="s">
         <v>9</v>
@@ -22099,7 +22099,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G722" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="H722" t="s">
         <v>9</v>
@@ -22125,7 +22125,7 @@
         <v>12.5</v>
       </c>
       <c r="G723" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="H723" t="s">
         <v>9</v>
@@ -22151,7 +22151,7 @@
         <v>13</v>
       </c>
       <c r="G724" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="H724" t="s">
         <v>9</v>
@@ -22177,7 +22177,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G725" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="H725" t="s">
         <v>9</v>
@@ -22203,7 +22203,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G726" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="H726" t="s">
         <v>9</v>
@@ -22229,7 +22229,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G727" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="H727" t="s">
         <v>9</v>
@@ -22255,7 +22255,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G728" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="H728" t="s">
         <v>9</v>
@@ -22281,7 +22281,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G729" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="H729" t="s">
         <v>9</v>
@@ -22307,7 +22307,7 @@
         <v>12.5</v>
       </c>
       <c r="G730" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="H730" t="s">
         <v>9</v>
@@ -22333,7 +22333,7 @@
         <v>12.25</v>
       </c>
       <c r="G731" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="H731" t="s">
         <v>9</v>
@@ -22359,7 +22359,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G732" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H732" t="s">
         <v>9</v>
@@ -22385,7 +22385,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G733" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="H733" t="s">
         <v>9</v>
@@ -22411,7 +22411,7 @@
         <v>12</v>
       </c>
       <c r="G734" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="H734" t="s">
         <v>9</v>
@@ -22437,7 +22437,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G735" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="H735" t="s">
         <v>9</v>
@@ -22463,7 +22463,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G736" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="H736" t="s">
         <v>9</v>
@@ -22489,7 +22489,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G737" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="H737" t="s">
         <v>9</v>
@@ -22515,7 +22515,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G738" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="H738" t="s">
         <v>9</v>
@@ -22541,7 +22541,7 @@
         <v>11.5</v>
       </c>
       <c r="G739" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="H739" t="s">
         <v>9</v>
@@ -22567,7 +22567,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G740" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="H740" t="s">
         <v>9</v>
@@ -22593,7 +22593,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G741" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="H741" t="s">
         <v>9</v>
@@ -22619,7 +22619,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G742" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="H742" t="s">
         <v>9</v>
@@ -22645,7 +22645,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G743" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="H743" t="s">
         <v>9</v>
@@ -22671,7 +22671,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G744" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="H744" t="s">
         <v>9</v>
@@ -22697,7 +22697,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G745" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="H745" t="s">
         <v>9</v>
@@ -22723,7 +22723,7 @@
         <v>11.5</v>
       </c>
       <c r="G746" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="H746" t="s">
         <v>9</v>
@@ -22749,7 +22749,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G747" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="H747" t="s">
         <v>9</v>
@@ -22775,7 +22775,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G748" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="H748" t="s">
         <v>9</v>
@@ -22801,7 +22801,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G749" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="H749" t="s">
         <v>9</v>
@@ -22827,7 +22827,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G750" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="H750" t="s">
         <v>9</v>
@@ -22853,7 +22853,7 @@
         <v>10.25</v>
       </c>
       <c r="G751" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="H751" t="s">
         <v>9</v>
@@ -22879,7 +22879,7 @@
         <v>10.25</v>
       </c>
       <c r="G752" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="H752" t="s">
         <v>9</v>
@@ -22905,7 +22905,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G753" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="H753" t="s">
         <v>9</v>
@@ -22931,7 +22931,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G754" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="H754" t="s">
         <v>9</v>
@@ -22957,7 +22957,7 @@
         <v>10.5</v>
       </c>
       <c r="G755" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="H755" t="s">
         <v>9</v>
@@ -22983,7 +22983,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G756" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="H756" t="s">
         <v>9</v>
@@ -23009,7 +23009,7 @@
         <v>10.5</v>
       </c>
       <c r="G757" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="H757" t="s">
         <v>9</v>
@@ -23035,7 +23035,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G758" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="H758" t="s">
         <v>9</v>
@@ -23061,7 +23061,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G759" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="H759" t="s">
         <v>9</v>
@@ -23087,7 +23087,7 @@
         <v>10.75</v>
       </c>
       <c r="G760" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="H760" t="s">
         <v>9</v>
@@ -23113,7 +23113,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G761" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="H761" t="s">
         <v>9</v>
@@ -23139,7 +23139,7 @@
         <v>11.5</v>
       </c>
       <c r="G762" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="H762" t="s">
         <v>9</v>
@@ -23165,7 +23165,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G763" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="H763" t="s">
         <v>9</v>
@@ -23191,7 +23191,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G764" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="H764" t="s">
         <v>9</v>
@@ -23217,7 +23217,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G765" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="H765" t="s">
         <v>9</v>
@@ -23243,7 +23243,7 @@
         <v>11.5</v>
       </c>
       <c r="G766" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="H766" t="s">
         <v>9</v>
@@ -23269,7 +23269,7 @@
         <v>11.5</v>
       </c>
       <c r="G767" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="H767" t="s">
         <v>9</v>
@@ -23295,7 +23295,7 @@
         <v>11.75</v>
       </c>
       <c r="G768" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="H768" t="s">
         <v>9</v>
@@ -23321,7 +23321,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G769" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="H769" t="s">
         <v>9</v>
@@ -23347,7 +23347,7 @@
         <v>12</v>
       </c>
       <c r="G770" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="H770" t="s">
         <v>9</v>
@@ -23373,7 +23373,7 @@
         <v>11.75</v>
       </c>
       <c r="G771" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="H771" t="s">
         <v>9</v>
@@ -23399,7 +23399,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G772" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="H772" t="s">
         <v>9</v>
@@ -23425,7 +23425,7 @@
         <v>11.5</v>
       </c>
       <c r="G773" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="H773" t="s">
         <v>9</v>
@@ -23451,7 +23451,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G774" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="H774" t="s">
         <v>9</v>
@@ -23477,7 +23477,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G775" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="H775" t="s">
         <v>9</v>
@@ -23503,7 +23503,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G776" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="H776" t="s">
         <v>9</v>
@@ -23529,7 +23529,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G777" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="H777" t="s">
         <v>9</v>
@@ -23555,7 +23555,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G778" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="H778" t="s">
         <v>9</v>
@@ -23581,7 +23581,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G779" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="H779" t="s">
         <v>9</v>
@@ -23607,7 +23607,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G780" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="H780" t="s">
         <v>9</v>
@@ -23633,7 +23633,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G781" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="H781" t="s">
         <v>9</v>
@@ -23659,7 +23659,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G782" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="H782" t="s">
         <v>9</v>
@@ -23685,7 +23685,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G783" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="H783" t="s">
         <v>9</v>
@@ -23711,7 +23711,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G784" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="H784" t="s">
         <v>9</v>
@@ -23737,7 +23737,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G785" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="H785" t="s">
         <v>9</v>
@@ -23763,7 +23763,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G786" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="H786" t="s">
         <v>9</v>
@@ -23789,7 +23789,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G787" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="H787" t="s">
         <v>9</v>
@@ -23815,7 +23815,7 @@
         <v>11.5</v>
       </c>
       <c r="G788" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="H788" t="s">
         <v>9</v>
@@ -23841,7 +23841,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G789" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="H789" t="s">
         <v>9</v>
@@ -23867,7 +23867,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G790" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="H790" t="s">
         <v>9</v>
@@ -23893,7 +23893,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G791" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="H791" t="s">
         <v>9</v>
@@ -23919,7 +23919,7 @@
         <v>11.5</v>
       </c>
       <c r="G792" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="H792" t="s">
         <v>9</v>
@@ -23945,7 +23945,7 @@
         <v>11.25</v>
       </c>
       <c r="G793" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="H793" t="s">
         <v>9</v>
@@ -23971,7 +23971,7 @@
         <v>11.25</v>
       </c>
       <c r="G794" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="H794" t="s">
         <v>9</v>
@@ -23997,7 +23997,7 @@
         <v>11.5</v>
       </c>
       <c r="G795" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="H795" t="s">
         <v>9</v>
@@ -24023,7 +24023,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G796" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="H796" t="s">
         <v>9</v>
@@ -24049,7 +24049,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G797" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="H797" t="s">
         <v>9</v>
@@ -24075,7 +24075,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G798" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="H798" t="s">
         <v>9</v>
@@ -24101,7 +24101,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G799" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="H799" t="s">
         <v>9</v>
@@ -24127,7 +24127,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G800" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="H800" t="s">
         <v>9</v>
@@ -24153,7 +24153,7 @@
         <v>11</v>
       </c>
       <c r="G801" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="H801" t="s">
         <v>9</v>
@@ -24179,7 +24179,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G802" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="H802" t="s">
         <v>9</v>
@@ -24205,7 +24205,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G803" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="H803" t="s">
         <v>9</v>
@@ -24231,7 +24231,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G804" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="H804" t="s">
         <v>9</v>
@@ -24257,7 +24257,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G805" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="H805" t="s">
         <v>9</v>
@@ -24283,7 +24283,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G806" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="H806" t="s">
         <v>9</v>
@@ -24309,7 +24309,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G807" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="H807" t="s">
         <v>9</v>
@@ -24335,7 +24335,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G808" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="H808" t="s">
         <v>9</v>
@@ -24361,7 +24361,7 @@
         <v>11</v>
       </c>
       <c r="G809" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="H809" t="s">
         <v>9</v>
@@ -24387,7 +24387,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G810" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="H810" t="s">
         <v>9</v>
@@ -24413,7 +24413,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G811" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="H811" t="s">
         <v>9</v>
@@ -24439,7 +24439,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G812" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="H812" t="s">
         <v>9</v>
@@ -24465,7 +24465,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G813" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="H813" t="s">
         <v>9</v>
@@ -24491,7 +24491,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G814" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="H814" t="s">
         <v>9</v>
@@ -24517,7 +24517,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G815" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="H815" t="s">
         <v>9</v>
@@ -24543,7 +24543,7 @@
         <v>10.75</v>
       </c>
       <c r="G816" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="H816" t="s">
         <v>9</v>
@@ -24569,7 +24569,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G817" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="H817" t="s">
         <v>9</v>
@@ -24595,7 +24595,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G818" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="H818" t="s">
         <v>9</v>
@@ -24621,7 +24621,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G819" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="H819" t="s">
         <v>9</v>
@@ -24647,7 +24647,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G820" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="H820" t="s">
         <v>9</v>
@@ -24673,7 +24673,7 @@
         <v>11.25</v>
       </c>
       <c r="G821" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="H821" t="s">
         <v>9</v>
@@ -24699,7 +24699,7 @@
         <v>11.25</v>
       </c>
       <c r="G822" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="H822" t="s">
         <v>9</v>
@@ -24725,7 +24725,7 @@
         <v>11.25</v>
       </c>
       <c r="G823" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="H823" t="s">
         <v>9</v>
@@ -24751,7 +24751,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G824" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="H824" t="s">
         <v>9</v>
@@ -24777,7 +24777,7 @@
         <v>11.5</v>
       </c>
       <c r="G825" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="H825" t="s">
         <v>9</v>
@@ -24803,7 +24803,7 @@
         <v>11.5</v>
       </c>
       <c r="G826" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="H826" t="s">
         <v>9</v>
@@ -24829,7 +24829,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G827" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="H827" t="s">
         <v>9</v>
@@ -24855,7 +24855,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G828" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="H828" t="s">
         <v>9</v>
@@ -24881,7 +24881,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G829" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="H829" t="s">
         <v>9</v>
@@ -24907,7 +24907,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G830" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="H830" t="s">
         <v>9</v>
@@ -24933,7 +24933,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G831" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="H831" t="s">
         <v>9</v>
@@ -24959,7 +24959,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G832" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="H832" t="s">
         <v>9</v>
@@ -24985,7 +24985,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G833" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="H833" t="s">
         <v>9</v>
@@ -25011,7 +25011,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G834" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="H834" t="s">
         <v>9</v>
@@ -25037,7 +25037,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G835" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="H835" t="s">
         <v>9</v>
@@ -25063,7 +25063,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G836" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="H836" t="s">
         <v>9</v>
@@ -25089,7 +25089,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G837" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="H837" t="s">
         <v>9</v>
@@ -25115,7 +25115,7 @@
         <v>11.5</v>
       </c>
       <c r="G838" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="H838" t="s">
         <v>9</v>
@@ -25141,7 +25141,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G839" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="H839" t="s">
         <v>9</v>
@@ -25167,7 +25167,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G840" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="H840" t="s">
         <v>9</v>
@@ -25193,7 +25193,7 @@
         <v>11.5</v>
       </c>
       <c r="G841" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="H841" t="s">
         <v>9</v>
@@ -25219,7 +25219,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G842" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="H842" t="s">
         <v>9</v>
@@ -25245,7 +25245,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G843" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="H843" t="s">
         <v>9</v>
@@ -25271,7 +25271,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G844" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="H844" t="s">
         <v>9</v>
@@ -25297,7 +25297,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G845" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="H845" t="s">
         <v>9</v>
@@ -25323,7 +25323,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G846" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="H846" t="s">
         <v>9</v>
@@ -25349,7 +25349,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G847" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -25375,7 +25375,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G848" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="H848" t="s">
         <v>9</v>
@@ -25401,7 +25401,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G849" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="H849" t="s">
         <v>9</v>
@@ -25427,7 +25427,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G850" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="H850" t="s">
         <v>9</v>
@@ -25453,7 +25453,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G851" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -25479,7 +25479,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G852" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="H852" t="s">
         <v>9</v>
@@ -25505,7 +25505,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G853" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -25531,7 +25531,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G854" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="H854" t="s">
         <v>9</v>
@@ -25557,7 +25557,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G855" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -25583,7 +25583,7 @@
         <v>11.5</v>
       </c>
       <c r="G856" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -25609,7 +25609,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G857" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="H857" t="s">
         <v>9</v>
@@ -25635,7 +25635,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G858" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -25661,7 +25661,7 @@
         <v>11.5</v>
       </c>
       <c r="G859" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="H859" t="s">
         <v>9</v>
@@ -25687,7 +25687,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G860" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="H860" t="s">
         <v>9</v>
@@ -25713,7 +25713,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G861" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -25739,7 +25739,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G862" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="H862" t="s">
         <v>9</v>
@@ -25765,7 +25765,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G863" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="H863" t="s">
         <v>9</v>
@@ -25791,7 +25791,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G864" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="H864" t="s">
         <v>9</v>
@@ -25817,7 +25817,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G865" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="H865" t="s">
         <v>9</v>
@@ -25843,7 +25843,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G866" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="H866" t="s">
         <v>9</v>
@@ -25869,7 +25869,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G867" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="H867" t="s">
         <v>9</v>
@@ -25895,7 +25895,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G868" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="H868" t="s">
         <v>9</v>
@@ -25921,7 +25921,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G869" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="H869" t="s">
         <v>9</v>
@@ -25947,7 +25947,7 @@
         <v>12</v>
       </c>
       <c r="G870" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="H870" t="s">
         <v>9</v>
@@ -25973,7 +25973,7 @@
         <v>12</v>
       </c>
       <c r="G871" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="H871" t="s">
         <v>9</v>
@@ -25999,7 +25999,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G872" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="H872" t="s">
         <v>9</v>
@@ -26025,7 +26025,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G873" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="H873" t="s">
         <v>9</v>
@@ -26051,7 +26051,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G874" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="H874" t="s">
         <v>9</v>
@@ -26077,7 +26077,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G875" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="H875" t="s">
         <v>9</v>
@@ -26103,7 +26103,7 @@
         <v>12</v>
       </c>
       <c r="G876" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="H876" t="s">
         <v>9</v>
@@ -26129,7 +26129,7 @@
         <v>12</v>
       </c>
       <c r="G877" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="H877" t="s">
         <v>9</v>
@@ -26155,7 +26155,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G878" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="H878" t="s">
         <v>9</v>
@@ -26181,7 +26181,7 @@
         <v>12</v>
       </c>
       <c r="G879" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="H879" t="s">
         <v>9</v>
@@ -26207,7 +26207,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G880" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="H880" t="s">
         <v>9</v>
@@ -26233,7 +26233,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G881" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="H881" t="s">
         <v>9</v>
@@ -26259,7 +26259,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G882" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="H882" t="s">
         <v>9</v>
@@ -26285,7 +26285,7 @@
         <v>12</v>
       </c>
       <c r="G883" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="H883" t="s">
         <v>9</v>
@@ -26311,7 +26311,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G884" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="H884" t="s">
         <v>9</v>
@@ -26337,7 +26337,7 @@
         <v>12.25</v>
       </c>
       <c r="G885" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="H885" t="s">
         <v>9</v>
@@ -26363,7 +26363,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G886" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="H886" t="s">
         <v>9</v>
@@ -26389,7 +26389,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G887" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="H887" t="s">
         <v>9</v>
@@ -26415,7 +26415,7 @@
         <v>12.25</v>
       </c>
       <c r="G888" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="H888" t="s">
         <v>9</v>
@@ -26441,7 +26441,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G889" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="H889" t="s">
         <v>9</v>
@@ -26467,7 +26467,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G890" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="H890" t="s">
         <v>9</v>
@@ -26493,7 +26493,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G891" t="s">
-        <v>326</v>
+        <v>252</v>
       </c>
       <c r="H891" t="s">
         <v>9</v>
@@ -26519,7 +26519,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G892" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H892" t="s">
         <v>9</v>
@@ -26545,7 +26545,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G893" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H893" t="s">
         <v>9</v>
@@ -26571,7 +26571,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G894" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H894" t="s">
         <v>9</v>
@@ -26597,7 +26597,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G895" t="s">
-        <v>326</v>
+        <v>252</v>
       </c>
       <c r="H895" t="s">
         <v>9</v>
@@ -26623,7 +26623,7 @@
         <v>12.5</v>
       </c>
       <c r="G896" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H896" t="s">
         <v>9</v>
@@ -26649,7 +26649,7 @@
         <v>12.5</v>
       </c>
       <c r="G897" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H897" t="s">
         <v>9</v>
@@ -26675,7 +26675,7 @@
         <v>12.5</v>
       </c>
       <c r="G898" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H898" t="s">
         <v>9</v>
@@ -26701,7 +26701,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G899" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H899" t="s">
         <v>9</v>
@@ -26727,7 +26727,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G900" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H900" t="s">
         <v>9</v>
@@ -26753,7 +26753,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G901" t="s">
-        <v>326</v>
+        <v>252</v>
       </c>
       <c r="H901" t="s">
         <v>9</v>
@@ -26779,7 +26779,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G902" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H902" t="s">
         <v>9</v>
@@ -26805,7 +26805,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G903" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H903" t="s">
         <v>9</v>
@@ -26831,7 +26831,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G904" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H904" t="s">
         <v>9</v>
@@ -26857,7 +26857,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G905" t="s">
-        <v>326</v>
+        <v>252</v>
       </c>
       <c r="H905" t="s">
         <v>9</v>
@@ -26883,7 +26883,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G906" t="s">
-        <v>326</v>
+        <v>252</v>
       </c>
       <c r="H906" t="s">
         <v>9</v>
@@ -26909,7 +26909,7 @@
         <v>12.75</v>
       </c>
       <c r="G907" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H907" t="s">
         <v>9</v>
@@ -26935,7 +26935,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G908" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H908" t="s">
         <v>9</v>
@@ -26961,7 +26961,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G909" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H909" t="s">
         <v>9</v>
@@ -26987,7 +26987,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G910" t="s">
-        <v>326</v>
+        <v>252</v>
       </c>
       <c r="H910" t="s">
         <v>9</v>
@@ -27013,7 +27013,7 @@
         <v>12.5</v>
       </c>
       <c r="G911" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H911" t="s">
         <v>9</v>
@@ -27039,7 +27039,7 @@
         <v>12.5</v>
       </c>
       <c r="G912" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H912" t="s">
         <v>9</v>
@@ -27065,7 +27065,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G913" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="H913" t="s">
         <v>9</v>
@@ -27091,7 +27091,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G914" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H914" t="s">
         <v>9</v>
@@ -27117,7 +27117,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G915" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H915" t="s">
         <v>9</v>
@@ -27143,7 +27143,7 @@
         <v>12.5</v>
       </c>
       <c r="G916" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H916" t="s">
         <v>9</v>
@@ -27169,7 +27169,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G917" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H917" t="s">
         <v>9</v>
@@ -27195,7 +27195,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G918" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="H918" t="s">
         <v>9</v>
@@ -27221,7 +27221,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G919" t="s">
-        <v>326</v>
+        <v>252</v>
       </c>
       <c r="H919" t="s">
         <v>9</v>
@@ -27247,7 +27247,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G920" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H920" t="s">
         <v>9</v>
@@ -27273,7 +27273,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G921" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H921" t="s">
         <v>9</v>
@@ -27299,7 +27299,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G922" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="H922" t="s">
         <v>9</v>
@@ -27325,7 +27325,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G923" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="H923" t="s">
         <v>9</v>
@@ -27351,7 +27351,7 @@
         <v>12.5</v>
       </c>
       <c r="G924" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H924" t="s">
         <v>9</v>
@@ -27377,7 +27377,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G925" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H925" t="s">
         <v>9</v>
@@ -27403,7 +27403,7 @@
         <v>12.5</v>
       </c>
       <c r="G926" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H926" t="s">
         <v>9</v>
@@ -27429,7 +27429,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G927" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H927" t="s">
         <v>9</v>
@@ -27455,7 +27455,7 @@
         <v>12.5</v>
       </c>
       <c r="G928" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H928" t="s">
         <v>9</v>
@@ -27481,7 +27481,7 @@
         <v>12.5</v>
       </c>
       <c r="G929" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H929" t="s">
         <v>9</v>
@@ -27507,7 +27507,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G930" t="s">
-        <v>326</v>
+        <v>252</v>
       </c>
       <c r="H930" t="s">
         <v>9</v>
@@ -27533,7 +27533,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G931" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H931" t="s">
         <v>9</v>
@@ -27559,7 +27559,7 @@
         <v>13</v>
       </c>
       <c r="G932" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H932" t="s">
         <v>9</v>
@@ -27585,7 +27585,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G933" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H933" t="s">
         <v>9</v>
@@ -27611,7 +27611,7 @@
         <v>13</v>
       </c>
       <c r="G934" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H934" t="s">
         <v>9</v>
@@ -27637,7 +27637,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G935" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H935" t="s">
         <v>9</v>
@@ -27663,7 +27663,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G936" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H936" t="s">
         <v>9</v>
@@ -27689,7 +27689,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G937" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H937" t="s">
         <v>9</v>
@@ -27715,7 +27715,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G938" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H938" t="s">
         <v>9</v>
@@ -27741,7 +27741,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G939" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H939" t="s">
         <v>9</v>
@@ -27767,7 +27767,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G940" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H940" t="s">
         <v>9</v>
@@ -27793,7 +27793,7 @@
         <v>13.25</v>
       </c>
       <c r="G941" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H941" t="s">
         <v>9</v>
@@ -27819,7 +27819,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G942" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H942" t="s">
         <v>9</v>
@@ -27845,7 +27845,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G943" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H943" t="s">
         <v>9</v>
@@ -27871,7 +27871,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G944" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H944" t="s">
         <v>9</v>
@@ -27897,7 +27897,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G945" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H945" t="s">
         <v>9</v>
@@ -27923,7 +27923,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G946" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H946" t="s">
         <v>9</v>
@@ -27949,7 +27949,7 @@
         <v>12.75</v>
       </c>
       <c r="G947" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H947" t="s">
         <v>9</v>
@@ -27975,7 +27975,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G948" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H948" t="s">
         <v>9</v>
@@ -28001,7 +28001,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G949" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H949" t="s">
         <v>9</v>
@@ -28027,7 +28027,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G950" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H950" t="s">
         <v>9</v>
@@ -28053,7 +28053,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G951" t="s">
-        <v>326</v>
+        <v>252</v>
       </c>
       <c r="H951" t="s">
         <v>9</v>
@@ -28079,7 +28079,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G952" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H952" t="s">
         <v>9</v>
@@ -28105,7 +28105,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G953" t="s">
-        <v>326</v>
+        <v>252</v>
       </c>
       <c r="H953" t="s">
         <v>9</v>
@@ -28131,7 +28131,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G954" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H954" t="s">
         <v>9</v>
@@ -28157,7 +28157,7 @@
         <v>12.5</v>
       </c>
       <c r="G955" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H955" t="s">
         <v>9</v>
@@ -28183,7 +28183,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G956" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="H956" t="s">
         <v>9</v>
@@ -28209,7 +28209,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G957" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="H957" t="s">
         <v>9</v>
@@ -28235,7 +28235,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G958" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="H958" t="s">
         <v>9</v>
@@ -28261,7 +28261,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G959" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="H959" t="s">
         <v>9</v>
@@ -28287,7 +28287,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G960" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="H960" t="s">
         <v>9</v>
@@ -28313,7 +28313,7 @@
         <v>11.75</v>
       </c>
       <c r="G961" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H961" t="s">
         <v>9</v>
@@ -28339,7 +28339,7 @@
         <v>11.5</v>
       </c>
       <c r="G962" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="H962" t="s">
         <v>9</v>
@@ -28365,7 +28365,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G963" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="H963" t="s">
         <v>9</v>
@@ -28391,7 +28391,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G964" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="H964" t="s">
         <v>9</v>
@@ -28417,7 +28417,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G965" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="H965" t="s">
         <v>9</v>
@@ -28443,7 +28443,7 @@
         <v>12.25</v>
       </c>
       <c r="G966" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="H966" t="s">
         <v>9</v>
@@ -28469,7 +28469,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G967" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="H967" t="s">
         <v>9</v>
@@ -28495,7 +28495,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G968" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="H968" t="s">
         <v>9</v>
@@ -28521,7 +28521,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G969" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H969" t="s">
         <v>9</v>
@@ -28547,7 +28547,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G970" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="H970" t="s">
         <v>9</v>
@@ -28573,7 +28573,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G971" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H971" t="s">
         <v>9</v>
@@ -28599,7 +28599,7 @@
         <v>12.25</v>
       </c>
       <c r="G972" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="H972" t="s">
         <v>9</v>
@@ -28625,7 +28625,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G973" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="H973" t="s">
         <v>9</v>
@@ -28651,7 +28651,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G974" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="H974" t="s">
         <v>9</v>
@@ -28677,7 +28677,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G975" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="H975" t="s">
         <v>9</v>
@@ -28703,7 +28703,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G976" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H976" t="s">
         <v>9</v>
@@ -28729,7 +28729,7 @@
         <v>12.5</v>
       </c>
       <c r="G977" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H977" t="s">
         <v>9</v>
@@ -28755,7 +28755,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G978" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="H978" t="s">
         <v>9</v>
@@ -28781,7 +28781,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G979" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H979" t="s">
         <v>9</v>
@@ -28807,7 +28807,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G980" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="H980" t="s">
         <v>9</v>
@@ -28833,7 +28833,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G981" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H981" t="s">
         <v>9</v>
@@ -28859,7 +28859,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G982" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H982" t="s">
         <v>9</v>
@@ -28885,7 +28885,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G983" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="H983" t="s">
         <v>9</v>
@@ -28911,7 +28911,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G984" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H984" t="s">
         <v>9</v>
@@ -28937,7 +28937,7 @@
         <v>12.25</v>
       </c>
       <c r="G985" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="H985" t="s">
         <v>9</v>
@@ -28963,7 +28963,7 @@
         <v>12.25</v>
       </c>
       <c r="G986" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="H986" t="s">
         <v>9</v>
@@ -28989,7 +28989,7 @@
         <v>12.25</v>
       </c>
       <c r="G987" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="H987" t="s">
         <v>9</v>
@@ -29015,7 +29015,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G988" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="H988" t="s">
         <v>9</v>
@@ -29041,7 +29041,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G989" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="H989" t="s">
         <v>9</v>
@@ -29067,7 +29067,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G990" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="H990" t="s">
         <v>9</v>
@@ -29093,7 +29093,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G991" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="H991" t="s">
         <v>9</v>
@@ -29119,7 +29119,7 @@
         <v>11.75</v>
       </c>
       <c r="G992" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H992" t="s">
         <v>9</v>
@@ -29145,7 +29145,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G993" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="H993" t="s">
         <v>9</v>
@@ -29171,7 +29171,7 @@
         <v>12</v>
       </c>
       <c r="G994" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="H994" t="s">
         <v>9</v>
@@ -29197,7 +29197,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G995" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="H995" t="s">
         <v>9</v>
@@ -29223,7 +29223,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G996" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="H996" t="s">
         <v>9</v>
@@ -29249,7 +29249,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G997" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="H997" t="s">
         <v>9</v>
@@ -29275,7 +29275,7 @@
         <v>12.25</v>
       </c>
       <c r="G998" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="H998" t="s">
         <v>9</v>
@@ -29301,7 +29301,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G999" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H999" t="s">
         <v>9</v>
@@ -29327,7 +29327,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1000" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H1000" t="s">
         <v>9</v>
@@ -29353,7 +29353,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G1001" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="H1001" t="s">
         <v>9</v>
@@ -29379,7 +29379,7 @@
         <v>12</v>
       </c>
       <c r="G1002" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="H1002" t="s">
         <v>9</v>
@@ -29405,7 +29405,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1003" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H1003" t="s">
         <v>9</v>
@@ -29431,7 +29431,7 @@
         <v>12.25</v>
       </c>
       <c r="G1004" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="H1004" t="s">
         <v>9</v>
@@ -29457,7 +29457,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G1005" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="H1005" t="s">
         <v>9</v>
@@ -29483,7 +29483,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G1006" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="H1006" t="s">
         <v>9</v>
@@ -29509,7 +29509,7 @@
         <v>12.25</v>
       </c>
       <c r="G1007" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="H1007" t="s">
         <v>9</v>
@@ -29535,7 +29535,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G1008" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H1008" t="s">
         <v>9</v>
@@ -29561,7 +29561,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G1009" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="H1009" t="s">
         <v>9</v>
@@ -29587,7 +29587,7 @@
         <v>12.5</v>
       </c>
       <c r="G1010" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H1010" t="s">
         <v>9</v>
@@ -29613,7 +29613,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G1011" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="H1011" t="s">
         <v>9</v>
@@ -29639,7 +29639,7 @@
         <v>12.5</v>
       </c>
       <c r="G1012" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H1012" t="s">
         <v>9</v>
@@ -29665,7 +29665,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1013" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H1013" t="s">
         <v>9</v>
@@ -29691,7 +29691,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1014" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H1014" t="s">
         <v>9</v>
@@ -29717,7 +29717,7 @@
         <v>12.75</v>
       </c>
       <c r="G1015" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H1015" t="s">
         <v>9</v>
@@ -29743,7 +29743,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G1016" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H1016" t="s">
         <v>9</v>
@@ -29769,7 +29769,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1017" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H1017" t="s">
         <v>9</v>
@@ -29795,7 +29795,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1018" t="s">
-        <v>326</v>
+        <v>252</v>
       </c>
       <c r="H1018" t="s">
         <v>9</v>
@@ -29821,7 +29821,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1019" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H1019" t="s">
         <v>9</v>
@@ -29847,7 +29847,7 @@
         <v>13.25</v>
       </c>
       <c r="G1020" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H1020" t="s">
         <v>9</v>
@@ -29873,7 +29873,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1021" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H1021" t="s">
         <v>9</v>
@@ -29899,7 +29899,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G1022" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H1022" t="s">
         <v>9</v>
@@ -29925,7 +29925,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1023" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H1023" t="s">
         <v>9</v>
@@ -29951,7 +29951,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G1024" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H1024" t="s">
         <v>9</v>
@@ -29977,7 +29977,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1025" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H1025" t="s">
         <v>9</v>
@@ -30003,7 +30003,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1026" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H1026" t="s">
         <v>9</v>
@@ -30029,7 +30029,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G1027" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H1027" t="s">
         <v>9</v>
@@ -30055,7 +30055,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1028" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H1028" t="s">
         <v>9</v>
@@ -30081,7 +30081,7 @@
         <v>13.5</v>
       </c>
       <c r="G1029" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H1029" t="s">
         <v>9</v>
@@ -30107,7 +30107,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G1030" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H1030" t="s">
         <v>9</v>
@@ -30133,7 +30133,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G1031" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H1031" t="s">
         <v>9</v>
@@ -30159,7 +30159,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G1032" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H1032" t="s">
         <v>9</v>
@@ -30185,7 +30185,7 @@
         <v>13.5</v>
       </c>
       <c r="G1033" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H1033" t="s">
         <v>9</v>
@@ -30211,7 +30211,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1034" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H1034" t="s">
         <v>9</v>
@@ -30237,7 +30237,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1035" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H1035" t="s">
         <v>9</v>
@@ -30263,7 +30263,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1036" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H1036" t="s">
         <v>9</v>
@@ -30289,7 +30289,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1037" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H1037" t="s">
         <v>9</v>
@@ -30315,7 +30315,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G1038" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H1038" t="s">
         <v>9</v>
@@ -30341,7 +30341,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1039" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H1039" t="s">
         <v>9</v>
@@ -30367,7 +30367,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G1040" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H1040" t="s">
         <v>9</v>
@@ -30393,7 +30393,7 @@
         <v>13.5</v>
       </c>
       <c r="G1041" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H1041" t="s">
         <v>9</v>
@@ -30419,7 +30419,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1042" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H1042" t="s">
         <v>9</v>
@@ -30445,7 +30445,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G1043" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H1043" t="s">
         <v>9</v>
@@ -30471,7 +30471,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G1044" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H1044" t="s">
         <v>9</v>
@@ -30497,7 +30497,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G1045" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H1045" t="s">
         <v>9</v>
@@ -30523,7 +30523,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G1046" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H1046" t="s">
         <v>9</v>
@@ -30549,7 +30549,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1047" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H1047" t="s">
         <v>9</v>
@@ -30575,7 +30575,7 @@
         <v>13.8500003814697</v>
       </c>
       <c r="G1048" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H1048" t="s">
         <v>9</v>
@@ -30601,7 +30601,7 @@
         <v>13.75</v>
       </c>
       <c r="G1049" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H1049" t="s">
         <v>9</v>
@@ -30627,7 +30627,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1050" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H1050" t="s">
         <v>9</v>
@@ -30653,7 +30653,7 @@
         <v>13.75</v>
       </c>
       <c r="G1051" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H1051" t="s">
         <v>9</v>
@@ -30679,7 +30679,7 @@
         <v>13.8500003814697</v>
       </c>
       <c r="G1052" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H1052" t="s">
         <v>9</v>
@@ -30705,7 +30705,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G1053" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H1053" t="s">
         <v>9</v>
@@ -30731,7 +30731,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G1054" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H1054" t="s">
         <v>9</v>
@@ -30757,7 +30757,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1055" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H1055" t="s">
         <v>9</v>
@@ -30783,7 +30783,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1056" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H1056" t="s">
         <v>9</v>
@@ -30809,7 +30809,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1057" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H1057" t="s">
         <v>9</v>
@@ -30835,7 +30835,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1058" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H1058" t="s">
         <v>9</v>
@@ -30861,7 +30861,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G1059" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H1059" t="s">
         <v>9</v>
@@ -30887,7 +30887,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1060" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H1060" t="s">
         <v>9</v>
@@ -30913,7 +30913,7 @@
         <v>14.0500001907349</v>
       </c>
       <c r="G1061" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H1061" t="s">
         <v>9</v>
@@ -30939,7 +30939,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1062" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H1062" t="s">
         <v>9</v>
@@ -30965,7 +30965,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1063" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H1063" t="s">
         <v>9</v>
@@ -30991,7 +30991,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G1064" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H1064" t="s">
         <v>9</v>
@@ -31017,7 +31017,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1065" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="H1065" t="s">
         <v>9</v>
@@ -31043,7 +31043,7 @@
         <v>12</v>
       </c>
       <c r="G1066" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="H1066" t="s">
         <v>9</v>
@@ -31069,7 +31069,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1067" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="H1067" t="s">
         <v>9</v>
@@ -31095,7 +31095,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G1068" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="H1068" t="s">
         <v>9</v>
@@ -31121,7 +31121,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G1069" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H1069" t="s">
         <v>9</v>
@@ -31147,7 +31147,7 @@
         <v>10.75</v>
       </c>
       <c r="G1070" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H1070" t="s">
         <v>9</v>
@@ -31173,7 +31173,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1071" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="H1071" t="s">
         <v>9</v>
@@ -31199,7 +31199,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1072" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="H1072" t="s">
         <v>9</v>
@@ -31225,7 +31225,7 @@
         <v>11.75</v>
       </c>
       <c r="G1073" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H1073" t="s">
         <v>9</v>
@@ -31251,7 +31251,7 @@
         <v>11.25</v>
       </c>
       <c r="G1074" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H1074" t="s">
         <v>9</v>
@@ -31277,7 +31277,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1075" t="s">
-        <v>361</v>
+        <v>280</v>
       </c>
       <c r="H1075" t="s">
         <v>9</v>
@@ -31303,7 +31303,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G1076" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="H1076" t="s">
         <v>9</v>
@@ -31329,7 +31329,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1077" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="H1077" t="s">
         <v>9</v>
@@ -31355,7 +31355,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1078" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="H1078" t="s">
         <v>9</v>
@@ -31381,7 +31381,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G1079" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="H1079" t="s">
         <v>9</v>
@@ -31407,7 +31407,7 @@
         <v>11.75</v>
       </c>
       <c r="G1080" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H1080" t="s">
         <v>9</v>
@@ -31433,7 +31433,7 @@
         <v>11.75</v>
       </c>
       <c r="G1081" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H1081" t="s">
         <v>9</v>
@@ -31459,7 +31459,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G1082" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="H1082" t="s">
         <v>9</v>
@@ -31485,7 +31485,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1083" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H1083" t="s">
         <v>9</v>
@@ -31511,7 +31511,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G1084" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="H1084" t="s">
         <v>9</v>
@@ -31537,7 +31537,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1085" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H1085" t="s">
         <v>9</v>
@@ -31563,7 +31563,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G1086" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H1086" t="s">
         <v>9</v>
@@ -31589,7 +31589,7 @@
         <v>12</v>
       </c>
       <c r="G1087" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="H1087" t="s">
         <v>9</v>
@@ -31615,7 +31615,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1088" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="H1088" t="s">
         <v>9</v>
@@ -31641,7 +31641,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1089" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="H1089" t="s">
         <v>9</v>
@@ -31667,7 +31667,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1090" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="H1090" t="s">
         <v>9</v>
@@ -31693,7 +31693,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G1091" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="H1091" t="s">
         <v>9</v>
@@ -31719,7 +31719,7 @@
         <v>12</v>
       </c>
       <c r="G1092" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="H1092" t="s">
         <v>9</v>
@@ -31745,7 +31745,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1093" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H1093" t="s">
         <v>9</v>
@@ -31771,7 +31771,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1094" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H1094" t="s">
         <v>9</v>
@@ -31797,7 +31797,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1095" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="H1095" t="s">
         <v>9</v>
@@ -31823,7 +31823,7 @@
         <v>12.5</v>
       </c>
       <c r="G1096" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H1096" t="s">
         <v>9</v>
@@ -31849,7 +31849,7 @@
         <v>13.5</v>
       </c>
       <c r="G1097" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H1097" t="s">
         <v>9</v>
@@ -31875,7 +31875,7 @@
         <v>13.75</v>
       </c>
       <c r="G1098" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H1098" t="s">
         <v>9</v>
@@ -31927,7 +31927,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G1100" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H1100" t="s">
         <v>9</v>
@@ -31953,7 +31953,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G1101" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H1101" t="s">
         <v>9</v>
@@ -31979,7 +31979,7 @@
         <v>13.5</v>
       </c>
       <c r="G1102" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H1102" t="s">
         <v>9</v>
@@ -32005,7 +32005,7 @@
         <v>13.5</v>
       </c>
       <c r="G1103" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H1103" t="s">
         <v>9</v>
@@ -32031,7 +32031,7 @@
         <v>13.25</v>
       </c>
       <c r="G1104" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H1104" t="s">
         <v>9</v>
@@ -32057,7 +32057,7 @@
         <v>13.5</v>
       </c>
       <c r="G1105" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H1105" t="s">
         <v>9</v>
@@ -32083,7 +32083,7 @@
         <v>13.5</v>
       </c>
       <c r="G1106" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H1106" t="s">
         <v>9</v>
@@ -32109,7 +32109,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1107" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H1107" t="s">
         <v>9</v>
@@ -32135,7 +32135,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G1108" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H1108" t="s">
         <v>9</v>
@@ -32187,7 +32187,7 @@
         <v>13.75</v>
       </c>
       <c r="G1110" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H1110" t="s">
         <v>9</v>
@@ -32213,7 +32213,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G1111" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H1111" t="s">
         <v>9</v>
@@ -32239,7 +32239,7 @@
         <v>13.8500003814697</v>
       </c>
       <c r="G1112" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H1112" t="s">
         <v>9</v>
@@ -32265,7 +32265,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G1113" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H1113" t="s">
         <v>9</v>
@@ -32291,7 +32291,7 @@
         <v>13.8500003814697</v>
       </c>
       <c r="G1114" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H1114" t="s">
         <v>9</v>
@@ -70051,7 +70051,7 @@
     </row>
     <row r="2567">
       <c r="A2567" s="1" t="n">
-        <v>46059.6912731481</v>
+        <v>46059.3333333333</v>
       </c>
       <c r="B2567" t="n">
         <v>7551</v>
@@ -70072,6 +70072,32 @@
         <v>972</v>
       </c>
       <c r="H2567" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2568">
+      <c r="A2568" s="1" t="n">
+        <v>46062.6912962963</v>
+      </c>
+      <c r="B2568" t="n">
+        <v>23290</v>
+      </c>
+      <c r="C2568" t="n">
+        <v>20.8999996185303</v>
+      </c>
+      <c r="D2568" t="n">
+        <v>20.2999992370605</v>
+      </c>
+      <c r="E2568" t="n">
+        <v>20.6000003814697</v>
+      </c>
+      <c r="F2568" t="n">
+        <v>20.6000003814697</v>
+      </c>
+      <c r="G2568" t="s">
+        <v>972</v>
+      </c>
+      <c r="H2568" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IWB.MI.xlsx
+++ b/data/IWB.MI.xlsx
@@ -44,10 +44,10 @@
     <t xml:space="preserve">IWB.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79867458343506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83063650131226</t>
+    <t xml:space="preserve">7.79867267608643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83063507080078</t>
   </si>
   <si>
     <t xml:space="preserve">7.7427396774292</t>
@@ -56,118 +56,118 @@
     <t xml:space="preserve">7.75073099136353</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71077871322632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69479846954346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5909218788147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51101732254028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31125688552856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44709491729736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35120964050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29527568817139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26331329345703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29927110671997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29128074645996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27130556106567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24733352661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37517738342285</t>
+    <t xml:space="preserve">7.71077919006348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69479751586914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59092140197754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51101779937744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31125736236572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44709300994873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35120868682861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29527711868286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26331424713135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29927158355713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29127979278564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27130603790283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24733257293701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37517881393433</t>
   </si>
   <si>
     <t xml:space="preserve">7.43111324310303</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47106409072876</t>
+    <t xml:space="preserve">7.47106552124023</t>
   </si>
   <si>
     <t xml:space="preserve">7.15144729614258</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41513204574585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3272385597229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28728580474854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99163961410522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11149549484253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19139957427979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25532341003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41912698745728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42312288284302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6308741569519</t>
+    <t xml:space="preserve">7.41513347625732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32723903656006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28728437423706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99163913726807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.111496925354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19140005111694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25532388687134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41912794113159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42312240600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63087511062622</t>
   </si>
   <si>
     <t xml:space="preserve">7.67082691192627</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49903249740601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58293104171753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89455938339233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9864501953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9105396270752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54298114776611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82264471054077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6428599357605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62288284301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77470207214355</t>
+    <t xml:space="preserve">7.49903202056885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58293056488037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89455795288086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98644876480103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91053915023804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54297971725464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82264566421509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64285850524902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62288331985474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77470254898071</t>
   </si>
   <si>
     <t xml:space="preserve">7.76671171188354</t>
@@ -176,28 +176,28 @@
     <t xml:space="preserve">7.79068326950073</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87058734893799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9664740562439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71876811981201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66283559799194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57094621658325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55896043777466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39116096496582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46307611465454</t>
+    <t xml:space="preserve">7.87058591842651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96647310256958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71876907348633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66283655166626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57094717025757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55895948410034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39116048812866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46307516098022</t>
   </si>
   <si>
     <t xml:space="preserve">7.60690355300903</t>
@@ -206,76 +206,76 @@
     <t xml:space="preserve">7.54697513580322</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36719036102295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31525278091431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33123350143433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34721374511719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50302648544312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24333715438843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22336149215698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23934364318848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45907974243164</t>
+    <t xml:space="preserve">7.36718988418579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31525087356567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33123254776001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34721422195435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50302696228027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24333572387695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22336101531982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23934316635132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45907926559448</t>
   </si>
   <si>
     <t xml:space="preserve">7.46707057952881</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10350513458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89974975585938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91173315048218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9516863822937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00761985778809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8717827796936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87577676773071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87977361679077</t>
+    <t xml:space="preserve">7.10350656509399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89974784851074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91173362731934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95168685913086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00762033462524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87178230285645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87577629089355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87977313995361</t>
   </si>
   <si>
     <t xml:space="preserve">6.8677864074707</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75192499160767</t>
+    <t xml:space="preserve">6.75192594528198</t>
   </si>
   <si>
     <t xml:space="preserve">6.74393463134766</t>
   </si>
   <si>
-    <t xml:space="preserve">6.82383966445923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66403150558472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83183097839355</t>
+    <t xml:space="preserve">6.82384061813354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66403198242188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83182954788208</t>
   </si>
   <si>
     <t xml:space="preserve">6.89575338363647</t>
@@ -284,112 +284,112 @@
     <t xml:space="preserve">7.03159141540527</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07154369354248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33522748947144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25931978225708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17941474914551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26730966567993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23135280609131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09551477432251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18340921401978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18740463256836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20738124847412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14345693588257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12348127365112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23534774780273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7467360496521</t>
+    <t xml:space="preserve">7.07154273986816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33522844314575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25931930541992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17941427230835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26730871200562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23135232925415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09551525115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18340969085693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18740320205688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2073802947998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14345598220825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12348079681396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23534822463989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74673700332642</t>
   </si>
   <si>
     <t xml:space="preserve">7.83463144302368</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98245429992676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92652177810669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78269195556641</t>
+    <t xml:space="preserve">7.98245525360107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92652130126953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78269243240356</t>
   </si>
   <si>
     <t xml:space="preserve">7.63886594772339</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73475122451782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07034873962402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21417617797852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16623401641846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18221282958984</t>
+    <t xml:space="preserve">7.73474884033203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07035064697266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21417808532715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16623497009277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18221378326416</t>
   </si>
   <si>
     <t xml:space="preserve">8.27011108398438</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57374668121338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54977512359619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35001182556152</t>
+    <t xml:space="preserve">8.57374572753906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54977607727051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35001468658447</t>
   </si>
   <si>
     <t xml:space="preserve">8.46987152099609</t>
   </si>
   <si>
-    <t xml:space="preserve">8.525803565979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50982284545898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59771728515625</t>
+    <t xml:space="preserve">8.52580547332764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50982475280762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59771919250488</t>
   </si>
   <si>
     <t xml:space="preserve">8.60570812225342</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58173656463623</t>
+    <t xml:space="preserve">8.58173751831055</t>
   </si>
   <si>
     <t xml:space="preserve">8.64687347412109</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67129898071289</t>
+    <t xml:space="preserve">8.67130184173584</t>
   </si>
   <si>
     <t xml:space="preserve">8.61430549621582</t>
@@ -404,70 +404,70 @@
     <t xml:space="preserve">8.82599830627441</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87485218048096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95627212524414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74457740783691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85856914520264</t>
+    <t xml:space="preserve">8.87485122680664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95627117156982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74457931518555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.858567237854</t>
   </si>
   <si>
     <t xml:space="preserve">8.84228229522705</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91556262969971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03769207000732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00512599945068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94813060760498</t>
+    <t xml:space="preserve">8.91556358337402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03769302368164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00512504577637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94812870025635</t>
   </si>
   <si>
     <t xml:space="preserve">8.99698162078857</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1272554397583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19239044189453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11911296844482</t>
+    <t xml:space="preserve">9.12725639343262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19239234924316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11911201477051</t>
   </si>
   <si>
     <t xml:space="preserve">9.14354133605957</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98069763183594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13539886474609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16796779632568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15982437133789</t>
+    <t xml:space="preserve">8.98069858551025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13539791107178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16796588897705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15982341766357</t>
   </si>
   <si>
     <t xml:space="preserve">9.18424987792969</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15168190002441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07026386260986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96441268920898</t>
+    <t xml:space="preserve">9.1516809463501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07026195526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9644136428833</t>
   </si>
   <si>
     <t xml:space="preserve">8.92370414733887</t>
@@ -488,19 +488,19 @@
     <t xml:space="preserve">8.89113616943359</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11097145080566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20053386688232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28195476531982</t>
+    <t xml:space="preserve">9.11097049713135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20053482055664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28195381164551</t>
   </si>
   <si>
     <t xml:space="preserve">9.35523414611816</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39594554901123</t>
+    <t xml:space="preserve">9.39594459533691</t>
   </si>
   <si>
     <t xml:space="preserve">9.32266521453857</t>
@@ -509,25 +509,25 @@
     <t xml:space="preserve">9.64834785461426</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60763931274414</t>
+    <t xml:space="preserve">9.60763835906982</t>
   </si>
   <si>
     <t xml:space="preserve">9.9007511138916</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99031448364258</t>
+    <t xml:space="preserve">9.99031543731689</t>
   </si>
   <si>
     <t xml:space="preserve">10.120587348938</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1368713378906</t>
+    <t xml:space="preserve">10.136869430542</t>
   </si>
   <si>
     <t xml:space="preserve">10.1775827407837</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1043043136597</t>
+    <t xml:space="preserve">10.1043033599854</t>
   </si>
   <si>
     <t xml:space="preserve">10.1531562805176</t>
@@ -536,49 +536,49 @@
     <t xml:space="preserve">10.0961618423462</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94146251678467</t>
+    <t xml:space="preserve">9.94146347045898</t>
   </si>
   <si>
     <t xml:space="preserve">9.90889453887939</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77048015594482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83561420440674</t>
+    <t xml:space="preserve">9.77047920227051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83561515808105</t>
   </si>
   <si>
     <t xml:space="preserve">9.91703605651855</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79490566253662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77861976623535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78676223754883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9577465057373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.014741897583</t>
+    <t xml:space="preserve">9.7949047088623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7786226272583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78676319122314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95774555206299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0147399902344</t>
   </si>
   <si>
     <t xml:space="preserve">9.99845600128174</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8844690322876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86004161834717</t>
+    <t xml:space="preserve">9.88446807861328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86003971099854</t>
   </si>
   <si>
     <t xml:space="preserve">9.85190010070801</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89260959625244</t>
+    <t xml:space="preserve">9.89261150360107</t>
   </si>
   <si>
     <t xml:space="preserve">10.2590026855469</t>
@@ -587,34 +587,34 @@
     <t xml:space="preserve">10.3404235839844</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4625558853149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5276918411255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5765428543091</t>
+    <t xml:space="preserve">10.4625539779663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5276908874512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5765419006348</t>
   </si>
   <si>
     <t xml:space="preserve">10.5439748764038</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5358333587646</t>
+    <t xml:space="preserve">10.5358324050903</t>
   </si>
   <si>
     <t xml:space="preserve">10.5032644271851</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5521183013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3485651016235</t>
+    <t xml:space="preserve">10.5521173477173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3485670089722</t>
   </si>
   <si>
     <t xml:space="preserve">10.4381275177002</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3241395950317</t>
+    <t xml:space="preserve">10.3241386413574</t>
   </si>
   <si>
     <t xml:space="preserve">10.3811340332031</t>
@@ -623,10 +623,10 @@
     <t xml:space="preserve">10.3648490905762</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4218444824219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4137010574341</t>
+    <t xml:space="preserve">10.4218435287476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4137020111084</t>
   </si>
   <si>
     <t xml:space="preserve">10.3729915618896</t>
@@ -635,49 +635,49 @@
     <t xml:space="preserve">10.3892765045166</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2915706634521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2671461105347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2264347076416</t>
+    <t xml:space="preserve">10.2915716171265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2671451568604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2264356613159</t>
   </si>
   <si>
     <t xml:space="preserve">10.1938667297363</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3159980773926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2182922363281</t>
+    <t xml:space="preserve">10.3159971237183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2182941436768</t>
   </si>
   <si>
     <t xml:space="preserve">10.283429145813</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4299869537354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3322820663452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2427186965942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5846862792969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6661062240601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7068157196045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7475290298462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.788236618042</t>
+    <t xml:space="preserve">10.429986000061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3322811126709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2427177429199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5846843719482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6661071777344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7068166732788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7475271224976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7882375717163</t>
   </si>
   <si>
     <t xml:space="preserve">10.6253957748413</t>
@@ -686,13 +686,13 @@
     <t xml:space="preserve">10.8696584701538</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8289480209351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0325002670288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2360515594482</t>
+    <t xml:space="preserve">10.8289499282837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0324983596802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2360525131226</t>
   </si>
   <si>
     <t xml:space="preserve">11.4396018981934</t>
@@ -701,424 +701,424 @@
     <t xml:space="preserve">11.6838645935059</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0732088088989</t>
+    <t xml:space="preserve">11.0732107162476</t>
   </si>
   <si>
     <t xml:space="preserve">10.9917898178101</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1546287536621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3174715042114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.276762008667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1953420639038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3581829071045</t>
+    <t xml:space="preserve">11.1546297073364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3174705505371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2767610549927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1953392028809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3581819534302</t>
   </si>
   <si>
     <t xml:space="preserve">11.4839172363281</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5258312225342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5677423477173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4000930786133</t>
+    <t xml:space="preserve">11.5258293151855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5677442550659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4000949859619</t>
   </si>
   <si>
     <t xml:space="preserve">11.0228843688965</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1486215591431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2324447631836</t>
+    <t xml:space="preserve">11.1486225128174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2324457168579</t>
   </si>
   <si>
     <t xml:space="preserve">11.1905336380005</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2743558883667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8971490859985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0647993087769</t>
+    <t xml:space="preserve">11.2743577957153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8971471786499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0647974014282</t>
   </si>
   <si>
     <t xml:space="preserve">11.4420051574707</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8552350997925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6875886917114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3254737854004</t>
+    <t xml:space="preserve">10.8552370071411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6875877380371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3254747390747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.282247543335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1957931518555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2390184402466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1525659561157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.936429977417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0661125183105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1093378067017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9796581268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7635221481323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.590615272522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8499774932861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7202959060669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6770687103271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8067502975464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8932046890259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6338415145874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4119281768799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4551563262939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3687009811401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5416088104248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6280632019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5848369598389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4609346389771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3312520980835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3744812011719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2880258560181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5041618347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0286655426025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94221115112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59639453887939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63961982727051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81252861022949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85575485229492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55316543579102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03444385528564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81830883026123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86153507232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77507972717285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07766914367676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16412544250488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25057888031006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33703231811523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29380512237549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2447996139526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68284606933594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1583452224731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98543643951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89898204803467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76930236816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72607421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46671390533447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50993919372559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38025951385498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42348575592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.207350730896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0718908309937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2972898483276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2077465057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1629762649536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3420600891113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.431601524353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3868322372437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1182069778442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2525186538696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.476372718811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6554546356201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7897691726685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7449970245361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5659141540527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7002258300781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1031646728516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9688510894775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9240808486938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8793096542358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1479339599609</t>
   </si>
   <si>
     <t xml:space="preserve">11.2822484970093</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1957931518555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0228853225708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2390213012695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1525650024414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9364318847656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0661125183105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.109338760376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9796590805054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7635231018066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5906143188477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8499774932861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7202949523926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6770696640015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8067502975464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8932046890259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.633843421936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4119291305542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4551544189453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3687009811401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5416097640991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6280641555786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5848350524902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4609346389771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3312540054321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3744802474976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2880258560181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5041608810425</t>
+    <t xml:space="preserve">11.2374773025513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4613304138184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3270177841187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1927061080933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3717889785767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4165620803833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0583934783936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6404142379761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7299556732178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6851854324341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7747240066528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8194961547852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8642683029175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5508728027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5956449508667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5211429595947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0136222839355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8345394134521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9985809326172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0881214141846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0433511734009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1328926086426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2224349975586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1776647567749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3567485809326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.267204284668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.401517868042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3119764328003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6701431274414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6253728866577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5806016921997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6106843948364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6257266998291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0734357833862</t>
   </si>
   <si>
     <t xml:space="preserve">10.0286636352539</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94221019744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59639263153076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63962078094482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81252861022949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85575675964355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55316734313965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0344409942627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81830787658691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86153602600098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77508068084717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07767105102539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16412353515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25057697296143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33703327178955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29380512237549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.244800567627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68284702301025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1583452224731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98543834686279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89898300170898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76930236816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72607421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46671199798584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5099401473999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38025951385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42348575592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20735168457031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.071891784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2972898483276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2077474594116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1629772186279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3420600891113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4316024780273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3868322372437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1182060241699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2525177001953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4763717651367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6554546356201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7897682189941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7449989318848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5659151077271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7002267837524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1031637191772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9688501358032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9240798950195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8793106079102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1479349136353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.237476348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4613313674927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.327018737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1927061080933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3717889785767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4165601730347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0583944320679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6404151916504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7299566268921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6851844787598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7747268676758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8194980621338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8642673492432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5508708953857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5956430435181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.521143913269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0136232376099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8345403671265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9985790252686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0881223678589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0433511734009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1328935623169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2224340438843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1776647567749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3567476272583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.267204284668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4015188217163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3119764328003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6701431274414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.625373840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5805997848511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6106863021851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62572574615479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0734348297119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0286626815796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.491060256958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9090394973755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1626205444336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6998720169067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8789548873901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0132675170898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1475791931152</t>
+    <t xml:space="preserve">12.4910593032837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9090385437012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1626224517822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6998729705811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8789539337158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0132665634155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1475801467896</t>
   </si>
   <si>
     <t xml:space="preserve">14.2371206283569</t>
@@ -1127,49 +1127,46 @@
     <t xml:space="preserve">14.1923503875732</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9237251281738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9684982299805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7894115447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2818918228149</t>
+    <t xml:space="preserve">13.9237270355225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9684963226318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7894134521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2818927764893</t>
   </si>
   <si>
     <t xml:space="preserve">13.8341836929321</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5207901000977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4312477111816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.565559387207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6103286743164</t>
+    <t xml:space="preserve">13.5207891464233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.431245803833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5655584335327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.610330581665</t>
   </si>
   <si>
     <t xml:space="preserve">13.7004642486572</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7906017303467</t>
+    <t xml:space="preserve">13.7905988693237</t>
   </si>
   <si>
     <t xml:space="preserve">13.8356666564941</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6553964614868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5201950073242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6103296279907</t>
+    <t xml:space="preserve">13.6553974151611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5201940536499</t>
   </si>
   <si>
     <t xml:space="preserve">13.2948579788208</t>
@@ -1184,10 +1181,10 @@
     <t xml:space="preserve">12.9793863296509</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7089834213257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5737810134888</t>
+    <t xml:space="preserve">12.7089824676514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5737829208374</t>
   </si>
   <si>
     <t xml:space="preserve">12.6188488006592</t>
@@ -1202,31 +1199,31 @@
     <t xml:space="preserve">13.4751272201538</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9343214035034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7540502548218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8441867828369</t>
+    <t xml:space="preserve">12.9343204498291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7540512084961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8441858291626</t>
   </si>
   <si>
     <t xml:space="preserve">14.0610036849976</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8807334899902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1962041854858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3314075469971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4215402603149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3764734268188</t>
+    <t xml:space="preserve">13.8807344436646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1962051391602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3314056396484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4215421676636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3764753341675</t>
   </si>
   <si>
     <t xml:space="preserve">14.5116767883301</t>
@@ -1238,10 +1235,10 @@
     <t xml:space="preserve">14.6018114089966</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6919450759888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8722143173218</t>
+    <t xml:space="preserve">14.6919441223145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8722152709961</t>
   </si>
   <si>
     <t xml:space="preserve">15.2327537536621</t>
@@ -1250,61 +1247,61 @@
     <t xml:space="preserve">15.0074167251587</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3228874206543</t>
+    <t xml:space="preserve">15.32288646698</t>
   </si>
   <si>
     <t xml:space="preserve">15.1876859664917</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2242336273193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9538307189941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8551769256592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3143672943115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9903793334961</t>
+    <t xml:space="preserve">16.224235534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9538297653198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8551788330078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3143692016602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9903812408447</t>
   </si>
   <si>
     <t xml:space="preserve">16.8101100921631</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7565250396729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0269260406494</t>
+    <t xml:space="preserve">17.7565231323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.026927947998</t>
   </si>
   <si>
     <t xml:space="preserve">17.9367923736572</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3509159088135</t>
+    <t xml:space="preserve">17.3509197235107</t>
   </si>
   <si>
     <t xml:space="preserve">17.4410514831543</t>
   </si>
   <si>
-    <t xml:space="preserve">17.486120223999</t>
+    <t xml:space="preserve">17.4861164093018</t>
   </si>
   <si>
     <t xml:space="preserve">17.0354461669922</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6298427581787</t>
+    <t xml:space="preserve">16.6298389434814</t>
   </si>
   <si>
     <t xml:space="preserve">16.7199745178223</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4045066833496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6749076843262</t>
+    <t xml:space="preserve">16.404504776001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6749057769775</t>
   </si>
   <si>
     <t xml:space="preserve">16.9453086853027</t>
@@ -1313,16 +1310,16 @@
     <t xml:space="preserve">16.7650413513184</t>
   </si>
   <si>
-    <t xml:space="preserve">15.863697052002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9988946914673</t>
+    <t xml:space="preserve">15.8636960983276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9988994598389</t>
   </si>
   <si>
     <t xml:space="preserve">16.4946384429932</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3594341278076</t>
+    <t xml:space="preserve">16.3594360351562</t>
   </si>
   <si>
     <t xml:space="preserve">16.1791667938232</t>
@@ -1331,25 +1328,25 @@
     <t xml:space="preserve">16.584774017334</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5397033691406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6834268569946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0890350341797</t>
+    <t xml:space="preserve">16.5397052764893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6834259033203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0890312194824</t>
   </si>
   <si>
     <t xml:space="preserve">15.5932912826538</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2693004608154</t>
+    <t xml:space="preserve">16.2693023681641</t>
   </si>
   <si>
     <t xml:space="preserve">17.1255798339844</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5762538909912</t>
+    <t xml:space="preserve">17.5762557983398</t>
   </si>
   <si>
     <t xml:space="preserve">17.666389465332</t>
@@ -1361,7 +1358,7 @@
     <t xml:space="preserve">18.5677356719971</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3874645233154</t>
+    <t xml:space="preserve">18.3874664306641</t>
   </si>
   <si>
     <t xml:space="preserve">18.7480030059814</t>
@@ -1373,70 +1370,73 @@
     <t xml:space="preserve">20.0098876953125</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5506954193115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4605617523193</t>
+    <t xml:space="preserve">20.5506973266602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4605598449707</t>
   </si>
   <si>
     <t xml:space="preserve">20.280294418335</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3704261779785</t>
+    <t xml:space="preserve">20.3704280853271</t>
   </si>
   <si>
     <t xml:space="preserve">20.1000232696533</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6408309936523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7309646606445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4435234069824</t>
+    <t xml:space="preserve">20.640832901001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7309665679932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4435195922852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9027156829834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5361423492432</t>
   </si>
   <si>
     <t xml:space="preserve">21.9027137756348</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5361442565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1695728302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7194328308105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3609313964844</t>
+    <t xml:space="preserve">21.1695690155029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7194309234619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.360933303833</t>
   </si>
   <si>
     <t xml:space="preserve">22.4525737762451</t>
   </si>
   <si>
-    <t xml:space="preserve">22.269287109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0860004425049</t>
+    <t xml:space="preserve">22.2692909240723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0860023498535</t>
   </si>
   <si>
     <t xml:space="preserve">21.9943599700928</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6277866363525</t>
+    <t xml:space="preserve">21.6277885437012</t>
   </si>
   <si>
     <t xml:space="preserve">23.2773628234863</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9107913970947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7275047302246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1776485443115</t>
+    <t xml:space="preserve">22.9107933044434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.727502822876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1776466369629</t>
   </si>
   <si>
     <t xml:space="preserve">22.6358604431152</t>
@@ -1445,67 +1445,67 @@
     <t xml:space="preserve">23.0024356842041</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0940780639648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1021518707275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.285436630249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9269409179688</t>
+    <t xml:space="preserve">23.0940761566162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1021499633789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2854404449463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9269428253174</t>
   </si>
   <si>
     <t xml:space="preserve">26.2099456787109</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8514461517334</t>
+    <t xml:space="preserve">26.851448059082</t>
   </si>
   <si>
     <t xml:space="preserve">26.6681613922119</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3096618652344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4848747253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7598037719727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5765190124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3015899658203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5684413909912</t>
+    <t xml:space="preserve">27.309663772583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4848728179932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7598056793213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5765171051025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.301586151123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5684432983398</t>
   </si>
   <si>
     <t xml:space="preserve">27.0347328186035</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1425266265869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4093818664551</t>
+    <t xml:space="preserve">29.1425247192383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4093799591064</t>
   </si>
   <si>
     <t xml:space="preserve">28.1344509124756</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2260932922363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3646850585938</t>
+    <t xml:space="preserve">28.226095199585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3646869659424</t>
   </si>
   <si>
     <t xml:space="preserve">28.4570770263672</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0875053405762</t>
+    <t xml:space="preserve">28.0875072479248</t>
   </si>
   <si>
     <t xml:space="preserve">27.9951114654541</t>
@@ -1517,19 +1517,19 @@
     <t xml:space="preserve">27.7179317474365</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1038284301758</t>
+    <t xml:space="preserve">29.1038303375244</t>
   </si>
   <si>
     <t xml:space="preserve">29.9353694915771</t>
   </si>
   <si>
-    <t xml:space="preserve">29.750581741333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.381010055542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8266525268555</t>
+    <t xml:space="preserve">29.7505836486816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3810062408447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8266506195068</t>
   </si>
   <si>
     <t xml:space="preserve">28.9190425872803</t>
@@ -1538,46 +1538,46 @@
     <t xml:space="preserve">28.7342548370361</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0114364624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8429737091064</t>
+    <t xml:space="preserve">29.0114345550537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8429756164551</t>
   </si>
   <si>
     <t xml:space="preserve">30.1201515197754</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2125473022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0277614593506</t>
+    <t xml:space="preserve">30.2125453948975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.027759552002</t>
   </si>
   <si>
     <t xml:space="preserve">30.3973350524902</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1364765167236</t>
+    <t xml:space="preserve">31.1364784240723</t>
   </si>
   <si>
     <t xml:space="preserve">30.8592987060547</t>
   </si>
   <si>
-    <t xml:space="preserve">31.0440826416016</t>
+    <t xml:space="preserve">31.0440845489502</t>
   </si>
   <si>
     <t xml:space="preserve">30.6745128631592</t>
   </si>
   <si>
-    <t xml:space="preserve">30.489725112915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2886161804199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4734001159668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.8919448852539</t>
+    <t xml:space="preserve">30.4897270202637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2886142730713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4734020233154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.8919486999512</t>
   </si>
   <si>
     <t xml:space="preserve">33.3539085388184</t>
@@ -1586,7 +1586,7 @@
     <t xml:space="preserve">34.5550231933594</t>
   </si>
   <si>
-    <t xml:space="preserve">34.0930633544922</t>
+    <t xml:space="preserve">34.0930595397949</t>
   </si>
   <si>
     <t xml:space="preserve">35.8485260009766</t>
@@ -1595,7 +1595,7 @@
     <t xml:space="preserve">37.4192085266113</t>
   </si>
   <si>
-    <t xml:space="preserve">40.0986137390137</t>
+    <t xml:space="preserve">40.0986099243164</t>
   </si>
   <si>
     <t xml:space="preserve">37.2344245910645</t>
@@ -1610,7 +1610,7 @@
     <t xml:space="preserve">37.6039962768555</t>
   </si>
   <si>
-    <t xml:space="preserve">37.6963844299316</t>
+    <t xml:space="preserve">37.6963882446289</t>
   </si>
   <si>
     <t xml:space="preserve">37.7887840270996</t>
@@ -1622,34 +1622,34 @@
     <t xml:space="preserve">38.5279273986816</t>
   </si>
   <si>
-    <t xml:space="preserve">38.3431434631348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.4952774047852</t>
+    <t xml:space="preserve">38.3431396484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.4952735900879</t>
   </si>
   <si>
     <t xml:space="preserve">35.9409217834473</t>
   </si>
   <si>
-    <t xml:space="preserve">36.402889251709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.6800651550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.9735717773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.0659637451172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.4355316162109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.805103302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.3594665527344</t>
+    <t xml:space="preserve">36.4028854370117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.6800689697266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.9735679626465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.0659561157227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.4355354309082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.8051071166992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.3594627380371</t>
   </si>
   <si>
     <t xml:space="preserve">39.8214263916016</t>
@@ -1658,58 +1658,58 @@
     <t xml:space="preserve">40.006217956543</t>
   </si>
   <si>
-    <t xml:space="preserve">40.5605735778809</t>
+    <t xml:space="preserve">40.5605773925781</t>
   </si>
   <si>
     <t xml:space="preserve">40.6529655456543</t>
   </si>
   <si>
-    <t xml:space="preserve">41.9464721679688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.1149368286133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.9301490783691</t>
+    <t xml:space="preserve">41.946475982666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.114933013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.9301452636719</t>
   </si>
   <si>
     <t xml:space="preserve">42.3160438537598</t>
   </si>
   <si>
-    <t xml:space="preserve">43.5171508789062</t>
+    <t xml:space="preserve">43.5171546936035</t>
   </si>
   <si>
     <t xml:space="preserve">44.0715103149414</t>
   </si>
   <si>
-    <t xml:space="preserve">43.8867263793945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.7019386291504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.979118347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.3486938476562</t>
+    <t xml:space="preserve">43.8867225646973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.7019424438477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.9791145324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.3486976623535</t>
   </si>
   <si>
     <t xml:space="preserve">44.9954452514648</t>
   </si>
   <si>
-    <t xml:space="preserve">44.810661315918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.5334739685059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.7943382263184</t>
+    <t xml:space="preserve">44.8106575012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.5334815979004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.7943344116211</t>
   </si>
   <si>
     <t xml:space="preserve">43.1475830078125</t>
   </si>
   <si>
-    <t xml:space="preserve">41.3921089172363</t>
+    <t xml:space="preserve">41.3921127319336</t>
   </si>
   <si>
     <t xml:space="preserve">41.8540802001953</t>
@@ -1718,19 +1718,19 @@
     <t xml:space="preserve">41.5769004821777</t>
   </si>
   <si>
-    <t xml:space="preserve">41.2073249816895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.1910018920898</t>
+    <t xml:space="preserve">41.2073287963867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.1910057067871</t>
   </si>
   <si>
     <t xml:space="preserve">39.4518585205078</t>
   </si>
   <si>
-    <t xml:space="preserve">38.9898910522461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.1746826171875</t>
+    <t xml:space="preserve">38.9898948669434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.1746788024902</t>
   </si>
   <si>
     <t xml:space="preserve">39.5442504882812</t>
@@ -1745,25 +1745,25 @@
     <t xml:space="preserve">39.7290344238281</t>
   </si>
   <si>
-    <t xml:space="preserve">39.9138298034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.4681816101074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.6366424560547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.6203155517578</t>
+    <t xml:space="preserve">39.9138221740723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.4681777954102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.6366500854492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.6203193664551</t>
   </si>
   <si>
     <t xml:space="preserve">39.2670707702637</t>
   </si>
   <si>
-    <t xml:space="preserve">37.3268203735352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.8974990844727</t>
+    <t xml:space="preserve">37.3268165588379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.8974952697754</t>
   </si>
   <si>
     <t xml:space="preserve">37.5115966796875</t>
@@ -1784,22 +1784,22 @@
     <t xml:space="preserve">36.2181015014648</t>
   </si>
   <si>
-    <t xml:space="preserve">35.3865585327148</t>
+    <t xml:space="preserve">35.3865623474121</t>
   </si>
   <si>
     <t xml:space="preserve">36.0333137512207</t>
   </si>
   <si>
-    <t xml:space="preserve">34.1854515075684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.7234840393066</t>
+    <t xml:space="preserve">34.1854476928711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.7234878540039</t>
   </si>
   <si>
     <t xml:space="preserve">33.1691246032715</t>
   </si>
   <si>
-    <t xml:space="preserve">32.6147651672363</t>
+    <t xml:space="preserve">32.6147689819336</t>
   </si>
   <si>
     <t xml:space="preserve">33.6310958862305</t>
@@ -1808,52 +1808,52 @@
     <t xml:space="preserve">32.707160949707</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9680156707764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0604133605957</t>
+    <t xml:space="preserve">31.9680118560791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0604095458984</t>
   </si>
   <si>
     <t xml:space="preserve">31.4136562347412</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6908359527588</t>
+    <t xml:space="preserve">31.6908340454102</t>
   </si>
   <si>
     <t xml:space="preserve">32.2451972961426</t>
   </si>
   <si>
-    <t xml:space="preserve">32.7995491027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9082679748535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.1093826293945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.739803314209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.0169906616211</t>
+    <t xml:space="preserve">32.7995529174805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.908275604248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.1093788146973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7398071289062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.0169868469238</t>
   </si>
   <si>
     <t xml:space="preserve">32.337589263916</t>
   </si>
   <si>
-    <t xml:space="preserve">32.4299812316895</t>
+    <t xml:space="preserve">32.4299774169922</t>
   </si>
   <si>
     <t xml:space="preserve">32.5223770141602</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5060501098633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3212661743164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5522499084473</t>
+    <t xml:space="preserve">31.5060482025146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.321268081665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5522480010986</t>
   </si>
   <si>
     <t xml:space="preserve">31.921817779541</t>
@@ -1862,43 +1862,43 @@
     <t xml:space="preserve">32.1528015136719</t>
   </si>
   <si>
-    <t xml:space="preserve">33.4925003051758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.3702354431152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8620758056641</t>
+    <t xml:space="preserve">33.492504119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.3702392578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8620719909668</t>
   </si>
   <si>
     <t xml:space="preserve">32.1066017150879</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5359230041504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3511333465576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7804527282715</t>
+    <t xml:space="preserve">30.5359210968018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3511371612549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7804546356201</t>
   </si>
   <si>
     <t xml:space="preserve">28.3643836975098</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3180351257324</t>
+    <t xml:space="preserve">28.3180332183838</t>
   </si>
   <si>
     <t xml:space="preserve">27.8082180023193</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7618713378906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0862998962402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9936084747314</t>
+    <t xml:space="preserve">27.7618732452393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0862979888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9936065673828</t>
   </si>
   <si>
     <t xml:space="preserve">28.642463684082</t>
@@ -1907,13 +1907,13 @@
     <t xml:space="preserve">29.5230579376221</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1255722045898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5694046020508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.105936050415</t>
+    <t xml:space="preserve">30.1255683898926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5694065093994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1059341430664</t>
   </si>
   <si>
     <t xml:space="preserve">27.9009132385254</t>
@@ -1922,19 +1922,19 @@
     <t xml:space="preserve">27.7155227661133</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1130123138428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4641551971436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4178085327148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.186071395874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6031970977783</t>
+    <t xml:space="preserve">27.1130142211914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4641532897949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4178066253662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1860733032227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6031951904297</t>
   </si>
   <si>
     <t xml:space="preserve">26.2324199676514</t>
@@ -1946,19 +1946,19 @@
     <t xml:space="preserve">26.3251132965088</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8152980804443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6299076080322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2591304779053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7029685974121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6566200256348</t>
+    <t xml:space="preserve">25.8152961730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6299057006836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2591323852539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7029666900635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6566219329834</t>
   </si>
   <si>
     <t xml:space="preserve">23.9614143371582</t>
@@ -1967,7 +1967,7 @@
     <t xml:space="preserve">23.729679107666</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0273971557617</t>
+    <t xml:space="preserve">25.0273952484131</t>
   </si>
   <si>
     <t xml:space="preserve">24.7956619262695</t>
@@ -1976,28 +1976,28 @@
     <t xml:space="preserve">24.2858448028564</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6102733612061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3321914672852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.517578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3785381317139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4712333679199</t>
+    <t xml:space="preserve">24.6102714538574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3321933746338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5175800323486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3785362243652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4712314605713</t>
   </si>
   <si>
     <t xml:space="preserve">23.8687210083008</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5442905426025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.100456237793</t>
+    <t xml:space="preserve">23.5442924499512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1004543304443</t>
   </si>
   <si>
     <t xml:space="preserve">23.4979457855225</t>
@@ -2006,16 +2006,16 @@
     <t xml:space="preserve">23.8223743438721</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9150676727295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1931495666504</t>
+    <t xml:space="preserve">23.9150657653809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.193151473999</t>
   </si>
   <si>
     <t xml:space="preserve">24.888355255127</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5835609436035</t>
+    <t xml:space="preserve">25.5835628509521</t>
   </si>
   <si>
     <t xml:space="preserve">25.9543361663818</t>
@@ -2024,31 +2024,31 @@
     <t xml:space="preserve">26.6958885192871</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7885837554932</t>
+    <t xml:space="preserve">26.7885818481445</t>
   </si>
   <si>
     <t xml:space="preserve">26.7422370910645</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4445209503174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.981050491333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8616428375244</t>
+    <t xml:space="preserve">25.444522857666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9810485839844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.861644744873</t>
   </si>
   <si>
     <t xml:space="preserve">25.1200923919678</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0077610015869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4515972137451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1271686553955</t>
+    <t xml:space="preserve">24.0077629089355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4515953063965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1271705627441</t>
   </si>
   <si>
     <t xml:space="preserve">23.0808200836182</t>
@@ -2069,19 +2069,19 @@
     <t xml:space="preserve">23.2662105560303</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3589057922363</t>
+    <t xml:space="preserve">23.3589038848877</t>
   </si>
   <si>
     <t xml:space="preserve">22.8027381896973</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6173534393311</t>
+    <t xml:space="preserve">22.6173496246338</t>
   </si>
   <si>
     <t xml:space="preserve">23.1735153198242</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8954334259033</t>
+    <t xml:space="preserve">22.895435333252</t>
   </si>
   <si>
     <t xml:space="preserve">21.9684925079346</t>
@@ -2093,7 +2093,7 @@
     <t xml:space="preserve">21.2732887268066</t>
   </si>
   <si>
-    <t xml:space="preserve">20.856164932251</t>
+    <t xml:space="preserve">20.8561630249023</t>
   </si>
   <si>
     <t xml:space="preserve">20.7171230316162</t>
@@ -2105,40 +2105,40 @@
     <t xml:space="preserve">20.1609592437744</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2073020935059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8365287780762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5584468841553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.604793548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9292240142822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.068265914917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1146125793457</t>
+    <t xml:space="preserve">20.2073059082031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8365306854248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5584487915039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6047916412354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9292221069336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0682621002197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1146106719971</t>
   </si>
   <si>
     <t xml:space="preserve">20.8098182678223</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9952030181885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5780811309814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0878982543945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5977172851562</t>
+    <t xml:space="preserve">20.9952049255371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5780830383301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0879001617432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5977153778076</t>
   </si>
   <si>
     <t xml:space="preserve">22.061185836792</t>
@@ -2147,13 +2147,13 @@
     <t xml:space="preserve">22.4319629669189</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3856143951416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3392677307129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6833324432373</t>
+    <t xml:space="preserve">22.3856163024902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3392696380615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6833343505859</t>
   </si>
   <si>
     <t xml:space="preserve">24.5639266967773</t>
@@ -2162,40 +2162,40 @@
     <t xml:space="preserve">24.4248847961426</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1664390563965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2127838134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.842004776001</t>
+    <t xml:space="preserve">25.1664352416992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2127857208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8420066833496</t>
   </si>
   <si>
     <t xml:space="preserve">25.7689476013184</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7226009368896</t>
+    <t xml:space="preserve">25.7226028442383</t>
   </si>
   <si>
     <t xml:space="preserve">25.3518257141113</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5372142791748</t>
+    <t xml:space="preserve">25.5372123718262</t>
   </si>
   <si>
     <t xml:space="preserve">25.305477142334</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6762542724609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4908695220947</t>
+    <t xml:space="preserve">25.6762561798096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4908657073975</t>
   </si>
   <si>
     <t xml:space="preserve">27.6691799163818</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2057075500488</t>
+    <t xml:space="preserve">27.2057056427002</t>
   </si>
   <si>
     <t xml:space="preserve">27.4837894439697</t>
@@ -2204,13 +2204,13 @@
     <t xml:space="preserve">27.2984027862549</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5764846801758</t>
+    <t xml:space="preserve">27.5764827728271</t>
   </si>
   <si>
     <t xml:space="preserve">28.0399551391602</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1789932250977</t>
+    <t xml:space="preserve">28.1789951324463</t>
   </si>
   <si>
     <t xml:space="preserve">28.2716884613037</t>
@@ -2219,7 +2219,7 @@
     <t xml:space="preserve">28.1326484680176</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4374408721924</t>
+    <t xml:space="preserve">27.437442779541</t>
   </si>
   <si>
     <t xml:space="preserve">27.5301361083984</t>
@@ -2231,13 +2231,13 @@
     <t xml:space="preserve">25.39817237854</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9417819976807</t>
+    <t xml:space="preserve">22.941780090332</t>
   </si>
   <si>
     <t xml:space="preserve">22.2002296447754</t>
   </si>
   <si>
-    <t xml:space="preserve">22.153881072998</t>
+    <t xml:space="preserve">22.1538791656494</t>
   </si>
   <si>
     <t xml:space="preserve">22.1075344085693</t>
@@ -2246,10 +2246,10 @@
     <t xml:space="preserve">22.7100448608398</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9881267547607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2198600769043</t>
+    <t xml:space="preserve">22.9881248474121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2198619842529</t>
   </si>
   <si>
     <t xml:space="preserve">21.8294506072998</t>
@@ -2261,10 +2261,10 @@
     <t xml:space="preserve">20.6707744598389</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4853897094727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2536525726318</t>
+    <t xml:space="preserve">20.485387802124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2536506652832</t>
   </si>
   <si>
     <t xml:space="preserve">20.5317344665527</t>
@@ -2273,28 +2273,28 @@
     <t xml:space="preserve">21.1342449188232</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7831058502197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6440620422363</t>
+    <t xml:space="preserve">21.7831039428711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.644063949585</t>
   </si>
   <si>
     <t xml:space="preserve">21.2269401550293</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3196334838867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8757972717285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1805953979492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9025115966797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6679420471191</t>
+    <t xml:space="preserve">21.3196353912354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8757991790771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.180591583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9025096893311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6679439544678</t>
   </si>
   <si>
     <t xml:space="preserve">21.4127311706543</t>
@@ -2303,7 +2303,7 @@
     <t xml:space="preserve">20.6213912963867</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5748443603516</t>
+    <t xml:space="preserve">20.5748424530029</t>
   </si>
   <si>
     <t xml:space="preserve">20.3886451721191</t>
@@ -2312,16 +2312,16 @@
     <t xml:space="preserve">21.3661842346191</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9937877655029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9006900787354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0403366088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1799850463867</t>
+    <t xml:space="preserve">20.9937858581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9006881713867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0403385162354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1799869537354</t>
   </si>
   <si>
     <t xml:space="preserve">21.2265338897705</t>
@@ -2330,13 +2330,13 @@
     <t xml:space="preserve">20.9472389221191</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4817447662354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3420963287354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2489986419678</t>
+    <t xml:space="preserve">20.4817428588867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3420944213867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2489967346191</t>
   </si>
   <si>
     <t xml:space="preserve">20.1558990478516</t>
@@ -2372,7 +2372,7 @@
     <t xml:space="preserve">19.5507564544678</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2024478912354</t>
+    <t xml:space="preserve">20.2024459838867</t>
   </si>
   <si>
     <t xml:space="preserve">20.4351959228516</t>
@@ -2381,10 +2381,10 @@
     <t xml:space="preserve">19.4576568603516</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0387134552002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9696998596191</t>
+    <t xml:space="preserve">19.0387115478516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9697017669678</t>
   </si>
   <si>
     <t xml:space="preserve">19.9231510162354</t>
@@ -2402,10 +2402,10 @@
     <t xml:space="preserve">19.1318111419678</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6197662353516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8525123596191</t>
+    <t xml:space="preserve">18.6197681427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8525161743164</t>
   </si>
   <si>
     <t xml:space="preserve">18.7128677368164</t>
@@ -2414,7 +2414,7 @@
     <t xml:space="preserve">18.6663150787354</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7594146728516</t>
+    <t xml:space="preserve">18.7594165802002</t>
   </si>
   <si>
     <t xml:space="preserve">18.5266666412354</t>
@@ -2423,16 +2423,16 @@
     <t xml:space="preserve">18.4708099365234</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3963317871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3404712677002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2287540435791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2101306915283</t>
+    <t xml:space="preserve">18.3963298797607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3404731750488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2287521362305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.210132598877</t>
   </si>
   <si>
     <t xml:space="preserve">17.968074798584</t>
@@ -2462,16 +2462,16 @@
     <t xml:space="preserve">16.7577896118164</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2232856750488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3350028991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.409481048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6515369415283</t>
+    <t xml:space="preserve">17.2232837677002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3350048065186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4094829559326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.651538848877</t>
   </si>
   <si>
     <t xml:space="preserve">17.7260189056396</t>
@@ -2486,13 +2486,13 @@
     <t xml:space="preserve">17.2605247497559</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2419033050537</t>
+    <t xml:space="preserve">17.2419052124023</t>
   </si>
   <si>
     <t xml:space="preserve">16.5715923309326</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5529727935791</t>
+    <t xml:space="preserve">16.5529747009277</t>
   </si>
   <si>
     <t xml:space="preserve">17.0929470062256</t>
@@ -2501,7 +2501,7 @@
     <t xml:space="preserve">16.9253673553467</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2736759185791</t>
+    <t xml:space="preserve">16.2736778259277</t>
   </si>
   <si>
     <t xml:space="preserve">16.0130004882812</t>
@@ -2510,16 +2510,16 @@
     <t xml:space="preserve">15.9757604598999</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2364387512207</t>
+    <t xml:space="preserve">16.2364368438721</t>
   </si>
   <si>
     <t xml:space="preserve">16.2922973632812</t>
   </si>
   <si>
-    <t xml:space="preserve">17.037088394165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.813648223877</t>
+    <t xml:space="preserve">17.0370864868164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8136501312256</t>
   </si>
   <si>
     <t xml:space="preserve">16.404016494751</t>
@@ -2534,19 +2534,19 @@
     <t xml:space="preserve">16.1805782318115</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3667755126953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4598751068115</t>
+    <t xml:space="preserve">16.3667736053467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4598731994629</t>
   </si>
   <si>
     <t xml:space="preserve">15.7709436416626</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7337017059326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8826608657837</t>
+    <t xml:space="preserve">15.7337036132812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.882661819458</t>
   </si>
   <si>
     <t xml:space="preserve">16.161958694458</t>
@@ -2564,10 +2564,10 @@
     <t xml:space="preserve">16.6460704803467</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8695106506348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1115665435791</t>
+    <t xml:space="preserve">16.8695087432861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1115646362305</t>
   </si>
   <si>
     <t xml:space="preserve">17.0184669494629</t>
@@ -2576,22 +2576,22 @@
     <t xml:space="preserve">17.0557060241699</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4839611053467</t>
+    <t xml:space="preserve">17.4839630126953</t>
   </si>
   <si>
     <t xml:space="preserve">17.3536224365234</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3722438812256</t>
+    <t xml:space="preserve">17.372241973877</t>
   </si>
   <si>
     <t xml:space="preserve">16.9998474121094</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0743255615234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6833114624023</t>
+    <t xml:space="preserve">17.0743274688721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.683313369751</t>
   </si>
   <si>
     <t xml:space="preserve">16.8881282806396</t>
@@ -2600,7 +2600,7 @@
     <t xml:space="preserve">16.6646919250488</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7205505371094</t>
+    <t xml:space="preserve">16.7205486297607</t>
   </si>
   <si>
     <t xml:space="preserve">16.8322696685791</t>
@@ -2612,19 +2612,19 @@
     <t xml:space="preserve">16.5902118682861</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3481559753418</t>
+    <t xml:space="preserve">16.3481540679932</t>
   </si>
   <si>
     <t xml:space="preserve">16.3109169006348</t>
   </si>
   <si>
-    <t xml:space="preserve">16.199197769165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6088333129883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0502376556396</t>
+    <t xml:space="preserve">16.1991958618164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6088314056396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0502395629883</t>
   </si>
   <si>
     <t xml:space="preserve">16.2550563812256</t>
@@ -2636,19 +2636,19 @@
     <t xml:space="preserve">17.1674251556396</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0053157806396</t>
+    <t xml:space="preserve">18.005313873291</t>
   </si>
   <si>
     <t xml:space="preserve">17.9122161865234</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4653434753418</t>
+    <t xml:space="preserve">17.4653415679932</t>
   </si>
   <si>
     <t xml:space="preserve">17.9494571685791</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8749771118164</t>
+    <t xml:space="preserve">17.8749752044678</t>
   </si>
   <si>
     <t xml:space="preserve">17.6422309875488</t>
@@ -2657,16 +2657,16 @@
     <t xml:space="preserve">17.5491313934326</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3629341125488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5025787353516</t>
+    <t xml:space="preserve">17.3629322052002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5025806427002</t>
   </si>
   <si>
     <t xml:space="preserve">17.4560317993164</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1542739868164</t>
+    <t xml:space="preserve">18.1542720794678</t>
   </si>
   <si>
     <t xml:space="preserve">18.0611743927002</t>
@@ -19473,7 +19473,7 @@
         <v>12.75</v>
       </c>
       <c r="G621" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -19551,7 +19551,7 @@
         <v>13</v>
       </c>
       <c r="G624" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -19577,7 +19577,7 @@
         <v>13</v>
       </c>
       <c r="G625" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -19603,7 +19603,7 @@
         <v>12.75</v>
       </c>
       <c r="G626" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -19629,7 +19629,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G627" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H627" t="s">
         <v>9</v>
@@ -19681,7 +19681,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G629" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H629" t="s">
         <v>9</v>
@@ -19707,7 +19707,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G630" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H630" t="s">
         <v>9</v>
@@ -19733,7 +19733,7 @@
         <v>12.75</v>
       </c>
       <c r="G631" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="H631" t="s">
         <v>9</v>
@@ -19759,7 +19759,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G632" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H632" t="s">
         <v>9</v>
@@ -19785,7 +19785,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G633" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H633" t="s">
         <v>9</v>
@@ -19811,7 +19811,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G634" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H634" t="s">
         <v>9</v>
@@ -19837,7 +19837,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G635" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H635" t="s">
         <v>9</v>
@@ -19863,7 +19863,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G636" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H636" t="s">
         <v>9</v>
@@ -19889,7 +19889,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G637" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H637" t="s">
         <v>9</v>
@@ -19915,7 +19915,7 @@
         <v>12.25</v>
       </c>
       <c r="G638" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H638" t="s">
         <v>9</v>
@@ -19941,7 +19941,7 @@
         <v>12.25</v>
       </c>
       <c r="G639" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H639" t="s">
         <v>9</v>
@@ -19967,7 +19967,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G640" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H640" t="s">
         <v>9</v>
@@ -19993,7 +19993,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G641" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H641" t="s">
         <v>9</v>
@@ -20019,7 +20019,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G642" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H642" t="s">
         <v>9</v>
@@ -20045,7 +20045,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G643" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H643" t="s">
         <v>9</v>
@@ -20071,7 +20071,7 @@
         <v>12.5</v>
       </c>
       <c r="G644" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H644" t="s">
         <v>9</v>
@@ -20097,7 +20097,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G645" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H645" t="s">
         <v>9</v>
@@ -20123,7 +20123,7 @@
         <v>12.5</v>
       </c>
       <c r="G646" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H646" t="s">
         <v>9</v>
@@ -20149,7 +20149,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G647" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H647" t="s">
         <v>9</v>
@@ -20175,7 +20175,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G648" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H648" t="s">
         <v>9</v>
@@ -20201,7 +20201,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G649" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H649" t="s">
         <v>9</v>
@@ -20227,7 +20227,7 @@
         <v>12.5</v>
       </c>
       <c r="G650" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H650" t="s">
         <v>9</v>
@@ -20253,7 +20253,7 @@
         <v>12.5</v>
       </c>
       <c r="G651" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H651" t="s">
         <v>9</v>
@@ -20279,7 +20279,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G652" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H652" t="s">
         <v>9</v>
@@ -20305,7 +20305,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G653" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H653" t="s">
         <v>9</v>
@@ -20331,7 +20331,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G654" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H654" t="s">
         <v>9</v>
@@ -20357,7 +20357,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G655" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H655" t="s">
         <v>9</v>
@@ -20435,7 +20435,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G658" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H658" t="s">
         <v>9</v>
@@ -20461,7 +20461,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G659" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H659" t="s">
         <v>9</v>
@@ -20487,7 +20487,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G660" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H660" t="s">
         <v>9</v>
@@ -20513,7 +20513,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G661" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H661" t="s">
         <v>9</v>
@@ -20539,7 +20539,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G662" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H662" t="s">
         <v>9</v>
@@ -20565,7 +20565,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G663" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H663" t="s">
         <v>9</v>
@@ -20591,7 +20591,7 @@
         <v>12.75</v>
       </c>
       <c r="G664" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -20617,7 +20617,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G665" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H665" t="s">
         <v>9</v>
@@ -20643,7 +20643,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G666" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H666" t="s">
         <v>9</v>
@@ -20669,7 +20669,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G667" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H667" t="s">
         <v>9</v>
@@ -20695,7 +20695,7 @@
         <v>12.25</v>
       </c>
       <c r="G668" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H668" t="s">
         <v>9</v>
@@ -20721,7 +20721,7 @@
         <v>12.25</v>
       </c>
       <c r="G669" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H669" t="s">
         <v>9</v>
@@ -20747,7 +20747,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G670" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H670" t="s">
         <v>9</v>
@@ -20773,7 +20773,7 @@
         <v>12.5</v>
       </c>
       <c r="G671" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H671" t="s">
         <v>9</v>
@@ -20799,7 +20799,7 @@
         <v>12.5</v>
       </c>
       <c r="G672" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H672" t="s">
         <v>9</v>
@@ -20825,7 +20825,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G673" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H673" t="s">
         <v>9</v>
@@ -20851,7 +20851,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G674" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H674" t="s">
         <v>9</v>
@@ -20877,7 +20877,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G675" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H675" t="s">
         <v>9</v>
@@ -20903,7 +20903,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G676" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H676" t="s">
         <v>9</v>
@@ -20929,7 +20929,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G677" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H677" t="s">
         <v>9</v>
@@ -20955,7 +20955,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G678" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H678" t="s">
         <v>9</v>
@@ -20981,7 +20981,7 @@
         <v>12.25</v>
       </c>
       <c r="G679" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H679" t="s">
         <v>9</v>
@@ -21007,7 +21007,7 @@
         <v>12.25</v>
       </c>
       <c r="G680" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H680" t="s">
         <v>9</v>
@@ -21033,7 +21033,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G681" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H681" t="s">
         <v>9</v>
@@ -21059,7 +21059,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G682" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H682" t="s">
         <v>9</v>
@@ -21085,7 +21085,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G683" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H683" t="s">
         <v>9</v>
@@ -21111,7 +21111,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G684" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H684" t="s">
         <v>9</v>
@@ -21137,7 +21137,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G685" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H685" t="s">
         <v>9</v>
@@ -21163,7 +21163,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G686" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H686" t="s">
         <v>9</v>
@@ -21189,7 +21189,7 @@
         <v>12.5</v>
       </c>
       <c r="G687" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H687" t="s">
         <v>9</v>
@@ -21215,7 +21215,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G688" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H688" t="s">
         <v>9</v>
@@ -21241,7 +21241,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G689" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H689" t="s">
         <v>9</v>
@@ -21267,7 +21267,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G690" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H690" t="s">
         <v>9</v>
@@ -21293,7 +21293,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G691" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H691" t="s">
         <v>9</v>
@@ -21319,7 +21319,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G692" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H692" t="s">
         <v>9</v>
@@ -21345,7 +21345,7 @@
         <v>12.75</v>
       </c>
       <c r="G693" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="H693" t="s">
         <v>9</v>
@@ -21371,7 +21371,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G694" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -21397,7 +21397,7 @@
         <v>13.25</v>
       </c>
       <c r="G695" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H695" t="s">
         <v>9</v>
@@ -21423,7 +21423,7 @@
         <v>13</v>
       </c>
       <c r="G696" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H696" t="s">
         <v>9</v>
@@ -21449,7 +21449,7 @@
         <v>13</v>
       </c>
       <c r="G697" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H697" t="s">
         <v>9</v>
@@ -21475,7 +21475,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G698" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H698" t="s">
         <v>9</v>
@@ -21553,7 +21553,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G701" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H701" t="s">
         <v>9</v>
@@ -21579,7 +21579,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G702" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H702" t="s">
         <v>9</v>
@@ -21605,7 +21605,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G703" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H703" t="s">
         <v>9</v>
@@ -21631,7 +21631,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G704" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H704" t="s">
         <v>9</v>
@@ -21657,7 +21657,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G705" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H705" t="s">
         <v>9</v>
@@ -21683,7 +21683,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G706" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H706" t="s">
         <v>9</v>
@@ -21709,7 +21709,7 @@
         <v>13.25</v>
       </c>
       <c r="G707" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H707" t="s">
         <v>9</v>
@@ -21787,7 +21787,7 @@
         <v>13</v>
       </c>
       <c r="G710" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H710" t="s">
         <v>9</v>
@@ -21813,7 +21813,7 @@
         <v>13</v>
       </c>
       <c r="G711" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H711" t="s">
         <v>9</v>
@@ -21865,7 +21865,7 @@
         <v>13</v>
       </c>
       <c r="G713" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H713" t="s">
         <v>9</v>
@@ -21891,7 +21891,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G714" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H714" t="s">
         <v>9</v>
@@ -21943,7 +21943,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G716" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H716" t="s">
         <v>9</v>
@@ -21969,7 +21969,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G717" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H717" t="s">
         <v>9</v>
@@ -21995,7 +21995,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G718" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H718" t="s">
         <v>9</v>
@@ -22021,7 +22021,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G719" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H719" t="s">
         <v>9</v>
@@ -22047,7 +22047,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G720" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H720" t="s">
         <v>9</v>
@@ -22073,7 +22073,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G721" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H721" t="s">
         <v>9</v>
@@ -22099,7 +22099,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G722" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H722" t="s">
         <v>9</v>
@@ -22125,7 +22125,7 @@
         <v>12.5</v>
       </c>
       <c r="G723" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H723" t="s">
         <v>9</v>
@@ -22151,7 +22151,7 @@
         <v>13</v>
       </c>
       <c r="G724" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H724" t="s">
         <v>9</v>
@@ -22177,7 +22177,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G725" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H725" t="s">
         <v>9</v>
@@ -22203,7 +22203,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G726" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H726" t="s">
         <v>9</v>
@@ -22229,7 +22229,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G727" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H727" t="s">
         <v>9</v>
@@ -22255,7 +22255,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G728" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H728" t="s">
         <v>9</v>
@@ -22281,7 +22281,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G729" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H729" t="s">
         <v>9</v>
@@ -22307,7 +22307,7 @@
         <v>12.5</v>
       </c>
       <c r="G730" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H730" t="s">
         <v>9</v>
@@ -22333,7 +22333,7 @@
         <v>12.25</v>
       </c>
       <c r="G731" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H731" t="s">
         <v>9</v>
@@ -22359,7 +22359,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G732" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H732" t="s">
         <v>9</v>
@@ -22385,7 +22385,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G733" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H733" t="s">
         <v>9</v>
@@ -22411,7 +22411,7 @@
         <v>12</v>
       </c>
       <c r="G734" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H734" t="s">
         <v>9</v>
@@ -22437,7 +22437,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G735" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H735" t="s">
         <v>9</v>
@@ -22463,7 +22463,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G736" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H736" t="s">
         <v>9</v>
@@ -22489,7 +22489,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G737" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H737" t="s">
         <v>9</v>
@@ -22515,7 +22515,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G738" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H738" t="s">
         <v>9</v>
@@ -22541,7 +22541,7 @@
         <v>11.5</v>
       </c>
       <c r="G739" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H739" t="s">
         <v>9</v>
@@ -22567,7 +22567,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G740" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H740" t="s">
         <v>9</v>
@@ -22593,7 +22593,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G741" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H741" t="s">
         <v>9</v>
@@ -22619,7 +22619,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G742" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H742" t="s">
         <v>9</v>
@@ -22645,7 +22645,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G743" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H743" t="s">
         <v>9</v>
@@ -22671,7 +22671,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G744" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H744" t="s">
         <v>9</v>
@@ -22697,7 +22697,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G745" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H745" t="s">
         <v>9</v>
@@ -22723,7 +22723,7 @@
         <v>11.5</v>
       </c>
       <c r="G746" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H746" t="s">
         <v>9</v>
@@ -22749,7 +22749,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G747" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H747" t="s">
         <v>9</v>
@@ -22775,7 +22775,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G748" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H748" t="s">
         <v>9</v>
@@ -22801,7 +22801,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G749" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H749" t="s">
         <v>9</v>
@@ -22827,7 +22827,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G750" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H750" t="s">
         <v>9</v>
@@ -22853,7 +22853,7 @@
         <v>10.25</v>
       </c>
       <c r="G751" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H751" t="s">
         <v>9</v>
@@ -22879,7 +22879,7 @@
         <v>10.25</v>
       </c>
       <c r="G752" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H752" t="s">
         <v>9</v>
@@ -22905,7 +22905,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G753" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H753" t="s">
         <v>9</v>
@@ -22931,7 +22931,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G754" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H754" t="s">
         <v>9</v>
@@ -22957,7 +22957,7 @@
         <v>10.5</v>
       </c>
       <c r="G755" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H755" t="s">
         <v>9</v>
@@ -22983,7 +22983,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G756" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H756" t="s">
         <v>9</v>
@@ -23009,7 +23009,7 @@
         <v>10.5</v>
       </c>
       <c r="G757" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H757" t="s">
         <v>9</v>
@@ -23035,7 +23035,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G758" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H758" t="s">
         <v>9</v>
@@ -23061,7 +23061,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G759" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H759" t="s">
         <v>9</v>
@@ -23087,7 +23087,7 @@
         <v>10.75</v>
       </c>
       <c r="G760" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H760" t="s">
         <v>9</v>
@@ -23113,7 +23113,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G761" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H761" t="s">
         <v>9</v>
@@ -23139,7 +23139,7 @@
         <v>11.5</v>
       </c>
       <c r="G762" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H762" t="s">
         <v>9</v>
@@ -23165,7 +23165,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G763" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H763" t="s">
         <v>9</v>
@@ -23191,7 +23191,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G764" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H764" t="s">
         <v>9</v>
@@ -23217,7 +23217,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G765" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H765" t="s">
         <v>9</v>
@@ -23243,7 +23243,7 @@
         <v>11.5</v>
       </c>
       <c r="G766" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H766" t="s">
         <v>9</v>
@@ -23269,7 +23269,7 @@
         <v>11.5</v>
       </c>
       <c r="G767" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H767" t="s">
         <v>9</v>
@@ -23295,7 +23295,7 @@
         <v>11.75</v>
       </c>
       <c r="G768" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H768" t="s">
         <v>9</v>
@@ -23321,7 +23321,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G769" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H769" t="s">
         <v>9</v>
@@ -23347,7 +23347,7 @@
         <v>12</v>
       </c>
       <c r="G770" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H770" t="s">
         <v>9</v>
@@ -23373,7 +23373,7 @@
         <v>11.75</v>
       </c>
       <c r="G771" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H771" t="s">
         <v>9</v>
@@ -23399,7 +23399,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G772" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H772" t="s">
         <v>9</v>
@@ -23425,7 +23425,7 @@
         <v>11.5</v>
       </c>
       <c r="G773" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H773" t="s">
         <v>9</v>
@@ -23451,7 +23451,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G774" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H774" t="s">
         <v>9</v>
@@ -23477,7 +23477,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G775" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H775" t="s">
         <v>9</v>
@@ -23503,7 +23503,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G776" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H776" t="s">
         <v>9</v>
@@ -23529,7 +23529,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G777" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H777" t="s">
         <v>9</v>
@@ -23555,7 +23555,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G778" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H778" t="s">
         <v>9</v>
@@ -23581,7 +23581,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G779" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H779" t="s">
         <v>9</v>
@@ -23607,7 +23607,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G780" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H780" t="s">
         <v>9</v>
@@ -23633,7 +23633,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G781" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H781" t="s">
         <v>9</v>
@@ -23659,7 +23659,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G782" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H782" t="s">
         <v>9</v>
@@ -23685,7 +23685,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G783" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H783" t="s">
         <v>9</v>
@@ -23711,7 +23711,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G784" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H784" t="s">
         <v>9</v>
@@ -23737,7 +23737,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G785" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H785" t="s">
         <v>9</v>
@@ -23763,7 +23763,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G786" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H786" t="s">
         <v>9</v>
@@ -23789,7 +23789,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G787" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H787" t="s">
         <v>9</v>
@@ -23815,7 +23815,7 @@
         <v>11.5</v>
       </c>
       <c r="G788" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H788" t="s">
         <v>9</v>
@@ -23841,7 +23841,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G789" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H789" t="s">
         <v>9</v>
@@ -23867,7 +23867,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G790" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H790" t="s">
         <v>9</v>
@@ -23893,7 +23893,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G791" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H791" t="s">
         <v>9</v>
@@ -23919,7 +23919,7 @@
         <v>11.5</v>
       </c>
       <c r="G792" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H792" t="s">
         <v>9</v>
@@ -23945,7 +23945,7 @@
         <v>11.25</v>
       </c>
       <c r="G793" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H793" t="s">
         <v>9</v>
@@ -23971,7 +23971,7 @@
         <v>11.25</v>
       </c>
       <c r="G794" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H794" t="s">
         <v>9</v>
@@ -23997,7 +23997,7 @@
         <v>11.5</v>
       </c>
       <c r="G795" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H795" t="s">
         <v>9</v>
@@ -24023,7 +24023,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G796" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H796" t="s">
         <v>9</v>
@@ -24049,7 +24049,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G797" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H797" t="s">
         <v>9</v>
@@ -24075,7 +24075,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G798" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H798" t="s">
         <v>9</v>
@@ -24101,7 +24101,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G799" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H799" t="s">
         <v>9</v>
@@ -24127,7 +24127,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G800" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H800" t="s">
         <v>9</v>
@@ -24153,7 +24153,7 @@
         <v>11</v>
       </c>
       <c r="G801" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H801" t="s">
         <v>9</v>
@@ -24179,7 +24179,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G802" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H802" t="s">
         <v>9</v>
@@ -24205,7 +24205,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G803" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H803" t="s">
         <v>9</v>
@@ -24231,7 +24231,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G804" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H804" t="s">
         <v>9</v>
@@ -24257,7 +24257,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G805" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H805" t="s">
         <v>9</v>
@@ -24283,7 +24283,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G806" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H806" t="s">
         <v>9</v>
@@ -24309,7 +24309,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G807" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H807" t="s">
         <v>9</v>
@@ -24335,7 +24335,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G808" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H808" t="s">
         <v>9</v>
@@ -24361,7 +24361,7 @@
         <v>11</v>
       </c>
       <c r="G809" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H809" t="s">
         <v>9</v>
@@ -24387,7 +24387,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G810" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H810" t="s">
         <v>9</v>
@@ -24413,7 +24413,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G811" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H811" t="s">
         <v>9</v>
@@ -24439,7 +24439,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G812" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H812" t="s">
         <v>9</v>
@@ -24465,7 +24465,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G813" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H813" t="s">
         <v>9</v>
@@ -24491,7 +24491,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G814" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H814" t="s">
         <v>9</v>
@@ -24517,7 +24517,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G815" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H815" t="s">
         <v>9</v>
@@ -24543,7 +24543,7 @@
         <v>10.75</v>
       </c>
       <c r="G816" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H816" t="s">
         <v>9</v>
@@ -24569,7 +24569,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G817" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H817" t="s">
         <v>9</v>
@@ -24595,7 +24595,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G818" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H818" t="s">
         <v>9</v>
@@ -24621,7 +24621,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G819" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H819" t="s">
         <v>9</v>
@@ -24647,7 +24647,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G820" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H820" t="s">
         <v>9</v>
@@ -24673,7 +24673,7 @@
         <v>11.25</v>
       </c>
       <c r="G821" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H821" t="s">
         <v>9</v>
@@ -24699,7 +24699,7 @@
         <v>11.25</v>
       </c>
       <c r="G822" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H822" t="s">
         <v>9</v>
@@ -24725,7 +24725,7 @@
         <v>11.25</v>
       </c>
       <c r="G823" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H823" t="s">
         <v>9</v>
@@ -24751,7 +24751,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G824" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H824" t="s">
         <v>9</v>
@@ -24777,7 +24777,7 @@
         <v>11.5</v>
       </c>
       <c r="G825" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H825" t="s">
         <v>9</v>
@@ -24803,7 +24803,7 @@
         <v>11.5</v>
       </c>
       <c r="G826" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H826" t="s">
         <v>9</v>
@@ -24829,7 +24829,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G827" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H827" t="s">
         <v>9</v>
@@ -24855,7 +24855,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G828" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H828" t="s">
         <v>9</v>
@@ -24881,7 +24881,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G829" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H829" t="s">
         <v>9</v>
@@ -24907,7 +24907,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G830" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H830" t="s">
         <v>9</v>
@@ -24933,7 +24933,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G831" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H831" t="s">
         <v>9</v>
@@ -24959,7 +24959,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G832" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H832" t="s">
         <v>9</v>
@@ -24985,7 +24985,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G833" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H833" t="s">
         <v>9</v>
@@ -25011,7 +25011,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G834" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H834" t="s">
         <v>9</v>
@@ -25037,7 +25037,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G835" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H835" t="s">
         <v>9</v>
@@ -25063,7 +25063,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G836" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H836" t="s">
         <v>9</v>
@@ -25089,7 +25089,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G837" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H837" t="s">
         <v>9</v>
@@ -25115,7 +25115,7 @@
         <v>11.5</v>
       </c>
       <c r="G838" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H838" t="s">
         <v>9</v>
@@ -25141,7 +25141,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G839" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H839" t="s">
         <v>9</v>
@@ -25167,7 +25167,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G840" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H840" t="s">
         <v>9</v>
@@ -25193,7 +25193,7 @@
         <v>11.5</v>
       </c>
       <c r="G841" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H841" t="s">
         <v>9</v>
@@ -25219,7 +25219,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G842" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H842" t="s">
         <v>9</v>
@@ -25245,7 +25245,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G843" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H843" t="s">
         <v>9</v>
@@ -25271,7 +25271,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G844" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H844" t="s">
         <v>9</v>
@@ -25297,7 +25297,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G845" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H845" t="s">
         <v>9</v>
@@ -25323,7 +25323,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G846" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H846" t="s">
         <v>9</v>
@@ -25349,7 +25349,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G847" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -25375,7 +25375,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G848" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H848" t="s">
         <v>9</v>
@@ -25401,7 +25401,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G849" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H849" t="s">
         <v>9</v>
@@ -25427,7 +25427,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G850" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H850" t="s">
         <v>9</v>
@@ -25453,7 +25453,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G851" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -25479,7 +25479,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G852" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H852" t="s">
         <v>9</v>
@@ -25505,7 +25505,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G853" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -25531,7 +25531,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G854" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H854" t="s">
         <v>9</v>
@@ -25557,7 +25557,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G855" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -25583,7 +25583,7 @@
         <v>11.5</v>
       </c>
       <c r="G856" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -25609,7 +25609,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G857" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H857" t="s">
         <v>9</v>
@@ -25635,7 +25635,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G858" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -25661,7 +25661,7 @@
         <v>11.5</v>
       </c>
       <c r="G859" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H859" t="s">
         <v>9</v>
@@ -25687,7 +25687,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G860" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H860" t="s">
         <v>9</v>
@@ -25713,7 +25713,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G861" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -25739,7 +25739,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G862" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H862" t="s">
         <v>9</v>
@@ -25765,7 +25765,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G863" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H863" t="s">
         <v>9</v>
@@ -25791,7 +25791,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G864" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H864" t="s">
         <v>9</v>
@@ -25817,7 +25817,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G865" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H865" t="s">
         <v>9</v>
@@ -25843,7 +25843,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G866" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H866" t="s">
         <v>9</v>
@@ -25869,7 +25869,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G867" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H867" t="s">
         <v>9</v>
@@ -25895,7 +25895,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G868" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H868" t="s">
         <v>9</v>
@@ -25921,7 +25921,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G869" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H869" t="s">
         <v>9</v>
@@ -25947,7 +25947,7 @@
         <v>12</v>
       </c>
       <c r="G870" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H870" t="s">
         <v>9</v>
@@ -25973,7 +25973,7 @@
         <v>12</v>
       </c>
       <c r="G871" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H871" t="s">
         <v>9</v>
@@ -25999,7 +25999,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G872" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H872" t="s">
         <v>9</v>
@@ -26025,7 +26025,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G873" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H873" t="s">
         <v>9</v>
@@ -26051,7 +26051,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G874" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H874" t="s">
         <v>9</v>
@@ -26077,7 +26077,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G875" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H875" t="s">
         <v>9</v>
@@ -26103,7 +26103,7 @@
         <v>12</v>
       </c>
       <c r="G876" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H876" t="s">
         <v>9</v>
@@ -26129,7 +26129,7 @@
         <v>12</v>
       </c>
       <c r="G877" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H877" t="s">
         <v>9</v>
@@ -26155,7 +26155,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G878" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H878" t="s">
         <v>9</v>
@@ -26181,7 +26181,7 @@
         <v>12</v>
       </c>
       <c r="G879" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H879" t="s">
         <v>9</v>
@@ -26207,7 +26207,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G880" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H880" t="s">
         <v>9</v>
@@ -26233,7 +26233,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G881" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H881" t="s">
         <v>9</v>
@@ -26259,7 +26259,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G882" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H882" t="s">
         <v>9</v>
@@ -26285,7 +26285,7 @@
         <v>12</v>
       </c>
       <c r="G883" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H883" t="s">
         <v>9</v>
@@ -26311,7 +26311,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G884" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H884" t="s">
         <v>9</v>
@@ -26337,7 +26337,7 @@
         <v>12.25</v>
       </c>
       <c r="G885" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H885" t="s">
         <v>9</v>
@@ -26363,7 +26363,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G886" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H886" t="s">
         <v>9</v>
@@ -26389,7 +26389,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G887" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H887" t="s">
         <v>9</v>
@@ -26415,7 +26415,7 @@
         <v>12.25</v>
       </c>
       <c r="G888" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H888" t="s">
         <v>9</v>
@@ -26441,7 +26441,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G889" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H889" t="s">
         <v>9</v>
@@ -26467,7 +26467,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G890" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H890" t="s">
         <v>9</v>
@@ -26493,7 +26493,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G891" t="s">
-        <v>251</v>
+        <v>326</v>
       </c>
       <c r="H891" t="s">
         <v>9</v>
@@ -26597,7 +26597,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G895" t="s">
-        <v>251</v>
+        <v>326</v>
       </c>
       <c r="H895" t="s">
         <v>9</v>
@@ -26753,7 +26753,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G901" t="s">
-        <v>251</v>
+        <v>326</v>
       </c>
       <c r="H901" t="s">
         <v>9</v>
@@ -26857,7 +26857,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G905" t="s">
-        <v>251</v>
+        <v>326</v>
       </c>
       <c r="H905" t="s">
         <v>9</v>
@@ -26883,7 +26883,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G906" t="s">
-        <v>251</v>
+        <v>326</v>
       </c>
       <c r="H906" t="s">
         <v>9</v>
@@ -26987,7 +26987,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G910" t="s">
-        <v>251</v>
+        <v>326</v>
       </c>
       <c r="H910" t="s">
         <v>9</v>
@@ -27065,7 +27065,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G913" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H913" t="s">
         <v>9</v>
@@ -27195,7 +27195,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G918" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H918" t="s">
         <v>9</v>
@@ -27221,7 +27221,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G919" t="s">
-        <v>251</v>
+        <v>326</v>
       </c>
       <c r="H919" t="s">
         <v>9</v>
@@ -27299,7 +27299,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G922" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H922" t="s">
         <v>9</v>
@@ -27325,7 +27325,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G923" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H923" t="s">
         <v>9</v>
@@ -27507,7 +27507,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G930" t="s">
-        <v>251</v>
+        <v>326</v>
       </c>
       <c r="H930" t="s">
         <v>9</v>
@@ -28053,7 +28053,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G951" t="s">
-        <v>251</v>
+        <v>326</v>
       </c>
       <c r="H951" t="s">
         <v>9</v>
@@ -28105,7 +28105,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G953" t="s">
-        <v>251</v>
+        <v>326</v>
       </c>
       <c r="H953" t="s">
         <v>9</v>
@@ -28183,7 +28183,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G956" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H956" t="s">
         <v>9</v>
@@ -28209,7 +28209,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G957" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H957" t="s">
         <v>9</v>
@@ -28235,7 +28235,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G958" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H958" t="s">
         <v>9</v>
@@ -28261,7 +28261,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G959" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H959" t="s">
         <v>9</v>
@@ -28287,7 +28287,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G960" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H960" t="s">
         <v>9</v>
@@ -28339,7 +28339,7 @@
         <v>11.5</v>
       </c>
       <c r="G962" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H962" t="s">
         <v>9</v>
@@ -28365,7 +28365,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G963" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H963" t="s">
         <v>9</v>
@@ -28391,7 +28391,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G964" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H964" t="s">
         <v>9</v>
@@ -28417,7 +28417,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G965" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H965" t="s">
         <v>9</v>
@@ -28443,7 +28443,7 @@
         <v>12.25</v>
       </c>
       <c r="G966" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H966" t="s">
         <v>9</v>
@@ -28469,7 +28469,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G967" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H967" t="s">
         <v>9</v>
@@ -28495,7 +28495,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G968" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H968" t="s">
         <v>9</v>
@@ -28547,7 +28547,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G970" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H970" t="s">
         <v>9</v>
@@ -28599,7 +28599,7 @@
         <v>12.25</v>
       </c>
       <c r="G972" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H972" t="s">
         <v>9</v>
@@ -28625,7 +28625,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G973" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H973" t="s">
         <v>9</v>
@@ -28651,7 +28651,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G974" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H974" t="s">
         <v>9</v>
@@ -28677,7 +28677,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G975" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H975" t="s">
         <v>9</v>
@@ -28755,7 +28755,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G978" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H978" t="s">
         <v>9</v>
@@ -28807,7 +28807,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G980" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H980" t="s">
         <v>9</v>
@@ -28885,7 +28885,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G983" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H983" t="s">
         <v>9</v>
@@ -28937,7 +28937,7 @@
         <v>12.25</v>
       </c>
       <c r="G985" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H985" t="s">
         <v>9</v>
@@ -28963,7 +28963,7 @@
         <v>12.25</v>
       </c>
       <c r="G986" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H986" t="s">
         <v>9</v>
@@ -28989,7 +28989,7 @@
         <v>12.25</v>
       </c>
       <c r="G987" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H987" t="s">
         <v>9</v>
@@ -29015,7 +29015,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G988" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H988" t="s">
         <v>9</v>
@@ -29041,7 +29041,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G989" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H989" t="s">
         <v>9</v>
@@ -29067,7 +29067,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G990" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H990" t="s">
         <v>9</v>
@@ -29093,7 +29093,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G991" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H991" t="s">
         <v>9</v>
@@ -29145,7 +29145,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G993" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H993" t="s">
         <v>9</v>
@@ -29171,7 +29171,7 @@
         <v>12</v>
       </c>
       <c r="G994" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H994" t="s">
         <v>9</v>
@@ -29197,7 +29197,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G995" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H995" t="s">
         <v>9</v>
@@ -29223,7 +29223,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G996" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H996" t="s">
         <v>9</v>
@@ -29249,7 +29249,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G997" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H997" t="s">
         <v>9</v>
@@ -29275,7 +29275,7 @@
         <v>12.25</v>
       </c>
       <c r="G998" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H998" t="s">
         <v>9</v>
@@ -29353,7 +29353,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G1001" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H1001" t="s">
         <v>9</v>
@@ -29379,7 +29379,7 @@
         <v>12</v>
       </c>
       <c r="G1002" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H1002" t="s">
         <v>9</v>
@@ -29431,7 +29431,7 @@
         <v>12.25</v>
       </c>
       <c r="G1004" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H1004" t="s">
         <v>9</v>
@@ -29457,7 +29457,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G1005" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H1005" t="s">
         <v>9</v>
@@ -29483,7 +29483,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G1006" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H1006" t="s">
         <v>9</v>
@@ -29509,7 +29509,7 @@
         <v>12.25</v>
       </c>
       <c r="G1007" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H1007" t="s">
         <v>9</v>
@@ -29561,7 +29561,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G1009" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H1009" t="s">
         <v>9</v>
@@ -29613,7 +29613,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G1011" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H1011" t="s">
         <v>9</v>
@@ -29795,7 +29795,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1018" t="s">
-        <v>251</v>
+        <v>326</v>
       </c>
       <c r="H1018" t="s">
         <v>9</v>
@@ -31017,7 +31017,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1065" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H1065" t="s">
         <v>9</v>
@@ -31043,7 +31043,7 @@
         <v>12</v>
       </c>
       <c r="G1066" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H1066" t="s">
         <v>9</v>
@@ -31069,7 +31069,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1067" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H1067" t="s">
         <v>9</v>
@@ -31095,7 +31095,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G1068" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H1068" t="s">
         <v>9</v>
@@ -31173,7 +31173,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1071" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H1071" t="s">
         <v>9</v>
@@ -31199,7 +31199,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1072" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H1072" t="s">
         <v>9</v>
@@ -31303,7 +31303,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G1076" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H1076" t="s">
         <v>9</v>
@@ -31329,7 +31329,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1077" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H1077" t="s">
         <v>9</v>
@@ -31355,7 +31355,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1078" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H1078" t="s">
         <v>9</v>
@@ -31381,7 +31381,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G1079" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H1079" t="s">
         <v>9</v>
@@ -31459,7 +31459,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G1082" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H1082" t="s">
         <v>9</v>
@@ -31511,7 +31511,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G1084" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H1084" t="s">
         <v>9</v>
@@ -31589,7 +31589,7 @@
         <v>12</v>
       </c>
       <c r="G1087" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H1087" t="s">
         <v>9</v>
@@ -31615,7 +31615,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1088" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H1088" t="s">
         <v>9</v>
@@ -31641,7 +31641,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1089" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H1089" t="s">
         <v>9</v>
@@ -31667,7 +31667,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1090" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H1090" t="s">
         <v>9</v>
@@ -31693,7 +31693,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G1091" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H1091" t="s">
         <v>9</v>
@@ -31719,7 +31719,7 @@
         <v>12</v>
       </c>
       <c r="G1092" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H1092" t="s">
         <v>9</v>
@@ -31797,7 +31797,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1095" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H1095" t="s">
         <v>9</v>
@@ -33019,7 +33019,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1142" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="H1142" t="s">
         <v>9</v>
@@ -33045,7 +33045,7 @@
         <v>14.75</v>
       </c>
       <c r="G1143" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H1143" t="s">
         <v>9</v>
@@ -33071,7 +33071,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1144" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H1144" t="s">
         <v>9</v>
@@ -33097,7 +33097,7 @@
         <v>14.5</v>
       </c>
       <c r="G1145" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1145" t="s">
         <v>9</v>
@@ -33123,7 +33123,7 @@
         <v>14.5</v>
       </c>
       <c r="G1146" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1146" t="s">
         <v>9</v>
@@ -33149,7 +33149,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1147" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1147" t="s">
         <v>9</v>
@@ -33175,7 +33175,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1148" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1148" t="s">
         <v>9</v>
@@ -33201,7 +33201,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G1149" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1149" t="s">
         <v>9</v>
@@ -33227,7 +33227,7 @@
         <v>14</v>
       </c>
       <c r="G1150" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1150" t="s">
         <v>9</v>
@@ -33253,7 +33253,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1151" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1151" t="s">
         <v>9</v>
@@ -33279,7 +33279,7 @@
         <v>14.5</v>
       </c>
       <c r="G1152" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1152" t="s">
         <v>9</v>
@@ -33305,7 +33305,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1153" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H1153" t="s">
         <v>9</v>
@@ -33331,7 +33331,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G1154" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H1154" t="s">
         <v>9</v>
@@ -33357,7 +33357,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G1155" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H1155" t="s">
         <v>9</v>
@@ -33383,7 +33383,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G1156" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H1156" t="s">
         <v>9</v>
@@ -33409,7 +33409,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1157" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H1157" t="s">
         <v>9</v>
@@ -33461,7 +33461,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1159" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H1159" t="s">
         <v>9</v>
@@ -33487,7 +33487,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1160" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H1160" t="s">
         <v>9</v>
@@ -33513,7 +33513,7 @@
         <v>14.5</v>
       </c>
       <c r="G1161" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1161" t="s">
         <v>9</v>
@@ -33539,7 +33539,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G1162" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1162" t="s">
         <v>9</v>
@@ -33565,7 +33565,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G1163" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H1163" t="s">
         <v>9</v>
@@ -33591,7 +33591,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1164" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1164" t="s">
         <v>9</v>
@@ -33617,7 +33617,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1165" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1165" t="s">
         <v>9</v>
@@ -33643,7 +33643,7 @@
         <v>14.25</v>
       </c>
       <c r="G1166" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1166" t="s">
         <v>9</v>
@@ -33669,7 +33669,7 @@
         <v>14.5</v>
       </c>
       <c r="G1167" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1167" t="s">
         <v>9</v>
@@ -33695,7 +33695,7 @@
         <v>14.5</v>
       </c>
       <c r="G1168" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1168" t="s">
         <v>9</v>
@@ -33747,7 +33747,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1170" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H1170" t="s">
         <v>9</v>
@@ -33799,7 +33799,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1172" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H1172" t="s">
         <v>9</v>
@@ -33851,7 +33851,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1174" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H1174" t="s">
         <v>9</v>
@@ -33877,7 +33877,7 @@
         <v>15.75</v>
       </c>
       <c r="G1175" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H1175" t="s">
         <v>9</v>
@@ -33903,7 +33903,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1176" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H1176" t="s">
         <v>9</v>
@@ -33929,7 +33929,7 @@
         <v>16</v>
       </c>
       <c r="G1177" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H1177" t="s">
         <v>9</v>
@@ -33955,7 +33955,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1178" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H1178" t="s">
         <v>9</v>
@@ -33981,7 +33981,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G1179" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H1179" t="s">
         <v>9</v>
@@ -34007,7 +34007,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1180" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H1180" t="s">
         <v>9</v>
@@ -34033,7 +34033,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1181" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H1181" t="s">
         <v>9</v>
@@ -34059,7 +34059,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1182" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H1182" t="s">
         <v>9</v>
@@ -34085,7 +34085,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1183" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H1183" t="s">
         <v>9</v>
@@ -34111,7 +34111,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1184" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H1184" t="s">
         <v>9</v>
@@ -34137,7 +34137,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1185" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H1185" t="s">
         <v>9</v>
@@ -34163,7 +34163,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1186" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H1186" t="s">
         <v>9</v>
@@ -34189,7 +34189,7 @@
         <v>16.5</v>
       </c>
       <c r="G1187" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H1187" t="s">
         <v>9</v>
@@ -34215,7 +34215,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1188" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H1188" t="s">
         <v>9</v>
@@ -34241,7 +34241,7 @@
         <v>16.5</v>
       </c>
       <c r="G1189" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H1189" t="s">
         <v>9</v>
@@ -34267,7 +34267,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1190" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H1190" t="s">
         <v>9</v>
@@ -34293,7 +34293,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G1191" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H1191" t="s">
         <v>9</v>
@@ -34319,7 +34319,7 @@
         <v>17</v>
       </c>
       <c r="G1192" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H1192" t="s">
         <v>9</v>
@@ -34345,7 +34345,7 @@
         <v>17</v>
       </c>
       <c r="G1193" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H1193" t="s">
         <v>9</v>
@@ -34371,7 +34371,7 @@
         <v>17</v>
       </c>
       <c r="G1194" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H1194" t="s">
         <v>9</v>
@@ -34397,7 +34397,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1195" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H1195" t="s">
         <v>9</v>
@@ -34423,7 +34423,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G1196" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H1196" t="s">
         <v>9</v>
@@ -34449,7 +34449,7 @@
         <v>18</v>
       </c>
       <c r="G1197" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H1197" t="s">
         <v>9</v>
@@ -34475,7 +34475,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1198" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H1198" t="s">
         <v>9</v>
@@ -34501,7 +34501,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1199" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H1199" t="s">
         <v>9</v>
@@ -34527,7 +34527,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1200" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H1200" t="s">
         <v>9</v>
@@ -34553,7 +34553,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G1201" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H1201" t="s">
         <v>9</v>
@@ -34579,7 +34579,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G1202" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H1202" t="s">
         <v>9</v>
@@ -34605,7 +34605,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1203" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H1203" t="s">
         <v>9</v>
@@ -34631,7 +34631,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G1204" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H1204" t="s">
         <v>9</v>
@@ -34657,7 +34657,7 @@
         <v>20</v>
       </c>
       <c r="G1205" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H1205" t="s">
         <v>9</v>
@@ -34683,7 +34683,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G1206" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H1206" t="s">
         <v>9</v>
@@ -34709,7 +34709,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G1207" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H1207" t="s">
         <v>9</v>
@@ -34735,7 +34735,7 @@
         <v>19.25</v>
       </c>
       <c r="G1208" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H1208" t="s">
         <v>9</v>
@@ -34761,7 +34761,7 @@
         <v>19.3500003814697</v>
       </c>
       <c r="G1209" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H1209" t="s">
         <v>9</v>
@@ -34787,7 +34787,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1210" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H1210" t="s">
         <v>9</v>
@@ -34813,7 +34813,7 @@
         <v>19.3500003814697</v>
       </c>
       <c r="G1211" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H1211" t="s">
         <v>9</v>
@@ -34839,7 +34839,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1212" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H1212" t="s">
         <v>9</v>
@@ -34865,7 +34865,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1213" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H1213" t="s">
         <v>9</v>
@@ -34891,7 +34891,7 @@
         <v>18.4500007629395</v>
       </c>
       <c r="G1214" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H1214" t="s">
         <v>9</v>
@@ -34917,7 +34917,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G1215" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H1215" t="s">
         <v>9</v>
@@ -34943,7 +34943,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1216" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1216" t="s">
         <v>9</v>
@@ -34969,7 +34969,7 @@
         <v>18.5</v>
       </c>
       <c r="G1217" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H1217" t="s">
         <v>9</v>
@@ -34995,7 +34995,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1218" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H1218" t="s">
         <v>9</v>
@@ -35021,7 +35021,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1219" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H1219" t="s">
         <v>9</v>
@@ -35047,7 +35047,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1220" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H1220" t="s">
         <v>9</v>
@@ -35073,7 +35073,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1221" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H1221" t="s">
         <v>9</v>
@@ -35099,7 +35099,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1222" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H1222" t="s">
         <v>9</v>
@@ -35125,7 +35125,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1223" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H1223" t="s">
         <v>9</v>
@@ -35151,7 +35151,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1224" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H1224" t="s">
         <v>9</v>
@@ -35177,7 +35177,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1225" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H1225" t="s">
         <v>9</v>
@@ -35203,7 +35203,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1226" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H1226" t="s">
         <v>9</v>
@@ -35229,7 +35229,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1227" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H1227" t="s">
         <v>9</v>
@@ -35255,7 +35255,7 @@
         <v>17.75</v>
       </c>
       <c r="G1228" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H1228" t="s">
         <v>9</v>
@@ -35281,7 +35281,7 @@
         <v>18</v>
       </c>
       <c r="G1229" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H1229" t="s">
         <v>9</v>
@@ -35307,7 +35307,7 @@
         <v>18.5</v>
       </c>
       <c r="G1230" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H1230" t="s">
         <v>9</v>
@@ -35333,7 +35333,7 @@
         <v>18.4500007629395</v>
       </c>
       <c r="G1231" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H1231" t="s">
         <v>9</v>
@@ -35359,7 +35359,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1232" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H1232" t="s">
         <v>9</v>
@@ -35385,7 +35385,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G1233" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H1233" t="s">
         <v>9</v>
@@ -35411,7 +35411,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1234" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H1234" t="s">
         <v>9</v>
@@ -35437,7 +35437,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1235" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H1235" t="s">
         <v>9</v>
@@ -35463,7 +35463,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1236" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H1236" t="s">
         <v>9</v>
@@ -35489,7 +35489,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G1237" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H1237" t="s">
         <v>9</v>
@@ -35515,7 +35515,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G1238" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H1238" t="s">
         <v>9</v>
@@ -35541,7 +35541,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G1239" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H1239" t="s">
         <v>9</v>
@@ -35567,7 +35567,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1240" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1240" t="s">
         <v>9</v>
@@ -35593,7 +35593,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1241" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H1241" t="s">
         <v>9</v>
@@ -35619,7 +35619,7 @@
         <v>18.5</v>
       </c>
       <c r="G1242" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H1242" t="s">
         <v>9</v>
@@ -35645,7 +35645,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1243" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H1243" t="s">
         <v>9</v>
@@ -35671,7 +35671,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G1244" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H1244" t="s">
         <v>9</v>
@@ -35697,7 +35697,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G1245" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H1245" t="s">
         <v>9</v>
@@ -35723,7 +35723,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1246" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H1246" t="s">
         <v>9</v>
@@ -35749,7 +35749,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1247" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H1247" t="s">
         <v>9</v>
@@ -35775,7 +35775,7 @@
         <v>17.75</v>
       </c>
       <c r="G1248" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H1248" t="s">
         <v>9</v>
@@ -35801,7 +35801,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1249" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H1249" t="s">
         <v>9</v>
@@ -35827,7 +35827,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1250" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H1250" t="s">
         <v>9</v>
@@ -35853,7 +35853,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1251" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H1251" t="s">
         <v>9</v>
@@ -35879,7 +35879,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G1252" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H1252" t="s">
         <v>9</v>
@@ -35905,7 +35905,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1253" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H1253" t="s">
         <v>9</v>
@@ -35931,7 +35931,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1254" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H1254" t="s">
         <v>9</v>
@@ -35957,7 +35957,7 @@
         <v>18.0499992370605</v>
       </c>
       <c r="G1255" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H1255" t="s">
         <v>9</v>
@@ -35983,7 +35983,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1256" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H1256" t="s">
         <v>9</v>
@@ -36009,7 +36009,7 @@
         <v>18</v>
       </c>
       <c r="G1257" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H1257" t="s">
         <v>9</v>
@@ -36035,7 +36035,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G1258" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H1258" t="s">
         <v>9</v>
@@ -36061,7 +36061,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G1259" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H1259" t="s">
         <v>9</v>
@@ -36087,7 +36087,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1260" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H1260" t="s">
         <v>9</v>
@@ -36113,7 +36113,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1261" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H1261" t="s">
         <v>9</v>
@@ -36139,7 +36139,7 @@
         <v>19</v>
       </c>
       <c r="G1262" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H1262" t="s">
         <v>9</v>
@@ -36165,7 +36165,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1263" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H1263" t="s">
         <v>9</v>
@@ -36191,7 +36191,7 @@
         <v>19.5</v>
       </c>
       <c r="G1264" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H1264" t="s">
         <v>9</v>
@@ -36217,7 +36217,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G1265" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H1265" t="s">
         <v>9</v>
@@ -36243,7 +36243,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G1266" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H1266" t="s">
         <v>9</v>
@@ -36269,7 +36269,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G1267" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H1267" t="s">
         <v>9</v>
@@ -36295,7 +36295,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G1268" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H1268" t="s">
         <v>9</v>
@@ -36321,7 +36321,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1269" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H1269" t="s">
         <v>9</v>
@@ -36347,7 +36347,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1270" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H1270" t="s">
         <v>9</v>
@@ -36373,7 +36373,7 @@
         <v>21.5</v>
       </c>
       <c r="G1271" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H1271" t="s">
         <v>9</v>
@@ -36399,7 +36399,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1272" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H1272" t="s">
         <v>9</v>
@@ -36425,7 +36425,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G1273" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H1273" t="s">
         <v>9</v>
@@ -36451,7 +36451,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1274" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H1274" t="s">
         <v>9</v>
@@ -36477,7 +36477,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G1275" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H1275" t="s">
         <v>9</v>
@@ -36503,7 +36503,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G1276" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H1276" t="s">
         <v>9</v>
@@ -36529,7 +36529,7 @@
         <v>22.5</v>
       </c>
       <c r="G1277" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H1277" t="s">
         <v>9</v>
@@ -36555,7 +36555,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G1278" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H1278" t="s">
         <v>9</v>
@@ -36581,7 +36581,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G1279" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H1279" t="s">
         <v>9</v>
@@ -36607,7 +36607,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G1280" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H1280" t="s">
         <v>9</v>
@@ -36633,7 +36633,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G1281" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H1281" t="s">
         <v>9</v>
@@ -36659,7 +36659,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1282" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H1282" t="s">
         <v>9</v>
@@ -36685,7 +36685,7 @@
         <v>23</v>
       </c>
       <c r="G1283" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H1283" t="s">
         <v>9</v>
@@ -36711,7 +36711,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G1284" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H1284" t="s">
         <v>9</v>
@@ -36737,7 +36737,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G1285" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H1285" t="s">
         <v>9</v>
@@ -36763,7 +36763,7 @@
         <v>23.5</v>
       </c>
       <c r="G1286" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H1286" t="s">
         <v>9</v>
@@ -36789,7 +36789,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G1287" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H1287" t="s">
         <v>9</v>
@@ -36841,7 +36841,7 @@
         <v>23.5</v>
       </c>
       <c r="G1289" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H1289" t="s">
         <v>9</v>
@@ -70337,7 +70337,7 @@
     </row>
     <row r="2578">
       <c r="A2578" s="1" t="n">
-        <v>46076.6911689815</v>
+        <v>46076.3333333333</v>
       </c>
       <c r="B2578" t="n">
         <v>5306</v>
@@ -70358,6 +70358,32 @@
         <v>974</v>
       </c>
       <c r="H2578" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2579">
+      <c r="A2579" s="1" t="n">
+        <v>46077.6912037037</v>
+      </c>
+      <c r="B2579" t="n">
+        <v>2417</v>
+      </c>
+      <c r="C2579" t="n">
+        <v>20.7000007629395</v>
+      </c>
+      <c r="D2579" t="n">
+        <v>20.2999992370605</v>
+      </c>
+      <c r="E2579" t="n">
+        <v>20.6000003814697</v>
+      </c>
+      <c r="F2579" t="n">
+        <v>20.3999996185303</v>
+      </c>
+      <c r="G2579" t="s">
+        <v>970</v>
+      </c>
+      <c r="H2579" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IWB.MI.xlsx
+++ b/data/IWB.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="999" uniqueCount="999">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1000" uniqueCount="1000">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,31 +38,31 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84661674499512</t>
+    <t xml:space="preserve">7.84661626815796</t>
   </si>
   <si>
     <t xml:space="preserve">IWB.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79867315292358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8306360244751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74274110794067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75073099136353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71078014373779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6947979927063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59092235565186</t>
+    <t xml:space="preserve">7.79867506027222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83063650131226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74274015426636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75073051452637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71077966690063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69479846954346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59092283248901</t>
   </si>
   <si>
     <t xml:space="preserve">7.51101589202881</t>
@@ -71,37 +71,37 @@
     <t xml:space="preserve">7.31125640869141</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44709348678589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35120916366577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29527568817139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26331520080566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29927206039429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2912802696228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27130556106567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24733304977417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3751802444458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43111276626587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47106456756592</t>
+    <t xml:space="preserve">7.44709396362305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35120868682861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29527616500854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26331424713135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2992696762085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29128122329712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27130365371704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24733257293701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37517976760864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43111371994019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47106647491455</t>
   </si>
   <si>
     <t xml:space="preserve">7.15144729614258</t>
@@ -110,130 +110,130 @@
     <t xml:space="preserve">7.41513204574585</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32723665237427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28728485107422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99163961410522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11149597167969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19139957427979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25532293319702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41912746429443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42312240600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63087463378906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67082738876343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49903202056885</t>
+    <t xml:space="preserve">7.32723760604858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28728532791138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99163913726807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11149549484253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1914005279541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25532341003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41912651062012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42312335968018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63087320327759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67082691192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49903249740601</t>
   </si>
   <si>
     <t xml:space="preserve">7.58293104171753</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89455842971802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98645067214966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91053867340088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54297876358032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82264471054077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64285945892334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62288427352905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77470350265503</t>
+    <t xml:space="preserve">7.89456033706665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9864501953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91053915023804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54297924041748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82264614105225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64286088943481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62288331985474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77470302581787</t>
   </si>
   <si>
     <t xml:space="preserve">7.7667121887207</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79068279266357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8705883026123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96647357940674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71876907348633</t>
+    <t xml:space="preserve">7.79068326950073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87058734893799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96647262573242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7187671661377</t>
   </si>
   <si>
     <t xml:space="preserve">7.66283512115479</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57094669342041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55896234512329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39116144180298</t>
+    <t xml:space="preserve">7.57094621658325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55896139144897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3911600112915</t>
   </si>
   <si>
     <t xml:space="preserve">7.46307563781738</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60690212249756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5469765663147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36718988418579</t>
+    <t xml:space="preserve">7.60690355300903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54697465896606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36718940734863</t>
   </si>
   <si>
     <t xml:space="preserve">7.31525087356567</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33123302459717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34721183776855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50302743911743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24333763122559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22336149215698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23934173583984</t>
+    <t xml:space="preserve">7.33123254776001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34721326828003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50302839279175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24333810806274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2233624458313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23934268951416</t>
   </si>
   <si>
     <t xml:space="preserve">7.45907974243164</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46707105636597</t>
+    <t xml:space="preserve">7.46706962585449</t>
   </si>
   <si>
     <t xml:space="preserve">7.10350608825684</t>
@@ -242,40 +242,40 @@
     <t xml:space="preserve">6.89974927902222</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91173410415649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9516863822937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0076208114624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8717827796936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87577772140503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87977170944214</t>
+    <t xml:space="preserve">6.91173315048218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95168685913086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00762033462524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87178325653076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87577676773071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87977266311646</t>
   </si>
   <si>
     <t xml:space="preserve">6.86778688430786</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75192594528198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74393463134766</t>
+    <t xml:space="preserve">6.75192642211914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74393558502197</t>
   </si>
   <si>
     <t xml:space="preserve">6.82383966445923</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6640305519104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8318305015564</t>
+    <t xml:space="preserve">6.66403007507324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83183002471924</t>
   </si>
   <si>
     <t xml:space="preserve">6.89575338363647</t>
@@ -287,7 +287,7 @@
     <t xml:space="preserve">7.07154369354248</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33522748947144</t>
+    <t xml:space="preserve">7.33522891998291</t>
   </si>
   <si>
     <t xml:space="preserve">7.25931882858276</t>
@@ -296,10 +296,10 @@
     <t xml:space="preserve">7.17941427230835</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26730966567993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23135137557983</t>
+    <t xml:space="preserve">7.26731061935425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23135328292847</t>
   </si>
   <si>
     <t xml:space="preserve">7.09551525115967</t>
@@ -308,13 +308,13 @@
     <t xml:space="preserve">7.18340921401978</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18740558624268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20738172531128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14345741271973</t>
+    <t xml:space="preserve">7.1874041557312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20738220214844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14345645904541</t>
   </si>
   <si>
     <t xml:space="preserve">7.12348222732544</t>
@@ -323,25 +323,25 @@
     <t xml:space="preserve">7.23534727096558</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74673557281494</t>
+    <t xml:space="preserve">7.7467360496521</t>
   </si>
   <si>
     <t xml:space="preserve">7.83463144302368</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98245286941528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9265193939209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78269100189209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63886499404907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73474979400635</t>
+    <t xml:space="preserve">7.98245334625244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92652130126953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78269195556641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63886594772339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73475074768066</t>
   </si>
   <si>
     <t xml:space="preserve">8.07034969329834</t>
@@ -350,10 +350,10 @@
     <t xml:space="preserve">8.21417617797852</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16623592376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18221569061279</t>
+    <t xml:space="preserve">8.16623687744141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18221378326416</t>
   </si>
   <si>
     <t xml:space="preserve">8.27011108398438</t>
@@ -362,73 +362,73 @@
     <t xml:space="preserve">8.57374572753906</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54977607727051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35001277923584</t>
+    <t xml:space="preserve">8.54977703094482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35001373291016</t>
   </si>
   <si>
     <t xml:space="preserve">8.46987056732178</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52580261230469</t>
+    <t xml:space="preserve">8.52580451965332</t>
   </si>
   <si>
     <t xml:space="preserve">8.50982284545898</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59771823883057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60571002960205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58173656463623</t>
+    <t xml:space="preserve">8.59771919250488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60570907592773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58173751831055</t>
   </si>
   <si>
     <t xml:space="preserve">8.64687347412109</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67129993438721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61430740356445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63058948516846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75271987915039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82600021362305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87485027313232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95627307891846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74457931518555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.858567237854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84228229522705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91556167602539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03769302368164</t>
+    <t xml:space="preserve">8.67130088806152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61430358886719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63059139251709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75272083282471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82599925994873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87485122680664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95627212524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74458026885986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85856819152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84228420257568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91556262969971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03769397735596</t>
   </si>
   <si>
     <t xml:space="preserve">9.00512599945068</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94813060760498</t>
+    <t xml:space="preserve">8.94812965393066</t>
   </si>
   <si>
     <t xml:space="preserve">8.99698257446289</t>
@@ -437,16 +437,16 @@
     <t xml:space="preserve">9.1272554397583</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19239234924316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11911392211914</t>
+    <t xml:space="preserve">9.19239139556885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11911487579346</t>
   </si>
   <si>
     <t xml:space="preserve">9.14353942871094</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98069763183594</t>
+    <t xml:space="preserve">8.98069858551025</t>
   </si>
   <si>
     <t xml:space="preserve">9.13539791107178</t>
@@ -455,28 +455,28 @@
     <t xml:space="preserve">9.16796684265137</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15982341766357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18424987792969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15168190002441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07026195526123</t>
+    <t xml:space="preserve">9.15982437133789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.184250831604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1516809463501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07026100158691</t>
   </si>
   <si>
     <t xml:space="preserve">8.96441459655762</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92370414733887</t>
+    <t xml:space="preserve">8.92370510101318</t>
   </si>
   <si>
     <t xml:space="preserve">8.80157279968262</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79343223571777</t>
+    <t xml:space="preserve">8.79343128204346</t>
   </si>
   <si>
     <t xml:space="preserve">8.8667106628418</t>
@@ -485,187 +485,187 @@
     <t xml:space="preserve">8.90741920471191</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89113616943359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11097240447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20053291320801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28195476531982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35523319244385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39594554901123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32266616821289</t>
+    <t xml:space="preserve">8.89113521575928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11097145080566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20053577423096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28195571899414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35523414611816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39594459533691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32266426086426</t>
   </si>
   <si>
     <t xml:space="preserve">9.64834880828857</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60763931274414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90075016021729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99031543731689</t>
+    <t xml:space="preserve">9.60763835906982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90075206756592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99031448364258</t>
   </si>
   <si>
     <t xml:space="preserve">10.1205883026123</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1368722915649</t>
+    <t xml:space="preserve">10.1368732452393</t>
   </si>
   <si>
     <t xml:space="preserve">10.1775827407837</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1043033599854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1531572341919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0961618423462</t>
+    <t xml:space="preserve">10.1043043136597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1531562805176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0961608886719</t>
   </si>
   <si>
     <t xml:space="preserve">9.94146251678467</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90889453887939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77048015594482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83561420440674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91703605651855</t>
+    <t xml:space="preserve">9.90889358520508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77047920227051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83561515808105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91703701019287</t>
   </si>
   <si>
     <t xml:space="preserve">9.7949047088623</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77862167358398</t>
+    <t xml:space="preserve">9.77862071990967</t>
   </si>
   <si>
     <t xml:space="preserve">9.78676319122314</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9577465057373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0147409439087</t>
+    <t xml:space="preserve">9.95774555206299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.014741897583</t>
   </si>
   <si>
     <t xml:space="preserve">9.99845790863037</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88446998596191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86004161834717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85190010070801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89260959625244</t>
+    <t xml:space="preserve">9.8844690322876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86003971099854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85189914703369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89261054992676</t>
   </si>
   <si>
     <t xml:space="preserve">10.2590036392212</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3404235839844</t>
+    <t xml:space="preserve">10.3404245376587</t>
   </si>
   <si>
     <t xml:space="preserve">10.4625539779663</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5276908874512</t>
+    <t xml:space="preserve">10.5276918411255</t>
   </si>
   <si>
     <t xml:space="preserve">10.5765428543091</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5439758300781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5358324050903</t>
+    <t xml:space="preserve">10.5439767837524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5358333587646</t>
   </si>
   <si>
     <t xml:space="preserve">10.5032644271851</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5521173477173</t>
+    <t xml:space="preserve">10.552116394043</t>
   </si>
   <si>
     <t xml:space="preserve">10.3485651016235</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4381265640259</t>
+    <t xml:space="preserve">10.4381284713745</t>
   </si>
   <si>
     <t xml:space="preserve">10.3241395950317</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3811349868774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3648481369019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4218463897705</t>
+    <t xml:space="preserve">10.3811340332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3648509979248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4218444824219</t>
   </si>
   <si>
     <t xml:space="preserve">10.4137020111084</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3729915618896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3892765045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2915716171265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2671461105347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2264347076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.193865776062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3159980773926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2182931900024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2834300994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4299879074097</t>
+    <t xml:space="preserve">10.3729906082153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.389274597168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2915706634521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2671451568604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2264337539673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1938667297363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3159971237183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2182922363281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.283429145813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.429986000061</t>
   </si>
   <si>
     <t xml:space="preserve">10.3322811126709</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2427206039429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5846872329712</t>
+    <t xml:space="preserve">10.2427186965942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5846853256226</t>
   </si>
   <si>
     <t xml:space="preserve">10.6661052703857</t>
@@ -680,58 +680,58 @@
     <t xml:space="preserve">10.7882375717163</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6253957748413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8696594238281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8289480209351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0325002670288</t>
+    <t xml:space="preserve">10.6253967285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8696584701538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8289489746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0324983596802</t>
   </si>
   <si>
     <t xml:space="preserve">11.2360515594482</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4396018981934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6838665008545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0732088088989</t>
+    <t xml:space="preserve">11.439603805542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6838645935059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0732097625732</t>
   </si>
   <si>
     <t xml:space="preserve">10.9917888641357</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1546306610107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3174705505371</t>
+    <t xml:space="preserve">11.1546316146851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3174715042114</t>
   </si>
   <si>
     <t xml:space="preserve">11.2767610549927</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1953420639038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3581819534302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4839181900024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5258312225342</t>
+    <t xml:space="preserve">11.1953401565552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3581809997559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4839172363281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5258302688599</t>
   </si>
   <si>
     <t xml:space="preserve">11.5677423477173</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4000940322876</t>
+    <t xml:space="preserve">11.4000930786133</t>
   </si>
   <si>
     <t xml:space="preserve">11.0228843688965</t>
@@ -740,286 +740,286 @@
     <t xml:space="preserve">11.1486215591431</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2324457168579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1905345916748</t>
+    <t xml:space="preserve">11.2324447631836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1905336380005</t>
   </si>
   <si>
     <t xml:space="preserve">11.274356842041</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8971500396729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0647964477539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3581829071045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4420051574707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8552370071411</t>
+    <t xml:space="preserve">10.8971481323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0647974014282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.442006111145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8552350997925</t>
   </si>
   <si>
     <t xml:space="preserve">10.6875886917114</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3254728317261</t>
+    <t xml:space="preserve">11.3254737854004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2822465896606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1957912445068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0228853225708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2390203475952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1525659561157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.936429977417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0661134719849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1093406677246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9796571731567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7635231018066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5906143188477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8499765396118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7202968597412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6770696640015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8067512512207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8932037353516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6338424682617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4119281768799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4551553726196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3687000274658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5416097640991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6280632019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5848350524902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4609346389771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3312530517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3744792938232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2880239486694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5041608810425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0286626815796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94221019744873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59639453887939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63962078094482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81253051757812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85575675964355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55316734313965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03444385528564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81830883026123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86153602600098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77508068084717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07767200469971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16412544250488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25057888031006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33703231811523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2938060760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2447986602783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68284797668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1583452224731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98543834686279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89898300170898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76930236816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72607421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46671295166016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5099401473999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3802604675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42348670959473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20735168457031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0718908309937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2972898483276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2077484130859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1629772186279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3420610427856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4316005706787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3868312835693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1182060241699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2525186538696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4763708114624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6554555892944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7897691726685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7449970245361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5659141540527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7002277374268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1031646728516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9688529968262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9240818023682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8793096542358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1479349136353</t>
   </si>
   <si>
     <t xml:space="preserve">11.282247543335</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1957941055298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0228862762451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2390222549438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1525659561157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9364309310913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0661134719849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1093397140503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9796571731567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7635231018066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5906162261963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8499774932861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7202968597412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6770687103271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8067512512207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8932046890259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6338424682617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4119272232056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4551553726196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3687000274658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5416107177734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6280632019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5848360061646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4609336853027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3312530517578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3744812011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2880268096924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5041599273682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0286645889282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94221019744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59639358520508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63961982727051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81252861022949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85575675964355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55316734313965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03444385528564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8183069229126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86153507232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77508068084717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07766914367676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16412353515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25057792663574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33703327178955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29380416870117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.244800567627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68284893035889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1583452224731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98543739318848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8989839553833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76930141448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72607421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46671295166016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5099401473999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38025951385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42348480224609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.207350730896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.071891784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2972898483276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2077474594116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1629772186279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3420610427856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4316024780273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3868312835693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1182050704956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2525196075439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.476372718811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6554555892944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7897682189941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7449979782104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5659151077271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7002267837524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1031637191772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9688520431519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9240818023682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8793096542358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1479349136353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2374773025513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4613313674927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.327018737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1927061080933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3717880249023</t>
+    <t xml:space="preserve">11.237476348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4613304138184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3270177841187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1927051544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.371789932251</t>
   </si>
   <si>
     <t xml:space="preserve">11.4165601730347</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0583944320679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6404151916504</t>
+    <t xml:space="preserve">11.0583934783936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6404142379761</t>
   </si>
   <si>
     <t xml:space="preserve">11.7299556732178</t>
@@ -1028,49 +1028,49 @@
     <t xml:space="preserve">11.6851844787598</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7747268676758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8194961547852</t>
+    <t xml:space="preserve">11.7747259140015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8194971084595</t>
   </si>
   <si>
     <t xml:space="preserve">11.8642683029175</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5508718490601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5956439971924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.521143913269</t>
+    <t xml:space="preserve">11.5508728027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5956430435181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5211429595947</t>
   </si>
   <si>
     <t xml:space="preserve">11.0136232376099</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8345384597778</t>
+    <t xml:space="preserve">10.8345394134521</t>
   </si>
   <si>
     <t xml:space="preserve">11.9985799789429</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0881223678589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0433511734009</t>
+    <t xml:space="preserve">12.0881204605103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0433502197266</t>
   </si>
   <si>
     <t xml:space="preserve">12.1328935623169</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2224349975586</t>
+    <t xml:space="preserve">12.2224340438843</t>
   </si>
   <si>
     <t xml:space="preserve">12.1776638031006</t>
   </si>
   <si>
-    <t xml:space="preserve">12.356746673584</t>
+    <t xml:space="preserve">12.3567476272583</t>
   </si>
   <si>
     <t xml:space="preserve">12.2672052383423</t>
@@ -1079,10 +1079,10 @@
     <t xml:space="preserve">12.401517868042</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3119764328003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6701431274414</t>
+    <t xml:space="preserve">12.3119773864746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6701421737671</t>
   </si>
   <si>
     <t xml:space="preserve">12.6253728866577</t>
@@ -1091,16 +1091,16 @@
     <t xml:space="preserve">12.5806016921997</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6106872558594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6257266998291</t>
+    <t xml:space="preserve">10.6106843948364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62572860717773</t>
   </si>
   <si>
     <t xml:space="preserve">10.0734348297119</t>
   </si>
   <si>
-    <t xml:space="preserve">12.491060256958</t>
+    <t xml:space="preserve">12.4910583496094</t>
   </si>
   <si>
     <t xml:space="preserve">11.9090394973755</t>
@@ -1112,10 +1112,10 @@
     <t xml:space="preserve">13.6998720169067</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8789548873901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0132665634155</t>
+    <t xml:space="preserve">13.8789539337158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0132684707642</t>
   </si>
   <si>
     <t xml:space="preserve">14.1475801467896</t>
@@ -1124,55 +1124,55 @@
     <t xml:space="preserve">14.2371215820312</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1923513412476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9237260818481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9684972763062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7894134521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2818927764893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8341846466064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5207891464233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.431245803833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.565559387207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6103296279907</t>
+    <t xml:space="preserve">14.1923522949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9237270355225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9684963226318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7894124984741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2818918228149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8341827392578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5207901000977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4312477111816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5655584335327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.610330581665</t>
   </si>
   <si>
     <t xml:space="preserve">13.7004632949829</t>
   </si>
   <si>
-    <t xml:space="preserve">13.790599822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8356657028198</t>
+    <t xml:space="preserve">13.7905988693237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8356666564941</t>
   </si>
   <si>
     <t xml:space="preserve">13.6553964614868</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5201950073242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.610330581665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2948579788208</t>
+    <t xml:space="preserve">13.5201940536499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6103315353394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2948589324951</t>
   </si>
   <si>
     <t xml:space="preserve">13.1596565246582</t>
@@ -1187,13 +1187,13 @@
     <t xml:space="preserve">12.708984375</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5737819671631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6188478469849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3399257659912</t>
+    <t xml:space="preserve">12.5737810134888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6188497543335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3399267196655</t>
   </si>
   <si>
     <t xml:space="preserve">13.1145896911621</t>
@@ -1202,10 +1202,10 @@
     <t xml:space="preserve">13.4751281738281</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9343214035034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7540502548218</t>
+    <t xml:space="preserve">12.9343204498291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7540512084961</t>
   </si>
   <si>
     <t xml:space="preserve">12.8441858291626</t>
@@ -1214,7 +1214,7 @@
     <t xml:space="preserve">14.0610027313232</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8807334899902</t>
+    <t xml:space="preserve">13.8807325363159</t>
   </si>
   <si>
     <t xml:space="preserve">14.1962051391602</t>
@@ -1223,25 +1223,25 @@
     <t xml:space="preserve">14.3314075469971</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4215421676636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3764743804932</t>
+    <t xml:space="preserve">14.4215412139893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3764734268188</t>
   </si>
   <si>
     <t xml:space="preserve">14.5116767883301</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4666090011597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6018123626709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6919450759888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8722143173218</t>
+    <t xml:space="preserve">14.4666080474854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6018104553223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6919441223145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8722162246704</t>
   </si>
   <si>
     <t xml:space="preserve">15.2327518463135</t>
@@ -1250,46 +1250,46 @@
     <t xml:space="preserve">15.0074167251587</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3228883743286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1876859664917</t>
+    <t xml:space="preserve">15.3228893280029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.187686920166</t>
   </si>
   <si>
     <t xml:space="preserve">16.2242336273193</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9538307189941</t>
+    <t xml:space="preserve">15.9538326263428</t>
   </si>
   <si>
     <t xml:space="preserve">16.8551750183105</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3143692016602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9903793334961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8101081848145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7565231323242</t>
+    <t xml:space="preserve">16.3143711090088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9903812408447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8101100921631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7565250396729</t>
   </si>
   <si>
     <t xml:space="preserve">18.0269260406494</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9367904663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3509178161621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4410533905029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.486120223999</t>
+    <t xml:space="preserve">17.9367923736572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3509159088135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4410514831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4861183166504</t>
   </si>
   <si>
     <t xml:space="preserve">17.0354442596436</t>
@@ -1301,7 +1301,7 @@
     <t xml:space="preserve">16.7199745178223</t>
   </si>
   <si>
-    <t xml:space="preserve">16.404504776001</t>
+    <t xml:space="preserve">16.4045028686523</t>
   </si>
   <si>
     <t xml:space="preserve">16.6749076843262</t>
@@ -1310,19 +1310,19 @@
     <t xml:space="preserve">16.9453105926514</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7650451660156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8636951446533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9988994598389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4946384429932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3594341278076</t>
+    <t xml:space="preserve">16.7650413513184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.863694190979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9988985061646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4946346282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3594360351562</t>
   </si>
   <si>
     <t xml:space="preserve">16.1791667938232</t>
@@ -1334,13 +1334,13 @@
     <t xml:space="preserve">16.5397052764893</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6834259033203</t>
+    <t xml:space="preserve">15.6834278106689</t>
   </si>
   <si>
     <t xml:space="preserve">16.0890312194824</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5932912826538</t>
+    <t xml:space="preserve">15.5932931900024</t>
   </si>
   <si>
     <t xml:space="preserve">16.2693023681641</t>
@@ -1349,16 +1349,16 @@
     <t xml:space="preserve">17.1255798339844</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5762519836426</t>
+    <t xml:space="preserve">17.5762538909912</t>
   </si>
   <si>
     <t xml:space="preserve">17.6663875579834</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8466567993164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5677375793457</t>
+    <t xml:space="preserve">17.846658706665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5677356719971</t>
   </si>
   <si>
     <t xml:space="preserve">18.3874664306641</t>
@@ -1373,91 +1373,91 @@
     <t xml:space="preserve">20.0098896026611</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5506973266602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.460563659668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2802925109863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3704280853271</t>
+    <t xml:space="preserve">20.5506954193115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4605617523193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2802906036377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3704299926758</t>
   </si>
   <si>
     <t xml:space="preserve">20.1000232696533</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6408309936523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7309646606445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4435234069824</t>
+    <t xml:space="preserve">20.6408290863037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7309665679932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4435253143311</t>
   </si>
   <si>
     <t xml:space="preserve">21.9027156829834</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5361461639404</t>
+    <t xml:space="preserve">21.5361423492432</t>
   </si>
   <si>
     <t xml:space="preserve">21.1695709228516</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7194309234619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3609313964844</t>
+    <t xml:space="preserve">21.7194290161133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.360933303833</t>
   </si>
   <si>
     <t xml:space="preserve">22.4525756835938</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2692890167236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0860004425049</t>
+    <t xml:space="preserve">22.269287109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0860023498535</t>
   </si>
   <si>
     <t xml:space="preserve">21.9943599700928</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6277866363525</t>
+    <t xml:space="preserve">21.6277885437012</t>
   </si>
   <si>
     <t xml:space="preserve">23.2773628234863</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9107913970947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7275047302246</t>
+    <t xml:space="preserve">22.9107894897461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.727502822876</t>
   </si>
   <si>
     <t xml:space="preserve">22.1776466369629</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6358642578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0024356842041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0940780639648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1021518707275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.285436630249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9269390106201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2099437713623</t>
+    <t xml:space="preserve">22.6358623504639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0024337768555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0940799713135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1021499633789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2854385375977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9269409179688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2099456787109</t>
   </si>
   <si>
     <t xml:space="preserve">26.8514442443848</t>
@@ -1466,46 +1466,46 @@
     <t xml:space="preserve">26.6681594848633</t>
   </si>
   <si>
-    <t xml:space="preserve">27.309663772583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4848747253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.759801864624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5765171051025</t>
+    <t xml:space="preserve">27.3096618652344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4848728179932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7598056793213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5765190124512</t>
   </si>
   <si>
     <t xml:space="preserve">26.3015880584717</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5684452056885</t>
+    <t xml:space="preserve">25.5684432983398</t>
   </si>
   <si>
     <t xml:space="preserve">27.0347328186035</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1425266265869</t>
+    <t xml:space="preserve">29.1425247192383</t>
   </si>
   <si>
     <t xml:space="preserve">28.4093818664551</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1344528198242</t>
+    <t xml:space="preserve">28.1344509124756</t>
   </si>
   <si>
     <t xml:space="preserve">28.2260932922363</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3646831512451</t>
+    <t xml:space="preserve">28.3646869659424</t>
   </si>
   <si>
     <t xml:space="preserve">28.4570770263672</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0875015258789</t>
+    <t xml:space="preserve">28.0875053405762</t>
   </si>
   <si>
     <t xml:space="preserve">27.9951114654541</t>
@@ -1514,7 +1514,7 @@
     <t xml:space="preserve">27.9027194976807</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7179336547852</t>
+    <t xml:space="preserve">27.7179317474365</t>
   </si>
   <si>
     <t xml:space="preserve">29.1038284301758</t>
@@ -1523,7 +1523,7 @@
     <t xml:space="preserve">29.9353694915771</t>
   </si>
   <si>
-    <t xml:space="preserve">29.750581741333</t>
+    <t xml:space="preserve">29.7505836486816</t>
   </si>
   <si>
     <t xml:space="preserve">29.3810081481934</t>
@@ -1532,49 +1532,49 @@
     <t xml:space="preserve">28.8266506195068</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9190406799316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7342567443848</t>
+    <t xml:space="preserve">28.9190425872803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7342548370361</t>
   </si>
   <si>
     <t xml:space="preserve">29.0114364624023</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8429737091064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1201496124268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2125453948975</t>
+    <t xml:space="preserve">29.8429756164551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1201515197754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2125473022461</t>
   </si>
   <si>
     <t xml:space="preserve">30.0277614593506</t>
   </si>
   <si>
-    <t xml:space="preserve">30.397331237793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.136474609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.859302520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0440845489502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6745147705078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4897270202637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2886180877686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4734020233154</t>
+    <t xml:space="preserve">30.3973331451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1364784240723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8592987060547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0440826416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6745109558105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.489725112915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2886161804199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4734001159668</t>
   </si>
   <si>
     <t xml:space="preserve">32.8919448852539</t>
@@ -1583,19 +1583,19 @@
     <t xml:space="preserve">33.3539085388184</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5550231933594</t>
+    <t xml:space="preserve">34.5550193786621</t>
   </si>
   <si>
     <t xml:space="preserve">34.0930595397949</t>
   </si>
   <si>
-    <t xml:space="preserve">35.8485221862793</t>
+    <t xml:space="preserve">35.8485260009766</t>
   </si>
   <si>
     <t xml:space="preserve">37.4192085266113</t>
   </si>
   <si>
-    <t xml:space="preserve">40.0986099243164</t>
+    <t xml:space="preserve">40.0986137390137</t>
   </si>
   <si>
     <t xml:space="preserve">37.2344207763672</t>
@@ -1610,7 +1610,7 @@
     <t xml:space="preserve">37.6039962768555</t>
   </si>
   <si>
-    <t xml:space="preserve">37.6963844299316</t>
+    <t xml:space="preserve">37.6963882446289</t>
   </si>
   <si>
     <t xml:space="preserve">37.7887840270996</t>
@@ -1619,34 +1619,34 @@
     <t xml:space="preserve">37.142032623291</t>
   </si>
   <si>
-    <t xml:space="preserve">38.5279312133789</t>
+    <t xml:space="preserve">38.5279273986816</t>
   </si>
   <si>
     <t xml:space="preserve">38.3431396484375</t>
   </si>
   <si>
-    <t xml:space="preserve">36.4952812194824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.9409217834473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.4028854370117</t>
+    <t xml:space="preserve">36.4952774047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.9409255981445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.402889251709</t>
   </si>
   <si>
     <t xml:space="preserve">36.6800651550293</t>
   </si>
   <si>
-    <t xml:space="preserve">37.9735679626465</t>
+    <t xml:space="preserve">37.9735717773438</t>
   </si>
   <si>
     <t xml:space="preserve">38.0659637451172</t>
   </si>
   <si>
-    <t xml:space="preserve">38.4355316162109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.8051071166992</t>
+    <t xml:space="preserve">38.4355278015137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.805103302002</t>
   </si>
   <si>
     <t xml:space="preserve">39.3594665527344</t>
@@ -1655,10 +1655,10 @@
     <t xml:space="preserve">39.8214263916016</t>
   </si>
   <si>
-    <t xml:space="preserve">40.006217956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.5605773925781</t>
+    <t xml:space="preserve">40.0062141418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.5605735778809</t>
   </si>
   <si>
     <t xml:space="preserve">40.6529693603516</t>
@@ -1670,55 +1670,55 @@
     <t xml:space="preserve">41.114933013916</t>
   </si>
   <si>
-    <t xml:space="preserve">40.9301452636719</t>
+    <t xml:space="preserve">40.9301528930664</t>
   </si>
   <si>
     <t xml:space="preserve">42.3160438537598</t>
   </si>
   <si>
-    <t xml:space="preserve">43.5171546936035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.0715141296387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.8867225646973</t>
+    <t xml:space="preserve">43.5171508789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.0715103149414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.8867263793945</t>
   </si>
   <si>
     <t xml:space="preserve">43.7019386291504</t>
   </si>
   <si>
-    <t xml:space="preserve">43.9791145324707</t>
+    <t xml:space="preserve">43.979118347168</t>
   </si>
   <si>
     <t xml:space="preserve">44.348690032959</t>
   </si>
   <si>
-    <t xml:space="preserve">44.9954452514648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.8106536865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.5334777832031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.7943344116211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.1475830078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.3921127319336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.854076385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.576904296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.2073249816895</t>
+    <t xml:space="preserve">44.9954490661621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.810661315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.5334739685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.7943420410156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.1475791931152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.3921089172363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.8540802001953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.5768966674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.2073211669922</t>
   </si>
   <si>
     <t xml:space="preserve">40.1910018920898</t>
@@ -1727,43 +1727,43 @@
     <t xml:space="preserve">39.4518585205078</t>
   </si>
   <si>
-    <t xml:space="preserve">38.9898948669434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.1746788024902</t>
+    <t xml:space="preserve">38.9898910522461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.1746826171875</t>
   </si>
   <si>
     <t xml:space="preserve">39.5442504882812</t>
   </si>
   <si>
-    <t xml:space="preserve">40.7453575134277</t>
+    <t xml:space="preserve">40.745361328125</t>
   </si>
   <si>
     <t xml:space="preserve">41.0225410461426</t>
   </si>
   <si>
-    <t xml:space="preserve">39.7290306091309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.9138221740723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.4681777954102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.6366424560547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.6203231811523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.2670707702637</t>
+    <t xml:space="preserve">39.7290344238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.9138259887695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.4681816101074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.6366386413574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.6203155517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.2670745849609</t>
   </si>
   <si>
     <t xml:space="preserve">37.3268203735352</t>
   </si>
   <si>
-    <t xml:space="preserve">38.8974952697754</t>
+    <t xml:space="preserve">38.8974990844727</t>
   </si>
   <si>
     <t xml:space="preserve">37.5116004943848</t>
@@ -1781,13 +1781,13 @@
     <t xml:space="preserve">36.310489654541</t>
   </si>
   <si>
-    <t xml:space="preserve">36.2180938720703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.3865547180176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.0333099365234</t>
+    <t xml:space="preserve">36.2181015014648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.3865585327148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.0333137512207</t>
   </si>
   <si>
     <t xml:space="preserve">34.1854515075684</t>
@@ -1796,7 +1796,7 @@
     <t xml:space="preserve">33.7234840393066</t>
   </si>
   <si>
-    <t xml:space="preserve">33.1691284179688</t>
+    <t xml:space="preserve">33.1691246032715</t>
   </si>
   <si>
     <t xml:space="preserve">32.6147651672363</t>
@@ -1808,37 +1808,37 @@
     <t xml:space="preserve">32.707160949707</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9680118560791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0604095458984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4136581420898</t>
+    <t xml:space="preserve">31.9680156707764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0604133605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4136562347412</t>
   </si>
   <si>
     <t xml:space="preserve">31.6908378601074</t>
   </si>
   <si>
-    <t xml:space="preserve">32.2451972961426</t>
+    <t xml:space="preserve">32.2452011108398</t>
   </si>
   <si>
     <t xml:space="preserve">32.7995529174805</t>
   </si>
   <si>
-    <t xml:space="preserve">33.9082717895508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.1093864440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7398071289062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.0169906616211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.337589263916</t>
+    <t xml:space="preserve">33.9082679748535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.1093826293945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.739803314209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.0169944763184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3375930786133</t>
   </si>
   <si>
     <t xml:space="preserve">32.4299774169922</t>
@@ -1847,34 +1847,34 @@
     <t xml:space="preserve">32.5223731994629</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5060482025146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3212623596191</t>
+    <t xml:space="preserve">31.5060501098633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3212661743164</t>
   </si>
   <si>
     <t xml:space="preserve">31.5522480010986</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9218235015869</t>
+    <t xml:space="preserve">31.9218196868896</t>
   </si>
   <si>
     <t xml:space="preserve">32.1528015136719</t>
   </si>
   <si>
-    <t xml:space="preserve">33.4924964904785</t>
+    <t xml:space="preserve">33.492504119873</t>
   </si>
   <si>
     <t xml:space="preserve">34.3702392578125</t>
   </si>
   <si>
-    <t xml:space="preserve">33.8620758056641</t>
+    <t xml:space="preserve">33.8620719909668</t>
   </si>
   <si>
     <t xml:space="preserve">32.1066017150879</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5359230041504</t>
+    <t xml:space="preserve">30.535924911499</t>
   </si>
   <si>
     <t xml:space="preserve">30.3511352539062</t>
@@ -1895,22 +1895,22 @@
     <t xml:space="preserve">27.7618713378906</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0863018035889</t>
+    <t xml:space="preserve">28.0862998962402</t>
   </si>
   <si>
     <t xml:space="preserve">27.9936084747314</t>
   </si>
   <si>
-    <t xml:space="preserve">28.642463684082</t>
+    <t xml:space="preserve">28.6424655914307</t>
   </si>
   <si>
     <t xml:space="preserve">29.5230579376221</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1255702972412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5694046020508</t>
+    <t xml:space="preserve">30.1255722045898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5694065093994</t>
   </si>
   <si>
     <t xml:space="preserve">29.105936050415</t>
@@ -1922,7 +1922,7 @@
     <t xml:space="preserve">27.7155227661133</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1130123138428</t>
+    <t xml:space="preserve">27.1130142211914</t>
   </si>
   <si>
     <t xml:space="preserve">26.4641532897949</t>
@@ -1931,7 +1931,7 @@
     <t xml:space="preserve">26.4178066253662</t>
   </si>
   <si>
-    <t xml:space="preserve">26.186071395874</t>
+    <t xml:space="preserve">26.1860733032227</t>
   </si>
   <si>
     <t xml:space="preserve">26.6031970977783</t>
@@ -1940,10 +1940,10 @@
     <t xml:space="preserve">26.2324180603027</t>
   </si>
   <si>
-    <t xml:space="preserve">26.556848526001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3251113891602</t>
+    <t xml:space="preserve">26.5568504333496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3251132965088</t>
   </si>
   <si>
     <t xml:space="preserve">25.8152980804443</t>
@@ -1952,19 +1952,19 @@
     <t xml:space="preserve">25.6299076080322</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2591323852539</t>
+    <t xml:space="preserve">25.2591304779053</t>
   </si>
   <si>
     <t xml:space="preserve">24.7029666900635</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6566200256348</t>
+    <t xml:space="preserve">24.6566219329834</t>
   </si>
   <si>
     <t xml:space="preserve">23.9614143371582</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7296810150146</t>
+    <t xml:space="preserve">23.729679107666</t>
   </si>
   <si>
     <t xml:space="preserve">25.0273971557617</t>
@@ -1976,7 +1976,7 @@
     <t xml:space="preserve">24.2858448028564</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6102714538574</t>
+    <t xml:space="preserve">24.6102733612061</t>
   </si>
   <si>
     <t xml:space="preserve">24.3321914672852</t>
@@ -1988,16 +1988,16 @@
     <t xml:space="preserve">24.3785381317139</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4712314605713</t>
+    <t xml:space="preserve">24.4712333679199</t>
   </si>
   <si>
     <t xml:space="preserve">23.8687210083008</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5442924499512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1004543304443</t>
+    <t xml:space="preserve">23.5442905426025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1004581451416</t>
   </si>
   <si>
     <t xml:space="preserve">23.4979457855225</t>
@@ -2012,19 +2012,19 @@
     <t xml:space="preserve">24.1931495666504</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8883533477783</t>
+    <t xml:space="preserve">24.888355255127</t>
   </si>
   <si>
     <t xml:space="preserve">25.5835609436035</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9543380737305</t>
+    <t xml:space="preserve">25.9543361663818</t>
   </si>
   <si>
     <t xml:space="preserve">26.6958885192871</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7885837554932</t>
+    <t xml:space="preserve">26.7885818481445</t>
   </si>
   <si>
     <t xml:space="preserve">26.7422370910645</t>
@@ -2036,16 +2036,16 @@
     <t xml:space="preserve">24.981050491333</t>
   </si>
   <si>
-    <t xml:space="preserve">25.861644744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1200923919678</t>
+    <t xml:space="preserve">25.8616428375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1200904846191</t>
   </si>
   <si>
     <t xml:space="preserve">24.0077610015869</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4515972137451</t>
+    <t xml:space="preserve">23.4515953063965</t>
   </si>
   <si>
     <t xml:space="preserve">23.1271686553955</t>
@@ -2054,25 +2054,25 @@
     <t xml:space="preserve">23.0808200836182</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3125553131104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6369876861572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5906410217285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.405252456665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2662086486816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3589057922363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8027400970459</t>
+    <t xml:space="preserve">23.312557220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6369857788086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5906391143799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4052505493164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2662105560303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3589038848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8027381896973</t>
   </si>
   <si>
     <t xml:space="preserve">22.6173515319824</t>
@@ -2093,7 +2093,7 @@
     <t xml:space="preserve">21.273286819458</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8561630249023</t>
+    <t xml:space="preserve">20.856164932251</t>
   </si>
   <si>
     <t xml:space="preserve">20.7171230316162</t>
@@ -2102,16 +2102,16 @@
     <t xml:space="preserve">19.9755687713623</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1609573364258</t>
+    <t xml:space="preserve">20.1609592437744</t>
   </si>
   <si>
     <t xml:space="preserve">20.2073040008545</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8365268707275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5584487915039</t>
+    <t xml:space="preserve">19.8365287780762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5584449768066</t>
   </si>
   <si>
     <t xml:space="preserve">19.604793548584</t>
@@ -2120,7 +2120,7 @@
     <t xml:space="preserve">19.9292221069336</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0682621002197</t>
+    <t xml:space="preserve">20.068265914917</t>
   </si>
   <si>
     <t xml:space="preserve">20.1146106719971</t>
@@ -2129,25 +2129,25 @@
     <t xml:space="preserve">20.8098182678223</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9952049255371</t>
+    <t xml:space="preserve">20.9952030181885</t>
   </si>
   <si>
     <t xml:space="preserve">20.5780811309814</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0879001617432</t>
+    <t xml:space="preserve">21.0878982543945</t>
   </si>
   <si>
     <t xml:space="preserve">21.5977172851562</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0611839294434</t>
+    <t xml:space="preserve">22.061185836792</t>
   </si>
   <si>
     <t xml:space="preserve">22.4319629669189</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3856143951416</t>
+    <t xml:space="preserve">22.3856163024902</t>
   </si>
   <si>
     <t xml:space="preserve">22.3392677307129</t>
@@ -2174,7 +2174,7 @@
     <t xml:space="preserve">25.768949508667</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7226028442383</t>
+    <t xml:space="preserve">25.7226009368896</t>
   </si>
   <si>
     <t xml:space="preserve">25.3518257141113</t>
@@ -2204,7 +2204,7 @@
     <t xml:space="preserve">27.2984027862549</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5764846801758</t>
+    <t xml:space="preserve">27.5764827728271</t>
   </si>
   <si>
     <t xml:space="preserve">28.0399551391602</t>
@@ -2225,22 +2225,22 @@
     <t xml:space="preserve">27.5301380157471</t>
   </si>
   <si>
-    <t xml:space="preserve">26.093376159668</t>
+    <t xml:space="preserve">26.0933780670166</t>
   </si>
   <si>
     <t xml:space="preserve">25.39817237854</t>
   </si>
   <si>
-    <t xml:space="preserve">22.941780090332</t>
+    <t xml:space="preserve">22.9417819976807</t>
   </si>
   <si>
     <t xml:space="preserve">22.2002277374268</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1538791656494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1075325012207</t>
+    <t xml:space="preserve">22.153881072998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1075344085693</t>
   </si>
   <si>
     <t xml:space="preserve">22.7100448608398</t>
@@ -2252,10 +2252,10 @@
     <t xml:space="preserve">23.2198619842529</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8294525146484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6244277954102</t>
+    <t xml:space="preserve">21.8294506072998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6244297027588</t>
   </si>
   <si>
     <t xml:space="preserve">20.6707744598389</t>
@@ -2270,10 +2270,10 @@
     <t xml:space="preserve">20.5317344665527</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1342468261719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7831058502197</t>
+    <t xml:space="preserve">21.1342449188232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7831039428711</t>
   </si>
   <si>
     <t xml:space="preserve">21.6440620422363</t>
@@ -2300,7 +2300,7 @@
     <t xml:space="preserve">21.4127311706543</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6213932037354</t>
+    <t xml:space="preserve">20.6213912963867</t>
   </si>
   <si>
     <t xml:space="preserve">20.5748443603516</t>
@@ -2324,16 +2324,16 @@
     <t xml:space="preserve">21.1799850463867</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2265357971191</t>
+    <t xml:space="preserve">21.2265338897705</t>
   </si>
   <si>
     <t xml:space="preserve">20.9472389221191</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4817428588867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3420944213867</t>
+    <t xml:space="preserve">20.4817447662354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3420963287354</t>
   </si>
   <si>
     <t xml:space="preserve">20.2489986419678</t>
@@ -2342,10 +2342,10 @@
     <t xml:space="preserve">20.1558990478516</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0162487030029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6904048919678</t>
+    <t xml:space="preserve">20.0162506103516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6904029846191</t>
   </si>
   <si>
     <t xml:space="preserve">19.6438541412354</t>
@@ -2384,16 +2384,16 @@
     <t xml:space="preserve">19.0387134552002</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9697017669678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9231491088867</t>
+    <t xml:space="preserve">19.9696998596191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9231510162354</t>
   </si>
   <si>
     <t xml:space="preserve">19.3645572662354</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1783618927002</t>
+    <t xml:space="preserve">19.1783599853516</t>
   </si>
   <si>
     <t xml:space="preserve">18.8990631103516</t>
@@ -2402,10 +2402,10 @@
     <t xml:space="preserve">19.1318111419678</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6197681427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8525142669678</t>
+    <t xml:space="preserve">18.6197662353516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8525123596191</t>
   </si>
   <si>
     <t xml:space="preserve">18.7128677368164</t>
@@ -2414,25 +2414,25 @@
     <t xml:space="preserve">18.6663150787354</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7594165802002</t>
+    <t xml:space="preserve">18.7594146728516</t>
   </si>
   <si>
     <t xml:space="preserve">18.5266666412354</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4708080291748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3963298797607</t>
+    <t xml:space="preserve">18.4708099365234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3963317871094</t>
   </si>
   <si>
     <t xml:space="preserve">18.3404712677002</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2287521362305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.210132598877</t>
+    <t xml:space="preserve">18.2287540435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2101306915283</t>
   </si>
   <si>
     <t xml:space="preserve">17.968074798584</t>
@@ -2441,7 +2441,7 @@
     <t xml:space="preserve">17.6701583862305</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5770606994629</t>
+    <t xml:space="preserve">17.5770587921143</t>
   </si>
   <si>
     <t xml:space="preserve">17.6887798309326</t>
@@ -2456,7 +2456,7 @@
     <t xml:space="preserve">17.3163833618164</t>
   </si>
   <si>
-    <t xml:space="preserve">17.130184173584</t>
+    <t xml:space="preserve">17.1301860809326</t>
   </si>
   <si>
     <t xml:space="preserve">16.7577896118164</t>
@@ -2465,13 +2465,13 @@
     <t xml:space="preserve">17.2232856750488</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3350048065186</t>
+    <t xml:space="preserve">17.3350028991699</t>
   </si>
   <si>
     <t xml:space="preserve">17.409481048584</t>
   </si>
   <si>
-    <t xml:space="preserve">17.651538848877</t>
+    <t xml:space="preserve">17.6515369415283</t>
   </si>
   <si>
     <t xml:space="preserve">17.7260189056396</t>
@@ -2516,7 +2516,7 @@
     <t xml:space="preserve">16.2922973632812</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0370864868164</t>
+    <t xml:space="preserve">17.037088394165</t>
   </si>
   <si>
     <t xml:space="preserve">16.813648223877</t>
@@ -2534,25 +2534,25 @@
     <t xml:space="preserve">16.1805782318115</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3667736053467</t>
+    <t xml:space="preserve">16.3667755126953</t>
   </si>
   <si>
     <t xml:space="preserve">16.4598751068115</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7709445953369</t>
+    <t xml:space="preserve">15.7709436416626</t>
   </si>
   <si>
     <t xml:space="preserve">15.7337017059326</t>
   </si>
   <si>
-    <t xml:space="preserve">15.882661819458</t>
+    <t xml:space="preserve">15.8826608657837</t>
   </si>
   <si>
     <t xml:space="preserve">16.161958694458</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1433372497559</t>
+    <t xml:space="preserve">16.1433391571045</t>
   </si>
   <si>
     <t xml:space="preserve">16.5157337188721</t>
@@ -2564,7 +2564,7 @@
     <t xml:space="preserve">16.6460704803467</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8695087432861</t>
+    <t xml:space="preserve">16.8695106506348</t>
   </si>
   <si>
     <t xml:space="preserve">17.1115665435791</t>
@@ -2573,19 +2573,19 @@
     <t xml:space="preserve">17.0184669494629</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0557079315186</t>
+    <t xml:space="preserve">17.0557060241699</t>
   </si>
   <si>
     <t xml:space="preserve">17.4839611053467</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3536205291748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.372241973877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.999849319458</t>
+    <t xml:space="preserve">17.3536224365234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3722438812256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9998474121094</t>
   </si>
   <si>
     <t xml:space="preserve">17.0743255615234</t>
@@ -2615,25 +2615,25 @@
     <t xml:space="preserve">16.3481559753418</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3109149932861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1991958618164</t>
+    <t xml:space="preserve">16.3109169006348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.199197769165</t>
   </si>
   <si>
     <t xml:space="preserve">16.6088333129883</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0502395629883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.255054473877</t>
+    <t xml:space="preserve">16.0502376556396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2550563812256</t>
   </si>
   <si>
     <t xml:space="preserve">16.1060981750488</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1674270629883</t>
+    <t xml:space="preserve">17.1674251556396</t>
   </si>
   <si>
     <t xml:space="preserve">18.0053157806396</t>
@@ -2642,7 +2642,7 @@
     <t xml:space="preserve">17.9122161865234</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4653415679932</t>
+    <t xml:space="preserve">17.4653434753418</t>
   </si>
   <si>
     <t xml:space="preserve">17.9494571685791</t>
@@ -2660,7 +2660,7 @@
     <t xml:space="preserve">17.3629341125488</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5025806427002</t>
+    <t xml:space="preserve">17.5025787353516</t>
   </si>
   <si>
     <t xml:space="preserve">17.4560317993164</t>
@@ -2684,7 +2684,7 @@
     <t xml:space="preserve">18.6370983123779</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8282489776611</t>
+    <t xml:space="preserve">18.8282508850098</t>
   </si>
   <si>
     <t xml:space="preserve">19.1149749755859</t>
@@ -2693,7 +2693,7 @@
     <t xml:space="preserve">18.9716129302979</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2105484008789</t>
+    <t xml:space="preserve">19.2105503082275</t>
   </si>
   <si>
     <t xml:space="preserve">20.0707225799561</t>
@@ -2702,7 +2702,7 @@
     <t xml:space="preserve">20.8353214263916</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0264720916748</t>
+    <t xml:space="preserve">21.0264701843262</t>
   </si>
   <si>
     <t xml:space="preserve">20.9308967590332</t>
@@ -2726,7 +2726,7 @@
     <t xml:space="preserve">21.217622756958</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7397480010986</t>
+    <t xml:space="preserve">20.73974609375</t>
   </si>
   <si>
     <t xml:space="preserve">21.1220455169678</t>
@@ -2735,7 +2735,7 @@
     <t xml:space="preserve">19.8795719146729</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7839984893799</t>
+    <t xml:space="preserve">19.7840003967285</t>
   </si>
   <si>
     <t xml:space="preserve">20.3574466705322</t>
@@ -2744,22 +2744,22 @@
     <t xml:space="preserve">19.9751472473145</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6884250640869</t>
+    <t xml:space="preserve">19.6884231567383</t>
   </si>
   <si>
     <t xml:space="preserve">21.3131942749023</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4087715148926</t>
+    <t xml:space="preserve">21.4087696075439</t>
   </si>
   <si>
     <t xml:space="preserve">21.5999221801758</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5043449401855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8866443634033</t>
+    <t xml:space="preserve">21.5043468475342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.886646270752</t>
   </si>
   <si>
     <t xml:space="preserve">22.5556697845459</t>
@@ -2768,10 +2768,10 @@
     <t xml:space="preserve">22.7468185424805</t>
   </si>
   <si>
-    <t xml:space="preserve">22.937967300415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8423938751221</t>
+    <t xml:space="preserve">22.9379692077637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8423919677734</t>
   </si>
   <si>
     <t xml:space="preserve">23.1291179656982</t>
@@ -2783,7 +2783,7 @@
     <t xml:space="preserve">22.0777950286865</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9822216033936</t>
+    <t xml:space="preserve">21.9822196960449</t>
   </si>
   <si>
     <t xml:space="preserve">22.1733722686768</t>
@@ -2792,7 +2792,7 @@
     <t xml:space="preserve">21.6954956054688</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7910709381104</t>
+    <t xml:space="preserve">21.7910690307617</t>
   </si>
   <si>
     <t xml:space="preserve">22.6512451171875</t>
@@ -3009,6 +3009,9 @@
   </si>
   <si>
     <t xml:space="preserve">19.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5499992370605</t>
   </si>
 </sst>
 </file>
@@ -19199,7 +19202,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G610" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -19251,7 +19254,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G612" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -19303,7 +19306,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G614" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -19329,7 +19332,7 @@
         <v>12.75</v>
       </c>
       <c r="G615" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -19355,7 +19358,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G616" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -19407,7 +19410,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G618" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -19433,7 +19436,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G619" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -19459,7 +19462,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G620" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -19485,7 +19488,7 @@
         <v>12.75</v>
       </c>
       <c r="G621" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -19511,7 +19514,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G622" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -19537,7 +19540,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G623" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -19563,7 +19566,7 @@
         <v>13</v>
       </c>
       <c r="G624" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -19589,7 +19592,7 @@
         <v>13</v>
       </c>
       <c r="G625" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -19615,7 +19618,7 @@
         <v>12.75</v>
       </c>
       <c r="G626" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -19641,7 +19644,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G627" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H627" t="s">
         <v>9</v>
@@ -19667,7 +19670,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G628" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H628" t="s">
         <v>9</v>
@@ -19693,7 +19696,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G629" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H629" t="s">
         <v>9</v>
@@ -19719,7 +19722,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G630" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H630" t="s">
         <v>9</v>
@@ -19745,7 +19748,7 @@
         <v>12.75</v>
       </c>
       <c r="G631" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H631" t="s">
         <v>9</v>
@@ -19771,7 +19774,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G632" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H632" t="s">
         <v>9</v>
@@ -19797,7 +19800,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G633" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H633" t="s">
         <v>9</v>
@@ -19823,7 +19826,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G634" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H634" t="s">
         <v>9</v>
@@ -19849,7 +19852,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G635" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H635" t="s">
         <v>9</v>
@@ -19875,7 +19878,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G636" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H636" t="s">
         <v>9</v>
@@ -19901,7 +19904,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G637" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H637" t="s">
         <v>9</v>
@@ -19927,7 +19930,7 @@
         <v>12.25</v>
       </c>
       <c r="G638" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H638" t="s">
         <v>9</v>
@@ -19953,7 +19956,7 @@
         <v>12.25</v>
       </c>
       <c r="G639" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H639" t="s">
         <v>9</v>
@@ -19979,7 +19982,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G640" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H640" t="s">
         <v>9</v>
@@ -20005,7 +20008,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G641" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H641" t="s">
         <v>9</v>
@@ -20031,7 +20034,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G642" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H642" t="s">
         <v>9</v>
@@ -20057,7 +20060,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G643" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H643" t="s">
         <v>9</v>
@@ -20083,7 +20086,7 @@
         <v>12.5</v>
       </c>
       <c r="G644" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H644" t="s">
         <v>9</v>
@@ -20109,7 +20112,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G645" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H645" t="s">
         <v>9</v>
@@ -20135,7 +20138,7 @@
         <v>12.5</v>
       </c>
       <c r="G646" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H646" t="s">
         <v>9</v>
@@ -20161,7 +20164,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G647" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H647" t="s">
         <v>9</v>
@@ -20187,7 +20190,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G648" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H648" t="s">
         <v>9</v>
@@ -20213,7 +20216,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G649" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H649" t="s">
         <v>9</v>
@@ -20239,7 +20242,7 @@
         <v>12.5</v>
       </c>
       <c r="G650" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H650" t="s">
         <v>9</v>
@@ -20265,7 +20268,7 @@
         <v>12.5</v>
       </c>
       <c r="G651" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H651" t="s">
         <v>9</v>
@@ -20291,7 +20294,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G652" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H652" t="s">
         <v>9</v>
@@ -20317,7 +20320,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G653" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H653" t="s">
         <v>9</v>
@@ -20343,7 +20346,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G654" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H654" t="s">
         <v>9</v>
@@ -20369,7 +20372,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G655" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H655" t="s">
         <v>9</v>
@@ -20395,7 +20398,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G656" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H656" t="s">
         <v>9</v>
@@ -20421,7 +20424,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G657" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H657" t="s">
         <v>9</v>
@@ -20447,7 +20450,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G658" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H658" t="s">
         <v>9</v>
@@ -20473,7 +20476,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G659" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H659" t="s">
         <v>9</v>
@@ -20499,7 +20502,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G660" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H660" t="s">
         <v>9</v>
@@ -20525,7 +20528,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G661" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H661" t="s">
         <v>9</v>
@@ -20551,7 +20554,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G662" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H662" t="s">
         <v>9</v>
@@ -20577,7 +20580,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G663" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H663" t="s">
         <v>9</v>
@@ -20603,7 +20606,7 @@
         <v>12.75</v>
       </c>
       <c r="G664" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -20629,7 +20632,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G665" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H665" t="s">
         <v>9</v>
@@ -20655,7 +20658,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G666" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H666" t="s">
         <v>9</v>
@@ -20681,7 +20684,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G667" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H667" t="s">
         <v>9</v>
@@ -20707,7 +20710,7 @@
         <v>12.25</v>
       </c>
       <c r="G668" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H668" t="s">
         <v>9</v>
@@ -20733,7 +20736,7 @@
         <v>12.25</v>
       </c>
       <c r="G669" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H669" t="s">
         <v>9</v>
@@ -20759,7 +20762,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G670" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H670" t="s">
         <v>9</v>
@@ -20785,7 +20788,7 @@
         <v>12.5</v>
       </c>
       <c r="G671" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H671" t="s">
         <v>9</v>
@@ -20811,7 +20814,7 @@
         <v>12.5</v>
       </c>
       <c r="G672" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H672" t="s">
         <v>9</v>
@@ -20837,7 +20840,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G673" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H673" t="s">
         <v>9</v>
@@ -20863,7 +20866,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G674" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H674" t="s">
         <v>9</v>
@@ -20889,7 +20892,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G675" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H675" t="s">
         <v>9</v>
@@ -20915,7 +20918,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G676" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H676" t="s">
         <v>9</v>
@@ -20941,7 +20944,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G677" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H677" t="s">
         <v>9</v>
@@ -20967,7 +20970,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G678" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H678" t="s">
         <v>9</v>
@@ -20993,7 +20996,7 @@
         <v>12.25</v>
       </c>
       <c r="G679" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H679" t="s">
         <v>9</v>
@@ -21019,7 +21022,7 @@
         <v>12.25</v>
       </c>
       <c r="G680" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H680" t="s">
         <v>9</v>
@@ -21045,7 +21048,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G681" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H681" t="s">
         <v>9</v>
@@ -21071,7 +21074,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G682" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H682" t="s">
         <v>9</v>
@@ -21097,7 +21100,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G683" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H683" t="s">
         <v>9</v>
@@ -21123,7 +21126,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G684" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H684" t="s">
         <v>9</v>
@@ -21149,7 +21152,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G685" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H685" t="s">
         <v>9</v>
@@ -21175,7 +21178,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G686" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H686" t="s">
         <v>9</v>
@@ -21201,7 +21204,7 @@
         <v>12.5</v>
       </c>
       <c r="G687" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H687" t="s">
         <v>9</v>
@@ -21227,7 +21230,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G688" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H688" t="s">
         <v>9</v>
@@ -21253,7 +21256,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G689" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H689" t="s">
         <v>9</v>
@@ -21279,7 +21282,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G690" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H690" t="s">
         <v>9</v>
@@ -21305,7 +21308,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G691" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H691" t="s">
         <v>9</v>
@@ -21331,7 +21334,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G692" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H692" t="s">
         <v>9</v>
@@ -21357,7 +21360,7 @@
         <v>12.75</v>
       </c>
       <c r="G693" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H693" t="s">
         <v>9</v>
@@ -21383,7 +21386,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G694" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -21409,7 +21412,7 @@
         <v>13.25</v>
       </c>
       <c r="G695" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H695" t="s">
         <v>9</v>
@@ -21435,7 +21438,7 @@
         <v>13</v>
       </c>
       <c r="G696" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H696" t="s">
         <v>9</v>
@@ -21461,7 +21464,7 @@
         <v>13</v>
       </c>
       <c r="G697" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H697" t="s">
         <v>9</v>
@@ -21487,7 +21490,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G698" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H698" t="s">
         <v>9</v>
@@ -21513,7 +21516,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G699" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H699" t="s">
         <v>9</v>
@@ -21539,7 +21542,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G700" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H700" t="s">
         <v>9</v>
@@ -21565,7 +21568,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G701" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H701" t="s">
         <v>9</v>
@@ -21591,7 +21594,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G702" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H702" t="s">
         <v>9</v>
@@ -21617,7 +21620,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G703" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H703" t="s">
         <v>9</v>
@@ -21643,7 +21646,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G704" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H704" t="s">
         <v>9</v>
@@ -21669,7 +21672,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G705" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H705" t="s">
         <v>9</v>
@@ -21695,7 +21698,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G706" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H706" t="s">
         <v>9</v>
@@ -21721,7 +21724,7 @@
         <v>13.25</v>
       </c>
       <c r="G707" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H707" t="s">
         <v>9</v>
@@ -21747,7 +21750,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G708" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H708" t="s">
         <v>9</v>
@@ -21773,7 +21776,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G709" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H709" t="s">
         <v>9</v>
@@ -21799,7 +21802,7 @@
         <v>13</v>
       </c>
       <c r="G710" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H710" t="s">
         <v>9</v>
@@ -21825,7 +21828,7 @@
         <v>13</v>
       </c>
       <c r="G711" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H711" t="s">
         <v>9</v>
@@ -21851,7 +21854,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G712" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H712" t="s">
         <v>9</v>
@@ -21877,7 +21880,7 @@
         <v>13</v>
       </c>
       <c r="G713" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H713" t="s">
         <v>9</v>
@@ -21903,7 +21906,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G714" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H714" t="s">
         <v>9</v>
@@ -21929,7 +21932,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G715" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H715" t="s">
         <v>9</v>
@@ -21955,7 +21958,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G716" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H716" t="s">
         <v>9</v>
@@ -21981,7 +21984,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G717" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H717" t="s">
         <v>9</v>
@@ -22007,7 +22010,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G718" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H718" t="s">
         <v>9</v>
@@ -22033,7 +22036,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G719" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H719" t="s">
         <v>9</v>
@@ -22059,7 +22062,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G720" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H720" t="s">
         <v>9</v>
@@ -22085,7 +22088,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G721" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H721" t="s">
         <v>9</v>
@@ -22111,7 +22114,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G722" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H722" t="s">
         <v>9</v>
@@ -22137,7 +22140,7 @@
         <v>12.5</v>
       </c